--- a/stock_data.xlsx
+++ b/stock_data.xlsx
@@ -513,16 +513,16 @@
         <v>45902</v>
       </c>
       <c r="B4" t="n">
-        <v>633.8644298326893</v>
+        <v>633.8644906037873</v>
       </c>
       <c r="C4" t="n">
-        <v>636.8373685858147</v>
+        <v>636.8374296419402</v>
       </c>
       <c r="D4" t="n">
-        <v>631.2991262066306</v>
+        <v>631.2991867317828</v>
       </c>
       <c r="E4" t="n">
-        <v>636.61865234375</v>
+        <v>636.6187133789062</v>
       </c>
       <c r="F4" t="n">
         <v>81983500</v>
@@ -553,16 +553,16 @@
         <v>45904</v>
       </c>
       <c r="B6" t="n">
-        <v>640.7449431803722</v>
+        <v>640.7450037735979</v>
       </c>
       <c r="C6" t="n">
-        <v>645.4480098993379</v>
+        <v>645.4480709373178</v>
       </c>
       <c r="D6" t="n">
-        <v>639.8401594892221</v>
+        <v>639.8402199968853</v>
       </c>
       <c r="E6" t="n">
-        <v>645.4181518554688</v>
+        <v>645.418212890625</v>
       </c>
       <c r="F6" t="n">
         <v>65219200</v>
@@ -593,16 +593,16 @@
         <v>45908</v>
       </c>
       <c r="B8" t="n">
-        <v>644.9209975333657</v>
+        <v>644.9210585487652</v>
       </c>
       <c r="C8" t="n">
-        <v>646.1340715853498</v>
+        <v>646.1341327155172</v>
       </c>
       <c r="D8" t="n">
-        <v>643.5389099622073</v>
+        <v>643.5389708468488</v>
       </c>
       <c r="E8" t="n">
-        <v>645.1298217773438</v>
+        <v>645.1298828125</v>
       </c>
       <c r="F8" t="n">
         <v>63133100</v>
@@ -633,16 +633,16 @@
         <v>45910</v>
       </c>
       <c r="B10" t="n">
-        <v>649.8925329397852</v>
+        <v>649.8924717726807</v>
       </c>
       <c r="C10" t="n">
-        <v>650.8172220560821</v>
+        <v>650.817160801947</v>
       </c>
       <c r="D10" t="n">
-        <v>646.9195940128865</v>
+        <v>646.9195331255914</v>
       </c>
       <c r="E10" t="n">
-        <v>648.4906005859375</v>
+        <v>648.4905395507812</v>
       </c>
       <c r="F10" t="n">
         <v>78034500</v>
@@ -673,16 +673,16 @@
         <v>45912</v>
       </c>
       <c r="B12" t="n">
-        <v>653.8498075653706</v>
+        <v>653.8497465125743</v>
       </c>
       <c r="C12" t="n">
-        <v>655.3512060315065</v>
+        <v>655.3511448385181</v>
       </c>
       <c r="D12" t="n">
-        <v>653.1538480823614</v>
+        <v>653.1537870945498</v>
       </c>
       <c r="E12" t="n">
-        <v>653.660888671875</v>
+        <v>653.6608276367188</v>
       </c>
       <c r="F12" t="n">
         <v>72780100</v>
@@ -753,16 +753,16 @@
         <v>45918</v>
       </c>
       <c r="B16" t="n">
-        <v>658.1153912564865</v>
+        <v>658.1153302554297</v>
       </c>
       <c r="C16" t="n">
-        <v>661.0982828700095</v>
+        <v>661.098221592467</v>
       </c>
       <c r="D16" t="n">
-        <v>656.5046346401509</v>
+        <v>656.504573788396</v>
       </c>
       <c r="E16" t="n">
-        <v>658.4832763671875</v>
+        <v>658.4832153320312</v>
       </c>
       <c r="F16" t="n">
         <v>90459200</v>
@@ -2885,7 +2885,7 @@
         <v>689.4299926757812</v>
       </c>
       <c r="F122" t="n">
-        <v>99952100</v>
+        <v>100034000</v>
       </c>
     </row>
     <row r="123">
@@ -2899,13 +2899,13 @@
         <v>690</v>
       </c>
       <c r="D123" t="n">
-        <v>680.3709716796875</v>
+        <v>680.3699951171875</v>
       </c>
       <c r="E123" t="n">
-        <v>682.9299926757812</v>
+        <v>682.3900146484375</v>
       </c>
       <c r="F123" t="n">
-        <v>48215603</v>
+        <v>90421900</v>
       </c>
     </row>
   </sheetData>
@@ -3039,16 +3039,16 @@
         <v>45904</v>
       </c>
       <c r="B6" t="n">
-        <v>237.996365667052</v>
+        <v>237.9963808412042</v>
       </c>
       <c r="C6" t="n">
-        <v>239.4436041167336</v>
+        <v>239.4436193831587</v>
       </c>
       <c r="D6" t="n">
-        <v>236.2896273284533</v>
+        <v>236.2896423937874</v>
       </c>
       <c r="E6" t="n">
-        <v>239.3238372802734</v>
+        <v>239.3238525390625</v>
       </c>
       <c r="F6" t="n">
         <v>47549400</v>
@@ -3159,16 +3159,16 @@
         <v>45912</v>
       </c>
       <c r="B12" t="n">
-        <v>228.7839306820605</v>
+        <v>228.7839456246826</v>
       </c>
       <c r="C12" t="n">
-        <v>234.063860229386</v>
+        <v>234.0638755168574</v>
       </c>
       <c r="D12" t="n">
-        <v>228.584314210114</v>
+        <v>228.5843291396984</v>
       </c>
       <c r="E12" t="n">
-        <v>233.6247100830078</v>
+        <v>233.6247253417969</v>
       </c>
       <c r="F12" t="n">
         <v>55824200</v>
@@ -3479,16 +3479,16 @@
         <v>45936</v>
       </c>
       <c r="B28" t="n">
-        <v>257.499174775338</v>
+        <v>257.4992054474702</v>
       </c>
       <c r="C28" t="n">
-        <v>258.5771371766132</v>
+        <v>258.5771679771474</v>
       </c>
       <c r="D28" t="n">
-        <v>254.5647807987102</v>
+        <v>254.5648111213107</v>
       </c>
       <c r="E28" t="n">
-        <v>256.20166015625</v>
+        <v>256.2016906738281</v>
       </c>
       <c r="F28" t="n">
         <v>44664100</v>
@@ -3499,16 +3499,16 @@
         <v>45937</v>
       </c>
       <c r="B29" t="n">
-        <v>256.3214547692021</v>
+        <v>256.3214394907812</v>
       </c>
       <c r="C29" t="n">
-        <v>256.9103287268919</v>
+        <v>256.9103134133703</v>
       </c>
       <c r="D29" t="n">
-        <v>254.9440751402397</v>
+        <v>254.9440599439195</v>
       </c>
       <c r="E29" t="n">
-        <v>255.9920959472656</v>
+        <v>255.9920806884766</v>
       </c>
       <c r="F29" t="n">
         <v>31955800</v>
@@ -3519,16 +3519,16 @@
         <v>45938</v>
       </c>
       <c r="B30" t="n">
-        <v>256.0320127996357</v>
+        <v>256.0319824641754</v>
       </c>
       <c r="C30" t="n">
-        <v>258.0282082133661</v>
+        <v>258.0281776413904</v>
       </c>
       <c r="D30" t="n">
-        <v>255.6227890846779</v>
+        <v>255.6227587977037</v>
       </c>
       <c r="E30" t="n">
-        <v>257.569091796875</v>
+        <v>257.5690612792969</v>
       </c>
       <c r="F30" t="n">
         <v>36496900</v>
@@ -3619,16 +3619,16 @@
         <v>45945</v>
       </c>
       <c r="B35" t="n">
-        <v>249.0153854047813</v>
+        <v>249.0153701368122</v>
       </c>
       <c r="C35" t="n">
-        <v>251.3409547309234</v>
+        <v>251.3409393203658</v>
       </c>
       <c r="D35" t="n">
-        <v>246.9992239099275</v>
+        <v>246.999208765576</v>
       </c>
       <c r="E35" t="n">
-        <v>248.8656616210938</v>
+        <v>248.8656463623047</v>
       </c>
       <c r="F35" t="n">
         <v>33893600</v>
@@ -3639,16 +3639,16 @@
         <v>45946</v>
       </c>
       <c r="B36" t="n">
-        <v>247.7777444808599</v>
+        <v>247.7777291727393</v>
       </c>
       <c r="C36" t="n">
-        <v>248.5662349323926</v>
+        <v>248.5662195755578</v>
       </c>
       <c r="D36" t="n">
-        <v>244.6636846503341</v>
+        <v>244.6636695346054</v>
       </c>
       <c r="E36" t="n">
-        <v>246.9792633056641</v>
+        <v>246.979248046875</v>
       </c>
       <c r="F36" t="n">
         <v>39777000</v>
@@ -3699,16 +3699,16 @@
         <v>45951</v>
       </c>
       <c r="B39" t="n">
-        <v>261.3817895915523</v>
+        <v>261.3818200057694</v>
       </c>
       <c r="C39" t="n">
-        <v>264.7853058703715</v>
+        <v>264.7853366806196</v>
       </c>
       <c r="D39" t="n">
-        <v>261.3318664386604</v>
+        <v>261.3318968470685</v>
       </c>
       <c r="E39" t="n">
-        <v>262.2700805664062</v>
+        <v>262.2701110839844</v>
       </c>
       <c r="F39" t="n">
         <v>46695900</v>
@@ -3759,16 +3759,16 @@
         <v>45954</v>
       </c>
       <c r="B42" t="n">
-        <v>260.6931337605782</v>
+        <v>260.6931034322695</v>
       </c>
       <c r="C42" t="n">
-        <v>263.6275433572314</v>
+        <v>263.6275126875418</v>
       </c>
       <c r="D42" t="n">
-        <v>258.6869476899315</v>
+        <v>258.6869175950168</v>
       </c>
       <c r="E42" t="n">
-        <v>262.3200378417969</v>
+        <v>262.3200073242188</v>
       </c>
       <c r="F42" t="n">
         <v>38253700</v>
@@ -5371,7 +5371,7 @@
         <v>264.5799865722656</v>
       </c>
       <c r="F122" t="n">
-        <v>42044900</v>
+        <v>42070500</v>
       </c>
     </row>
     <row r="123">
@@ -5382,16 +5382,16 @@
         <v>263.489990234375</v>
       </c>
       <c r="C123" t="n">
-        <v>268.9299011230469</v>
+        <v>269.4299926757812</v>
       </c>
       <c r="D123" t="n">
-        <v>263.3810119628906</v>
+        <v>263.3800048828125</v>
       </c>
       <c r="E123" t="n">
-        <v>268.7040100097656</v>
+        <v>266.1799926757812</v>
       </c>
       <c r="F123" t="n">
-        <v>17837923</v>
+        <v>37266000</v>
       </c>
     </row>
   </sheetData>
@@ -7857,7 +7857,7 @@
         <v>397.2300109863281</v>
       </c>
       <c r="F122" t="n">
-        <v>33960000</v>
+        <v>34015200</v>
       </c>
     </row>
     <row r="123">
@@ -7865,19 +7865,19 @@
         <v>46076</v>
       </c>
       <c r="B123" t="n">
-        <v>395.1900024414062</v>
+        <v>395</v>
       </c>
       <c r="C123" t="n">
-        <v>395.3099975585938</v>
+        <v>395.3599853515625</v>
       </c>
       <c r="D123" t="n">
-        <v>385.1000061035156</v>
+        <v>383.1000061035156</v>
       </c>
       <c r="E123" t="n">
-        <v>387.0549926757812</v>
+        <v>384.4700012207031</v>
       </c>
       <c r="F123" t="n">
-        <v>24476560</v>
+        <v>43133000</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data.xlsx
+++ b/stock_data.xlsx
@@ -1,8 +1,26 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPY" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSFT" sheetId="3" state="visible" r:id="rId3"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -42,15 +60,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -410,4 +425,7522 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F124"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B2" t="n">
+        <v>655.7760789419195</v>
+      </c>
+      <c r="C2" t="n">
+        <v>658.619871988132</v>
+      </c>
+      <c r="D2" t="n">
+        <v>654.1553026157394</v>
+      </c>
+      <c r="E2" t="n">
+        <v>658.072998046875</v>
+      </c>
+      <c r="F2" t="n">
+        <v>69179200</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B3" t="n">
+        <v>660.5985670660314</v>
+      </c>
+      <c r="C3" t="n">
+        <v>661.5134019828115</v>
+      </c>
+      <c r="D3" t="n">
+        <v>658.112721358766</v>
+      </c>
+      <c r="E3" t="n">
+        <v>659.9224243164062</v>
+      </c>
+      <c r="F3" t="n">
+        <v>73499000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B4" t="n">
+        <v>659.1766647693167</v>
+      </c>
+      <c r="C4" t="n">
+        <v>662.8756347075731</v>
+      </c>
+      <c r="D4" t="n">
+        <v>657.8641309647478</v>
+      </c>
+      <c r="E4" t="n">
+        <v>662.4082641601562</v>
+      </c>
+      <c r="F4" t="n">
+        <v>86288000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B5" t="n">
+        <v>659.4153308150761</v>
+      </c>
+      <c r="C5" t="n">
+        <v>665.5802405756418</v>
+      </c>
+      <c r="D5" t="n">
+        <v>659.3059681646932</v>
+      </c>
+      <c r="E5" t="n">
+        <v>664.6654663085938</v>
+      </c>
+      <c r="F5" t="n">
+        <v>72545400</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B6" t="n">
+        <v>666.6540464714482</v>
+      </c>
+      <c r="C6" t="n">
+        <v>666.7733621981591</v>
+      </c>
+      <c r="D6" t="n">
+        <v>663.004842335434</v>
+      </c>
+      <c r="E6" t="n">
+        <v>665.4309692382812</v>
+      </c>
+      <c r="F6" t="n">
+        <v>56896000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B7" t="n">
+        <v>666.1966948783695</v>
+      </c>
+      <c r="C7" t="n">
+        <v>668.8714672806448</v>
+      </c>
+      <c r="D7" t="n">
+        <v>664.377038831869</v>
+      </c>
+      <c r="E7" t="n">
+        <v>665.421142578125</v>
+      </c>
+      <c r="F7" t="n">
+        <v>70494400</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B8" t="n">
+        <v>667.8174482099862</v>
+      </c>
+      <c r="C8" t="n">
+        <v>668.7024238148077</v>
+      </c>
+      <c r="D8" t="n">
+        <v>665.6697043011241</v>
+      </c>
+      <c r="E8" t="n">
+        <v>667.8074951171875</v>
+      </c>
+      <c r="F8" t="n">
+        <v>54623300</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B9" t="n">
+        <v>668.7322238208072</v>
+      </c>
+      <c r="C9" t="n">
+        <v>669.1796881705657</v>
+      </c>
+      <c r="D9" t="n">
+        <v>663.8898014056139</v>
+      </c>
+      <c r="E9" t="n">
+        <v>665.3316040039062</v>
+      </c>
+      <c r="F9" t="n">
+        <v>72020100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B10" t="n">
+        <v>666.4552183740389</v>
+      </c>
+      <c r="C10" t="n">
+        <v>669.3984814701651</v>
+      </c>
+      <c r="D10" t="n">
+        <v>665.6299006256374</v>
+      </c>
+      <c r="E10" t="n">
+        <v>669.2990112304688</v>
+      </c>
+      <c r="F10" t="n">
+        <v>60702200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B11" t="n">
+        <v>669.7166839203261</v>
+      </c>
+      <c r="C11" t="n">
+        <v>670.1243359074817</v>
+      </c>
+      <c r="D11" t="n">
+        <v>665.4211353124821</v>
+      </c>
+      <c r="E11" t="n">
+        <v>667.3600463867188</v>
+      </c>
+      <c r="F11" t="n">
+        <v>66501900</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B12" t="n">
+        <v>668.324542434099</v>
+      </c>
+      <c r="C12" t="n">
+        <v>670.1342452495495</v>
+      </c>
+      <c r="D12" t="n">
+        <v>649.1437803121401</v>
+      </c>
+      <c r="E12" t="n">
+        <v>649.32275390625</v>
+      </c>
+      <c r="F12" t="n">
+        <v>159422600</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B13" t="n">
+        <v>656.9095884512618</v>
+      </c>
+      <c r="C13" t="n">
+        <v>661.3642043859337</v>
+      </c>
+      <c r="D13" t="n">
+        <v>656.0345659370097</v>
+      </c>
+      <c r="E13" t="n">
+        <v>659.2860107421875</v>
+      </c>
+      <c r="F13" t="n">
+        <v>79560500</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B14" t="n">
+        <v>653.4492417720955</v>
+      </c>
+      <c r="C14" t="n">
+        <v>662.0602448848334</v>
+      </c>
+      <c r="D14" t="n">
+        <v>649.4718888267987</v>
+      </c>
+      <c r="E14" t="n">
+        <v>658.4805908203125</v>
+      </c>
+      <c r="F14" t="n">
+        <v>88779600</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B15" t="n">
+        <v>663.0446741742268</v>
+      </c>
+      <c r="C15" t="n">
+        <v>666.4353410824248</v>
+      </c>
+      <c r="D15" t="n">
+        <v>655.1993304017814</v>
+      </c>
+      <c r="E15" t="n">
+        <v>661.4039916992188</v>
+      </c>
+      <c r="F15" t="n">
+        <v>81702600</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B16" t="n">
+        <v>663.0446615126489</v>
+      </c>
+      <c r="C16" t="n">
+        <v>664.9239754340409</v>
+      </c>
+      <c r="D16" t="n">
+        <v>653.3896149312258</v>
+      </c>
+      <c r="E16" t="n">
+        <v>656.899658203125</v>
+      </c>
+      <c r="F16" t="n">
+        <v>110563300</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B17" t="n">
+        <v>655.7660892614911</v>
+      </c>
+      <c r="C17" t="n">
+        <v>661.9906565438909</v>
+      </c>
+      <c r="D17" t="n">
+        <v>654.4138037793879</v>
+      </c>
+      <c r="E17" t="n">
+        <v>660.62841796875</v>
+      </c>
+      <c r="F17" t="n">
+        <v>96500900</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B18" t="n">
+        <v>663.5418206897375</v>
+      </c>
+      <c r="C18" t="n">
+        <v>668.4041493887289</v>
+      </c>
+      <c r="D18" t="n">
+        <v>663.4921159142255</v>
+      </c>
+      <c r="E18" t="n">
+        <v>667.499267578125</v>
+      </c>
+      <c r="F18" t="n">
+        <v>60493400</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B19" t="n">
+        <v>667.6384328159621</v>
+      </c>
+      <c r="C19" t="n">
+        <v>669.1796448635298</v>
+      </c>
+      <c r="D19" t="n">
+        <v>666.1866772188026</v>
+      </c>
+      <c r="E19" t="n">
+        <v>667.4892578125</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56249000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B20" t="n">
+        <v>668.1953369980629</v>
+      </c>
+      <c r="C20" t="n">
+        <v>668.1953369980629</v>
+      </c>
+      <c r="D20" t="n">
+        <v>659.5445816579371</v>
+      </c>
+      <c r="E20" t="n">
+        <v>664.0191040039062</v>
+      </c>
+      <c r="F20" t="n">
+        <v>80564000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B21" t="n">
+        <v>664.3372592841532</v>
+      </c>
+      <c r="C21" t="n">
+        <v>668.9012985038863</v>
+      </c>
+      <c r="D21" t="n">
+        <v>664.019063764971</v>
+      </c>
+      <c r="E21" t="n">
+        <v>667.9566650390625</v>
+      </c>
+      <c r="F21" t="n">
+        <v>65604500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B22" t="n">
+        <v>672.6300829996666</v>
+      </c>
+      <c r="C22" t="n">
+        <v>674.628651928334</v>
+      </c>
+      <c r="D22" t="n">
+        <v>671.8246714345047</v>
+      </c>
+      <c r="E22" t="n">
+        <v>673.4155883789062</v>
+      </c>
+      <c r="F22" t="n">
+        <v>74356500</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B23" t="n">
+        <v>678.8645527756448</v>
+      </c>
+      <c r="C23" t="n">
+        <v>681.658640907831</v>
+      </c>
+      <c r="D23" t="n">
+        <v>678.2580209918731</v>
+      </c>
+      <c r="E23" t="n">
+        <v>681.3603515625</v>
+      </c>
+      <c r="F23" t="n">
+        <v>63339800</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B24" t="n">
+        <v>683.1600908523567</v>
+      </c>
+      <c r="C24" t="n">
+        <v>685.0095454543999</v>
+      </c>
+      <c r="D24" t="n">
+        <v>680.9526890414517</v>
+      </c>
+      <c r="E24" t="n">
+        <v>683.1700439453125</v>
+      </c>
+      <c r="F24" t="n">
+        <v>61738100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B25" t="n">
+        <v>684.8205950917289</v>
+      </c>
+      <c r="C25" t="n">
+        <v>685.795087823854</v>
+      </c>
+      <c r="D25" t="n">
+        <v>679.0037407351697</v>
+      </c>
+      <c r="E25" t="n">
+        <v>683.4981689453125</v>
+      </c>
+      <c r="F25" t="n">
+        <v>85657100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B26" t="n">
+        <v>680.0279207971732</v>
+      </c>
+      <c r="C26" t="n">
+        <v>682.0563488815194</v>
+      </c>
+      <c r="D26" t="n">
+        <v>675.98095703125</v>
+      </c>
+      <c r="E26" t="n">
+        <v>675.98095703125</v>
+      </c>
+      <c r="F26" t="n">
+        <v>76335800</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B27" t="n">
+        <v>681.1614729090464</v>
+      </c>
+      <c r="C27" t="n">
+        <v>681.2012852815519</v>
+      </c>
+      <c r="D27" t="n">
+        <v>675.3943230278239</v>
+      </c>
+      <c r="E27" t="n">
+        <v>678.1983642578125</v>
+      </c>
+      <c r="F27" t="n">
+        <v>87164100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B28" t="n">
+        <v>681.7878948104295</v>
+      </c>
+      <c r="C28" t="n">
+        <v>681.9171636388411</v>
+      </c>
+      <c r="D28" t="n">
+        <v>676.0903560257897</v>
+      </c>
+      <c r="E28" t="n">
+        <v>679.4711303710938</v>
+      </c>
+      <c r="F28" t="n">
+        <v>57315000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B29" t="n">
+        <v>672.2820616639051</v>
+      </c>
+      <c r="C29" t="n">
+        <v>676.1103005794487</v>
+      </c>
+      <c r="D29" t="n">
+        <v>670.7607556049009</v>
+      </c>
+      <c r="E29" t="n">
+        <v>671.4169921875</v>
+      </c>
+      <c r="F29" t="n">
+        <v>78427000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B30" t="n">
+        <v>671.1583975728993</v>
+      </c>
+      <c r="C30" t="n">
+        <v>677.0051112074705</v>
+      </c>
+      <c r="D30" t="n">
+        <v>670.3529860359731</v>
+      </c>
+      <c r="E30" t="n">
+        <v>673.7437133789062</v>
+      </c>
+      <c r="F30" t="n">
+        <v>74402400</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B31" t="n">
+        <v>672.6399897028363</v>
+      </c>
+      <c r="C31" t="n">
+        <v>673.5448715272548</v>
+      </c>
+      <c r="D31" t="n">
+        <v>664.9338680034818</v>
+      </c>
+      <c r="E31" t="n">
+        <v>666.514892578125</v>
+      </c>
+      <c r="F31" t="n">
+        <v>85035300</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B32" t="n">
+        <v>664.1284090392404</v>
+      </c>
+      <c r="C32" t="n">
+        <v>667.2805048704689</v>
+      </c>
+      <c r="D32" t="n">
+        <v>657.4663915648358</v>
+      </c>
+      <c r="E32" t="n">
+        <v>667.1710815429688</v>
+      </c>
+      <c r="F32" t="n">
+        <v>100592400</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B33" t="n">
+        <v>673.4056760856186</v>
+      </c>
+      <c r="C33" t="n">
+        <v>678.317709828293</v>
+      </c>
+      <c r="D33" t="n">
+        <v>671.2082272333661</v>
+      </c>
+      <c r="E33" t="n">
+        <v>677.5819091796875</v>
+      </c>
+      <c r="F33" t="n">
+        <v>75842900</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B34" t="n">
+        <v>676.1002762110339</v>
+      </c>
+      <c r="C34" t="n">
+        <v>679.6997756663966</v>
+      </c>
+      <c r="D34" t="n">
+        <v>674.8871520395073</v>
+      </c>
+      <c r="E34" t="n">
+        <v>679.1329956054688</v>
+      </c>
+      <c r="F34" t="n">
+        <v>58953400</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B35" t="n">
+        <v>680.9128544582501</v>
+      </c>
+      <c r="C35" t="n">
+        <v>681.081935653801</v>
+      </c>
+      <c r="D35" t="n">
+        <v>677.0946296424269</v>
+      </c>
+      <c r="E35" t="n">
+        <v>679.5108642578125</v>
+      </c>
+      <c r="F35" t="n">
+        <v>62312500</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B36" t="n">
+        <v>676.6471697129602</v>
+      </c>
+      <c r="C36" t="n">
+        <v>677.0051169124795</v>
+      </c>
+      <c r="D36" t="n">
+        <v>666.7236935366629</v>
+      </c>
+      <c r="E36" t="n">
+        <v>668.2350463867188</v>
+      </c>
+      <c r="F36" t="n">
+        <v>103457800</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B37" t="n">
+        <v>661.6128286383953</v>
+      </c>
+      <c r="C37" t="n">
+        <v>671.8345948923219</v>
+      </c>
+      <c r="D37" t="n">
+        <v>659.5147893727298</v>
+      </c>
+      <c r="E37" t="n">
+        <v>668.125732421875</v>
+      </c>
+      <c r="F37" t="n">
+        <v>96846700</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B38" t="n">
+        <v>665.9083353081996</v>
+      </c>
+      <c r="C38" t="n">
+        <v>669.8956413839408</v>
+      </c>
+      <c r="D38" t="n">
+        <v>658.4209391867944</v>
+      </c>
+      <c r="E38" t="n">
+        <v>661.901123046875</v>
+      </c>
+      <c r="F38" t="n">
+        <v>90456100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B39" t="n">
+        <v>658.351356546523</v>
+      </c>
+      <c r="C39" t="n">
+        <v>661.3542775984923</v>
+      </c>
+      <c r="D39" t="n">
+        <v>652.1466953365565</v>
+      </c>
+      <c r="E39" t="n">
+        <v>656.3428344726562</v>
+      </c>
+      <c r="F39" t="n">
+        <v>114467500</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B40" t="n">
+        <v>657.0389163187169</v>
+      </c>
+      <c r="C40" t="n">
+        <v>663.561773390439</v>
+      </c>
+      <c r="D40" t="n">
+        <v>655.020380360944</v>
+      </c>
+      <c r="E40" t="n">
+        <v>658.87841796875</v>
+      </c>
+      <c r="F40" t="n">
+        <v>94703000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B41" t="n">
+        <v>669.1001291109939</v>
+      </c>
+      <c r="C41" t="n">
+        <v>671.7351497651099</v>
+      </c>
+      <c r="D41" t="n">
+        <v>648.1991802397498</v>
+      </c>
+      <c r="E41" t="n">
+        <v>648.8355712890625</v>
+      </c>
+      <c r="F41" t="n">
+        <v>165293500</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B42" t="n">
+        <v>651.3412595795126</v>
+      </c>
+      <c r="C42" t="n">
+        <v>660.7874729698119</v>
+      </c>
+      <c r="D42" t="n">
+        <v>647.1650267848305</v>
+      </c>
+      <c r="E42" t="n">
+        <v>655.2987670898438</v>
+      </c>
+      <c r="F42" t="n">
+        <v>123956200</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B43" t="n">
+        <v>658.9380055466532</v>
+      </c>
+      <c r="C43" t="n">
+        <v>666.2662734630499</v>
+      </c>
+      <c r="D43" t="n">
+        <v>657.8442577670318</v>
+      </c>
+      <c r="E43" t="n">
+        <v>664.9437866210938</v>
+      </c>
+      <c r="F43" t="n">
+        <v>80437900</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B44" t="n">
+        <v>664.8443455838128</v>
+      </c>
+      <c r="C44" t="n">
+        <v>672.3814460202411</v>
+      </c>
+      <c r="D44" t="n">
+        <v>660.7178178396566</v>
+      </c>
+      <c r="E44" t="n">
+        <v>671.1981811523438</v>
+      </c>
+      <c r="F44" t="n">
+        <v>81077100</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B45" t="n">
+        <v>673.7934667684052</v>
+      </c>
+      <c r="C45" t="n">
+        <v>677.8404309302599</v>
+      </c>
+      <c r="D45" t="n">
+        <v>672.8885849296569</v>
+      </c>
+      <c r="E45" t="n">
+        <v>675.8318481445312</v>
+      </c>
+      <c r="F45" t="n">
+        <v>71879600</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B46" t="n">
+        <v>677.0051081523229</v>
+      </c>
+      <c r="C46" t="n">
+        <v>679.7991961322198</v>
+      </c>
+      <c r="D46" t="n">
+        <v>676.6471609574353</v>
+      </c>
+      <c r="E46" t="n">
+        <v>679.5208129882812</v>
+      </c>
+      <c r="F46" t="n">
+        <v>49212000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B47" t="n">
+        <v>674.9667623359846</v>
+      </c>
+      <c r="C47" t="n">
+        <v>679.1230890446475</v>
+      </c>
+      <c r="D47" t="n">
+        <v>674.8971513739515</v>
+      </c>
+      <c r="E47" t="n">
+        <v>676.4185180664062</v>
+      </c>
+      <c r="F47" t="n">
+        <v>61201200</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B48" t="n">
+        <v>678.0591325179204</v>
+      </c>
+      <c r="C48" t="n">
+        <v>679.9483994968172</v>
+      </c>
+      <c r="D48" t="n">
+        <v>675.4838303983408</v>
+      </c>
+      <c r="E48" t="n">
+        <v>677.67138671875</v>
+      </c>
+      <c r="F48" t="n">
+        <v>62953800</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B49" t="n">
+        <v>676.7167950740063</v>
+      </c>
+      <c r="C49" t="n">
+        <v>681.0321891246488</v>
+      </c>
+      <c r="D49" t="n">
+        <v>675.8417725523884</v>
+      </c>
+      <c r="E49" t="n">
+        <v>680.0180053710938</v>
+      </c>
+      <c r="F49" t="n">
+        <v>57238500</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B50" t="n">
+        <v>681.4199577792665</v>
+      </c>
+      <c r="C50" t="n">
+        <v>681.4895687361658</v>
+      </c>
+      <c r="D50" t="n">
+        <v>677.4824173401821</v>
+      </c>
+      <c r="E50" t="n">
+        <v>680.51513671875</v>
+      </c>
+      <c r="F50" t="n">
+        <v>61970300</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B51" t="n">
+        <v>681.5890143183475</v>
+      </c>
+      <c r="C51" t="n">
+        <v>684.4925257185774</v>
+      </c>
+      <c r="D51" t="n">
+        <v>680.7040993957534</v>
+      </c>
+      <c r="E51" t="n">
+        <v>681.8078002929688</v>
+      </c>
+      <c r="F51" t="n">
+        <v>79241000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B52" t="n">
+        <v>682.7027235077143</v>
+      </c>
+      <c r="C52" t="n">
+        <v>682.7524282821314</v>
+      </c>
+      <c r="D52" t="n">
+        <v>677.7111260885928</v>
+      </c>
+      <c r="E52" t="n">
+        <v>679.7594604492188</v>
+      </c>
+      <c r="F52" t="n">
+        <v>55231500</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B53" t="n">
+        <v>679.2821528162136</v>
+      </c>
+      <c r="C53" t="n">
+        <v>681.5094606319436</v>
+      </c>
+      <c r="D53" t="n">
+        <v>678.7253258622812</v>
+      </c>
+      <c r="E53" t="n">
+        <v>679.1727294921875</v>
+      </c>
+      <c r="F53" t="n">
+        <v>58310100</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B54" t="n">
+        <v>678.6955405173951</v>
+      </c>
+      <c r="C54" t="n">
+        <v>685.0692222502689</v>
+      </c>
+      <c r="D54" t="n">
+        <v>677.4526176554032</v>
+      </c>
+      <c r="E54" t="n">
+        <v>683.6771850585938</v>
+      </c>
+      <c r="F54" t="n">
+        <v>85671300</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B55" t="n">
+        <v>681.2609148661827</v>
+      </c>
+      <c r="C55" t="n">
+        <v>685.3476304583654</v>
+      </c>
+      <c r="D55" t="n">
+        <v>678.3076987410943</v>
+      </c>
+      <c r="E55" t="n">
+        <v>685.26806640625</v>
+      </c>
+      <c r="F55" t="n">
+        <v>86173700</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B56" t="n">
+        <v>684.2737056052856</v>
+      </c>
+      <c r="C56" t="n">
+        <v>684.9797075791527</v>
+      </c>
+      <c r="D56" t="n">
+        <v>675.3246617594549</v>
+      </c>
+      <c r="E56" t="n">
+        <v>677.9000244140625</v>
+      </c>
+      <c r="F56" t="n">
+        <v>113160300</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B57" t="n">
+        <v>681.8574988128718</v>
+      </c>
+      <c r="C57" t="n">
+        <v>681.8774049984522</v>
+      </c>
+      <c r="D57" t="n">
+        <v>675.4042533093998</v>
+      </c>
+      <c r="E57" t="n">
+        <v>676.8758544921875</v>
+      </c>
+      <c r="F57" t="n">
+        <v>90811000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B58" t="n">
+        <v>675.3843754405706</v>
+      </c>
+      <c r="C58" t="n">
+        <v>677.2239376857725</v>
+      </c>
+      <c r="D58" t="n">
+        <v>671.1584377196804</v>
+      </c>
+      <c r="E58" t="n">
+        <v>675.0264282226562</v>
+      </c>
+      <c r="F58" t="n">
+        <v>122030600</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B59" t="n">
+        <v>676.0406154817738</v>
+      </c>
+      <c r="C59" t="n">
+        <v>676.5874893555698</v>
+      </c>
+      <c r="D59" t="n">
+        <v>667.3998140691156</v>
+      </c>
+      <c r="E59" t="n">
+        <v>667.5986938476562</v>
+      </c>
+      <c r="F59" t="n">
+        <v>110625200</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B60" t="n">
+        <v>673.7635606688432</v>
+      </c>
+      <c r="C60" t="n">
+        <v>676.8857972779194</v>
+      </c>
+      <c r="D60" t="n">
+        <v>671.0788959983324</v>
+      </c>
+      <c r="E60" t="n">
+        <v>672.6399536132812</v>
+      </c>
+      <c r="F60" t="n">
+        <v>108650100</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B61" t="n">
+        <v>674.747283458469</v>
+      </c>
+      <c r="C61" t="n">
+        <v>679.2350273728672</v>
+      </c>
+      <c r="D61" t="n">
+        <v>674.6275542880097</v>
+      </c>
+      <c r="E61" t="n">
+        <v>678.7363891601562</v>
+      </c>
+      <c r="F61" t="n">
+        <v>103599500</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B62" t="n">
+        <v>682.0772531068674</v>
+      </c>
+      <c r="C62" t="n">
+        <v>683.4933686131409</v>
+      </c>
+      <c r="D62" t="n">
+        <v>678.7364013691785</v>
+      </c>
+      <c r="E62" t="n">
+        <v>682.96484375</v>
+      </c>
+      <c r="F62" t="n">
+        <v>69556700</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B63" t="n">
+        <v>682.0572680421344</v>
+      </c>
+      <c r="C63" t="n">
+        <v>686.325640311278</v>
+      </c>
+      <c r="D63" t="n">
+        <v>682.0074163952171</v>
+      </c>
+      <c r="E63" t="n">
+        <v>686.0863037109375</v>
+      </c>
+      <c r="F63" t="n">
+        <v>64840000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B64" t="n">
+        <v>686.0763204450832</v>
+      </c>
+      <c r="C64" t="n">
+        <v>688.9484813838191</v>
+      </c>
+      <c r="D64" t="n">
+        <v>685.9267046355759</v>
+      </c>
+      <c r="E64" t="n">
+        <v>688.4996948242188</v>
+      </c>
+      <c r="F64" t="n">
+        <v>39445600</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B65" t="n">
+        <v>688.758988861415</v>
+      </c>
+      <c r="C65" t="n">
+        <v>689.7761694005526</v>
+      </c>
+      <c r="D65" t="n">
+        <v>687.392725060237</v>
+      </c>
+      <c r="E65" t="n">
+        <v>688.4298706054688</v>
+      </c>
+      <c r="F65" t="n">
+        <v>41613300</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B66" t="n">
+        <v>685.6674092439482</v>
+      </c>
+      <c r="C66" t="n">
+        <v>687.322922191004</v>
+      </c>
+      <c r="D66" t="n">
+        <v>684.2014421207446</v>
+      </c>
+      <c r="E66" t="n">
+        <v>685.9765625</v>
+      </c>
+      <c r="F66" t="n">
+        <v>62559500</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B67" t="n">
+        <v>685.5777200962995</v>
+      </c>
+      <c r="C67" t="n">
+        <v>686.6846823672308</v>
+      </c>
+      <c r="D67" t="n">
+        <v>684.7100944386586</v>
+      </c>
+      <c r="E67" t="n">
+        <v>685.138916015625</v>
+      </c>
+      <c r="F67" t="n">
+        <v>47160700</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B68" t="n">
+        <v>685.2685588951464</v>
+      </c>
+      <c r="C68" t="n">
+        <v>685.4879304984822</v>
+      </c>
+      <c r="D68" t="n">
+        <v>679.8533550408816</v>
+      </c>
+      <c r="E68" t="n">
+        <v>680.062744140625</v>
+      </c>
+      <c r="F68" t="n">
+        <v>74144800</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B69" t="n">
+        <v>683.8424472770359</v>
+      </c>
+      <c r="C69" t="n">
+        <v>684.999261161205</v>
+      </c>
+      <c r="D69" t="n">
+        <v>677.9684744567207</v>
+      </c>
+      <c r="E69" t="n">
+        <v>681.309326171875</v>
+      </c>
+      <c r="F69" t="n">
+        <v>89377200</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B70" t="n">
+        <v>684.6701449336617</v>
+      </c>
+      <c r="C70" t="n">
+        <v>687.5522884526621</v>
+      </c>
+      <c r="D70" t="n">
+        <v>684.5106074856512</v>
+      </c>
+      <c r="E70" t="n">
+        <v>685.846923828125</v>
+      </c>
+      <c r="F70" t="n">
+        <v>71927200</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B71" t="n">
+        <v>686.0563439630641</v>
+      </c>
+      <c r="C71" t="n">
+        <v>690.4344019511112</v>
+      </c>
+      <c r="D71" t="n">
+        <v>685.9067890249802</v>
+      </c>
+      <c r="E71" t="n">
+        <v>689.92578125</v>
+      </c>
+      <c r="F71" t="n">
+        <v>69273800</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B72" t="n">
+        <v>690.3047811958188</v>
+      </c>
+      <c r="C72" t="n">
+        <v>692.0699799720542</v>
+      </c>
+      <c r="D72" t="n">
+        <v>687.4426026835383</v>
+      </c>
+      <c r="E72" t="n">
+        <v>687.701904296875</v>
+      </c>
+      <c r="F72" t="n">
+        <v>75588300</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B73" t="n">
+        <v>686.9439569075789</v>
+      </c>
+      <c r="C73" t="n">
+        <v>688.7390423054183</v>
+      </c>
+      <c r="D73" t="n">
+        <v>685.6175622141362</v>
+      </c>
+      <c r="E73" t="n">
+        <v>687.632080078125</v>
+      </c>
+      <c r="F73" t="n">
+        <v>64019200</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B74" t="n">
+        <v>688.7489932725086</v>
+      </c>
+      <c r="C74" t="n">
+        <v>693.4162394407576</v>
+      </c>
+      <c r="D74" t="n">
+        <v>687.3029303433501</v>
+      </c>
+      <c r="E74" t="n">
+        <v>692.1796264648438</v>
+      </c>
+      <c r="F74" t="n">
+        <v>80125500</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B75" t="n">
+        <v>688.7988836287034</v>
+      </c>
+      <c r="C75" t="n">
+        <v>694.1941832506386</v>
+      </c>
+      <c r="D75" t="n">
+        <v>688.7490319805348</v>
+      </c>
+      <c r="E75" t="n">
+        <v>693.2666625976562</v>
+      </c>
+      <c r="F75" t="n">
+        <v>63976000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B76" t="n">
+        <v>693.595779418591</v>
+      </c>
+      <c r="C76" t="n">
+        <v>694.1941818021349</v>
+      </c>
+      <c r="D76" t="n">
+        <v>689.467040360938</v>
+      </c>
+      <c r="E76" t="n">
+        <v>691.8804931640625</v>
+      </c>
+      <c r="F76" t="n">
+        <v>78309700</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B77" t="n">
+        <v>689.1180078469732</v>
+      </c>
+      <c r="C77" t="n">
+        <v>689.8360176539858</v>
+      </c>
+      <c r="D77" t="n">
+        <v>684.1714948792828</v>
+      </c>
+      <c r="E77" t="n">
+        <v>688.479736328125</v>
+      </c>
+      <c r="F77" t="n">
+        <v>94676700</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B78" t="n">
+        <v>692.6782853429351</v>
+      </c>
+      <c r="C78" t="n">
+        <v>693.5558934557131</v>
+      </c>
+      <c r="D78" t="n">
+        <v>689.3673203481677</v>
+      </c>
+      <c r="E78" t="n">
+        <v>690.3546142578125</v>
+      </c>
+      <c r="F78" t="n">
+        <v>77862000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B79" t="n">
+        <v>691.7707369284135</v>
+      </c>
+      <c r="C79" t="n">
+        <v>692.3591568004221</v>
+      </c>
+      <c r="D79" t="n">
+        <v>688.22043529661</v>
+      </c>
+      <c r="E79" t="n">
+        <v>689.7761840820312</v>
+      </c>
+      <c r="F79" t="n">
+        <v>79289200</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B80" t="n">
+        <v>679.6338820353151</v>
+      </c>
+      <c r="C80" t="n">
+        <v>682.9049778344743</v>
+      </c>
+      <c r="D80" t="n">
+        <v>674.7272992054969</v>
+      </c>
+      <c r="E80" t="n">
+        <v>675.7345581054688</v>
+      </c>
+      <c r="F80" t="n">
+        <v>111623300</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B81" t="n">
+        <v>677.7989248999835</v>
+      </c>
+      <c r="C81" t="n">
+        <v>686.8641332264262</v>
+      </c>
+      <c r="D81" t="n">
+        <v>676.2830453044572</v>
+      </c>
+      <c r="E81" t="n">
+        <v>683.5332641601562</v>
+      </c>
+      <c r="F81" t="n">
+        <v>127844500</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B82" t="n">
+        <v>687.9711412752974</v>
+      </c>
+      <c r="C82" t="n">
+        <v>689.2476843606095</v>
+      </c>
+      <c r="D82" t="n">
+        <v>685.0491285530771</v>
+      </c>
+      <c r="E82" t="n">
+        <v>687.103515625</v>
+      </c>
+      <c r="F82" t="n">
+        <v>77112200</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B83" t="n">
+        <v>686.2757685331861</v>
+      </c>
+      <c r="C83" t="n">
+        <v>689.0781127396581</v>
+      </c>
+      <c r="D83" t="n">
+        <v>685.2884137823622</v>
+      </c>
+      <c r="E83" t="n">
+        <v>687.352783203125</v>
+      </c>
+      <c r="F83" t="n">
+        <v>63059600</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B84" t="n">
+        <v>688.609372319757</v>
+      </c>
+      <c r="C84" t="n">
+        <v>692.2394730275811</v>
+      </c>
+      <c r="D84" t="n">
+        <v>688.0409174669724</v>
+      </c>
+      <c r="E84" t="n">
+        <v>690.84326171875</v>
+      </c>
+      <c r="F84" t="n">
+        <v>60473800</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B85" t="n">
+        <v>692.2893344912051</v>
+      </c>
+      <c r="C85" t="n">
+        <v>694.6329705879123</v>
+      </c>
+      <c r="D85" t="n">
+        <v>691.6810104865692</v>
+      </c>
+      <c r="E85" t="n">
+        <v>693.5957641601562</v>
+      </c>
+      <c r="F85" t="n">
+        <v>55506100</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B86" t="n">
+        <v>695.1515053497095</v>
+      </c>
+      <c r="C86" t="n">
+        <v>695.9393926651097</v>
+      </c>
+      <c r="D86" t="n">
+        <v>692.0499903412962</v>
+      </c>
+      <c r="E86" t="n">
+        <v>693.5259399414062</v>
+      </c>
+      <c r="F86" t="n">
+        <v>61172200</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B87" t="n">
+        <v>694.4933553961189</v>
+      </c>
+      <c r="C87" t="n">
+        <v>695.1615135683285</v>
+      </c>
+      <c r="D87" t="n">
+        <v>682.9648421722587</v>
+      </c>
+      <c r="E87" t="n">
+        <v>692.1497192382812</v>
+      </c>
+      <c r="F87" t="n">
+        <v>97486200</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B88" t="n">
+        <v>689.9058246991844</v>
+      </c>
+      <c r="C88" t="n">
+        <v>692.3192774332931</v>
+      </c>
+      <c r="D88" t="n">
+        <v>685.2485609149509</v>
+      </c>
+      <c r="E88" t="n">
+        <v>690.0853271484375</v>
+      </c>
+      <c r="F88" t="n">
+        <v>101835100</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B89" t="n">
+        <v>687.7019133171445</v>
+      </c>
+      <c r="C89" t="n">
+        <v>695.0318708971434</v>
+      </c>
+      <c r="D89" t="n">
+        <v>687.5423149981101</v>
+      </c>
+      <c r="E89" t="n">
+        <v>693.5159912109375</v>
+      </c>
+      <c r="F89" t="n">
+        <v>79286500</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B90" t="n">
+        <v>694.3138377504575</v>
+      </c>
+      <c r="C90" t="n">
+        <v>695.0617950648859</v>
+      </c>
+      <c r="D90" t="n">
+        <v>682.1670182684101</v>
+      </c>
+      <c r="E90" t="n">
+        <v>687.6520385742188</v>
+      </c>
+      <c r="F90" t="n">
+        <v>107904600</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B91" t="n">
+        <v>688.4697490630058</v>
+      </c>
+      <c r="C91" t="n">
+        <v>689.5667896413613</v>
+      </c>
+      <c r="D91" t="n">
+        <v>679.9031787408285</v>
+      </c>
+      <c r="E91" t="n">
+        <v>684.3211059570312</v>
+      </c>
+      <c r="F91" t="n">
+        <v>105204600</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B92" t="n">
+        <v>679.0854402743204</v>
+      </c>
+      <c r="C92" t="n">
+        <v>681.8279505601881</v>
+      </c>
+      <c r="D92" t="n">
+        <v>673.9494421186707</v>
+      </c>
+      <c r="E92" t="n">
+        <v>675.7744750976562</v>
+      </c>
+      <c r="F92" t="n">
+        <v>113610800</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B93" t="n">
+        <v>679.6039887472712</v>
+      </c>
+      <c r="C93" t="n">
+        <v>690.4244132010324</v>
+      </c>
+      <c r="D93" t="n">
+        <v>678.995603890688</v>
+      </c>
+      <c r="E93" t="n">
+        <v>688.739013671875</v>
+      </c>
+      <c r="F93" t="n">
+        <v>89127600</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B94" t="n">
+        <v>687.5423060693106</v>
+      </c>
+      <c r="C94" t="n">
+        <v>693.9747512796714</v>
+      </c>
+      <c r="D94" t="n">
+        <v>686.4652913399738</v>
+      </c>
+      <c r="E94" t="n">
+        <v>692.0599975585938</v>
+      </c>
+      <c r="F94" t="n">
+        <v>73885200</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B95" t="n">
+        <v>693.0572335194393</v>
+      </c>
+      <c r="C95" t="n">
+        <v>694.64286887948</v>
+      </c>
+      <c r="D95" t="n">
+        <v>689.7761552680904</v>
+      </c>
+      <c r="E95" t="n">
+        <v>690.2349243164062</v>
+      </c>
+      <c r="F95" t="n">
+        <v>65185700</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B96" t="n">
+        <v>694.4933668556342</v>
+      </c>
+      <c r="C96" t="n">
+        <v>695.2413241987686</v>
+      </c>
+      <c r="D96" t="n">
+        <v>687.3029816841566</v>
+      </c>
+      <c r="E96" t="n">
+        <v>690.075439453125</v>
+      </c>
+      <c r="F96" t="n">
+        <v>76353900</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B97" t="n">
+        <v>692.3491972008484</v>
+      </c>
+      <c r="C97" t="n">
+        <v>693.4561594586687</v>
+      </c>
+      <c r="D97" t="n">
+        <v>678.5169776231163</v>
+      </c>
+      <c r="E97" t="n">
+        <v>679.41455078125</v>
+      </c>
+      <c r="F97" t="n">
+        <v>118829000</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B98" t="n">
+        <v>679.833354327075</v>
+      </c>
+      <c r="C98" t="n">
+        <v>684.410879804094</v>
+      </c>
+      <c r="D98" t="n">
+        <v>675.6747287653898</v>
+      </c>
+      <c r="E98" t="n">
+        <v>679.8931884765625</v>
+      </c>
+      <c r="F98" t="n">
+        <v>96267500</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B99" t="n">
+        <v>678.287593220413</v>
+      </c>
+      <c r="C99" t="n">
+        <v>683.074507822494</v>
+      </c>
+      <c r="D99" t="n">
+        <v>673.9394826742099</v>
+      </c>
+      <c r="E99" t="n">
+        <v>680.9901733398438</v>
+      </c>
+      <c r="F99" t="n">
+        <v>81354700</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B100" t="n">
+        <v>682.157061237011</v>
+      </c>
+      <c r="C100" t="n">
+        <v>687.2730943282486</v>
+      </c>
+      <c r="D100" t="n">
+        <v>680.9702998190471</v>
+      </c>
+      <c r="E100" t="n">
+        <v>684.4208374023438</v>
+      </c>
+      <c r="F100" t="n">
+        <v>73570300</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B101" t="n">
+        <v>681.9775120282383</v>
+      </c>
+      <c r="C101" t="n">
+        <v>684.311104689823</v>
+      </c>
+      <c r="D101" t="n">
+        <v>679.6937101433548</v>
+      </c>
+      <c r="E101" t="n">
+        <v>682.61572265625</v>
+      </c>
+      <c r="F101" t="n">
+        <v>58649400</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B102" t="n">
+        <v>680.4616860592505</v>
+      </c>
+      <c r="C102" t="n">
+        <v>688.1805961724377</v>
+      </c>
+      <c r="D102" t="n">
+        <v>679.8732661615737</v>
+      </c>
+      <c r="E102" t="n">
+        <v>687.5523071289062</v>
+      </c>
+      <c r="F102" t="n">
+        <v>100034000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B103" t="n">
+        <v>685.9566804858357</v>
+      </c>
+      <c r="C103" t="n">
+        <v>688.1207533479937</v>
+      </c>
+      <c r="D103" t="n">
+        <v>678.5169762252317</v>
+      </c>
+      <c r="E103" t="n">
+        <v>680.531494140625</v>
+      </c>
+      <c r="F103" t="n">
+        <v>90558100</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B104" t="n">
+        <v>680.0427976196477</v>
+      </c>
+      <c r="C104" t="n">
+        <v>686.4751816677359</v>
+      </c>
+      <c r="D104" t="n">
+        <v>678.1479481229125</v>
+      </c>
+      <c r="E104" t="n">
+        <v>685.4779052734375</v>
+      </c>
+      <c r="F104" t="n">
+        <v>73798700</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B105" t="n">
+        <v>688.3002642742074</v>
+      </c>
+      <c r="C105" t="n">
+        <v>691.7907319065998</v>
+      </c>
+      <c r="D105" t="n">
+        <v>688.2204651135966</v>
+      </c>
+      <c r="E105" t="n">
+        <v>691.26220703125</v>
+      </c>
+      <c r="F105" t="n">
+        <v>56369500</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B106" t="n">
+        <v>691.391808867856</v>
+      </c>
+      <c r="C106" t="n">
+        <v>691.4117130049051</v>
+      </c>
+      <c r="D106" t="n">
+        <v>682.4860770890911</v>
+      </c>
+      <c r="E106" t="n">
+        <v>687.422607421875</v>
+      </c>
+      <c r="F106" t="n">
+        <v>71671000</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B107" t="n">
+        <v>681.2295779636313</v>
+      </c>
+      <c r="C107" t="n">
+        <v>684.9892686841309</v>
+      </c>
+      <c r="D107" t="n">
+        <v>679.7835149777827</v>
+      </c>
+      <c r="E107" t="n">
+        <v>684.1216430664062</v>
+      </c>
+      <c r="F107" t="n">
+        <v>83308900</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B108" t="n">
+        <v>676.8515442239554</v>
+      </c>
+      <c r="C108" t="n">
+        <v>686.744509644098</v>
+      </c>
+      <c r="D108" t="n">
+        <v>676.1734035367807</v>
+      </c>
+      <c r="E108" t="n">
+        <v>684.5106201171875</v>
+      </c>
+      <c r="F108" t="n">
+        <v>87477200</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B109" t="n">
+        <v>673.221445388408</v>
+      </c>
+      <c r="C109" t="n">
+        <v>680.7508704958498</v>
+      </c>
+      <c r="D109" t="n">
+        <v>667.8361281509542</v>
+      </c>
+      <c r="E109" t="n">
+        <v>678.4771118164062</v>
+      </c>
+      <c r="F109" t="n">
+        <v>105003100</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B110" t="n">
+        <v>679.7735096903759</v>
+      </c>
+      <c r="C110" t="n">
+        <v>685.2186606854194</v>
+      </c>
+      <c r="D110" t="n">
+        <v>677.7689744100875</v>
+      </c>
+      <c r="E110" t="n">
+        <v>683.2639770507812</v>
+      </c>
+      <c r="F110" t="n">
+        <v>79182200</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B111" t="n">
+        <v>680.2223290726917</v>
+      </c>
+      <c r="C111" t="n">
+        <v>683.6629449535216</v>
+      </c>
+      <c r="D111" t="n">
+        <v>673.7699188745959</v>
+      </c>
+      <c r="E111" t="n">
+        <v>679.4544067382812</v>
+      </c>
+      <c r="F111" t="n">
+        <v>106606500</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B112" t="n">
+        <v>671.5758690877306</v>
+      </c>
+      <c r="C112" t="n">
+        <v>674.2685275228549</v>
+      </c>
+      <c r="D112" t="n">
+        <v>667.9358467743081</v>
+      </c>
+      <c r="E112" t="n">
+        <v>670.5487060546875</v>
+      </c>
+      <c r="F112" t="n">
+        <v>100687000</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B113" t="n">
+        <v>664.5750801817165</v>
+      </c>
+      <c r="C113" t="n">
+        <v>678.0681991431876</v>
+      </c>
+      <c r="D113" t="n">
+        <v>660.5859743093405</v>
+      </c>
+      <c r="E113" t="n">
+        <v>676.4227294921875</v>
+      </c>
+      <c r="F113" t="n">
+        <v>102667700</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B114" t="n">
+        <v>675.87413967305</v>
+      </c>
+      <c r="C114" t="n">
+        <v>681.4987932365287</v>
+      </c>
+      <c r="D114" t="n">
+        <v>672.9222404542279</v>
+      </c>
+      <c r="E114" t="n">
+        <v>675.3356323242188</v>
+      </c>
+      <c r="F114" t="n">
+        <v>81505300</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B115" t="n">
+        <v>675.7345715953234</v>
+      </c>
+      <c r="C115" t="n">
+        <v>678.2277626375325</v>
+      </c>
+      <c r="D115" t="n">
+        <v>671.5061293267642</v>
+      </c>
+      <c r="E115" t="n">
+        <v>674.4879760742188</v>
+      </c>
+      <c r="F115" t="n">
+        <v>68441700</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B116" t="n">
+        <v>669.3319958917509</v>
+      </c>
+      <c r="C116" t="n">
+        <v>669.8207124533001</v>
+      </c>
+      <c r="D116" t="n">
+        <v>664.0564256954588</v>
+      </c>
+      <c r="E116" t="n">
+        <v>664.2459106445312</v>
+      </c>
+      <c r="F116" t="n">
+        <v>108882200</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B117" t="n">
+        <v>667.4472371497842</v>
+      </c>
+      <c r="C117" t="n">
+        <v>670.5088831921612</v>
+      </c>
+      <c r="D117" t="n">
+        <v>659.5587462493693</v>
+      </c>
+      <c r="E117" t="n">
+        <v>660.4862060546875</v>
+      </c>
+      <c r="F117" t="n">
+        <v>97200200</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B118" t="n">
+        <v>666.5596317087426</v>
+      </c>
+      <c r="C118" t="n">
+        <v>670.239584206393</v>
+      </c>
+      <c r="D118" t="n">
+        <v>665.3030536555561</v>
+      </c>
+      <c r="E118" t="n">
+        <v>667.2078857421875</v>
+      </c>
+      <c r="F118" t="n">
+        <v>82023100</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B119" t="n">
+        <v>670.5586914524959</v>
+      </c>
+      <c r="C119" t="n">
+        <v>672.60309589337</v>
+      </c>
+      <c r="D119" t="n">
+        <v>667.8760155087483</v>
+      </c>
+      <c r="E119" t="n">
+        <v>668.9630126953125</v>
+      </c>
+      <c r="F119" t="n">
+        <v>87128000</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B120" t="n">
+        <v>666.5396583763402</v>
+      </c>
+      <c r="C120" t="n">
+        <v>667.8959397089973</v>
+      </c>
+      <c r="D120" t="n">
+        <v>659.3892034355257</v>
+      </c>
+      <c r="E120" t="n">
+        <v>659.6285400390625</v>
+      </c>
+      <c r="F120" t="n">
+        <v>82062600</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B121" t="n">
+        <v>655.1806813207687</v>
+      </c>
+      <c r="C121" t="n">
+        <v>661.1743225351036</v>
+      </c>
+      <c r="D121" t="n">
+        <v>653.3855958813168</v>
+      </c>
+      <c r="E121" t="n">
+        <v>658.0029907226562</v>
+      </c>
+      <c r="F121" t="n">
+        <v>111272500</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B122" t="n">
+        <v>656.510009765625</v>
+      </c>
+      <c r="C122" t="n">
+        <v>656.6900024414062</v>
+      </c>
+      <c r="D122" t="n">
+        <v>644.719970703125</v>
+      </c>
+      <c r="E122" t="n">
+        <v>648.5700073242188</v>
+      </c>
+      <c r="F122" t="n">
+        <v>163617500</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B123" t="n">
+        <v>658.0700073242188</v>
+      </c>
+      <c r="C123" t="n">
+        <v>662.6199951171875</v>
+      </c>
+      <c r="D123" t="n">
+        <v>653.9400024414062</v>
+      </c>
+      <c r="E123" t="n">
+        <v>655.3800048828125</v>
+      </c>
+      <c r="F123" t="n">
+        <v>134802700</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B124" t="n">
+        <v>651.3200073242188</v>
+      </c>
+      <c r="C124" t="n">
+        <v>657.030029296875</v>
+      </c>
+      <c r="D124" t="n">
+        <v>649.8800048828125</v>
+      </c>
+      <c r="E124" t="n">
+        <v>653.1799926757812</v>
+      </c>
+      <c r="F124" t="n">
+        <v>96120900</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F124"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B2" t="n">
+        <v>253.6166009653311</v>
+      </c>
+      <c r="C2" t="n">
+        <v>257.1099424925133</v>
+      </c>
+      <c r="D2" t="n">
+        <v>253.2972024297037</v>
+      </c>
+      <c r="E2" t="n">
+        <v>254.9740142822266</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46076300</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B3" t="n">
+        <v>254.0757261912774</v>
+      </c>
+      <c r="C3" t="n">
+        <v>254.5148915782133</v>
+      </c>
+      <c r="D3" t="n">
+        <v>252.5286718435753</v>
+      </c>
+      <c r="E3" t="n">
+        <v>253.9459686279297</v>
+      </c>
+      <c r="F3" t="n">
+        <v>40127700</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B4" t="n">
+        <v>254.3751575512532</v>
+      </c>
+      <c r="C4" t="n">
+        <v>255.4331385813304</v>
+      </c>
+      <c r="D4" t="n">
+        <v>252.6284867333586</v>
+      </c>
+      <c r="E4" t="n">
+        <v>254.1455993652344</v>
+      </c>
+      <c r="F4" t="n">
+        <v>37704300</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B5" t="n">
+        <v>254.5548113531499</v>
+      </c>
+      <c r="C5" t="n">
+        <v>258.2976926733417</v>
+      </c>
+      <c r="D5" t="n">
+        <v>254.4450200053069</v>
+      </c>
+      <c r="E5" t="n">
+        <v>254.9640350341797</v>
+      </c>
+      <c r="F5" t="n">
+        <v>48713900</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B6" t="n">
+        <v>256.0918666719083</v>
+      </c>
+      <c r="C6" t="n">
+        <v>257.6888289105058</v>
+      </c>
+      <c r="D6" t="n">
+        <v>253.666496834403</v>
+      </c>
+      <c r="E6" t="n">
+        <v>256.6408386230469</v>
+      </c>
+      <c r="F6" t="n">
+        <v>42630200</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B7" t="n">
+        <v>254.1855263026656</v>
+      </c>
+      <c r="C7" t="n">
+        <v>258.7468246365968</v>
+      </c>
+      <c r="D7" t="n">
+        <v>253.4668947774022</v>
+      </c>
+      <c r="E7" t="n">
+        <v>257.5291442871094</v>
+      </c>
+      <c r="F7" t="n">
+        <v>49155600</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B8" t="n">
+        <v>257.499174775338</v>
+      </c>
+      <c r="C8" t="n">
+        <v>258.5771371766132</v>
+      </c>
+      <c r="D8" t="n">
+        <v>254.5647807987102</v>
+      </c>
+      <c r="E8" t="n">
+        <v>256.20166015625</v>
+      </c>
+      <c r="F8" t="n">
+        <v>44664100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B9" t="n">
+        <v>256.3214547692021</v>
+      </c>
+      <c r="C9" t="n">
+        <v>256.9103287268919</v>
+      </c>
+      <c r="D9" t="n">
+        <v>254.9440751402397</v>
+      </c>
+      <c r="E9" t="n">
+        <v>255.9920959472656</v>
+      </c>
+      <c r="F9" t="n">
+        <v>31955800</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B10" t="n">
+        <v>256.0320127996357</v>
+      </c>
+      <c r="C10" t="n">
+        <v>258.0282082133661</v>
+      </c>
+      <c r="D10" t="n">
+        <v>255.6227890846779</v>
+      </c>
+      <c r="E10" t="n">
+        <v>257.569091796875</v>
+      </c>
+      <c r="F10" t="n">
+        <v>36496900</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B11" t="n">
+        <v>257.3195337882977</v>
+      </c>
+      <c r="C11" t="n">
+        <v>257.5091747646147</v>
+      </c>
+      <c r="D11" t="n">
+        <v>252.6584199331141</v>
+      </c>
+      <c r="E11" t="n">
+        <v>253.5567016601562</v>
+      </c>
+      <c r="F11" t="n">
+        <v>38322000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B12" t="n">
+        <v>254.4550078501572</v>
+      </c>
+      <c r="C12" t="n">
+        <v>255.8922708493858</v>
+      </c>
+      <c r="D12" t="n">
+        <v>243.535817529099</v>
+      </c>
+      <c r="E12" t="n">
+        <v>244.8034057617188</v>
+      </c>
+      <c r="F12" t="n">
+        <v>61999100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B13" t="n">
+        <v>248.9055871417832</v>
+      </c>
+      <c r="C13" t="n">
+        <v>249.2149949644775</v>
+      </c>
+      <c r="D13" t="n">
+        <v>245.0928469569099</v>
+      </c>
+      <c r="E13" t="n">
+        <v>247.1888580322266</v>
+      </c>
+      <c r="F13" t="n">
+        <v>38142900</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B14" t="n">
+        <v>246.1308726626428</v>
+      </c>
+      <c r="C14" t="n">
+        <v>248.3765922481423</v>
+      </c>
+      <c r="D14" t="n">
+        <v>244.2344780970313</v>
+      </c>
+      <c r="E14" t="n">
+        <v>247.2986450195312</v>
+      </c>
+      <c r="F14" t="n">
+        <v>35478000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B15" t="n">
+        <v>249.0153854047813</v>
+      </c>
+      <c r="C15" t="n">
+        <v>251.3409547309234</v>
+      </c>
+      <c r="D15" t="n">
+        <v>246.9992239099275</v>
+      </c>
+      <c r="E15" t="n">
+        <v>248.8656616210938</v>
+      </c>
+      <c r="F15" t="n">
+        <v>33893600</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B16" t="n">
+        <v>247.7777444808599</v>
+      </c>
+      <c r="C16" t="n">
+        <v>248.5662349323926</v>
+      </c>
+      <c r="D16" t="n">
+        <v>244.6636846503341</v>
+      </c>
+      <c r="E16" t="n">
+        <v>246.9792633056641</v>
+      </c>
+      <c r="F16" t="n">
+        <v>39777000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B17" t="n">
+        <v>247.5481624372989</v>
+      </c>
+      <c r="C17" t="n">
+        <v>252.8979659970864</v>
+      </c>
+      <c r="D17" t="n">
+        <v>246.7995892632415</v>
+      </c>
+      <c r="E17" t="n">
+        <v>251.8100280761719</v>
+      </c>
+      <c r="F17" t="n">
+        <v>49147000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B18" t="n">
+        <v>255.4032084113237</v>
+      </c>
+      <c r="C18" t="n">
+        <v>263.8770629877272</v>
+      </c>
+      <c r="D18" t="n">
+        <v>255.143708503654</v>
+      </c>
+      <c r="E18" t="n">
+        <v>261.7411193847656</v>
+      </c>
+      <c r="F18" t="n">
+        <v>90483000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B19" t="n">
+        <v>261.3817895915523</v>
+      </c>
+      <c r="C19" t="n">
+        <v>264.7853058703715</v>
+      </c>
+      <c r="D19" t="n">
+        <v>261.3318664386604</v>
+      </c>
+      <c r="E19" t="n">
+        <v>262.2700805664062</v>
+      </c>
+      <c r="F19" t="n">
+        <v>46695900</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B20" t="n">
+        <v>262.1503352574342</v>
+      </c>
+      <c r="C20" t="n">
+        <v>262.349966966352</v>
+      </c>
+      <c r="D20" t="n">
+        <v>254.9440691826199</v>
+      </c>
+      <c r="E20" t="n">
+        <v>257.9583435058594</v>
+      </c>
+      <c r="F20" t="n">
+        <v>45015300</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B21" t="n">
+        <v>259.4454820834593</v>
+      </c>
+      <c r="C21" t="n">
+        <v>260.1241811137136</v>
+      </c>
+      <c r="D21" t="n">
+        <v>257.5191611036844</v>
+      </c>
+      <c r="E21" t="n">
+        <v>259.0861511230469</v>
+      </c>
+      <c r="F21" t="n">
+        <v>32754900</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B22" t="n">
+        <v>260.6931337605782</v>
+      </c>
+      <c r="C22" t="n">
+        <v>263.6275433572314</v>
+      </c>
+      <c r="D22" t="n">
+        <v>258.6869476899315</v>
+      </c>
+      <c r="E22" t="n">
+        <v>262.3200378417969</v>
+      </c>
+      <c r="F22" t="n">
+        <v>38253700</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B23" t="n">
+        <v>264.376098228409</v>
+      </c>
+      <c r="C23" t="n">
+        <v>268.60802232244</v>
+      </c>
+      <c r="D23" t="n">
+        <v>264.1465248140549</v>
+      </c>
+      <c r="E23" t="n">
+        <v>268.2986145019531</v>
+      </c>
+      <c r="F23" t="n">
+        <v>44888200</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B24" t="n">
+        <v>268.4782600095115</v>
+      </c>
+      <c r="C24" t="n">
+        <v>269.3765722048576</v>
+      </c>
+      <c r="D24" t="n">
+        <v>267.6398616921066</v>
+      </c>
+      <c r="E24" t="n">
+        <v>268.4882507324219</v>
+      </c>
+      <c r="F24" t="n">
+        <v>41534800</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B25" t="n">
+        <v>268.7677057947778</v>
+      </c>
+      <c r="C25" t="n">
+        <v>270.8936584399069</v>
+      </c>
+      <c r="D25" t="n">
+        <v>266.6018207191691</v>
+      </c>
+      <c r="E25" t="n">
+        <v>269.1869201660156</v>
+      </c>
+      <c r="F25" t="n">
+        <v>51086700</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B26" t="n">
+        <v>271.4725408872279</v>
+      </c>
+      <c r="C26" t="n">
+        <v>273.6184749716116</v>
+      </c>
+      <c r="D26" t="n">
+        <v>267.969239224885</v>
+      </c>
+      <c r="E26" t="n">
+        <v>270.8836669921875</v>
+      </c>
+      <c r="F26" t="n">
+        <v>69886500</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B27" t="n">
+        <v>276.4630533049319</v>
+      </c>
+      <c r="C27" t="n">
+        <v>276.7924425807819</v>
+      </c>
+      <c r="D27" t="n">
+        <v>268.647962249571</v>
+      </c>
+      <c r="E27" t="n">
+        <v>269.8556518554688</v>
+      </c>
+      <c r="F27" t="n">
+        <v>86167100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B28" t="n">
+        <v>269.9055662700252</v>
+      </c>
+      <c r="C28" t="n">
+        <v>270.3347409275427</v>
+      </c>
+      <c r="D28" t="n">
+        <v>265.7434858777505</v>
+      </c>
+      <c r="E28" t="n">
+        <v>268.5381469726562</v>
+      </c>
+      <c r="F28" t="n">
+        <v>50194600</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B29" t="n">
+        <v>267.8195068636227</v>
+      </c>
+      <c r="C29" t="n">
+        <v>270.9734988318123</v>
+      </c>
+      <c r="D29" t="n">
+        <v>267.1108661194202</v>
+      </c>
+      <c r="E29" t="n">
+        <v>269.5262756347656</v>
+      </c>
+      <c r="F29" t="n">
+        <v>49274800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B30" t="n">
+        <v>268.0989800730272</v>
+      </c>
+      <c r="C30" t="n">
+        <v>271.1831284425123</v>
+      </c>
+      <c r="D30" t="n">
+        <v>266.4221834255846</v>
+      </c>
+      <c r="E30" t="n">
+        <v>269.6260986328125</v>
+      </c>
+      <c r="F30" t="n">
+        <v>43683100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B31" t="n">
+        <v>267.3803770260164</v>
+      </c>
+      <c r="C31" t="n">
+        <v>272.8798740142925</v>
+      </c>
+      <c r="D31" t="n">
+        <v>267.3803770260164</v>
+      </c>
+      <c r="E31" t="n">
+        <v>269.2567749023438</v>
+      </c>
+      <c r="F31" t="n">
+        <v>51204000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B32" t="n">
+        <v>269.2867154149515</v>
+      </c>
+      <c r="C32" t="n">
+        <v>271.7719991063764</v>
+      </c>
+      <c r="D32" t="n">
+        <v>266.2624809601513</v>
+      </c>
+      <c r="E32" t="n">
+        <v>267.9592590332031</v>
+      </c>
+      <c r="F32" t="n">
+        <v>48227400</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B33" t="n">
+        <v>268.7085692371889</v>
+      </c>
+      <c r="C33" t="n">
+        <v>273.4741297822401</v>
+      </c>
+      <c r="D33" t="n">
+        <v>267.2099714283653</v>
+      </c>
+      <c r="E33" t="n">
+        <v>269.1781311035156</v>
+      </c>
+      <c r="F33" t="n">
+        <v>41312400</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B34" t="n">
+        <v>269.5577590596557</v>
+      </c>
+      <c r="C34" t="n">
+        <v>275.6520624227355</v>
+      </c>
+      <c r="D34" t="n">
+        <v>269.5477586519058</v>
+      </c>
+      <c r="E34" t="n">
+        <v>274.99267578125</v>
+      </c>
+      <c r="F34" t="n">
+        <v>46208300</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B35" t="n">
+        <v>274.7429239716485</v>
+      </c>
+      <c r="C35" t="n">
+        <v>275.4722525277038</v>
+      </c>
+      <c r="D35" t="n">
+        <v>271.4460210796085</v>
+      </c>
+      <c r="E35" t="n">
+        <v>273.21435546875</v>
+      </c>
+      <c r="F35" t="n">
+        <v>48398000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B36" t="n">
+        <v>273.8537435218178</v>
+      </c>
+      <c r="C36" t="n">
+        <v>276.4413491841305</v>
+      </c>
+      <c r="D36" t="n">
+        <v>271.8356428219928</v>
+      </c>
+      <c r="E36" t="n">
+        <v>272.6948547363281</v>
+      </c>
+      <c r="F36" t="n">
+        <v>49602800</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B37" t="n">
+        <v>270.7965900477885</v>
+      </c>
+      <c r="C37" t="n">
+        <v>275.702003472256</v>
+      </c>
+      <c r="D37" t="n">
+        <v>269.3479639093673</v>
+      </c>
+      <c r="E37" t="n">
+        <v>272.1553344726562</v>
+      </c>
+      <c r="F37" t="n">
+        <v>47431300</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B38" t="n">
+        <v>268.5687054184609</v>
+      </c>
+      <c r="C38" t="n">
+        <v>270.2371271729127</v>
+      </c>
+      <c r="D38" t="n">
+        <v>265.4815977121726</v>
+      </c>
+      <c r="E38" t="n">
+        <v>267.2099609375</v>
+      </c>
+      <c r="F38" t="n">
+        <v>45018300</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B39" t="n">
+        <v>269.7376065335732</v>
+      </c>
+      <c r="C39" t="n">
+        <v>270.4569347049811</v>
+      </c>
+      <c r="D39" t="n">
+        <v>265.0719890725528</v>
+      </c>
+      <c r="E39" t="n">
+        <v>267.1900024414062</v>
+      </c>
+      <c r="F39" t="n">
+        <v>45677300</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B40" t="n">
+        <v>265.2817633125939</v>
+      </c>
+      <c r="C40" t="n">
+        <v>271.9555110777923</v>
+      </c>
+      <c r="D40" t="n">
+        <v>265.2517925781922</v>
+      </c>
+      <c r="E40" t="n">
+        <v>268.3089294433594</v>
+      </c>
+      <c r="F40" t="n">
+        <v>40424500</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B41" t="n">
+        <v>270.5768036466949</v>
+      </c>
+      <c r="C41" t="n">
+        <v>275.1725094767523</v>
+      </c>
+      <c r="D41" t="n">
+        <v>265.6714205454633</v>
+      </c>
+      <c r="E41" t="n">
+        <v>266.0010986328125</v>
+      </c>
+      <c r="F41" t="n">
+        <v>45823600</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B42" t="n">
+        <v>265.7013768088059</v>
+      </c>
+      <c r="C42" t="n">
+        <v>273.0744516711978</v>
+      </c>
+      <c r="D42" t="n">
+        <v>265.4216397990326</v>
+      </c>
+      <c r="E42" t="n">
+        <v>271.2361755371094</v>
+      </c>
+      <c r="F42" t="n">
+        <v>59030800</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B43" t="n">
+        <v>270.6467521230613</v>
+      </c>
+      <c r="C43" t="n">
+        <v>276.7410558404627</v>
+      </c>
+      <c r="D43" t="n">
+        <v>270.6467521230613</v>
+      </c>
+      <c r="E43" t="n">
+        <v>275.6620788574219</v>
+      </c>
+      <c r="F43" t="n">
+        <v>65585800</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B44" t="n">
+        <v>275.012667049666</v>
+      </c>
+      <c r="C44" t="n">
+        <v>280.1179060838009</v>
+      </c>
+      <c r="D44" t="n">
+        <v>274.9926967216935</v>
+      </c>
+      <c r="E44" t="n">
+        <v>276.7110900878906</v>
+      </c>
+      <c r="F44" t="n">
+        <v>46914200</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B45" t="n">
+        <v>276.7010825487222</v>
+      </c>
+      <c r="C45" t="n">
+        <v>279.2686873678638</v>
+      </c>
+      <c r="D45" t="n">
+        <v>276.3714044558947</v>
+      </c>
+      <c r="E45" t="n">
+        <v>277.29052734375</v>
+      </c>
+      <c r="F45" t="n">
+        <v>33431400</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B46" t="n">
+        <v>277.0008150112318</v>
+      </c>
+      <c r="C46" t="n">
+        <v>278.7391786268174</v>
+      </c>
+      <c r="D46" t="n">
+        <v>275.7319827496524</v>
+      </c>
+      <c r="E46" t="n">
+        <v>278.5893249511719</v>
+      </c>
+      <c r="F46" t="n">
+        <v>20135600</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B47" t="n">
+        <v>277.7501195744996</v>
+      </c>
+      <c r="C47" t="n">
+        <v>283.1550658399818</v>
+      </c>
+      <c r="D47" t="n">
+        <v>275.881872572025</v>
+      </c>
+      <c r="E47" t="n">
+        <v>282.8353576660156</v>
+      </c>
+      <c r="F47" t="n">
+        <v>46587700</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B48" t="n">
+        <v>282.7354345985028</v>
+      </c>
+      <c r="C48" t="n">
+        <v>287.1313151163589</v>
+      </c>
+      <c r="D48" t="n">
+        <v>282.3657853749787</v>
+      </c>
+      <c r="E48" t="n">
+        <v>285.9224548339844</v>
+      </c>
+      <c r="F48" t="n">
+        <v>53669500</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B49" t="n">
+        <v>285.9324708384744</v>
+      </c>
+      <c r="C49" t="n">
+        <v>288.3501915351014</v>
+      </c>
+      <c r="D49" t="n">
+        <v>283.0351573834178</v>
+      </c>
+      <c r="E49" t="n">
+        <v>283.8843688964844</v>
+      </c>
+      <c r="F49" t="n">
+        <v>43538700</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B50" t="n">
+        <v>283.8344068650217</v>
+      </c>
+      <c r="C50" t="n">
+        <v>284.4638227692578</v>
+      </c>
+      <c r="D50" t="n">
+        <v>278.3295482939282</v>
+      </c>
+      <c r="E50" t="n">
+        <v>280.4375915527344</v>
+      </c>
+      <c r="F50" t="n">
+        <v>43989100</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B51" t="n">
+        <v>280.2777430659675</v>
+      </c>
+      <c r="C51" t="n">
+        <v>280.8771882481053</v>
+      </c>
+      <c r="D51" t="n">
+        <v>277.7900501334527</v>
+      </c>
+      <c r="E51" t="n">
+        <v>278.5193786621094</v>
+      </c>
+      <c r="F51" t="n">
+        <v>47265800</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B52" t="n">
+        <v>277.8699843761556</v>
+      </c>
+      <c r="C52" t="n">
+        <v>279.4085531850005</v>
+      </c>
+      <c r="D52" t="n">
+        <v>275.8918244790692</v>
+      </c>
+      <c r="E52" t="n">
+        <v>277.6302185058594</v>
+      </c>
+      <c r="F52" t="n">
+        <v>38211800</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B53" t="n">
+        <v>277.8999627322321</v>
+      </c>
+      <c r="C53" t="n">
+        <v>279.7682096639769</v>
+      </c>
+      <c r="D53" t="n">
+        <v>276.6611317163261</v>
+      </c>
+      <c r="E53" t="n">
+        <v>276.9208679199219</v>
+      </c>
+      <c r="F53" t="n">
+        <v>32193300</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B54" t="n">
+        <v>277.490342786908</v>
+      </c>
+      <c r="C54" t="n">
+        <v>279.4884730680018</v>
+      </c>
+      <c r="D54" t="n">
+        <v>276.1815698919154</v>
+      </c>
+      <c r="E54" t="n">
+        <v>278.5193786621094</v>
+      </c>
+      <c r="F54" t="n">
+        <v>33038300</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B55" t="n">
+        <v>278.8390875870869</v>
+      </c>
+      <c r="C55" t="n">
+        <v>279.3286197507982</v>
+      </c>
+      <c r="D55" t="n">
+        <v>273.5540244422053</v>
+      </c>
+      <c r="E55" t="n">
+        <v>277.7700805664062</v>
+      </c>
+      <c r="F55" t="n">
+        <v>33248000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B56" t="n">
+        <v>277.64021728323</v>
+      </c>
+      <c r="C56" t="n">
+        <v>278.9589906850317</v>
+      </c>
+      <c r="D56" t="n">
+        <v>276.5612402656973</v>
+      </c>
+      <c r="E56" t="n">
+        <v>278.0198669433594</v>
+      </c>
+      <c r="F56" t="n">
+        <v>39532900</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B57" t="n">
+        <v>279.8880911943856</v>
+      </c>
+      <c r="C57" t="n">
+        <v>279.8880911943856</v>
+      </c>
+      <c r="D57" t="n">
+        <v>272.5849275039148</v>
+      </c>
+      <c r="E57" t="n">
+        <v>273.8537292480469</v>
+      </c>
+      <c r="F57" t="n">
+        <v>50409100</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B58" t="n">
+        <v>272.5649667835892</v>
+      </c>
+      <c r="C58" t="n">
+        <v>275.2424541197232</v>
+      </c>
+      <c r="D58" t="n">
+        <v>271.535930878856</v>
+      </c>
+      <c r="E58" t="n">
+        <v>274.353271484375</v>
+      </c>
+      <c r="F58" t="n">
+        <v>37648600</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B59" t="n">
+        <v>274.7529265191943</v>
+      </c>
+      <c r="C59" t="n">
+        <v>275.9018453851206</v>
+      </c>
+      <c r="D59" t="n">
+        <v>271.3860817211021</v>
+      </c>
+      <c r="E59" t="n">
+        <v>271.5858764648438</v>
+      </c>
+      <c r="F59" t="n">
+        <v>50138700</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B60" t="n">
+        <v>273.3542023206923</v>
+      </c>
+      <c r="C60" t="n">
+        <v>273.374203136776</v>
+      </c>
+      <c r="D60" t="n">
+        <v>266.7004552212896</v>
+      </c>
+      <c r="E60" t="n">
+        <v>271.935546875</v>
+      </c>
+      <c r="F60" t="n">
+        <v>51630700</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B61" t="n">
+        <v>271.8955859651445</v>
+      </c>
+      <c r="C61" t="n">
+        <v>274.343307881706</v>
+      </c>
+      <c r="D61" t="n">
+        <v>269.6476892826471</v>
+      </c>
+      <c r="E61" t="n">
+        <v>273.4141845703125</v>
+      </c>
+      <c r="F61" t="n">
+        <v>144632000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B62" t="n">
+        <v>272.6048920133635</v>
+      </c>
+      <c r="C62" t="n">
+        <v>273.6239579412959</v>
+      </c>
+      <c r="D62" t="n">
+        <v>270.2571133897843</v>
+      </c>
+      <c r="E62" t="n">
+        <v>270.7166748046875</v>
+      </c>
+      <c r="F62" t="n">
+        <v>36571800</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B63" t="n">
+        <v>270.5868091030317</v>
+      </c>
+      <c r="C63" t="n">
+        <v>272.2452609569047</v>
+      </c>
+      <c r="D63" t="n">
+        <v>269.3080068949797</v>
+      </c>
+      <c r="E63" t="n">
+        <v>272.1053771972656</v>
+      </c>
+      <c r="F63" t="n">
+        <v>29642000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B64" t="n">
+        <v>272.085389177814</v>
+      </c>
+      <c r="C64" t="n">
+        <v>275.1724967178681</v>
+      </c>
+      <c r="D64" t="n">
+        <v>271.9455359163183</v>
+      </c>
+      <c r="E64" t="n">
+        <v>273.5540161132812</v>
+      </c>
+      <c r="F64" t="n">
+        <v>17910600</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B65" t="n">
+        <v>273.9037084592662</v>
+      </c>
+      <c r="C65" t="n">
+        <v>275.1125687682936</v>
+      </c>
+      <c r="D65" t="n">
+        <v>272.6049054553</v>
+      </c>
+      <c r="E65" t="n">
+        <v>273.1444091796875</v>
+      </c>
+      <c r="F65" t="n">
+        <v>21521800</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B66" t="n">
+        <v>272.4350823114352</v>
+      </c>
+      <c r="C66" t="n">
+        <v>274.103504063292</v>
+      </c>
+      <c r="D66" t="n">
+        <v>272.0954038139857</v>
+      </c>
+      <c r="E66" t="n">
+        <v>273.5040893554688</v>
+      </c>
+      <c r="F66" t="n">
+        <v>23715200</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B67" t="n">
+        <v>272.5549704076282</v>
+      </c>
+      <c r="C67" t="n">
+        <v>273.8237722152489</v>
+      </c>
+      <c r="D67" t="n">
+        <v>272.0254670796708</v>
+      </c>
+      <c r="E67" t="n">
+        <v>272.82470703125</v>
+      </c>
+      <c r="F67" t="n">
+        <v>22139600</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B68" t="n">
+        <v>272.804725327361</v>
+      </c>
+      <c r="C68" t="n">
+        <v>273.4241408373621</v>
+      </c>
+      <c r="D68" t="n">
+        <v>271.4959524300237</v>
+      </c>
+      <c r="E68" t="n">
+        <v>271.6058349609375</v>
+      </c>
+      <c r="F68" t="n">
+        <v>27293600</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B69" t="n">
+        <v>272.0054842546519</v>
+      </c>
+      <c r="C69" t="n">
+        <v>277.5802543100492</v>
+      </c>
+      <c r="D69" t="n">
+        <v>268.7485221479618</v>
+      </c>
+      <c r="E69" t="n">
+        <v>270.7566528320312</v>
+      </c>
+      <c r="F69" t="n">
+        <v>37838100</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B70" t="n">
+        <v>270.387007446453</v>
+      </c>
+      <c r="C70" t="n">
+        <v>271.2561892506844</v>
+      </c>
+      <c r="D70" t="n">
+        <v>265.8912142612155</v>
+      </c>
+      <c r="E70" t="n">
+        <v>267.0101623535156</v>
+      </c>
+      <c r="F70" t="n">
+        <v>45647200</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B71" t="n">
+        <v>266.7503924619391</v>
+      </c>
+      <c r="C71" t="n">
+        <v>267.2998660934885</v>
+      </c>
+      <c r="D71" t="n">
+        <v>261.8749496989937</v>
+      </c>
+      <c r="E71" t="n">
+        <v>262.1147155761719</v>
+      </c>
+      <c r="F71" t="n">
+        <v>52352100</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B72" t="n">
+        <v>262.9539513876447</v>
+      </c>
+      <c r="C72" t="n">
+        <v>263.4334831315393</v>
+      </c>
+      <c r="D72" t="n">
+        <v>259.5671060011504</v>
+      </c>
+      <c r="E72" t="n">
+        <v>260.0866088867188</v>
+      </c>
+      <c r="F72" t="n">
+        <v>48309800</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B73" t="n">
+        <v>256.7797203952787</v>
+      </c>
+      <c r="C73" t="n">
+        <v>259.0476178563403</v>
+      </c>
+      <c r="D73" t="n">
+        <v>255.4609622909548</v>
+      </c>
+      <c r="E73" t="n">
+        <v>258.7978515625</v>
+      </c>
+      <c r="F73" t="n">
+        <v>50419300</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B74" t="n">
+        <v>258.8377955175017</v>
+      </c>
+      <c r="C74" t="n">
+        <v>259.9667440583015</v>
+      </c>
+      <c r="D74" t="n">
+        <v>255.9804837142826</v>
+      </c>
+      <c r="E74" t="n">
+        <v>259.1275329589844</v>
+      </c>
+      <c r="F74" t="n">
+        <v>39997000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B75" t="n">
+        <v>258.9177364764393</v>
+      </c>
+      <c r="C75" t="n">
+        <v>261.055720113683</v>
+      </c>
+      <c r="D75" t="n">
+        <v>256.5599267903311</v>
+      </c>
+      <c r="E75" t="n">
+        <v>260.0067138671875</v>
+      </c>
+      <c r="F75" t="n">
+        <v>45263800</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B76" t="n">
+        <v>258.4781303943212</v>
+      </c>
+      <c r="C76" t="n">
+        <v>261.5652379723006</v>
+      </c>
+      <c r="D76" t="n">
+        <v>258.148452318208</v>
+      </c>
+      <c r="E76" t="n">
+        <v>260.8059387207031</v>
+      </c>
+      <c r="F76" t="n">
+        <v>45730800</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B77" t="n">
+        <v>259.247418118488</v>
+      </c>
+      <c r="C77" t="n">
+        <v>261.5752571005171</v>
+      </c>
+      <c r="D77" t="n">
+        <v>256.4700180914029</v>
+      </c>
+      <c r="E77" t="n">
+        <v>259.7169799804688</v>
+      </c>
+      <c r="F77" t="n">
+        <v>40019400</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B78" t="n">
+        <v>260.4063187564486</v>
+      </c>
+      <c r="C78" t="n">
+        <v>260.7959687899761</v>
+      </c>
+      <c r="D78" t="n">
+        <v>256.8096782083212</v>
+      </c>
+      <c r="E78" t="n">
+        <v>257.9685974121094</v>
+      </c>
+      <c r="F78" t="n">
+        <v>39388600</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B79" t="n">
+        <v>257.6589020182799</v>
+      </c>
+      <c r="C79" t="n">
+        <v>258.6579671912775</v>
+      </c>
+      <c r="D79" t="n">
+        <v>254.6916772349149</v>
+      </c>
+      <c r="E79" t="n">
+        <v>255.2911224365234</v>
+      </c>
+      <c r="F79" t="n">
+        <v>72142800</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B80" t="n">
+        <v>252.4937373957159</v>
+      </c>
+      <c r="C80" t="n">
+        <v>254.5518092169813</v>
+      </c>
+      <c r="D80" t="n">
+        <v>243.1924430560896</v>
+      </c>
+      <c r="E80" t="n">
+        <v>246.4693756103516</v>
+      </c>
+      <c r="F80" t="n">
+        <v>80267500</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B81" t="n">
+        <v>248.4675090444481</v>
+      </c>
+      <c r="C81" t="n">
+        <v>251.3248360900433</v>
+      </c>
+      <c r="D81" t="n">
+        <v>244.9507953165175</v>
+      </c>
+      <c r="E81" t="n">
+        <v>247.4184875488281</v>
+      </c>
+      <c r="F81" t="n">
+        <v>54641700</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B82" t="n">
+        <v>248.9670398844787</v>
+      </c>
+      <c r="C82" t="n">
+        <v>250.7653602579427</v>
+      </c>
+      <c r="D82" t="n">
+        <v>247.9180183962477</v>
+      </c>
+      <c r="E82" t="n">
+        <v>248.1178436279297</v>
+      </c>
+      <c r="F82" t="n">
+        <v>39708300</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B83" t="n">
+        <v>247.0888078223564</v>
+      </c>
+      <c r="C83" t="n">
+        <v>249.176850391454</v>
+      </c>
+      <c r="D83" t="n">
+        <v>244.4512611104123</v>
+      </c>
+      <c r="E83" t="n">
+        <v>247.8081207275391</v>
+      </c>
+      <c r="F83" t="n">
+        <v>41689000</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B84" t="n">
+        <v>251.2449001563489</v>
+      </c>
+      <c r="C84" t="n">
+        <v>256.320152957849</v>
+      </c>
+      <c r="D84" t="n">
+        <v>249.5664780183616</v>
+      </c>
+      <c r="E84" t="n">
+        <v>255.1712341308594</v>
+      </c>
+      <c r="F84" t="n">
+        <v>55969200</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B85" t="n">
+        <v>258.9277169221324</v>
+      </c>
+      <c r="C85" t="n">
+        <v>261.705116697089</v>
+      </c>
+      <c r="D85" t="n">
+        <v>257.9685924683142</v>
+      </c>
+      <c r="E85" t="n">
+        <v>258.0285339355469</v>
+      </c>
+      <c r="F85" t="n">
+        <v>49648300</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B86" t="n">
+        <v>257.409147241713</v>
+      </c>
+      <c r="C86" t="n">
+        <v>258.6180076181917</v>
+      </c>
+      <c r="D86" t="n">
+        <v>254.2720830679268</v>
+      </c>
+      <c r="E86" t="n">
+        <v>256.2002868652344</v>
+      </c>
+      <c r="F86" t="n">
+        <v>41288000</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B87" t="n">
+        <v>257.758806680925</v>
+      </c>
+      <c r="C87" t="n">
+        <v>259.4072580677027</v>
+      </c>
+      <c r="D87" t="n">
+        <v>254.1721664792058</v>
+      </c>
+      <c r="E87" t="n">
+        <v>258.0385437011719</v>
+      </c>
+      <c r="F87" t="n">
+        <v>67253000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B88" t="n">
+        <v>254.9314433110553</v>
+      </c>
+      <c r="C88" t="n">
+        <v>261.6551472598355</v>
+      </c>
+      <c r="D88" t="n">
+        <v>251.9442331321547</v>
+      </c>
+      <c r="E88" t="n">
+        <v>259.2374267578125</v>
+      </c>
+      <c r="F88" t="n">
+        <v>92443400</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B89" t="n">
+        <v>259.7869174093499</v>
+      </c>
+      <c r="C89" t="n">
+        <v>270.2371306501278</v>
+      </c>
+      <c r="D89" t="n">
+        <v>258.9676766447768</v>
+      </c>
+      <c r="E89" t="n">
+        <v>269.7575988769531</v>
+      </c>
+      <c r="F89" t="n">
+        <v>73913400</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B90" t="n">
+        <v>268.9483513556569</v>
+      </c>
+      <c r="C90" t="n">
+        <v>271.6258386480508</v>
+      </c>
+      <c r="D90" t="n">
+        <v>267.3598109321867</v>
+      </c>
+      <c r="E90" t="n">
+        <v>269.2280883789062</v>
+      </c>
+      <c r="F90" t="n">
+        <v>64394700</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B91" t="n">
+        <v>272.03545112075</v>
+      </c>
+      <c r="C91" t="n">
+        <v>278.6892285045384</v>
+      </c>
+      <c r="D91" t="n">
+        <v>272.03545112075</v>
+      </c>
+      <c r="E91" t="n">
+        <v>276.2315063476562</v>
+      </c>
+      <c r="F91" t="n">
+        <v>90545700</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B92" t="n">
+        <v>277.8699949435269</v>
+      </c>
+      <c r="C92" t="n">
+        <v>279.2387093202658</v>
+      </c>
+      <c r="D92" t="n">
+        <v>272.9745818081728</v>
+      </c>
+      <c r="E92" t="n">
+        <v>275.6520690917969</v>
+      </c>
+      <c r="F92" t="n">
+        <v>52977400</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B93" t="n">
+        <v>276.8609202349588</v>
+      </c>
+      <c r="C93" t="n">
+        <v>280.6473855638201</v>
+      </c>
+      <c r="D93" t="n">
+        <v>276.6710954236804</v>
+      </c>
+      <c r="E93" t="n">
+        <v>277.8599853515625</v>
+      </c>
+      <c r="F93" t="n">
+        <v>50453400</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B94" t="n">
+        <v>277.9100036621094</v>
+      </c>
+      <c r="C94" t="n">
+        <v>278.2000122070312</v>
+      </c>
+      <c r="D94" t="n">
+        <v>271.7000122070312</v>
+      </c>
+      <c r="E94" t="n">
+        <v>274.6199951171875</v>
+      </c>
+      <c r="F94" t="n">
+        <v>44623400</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B95" t="n">
+        <v>274.8900146484375</v>
+      </c>
+      <c r="C95" t="n">
+        <v>275.3699951171875</v>
+      </c>
+      <c r="D95" t="n">
+        <v>272.9400024414062</v>
+      </c>
+      <c r="E95" t="n">
+        <v>273.6799926757812</v>
+      </c>
+      <c r="F95" t="n">
+        <v>34376900</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B96" t="n">
+        <v>274.7000122070312</v>
+      </c>
+      <c r="C96" t="n">
+        <v>280.1799926757812</v>
+      </c>
+      <c r="D96" t="n">
+        <v>274.4500122070312</v>
+      </c>
+      <c r="E96" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="F96" t="n">
+        <v>51931300</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B97" t="n">
+        <v>275.5899963378906</v>
+      </c>
+      <c r="C97" t="n">
+        <v>275.7200012207031</v>
+      </c>
+      <c r="D97" t="n">
+        <v>260.1799926757812</v>
+      </c>
+      <c r="E97" t="n">
+        <v>261.7300109863281</v>
+      </c>
+      <c r="F97" t="n">
+        <v>81077200</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B98" t="n">
+        <v>262.010009765625</v>
+      </c>
+      <c r="C98" t="n">
+        <v>262.2300109863281</v>
+      </c>
+      <c r="D98" t="n">
+        <v>255.4499969482422</v>
+      </c>
+      <c r="E98" t="n">
+        <v>255.7799987792969</v>
+      </c>
+      <c r="F98" t="n">
+        <v>56290700</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B99" t="n">
+        <v>258.0499877929688</v>
+      </c>
+      <c r="C99" t="n">
+        <v>266.2900085449219</v>
+      </c>
+      <c r="D99" t="n">
+        <v>255.5399932861328</v>
+      </c>
+      <c r="E99" t="n">
+        <v>263.8800048828125</v>
+      </c>
+      <c r="F99" t="n">
+        <v>58469100</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B100" t="n">
+        <v>263.6000061035156</v>
+      </c>
+      <c r="C100" t="n">
+        <v>266.8200073242188</v>
+      </c>
+      <c r="D100" t="n">
+        <v>262.4500122070312</v>
+      </c>
+      <c r="E100" t="n">
+        <v>264.3500061035156</v>
+      </c>
+      <c r="F100" t="n">
+        <v>34203300</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B101" t="n">
+        <v>262.6000061035156</v>
+      </c>
+      <c r="C101" t="n">
+        <v>264.4800109863281</v>
+      </c>
+      <c r="D101" t="n">
+        <v>260.0499877929688</v>
+      </c>
+      <c r="E101" t="n">
+        <v>260.5799865722656</v>
+      </c>
+      <c r="F101" t="n">
+        <v>30845300</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B102" t="n">
+        <v>258.9700012207031</v>
+      </c>
+      <c r="C102" t="n">
+        <v>264.75</v>
+      </c>
+      <c r="D102" t="n">
+        <v>258.1600036621094</v>
+      </c>
+      <c r="E102" t="n">
+        <v>264.5799865722656</v>
+      </c>
+      <c r="F102" t="n">
+        <v>42070500</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B103" t="n">
+        <v>263.489990234375</v>
+      </c>
+      <c r="C103" t="n">
+        <v>269.4299926757812</v>
+      </c>
+      <c r="D103" t="n">
+        <v>263.3800048828125</v>
+      </c>
+      <c r="E103" t="n">
+        <v>266.1799926757812</v>
+      </c>
+      <c r="F103" t="n">
+        <v>37308200</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B104" t="n">
+        <v>267.8599853515625</v>
+      </c>
+      <c r="C104" t="n">
+        <v>274.8900146484375</v>
+      </c>
+      <c r="D104" t="n">
+        <v>267.7099914550781</v>
+      </c>
+      <c r="E104" t="n">
+        <v>272.1400146484375</v>
+      </c>
+      <c r="F104" t="n">
+        <v>47014600</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B105" t="n">
+        <v>271.7799987792969</v>
+      </c>
+      <c r="C105" t="n">
+        <v>274.9400024414062</v>
+      </c>
+      <c r="D105" t="n">
+        <v>271.0499877929688</v>
+      </c>
+      <c r="E105" t="n">
+        <v>274.2300109863281</v>
+      </c>
+      <c r="F105" t="n">
+        <v>33714300</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B106" t="n">
+        <v>274.9500122070312</v>
+      </c>
+      <c r="C106" t="n">
+        <v>276.1099853515625</v>
+      </c>
+      <c r="D106" t="n">
+        <v>270.7999877929688</v>
+      </c>
+      <c r="E106" t="n">
+        <v>272.9500122070312</v>
+      </c>
+      <c r="F106" t="n">
+        <v>32345100</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B107" t="n">
+        <v>272.8099975585938</v>
+      </c>
+      <c r="C107" t="n">
+        <v>272.8099975585938</v>
+      </c>
+      <c r="D107" t="n">
+        <v>262.8900146484375</v>
+      </c>
+      <c r="E107" t="n">
+        <v>264.1799926757812</v>
+      </c>
+      <c r="F107" t="n">
+        <v>72366500</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B108" t="n">
+        <v>262.4100036621094</v>
+      </c>
+      <c r="C108" t="n">
+        <v>266.5299987792969</v>
+      </c>
+      <c r="D108" t="n">
+        <v>260.2000122070312</v>
+      </c>
+      <c r="E108" t="n">
+        <v>264.7200012207031</v>
+      </c>
+      <c r="F108" t="n">
+        <v>41827900</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B109" t="n">
+        <v>263.4800109863281</v>
+      </c>
+      <c r="C109" t="n">
+        <v>265.5599975585938</v>
+      </c>
+      <c r="D109" t="n">
+        <v>260.1300048828125</v>
+      </c>
+      <c r="E109" t="n">
+        <v>263.75</v>
+      </c>
+      <c r="F109" t="n">
+        <v>38568900</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B110" t="n">
+        <v>264.6499938964844</v>
+      </c>
+      <c r="C110" t="n">
+        <v>266.1499938964844</v>
+      </c>
+      <c r="D110" t="n">
+        <v>261.4200134277344</v>
+      </c>
+      <c r="E110" t="n">
+        <v>262.5199890136719</v>
+      </c>
+      <c r="F110" t="n">
+        <v>39803100</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B111" t="n">
+        <v>260.7900085449219</v>
+      </c>
+      <c r="C111" t="n">
+        <v>261.5599975585938</v>
+      </c>
+      <c r="D111" t="n">
+        <v>257.25</v>
+      </c>
+      <c r="E111" t="n">
+        <v>260.2900085449219</v>
+      </c>
+      <c r="F111" t="n">
+        <v>49658600</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B112" t="n">
+        <v>258.6300048828125</v>
+      </c>
+      <c r="C112" t="n">
+        <v>258.7699890136719</v>
+      </c>
+      <c r="D112" t="n">
+        <v>254.3699951171875</v>
+      </c>
+      <c r="E112" t="n">
+        <v>257.4599914550781</v>
+      </c>
+      <c r="F112" t="n">
+        <v>41120000</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B113" t="n">
+        <v>255.6900024414062</v>
+      </c>
+      <c r="C113" t="n">
+        <v>261.1499938964844</v>
+      </c>
+      <c r="D113" t="n">
+        <v>253.6799926757812</v>
+      </c>
+      <c r="E113" t="n">
+        <v>259.8800048828125</v>
+      </c>
+      <c r="F113" t="n">
+        <v>38218500</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B114" t="n">
+        <v>257.6499938964844</v>
+      </c>
+      <c r="C114" t="n">
+        <v>262.4800109863281</v>
+      </c>
+      <c r="D114" t="n">
+        <v>256.9500122070312</v>
+      </c>
+      <c r="E114" t="n">
+        <v>260.8299865722656</v>
+      </c>
+      <c r="F114" t="n">
+        <v>30590800</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B115" t="n">
+        <v>261.0899963378906</v>
+      </c>
+      <c r="C115" t="n">
+        <v>262.1300048828125</v>
+      </c>
+      <c r="D115" t="n">
+        <v>259.5499877929688</v>
+      </c>
+      <c r="E115" t="n">
+        <v>260.8099975585938</v>
+      </c>
+      <c r="F115" t="n">
+        <v>26218900</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B116" t="n">
+        <v>258.6600036621094</v>
+      </c>
+      <c r="C116" t="n">
+        <v>258.9500122070312</v>
+      </c>
+      <c r="D116" t="n">
+        <v>254.1799926757812</v>
+      </c>
+      <c r="E116" t="n">
+        <v>255.7599945068359</v>
+      </c>
+      <c r="F116" t="n">
+        <v>40794000</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B117" t="n">
+        <v>255.4799957275391</v>
+      </c>
+      <c r="C117" t="n">
+        <v>256.3299865722656</v>
+      </c>
+      <c r="D117" t="n">
+        <v>249.5200042724609</v>
+      </c>
+      <c r="E117" t="n">
+        <v>250.1199951171875</v>
+      </c>
+      <c r="F117" t="n">
+        <v>36930000</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B118" t="n">
+        <v>252.1100006103516</v>
+      </c>
+      <c r="C118" t="n">
+        <v>253.8899993896484</v>
+      </c>
+      <c r="D118" t="n">
+        <v>249.8800048828125</v>
+      </c>
+      <c r="E118" t="n">
+        <v>252.8200073242188</v>
+      </c>
+      <c r="F118" t="n">
+        <v>32074200</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B119" t="n">
+        <v>252.9600067138672</v>
+      </c>
+      <c r="C119" t="n">
+        <v>255.1300048828125</v>
+      </c>
+      <c r="D119" t="n">
+        <v>252.1799926757812</v>
+      </c>
+      <c r="E119" t="n">
+        <v>254.2299957275391</v>
+      </c>
+      <c r="F119" t="n">
+        <v>32361600</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B120" t="n">
+        <v>252.6300048828125</v>
+      </c>
+      <c r="C120" t="n">
+        <v>254.9400024414062</v>
+      </c>
+      <c r="D120" t="n">
+        <v>249</v>
+      </c>
+      <c r="E120" t="n">
+        <v>249.9400024414062</v>
+      </c>
+      <c r="F120" t="n">
+        <v>35757900</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B121" t="n">
+        <v>249.3999938964844</v>
+      </c>
+      <c r="C121" t="n">
+        <v>251.8300018310547</v>
+      </c>
+      <c r="D121" t="n">
+        <v>247.3000030517578</v>
+      </c>
+      <c r="E121" t="n">
+        <v>248.9600067138672</v>
+      </c>
+      <c r="F121" t="n">
+        <v>34864100</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B122" t="n">
+        <v>247.9799957275391</v>
+      </c>
+      <c r="C122" t="n">
+        <v>249.1999969482422</v>
+      </c>
+      <c r="D122" t="n">
+        <v>246</v>
+      </c>
+      <c r="E122" t="n">
+        <v>247.9900054931641</v>
+      </c>
+      <c r="F122" t="n">
+        <v>88331100</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B123" t="n">
+        <v>253.9700012207031</v>
+      </c>
+      <c r="C123" t="n">
+        <v>254.6000061035156</v>
+      </c>
+      <c r="D123" t="n">
+        <v>250.2799987792969</v>
+      </c>
+      <c r="E123" t="n">
+        <v>251.4900054931641</v>
+      </c>
+      <c r="F123" t="n">
+        <v>40546100</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B124" t="n">
+        <v>250.3500061035156</v>
+      </c>
+      <c r="C124" t="n">
+        <v>254.8300018310547</v>
+      </c>
+      <c r="D124" t="n">
+        <v>249.5500030517578</v>
+      </c>
+      <c r="E124" t="n">
+        <v>251.6399993896484</v>
+      </c>
+      <c r="F124" t="n">
+        <v>45111500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F124"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B2" t="n">
+        <v>507.9477836110377</v>
+      </c>
+      <c r="C2" t="n">
+        <v>511.8117209714621</v>
+      </c>
+      <c r="D2" t="n">
+        <v>504.5220265940347</v>
+      </c>
+      <c r="E2" t="n">
+        <v>509.3419799804688</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16213100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B3" t="n">
+        <v>509.3817950243417</v>
+      </c>
+      <c r="C3" t="n">
+        <v>514.7096154882738</v>
+      </c>
+      <c r="D3" t="n">
+        <v>506.7726497345118</v>
+      </c>
+      <c r="E3" t="n">
+        <v>512.4689331054688</v>
+      </c>
+      <c r="F3" t="n">
+        <v>17617800</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B4" t="n">
+        <v>511.1145975787894</v>
+      </c>
+      <c r="C4" t="n">
+        <v>516.0142062084105</v>
+      </c>
+      <c r="D4" t="n">
+        <v>507.549436190283</v>
+      </c>
+      <c r="E4" t="n">
+        <v>515.8051147460938</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19728200</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B5" t="n">
+        <v>512.6681599915194</v>
+      </c>
+      <c r="C5" t="n">
+        <v>518.3545363078492</v>
+      </c>
+      <c r="D5" t="n">
+        <v>509.5710533372991</v>
+      </c>
+      <c r="E5" t="n">
+        <v>517.557861328125</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22632300</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B6" t="n">
+        <v>515.496404228155</v>
+      </c>
+      <c r="C6" t="n">
+        <v>519.4399664845459</v>
+      </c>
+      <c r="D6" t="n">
+        <v>508.5652045551738</v>
+      </c>
+      <c r="E6" t="n">
+        <v>513.604248046875</v>
+      </c>
+      <c r="F6" t="n">
+        <v>21222900</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B7" t="n">
+        <v>514.9585548343116</v>
+      </c>
+      <c r="C7" t="n">
+        <v>518.3345307125708</v>
+      </c>
+      <c r="D7" t="n">
+        <v>512.8672756929882</v>
+      </c>
+      <c r="E7" t="n">
+        <v>515.20751953125</v>
+      </c>
+      <c r="F7" t="n">
+        <v>15112300</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B8" t="n">
+        <v>516.4623876768178</v>
+      </c>
+      <c r="C8" t="n">
+        <v>528.8309994124726</v>
+      </c>
+      <c r="D8" t="n">
+        <v>516.0541122577388</v>
+      </c>
+      <c r="E8" t="n">
+        <v>526.3811645507812</v>
+      </c>
+      <c r="F8" t="n">
+        <v>21388600</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B9" t="n">
+        <v>526.1022689962125</v>
+      </c>
+      <c r="C9" t="n">
+        <v>527.6060256392368</v>
+      </c>
+      <c r="D9" t="n">
+        <v>519.2806599401652</v>
+      </c>
+      <c r="E9" t="n">
+        <v>521.8101196289062</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14615200</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B10" t="n">
+        <v>521.1130687043808</v>
+      </c>
+      <c r="C10" t="n">
+        <v>524.7678538085896</v>
+      </c>
+      <c r="D10" t="n">
+        <v>520.923853084141</v>
+      </c>
+      <c r="E10" t="n">
+        <v>522.676513671875</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13363400</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B11" t="n">
+        <v>520.1769452354545</v>
+      </c>
+      <c r="C11" t="n">
+        <v>522.158694647609</v>
+      </c>
+      <c r="D11" t="n">
+        <v>515.2574000210162</v>
+      </c>
+      <c r="E11" t="n">
+        <v>520.2366943359375</v>
+      </c>
+      <c r="F11" t="n">
+        <v>18343600</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B12" t="n">
+        <v>517.4881335274953</v>
+      </c>
+      <c r="C12" t="n">
+        <v>521.4118200258811</v>
+      </c>
+      <c r="D12" t="n">
+        <v>507.5195762105422</v>
+      </c>
+      <c r="E12" t="n">
+        <v>508.8440551757812</v>
+      </c>
+      <c r="F12" t="n">
+        <v>24133800</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B13" t="n">
+        <v>514.2714464494894</v>
+      </c>
+      <c r="C13" t="n">
+        <v>514.2714464494894</v>
+      </c>
+      <c r="D13" t="n">
+        <v>509.5610534984588</v>
+      </c>
+      <c r="E13" t="n">
+        <v>511.9212341308594</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14284200</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B14" t="n">
+        <v>508.1170723899241</v>
+      </c>
+      <c r="C14" t="n">
+        <v>513.1461778212379</v>
+      </c>
+      <c r="D14" t="n">
+        <v>503.9045785101632</v>
+      </c>
+      <c r="E14" t="n">
+        <v>511.4432373046875</v>
+      </c>
+      <c r="F14" t="n">
+        <v>14684300</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B15" t="n">
+        <v>512.8274957075639</v>
+      </c>
+      <c r="C15" t="n">
+        <v>515.0482414945574</v>
+      </c>
+      <c r="D15" t="n">
+        <v>507.888013925759</v>
+      </c>
+      <c r="E15" t="n">
+        <v>511.3038024902344</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14694700</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B16" t="n">
+        <v>510.4573477017149</v>
+      </c>
+      <c r="C16" t="n">
+        <v>514.7096236704256</v>
+      </c>
+      <c r="D16" t="n">
+        <v>506.0257636510178</v>
+      </c>
+      <c r="E16" t="n">
+        <v>509.4913330078125</v>
+      </c>
+      <c r="F16" t="n">
+        <v>15559600</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B17" t="n">
+        <v>506.9320390116644</v>
+      </c>
+      <c r="C17" t="n">
+        <v>513.3453425707617</v>
+      </c>
+      <c r="D17" t="n">
+        <v>505.2091921192977</v>
+      </c>
+      <c r="E17" t="n">
+        <v>511.4532470703125</v>
+      </c>
+      <c r="F17" t="n">
+        <v>19867800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B18" t="n">
+        <v>512.4788764440519</v>
+      </c>
+      <c r="C18" t="n">
+        <v>516.5519656323323</v>
+      </c>
+      <c r="D18" t="n">
+        <v>511.3037703677804</v>
+      </c>
+      <c r="E18" t="n">
+        <v>514.6498413085938</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14665600</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B19" t="n">
+        <v>515.3569857054445</v>
+      </c>
+      <c r="C19" t="n">
+        <v>516.5420602391357</v>
+      </c>
+      <c r="D19" t="n">
+        <v>510.9154330870712</v>
+      </c>
+      <c r="E19" t="n">
+        <v>515.5162963867188</v>
+      </c>
+      <c r="F19" t="n">
+        <v>15586200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B20" t="n">
+        <v>518.9919195722497</v>
+      </c>
+      <c r="C20" t="n">
+        <v>523.0549803520576</v>
+      </c>
+      <c r="D20" t="n">
+        <v>515.5661623300699</v>
+      </c>
+      <c r="E20" t="n">
+        <v>518.3843994140625</v>
+      </c>
+      <c r="F20" t="n">
+        <v>18962700</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B21" t="n">
+        <v>520.2964530626382</v>
+      </c>
+      <c r="C21" t="n">
+        <v>521.7802730707533</v>
+      </c>
+      <c r="D21" t="n">
+        <v>516.4623598997719</v>
+      </c>
+      <c r="E21" t="n">
+        <v>518.404296875</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14023500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B22" t="n">
+        <v>520.6250388201142</v>
+      </c>
+      <c r="C22" t="n">
+        <v>523.1744351060786</v>
+      </c>
+      <c r="D22" t="n">
+        <v>518.5536961256696</v>
+      </c>
+      <c r="E22" t="n">
+        <v>521.441650390625</v>
+      </c>
+      <c r="F22" t="n">
+        <v>15532400</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B23" t="n">
+        <v>529.577902779321</v>
+      </c>
+      <c r="C23" t="n">
+        <v>532.3662956890146</v>
+      </c>
+      <c r="D23" t="n">
+        <v>526.819354031342</v>
+      </c>
+      <c r="E23" t="n">
+        <v>529.3189697265625</v>
+      </c>
+      <c r="F23" t="n">
+        <v>18734700</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B24" t="n">
+        <v>547.7224103521172</v>
+      </c>
+      <c r="C24" t="n">
+        <v>551.4269763883988</v>
+      </c>
+      <c r="D24" t="n">
+        <v>538.5306518978505</v>
+      </c>
+      <c r="E24" t="n">
+        <v>539.8252563476562</v>
+      </c>
+      <c r="F24" t="n">
+        <v>29986700</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B25" t="n">
+        <v>542.6833492925585</v>
+      </c>
+      <c r="C25" t="n">
+        <v>544.0078586434945</v>
+      </c>
+      <c r="D25" t="n">
+        <v>534.507325873603</v>
+      </c>
+      <c r="E25" t="n">
+        <v>539.307373046875</v>
+      </c>
+      <c r="F25" t="n">
+        <v>36023000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B26" t="n">
+        <v>528.2831883129468</v>
+      </c>
+      <c r="C26" t="n">
+        <v>532.7545848667123</v>
+      </c>
+      <c r="D26" t="n">
+        <v>519.9578228356851</v>
+      </c>
+      <c r="E26" t="n">
+        <v>523.582763671875</v>
+      </c>
+      <c r="F26" t="n">
+        <v>41023100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B27" t="n">
+        <v>526.6898137654194</v>
+      </c>
+      <c r="C27" t="n">
+        <v>527.1279940743384</v>
+      </c>
+      <c r="D27" t="n">
+        <v>512.9668501497666</v>
+      </c>
+      <c r="E27" t="n">
+        <v>515.6656494140625</v>
+      </c>
+      <c r="F27" t="n">
+        <v>34006400</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B28" t="n">
+        <v>517.657371934483</v>
+      </c>
+      <c r="C28" t="n">
+        <v>522.7860691817526</v>
+      </c>
+      <c r="D28" t="n">
+        <v>512.4590180581705</v>
+      </c>
+      <c r="E28" t="n">
+        <v>514.888916015625</v>
+      </c>
+      <c r="F28" t="n">
+        <v>22374700</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B29" t="n">
+        <v>509.6407695643784</v>
+      </c>
+      <c r="C29" t="n">
+        <v>513.4150529816625</v>
+      </c>
+      <c r="D29" t="n">
+        <v>505.7369892339689</v>
+      </c>
+      <c r="E29" t="n">
+        <v>512.2001342773438</v>
+      </c>
+      <c r="F29" t="n">
+        <v>20958700</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B30" t="n">
+        <v>511.1743415428253</v>
+      </c>
+      <c r="C30" t="n">
+        <v>512.6980347767452</v>
+      </c>
+      <c r="D30" t="n">
+        <v>504.4821687767013</v>
+      </c>
+      <c r="E30" t="n">
+        <v>505.0597839355469</v>
+      </c>
+      <c r="F30" t="n">
+        <v>23024300</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B31" t="n">
+        <v>503.5659922381216</v>
+      </c>
+      <c r="C31" t="n">
+        <v>503.6058351018555</v>
+      </c>
+      <c r="D31" t="n">
+        <v>493.7567764386794</v>
+      </c>
+      <c r="E31" t="n">
+        <v>495.0414428710938</v>
+      </c>
+      <c r="F31" t="n">
+        <v>27406500</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B32" t="n">
+        <v>494.8920702735404</v>
+      </c>
+      <c r="C32" t="n">
+        <v>497.3119999979126</v>
+      </c>
+      <c r="D32" t="n">
+        <v>491.2073803526309</v>
+      </c>
+      <c r="E32" t="n">
+        <v>494.7626037597656</v>
+      </c>
+      <c r="F32" t="n">
+        <v>24019800</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B33" t="n">
+        <v>497.9692613740871</v>
+      </c>
+      <c r="C33" t="n">
+        <v>504.7510576229119</v>
+      </c>
+      <c r="D33" t="n">
+        <v>496.7343757501637</v>
+      </c>
+      <c r="E33" t="n">
+        <v>503.9045715332031</v>
+      </c>
+      <c r="F33" t="n">
+        <v>26101500</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B34" t="n">
+        <v>502.7095490222416</v>
+      </c>
+      <c r="C34" t="n">
+        <v>507.4896898672195</v>
+      </c>
+      <c r="D34" t="n">
+        <v>500.2697130079767</v>
+      </c>
+      <c r="E34" t="n">
+        <v>506.573486328125</v>
+      </c>
+      <c r="F34" t="n">
+        <v>17980000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B35" t="n">
+        <v>507.2506574723947</v>
+      </c>
+      <c r="C35" t="n">
+        <v>509.5511194130969</v>
+      </c>
+      <c r="D35" t="n">
+        <v>497.0530724082431</v>
+      </c>
+      <c r="E35" t="n">
+        <v>509.0233154296875</v>
+      </c>
+      <c r="F35" t="n">
+        <v>26574900</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B36" t="n">
+        <v>508.1967287528611</v>
+      </c>
+      <c r="C36" t="n">
+        <v>511.3735209246628</v>
+      </c>
+      <c r="D36" t="n">
+        <v>499.2140928412288</v>
+      </c>
+      <c r="E36" t="n">
+        <v>501.205810546875</v>
+      </c>
+      <c r="F36" t="n">
+        <v>25273100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B37" t="n">
+        <v>496.166765720741</v>
+      </c>
+      <c r="C37" t="n">
+        <v>509.4813936811572</v>
+      </c>
+      <c r="D37" t="n">
+        <v>495.3800287197931</v>
+      </c>
+      <c r="E37" t="n">
+        <v>508.0672607421875</v>
+      </c>
+      <c r="F37" t="n">
+        <v>28505700</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B38" t="n">
+        <v>506.3444435928635</v>
+      </c>
+      <c r="C38" t="n">
+        <v>509.9992285471841</v>
+      </c>
+      <c r="D38" t="n">
+        <v>502.8190947602184</v>
+      </c>
+      <c r="E38" t="n">
+        <v>505.3883972167969</v>
+      </c>
+      <c r="F38" t="n">
+        <v>19092800</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B39" t="n">
+        <v>493.3186219236692</v>
+      </c>
+      <c r="C39" t="n">
+        <v>500.8971240097587</v>
+      </c>
+      <c r="D39" t="n">
+        <v>484.7641975590383</v>
+      </c>
+      <c r="E39" t="n">
+        <v>491.7451782226562</v>
+      </c>
+      <c r="F39" t="n">
+        <v>33815100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B40" t="n">
+        <v>488.0704229659532</v>
+      </c>
+      <c r="C40" t="n">
+        <v>493.1393408084164</v>
+      </c>
+      <c r="D40" t="n">
+        <v>480.8305097576304</v>
+      </c>
+      <c r="E40" t="n">
+        <v>485.1027526855469</v>
+      </c>
+      <c r="F40" t="n">
+        <v>23245300</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B41" t="n">
+        <v>491.5879641710541</v>
+      </c>
+      <c r="C41" t="n">
+        <v>492.4460215630244</v>
+      </c>
+      <c r="D41" t="n">
+        <v>474.4171642897319</v>
+      </c>
+      <c r="E41" t="n">
+        <v>477.3404846191406</v>
+      </c>
+      <c r="F41" t="n">
+        <v>26802500</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B42" t="n">
+        <v>477.4103368698009</v>
+      </c>
+      <c r="C42" t="n">
+        <v>477.8293938228302</v>
+      </c>
+      <c r="D42" t="n">
+        <v>467.2036221547232</v>
+      </c>
+      <c r="E42" t="n">
+        <v>471.0448608398438</v>
+      </c>
+      <c r="F42" t="n">
+        <v>31769200</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B43" t="n">
+        <v>473.9183160323131</v>
+      </c>
+      <c r="C43" t="n">
+        <v>475.8139832068258</v>
+      </c>
+      <c r="D43" t="n">
+        <v>466.9542001322548</v>
+      </c>
+      <c r="E43" t="n">
+        <v>472.9205932617188</v>
+      </c>
+      <c r="F43" t="n">
+        <v>34421000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B44" t="n">
+        <v>472.9904142849383</v>
+      </c>
+      <c r="C44" t="n">
+        <v>478.0588322743821</v>
+      </c>
+      <c r="D44" t="n">
+        <v>463.8313270788984</v>
+      </c>
+      <c r="E44" t="n">
+        <v>475.9037475585938</v>
+      </c>
+      <c r="F44" t="n">
+        <v>28019800</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B45" t="n">
+        <v>485.2025316262965</v>
+      </c>
+      <c r="C45" t="n">
+        <v>487.1979770584782</v>
+      </c>
+      <c r="D45" t="n">
+        <v>480.1041831621511</v>
+      </c>
+      <c r="E45" t="n">
+        <v>484.3943786621094</v>
+      </c>
+      <c r="F45" t="n">
+        <v>25709100</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B46" t="n">
+        <v>486.489626354464</v>
+      </c>
+      <c r="C46" t="n">
+        <v>491.5081706450152</v>
+      </c>
+      <c r="D46" t="n">
+        <v>485.541777548382</v>
+      </c>
+      <c r="E46" t="n">
+        <v>490.8895874023438</v>
+      </c>
+      <c r="F46" t="n">
+        <v>14386700</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B47" t="n">
+        <v>487.3277021324388</v>
+      </c>
+      <c r="C47" t="n">
+        <v>488.7444513856018</v>
+      </c>
+      <c r="D47" t="n">
+        <v>483.5463243869077</v>
+      </c>
+      <c r="E47" t="n">
+        <v>485.6315612792969</v>
+      </c>
+      <c r="F47" t="n">
+        <v>23964000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B48" t="n">
+        <v>485.6116258193264</v>
+      </c>
+      <c r="C48" t="n">
+        <v>492.3761849539621</v>
+      </c>
+      <c r="D48" t="n">
+        <v>485.2125428025972</v>
+      </c>
+      <c r="E48" t="n">
+        <v>488.8841552734375</v>
+      </c>
+      <c r="F48" t="n">
+        <v>19562700</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B49" t="n">
+        <v>475.235297143397</v>
+      </c>
+      <c r="C49" t="n">
+        <v>483.1372440988117</v>
+      </c>
+      <c r="D49" t="n">
+        <v>474.1178525596479</v>
+      </c>
+      <c r="E49" t="n">
+        <v>476.64208984375</v>
+      </c>
+      <c r="F49" t="n">
+        <v>34615100</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B50" t="n">
+        <v>478.6674679630734</v>
+      </c>
+      <c r="C50" t="n">
+        <v>480.2239129901724</v>
+      </c>
+      <c r="D50" t="n">
+        <v>475.4048951405118</v>
+      </c>
+      <c r="E50" t="n">
+        <v>479.7449951171875</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22318200</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B51" t="n">
+        <v>481.4211657314621</v>
+      </c>
+      <c r="C51" t="n">
+        <v>482.299166614698</v>
+      </c>
+      <c r="D51" t="n">
+        <v>477.7894707894466</v>
+      </c>
+      <c r="E51" t="n">
+        <v>482.0597229003906</v>
+      </c>
+      <c r="F51" t="n">
+        <v>22608700</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B52" t="n">
+        <v>483.7858099301447</v>
+      </c>
+      <c r="C52" t="n">
+        <v>491.1789088824644</v>
+      </c>
+      <c r="D52" t="n">
+        <v>483.2769615726175</v>
+      </c>
+      <c r="E52" t="n">
+        <v>489.9018249511719</v>
+      </c>
+      <c r="F52" t="n">
+        <v>21965900</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B53" t="n">
+        <v>487.9862027558801</v>
+      </c>
+      <c r="C53" t="n">
+        <v>490.9993144973556</v>
+      </c>
+      <c r="D53" t="n">
+        <v>487.3875630167038</v>
+      </c>
+      <c r="E53" t="n">
+        <v>490.8995361328125</v>
+      </c>
+      <c r="F53" t="n">
+        <v>14696100</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B54" t="n">
+        <v>482.9277288439703</v>
+      </c>
+      <c r="C54" t="n">
+        <v>483.1472290611572</v>
+      </c>
+      <c r="D54" t="n">
+        <v>473.9980982856002</v>
+      </c>
+      <c r="E54" t="n">
+        <v>477.4701843261719</v>
+      </c>
+      <c r="F54" t="n">
+        <v>35756200</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B55" t="n">
+        <v>475.5445986070271</v>
+      </c>
+      <c r="C55" t="n">
+        <v>484.9231863556336</v>
+      </c>
+      <c r="D55" t="n">
+        <v>474.7763326037194</v>
+      </c>
+      <c r="E55" t="n">
+        <v>482.3690185546875</v>
+      </c>
+      <c r="F55" t="n">
+        <v>24669200</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B56" t="n">
+        <v>478.7273480015789</v>
+      </c>
+      <c r="C56" t="n">
+        <v>481.3513637649093</v>
+      </c>
+      <c r="D56" t="n">
+        <v>475.2552617920193</v>
+      </c>
+      <c r="E56" t="n">
+        <v>477.4402770996094</v>
+      </c>
+      <c r="F56" t="n">
+        <v>21248100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B57" t="n">
+        <v>479.0066832317436</v>
+      </c>
+      <c r="C57" t="n">
+        <v>479.6252664455081</v>
+      </c>
+      <c r="D57" t="n">
+        <v>471.4439279747418</v>
+      </c>
+      <c r="E57" t="n">
+        <v>473.7387084960938</v>
+      </c>
+      <c r="F57" t="n">
+        <v>23727700</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B58" t="n">
+        <v>470.8353364785088</v>
+      </c>
+      <c r="C58" t="n">
+        <v>476.8017293564801</v>
+      </c>
+      <c r="D58" t="n">
+        <v>469.8076832860371</v>
+      </c>
+      <c r="E58" t="n">
+        <v>475.3051452636719</v>
+      </c>
+      <c r="F58" t="n">
+        <v>20705600</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B59" t="n">
+        <v>475.8239455574328</v>
+      </c>
+      <c r="C59" t="n">
+        <v>478.9069051052783</v>
+      </c>
+      <c r="D59" t="n">
+        <v>473.9182915104317</v>
+      </c>
+      <c r="E59" t="n">
+        <v>475.0357360839844</v>
+      </c>
+      <c r="F59" t="n">
+        <v>24527200</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B60" t="n">
+        <v>477.1010453906704</v>
+      </c>
+      <c r="C60" t="n">
+        <v>488.4850656489584</v>
+      </c>
+      <c r="D60" t="n">
+        <v>476.8017407441929</v>
+      </c>
+      <c r="E60" t="n">
+        <v>482.8778686523438</v>
+      </c>
+      <c r="F60" t="n">
+        <v>28573500</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B61" t="n">
+        <v>486.2501387748106</v>
+      </c>
+      <c r="C61" t="n">
+        <v>486.7390436209232</v>
+      </c>
+      <c r="D61" t="n">
+        <v>481.39123391446</v>
+      </c>
+      <c r="E61" t="n">
+        <v>484.8134460449219</v>
+      </c>
+      <c r="F61" t="n">
+        <v>70836100</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B62" t="n">
+        <v>485.0129839081317</v>
+      </c>
+      <c r="C62" t="n">
+        <v>487.6170561484318</v>
+      </c>
+      <c r="D62" t="n">
+        <v>481.5908021440126</v>
+      </c>
+      <c r="E62" t="n">
+        <v>483.8157348632812</v>
+      </c>
+      <c r="F62" t="n">
+        <v>16963000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B63" t="n">
+        <v>483.8755963136496</v>
+      </c>
+      <c r="C63" t="n">
+        <v>486.7190818282799</v>
+      </c>
+      <c r="D63" t="n">
+        <v>483.6361221459561</v>
+      </c>
+      <c r="E63" t="n">
+        <v>485.7413330078125</v>
+      </c>
+      <c r="F63" t="n">
+        <v>14683600</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B64" t="n">
+        <v>484.5739628623746</v>
+      </c>
+      <c r="C64" t="n">
+        <v>488.0460488858467</v>
+      </c>
+      <c r="D64" t="n">
+        <v>483.7258924615979</v>
+      </c>
+      <c r="E64" t="n">
+        <v>486.9086303710938</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5855900</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B65" t="n">
+        <v>485.601642461088</v>
+      </c>
+      <c r="C65" t="n">
+        <v>487.0084352251927</v>
+      </c>
+      <c r="D65" t="n">
+        <v>484.8533503811227</v>
+      </c>
+      <c r="E65" t="n">
+        <v>486.599365234375</v>
+      </c>
+      <c r="F65" t="n">
+        <v>8842200</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B66" t="n">
+        <v>483.7558335295542</v>
+      </c>
+      <c r="C66" t="n">
+        <v>487.2379065999322</v>
+      </c>
+      <c r="D66" t="n">
+        <v>483.0773893732932</v>
+      </c>
+      <c r="E66" t="n">
+        <v>485.9907531738281</v>
+      </c>
+      <c r="F66" t="n">
+        <v>10893400</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B67" t="n">
+        <v>484.8234150126488</v>
+      </c>
+      <c r="C67" t="n">
+        <v>488.5648753746365</v>
+      </c>
+      <c r="D67" t="n">
+        <v>484.3944015320139</v>
+      </c>
+      <c r="E67" t="n">
+        <v>486.3699035644531</v>
+      </c>
+      <c r="F67" t="n">
+        <v>13944500</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B68" t="n">
+        <v>486.7290680267604</v>
+      </c>
+      <c r="C68" t="n">
+        <v>487.0284031238816</v>
+      </c>
+      <c r="D68" t="n">
+        <v>482.1993981667827</v>
+      </c>
+      <c r="E68" t="n">
+        <v>482.5186767578125</v>
+      </c>
+      <c r="F68" t="n">
+        <v>15601600</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B69" t="n">
+        <v>483.2869444224563</v>
+      </c>
+      <c r="C69" t="n">
+        <v>483.5563186075122</v>
+      </c>
+      <c r="D69" t="n">
+        <v>469.0893385249197</v>
+      </c>
+      <c r="E69" t="n">
+        <v>471.8630065917969</v>
+      </c>
+      <c r="F69" t="n">
+        <v>25571600</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B70" t="n">
+        <v>472.9804293228547</v>
+      </c>
+      <c r="C70" t="n">
+        <v>474.9858617296903</v>
+      </c>
+      <c r="D70" t="n">
+        <v>468.4308161640092</v>
+      </c>
+      <c r="E70" t="n">
+        <v>471.773193359375</v>
+      </c>
+      <c r="F70" t="n">
+        <v>25250300</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B71" t="n">
+        <v>472.7210225701547</v>
+      </c>
+      <c r="C71" t="n">
+        <v>477.6497753472042</v>
+      </c>
+      <c r="D71" t="n">
+        <v>468.6802576477938</v>
+      </c>
+      <c r="E71" t="n">
+        <v>477.4203186035156</v>
+      </c>
+      <c r="F71" t="n">
+        <v>23037700</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B72" t="n">
+        <v>478.6674756822987</v>
+      </c>
+      <c r="C72" t="n">
+        <v>488.5848422406915</v>
+      </c>
+      <c r="D72" t="n">
+        <v>476.861599942913</v>
+      </c>
+      <c r="E72" t="n">
+        <v>482.3690185546875</v>
+      </c>
+      <c r="F72" t="n">
+        <v>25564200</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B73" t="n">
+        <v>480.1440867981462</v>
+      </c>
+      <c r="C73" t="n">
+        <v>481.5608665012806</v>
+      </c>
+      <c r="D73" t="n">
+        <v>474.7763335277468</v>
+      </c>
+      <c r="E73" t="n">
+        <v>477.0212097167969</v>
+      </c>
+      <c r="F73" t="n">
+        <v>18162600</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B74" t="n">
+        <v>472.9804540365218</v>
+      </c>
+      <c r="C74" t="n">
+        <v>478.7273469366413</v>
+      </c>
+      <c r="D74" t="n">
+        <v>471.1247042989064</v>
+      </c>
+      <c r="E74" t="n">
+        <v>478.1885681152344</v>
+      </c>
+      <c r="F74" t="n">
+        <v>18491000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B75" t="n">
+        <v>475.5845048686955</v>
+      </c>
+      <c r="C75" t="n">
+        <v>479.894643901475</v>
+      </c>
+      <c r="D75" t="n">
+        <v>474.5967386659474</v>
+      </c>
+      <c r="E75" t="n">
+        <v>476.0933227539062</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23519900</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B76" t="n">
+        <v>473.5990225282599</v>
+      </c>
+      <c r="C76" t="n">
+        <v>474.6965236309785</v>
+      </c>
+      <c r="D76" t="n">
+        <v>464.888922501957</v>
+      </c>
+      <c r="E76" t="n">
+        <v>469.5981750488281</v>
+      </c>
+      <c r="F76" t="n">
+        <v>28545800</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B77" t="n">
+        <v>465.3977566654985</v>
+      </c>
+      <c r="C77" t="n">
+        <v>467.1338149970701</v>
+      </c>
+      <c r="D77" t="n">
+        <v>456.1289340170423</v>
+      </c>
+      <c r="E77" t="n">
+        <v>458.3338928222656</v>
+      </c>
+      <c r="F77" t="n">
+        <v>28184300</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B78" t="n">
+        <v>463.0630900555096</v>
+      </c>
+      <c r="C78" t="n">
+        <v>463.1927988881192</v>
+      </c>
+      <c r="D78" t="n">
+        <v>454.8618076165624</v>
+      </c>
+      <c r="E78" t="n">
+        <v>455.6200866699219</v>
+      </c>
+      <c r="F78" t="n">
+        <v>23225800</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B79" t="n">
+        <v>456.7873986695315</v>
+      </c>
+      <c r="C79" t="n">
+        <v>462.1352085061545</v>
+      </c>
+      <c r="D79" t="n">
+        <v>455.4404972994736</v>
+      </c>
+      <c r="E79" t="n">
+        <v>458.8127746582031</v>
+      </c>
+      <c r="F79" t="n">
+        <v>34246700</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B80" t="n">
+        <v>450.1924514863621</v>
+      </c>
+      <c r="C80" t="n">
+        <v>455.7597309230742</v>
+      </c>
+      <c r="D80" t="n">
+        <v>448.2568669541529</v>
+      </c>
+      <c r="E80" t="n">
+        <v>453.4849243164062</v>
+      </c>
+      <c r="F80" t="n">
+        <v>26130000</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B81" t="n">
+        <v>451.5693196059127</v>
+      </c>
+      <c r="C81" t="n">
+        <v>451.6591109990197</v>
+      </c>
+      <c r="D81" t="n">
+        <v>437.6810056251358</v>
+      </c>
+      <c r="E81" t="n">
+        <v>443.0986328125</v>
+      </c>
+      <c r="F81" t="n">
+        <v>37980500</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B82" t="n">
+        <v>446.600636936346</v>
+      </c>
+      <c r="C82" t="n">
+        <v>451.8087507279656</v>
+      </c>
+      <c r="D82" t="n">
+        <v>443.6873036586902</v>
+      </c>
+      <c r="E82" t="n">
+        <v>450.1126403808594</v>
+      </c>
+      <c r="F82" t="n">
+        <v>25349400</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B83" t="n">
+        <v>450.8409629929935</v>
+      </c>
+      <c r="C83" t="n">
+        <v>470.0271819611143</v>
+      </c>
+      <c r="D83" t="n">
+        <v>449.5040181949105</v>
+      </c>
+      <c r="E83" t="n">
+        <v>464.888916015625</v>
+      </c>
+      <c r="F83" t="n">
+        <v>38000200</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B84" t="n">
+        <v>464.2503622118351</v>
+      </c>
+      <c r="C84" t="n">
+        <v>473.1700058760031</v>
+      </c>
+      <c r="D84" t="n">
+        <v>460.9479024031912</v>
+      </c>
+      <c r="E84" t="n">
+        <v>469.2090454101562</v>
+      </c>
+      <c r="F84" t="n">
+        <v>29291200</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B85" t="n">
+        <v>472.62128861771</v>
+      </c>
+      <c r="C85" t="n">
+        <v>481.7703893732875</v>
+      </c>
+      <c r="D85" t="n">
+        <v>472.0825097961169</v>
+      </c>
+      <c r="E85" t="n">
+        <v>479.485595703125</v>
+      </c>
+      <c r="F85" t="n">
+        <v>29213900</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B86" t="n">
+        <v>482.1095916405993</v>
+      </c>
+      <c r="C86" t="n">
+        <v>482.6383834693597</v>
+      </c>
+      <c r="D86" t="n">
+        <v>476.9114647448887</v>
+      </c>
+      <c r="E86" t="n">
+        <v>480.533203125</v>
+      </c>
+      <c r="F86" t="n">
+        <v>36875400</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B87" t="n">
+        <v>438.9880283656418</v>
+      </c>
+      <c r="C87" t="n">
+        <v>441.4923222419712</v>
+      </c>
+      <c r="D87" t="n">
+        <v>420.0612263501361</v>
+      </c>
+      <c r="E87" t="n">
+        <v>432.5128173828125</v>
+      </c>
+      <c r="F87" t="n">
+        <v>128855300</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B88" t="n">
+        <v>438.1699022937122</v>
+      </c>
+      <c r="C88" t="n">
+        <v>438.5989157576861</v>
+      </c>
+      <c r="D88" t="n">
+        <v>425.4788680207893</v>
+      </c>
+      <c r="E88" t="n">
+        <v>429.3101196289062</v>
+      </c>
+      <c r="F88" t="n">
+        <v>58566800</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B89" t="n">
+        <v>429.2602343395754</v>
+      </c>
+      <c r="C89" t="n">
+        <v>429.7590957240154</v>
+      </c>
+      <c r="D89" t="n">
+        <v>421.28843915961</v>
+      </c>
+      <c r="E89" t="n">
+        <v>422.4058837890625</v>
+      </c>
+      <c r="F89" t="n">
+        <v>42219900</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B90" t="n">
+        <v>421.0489834358989</v>
+      </c>
+      <c r="C90" t="n">
+        <v>421.0888704228976</v>
+      </c>
+      <c r="D90" t="n">
+        <v>407.6296003977664</v>
+      </c>
+      <c r="E90" t="n">
+        <v>410.2735595703125</v>
+      </c>
+      <c r="F90" t="n">
+        <v>61424100</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B91" t="n">
+        <v>410.0640575889883</v>
+      </c>
+      <c r="C91" t="n">
+        <v>418.8440057668918</v>
+      </c>
+      <c r="D91" t="n">
+        <v>408.3080557741746</v>
+      </c>
+      <c r="E91" t="n">
+        <v>413.2467956542969</v>
+      </c>
+      <c r="F91" t="n">
+        <v>45012400</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B92" t="n">
+        <v>406.5121603821183</v>
+      </c>
+      <c r="C92" t="n">
+        <v>407.3701873334875</v>
+      </c>
+      <c r="D92" t="n">
+        <v>391.4265972483441</v>
+      </c>
+      <c r="E92" t="n">
+        <v>392.7735290527344</v>
+      </c>
+      <c r="F92" t="n">
+        <v>66289200</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B93" t="n">
+        <v>398.2609865133262</v>
+      </c>
+      <c r="C93" t="n">
+        <v>400.875015135043</v>
+      </c>
+      <c r="D93" t="n">
+        <v>392.0252195920243</v>
+      </c>
+      <c r="E93" t="n">
+        <v>400.2265014648438</v>
+      </c>
+      <c r="F93" t="n">
+        <v>53515300</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B94" t="n">
+        <v>403.9280678877113</v>
+      </c>
+      <c r="C94" t="n">
+        <v>413.9452129833927</v>
+      </c>
+      <c r="D94" t="n">
+        <v>399.9571203178888</v>
+      </c>
+      <c r="E94" t="n">
+        <v>412.6581420898438</v>
+      </c>
+      <c r="F94" t="n">
+        <v>45480500</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B95" t="n">
+        <v>418.6644027817824</v>
+      </c>
+      <c r="C95" t="n">
+        <v>422.7151545880433</v>
+      </c>
+      <c r="D95" t="n">
+        <v>411.76017861217</v>
+      </c>
+      <c r="E95" t="n">
+        <v>412.328857421875</v>
+      </c>
+      <c r="F95" t="n">
+        <v>44857900</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B96" t="n">
+        <v>415.2322299614449</v>
+      </c>
+      <c r="C96" t="n">
+        <v>415.5115911022014</v>
+      </c>
+      <c r="D96" t="n">
+        <v>400.096793508188</v>
+      </c>
+      <c r="E96" t="n">
+        <v>403.4491271972656</v>
+      </c>
+      <c r="F96" t="n">
+        <v>42491000</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B97" t="n">
+        <v>404.0777037056333</v>
+      </c>
+      <c r="C97" t="n">
+        <v>405.2749831551046</v>
+      </c>
+      <c r="D97" t="n">
+        <v>397.1036315998776</v>
+      </c>
+      <c r="E97" t="n">
+        <v>400.9248962402344</v>
+      </c>
+      <c r="F97" t="n">
+        <v>40802400</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B98" t="n">
+        <v>403.528974460687</v>
+      </c>
+      <c r="C98" t="n">
+        <v>404.6164885937555</v>
+      </c>
+      <c r="D98" t="n">
+        <v>397.1435245648219</v>
+      </c>
+      <c r="E98" t="n">
+        <v>400.4060974121094</v>
+      </c>
+      <c r="F98" t="n">
+        <v>34091600</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B99" t="n">
+        <v>398.3108793269315</v>
+      </c>
+      <c r="C99" t="n">
+        <v>399.6079067287359</v>
+      </c>
+      <c r="D99" t="n">
+        <v>393.6315571718042</v>
+      </c>
+      <c r="E99" t="n">
+        <v>395.9562377929688</v>
+      </c>
+      <c r="F99" t="n">
+        <v>32078800</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B100" t="n">
+        <v>397.2233488345012</v>
+      </c>
+      <c r="C100" t="n">
+        <v>401.6432531481791</v>
+      </c>
+      <c r="D100" t="n">
+        <v>395.4174731587443</v>
+      </c>
+      <c r="E100" t="n">
+        <v>398.6900024414062</v>
+      </c>
+      <c r="F100" t="n">
+        <v>23223400</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B101" t="n">
+        <v>400.6900024414062</v>
+      </c>
+      <c r="C101" t="n">
+        <v>404.4299926757812</v>
+      </c>
+      <c r="D101" t="n">
+        <v>396.6700134277344</v>
+      </c>
+      <c r="E101" t="n">
+        <v>398.4599914550781</v>
+      </c>
+      <c r="F101" t="n">
+        <v>28234000</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B102" t="n">
+        <v>396.1099853515625</v>
+      </c>
+      <c r="C102" t="n">
+        <v>400.1199951171875</v>
+      </c>
+      <c r="D102" t="n">
+        <v>395.1600036621094</v>
+      </c>
+      <c r="E102" t="n">
+        <v>397.2300109863281</v>
+      </c>
+      <c r="F102" t="n">
+        <v>34015200</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B103" t="n">
+        <v>395</v>
+      </c>
+      <c r="C103" t="n">
+        <v>395.3599853515625</v>
+      </c>
+      <c r="D103" t="n">
+        <v>383.1000061035156</v>
+      </c>
+      <c r="E103" t="n">
+        <v>384.4700012207031</v>
+      </c>
+      <c r="F103" t="n">
+        <v>43238300</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B104" t="n">
+        <v>384.1400146484375</v>
+      </c>
+      <c r="C104" t="n">
+        <v>389.3599853515625</v>
+      </c>
+      <c r="D104" t="n">
+        <v>381.7099914550781</v>
+      </c>
+      <c r="E104" t="n">
+        <v>389</v>
+      </c>
+      <c r="F104" t="n">
+        <v>33884700</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B105" t="n">
+        <v>390.5299987792969</v>
+      </c>
+      <c r="C105" t="n">
+        <v>401.4700012207031</v>
+      </c>
+      <c r="D105" t="n">
+        <v>390.1600036621094</v>
+      </c>
+      <c r="E105" t="n">
+        <v>400.6000061035156</v>
+      </c>
+      <c r="F105" t="n">
+        <v>43625500</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B106" t="n">
+        <v>404.7099914550781</v>
+      </c>
+      <c r="C106" t="n">
+        <v>407.489990234375</v>
+      </c>
+      <c r="D106" t="n">
+        <v>398.739990234375</v>
+      </c>
+      <c r="E106" t="n">
+        <v>401.7200012207031</v>
+      </c>
+      <c r="F106" t="n">
+        <v>34405900</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B107" t="n">
+        <v>390.8800048828125</v>
+      </c>
+      <c r="C107" t="n">
+        <v>396.8200073242188</v>
+      </c>
+      <c r="D107" t="n">
+        <v>389.8800048828125</v>
+      </c>
+      <c r="E107" t="n">
+        <v>392.739990234375</v>
+      </c>
+      <c r="F107" t="n">
+        <v>51367200</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B108" t="n">
+        <v>392.8599853515625</v>
+      </c>
+      <c r="C108" t="n">
+        <v>401.1900024414062</v>
+      </c>
+      <c r="D108" t="n">
+        <v>390.6300048828125</v>
+      </c>
+      <c r="E108" t="n">
+        <v>398.5499877929688</v>
+      </c>
+      <c r="F108" t="n">
+        <v>35474900</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B109" t="n">
+        <v>393.1400146484375</v>
+      </c>
+      <c r="C109" t="n">
+        <v>406.7000122070312</v>
+      </c>
+      <c r="D109" t="n">
+        <v>392.6700134277344</v>
+      </c>
+      <c r="E109" t="n">
+        <v>403.9299926757812</v>
+      </c>
+      <c r="F109" t="n">
+        <v>38199200</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B110" t="n">
+        <v>401.2699890136719</v>
+      </c>
+      <c r="C110" t="n">
+        <v>411.0299987792969</v>
+      </c>
+      <c r="D110" t="n">
+        <v>400.3099975585938</v>
+      </c>
+      <c r="E110" t="n">
+        <v>405.2000122070312</v>
+      </c>
+      <c r="F110" t="n">
+        <v>35808000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B111" t="n">
+        <v>404.4200134277344</v>
+      </c>
+      <c r="C111" t="n">
+        <v>411.6099853515625</v>
+      </c>
+      <c r="D111" t="n">
+        <v>404.3999938964844</v>
+      </c>
+      <c r="E111" t="n">
+        <v>410.6799926757812</v>
+      </c>
+      <c r="F111" t="n">
+        <v>39001300</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B112" t="n">
+        <v>409.2000122070312</v>
+      </c>
+      <c r="C112" t="n">
+        <v>413.0499877929688</v>
+      </c>
+      <c r="D112" t="n">
+        <v>408.510009765625</v>
+      </c>
+      <c r="E112" t="n">
+        <v>408.9599914550781</v>
+      </c>
+      <c r="F112" t="n">
+        <v>31123900</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B113" t="n">
+        <v>404.9200134277344</v>
+      </c>
+      <c r="C113" t="n">
+        <v>410.2099914550781</v>
+      </c>
+      <c r="D113" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="E113" t="n">
+        <v>409.4100036621094</v>
+      </c>
+      <c r="F113" t="n">
+        <v>30131900</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B114" t="n">
+        <v>410.0299987792969</v>
+      </c>
+      <c r="C114" t="n">
+        <v>410.2000122070312</v>
+      </c>
+      <c r="D114" t="n">
+        <v>402.9299926757812</v>
+      </c>
+      <c r="E114" t="n">
+        <v>405.760009765625</v>
+      </c>
+      <c r="F114" t="n">
+        <v>31706400</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B115" t="n">
+        <v>405.5700073242188</v>
+      </c>
+      <c r="C115" t="n">
+        <v>409.010009765625</v>
+      </c>
+      <c r="D115" t="n">
+        <v>401.5899963378906</v>
+      </c>
+      <c r="E115" t="n">
+        <v>404.8800048828125</v>
+      </c>
+      <c r="F115" t="n">
+        <v>25512100</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B116" t="n">
+        <v>404.6300048828125</v>
+      </c>
+      <c r="C116" t="n">
+        <v>406.1199951171875</v>
+      </c>
+      <c r="D116" t="n">
+        <v>401.7099914550781</v>
+      </c>
+      <c r="E116" t="n">
+        <v>401.8599853515625</v>
+      </c>
+      <c r="F116" t="n">
+        <v>27263900</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B117" t="n">
+        <v>401</v>
+      </c>
+      <c r="C117" t="n">
+        <v>404.7999877929688</v>
+      </c>
+      <c r="D117" t="n">
+        <v>394.25</v>
+      </c>
+      <c r="E117" t="n">
+        <v>395.5499877929688</v>
+      </c>
+      <c r="F117" t="n">
+        <v>26848000</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B118" t="n">
+        <v>398.0700073242188</v>
+      </c>
+      <c r="C118" t="n">
+        <v>400.6300048828125</v>
+      </c>
+      <c r="D118" t="n">
+        <v>394.7900085449219</v>
+      </c>
+      <c r="E118" t="n">
+        <v>399.9500122070312</v>
+      </c>
+      <c r="F118" t="n">
+        <v>27733700</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B119" t="n">
+        <v>400.2699890136719</v>
+      </c>
+      <c r="C119" t="n">
+        <v>404.3999938964844</v>
+      </c>
+      <c r="D119" t="n">
+        <v>397.75</v>
+      </c>
+      <c r="E119" t="n">
+        <v>399.4100036621094</v>
+      </c>
+      <c r="F119" t="n">
+        <v>26228300</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B120" t="n">
+        <v>397.1300048828125</v>
+      </c>
+      <c r="C120" t="n">
+        <v>398</v>
+      </c>
+      <c r="D120" t="n">
+        <v>391</v>
+      </c>
+      <c r="E120" t="n">
+        <v>391.7900085449219</v>
+      </c>
+      <c r="F120" t="n">
+        <v>25908500</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B121" t="n">
+        <v>390.1000061035156</v>
+      </c>
+      <c r="C121" t="n">
+        <v>392.489990234375</v>
+      </c>
+      <c r="D121" t="n">
+        <v>387.0599975585938</v>
+      </c>
+      <c r="E121" t="n">
+        <v>389.0199890136719</v>
+      </c>
+      <c r="F121" t="n">
+        <v>25138800</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B122" t="n">
+        <v>386.7900085449219</v>
+      </c>
+      <c r="C122" t="n">
+        <v>387</v>
+      </c>
+      <c r="D122" t="n">
+        <v>380.1199951171875</v>
+      </c>
+      <c r="E122" t="n">
+        <v>381.8699951171875</v>
+      </c>
+      <c r="F122" t="n">
+        <v>50853200</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B123" t="n">
+        <v>383.8999938964844</v>
+      </c>
+      <c r="C123" t="n">
+        <v>387.2099914550781</v>
+      </c>
+      <c r="D123" t="n">
+        <v>381.6799926757812</v>
+      </c>
+      <c r="E123" t="n">
+        <v>383</v>
+      </c>
+      <c r="F123" t="n">
+        <v>29680100</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B124" t="n">
+        <v>382.3599853515625</v>
+      </c>
+      <c r="C124" t="n">
+        <v>382.4700012207031</v>
+      </c>
+      <c r="D124" t="n">
+        <v>371.8500061035156</v>
+      </c>
+      <c r="E124" t="n">
+        <v>372.739990234375</v>
+      </c>
+      <c r="F124" t="n">
+        <v>42636600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/stock_data.xlsx
+++ b/stock_data.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,2462 +470,2482 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B2" t="n">
-        <v>655.7760789419195</v>
+        <v>660.5985670660314</v>
       </c>
       <c r="C2" t="n">
-        <v>658.619871988132</v>
+        <v>661.5134019828115</v>
       </c>
       <c r="D2" t="n">
-        <v>654.1553026157394</v>
+        <v>658.112721358766</v>
       </c>
       <c r="E2" t="n">
-        <v>658.072998046875</v>
+        <v>659.9224243164062</v>
       </c>
       <c r="F2" t="n">
-        <v>69179200</v>
+        <v>73499000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B3" t="n">
-        <v>660.5985670660314</v>
+        <v>659.1766647693167</v>
       </c>
       <c r="C3" t="n">
-        <v>661.5134019828115</v>
+        <v>662.8756347075731</v>
       </c>
       <c r="D3" t="n">
-        <v>658.112721358766</v>
+        <v>657.8641309647478</v>
       </c>
       <c r="E3" t="n">
-        <v>659.9224243164062</v>
+        <v>662.4082641601562</v>
       </c>
       <c r="F3" t="n">
-        <v>73499000</v>
+        <v>86288000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B4" t="n">
-        <v>659.1766647693167</v>
+        <v>659.4152702620313</v>
       </c>
       <c r="C4" t="n">
-        <v>662.8756347075731</v>
+        <v>665.5801794564833</v>
       </c>
       <c r="D4" t="n">
-        <v>657.8641309647478</v>
+        <v>659.3059076216911</v>
       </c>
       <c r="E4" t="n">
-        <v>662.4082641601562</v>
+        <v>664.6654052734375</v>
       </c>
       <c r="F4" t="n">
-        <v>86288000</v>
+        <v>72545400</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B5" t="n">
-        <v>659.4153308150761</v>
+        <v>666.6540464714482</v>
       </c>
       <c r="C5" t="n">
-        <v>665.5802405756418</v>
+        <v>666.7733621981591</v>
       </c>
       <c r="D5" t="n">
-        <v>659.3059681646932</v>
+        <v>663.004842335434</v>
       </c>
       <c r="E5" t="n">
-        <v>664.6654663085938</v>
+        <v>665.4309692382812</v>
       </c>
       <c r="F5" t="n">
-        <v>72545400</v>
+        <v>56896000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B6" t="n">
-        <v>666.6540464714482</v>
+        <v>666.1966948783695</v>
       </c>
       <c r="C6" t="n">
-        <v>666.7733621981591</v>
+        <v>668.8714672806448</v>
       </c>
       <c r="D6" t="n">
-        <v>663.004842335434</v>
+        <v>664.377038831869</v>
       </c>
       <c r="E6" t="n">
-        <v>665.4309692382812</v>
+        <v>665.421142578125</v>
       </c>
       <c r="F6" t="n">
-        <v>56896000</v>
+        <v>70494400</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B7" t="n">
-        <v>666.1966948783695</v>
+        <v>667.8174482099862</v>
       </c>
       <c r="C7" t="n">
-        <v>668.8714672806448</v>
+        <v>668.7024238148077</v>
       </c>
       <c r="D7" t="n">
-        <v>664.377038831869</v>
+        <v>665.6697043011241</v>
       </c>
       <c r="E7" t="n">
-        <v>665.421142578125</v>
+        <v>667.8074951171875</v>
       </c>
       <c r="F7" t="n">
-        <v>70494400</v>
+        <v>54623300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B8" t="n">
-        <v>667.8174482099862</v>
+        <v>668.7322238208072</v>
       </c>
       <c r="C8" t="n">
-        <v>668.7024238148077</v>
+        <v>669.1796881705657</v>
       </c>
       <c r="D8" t="n">
-        <v>665.6697043011241</v>
+        <v>663.8898014056139</v>
       </c>
       <c r="E8" t="n">
-        <v>667.8074951171875</v>
+        <v>665.3316040039062</v>
       </c>
       <c r="F8" t="n">
-        <v>54623300</v>
+        <v>72020100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B9" t="n">
-        <v>668.7322238208072</v>
+        <v>666.4552183740389</v>
       </c>
       <c r="C9" t="n">
-        <v>669.1796881705657</v>
+        <v>669.3984814701651</v>
       </c>
       <c r="D9" t="n">
-        <v>663.8898014056139</v>
+        <v>665.6299006256374</v>
       </c>
       <c r="E9" t="n">
-        <v>665.3316040039062</v>
+        <v>669.2990112304688</v>
       </c>
       <c r="F9" t="n">
-        <v>72020100</v>
+        <v>60702200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B10" t="n">
-        <v>666.4552183740389</v>
+        <v>669.7166839203261</v>
       </c>
       <c r="C10" t="n">
-        <v>669.3984814701651</v>
+        <v>670.1243359074817</v>
       </c>
       <c r="D10" t="n">
-        <v>665.6299006256374</v>
+        <v>665.4211353124821</v>
       </c>
       <c r="E10" t="n">
-        <v>669.2990112304688</v>
+        <v>667.3600463867188</v>
       </c>
       <c r="F10" t="n">
-        <v>60702200</v>
+        <v>66501900</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B11" t="n">
-        <v>669.7166839203261</v>
+        <v>668.324542434099</v>
       </c>
       <c r="C11" t="n">
-        <v>670.1243359074817</v>
+        <v>670.1342452495495</v>
       </c>
       <c r="D11" t="n">
-        <v>665.4211353124821</v>
+        <v>649.1437803121401</v>
       </c>
       <c r="E11" t="n">
-        <v>667.3600463867188</v>
+        <v>649.32275390625</v>
       </c>
       <c r="F11" t="n">
-        <v>66501900</v>
+        <v>159422600</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B12" t="n">
-        <v>668.324542434099</v>
+        <v>656.9095884512618</v>
       </c>
       <c r="C12" t="n">
-        <v>670.1342452495495</v>
+        <v>661.3642043859337</v>
       </c>
       <c r="D12" t="n">
-        <v>649.1437803121401</v>
+        <v>656.0345659370097</v>
       </c>
       <c r="E12" t="n">
-        <v>649.32275390625</v>
+        <v>659.2860107421875</v>
       </c>
       <c r="F12" t="n">
-        <v>159422600</v>
+        <v>79560500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B13" t="n">
-        <v>656.9095884512618</v>
+        <v>653.4492417720955</v>
       </c>
       <c r="C13" t="n">
-        <v>661.3642043859337</v>
+        <v>662.0602448848334</v>
       </c>
       <c r="D13" t="n">
-        <v>656.0345659370097</v>
+        <v>649.4718888267987</v>
       </c>
       <c r="E13" t="n">
-        <v>659.2860107421875</v>
+        <v>658.4805908203125</v>
       </c>
       <c r="F13" t="n">
-        <v>79560500</v>
+        <v>88779600</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B14" t="n">
-        <v>653.4492417720955</v>
+        <v>663.0446129876665</v>
       </c>
       <c r="C14" t="n">
-        <v>662.0602448848334</v>
+        <v>666.4352795829697</v>
       </c>
       <c r="D14" t="n">
-        <v>649.4718888267987</v>
+        <v>655.1992699391986</v>
       </c>
       <c r="E14" t="n">
-        <v>658.4805908203125</v>
+        <v>661.4039306640625</v>
       </c>
       <c r="F14" t="n">
-        <v>88779600</v>
+        <v>81702600</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B15" t="n">
-        <v>663.0446741742268</v>
+        <v>663.0445999065358</v>
       </c>
       <c r="C15" t="n">
-        <v>666.4353410824248</v>
+        <v>664.9239136533134</v>
       </c>
       <c r="D15" t="n">
-        <v>655.1993304017814</v>
+        <v>653.3895542222015</v>
       </c>
       <c r="E15" t="n">
-        <v>661.4039916992188</v>
+        <v>656.8995971679688</v>
       </c>
       <c r="F15" t="n">
-        <v>81702600</v>
+        <v>110563300</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B16" t="n">
-        <v>663.0446615126489</v>
+        <v>655.7660892614911</v>
       </c>
       <c r="C16" t="n">
-        <v>664.9239754340409</v>
+        <v>661.9906565438909</v>
       </c>
       <c r="D16" t="n">
-        <v>653.3896149312258</v>
+        <v>654.4138037793879</v>
       </c>
       <c r="E16" t="n">
-        <v>656.899658203125</v>
+        <v>660.62841796875</v>
       </c>
       <c r="F16" t="n">
-        <v>110563300</v>
+        <v>96500900</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B17" t="n">
-        <v>655.7660892614911</v>
+        <v>663.5418206897375</v>
       </c>
       <c r="C17" t="n">
-        <v>661.9906565438909</v>
+        <v>668.4041493887289</v>
       </c>
       <c r="D17" t="n">
-        <v>654.4138037793879</v>
+        <v>663.4921159142255</v>
       </c>
       <c r="E17" t="n">
-        <v>660.62841796875</v>
+        <v>667.499267578125</v>
       </c>
       <c r="F17" t="n">
-        <v>96500900</v>
+        <v>60493400</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B18" t="n">
-        <v>663.5418206897375</v>
+        <v>667.638493864759</v>
       </c>
       <c r="C18" t="n">
-        <v>668.4041493887289</v>
+        <v>669.1797060532549</v>
       </c>
       <c r="D18" t="n">
-        <v>663.4921159142255</v>
+        <v>666.1867381348511</v>
       </c>
       <c r="E18" t="n">
-        <v>667.499267578125</v>
+        <v>667.4893188476562</v>
       </c>
       <c r="F18" t="n">
-        <v>60493400</v>
+        <v>56249000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B19" t="n">
-        <v>667.6384328159621</v>
+        <v>668.1953369980629</v>
       </c>
       <c r="C19" t="n">
-        <v>669.1796448635298</v>
+        <v>668.1953369980629</v>
       </c>
       <c r="D19" t="n">
-        <v>666.1866772188026</v>
+        <v>659.5445816579371</v>
       </c>
       <c r="E19" t="n">
-        <v>667.4892578125</v>
+        <v>664.0191040039062</v>
       </c>
       <c r="F19" t="n">
-        <v>56249000</v>
+        <v>80564000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B20" t="n">
-        <v>668.1953369980629</v>
+        <v>664.3372592841532</v>
       </c>
       <c r="C20" t="n">
-        <v>668.1953369980629</v>
+        <v>668.9012985038863</v>
       </c>
       <c r="D20" t="n">
-        <v>659.5445816579371</v>
+        <v>664.019063764971</v>
       </c>
       <c r="E20" t="n">
-        <v>664.0191040039062</v>
+        <v>667.9566650390625</v>
       </c>
       <c r="F20" t="n">
-        <v>80564000</v>
+        <v>65604500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B21" t="n">
-        <v>664.3372592841532</v>
+        <v>672.6300829996666</v>
       </c>
       <c r="C21" t="n">
-        <v>668.9012985038863</v>
+        <v>674.628651928334</v>
       </c>
       <c r="D21" t="n">
-        <v>664.019063764971</v>
+        <v>671.8246714345047</v>
       </c>
       <c r="E21" t="n">
-        <v>667.9566650390625</v>
+        <v>673.4155883789062</v>
       </c>
       <c r="F21" t="n">
-        <v>65604500</v>
+        <v>74356500</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B22" t="n">
-        <v>672.6300829996666</v>
+        <v>678.8645527756448</v>
       </c>
       <c r="C22" t="n">
-        <v>674.628651928334</v>
+        <v>681.658640907831</v>
       </c>
       <c r="D22" t="n">
-        <v>671.8246714345047</v>
+        <v>678.2580209918731</v>
       </c>
       <c r="E22" t="n">
-        <v>673.4155883789062</v>
+        <v>681.3603515625</v>
       </c>
       <c r="F22" t="n">
-        <v>74356500</v>
+        <v>63339800</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B23" t="n">
-        <v>678.8645527756448</v>
+        <v>683.1600908523567</v>
       </c>
       <c r="C23" t="n">
-        <v>681.658640907831</v>
+        <v>685.0095454543999</v>
       </c>
       <c r="D23" t="n">
-        <v>678.2580209918731</v>
+        <v>680.9526890414517</v>
       </c>
       <c r="E23" t="n">
-        <v>681.3603515625</v>
+        <v>683.1700439453125</v>
       </c>
       <c r="F23" t="n">
-        <v>63339800</v>
+        <v>61738100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B24" t="n">
-        <v>683.1600908523567</v>
+        <v>684.8206562449755</v>
       </c>
       <c r="C24" t="n">
-        <v>685.0095454543999</v>
+        <v>685.795149064121</v>
       </c>
       <c r="D24" t="n">
-        <v>680.9526890414517</v>
+        <v>679.0038013689816</v>
       </c>
       <c r="E24" t="n">
-        <v>683.1700439453125</v>
+        <v>683.4982299804688</v>
       </c>
       <c r="F24" t="n">
-        <v>61738100</v>
+        <v>85657100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B25" t="n">
-        <v>684.8205950917289</v>
+        <v>680.0279821977349</v>
       </c>
       <c r="C25" t="n">
-        <v>685.795087823854</v>
+        <v>682.0564104652303</v>
       </c>
       <c r="D25" t="n">
-        <v>679.0037407351697</v>
+        <v>675.9810180664062</v>
       </c>
       <c r="E25" t="n">
-        <v>683.4981689453125</v>
+        <v>675.9810180664062</v>
       </c>
       <c r="F25" t="n">
-        <v>85657100</v>
+        <v>76335800</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B26" t="n">
-        <v>680.0279207971732</v>
+        <v>681.1614116072222</v>
       </c>
       <c r="C26" t="n">
-        <v>682.0563488815194</v>
+        <v>681.2012239761448</v>
       </c>
       <c r="D26" t="n">
-        <v>675.98095703125</v>
+        <v>675.3942622450203</v>
       </c>
       <c r="E26" t="n">
-        <v>675.98095703125</v>
+        <v>678.1983032226562</v>
       </c>
       <c r="F26" t="n">
-        <v>76335800</v>
+        <v>87164100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B27" t="n">
-        <v>681.1614729090464</v>
+        <v>681.7878948104295</v>
       </c>
       <c r="C27" t="n">
-        <v>681.2012852815519</v>
+        <v>681.9171636388411</v>
       </c>
       <c r="D27" t="n">
-        <v>675.3943230278239</v>
+        <v>676.0903560257897</v>
       </c>
       <c r="E27" t="n">
-        <v>678.1983642578125</v>
+        <v>679.4711303710938</v>
       </c>
       <c r="F27" t="n">
-        <v>87164100</v>
+        <v>57315000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B28" t="n">
-        <v>681.7878948104295</v>
+        <v>672.2820616639051</v>
       </c>
       <c r="C28" t="n">
-        <v>681.9171636388411</v>
+        <v>676.1103005794487</v>
       </c>
       <c r="D28" t="n">
-        <v>676.0903560257897</v>
+        <v>670.7607556049009</v>
       </c>
       <c r="E28" t="n">
-        <v>679.4711303710938</v>
+        <v>671.4169921875</v>
       </c>
       <c r="F28" t="n">
-        <v>57315000</v>
+        <v>78427000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B29" t="n">
-        <v>672.2820616639051</v>
+        <v>671.1583975728993</v>
       </c>
       <c r="C29" t="n">
-        <v>676.1103005794487</v>
+        <v>677.0051112074705</v>
       </c>
       <c r="D29" t="n">
-        <v>670.7607556049009</v>
+        <v>670.3529860359731</v>
       </c>
       <c r="E29" t="n">
-        <v>671.4169921875</v>
+        <v>673.7437133789062</v>
       </c>
       <c r="F29" t="n">
-        <v>78427000</v>
+        <v>74402400</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B30" t="n">
-        <v>671.1583975728993</v>
+        <v>672.6399897028363</v>
       </c>
       <c r="C30" t="n">
-        <v>677.0051112074705</v>
+        <v>673.5448715272548</v>
       </c>
       <c r="D30" t="n">
-        <v>670.3529860359731</v>
+        <v>664.9338680034818</v>
       </c>
       <c r="E30" t="n">
-        <v>673.7437133789062</v>
+        <v>666.514892578125</v>
       </c>
       <c r="F30" t="n">
-        <v>74402400</v>
+        <v>85035300</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B31" t="n">
-        <v>672.6399897028363</v>
+        <v>664.1284090392404</v>
       </c>
       <c r="C31" t="n">
-        <v>673.5448715272548</v>
+        <v>667.2805048704689</v>
       </c>
       <c r="D31" t="n">
-        <v>664.9338680034818</v>
+        <v>657.4663915648358</v>
       </c>
       <c r="E31" t="n">
-        <v>666.514892578125</v>
+        <v>667.1710815429688</v>
       </c>
       <c r="F31" t="n">
-        <v>85035300</v>
+        <v>100592400</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B32" t="n">
-        <v>664.1284090392404</v>
+        <v>673.4056154266486</v>
       </c>
       <c r="C32" t="n">
-        <v>667.2805048704689</v>
+        <v>678.3176487268574</v>
       </c>
       <c r="D32" t="n">
-        <v>657.4663915648358</v>
+        <v>671.2081667723378</v>
       </c>
       <c r="E32" t="n">
-        <v>667.1710815429688</v>
+        <v>677.5818481445312</v>
       </c>
       <c r="F32" t="n">
-        <v>100592400</v>
+        <v>75842900</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B33" t="n">
-        <v>673.4056760856186</v>
+        <v>676.1002762110339</v>
       </c>
       <c r="C33" t="n">
-        <v>678.317709828293</v>
+        <v>679.6997756663966</v>
       </c>
       <c r="D33" t="n">
-        <v>671.2082272333661</v>
+        <v>674.8871520395073</v>
       </c>
       <c r="E33" t="n">
-        <v>677.5819091796875</v>
+        <v>679.1329956054688</v>
       </c>
       <c r="F33" t="n">
-        <v>75842900</v>
+        <v>58953400</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B34" t="n">
-        <v>676.1002762110339</v>
+        <v>680.9129156193362</v>
       </c>
       <c r="C34" t="n">
-        <v>679.6997756663966</v>
+        <v>681.0819968300743</v>
       </c>
       <c r="D34" t="n">
-        <v>674.8871520395073</v>
+        <v>677.0946904605516</v>
       </c>
       <c r="E34" t="n">
-        <v>679.1329956054688</v>
+        <v>679.5109252929688</v>
       </c>
       <c r="F34" t="n">
-        <v>58953400</v>
+        <v>62312500</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B35" t="n">
-        <v>680.9128544582501</v>
+        <v>676.6472315164618</v>
       </c>
       <c r="C35" t="n">
-        <v>681.081935653801</v>
+        <v>677.0051787486752</v>
       </c>
       <c r="D35" t="n">
-        <v>677.0946296424269</v>
+        <v>666.7237544337754</v>
       </c>
       <c r="E35" t="n">
-        <v>679.5108642578125</v>
+        <v>668.235107421875</v>
       </c>
       <c r="F35" t="n">
-        <v>62312500</v>
+        <v>103457800</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B36" t="n">
-        <v>676.6471697129602</v>
+        <v>661.612768198211</v>
       </c>
       <c r="C36" t="n">
-        <v>677.0051169124795</v>
+        <v>671.8345335183507</v>
       </c>
       <c r="D36" t="n">
-        <v>666.7236935366629</v>
+        <v>659.5147291242073</v>
       </c>
       <c r="E36" t="n">
-        <v>668.2350463867188</v>
+        <v>668.1256713867188</v>
       </c>
       <c r="F36" t="n">
-        <v>103457800</v>
+        <v>96846700</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B37" t="n">
-        <v>661.6128286383953</v>
+        <v>665.9083353081996</v>
       </c>
       <c r="C37" t="n">
-        <v>671.8345948923219</v>
+        <v>669.8956413839408</v>
       </c>
       <c r="D37" t="n">
-        <v>659.5147893727298</v>
+        <v>658.4209391867944</v>
       </c>
       <c r="E37" t="n">
-        <v>668.125732421875</v>
+        <v>661.901123046875</v>
       </c>
       <c r="F37" t="n">
-        <v>96846700</v>
+        <v>90456100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B38" t="n">
-        <v>665.9083353081996</v>
+        <v>658.3512953245886</v>
       </c>
       <c r="C38" t="n">
-        <v>669.8956413839408</v>
+        <v>661.354216097308</v>
       </c>
       <c r="D38" t="n">
-        <v>658.4209391867944</v>
+        <v>652.146634691611</v>
       </c>
       <c r="E38" t="n">
-        <v>661.901123046875</v>
+        <v>656.3427734375</v>
       </c>
       <c r="F38" t="n">
-        <v>90456100</v>
+        <v>114467500</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B39" t="n">
-        <v>658.351356546523</v>
+        <v>657.0388554539629</v>
       </c>
       <c r="C39" t="n">
-        <v>661.3542775984923</v>
+        <v>663.5617119214406</v>
       </c>
       <c r="D39" t="n">
-        <v>652.1466953365565</v>
+        <v>655.0203196831769</v>
       </c>
       <c r="E39" t="n">
-        <v>656.3428344726562</v>
+        <v>658.8783569335938</v>
       </c>
       <c r="F39" t="n">
-        <v>114467500</v>
+        <v>94703000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B40" t="n">
-        <v>657.0389163187169</v>
+        <v>669.1001291109939</v>
       </c>
       <c r="C40" t="n">
-        <v>663.561773390439</v>
+        <v>671.7351497651099</v>
       </c>
       <c r="D40" t="n">
-        <v>655.020380360944</v>
+        <v>648.1991802397498</v>
       </c>
       <c r="E40" t="n">
-        <v>658.87841796875</v>
+        <v>648.8355712890625</v>
       </c>
       <c r="F40" t="n">
-        <v>94703000</v>
+        <v>165293500</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B41" t="n">
-        <v>669.1001291109939</v>
+        <v>651.3412595795126</v>
       </c>
       <c r="C41" t="n">
-        <v>671.7351497651099</v>
+        <v>660.7874729698119</v>
       </c>
       <c r="D41" t="n">
-        <v>648.1991802397498</v>
+        <v>647.1650267848305</v>
       </c>
       <c r="E41" t="n">
-        <v>648.8355712890625</v>
+        <v>655.2987670898438</v>
       </c>
       <c r="F41" t="n">
-        <v>165293500</v>
+        <v>123956200</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B42" t="n">
-        <v>651.3412595795126</v>
+        <v>658.9380055466532</v>
       </c>
       <c r="C42" t="n">
-        <v>660.7874729698119</v>
+        <v>666.2662734630499</v>
       </c>
       <c r="D42" t="n">
-        <v>647.1650267848305</v>
+        <v>657.8442577670318</v>
       </c>
       <c r="E42" t="n">
-        <v>655.2987670898438</v>
+        <v>664.9437866210938</v>
       </c>
       <c r="F42" t="n">
-        <v>123956200</v>
+        <v>80437900</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B43" t="n">
-        <v>658.9380055466532</v>
+        <v>664.8444060411854</v>
       </c>
       <c r="C43" t="n">
-        <v>666.2662734630499</v>
+        <v>672.3815071629971</v>
       </c>
       <c r="D43" t="n">
-        <v>657.8442577670318</v>
+        <v>660.717877921785</v>
       </c>
       <c r="E43" t="n">
-        <v>664.9437866210938</v>
+        <v>671.1982421875</v>
       </c>
       <c r="F43" t="n">
-        <v>80437900</v>
+        <v>81077100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B44" t="n">
-        <v>664.8443455838128</v>
+        <v>673.7934667684052</v>
       </c>
       <c r="C44" t="n">
-        <v>672.3814460202411</v>
+        <v>677.8404309302599</v>
       </c>
       <c r="D44" t="n">
-        <v>660.7178178396566</v>
+        <v>672.8885849296569</v>
       </c>
       <c r="E44" t="n">
-        <v>671.1981811523438</v>
+        <v>675.8318481445312</v>
       </c>
       <c r="F44" t="n">
-        <v>81077100</v>
+        <v>71879600</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B45" t="n">
-        <v>673.7934667684052</v>
+        <v>677.0051081523229</v>
       </c>
       <c r="C45" t="n">
-        <v>677.8404309302599</v>
+        <v>679.7991961322198</v>
       </c>
       <c r="D45" t="n">
-        <v>672.8885849296569</v>
+        <v>676.6471609574353</v>
       </c>
       <c r="E45" t="n">
-        <v>675.8318481445312</v>
+        <v>679.5208129882812</v>
       </c>
       <c r="F45" t="n">
-        <v>71879600</v>
+        <v>49212000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B46" t="n">
-        <v>677.0051081523229</v>
+        <v>674.9667014318244</v>
       </c>
       <c r="C46" t="n">
-        <v>679.7991961322198</v>
+        <v>679.1230277654502</v>
       </c>
       <c r="D46" t="n">
-        <v>676.6471609574353</v>
+        <v>674.8970904760725</v>
       </c>
       <c r="E46" t="n">
-        <v>679.5208129882812</v>
+        <v>676.41845703125</v>
       </c>
       <c r="F46" t="n">
-        <v>49212000</v>
+        <v>61201200</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B47" t="n">
-        <v>674.9667623359846</v>
+        <v>678.0591325179204</v>
       </c>
       <c r="C47" t="n">
-        <v>679.1230890446475</v>
+        <v>679.9483994968172</v>
       </c>
       <c r="D47" t="n">
-        <v>674.8971513739515</v>
+        <v>675.4838303983408</v>
       </c>
       <c r="E47" t="n">
-        <v>676.4185180664062</v>
+        <v>677.67138671875</v>
       </c>
       <c r="F47" t="n">
-        <v>61201200</v>
+        <v>62953800</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B48" t="n">
-        <v>678.0591325179204</v>
+        <v>676.7167950740063</v>
       </c>
       <c r="C48" t="n">
-        <v>679.9483994968172</v>
+        <v>681.0321891246488</v>
       </c>
       <c r="D48" t="n">
-        <v>675.4838303983408</v>
+        <v>675.8417725523884</v>
       </c>
       <c r="E48" t="n">
-        <v>677.67138671875</v>
+        <v>680.0180053710938</v>
       </c>
       <c r="F48" t="n">
-        <v>62953800</v>
+        <v>57238500</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B49" t="n">
-        <v>676.7167950740063</v>
+        <v>681.4199577792665</v>
       </c>
       <c r="C49" t="n">
-        <v>681.0321891246488</v>
+        <v>681.4895687361658</v>
       </c>
       <c r="D49" t="n">
-        <v>675.8417725523884</v>
+        <v>677.4824173401821</v>
       </c>
       <c r="E49" t="n">
-        <v>680.0180053710938</v>
+        <v>680.51513671875</v>
       </c>
       <c r="F49" t="n">
-        <v>57238500</v>
+        <v>61970300</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B50" t="n">
-        <v>681.4199577792665</v>
+        <v>681.5890143183475</v>
       </c>
       <c r="C50" t="n">
-        <v>681.4895687361658</v>
+        <v>684.4925257185774</v>
       </c>
       <c r="D50" t="n">
-        <v>677.4824173401821</v>
+        <v>680.7040993957534</v>
       </c>
       <c r="E50" t="n">
-        <v>680.51513671875</v>
+        <v>681.8078002929688</v>
       </c>
       <c r="F50" t="n">
-        <v>61970300</v>
+        <v>79241000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B51" t="n">
-        <v>681.5890143183475</v>
+        <v>682.7027235077143</v>
       </c>
       <c r="C51" t="n">
-        <v>684.4925257185774</v>
+        <v>682.7524282821314</v>
       </c>
       <c r="D51" t="n">
-        <v>680.7040993957534</v>
+        <v>677.7111260885928</v>
       </c>
       <c r="E51" t="n">
-        <v>681.8078002929688</v>
+        <v>679.7594604492188</v>
       </c>
       <c r="F51" t="n">
-        <v>79241000</v>
+        <v>55231500</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B52" t="n">
-        <v>682.7027235077143</v>
+        <v>679.2822138612034</v>
       </c>
       <c r="C52" t="n">
-        <v>682.7524282821314</v>
+        <v>681.5095218770947</v>
       </c>
       <c r="D52" t="n">
-        <v>677.7111260885928</v>
+        <v>678.7253868572307</v>
       </c>
       <c r="E52" t="n">
-        <v>679.7594604492188</v>
+        <v>679.1727905273438</v>
       </c>
       <c r="F52" t="n">
-        <v>55231500</v>
+        <v>58310100</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B53" t="n">
-        <v>679.2821528162136</v>
+        <v>678.6955405173951</v>
       </c>
       <c r="C53" t="n">
-        <v>681.5094606319436</v>
+        <v>685.0692222502689</v>
       </c>
       <c r="D53" t="n">
-        <v>678.7253258622812</v>
+        <v>677.4526176554032</v>
       </c>
       <c r="E53" t="n">
-        <v>679.1727294921875</v>
+        <v>683.6771850585938</v>
       </c>
       <c r="F53" t="n">
-        <v>58310100</v>
+        <v>85671300</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B54" t="n">
-        <v>678.6955405173951</v>
+        <v>681.2609148661827</v>
       </c>
       <c r="C54" t="n">
-        <v>685.0692222502689</v>
+        <v>685.3476304583654</v>
       </c>
       <c r="D54" t="n">
-        <v>677.4526176554032</v>
+        <v>678.3076987410943</v>
       </c>
       <c r="E54" t="n">
-        <v>683.6771850585938</v>
+        <v>685.26806640625</v>
       </c>
       <c r="F54" t="n">
-        <v>85671300</v>
+        <v>86173700</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B55" t="n">
-        <v>681.2609148661827</v>
+        <v>684.2737672143002</v>
       </c>
       <c r="C55" t="n">
-        <v>685.3476304583654</v>
+        <v>684.9797692517327</v>
       </c>
       <c r="D55" t="n">
-        <v>678.3076987410943</v>
+        <v>675.3247225627367</v>
       </c>
       <c r="E55" t="n">
-        <v>685.26806640625</v>
+        <v>677.9000854492188</v>
       </c>
       <c r="F55" t="n">
-        <v>86173700</v>
+        <v>113160300</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B56" t="n">
-        <v>684.2737056052856</v>
+        <v>681.8574988128718</v>
       </c>
       <c r="C56" t="n">
-        <v>684.9797075791527</v>
+        <v>681.8774049984522</v>
       </c>
       <c r="D56" t="n">
-        <v>675.3246617594549</v>
+        <v>675.4042533093998</v>
       </c>
       <c r="E56" t="n">
-        <v>677.9000244140625</v>
+        <v>676.8758544921875</v>
       </c>
       <c r="F56" t="n">
-        <v>113160300</v>
+        <v>90811000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B57" t="n">
-        <v>681.8574988128718</v>
+        <v>675.3843754405706</v>
       </c>
       <c r="C57" t="n">
-        <v>681.8774049984522</v>
+        <v>677.2239376857725</v>
       </c>
       <c r="D57" t="n">
-        <v>675.4042533093998</v>
+        <v>671.1584377196804</v>
       </c>
       <c r="E57" t="n">
-        <v>676.8758544921875</v>
+        <v>675.0264282226562</v>
       </c>
       <c r="F57" t="n">
-        <v>90811000</v>
+        <v>122030600</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B58" t="n">
-        <v>675.3843754405706</v>
+        <v>676.0406154817738</v>
       </c>
       <c r="C58" t="n">
-        <v>677.2239376857725</v>
+        <v>676.5874893555698</v>
       </c>
       <c r="D58" t="n">
-        <v>671.1584377196804</v>
+        <v>667.3998140691156</v>
       </c>
       <c r="E58" t="n">
-        <v>675.0264282226562</v>
+        <v>667.5986938476562</v>
       </c>
       <c r="F58" t="n">
-        <v>122030600</v>
+        <v>110625200</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B59" t="n">
-        <v>676.0406154817738</v>
+        <v>673.7635606688432</v>
       </c>
       <c r="C59" t="n">
-        <v>676.5874893555698</v>
+        <v>676.8857972779194</v>
       </c>
       <c r="D59" t="n">
-        <v>667.3998140691156</v>
+        <v>671.0788959983324</v>
       </c>
       <c r="E59" t="n">
-        <v>667.5986938476562</v>
+        <v>672.6399536132812</v>
       </c>
       <c r="F59" t="n">
-        <v>110625200</v>
+        <v>108650100</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B60" t="n">
-        <v>673.7635606688432</v>
+        <v>674.747283458469</v>
       </c>
       <c r="C60" t="n">
-        <v>676.8857972779194</v>
+        <v>679.2350273728672</v>
       </c>
       <c r="D60" t="n">
-        <v>671.0788959983324</v>
+        <v>674.6275542880097</v>
       </c>
       <c r="E60" t="n">
-        <v>672.6399536132812</v>
+        <v>678.7363891601562</v>
       </c>
       <c r="F60" t="n">
-        <v>108650100</v>
+        <v>103599500</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B61" t="n">
-        <v>674.747283458469</v>
+        <v>682.0772531068674</v>
       </c>
       <c r="C61" t="n">
-        <v>679.2350273728672</v>
+        <v>683.4933686131409</v>
       </c>
       <c r="D61" t="n">
-        <v>674.6275542880097</v>
+        <v>678.7364013691785</v>
       </c>
       <c r="E61" t="n">
-        <v>678.7363891601562</v>
+        <v>682.96484375</v>
       </c>
       <c r="F61" t="n">
-        <v>103599500</v>
+        <v>69556700</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B62" t="n">
-        <v>682.0772531068674</v>
+        <v>682.0572680421344</v>
       </c>
       <c r="C62" t="n">
-        <v>683.4933686131409</v>
+        <v>686.325640311278</v>
       </c>
       <c r="D62" t="n">
-        <v>678.7364013691785</v>
+        <v>682.0074163952171</v>
       </c>
       <c r="E62" t="n">
-        <v>682.96484375</v>
+        <v>686.0863037109375</v>
       </c>
       <c r="F62" t="n">
-        <v>69556700</v>
+        <v>64840000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B63" t="n">
-        <v>682.0572680421344</v>
+        <v>686.0763204450832</v>
       </c>
       <c r="C63" t="n">
-        <v>686.325640311278</v>
+        <v>688.9484813838191</v>
       </c>
       <c r="D63" t="n">
-        <v>682.0074163952171</v>
+        <v>685.9267046355759</v>
       </c>
       <c r="E63" t="n">
-        <v>686.0863037109375</v>
+        <v>688.4996948242188</v>
       </c>
       <c r="F63" t="n">
-        <v>64840000</v>
+        <v>39445600</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B64" t="n">
-        <v>686.0763204450832</v>
+        <v>688.758988861415</v>
       </c>
       <c r="C64" t="n">
-        <v>688.9484813838191</v>
+        <v>689.7761694005526</v>
       </c>
       <c r="D64" t="n">
-        <v>685.9267046355759</v>
+        <v>687.392725060237</v>
       </c>
       <c r="E64" t="n">
-        <v>688.4996948242188</v>
+        <v>688.4298706054688</v>
       </c>
       <c r="F64" t="n">
-        <v>39445600</v>
+        <v>41613300</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B65" t="n">
-        <v>688.758988861415</v>
+        <v>685.6674092439482</v>
       </c>
       <c r="C65" t="n">
-        <v>689.7761694005526</v>
+        <v>687.322922191004</v>
       </c>
       <c r="D65" t="n">
-        <v>687.392725060237</v>
+        <v>684.2014421207446</v>
       </c>
       <c r="E65" t="n">
-        <v>688.4298706054688</v>
+        <v>685.9765625</v>
       </c>
       <c r="F65" t="n">
-        <v>41613300</v>
+        <v>62559500</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B66" t="n">
-        <v>685.6674092439482</v>
+        <v>685.5777200962995</v>
       </c>
       <c r="C66" t="n">
-        <v>687.322922191004</v>
+        <v>686.6846823672308</v>
       </c>
       <c r="D66" t="n">
-        <v>684.2014421207446</v>
+        <v>684.7100944386586</v>
       </c>
       <c r="E66" t="n">
-        <v>685.9765625</v>
+        <v>685.138916015625</v>
       </c>
       <c r="F66" t="n">
-        <v>62559500</v>
+        <v>47160700</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B67" t="n">
-        <v>685.5777200962995</v>
+        <v>685.2685588951464</v>
       </c>
       <c r="C67" t="n">
-        <v>686.6846823672308</v>
+        <v>685.4879304984822</v>
       </c>
       <c r="D67" t="n">
-        <v>684.7100944386586</v>
+        <v>679.8533550408816</v>
       </c>
       <c r="E67" t="n">
-        <v>685.138916015625</v>
+        <v>680.062744140625</v>
       </c>
       <c r="F67" t="n">
-        <v>47160700</v>
+        <v>74144800</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B68" t="n">
-        <v>685.2685588951464</v>
+        <v>683.8424472770359</v>
       </c>
       <c r="C68" t="n">
-        <v>685.4879304984822</v>
+        <v>684.999261161205</v>
       </c>
       <c r="D68" t="n">
-        <v>679.8533550408816</v>
+        <v>677.9684744567207</v>
       </c>
       <c r="E68" t="n">
-        <v>680.062744140625</v>
+        <v>681.309326171875</v>
       </c>
       <c r="F68" t="n">
-        <v>74144800</v>
+        <v>89377200</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B69" t="n">
-        <v>683.8424472770359</v>
+        <v>684.6701449336617</v>
       </c>
       <c r="C69" t="n">
-        <v>684.999261161205</v>
+        <v>687.5522884526621</v>
       </c>
       <c r="D69" t="n">
-        <v>677.9684744567207</v>
+        <v>684.5106074856512</v>
       </c>
       <c r="E69" t="n">
-        <v>681.309326171875</v>
+        <v>685.846923828125</v>
       </c>
       <c r="F69" t="n">
-        <v>89377200</v>
+        <v>71927200</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B70" t="n">
-        <v>684.6701449336617</v>
+        <v>686.0563439630641</v>
       </c>
       <c r="C70" t="n">
-        <v>687.5522884526621</v>
+        <v>690.4344019511112</v>
       </c>
       <c r="D70" t="n">
-        <v>684.5106074856512</v>
+        <v>685.9067890249802</v>
       </c>
       <c r="E70" t="n">
-        <v>685.846923828125</v>
+        <v>689.92578125</v>
       </c>
       <c r="F70" t="n">
-        <v>71927200</v>
+        <v>69273800</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B71" t="n">
-        <v>686.0563439630641</v>
+        <v>690.3047811958188</v>
       </c>
       <c r="C71" t="n">
-        <v>690.4344019511112</v>
+        <v>692.0699799720542</v>
       </c>
       <c r="D71" t="n">
-        <v>685.9067890249802</v>
+        <v>687.4426026835383</v>
       </c>
       <c r="E71" t="n">
-        <v>689.92578125</v>
+        <v>687.701904296875</v>
       </c>
       <c r="F71" t="n">
-        <v>69273800</v>
+        <v>75588300</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B72" t="n">
-        <v>690.3047811958188</v>
+        <v>686.9439569075789</v>
       </c>
       <c r="C72" t="n">
-        <v>692.0699799720542</v>
+        <v>688.7390423054183</v>
       </c>
       <c r="D72" t="n">
-        <v>687.4426026835383</v>
+        <v>685.6175622141362</v>
       </c>
       <c r="E72" t="n">
-        <v>687.701904296875</v>
+        <v>687.632080078125</v>
       </c>
       <c r="F72" t="n">
-        <v>75588300</v>
+        <v>64019200</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B73" t="n">
-        <v>686.9439569075789</v>
+        <v>688.7489932725086</v>
       </c>
       <c r="C73" t="n">
-        <v>688.7390423054183</v>
+        <v>693.4162394407576</v>
       </c>
       <c r="D73" t="n">
-        <v>685.6175622141362</v>
+        <v>687.3029303433501</v>
       </c>
       <c r="E73" t="n">
-        <v>687.632080078125</v>
+        <v>692.1796264648438</v>
       </c>
       <c r="F73" t="n">
-        <v>64019200</v>
+        <v>80125500</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B74" t="n">
-        <v>688.7489932725086</v>
+        <v>688.7988836287034</v>
       </c>
       <c r="C74" t="n">
-        <v>693.4162394407576</v>
+        <v>694.1941832506386</v>
       </c>
       <c r="D74" t="n">
-        <v>687.3029303433501</v>
+        <v>688.7490319805348</v>
       </c>
       <c r="E74" t="n">
-        <v>692.1796264648438</v>
+        <v>693.2666625976562</v>
       </c>
       <c r="F74" t="n">
-        <v>80125500</v>
+        <v>63976000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B75" t="n">
-        <v>688.7988836287034</v>
+        <v>693.595779418591</v>
       </c>
       <c r="C75" t="n">
-        <v>694.1941832506386</v>
+        <v>694.1941818021349</v>
       </c>
       <c r="D75" t="n">
-        <v>688.7490319805348</v>
+        <v>689.467040360938</v>
       </c>
       <c r="E75" t="n">
-        <v>693.2666625976562</v>
+        <v>691.8804931640625</v>
       </c>
       <c r="F75" t="n">
-        <v>63976000</v>
+        <v>78309700</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B76" t="n">
-        <v>693.595779418591</v>
+        <v>689.1180078469732</v>
       </c>
       <c r="C76" t="n">
-        <v>694.1941818021349</v>
+        <v>689.8360176539858</v>
       </c>
       <c r="D76" t="n">
-        <v>689.467040360938</v>
+        <v>684.1714948792828</v>
       </c>
       <c r="E76" t="n">
-        <v>691.8804931640625</v>
+        <v>688.479736328125</v>
       </c>
       <c r="F76" t="n">
-        <v>78309700</v>
+        <v>94676700</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B77" t="n">
-        <v>689.1180078469732</v>
+        <v>692.6782853429351</v>
       </c>
       <c r="C77" t="n">
-        <v>689.8360176539858</v>
+        <v>693.5558934557131</v>
       </c>
       <c r="D77" t="n">
-        <v>684.1714948792828</v>
+        <v>689.3673203481677</v>
       </c>
       <c r="E77" t="n">
-        <v>688.479736328125</v>
+        <v>690.3546142578125</v>
       </c>
       <c r="F77" t="n">
-        <v>94676700</v>
+        <v>77862000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B78" t="n">
-        <v>692.6782853429351</v>
+        <v>691.7707369284135</v>
       </c>
       <c r="C78" t="n">
-        <v>693.5558934557131</v>
+        <v>692.3591568004221</v>
       </c>
       <c r="D78" t="n">
-        <v>689.3673203481677</v>
+        <v>688.22043529661</v>
       </c>
       <c r="E78" t="n">
-        <v>690.3546142578125</v>
+        <v>689.7761840820312</v>
       </c>
       <c r="F78" t="n">
-        <v>77862000</v>
+        <v>79289200</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B79" t="n">
-        <v>691.7707369284135</v>
+        <v>679.6338820353151</v>
       </c>
       <c r="C79" t="n">
-        <v>692.3591568004221</v>
+        <v>682.9049778344743</v>
       </c>
       <c r="D79" t="n">
-        <v>688.22043529661</v>
+        <v>674.7272992054969</v>
       </c>
       <c r="E79" t="n">
-        <v>689.7761840820312</v>
+        <v>675.7345581054688</v>
       </c>
       <c r="F79" t="n">
-        <v>79289200</v>
+        <v>111623300</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B80" t="n">
-        <v>679.6338820353151</v>
+        <v>677.7989248999835</v>
       </c>
       <c r="C80" t="n">
-        <v>682.9049778344743</v>
+        <v>686.8641332264262</v>
       </c>
       <c r="D80" t="n">
-        <v>674.7272992054969</v>
+        <v>676.2830453044572</v>
       </c>
       <c r="E80" t="n">
-        <v>675.7345581054688</v>
+        <v>683.5332641601562</v>
       </c>
       <c r="F80" t="n">
-        <v>111623300</v>
+        <v>127844500</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B81" t="n">
-        <v>677.7989248999835</v>
+        <v>687.9711412752974</v>
       </c>
       <c r="C81" t="n">
-        <v>686.8641332264262</v>
+        <v>689.2476843606095</v>
       </c>
       <c r="D81" t="n">
-        <v>676.2830453044572</v>
+        <v>685.0491285530771</v>
       </c>
       <c r="E81" t="n">
-        <v>683.5332641601562</v>
+        <v>687.103515625</v>
       </c>
       <c r="F81" t="n">
-        <v>127844500</v>
+        <v>77112200</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B82" t="n">
-        <v>687.9711412752974</v>
+        <v>686.2757685331861</v>
       </c>
       <c r="C82" t="n">
-        <v>689.2476843606095</v>
+        <v>689.0781127396581</v>
       </c>
       <c r="D82" t="n">
-        <v>685.0491285530771</v>
+        <v>685.2884137823622</v>
       </c>
       <c r="E82" t="n">
-        <v>687.103515625</v>
+        <v>687.352783203125</v>
       </c>
       <c r="F82" t="n">
-        <v>77112200</v>
+        <v>63059600</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B83" t="n">
-        <v>686.2757685331861</v>
+        <v>688.609372319757</v>
       </c>
       <c r="C83" t="n">
-        <v>689.0781127396581</v>
+        <v>692.2394730275811</v>
       </c>
       <c r="D83" t="n">
-        <v>685.2884137823622</v>
+        <v>688.0409174669724</v>
       </c>
       <c r="E83" t="n">
-        <v>687.352783203125</v>
+        <v>690.84326171875</v>
       </c>
       <c r="F83" t="n">
-        <v>63059600</v>
+        <v>60473800</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B84" t="n">
-        <v>688.609372319757</v>
+        <v>692.2893344912051</v>
       </c>
       <c r="C84" t="n">
-        <v>692.2394730275811</v>
+        <v>694.6329705879123</v>
       </c>
       <c r="D84" t="n">
-        <v>688.0409174669724</v>
+        <v>691.6810104865692</v>
       </c>
       <c r="E84" t="n">
-        <v>690.84326171875</v>
+        <v>693.5957641601562</v>
       </c>
       <c r="F84" t="n">
-        <v>60473800</v>
+        <v>55506100</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B85" t="n">
-        <v>692.2893344912051</v>
+        <v>695.1515053497095</v>
       </c>
       <c r="C85" t="n">
-        <v>694.6329705879123</v>
+        <v>695.9393926651097</v>
       </c>
       <c r="D85" t="n">
-        <v>691.6810104865692</v>
+        <v>692.0499903412962</v>
       </c>
       <c r="E85" t="n">
-        <v>693.5957641601562</v>
+        <v>693.5259399414062</v>
       </c>
       <c r="F85" t="n">
-        <v>55506100</v>
+        <v>61172200</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B86" t="n">
-        <v>695.1515053497095</v>
+        <v>694.4933553961189</v>
       </c>
       <c r="C86" t="n">
-        <v>695.9393926651097</v>
+        <v>695.1615135683285</v>
       </c>
       <c r="D86" t="n">
-        <v>692.0499903412962</v>
+        <v>682.9648421722587</v>
       </c>
       <c r="E86" t="n">
-        <v>693.5259399414062</v>
+        <v>692.1497192382812</v>
       </c>
       <c r="F86" t="n">
-        <v>61172200</v>
+        <v>97486200</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B87" t="n">
-        <v>694.4933553961189</v>
+        <v>689.9058246991844</v>
       </c>
       <c r="C87" t="n">
-        <v>695.1615135683285</v>
+        <v>692.3192774332931</v>
       </c>
       <c r="D87" t="n">
-        <v>682.9648421722587</v>
+        <v>685.2485609149509</v>
       </c>
       <c r="E87" t="n">
-        <v>692.1497192382812</v>
+        <v>690.0853271484375</v>
       </c>
       <c r="F87" t="n">
-        <v>97486200</v>
+        <v>101835100</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B88" t="n">
-        <v>689.9058246991844</v>
+        <v>687.7019133171445</v>
       </c>
       <c r="C88" t="n">
-        <v>692.3192774332931</v>
+        <v>695.0318708971434</v>
       </c>
       <c r="D88" t="n">
-        <v>685.2485609149509</v>
+        <v>687.5423149981101</v>
       </c>
       <c r="E88" t="n">
-        <v>690.0853271484375</v>
+        <v>693.5159912109375</v>
       </c>
       <c r="F88" t="n">
-        <v>101835100</v>
+        <v>79286500</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B89" t="n">
-        <v>687.7019133171445</v>
+        <v>694.3138377504575</v>
       </c>
       <c r="C89" t="n">
-        <v>695.0318708971434</v>
+        <v>695.0617950648859</v>
       </c>
       <c r="D89" t="n">
-        <v>687.5423149981101</v>
+        <v>682.1670182684101</v>
       </c>
       <c r="E89" t="n">
-        <v>693.5159912109375</v>
+        <v>687.6520385742188</v>
       </c>
       <c r="F89" t="n">
-        <v>79286500</v>
+        <v>107904600</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B90" t="n">
-        <v>694.3138377504575</v>
+        <v>688.4697490630058</v>
       </c>
       <c r="C90" t="n">
-        <v>695.0617950648859</v>
+        <v>689.5667896413613</v>
       </c>
       <c r="D90" t="n">
-        <v>682.1670182684101</v>
+        <v>679.9031787408285</v>
       </c>
       <c r="E90" t="n">
-        <v>687.6520385742188</v>
+        <v>684.3211059570312</v>
       </c>
       <c r="F90" t="n">
-        <v>107904600</v>
+        <v>105204600</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B91" t="n">
-        <v>688.4697490630058</v>
+        <v>679.0854402743204</v>
       </c>
       <c r="C91" t="n">
-        <v>689.5667896413613</v>
+        <v>681.8279505601881</v>
       </c>
       <c r="D91" t="n">
-        <v>679.9031787408285</v>
+        <v>673.9494421186707</v>
       </c>
       <c r="E91" t="n">
-        <v>684.3211059570312</v>
+        <v>675.7744750976562</v>
       </c>
       <c r="F91" t="n">
-        <v>105204600</v>
+        <v>113610800</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B92" t="n">
-        <v>679.0854402743204</v>
+        <v>679.6039887472712</v>
       </c>
       <c r="C92" t="n">
-        <v>681.8279505601881</v>
+        <v>690.4244132010324</v>
       </c>
       <c r="D92" t="n">
-        <v>673.9494421186707</v>
+        <v>678.995603890688</v>
       </c>
       <c r="E92" t="n">
-        <v>675.7744750976562</v>
+        <v>688.739013671875</v>
       </c>
       <c r="F92" t="n">
-        <v>113610800</v>
+        <v>89127600</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B93" t="n">
-        <v>679.6039887472712</v>
+        <v>687.5423060693106</v>
       </c>
       <c r="C93" t="n">
-        <v>690.4244132010324</v>
+        <v>693.9747512796714</v>
       </c>
       <c r="D93" t="n">
-        <v>678.995603890688</v>
+        <v>686.4652913399738</v>
       </c>
       <c r="E93" t="n">
-        <v>688.739013671875</v>
+        <v>692.0599975585938</v>
       </c>
       <c r="F93" t="n">
-        <v>89127600</v>
+        <v>73885200</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B94" t="n">
-        <v>687.5423060693106</v>
+        <v>693.0572335194393</v>
       </c>
       <c r="C94" t="n">
-        <v>693.9747512796714</v>
+        <v>694.64286887948</v>
       </c>
       <c r="D94" t="n">
-        <v>686.4652913399738</v>
+        <v>689.7761552680904</v>
       </c>
       <c r="E94" t="n">
-        <v>692.0599975585938</v>
+        <v>690.2349243164062</v>
       </c>
       <c r="F94" t="n">
-        <v>73885200</v>
+        <v>65185700</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B95" t="n">
-        <v>693.0572335194393</v>
+        <v>694.4933668556342</v>
       </c>
       <c r="C95" t="n">
-        <v>694.64286887948</v>
+        <v>695.2413241987686</v>
       </c>
       <c r="D95" t="n">
-        <v>689.7761552680904</v>
+        <v>687.3029816841566</v>
       </c>
       <c r="E95" t="n">
-        <v>690.2349243164062</v>
+        <v>690.075439453125</v>
       </c>
       <c r="F95" t="n">
-        <v>65185700</v>
+        <v>76353900</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B96" t="n">
-        <v>694.4933668556342</v>
+        <v>692.3491972008484</v>
       </c>
       <c r="C96" t="n">
-        <v>695.2413241987686</v>
+        <v>693.4561594586687</v>
       </c>
       <c r="D96" t="n">
-        <v>687.3029816841566</v>
+        <v>678.5169776231163</v>
       </c>
       <c r="E96" t="n">
-        <v>690.075439453125</v>
+        <v>679.41455078125</v>
       </c>
       <c r="F96" t="n">
-        <v>76353900</v>
+        <v>118829000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B97" t="n">
-        <v>692.3491972008484</v>
+        <v>679.833354327075</v>
       </c>
       <c r="C97" t="n">
-        <v>693.4561594586687</v>
+        <v>684.410879804094</v>
       </c>
       <c r="D97" t="n">
-        <v>678.5169776231163</v>
+        <v>675.6747287653898</v>
       </c>
       <c r="E97" t="n">
-        <v>679.41455078125</v>
+        <v>679.8931884765625</v>
       </c>
       <c r="F97" t="n">
-        <v>118829000</v>
+        <v>96267500</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B98" t="n">
-        <v>679.833354327075</v>
+        <v>678.287593220413</v>
       </c>
       <c r="C98" t="n">
-        <v>684.410879804094</v>
+        <v>683.074507822494</v>
       </c>
       <c r="D98" t="n">
-        <v>675.6747287653898</v>
+        <v>673.9394826742099</v>
       </c>
       <c r="E98" t="n">
-        <v>679.8931884765625</v>
+        <v>680.9901733398438</v>
       </c>
       <c r="F98" t="n">
-        <v>96267500</v>
+        <v>81354700</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B99" t="n">
-        <v>678.287593220413</v>
+        <v>682.157061237011</v>
       </c>
       <c r="C99" t="n">
-        <v>683.074507822494</v>
+        <v>687.2730943282486</v>
       </c>
       <c r="D99" t="n">
-        <v>673.9394826742099</v>
+        <v>680.9702998190471</v>
       </c>
       <c r="E99" t="n">
-        <v>680.9901733398438</v>
+        <v>684.4208374023438</v>
       </c>
       <c r="F99" t="n">
-        <v>81354700</v>
+        <v>73570300</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B100" t="n">
-        <v>682.157061237011</v>
+        <v>681.9775120282383</v>
       </c>
       <c r="C100" t="n">
-        <v>687.2730943282486</v>
+        <v>684.311104689823</v>
       </c>
       <c r="D100" t="n">
-        <v>680.9702998190471</v>
+        <v>679.6937101433548</v>
       </c>
       <c r="E100" t="n">
-        <v>684.4208374023438</v>
+        <v>682.61572265625</v>
       </c>
       <c r="F100" t="n">
-        <v>73570300</v>
+        <v>58649400</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B101" t="n">
-        <v>681.9775120282383</v>
+        <v>680.4616860592505</v>
       </c>
       <c r="C101" t="n">
-        <v>684.311104689823</v>
+        <v>688.1805961724377</v>
       </c>
       <c r="D101" t="n">
-        <v>679.6937101433548</v>
+        <v>679.8732661615737</v>
       </c>
       <c r="E101" t="n">
-        <v>682.61572265625</v>
+        <v>687.5523071289062</v>
       </c>
       <c r="F101" t="n">
-        <v>58649400</v>
+        <v>100034000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B102" t="n">
-        <v>680.4616860592505</v>
+        <v>685.9566804858357</v>
       </c>
       <c r="C102" t="n">
-        <v>688.1805961724377</v>
+        <v>688.1207533479937</v>
       </c>
       <c r="D102" t="n">
-        <v>679.8732661615737</v>
+        <v>678.5169762252317</v>
       </c>
       <c r="E102" t="n">
-        <v>687.5523071289062</v>
+        <v>680.531494140625</v>
       </c>
       <c r="F102" t="n">
-        <v>100034000</v>
+        <v>90558100</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B103" t="n">
-        <v>685.9566804858357</v>
+        <v>680.0427976196477</v>
       </c>
       <c r="C103" t="n">
-        <v>688.1207533479937</v>
+        <v>686.4751816677359</v>
       </c>
       <c r="D103" t="n">
-        <v>678.5169762252317</v>
+        <v>678.1479481229125</v>
       </c>
       <c r="E103" t="n">
-        <v>680.531494140625</v>
+        <v>685.4779052734375</v>
       </c>
       <c r="F103" t="n">
-        <v>90558100</v>
+        <v>73798700</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B104" t="n">
-        <v>680.0427976196477</v>
+        <v>688.3002642742074</v>
       </c>
       <c r="C104" t="n">
-        <v>686.4751816677359</v>
+        <v>691.7907319065998</v>
       </c>
       <c r="D104" t="n">
-        <v>678.1479481229125</v>
+        <v>688.2204651135966</v>
       </c>
       <c r="E104" t="n">
-        <v>685.4779052734375</v>
+        <v>691.26220703125</v>
       </c>
       <c r="F104" t="n">
-        <v>73798700</v>
+        <v>56369500</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B105" t="n">
-        <v>688.3002642742074</v>
+        <v>691.391808867856</v>
       </c>
       <c r="C105" t="n">
-        <v>691.7907319065998</v>
+        <v>691.4117130049051</v>
       </c>
       <c r="D105" t="n">
-        <v>688.2204651135966</v>
+        <v>682.4860770890911</v>
       </c>
       <c r="E105" t="n">
-        <v>691.26220703125</v>
+        <v>687.422607421875</v>
       </c>
       <c r="F105" t="n">
-        <v>56369500</v>
+        <v>71671000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B106" t="n">
-        <v>691.391808867856</v>
+        <v>681.2295779636313</v>
       </c>
       <c r="C106" t="n">
-        <v>691.4117130049051</v>
+        <v>684.9892686841309</v>
       </c>
       <c r="D106" t="n">
-        <v>682.4860770890911</v>
+        <v>679.7835149777827</v>
       </c>
       <c r="E106" t="n">
-        <v>687.422607421875</v>
+        <v>684.1216430664062</v>
       </c>
       <c r="F106" t="n">
-        <v>71671000</v>
+        <v>83308900</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B107" t="n">
-        <v>681.2295779636313</v>
+        <v>676.8515442239554</v>
       </c>
       <c r="C107" t="n">
-        <v>684.9892686841309</v>
+        <v>686.744509644098</v>
       </c>
       <c r="D107" t="n">
-        <v>679.7835149777827</v>
+        <v>676.1734035367807</v>
       </c>
       <c r="E107" t="n">
-        <v>684.1216430664062</v>
+        <v>684.5106201171875</v>
       </c>
       <c r="F107" t="n">
-        <v>83308900</v>
+        <v>87477200</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B108" t="n">
-        <v>676.8515442239554</v>
+        <v>673.221445388408</v>
       </c>
       <c r="C108" t="n">
-        <v>686.744509644098</v>
+        <v>680.7508704958498</v>
       </c>
       <c r="D108" t="n">
-        <v>676.1734035367807</v>
+        <v>667.8361281509542</v>
       </c>
       <c r="E108" t="n">
-        <v>684.5106201171875</v>
+        <v>678.4771118164062</v>
       </c>
       <c r="F108" t="n">
-        <v>87477200</v>
+        <v>105003100</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B109" t="n">
-        <v>673.221445388408</v>
+        <v>679.7735096903759</v>
       </c>
       <c r="C109" t="n">
-        <v>680.7508704958498</v>
+        <v>685.2186606854194</v>
       </c>
       <c r="D109" t="n">
-        <v>667.8361281509542</v>
+        <v>677.7689744100875</v>
       </c>
       <c r="E109" t="n">
-        <v>678.4771118164062</v>
+        <v>683.2639770507812</v>
       </c>
       <c r="F109" t="n">
-        <v>105003100</v>
+        <v>79182200</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B110" t="n">
-        <v>679.7735096903759</v>
+        <v>680.2223290726917</v>
       </c>
       <c r="C110" t="n">
-        <v>685.2186606854194</v>
+        <v>683.6629449535216</v>
       </c>
       <c r="D110" t="n">
-        <v>677.7689744100875</v>
+        <v>673.7699188745959</v>
       </c>
       <c r="E110" t="n">
-        <v>683.2639770507812</v>
+        <v>679.4544067382812</v>
       </c>
       <c r="F110" t="n">
-        <v>79182200</v>
+        <v>106606500</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B111" t="n">
-        <v>680.2223290726917</v>
+        <v>671.5758690877306</v>
       </c>
       <c r="C111" t="n">
-        <v>683.6629449535216</v>
+        <v>674.2685275228549</v>
       </c>
       <c r="D111" t="n">
-        <v>673.7699188745959</v>
+        <v>667.9358467743081</v>
       </c>
       <c r="E111" t="n">
-        <v>679.4544067382812</v>
+        <v>670.5487060546875</v>
       </c>
       <c r="F111" t="n">
-        <v>106606500</v>
+        <v>100687000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B112" t="n">
-        <v>671.5758690877306</v>
+        <v>664.5750801817165</v>
       </c>
       <c r="C112" t="n">
-        <v>674.2685275228549</v>
+        <v>678.0681991431876</v>
       </c>
       <c r="D112" t="n">
-        <v>667.9358467743081</v>
+        <v>660.5859743093405</v>
       </c>
       <c r="E112" t="n">
-        <v>670.5487060546875</v>
+        <v>676.4227294921875</v>
       </c>
       <c r="F112" t="n">
-        <v>100687000</v>
+        <v>102667700</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B113" t="n">
-        <v>664.5750801817165</v>
+        <v>675.87413967305</v>
       </c>
       <c r="C113" t="n">
-        <v>678.0681991431876</v>
+        <v>681.4987932365287</v>
       </c>
       <c r="D113" t="n">
-        <v>660.5859743093405</v>
+        <v>672.9222404542279</v>
       </c>
       <c r="E113" t="n">
-        <v>676.4227294921875</v>
+        <v>675.3356323242188</v>
       </c>
       <c r="F113" t="n">
-        <v>102667700</v>
+        <v>81505300</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B114" t="n">
-        <v>675.87413967305</v>
+        <v>675.7345715953234</v>
       </c>
       <c r="C114" t="n">
-        <v>681.4987932365287</v>
+        <v>678.2277626375325</v>
       </c>
       <c r="D114" t="n">
-        <v>672.9222404542279</v>
+        <v>671.5061293267642</v>
       </c>
       <c r="E114" t="n">
-        <v>675.3356323242188</v>
+        <v>674.4879760742188</v>
       </c>
       <c r="F114" t="n">
-        <v>81505300</v>
+        <v>68441700</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B115" t="n">
-        <v>675.7345715953234</v>
+        <v>669.3319958917509</v>
       </c>
       <c r="C115" t="n">
-        <v>678.2277626375325</v>
+        <v>669.8207124533001</v>
       </c>
       <c r="D115" t="n">
-        <v>671.5061293267642</v>
+        <v>664.0564256954588</v>
       </c>
       <c r="E115" t="n">
-        <v>674.4879760742188</v>
+        <v>664.2459106445312</v>
       </c>
       <c r="F115" t="n">
-        <v>68441700</v>
+        <v>108882200</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B116" t="n">
-        <v>669.3319958917509</v>
+        <v>667.4472371497842</v>
       </c>
       <c r="C116" t="n">
-        <v>669.8207124533001</v>
+        <v>670.5088831921612</v>
       </c>
       <c r="D116" t="n">
-        <v>664.0564256954588</v>
+        <v>659.5587462493693</v>
       </c>
       <c r="E116" t="n">
-        <v>664.2459106445312</v>
+        <v>660.4862060546875</v>
       </c>
       <c r="F116" t="n">
-        <v>108882200</v>
+        <v>97200200</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B117" t="n">
-        <v>667.4472371497842</v>
+        <v>666.5596317087426</v>
       </c>
       <c r="C117" t="n">
-        <v>670.5088831921612</v>
+        <v>670.239584206393</v>
       </c>
       <c r="D117" t="n">
-        <v>659.5587462493693</v>
+        <v>665.3030536555561</v>
       </c>
       <c r="E117" t="n">
-        <v>660.4862060546875</v>
+        <v>667.2078857421875</v>
       </c>
       <c r="F117" t="n">
-        <v>97200200</v>
+        <v>82023100</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B118" t="n">
-        <v>666.5596317087426</v>
+        <v>670.5586914524959</v>
       </c>
       <c r="C118" t="n">
-        <v>670.239584206393</v>
+        <v>672.60309589337</v>
       </c>
       <c r="D118" t="n">
-        <v>665.3030536555561</v>
+        <v>667.8760155087483</v>
       </c>
       <c r="E118" t="n">
-        <v>667.2078857421875</v>
+        <v>668.9630126953125</v>
       </c>
       <c r="F118" t="n">
-        <v>82023100</v>
+        <v>87128000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B119" t="n">
-        <v>670.5586914524959</v>
+        <v>666.5396583763402</v>
       </c>
       <c r="C119" t="n">
-        <v>672.60309589337</v>
+        <v>667.8959397089973</v>
       </c>
       <c r="D119" t="n">
-        <v>667.8760155087483</v>
+        <v>659.3892034355257</v>
       </c>
       <c r="E119" t="n">
-        <v>668.9630126953125</v>
+        <v>659.6285400390625</v>
       </c>
       <c r="F119" t="n">
-        <v>87128000</v>
+        <v>82062600</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B120" t="n">
-        <v>666.5396583763402</v>
+        <v>655.1806813207687</v>
       </c>
       <c r="C120" t="n">
-        <v>667.8959397089973</v>
+        <v>661.1743225351036</v>
       </c>
       <c r="D120" t="n">
-        <v>659.3892034355257</v>
+        <v>653.3855958813168</v>
       </c>
       <c r="E120" t="n">
-        <v>659.6285400390625</v>
+        <v>658.0029907226562</v>
       </c>
       <c r="F120" t="n">
-        <v>82062600</v>
+        <v>111272500</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B121" t="n">
-        <v>655.1806813207687</v>
+        <v>656.510009765625</v>
       </c>
       <c r="C121" t="n">
-        <v>661.1743225351036</v>
+        <v>656.6900024414062</v>
       </c>
       <c r="D121" t="n">
-        <v>653.3855958813168</v>
+        <v>644.719970703125</v>
       </c>
       <c r="E121" t="n">
-        <v>658.0029907226562</v>
+        <v>648.5700073242188</v>
       </c>
       <c r="F121" t="n">
-        <v>111272500</v>
+        <v>163617500</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B122" t="n">
-        <v>656.510009765625</v>
+        <v>658.0700073242188</v>
       </c>
       <c r="C122" t="n">
-        <v>656.6900024414062</v>
+        <v>662.6199951171875</v>
       </c>
       <c r="D122" t="n">
-        <v>644.719970703125</v>
+        <v>653.9400024414062</v>
       </c>
       <c r="E122" t="n">
-        <v>648.5700073242188</v>
+        <v>655.3800048828125</v>
       </c>
       <c r="F122" t="n">
-        <v>163617500</v>
+        <v>134802700</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B123" t="n">
-        <v>658.0700073242188</v>
+        <v>651.3200073242188</v>
       </c>
       <c r="C123" t="n">
-        <v>662.6199951171875</v>
+        <v>657.030029296875</v>
       </c>
       <c r="D123" t="n">
-        <v>653.9400024414062</v>
+        <v>649.8800048828125</v>
       </c>
       <c r="E123" t="n">
-        <v>655.3800048828125</v>
+        <v>653.1799926757812</v>
       </c>
       <c r="F123" t="n">
-        <v>134802700</v>
+        <v>96457500</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B124" t="n">
-        <v>651.3200073242188</v>
+        <v>658.6699829101562</v>
       </c>
       <c r="C124" t="n">
-        <v>657.030029296875</v>
+        <v>660.8900146484375</v>
       </c>
       <c r="D124" t="n">
-        <v>649.8800048828125</v>
+        <v>654.239990234375</v>
       </c>
       <c r="E124" t="n">
-        <v>653.1799926757812</v>
+        <v>656.8200073242188</v>
       </c>
       <c r="F124" t="n">
-        <v>96120900</v>
+        <v>90653800</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B125" t="n">
+        <v>652.0599975585938</v>
+      </c>
+      <c r="C125" t="n">
+        <v>654.8499755859375</v>
+      </c>
+      <c r="D125" t="n">
+        <v>644.8200073242188</v>
+      </c>
+      <c r="E125" t="n">
+        <v>645.0900268554688</v>
+      </c>
+      <c r="F125" t="n">
+        <v>96353600</v>
       </c>
     </row>
   </sheetData>
@@ -2939,7 +2959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2976,2462 +2996,2482 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B2" t="n">
-        <v>253.6166009653311</v>
+        <v>254.0757261912774</v>
       </c>
       <c r="C2" t="n">
-        <v>257.1099424925133</v>
+        <v>254.5148915782133</v>
       </c>
       <c r="D2" t="n">
-        <v>253.2972024297037</v>
+        <v>252.5286718435753</v>
       </c>
       <c r="E2" t="n">
-        <v>254.9740142822266</v>
+        <v>253.9459686279297</v>
       </c>
       <c r="F2" t="n">
-        <v>46076300</v>
+        <v>40127700</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B3" t="n">
-        <v>254.0757261912774</v>
+        <v>254.3751575512532</v>
       </c>
       <c r="C3" t="n">
-        <v>254.5148915782133</v>
+        <v>255.4331385813304</v>
       </c>
       <c r="D3" t="n">
-        <v>252.5286718435753</v>
+        <v>252.6284867333586</v>
       </c>
       <c r="E3" t="n">
-        <v>253.9459686279297</v>
+        <v>254.1455993652344</v>
       </c>
       <c r="F3" t="n">
-        <v>40127700</v>
+        <v>37704300</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B4" t="n">
-        <v>254.3751575512532</v>
+        <v>254.5548113531499</v>
       </c>
       <c r="C4" t="n">
-        <v>255.4331385813304</v>
+        <v>258.2976926733417</v>
       </c>
       <c r="D4" t="n">
-        <v>252.6284867333586</v>
+        <v>254.4450200053069</v>
       </c>
       <c r="E4" t="n">
-        <v>254.1455993652344</v>
+        <v>254.9640350341797</v>
       </c>
       <c r="F4" t="n">
-        <v>37704300</v>
+        <v>48713900</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B5" t="n">
-        <v>254.5548113531499</v>
+        <v>256.0918666719083</v>
       </c>
       <c r="C5" t="n">
-        <v>258.2976926733417</v>
+        <v>257.6888289105058</v>
       </c>
       <c r="D5" t="n">
-        <v>254.4450200053069</v>
+        <v>253.666496834403</v>
       </c>
       <c r="E5" t="n">
-        <v>254.9640350341797</v>
+        <v>256.6408386230469</v>
       </c>
       <c r="F5" t="n">
-        <v>48713900</v>
+        <v>42630200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B6" t="n">
-        <v>256.0918666719083</v>
+        <v>254.1855263026656</v>
       </c>
       <c r="C6" t="n">
-        <v>257.6888289105058</v>
+        <v>258.7468246365968</v>
       </c>
       <c r="D6" t="n">
-        <v>253.666496834403</v>
+        <v>253.4668947774022</v>
       </c>
       <c r="E6" t="n">
-        <v>256.6408386230469</v>
+        <v>257.5291442871094</v>
       </c>
       <c r="F6" t="n">
-        <v>42630200</v>
+        <v>49155600</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B7" t="n">
-        <v>254.1855263026656</v>
+        <v>257.499174775338</v>
       </c>
       <c r="C7" t="n">
-        <v>258.7468246365968</v>
+        <v>258.5771371766132</v>
       </c>
       <c r="D7" t="n">
-        <v>253.4668947774022</v>
+        <v>254.5647807987102</v>
       </c>
       <c r="E7" t="n">
-        <v>257.5291442871094</v>
+        <v>256.20166015625</v>
       </c>
       <c r="F7" t="n">
-        <v>49155600</v>
+        <v>44664100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B8" t="n">
-        <v>257.499174775338</v>
+        <v>256.3214547692021</v>
       </c>
       <c r="C8" t="n">
-        <v>258.5771371766132</v>
+        <v>256.9103287268919</v>
       </c>
       <c r="D8" t="n">
-        <v>254.5647807987102</v>
+        <v>254.9440751402397</v>
       </c>
       <c r="E8" t="n">
-        <v>256.20166015625</v>
+        <v>255.9920959472656</v>
       </c>
       <c r="F8" t="n">
-        <v>44664100</v>
+        <v>31955800</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B9" t="n">
-        <v>256.3214547692021</v>
+        <v>256.0320127996357</v>
       </c>
       <c r="C9" t="n">
-        <v>256.9103287268919</v>
+        <v>258.0282082133661</v>
       </c>
       <c r="D9" t="n">
-        <v>254.9440751402397</v>
+        <v>255.6227890846779</v>
       </c>
       <c r="E9" t="n">
-        <v>255.9920959472656</v>
+        <v>257.569091796875</v>
       </c>
       <c r="F9" t="n">
-        <v>31955800</v>
+        <v>36496900</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B10" t="n">
-        <v>256.0320127996357</v>
+        <v>257.3195337882977</v>
       </c>
       <c r="C10" t="n">
-        <v>258.0282082133661</v>
+        <v>257.5091747646147</v>
       </c>
       <c r="D10" t="n">
-        <v>255.6227890846779</v>
+        <v>252.6584199331141</v>
       </c>
       <c r="E10" t="n">
-        <v>257.569091796875</v>
+        <v>253.5567016601562</v>
       </c>
       <c r="F10" t="n">
-        <v>36496900</v>
+        <v>38322000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B11" t="n">
-        <v>257.3195337882977</v>
+        <v>254.4550078501572</v>
       </c>
       <c r="C11" t="n">
-        <v>257.5091747646147</v>
+        <v>255.8922708493858</v>
       </c>
       <c r="D11" t="n">
-        <v>252.6584199331141</v>
+        <v>243.535817529099</v>
       </c>
       <c r="E11" t="n">
-        <v>253.5567016601562</v>
+        <v>244.8034057617188</v>
       </c>
       <c r="F11" t="n">
-        <v>38322000</v>
+        <v>61999100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B12" t="n">
-        <v>254.4550078501572</v>
+        <v>248.9055871417832</v>
       </c>
       <c r="C12" t="n">
-        <v>255.8922708493858</v>
+        <v>249.2149949644775</v>
       </c>
       <c r="D12" t="n">
-        <v>243.535817529099</v>
+        <v>245.0928469569099</v>
       </c>
       <c r="E12" t="n">
-        <v>244.8034057617188</v>
+        <v>247.1888580322266</v>
       </c>
       <c r="F12" t="n">
-        <v>61999100</v>
+        <v>38142900</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B13" t="n">
-        <v>248.9055871417832</v>
+        <v>246.1308726626428</v>
       </c>
       <c r="C13" t="n">
-        <v>249.2149949644775</v>
+        <v>248.3765922481423</v>
       </c>
       <c r="D13" t="n">
-        <v>245.0928469569099</v>
+        <v>244.2344780970313</v>
       </c>
       <c r="E13" t="n">
-        <v>247.1888580322266</v>
+        <v>247.2986450195312</v>
       </c>
       <c r="F13" t="n">
-        <v>38142900</v>
+        <v>35478000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B14" t="n">
-        <v>246.1308726626428</v>
+        <v>249.0153854047813</v>
       </c>
       <c r="C14" t="n">
-        <v>248.3765922481423</v>
+        <v>251.3409547309234</v>
       </c>
       <c r="D14" t="n">
-        <v>244.2344780970313</v>
+        <v>246.9992239099275</v>
       </c>
       <c r="E14" t="n">
-        <v>247.2986450195312</v>
+        <v>248.8656616210938</v>
       </c>
       <c r="F14" t="n">
-        <v>35478000</v>
+        <v>33893600</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B15" t="n">
-        <v>249.0153854047813</v>
+        <v>247.7777444808599</v>
       </c>
       <c r="C15" t="n">
-        <v>251.3409547309234</v>
+        <v>248.5662349323926</v>
       </c>
       <c r="D15" t="n">
-        <v>246.9992239099275</v>
+        <v>244.6636846503341</v>
       </c>
       <c r="E15" t="n">
-        <v>248.8656616210938</v>
+        <v>246.9792633056641</v>
       </c>
       <c r="F15" t="n">
-        <v>33893600</v>
+        <v>39777000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B16" t="n">
-        <v>247.7777444808599</v>
+        <v>247.5481624372989</v>
       </c>
       <c r="C16" t="n">
-        <v>248.5662349323926</v>
+        <v>252.8979659970864</v>
       </c>
       <c r="D16" t="n">
-        <v>244.6636846503341</v>
+        <v>246.7995892632415</v>
       </c>
       <c r="E16" t="n">
-        <v>246.9792633056641</v>
+        <v>251.8100280761719</v>
       </c>
       <c r="F16" t="n">
-        <v>39777000</v>
+        <v>49147000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B17" t="n">
-        <v>247.5481624372989</v>
+        <v>255.4032084113237</v>
       </c>
       <c r="C17" t="n">
-        <v>252.8979659970864</v>
+        <v>263.8770629877272</v>
       </c>
       <c r="D17" t="n">
-        <v>246.7995892632415</v>
+        <v>255.143708503654</v>
       </c>
       <c r="E17" t="n">
-        <v>251.8100280761719</v>
+        <v>261.7411193847656</v>
       </c>
       <c r="F17" t="n">
-        <v>49147000</v>
+        <v>90483000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B18" t="n">
-        <v>255.4032084113237</v>
+        <v>261.3817895915523</v>
       </c>
       <c r="C18" t="n">
-        <v>263.8770629877272</v>
+        <v>264.7853058703715</v>
       </c>
       <c r="D18" t="n">
-        <v>255.143708503654</v>
+        <v>261.3318664386604</v>
       </c>
       <c r="E18" t="n">
-        <v>261.7411193847656</v>
+        <v>262.2700805664062</v>
       </c>
       <c r="F18" t="n">
-        <v>90483000</v>
+        <v>46695900</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B19" t="n">
-        <v>261.3817895915523</v>
+        <v>262.1503352574342</v>
       </c>
       <c r="C19" t="n">
-        <v>264.7853058703715</v>
+        <v>262.349966966352</v>
       </c>
       <c r="D19" t="n">
-        <v>261.3318664386604</v>
+        <v>254.9440691826199</v>
       </c>
       <c r="E19" t="n">
-        <v>262.2700805664062</v>
+        <v>257.9583435058594</v>
       </c>
       <c r="F19" t="n">
-        <v>46695900</v>
+        <v>45015300</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B20" t="n">
-        <v>262.1503352574342</v>
+        <v>259.4454820834593</v>
       </c>
       <c r="C20" t="n">
-        <v>262.349966966352</v>
+        <v>260.1241811137136</v>
       </c>
       <c r="D20" t="n">
-        <v>254.9440691826199</v>
+        <v>257.5191611036844</v>
       </c>
       <c r="E20" t="n">
-        <v>257.9583435058594</v>
+        <v>259.0861511230469</v>
       </c>
       <c r="F20" t="n">
-        <v>45015300</v>
+        <v>32754900</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B21" t="n">
-        <v>259.4454820834593</v>
+        <v>260.6931337605782</v>
       </c>
       <c r="C21" t="n">
-        <v>260.1241811137136</v>
+        <v>263.6275433572314</v>
       </c>
       <c r="D21" t="n">
-        <v>257.5191611036844</v>
+        <v>258.6869476899315</v>
       </c>
       <c r="E21" t="n">
-        <v>259.0861511230469</v>
+        <v>262.3200378417969</v>
       </c>
       <c r="F21" t="n">
-        <v>32754900</v>
+        <v>38253700</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B22" t="n">
-        <v>260.6931337605782</v>
+        <v>264.376098228409</v>
       </c>
       <c r="C22" t="n">
-        <v>263.6275433572314</v>
+        <v>268.60802232244</v>
       </c>
       <c r="D22" t="n">
-        <v>258.6869476899315</v>
+        <v>264.1465248140549</v>
       </c>
       <c r="E22" t="n">
-        <v>262.3200378417969</v>
+        <v>268.2986145019531</v>
       </c>
       <c r="F22" t="n">
-        <v>38253700</v>
+        <v>44888200</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B23" t="n">
-        <v>264.376098228409</v>
+        <v>268.4782600095115</v>
       </c>
       <c r="C23" t="n">
-        <v>268.60802232244</v>
+        <v>269.3765722048576</v>
       </c>
       <c r="D23" t="n">
-        <v>264.1465248140549</v>
+        <v>267.6398616921066</v>
       </c>
       <c r="E23" t="n">
-        <v>268.2986145019531</v>
+        <v>268.4882507324219</v>
       </c>
       <c r="F23" t="n">
-        <v>44888200</v>
+        <v>41534800</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B24" t="n">
-        <v>268.4782600095115</v>
+        <v>268.7677057947778</v>
       </c>
       <c r="C24" t="n">
-        <v>269.3765722048576</v>
+        <v>270.8936584399069</v>
       </c>
       <c r="D24" t="n">
-        <v>267.6398616921066</v>
+        <v>266.6018207191691</v>
       </c>
       <c r="E24" t="n">
-        <v>268.4882507324219</v>
+        <v>269.1869201660156</v>
       </c>
       <c r="F24" t="n">
-        <v>41534800</v>
+        <v>51086700</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B25" t="n">
-        <v>268.7677057947778</v>
+        <v>271.4725408872279</v>
       </c>
       <c r="C25" t="n">
-        <v>270.8936584399069</v>
+        <v>273.6184749716116</v>
       </c>
       <c r="D25" t="n">
-        <v>266.6018207191691</v>
+        <v>267.969239224885</v>
       </c>
       <c r="E25" t="n">
-        <v>269.1869201660156</v>
+        <v>270.8836669921875</v>
       </c>
       <c r="F25" t="n">
-        <v>51086700</v>
+        <v>69886500</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B26" t="n">
-        <v>271.4725408872279</v>
+        <v>276.4630533049319</v>
       </c>
       <c r="C26" t="n">
-        <v>273.6184749716116</v>
+        <v>276.7924425807819</v>
       </c>
       <c r="D26" t="n">
-        <v>267.969239224885</v>
+        <v>268.647962249571</v>
       </c>
       <c r="E26" t="n">
-        <v>270.8836669921875</v>
+        <v>269.8556518554688</v>
       </c>
       <c r="F26" t="n">
-        <v>69886500</v>
+        <v>86167100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B27" t="n">
-        <v>276.4630533049319</v>
+        <v>269.9055662700252</v>
       </c>
       <c r="C27" t="n">
-        <v>276.7924425807819</v>
+        <v>270.3347409275427</v>
       </c>
       <c r="D27" t="n">
-        <v>268.647962249571</v>
+        <v>265.7434858777505</v>
       </c>
       <c r="E27" t="n">
-        <v>269.8556518554688</v>
+        <v>268.5381469726562</v>
       </c>
       <c r="F27" t="n">
-        <v>86167100</v>
+        <v>50194600</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B28" t="n">
-        <v>269.9055662700252</v>
+        <v>267.8195068636227</v>
       </c>
       <c r="C28" t="n">
-        <v>270.3347409275427</v>
+        <v>270.9734988318123</v>
       </c>
       <c r="D28" t="n">
-        <v>265.7434858777505</v>
+        <v>267.1108661194202</v>
       </c>
       <c r="E28" t="n">
-        <v>268.5381469726562</v>
+        <v>269.5262756347656</v>
       </c>
       <c r="F28" t="n">
-        <v>50194600</v>
+        <v>49274800</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B29" t="n">
-        <v>267.8195068636227</v>
+        <v>268.0989800730272</v>
       </c>
       <c r="C29" t="n">
-        <v>270.9734988318123</v>
+        <v>271.1831284425123</v>
       </c>
       <c r="D29" t="n">
-        <v>267.1108661194202</v>
+        <v>266.4221834255846</v>
       </c>
       <c r="E29" t="n">
-        <v>269.5262756347656</v>
+        <v>269.6260986328125</v>
       </c>
       <c r="F29" t="n">
-        <v>49274800</v>
+        <v>43683100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B30" t="n">
-        <v>268.0989800730272</v>
+        <v>267.3803770260164</v>
       </c>
       <c r="C30" t="n">
-        <v>271.1831284425123</v>
+        <v>272.8798740142925</v>
       </c>
       <c r="D30" t="n">
-        <v>266.4221834255846</v>
+        <v>267.3803770260164</v>
       </c>
       <c r="E30" t="n">
-        <v>269.6260986328125</v>
+        <v>269.2567749023438</v>
       </c>
       <c r="F30" t="n">
-        <v>43683100</v>
+        <v>51204000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B31" t="n">
-        <v>267.3803770260164</v>
+        <v>269.2867154149515</v>
       </c>
       <c r="C31" t="n">
-        <v>272.8798740142925</v>
+        <v>271.7719991063764</v>
       </c>
       <c r="D31" t="n">
-        <v>267.3803770260164</v>
+        <v>266.2624809601513</v>
       </c>
       <c r="E31" t="n">
-        <v>269.2567749023438</v>
+        <v>267.9592590332031</v>
       </c>
       <c r="F31" t="n">
-        <v>51204000</v>
+        <v>48227400</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B32" t="n">
-        <v>269.2867154149515</v>
+        <v>268.7085692371889</v>
       </c>
       <c r="C32" t="n">
-        <v>271.7719991063764</v>
+        <v>273.4741297822401</v>
       </c>
       <c r="D32" t="n">
-        <v>266.2624809601513</v>
+        <v>267.2099714283653</v>
       </c>
       <c r="E32" t="n">
-        <v>267.9592590332031</v>
+        <v>269.1781311035156</v>
       </c>
       <c r="F32" t="n">
-        <v>48227400</v>
+        <v>41312400</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B33" t="n">
-        <v>268.7085692371889</v>
+        <v>269.5577590596557</v>
       </c>
       <c r="C33" t="n">
-        <v>273.4741297822401</v>
+        <v>275.6520624227355</v>
       </c>
       <c r="D33" t="n">
-        <v>267.2099714283653</v>
+        <v>269.5477586519058</v>
       </c>
       <c r="E33" t="n">
-        <v>269.1781311035156</v>
+        <v>274.99267578125</v>
       </c>
       <c r="F33" t="n">
-        <v>41312400</v>
+        <v>46208300</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B34" t="n">
-        <v>269.5577590596557</v>
+        <v>274.7429239716485</v>
       </c>
       <c r="C34" t="n">
-        <v>275.6520624227355</v>
+        <v>275.4722525277038</v>
       </c>
       <c r="D34" t="n">
-        <v>269.5477586519058</v>
+        <v>271.4460210796085</v>
       </c>
       <c r="E34" t="n">
-        <v>274.99267578125</v>
+        <v>273.21435546875</v>
       </c>
       <c r="F34" t="n">
-        <v>46208300</v>
+        <v>48398000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B35" t="n">
-        <v>274.7429239716485</v>
+        <v>273.8537435218178</v>
       </c>
       <c r="C35" t="n">
-        <v>275.4722525277038</v>
+        <v>276.4413491841305</v>
       </c>
       <c r="D35" t="n">
-        <v>271.4460210796085</v>
+        <v>271.8356428219928</v>
       </c>
       <c r="E35" t="n">
-        <v>273.21435546875</v>
+        <v>272.6948547363281</v>
       </c>
       <c r="F35" t="n">
-        <v>48398000</v>
+        <v>49602800</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B36" t="n">
-        <v>273.8537435218178</v>
+        <v>270.7965900477885</v>
       </c>
       <c r="C36" t="n">
-        <v>276.4413491841305</v>
+        <v>275.702003472256</v>
       </c>
       <c r="D36" t="n">
-        <v>271.8356428219928</v>
+        <v>269.3479639093673</v>
       </c>
       <c r="E36" t="n">
-        <v>272.6948547363281</v>
+        <v>272.1553344726562</v>
       </c>
       <c r="F36" t="n">
-        <v>49602800</v>
+        <v>47431300</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B37" t="n">
-        <v>270.7965900477885</v>
+        <v>268.5687054184609</v>
       </c>
       <c r="C37" t="n">
-        <v>275.702003472256</v>
+        <v>270.2371271729127</v>
       </c>
       <c r="D37" t="n">
-        <v>269.3479639093673</v>
+        <v>265.4815977121726</v>
       </c>
       <c r="E37" t="n">
-        <v>272.1553344726562</v>
+        <v>267.2099609375</v>
       </c>
       <c r="F37" t="n">
-        <v>47431300</v>
+        <v>45018300</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B38" t="n">
-        <v>268.5687054184609</v>
+        <v>269.7376065335732</v>
       </c>
       <c r="C38" t="n">
-        <v>270.2371271729127</v>
+        <v>270.4569347049811</v>
       </c>
       <c r="D38" t="n">
-        <v>265.4815977121726</v>
+        <v>265.0719890725528</v>
       </c>
       <c r="E38" t="n">
-        <v>267.2099609375</v>
+        <v>267.1900024414062</v>
       </c>
       <c r="F38" t="n">
-        <v>45018300</v>
+        <v>45677300</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B39" t="n">
-        <v>269.7376065335732</v>
+        <v>265.2817633125939</v>
       </c>
       <c r="C39" t="n">
-        <v>270.4569347049811</v>
+        <v>271.9555110777923</v>
       </c>
       <c r="D39" t="n">
-        <v>265.0719890725528</v>
+        <v>265.2517925781922</v>
       </c>
       <c r="E39" t="n">
-        <v>267.1900024414062</v>
+        <v>268.3089294433594</v>
       </c>
       <c r="F39" t="n">
-        <v>45677300</v>
+        <v>40424500</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B40" t="n">
-        <v>265.2817633125939</v>
+        <v>270.5768036466949</v>
       </c>
       <c r="C40" t="n">
-        <v>271.9555110777923</v>
+        <v>275.1725094767523</v>
       </c>
       <c r="D40" t="n">
-        <v>265.2517925781922</v>
+        <v>265.6714205454633</v>
       </c>
       <c r="E40" t="n">
-        <v>268.3089294433594</v>
+        <v>266.0010986328125</v>
       </c>
       <c r="F40" t="n">
-        <v>40424500</v>
+        <v>45823600</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B41" t="n">
-        <v>270.5768036466949</v>
+        <v>265.7013768088059</v>
       </c>
       <c r="C41" t="n">
-        <v>275.1725094767523</v>
+        <v>273.0744516711978</v>
       </c>
       <c r="D41" t="n">
-        <v>265.6714205454633</v>
+        <v>265.4216397990326</v>
       </c>
       <c r="E41" t="n">
-        <v>266.0010986328125</v>
+        <v>271.2361755371094</v>
       </c>
       <c r="F41" t="n">
-        <v>45823600</v>
+        <v>59030800</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B42" t="n">
-        <v>265.7013768088059</v>
+        <v>270.6467521230613</v>
       </c>
       <c r="C42" t="n">
-        <v>273.0744516711978</v>
+        <v>276.7410558404627</v>
       </c>
       <c r="D42" t="n">
-        <v>265.4216397990326</v>
+        <v>270.6467521230613</v>
       </c>
       <c r="E42" t="n">
-        <v>271.2361755371094</v>
+        <v>275.6620788574219</v>
       </c>
       <c r="F42" t="n">
-        <v>59030800</v>
+        <v>65585800</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B43" t="n">
-        <v>270.6467521230613</v>
+        <v>275.012667049666</v>
       </c>
       <c r="C43" t="n">
-        <v>276.7410558404627</v>
+        <v>280.1179060838009</v>
       </c>
       <c r="D43" t="n">
-        <v>270.6467521230613</v>
+        <v>274.9926967216935</v>
       </c>
       <c r="E43" t="n">
-        <v>275.6620788574219</v>
+        <v>276.7110900878906</v>
       </c>
       <c r="F43" t="n">
-        <v>65585800</v>
+        <v>46914200</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B44" t="n">
-        <v>275.012667049666</v>
+        <v>276.7010825487222</v>
       </c>
       <c r="C44" t="n">
-        <v>280.1179060838009</v>
+        <v>279.2686873678638</v>
       </c>
       <c r="D44" t="n">
-        <v>274.9926967216935</v>
+        <v>276.3714044558947</v>
       </c>
       <c r="E44" t="n">
-        <v>276.7110900878906</v>
+        <v>277.29052734375</v>
       </c>
       <c r="F44" t="n">
-        <v>46914200</v>
+        <v>33431400</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B45" t="n">
-        <v>276.7010825487222</v>
+        <v>277.0008150112318</v>
       </c>
       <c r="C45" t="n">
-        <v>279.2686873678638</v>
+        <v>278.7391786268174</v>
       </c>
       <c r="D45" t="n">
-        <v>276.3714044558947</v>
+        <v>275.7319827496524</v>
       </c>
       <c r="E45" t="n">
-        <v>277.29052734375</v>
+        <v>278.5893249511719</v>
       </c>
       <c r="F45" t="n">
-        <v>33431400</v>
+        <v>20135600</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B46" t="n">
-        <v>277.0008150112318</v>
+        <v>277.7501195744996</v>
       </c>
       <c r="C46" t="n">
-        <v>278.7391786268174</v>
+        <v>283.1550658399818</v>
       </c>
       <c r="D46" t="n">
-        <v>275.7319827496524</v>
+        <v>275.881872572025</v>
       </c>
       <c r="E46" t="n">
-        <v>278.5893249511719</v>
+        <v>282.8353576660156</v>
       </c>
       <c r="F46" t="n">
-        <v>20135600</v>
+        <v>46587700</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B47" t="n">
-        <v>277.7501195744996</v>
+        <v>282.7354345985028</v>
       </c>
       <c r="C47" t="n">
-        <v>283.1550658399818</v>
+        <v>287.1313151163589</v>
       </c>
       <c r="D47" t="n">
-        <v>275.881872572025</v>
+        <v>282.3657853749787</v>
       </c>
       <c r="E47" t="n">
-        <v>282.8353576660156</v>
+        <v>285.9224548339844</v>
       </c>
       <c r="F47" t="n">
-        <v>46587700</v>
+        <v>53669500</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B48" t="n">
-        <v>282.7354345985028</v>
+        <v>285.9324708384744</v>
       </c>
       <c r="C48" t="n">
-        <v>287.1313151163589</v>
+        <v>288.3501915351014</v>
       </c>
       <c r="D48" t="n">
-        <v>282.3657853749787</v>
+        <v>283.0351573834178</v>
       </c>
       <c r="E48" t="n">
-        <v>285.9224548339844</v>
+        <v>283.8843688964844</v>
       </c>
       <c r="F48" t="n">
-        <v>53669500</v>
+        <v>43538700</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B49" t="n">
-        <v>285.9324708384744</v>
+        <v>283.8344068650217</v>
       </c>
       <c r="C49" t="n">
-        <v>288.3501915351014</v>
+        <v>284.4638227692578</v>
       </c>
       <c r="D49" t="n">
-        <v>283.0351573834178</v>
+        <v>278.3295482939282</v>
       </c>
       <c r="E49" t="n">
-        <v>283.8843688964844</v>
+        <v>280.4375915527344</v>
       </c>
       <c r="F49" t="n">
-        <v>43538700</v>
+        <v>43989100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B50" t="n">
-        <v>283.8344068650217</v>
+        <v>280.2777430659675</v>
       </c>
       <c r="C50" t="n">
-        <v>284.4638227692578</v>
+        <v>280.8771882481053</v>
       </c>
       <c r="D50" t="n">
-        <v>278.3295482939282</v>
+        <v>277.7900501334527</v>
       </c>
       <c r="E50" t="n">
-        <v>280.4375915527344</v>
+        <v>278.5193786621094</v>
       </c>
       <c r="F50" t="n">
-        <v>43989100</v>
+        <v>47265800</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B51" t="n">
-        <v>280.2777430659675</v>
+        <v>277.8699843761556</v>
       </c>
       <c r="C51" t="n">
-        <v>280.8771882481053</v>
+        <v>279.4085531850005</v>
       </c>
       <c r="D51" t="n">
-        <v>277.7900501334527</v>
+        <v>275.8918244790692</v>
       </c>
       <c r="E51" t="n">
-        <v>278.5193786621094</v>
+        <v>277.6302185058594</v>
       </c>
       <c r="F51" t="n">
-        <v>47265800</v>
+        <v>38211800</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B52" t="n">
-        <v>277.8699843761556</v>
+        <v>277.8999627322321</v>
       </c>
       <c r="C52" t="n">
-        <v>279.4085531850005</v>
+        <v>279.7682096639769</v>
       </c>
       <c r="D52" t="n">
-        <v>275.8918244790692</v>
+        <v>276.6611317163261</v>
       </c>
       <c r="E52" t="n">
-        <v>277.6302185058594</v>
+        <v>276.9208679199219</v>
       </c>
       <c r="F52" t="n">
-        <v>38211800</v>
+        <v>32193300</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B53" t="n">
-        <v>277.8999627322321</v>
+        <v>277.490342786908</v>
       </c>
       <c r="C53" t="n">
-        <v>279.7682096639769</v>
+        <v>279.4884730680018</v>
       </c>
       <c r="D53" t="n">
-        <v>276.6611317163261</v>
+        <v>276.1815698919154</v>
       </c>
       <c r="E53" t="n">
-        <v>276.9208679199219</v>
+        <v>278.5193786621094</v>
       </c>
       <c r="F53" t="n">
-        <v>32193300</v>
+        <v>33038300</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B54" t="n">
-        <v>277.490342786908</v>
+        <v>278.8390875870869</v>
       </c>
       <c r="C54" t="n">
-        <v>279.4884730680018</v>
+        <v>279.3286197507982</v>
       </c>
       <c r="D54" t="n">
-        <v>276.1815698919154</v>
+        <v>273.5540244422053</v>
       </c>
       <c r="E54" t="n">
-        <v>278.5193786621094</v>
+        <v>277.7700805664062</v>
       </c>
       <c r="F54" t="n">
-        <v>33038300</v>
+        <v>33248000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B55" t="n">
-        <v>278.8390875870869</v>
+        <v>277.64021728323</v>
       </c>
       <c r="C55" t="n">
-        <v>279.3286197507982</v>
+        <v>278.9589906850317</v>
       </c>
       <c r="D55" t="n">
-        <v>273.5540244422053</v>
+        <v>276.5612402656973</v>
       </c>
       <c r="E55" t="n">
-        <v>277.7700805664062</v>
+        <v>278.0198669433594</v>
       </c>
       <c r="F55" t="n">
-        <v>33248000</v>
+        <v>39532900</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B56" t="n">
-        <v>277.64021728323</v>
+        <v>279.8880911943856</v>
       </c>
       <c r="C56" t="n">
-        <v>278.9589906850317</v>
+        <v>279.8880911943856</v>
       </c>
       <c r="D56" t="n">
-        <v>276.5612402656973</v>
+        <v>272.5849275039148</v>
       </c>
       <c r="E56" t="n">
-        <v>278.0198669433594</v>
+        <v>273.8537292480469</v>
       </c>
       <c r="F56" t="n">
-        <v>39532900</v>
+        <v>50409100</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B57" t="n">
-        <v>279.8880911943856</v>
+        <v>272.5649667835892</v>
       </c>
       <c r="C57" t="n">
-        <v>279.8880911943856</v>
+        <v>275.2424541197232</v>
       </c>
       <c r="D57" t="n">
-        <v>272.5849275039148</v>
+        <v>271.535930878856</v>
       </c>
       <c r="E57" t="n">
-        <v>273.8537292480469</v>
+        <v>274.353271484375</v>
       </c>
       <c r="F57" t="n">
-        <v>50409100</v>
+        <v>37648600</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B58" t="n">
-        <v>272.5649667835892</v>
+        <v>274.7529265191943</v>
       </c>
       <c r="C58" t="n">
-        <v>275.2424541197232</v>
+        <v>275.9018453851206</v>
       </c>
       <c r="D58" t="n">
-        <v>271.535930878856</v>
+        <v>271.3860817211021</v>
       </c>
       <c r="E58" t="n">
-        <v>274.353271484375</v>
+        <v>271.5858764648438</v>
       </c>
       <c r="F58" t="n">
-        <v>37648600</v>
+        <v>50138700</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B59" t="n">
-        <v>274.7529265191943</v>
+        <v>273.3542023206923</v>
       </c>
       <c r="C59" t="n">
-        <v>275.9018453851206</v>
+        <v>273.374203136776</v>
       </c>
       <c r="D59" t="n">
-        <v>271.3860817211021</v>
+        <v>266.7004552212896</v>
       </c>
       <c r="E59" t="n">
-        <v>271.5858764648438</v>
+        <v>271.935546875</v>
       </c>
       <c r="F59" t="n">
-        <v>50138700</v>
+        <v>51630700</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B60" t="n">
-        <v>273.3542023206923</v>
+        <v>271.8955859651445</v>
       </c>
       <c r="C60" t="n">
-        <v>273.374203136776</v>
+        <v>274.343307881706</v>
       </c>
       <c r="D60" t="n">
-        <v>266.7004552212896</v>
+        <v>269.6476892826471</v>
       </c>
       <c r="E60" t="n">
-        <v>271.935546875</v>
+        <v>273.4141845703125</v>
       </c>
       <c r="F60" t="n">
-        <v>51630700</v>
+        <v>144632000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B61" t="n">
-        <v>271.8955859651445</v>
+        <v>272.6048920133635</v>
       </c>
       <c r="C61" t="n">
-        <v>274.343307881706</v>
+        <v>273.6239579412959</v>
       </c>
       <c r="D61" t="n">
-        <v>269.6476892826471</v>
+        <v>270.2571133897843</v>
       </c>
       <c r="E61" t="n">
-        <v>273.4141845703125</v>
+        <v>270.7166748046875</v>
       </c>
       <c r="F61" t="n">
-        <v>144632000</v>
+        <v>36571800</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B62" t="n">
-        <v>272.6048920133635</v>
+        <v>270.5868091030317</v>
       </c>
       <c r="C62" t="n">
-        <v>273.6239579412959</v>
+        <v>272.2452609569047</v>
       </c>
       <c r="D62" t="n">
-        <v>270.2571133897843</v>
+        <v>269.3080068949797</v>
       </c>
       <c r="E62" t="n">
-        <v>270.7166748046875</v>
+        <v>272.1053771972656</v>
       </c>
       <c r="F62" t="n">
-        <v>36571800</v>
+        <v>29642000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B63" t="n">
-        <v>270.5868091030317</v>
+        <v>272.085389177814</v>
       </c>
       <c r="C63" t="n">
-        <v>272.2452609569047</v>
+        <v>275.1724967178681</v>
       </c>
       <c r="D63" t="n">
-        <v>269.3080068949797</v>
+        <v>271.9455359163183</v>
       </c>
       <c r="E63" t="n">
-        <v>272.1053771972656</v>
+        <v>273.5540161132812</v>
       </c>
       <c r="F63" t="n">
-        <v>29642000</v>
+        <v>17910600</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B64" t="n">
-        <v>272.085389177814</v>
+        <v>273.9037084592662</v>
       </c>
       <c r="C64" t="n">
-        <v>275.1724967178681</v>
+        <v>275.1125687682936</v>
       </c>
       <c r="D64" t="n">
-        <v>271.9455359163183</v>
+        <v>272.6049054553</v>
       </c>
       <c r="E64" t="n">
-        <v>273.5540161132812</v>
+        <v>273.1444091796875</v>
       </c>
       <c r="F64" t="n">
-        <v>17910600</v>
+        <v>21521800</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B65" t="n">
-        <v>273.9037084592662</v>
+        <v>272.4350823114352</v>
       </c>
       <c r="C65" t="n">
-        <v>275.1125687682936</v>
+        <v>274.103504063292</v>
       </c>
       <c r="D65" t="n">
-        <v>272.6049054553</v>
+        <v>272.0954038139857</v>
       </c>
       <c r="E65" t="n">
-        <v>273.1444091796875</v>
+        <v>273.5040893554688</v>
       </c>
       <c r="F65" t="n">
-        <v>21521800</v>
+        <v>23715200</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B66" t="n">
-        <v>272.4350823114352</v>
+        <v>272.5549704076282</v>
       </c>
       <c r="C66" t="n">
-        <v>274.103504063292</v>
+        <v>273.8237722152489</v>
       </c>
       <c r="D66" t="n">
-        <v>272.0954038139857</v>
+        <v>272.0254670796708</v>
       </c>
       <c r="E66" t="n">
-        <v>273.5040893554688</v>
+        <v>272.82470703125</v>
       </c>
       <c r="F66" t="n">
-        <v>23715200</v>
+        <v>22139600</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B67" t="n">
-        <v>272.5549704076282</v>
+        <v>272.804725327361</v>
       </c>
       <c r="C67" t="n">
-        <v>273.8237722152489</v>
+        <v>273.4241408373621</v>
       </c>
       <c r="D67" t="n">
-        <v>272.0254670796708</v>
+        <v>271.4959524300237</v>
       </c>
       <c r="E67" t="n">
-        <v>272.82470703125</v>
+        <v>271.6058349609375</v>
       </c>
       <c r="F67" t="n">
-        <v>22139600</v>
+        <v>27293600</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B68" t="n">
-        <v>272.804725327361</v>
+        <v>272.0054842546519</v>
       </c>
       <c r="C68" t="n">
-        <v>273.4241408373621</v>
+        <v>277.5802543100492</v>
       </c>
       <c r="D68" t="n">
-        <v>271.4959524300237</v>
+        <v>268.7485221479618</v>
       </c>
       <c r="E68" t="n">
-        <v>271.6058349609375</v>
+        <v>270.7566528320312</v>
       </c>
       <c r="F68" t="n">
-        <v>27293600</v>
+        <v>37838100</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B69" t="n">
-        <v>272.0054842546519</v>
+        <v>270.387007446453</v>
       </c>
       <c r="C69" t="n">
-        <v>277.5802543100492</v>
+        <v>271.2561892506844</v>
       </c>
       <c r="D69" t="n">
-        <v>268.7485221479618</v>
+        <v>265.8912142612155</v>
       </c>
       <c r="E69" t="n">
-        <v>270.7566528320312</v>
+        <v>267.0101623535156</v>
       </c>
       <c r="F69" t="n">
-        <v>37838100</v>
+        <v>45647200</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B70" t="n">
-        <v>270.387007446453</v>
+        <v>266.7503924619391</v>
       </c>
       <c r="C70" t="n">
-        <v>271.2561892506844</v>
+        <v>267.2998660934885</v>
       </c>
       <c r="D70" t="n">
-        <v>265.8912142612155</v>
+        <v>261.8749496989937</v>
       </c>
       <c r="E70" t="n">
-        <v>267.0101623535156</v>
+        <v>262.1147155761719</v>
       </c>
       <c r="F70" t="n">
-        <v>45647200</v>
+        <v>52352100</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B71" t="n">
-        <v>266.7503924619391</v>
+        <v>262.9539513876447</v>
       </c>
       <c r="C71" t="n">
-        <v>267.2998660934885</v>
+        <v>263.4334831315393</v>
       </c>
       <c r="D71" t="n">
-        <v>261.8749496989937</v>
+        <v>259.5671060011504</v>
       </c>
       <c r="E71" t="n">
-        <v>262.1147155761719</v>
+        <v>260.0866088867188</v>
       </c>
       <c r="F71" t="n">
-        <v>52352100</v>
+        <v>48309800</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B72" t="n">
-        <v>262.9539513876447</v>
+        <v>256.7797203952787</v>
       </c>
       <c r="C72" t="n">
-        <v>263.4334831315393</v>
+        <v>259.0476178563403</v>
       </c>
       <c r="D72" t="n">
-        <v>259.5671060011504</v>
+        <v>255.4609622909548</v>
       </c>
       <c r="E72" t="n">
-        <v>260.0866088867188</v>
+        <v>258.7978515625</v>
       </c>
       <c r="F72" t="n">
-        <v>48309800</v>
+        <v>50419300</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B73" t="n">
-        <v>256.7797203952787</v>
+        <v>258.8377955175017</v>
       </c>
       <c r="C73" t="n">
-        <v>259.0476178563403</v>
+        <v>259.9667440583015</v>
       </c>
       <c r="D73" t="n">
-        <v>255.4609622909548</v>
+        <v>255.9804837142826</v>
       </c>
       <c r="E73" t="n">
-        <v>258.7978515625</v>
+        <v>259.1275329589844</v>
       </c>
       <c r="F73" t="n">
-        <v>50419300</v>
+        <v>39997000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B74" t="n">
-        <v>258.8377955175017</v>
+        <v>258.9177364764393</v>
       </c>
       <c r="C74" t="n">
-        <v>259.9667440583015</v>
+        <v>261.055720113683</v>
       </c>
       <c r="D74" t="n">
-        <v>255.9804837142826</v>
+        <v>256.5599267903311</v>
       </c>
       <c r="E74" t="n">
-        <v>259.1275329589844</v>
+        <v>260.0067138671875</v>
       </c>
       <c r="F74" t="n">
-        <v>39997000</v>
+        <v>45263800</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B75" t="n">
-        <v>258.9177364764393</v>
+        <v>258.4781303943212</v>
       </c>
       <c r="C75" t="n">
-        <v>261.055720113683</v>
+        <v>261.5652379723006</v>
       </c>
       <c r="D75" t="n">
-        <v>256.5599267903311</v>
+        <v>258.148452318208</v>
       </c>
       <c r="E75" t="n">
-        <v>260.0067138671875</v>
+        <v>260.8059387207031</v>
       </c>
       <c r="F75" t="n">
-        <v>45263800</v>
+        <v>45730800</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B76" t="n">
-        <v>258.4781303943212</v>
+        <v>259.247418118488</v>
       </c>
       <c r="C76" t="n">
-        <v>261.5652379723006</v>
+        <v>261.5752571005171</v>
       </c>
       <c r="D76" t="n">
-        <v>258.148452318208</v>
+        <v>256.4700180914029</v>
       </c>
       <c r="E76" t="n">
-        <v>260.8059387207031</v>
+        <v>259.7169799804688</v>
       </c>
       <c r="F76" t="n">
-        <v>45730800</v>
+        <v>40019400</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B77" t="n">
-        <v>259.247418118488</v>
+        <v>260.4063187564486</v>
       </c>
       <c r="C77" t="n">
-        <v>261.5752571005171</v>
+        <v>260.7959687899761</v>
       </c>
       <c r="D77" t="n">
-        <v>256.4700180914029</v>
+        <v>256.8096782083212</v>
       </c>
       <c r="E77" t="n">
-        <v>259.7169799804688</v>
+        <v>257.9685974121094</v>
       </c>
       <c r="F77" t="n">
-        <v>40019400</v>
+        <v>39388600</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B78" t="n">
-        <v>260.4063187564486</v>
+        <v>257.6589020182799</v>
       </c>
       <c r="C78" t="n">
-        <v>260.7959687899761</v>
+        <v>258.6579671912775</v>
       </c>
       <c r="D78" t="n">
-        <v>256.8096782083212</v>
+        <v>254.6916772349149</v>
       </c>
       <c r="E78" t="n">
-        <v>257.9685974121094</v>
+        <v>255.2911224365234</v>
       </c>
       <c r="F78" t="n">
-        <v>39388600</v>
+        <v>72142800</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B79" t="n">
-        <v>257.6589020182799</v>
+        <v>252.4937373957159</v>
       </c>
       <c r="C79" t="n">
-        <v>258.6579671912775</v>
+        <v>254.5518092169813</v>
       </c>
       <c r="D79" t="n">
-        <v>254.6916772349149</v>
+        <v>243.1924430560896</v>
       </c>
       <c r="E79" t="n">
-        <v>255.2911224365234</v>
+        <v>246.4693756103516</v>
       </c>
       <c r="F79" t="n">
-        <v>72142800</v>
+        <v>80267500</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B80" t="n">
-        <v>252.4937373957159</v>
+        <v>248.4675090444481</v>
       </c>
       <c r="C80" t="n">
-        <v>254.5518092169813</v>
+        <v>251.3248360900433</v>
       </c>
       <c r="D80" t="n">
-        <v>243.1924430560896</v>
+        <v>244.9507953165175</v>
       </c>
       <c r="E80" t="n">
-        <v>246.4693756103516</v>
+        <v>247.4184875488281</v>
       </c>
       <c r="F80" t="n">
-        <v>80267500</v>
+        <v>54641700</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B81" t="n">
-        <v>248.4675090444481</v>
+        <v>248.9670398844787</v>
       </c>
       <c r="C81" t="n">
-        <v>251.3248360900433</v>
+        <v>250.7653602579427</v>
       </c>
       <c r="D81" t="n">
-        <v>244.9507953165175</v>
+        <v>247.9180183962477</v>
       </c>
       <c r="E81" t="n">
-        <v>247.4184875488281</v>
+        <v>248.1178436279297</v>
       </c>
       <c r="F81" t="n">
-        <v>54641700</v>
+        <v>39708300</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B82" t="n">
-        <v>248.9670398844787</v>
+        <v>247.0888078223564</v>
       </c>
       <c r="C82" t="n">
-        <v>250.7653602579427</v>
+        <v>249.176850391454</v>
       </c>
       <c r="D82" t="n">
-        <v>247.9180183962477</v>
+        <v>244.4512611104123</v>
       </c>
       <c r="E82" t="n">
-        <v>248.1178436279297</v>
+        <v>247.8081207275391</v>
       </c>
       <c r="F82" t="n">
-        <v>39708300</v>
+        <v>41689000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B83" t="n">
-        <v>247.0888078223564</v>
+        <v>251.2449001563489</v>
       </c>
       <c r="C83" t="n">
-        <v>249.176850391454</v>
+        <v>256.320152957849</v>
       </c>
       <c r="D83" t="n">
-        <v>244.4512611104123</v>
+        <v>249.5664780183616</v>
       </c>
       <c r="E83" t="n">
-        <v>247.8081207275391</v>
+        <v>255.1712341308594</v>
       </c>
       <c r="F83" t="n">
-        <v>41689000</v>
+        <v>55969200</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B84" t="n">
-        <v>251.2449001563489</v>
+        <v>258.9277169221324</v>
       </c>
       <c r="C84" t="n">
-        <v>256.320152957849</v>
+        <v>261.705116697089</v>
       </c>
       <c r="D84" t="n">
-        <v>249.5664780183616</v>
+        <v>257.9685924683142</v>
       </c>
       <c r="E84" t="n">
-        <v>255.1712341308594</v>
+        <v>258.0285339355469</v>
       </c>
       <c r="F84" t="n">
-        <v>55969200</v>
+        <v>49648300</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B85" t="n">
-        <v>258.9277169221324</v>
+        <v>257.409147241713</v>
       </c>
       <c r="C85" t="n">
-        <v>261.705116697089</v>
+        <v>258.6180076181917</v>
       </c>
       <c r="D85" t="n">
-        <v>257.9685924683142</v>
+        <v>254.2720830679268</v>
       </c>
       <c r="E85" t="n">
-        <v>258.0285339355469</v>
+        <v>256.2002868652344</v>
       </c>
       <c r="F85" t="n">
-        <v>49648300</v>
+        <v>41288000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B86" t="n">
-        <v>257.409147241713</v>
+        <v>257.758806680925</v>
       </c>
       <c r="C86" t="n">
-        <v>258.6180076181917</v>
+        <v>259.4072580677027</v>
       </c>
       <c r="D86" t="n">
-        <v>254.2720830679268</v>
+        <v>254.1721664792058</v>
       </c>
       <c r="E86" t="n">
-        <v>256.2002868652344</v>
+        <v>258.0385437011719</v>
       </c>
       <c r="F86" t="n">
-        <v>41288000</v>
+        <v>67253000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B87" t="n">
-        <v>257.758806680925</v>
+        <v>254.9314433110553</v>
       </c>
       <c r="C87" t="n">
-        <v>259.4072580677027</v>
+        <v>261.6551472598355</v>
       </c>
       <c r="D87" t="n">
-        <v>254.1721664792058</v>
+        <v>251.9442331321547</v>
       </c>
       <c r="E87" t="n">
-        <v>258.0385437011719</v>
+        <v>259.2374267578125</v>
       </c>
       <c r="F87" t="n">
-        <v>67253000</v>
+        <v>92443400</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B88" t="n">
-        <v>254.9314433110553</v>
+        <v>259.7869174093499</v>
       </c>
       <c r="C88" t="n">
-        <v>261.6551472598355</v>
+        <v>270.2371306501278</v>
       </c>
       <c r="D88" t="n">
-        <v>251.9442331321547</v>
+        <v>258.9676766447768</v>
       </c>
       <c r="E88" t="n">
-        <v>259.2374267578125</v>
+        <v>269.7575988769531</v>
       </c>
       <c r="F88" t="n">
-        <v>92443400</v>
+        <v>73913400</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B89" t="n">
-        <v>259.7869174093499</v>
+        <v>268.9483513556569</v>
       </c>
       <c r="C89" t="n">
-        <v>270.2371306501278</v>
+        <v>271.6258386480508</v>
       </c>
       <c r="D89" t="n">
-        <v>258.9676766447768</v>
+        <v>267.3598109321867</v>
       </c>
       <c r="E89" t="n">
-        <v>269.7575988769531</v>
+        <v>269.2280883789062</v>
       </c>
       <c r="F89" t="n">
-        <v>73913400</v>
+        <v>64394700</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B90" t="n">
-        <v>268.9483513556569</v>
+        <v>272.03545112075</v>
       </c>
       <c r="C90" t="n">
-        <v>271.6258386480508</v>
+        <v>278.6892285045384</v>
       </c>
       <c r="D90" t="n">
-        <v>267.3598109321867</v>
+        <v>272.03545112075</v>
       </c>
       <c r="E90" t="n">
-        <v>269.2280883789062</v>
+        <v>276.2315063476562</v>
       </c>
       <c r="F90" t="n">
-        <v>64394700</v>
+        <v>90545700</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B91" t="n">
-        <v>272.03545112075</v>
+        <v>277.8699949435269</v>
       </c>
       <c r="C91" t="n">
-        <v>278.6892285045384</v>
+        <v>279.2387093202658</v>
       </c>
       <c r="D91" t="n">
-        <v>272.03545112075</v>
+        <v>272.9745818081728</v>
       </c>
       <c r="E91" t="n">
-        <v>276.2315063476562</v>
+        <v>275.6520690917969</v>
       </c>
       <c r="F91" t="n">
-        <v>90545700</v>
+        <v>52977400</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B92" t="n">
-        <v>277.8699949435269</v>
+        <v>276.8609202349588</v>
       </c>
       <c r="C92" t="n">
-        <v>279.2387093202658</v>
+        <v>280.6473855638201</v>
       </c>
       <c r="D92" t="n">
-        <v>272.9745818081728</v>
+        <v>276.6710954236804</v>
       </c>
       <c r="E92" t="n">
-        <v>275.6520690917969</v>
+        <v>277.8599853515625</v>
       </c>
       <c r="F92" t="n">
-        <v>52977400</v>
+        <v>50453400</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B93" t="n">
-        <v>276.8609202349588</v>
+        <v>277.9100036621094</v>
       </c>
       <c r="C93" t="n">
-        <v>280.6473855638201</v>
+        <v>278.2000122070312</v>
       </c>
       <c r="D93" t="n">
-        <v>276.6710954236804</v>
+        <v>271.7000122070312</v>
       </c>
       <c r="E93" t="n">
-        <v>277.8599853515625</v>
+        <v>274.6199951171875</v>
       </c>
       <c r="F93" t="n">
-        <v>50453400</v>
+        <v>44623400</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B94" t="n">
-        <v>277.9100036621094</v>
+        <v>274.8900146484375</v>
       </c>
       <c r="C94" t="n">
-        <v>278.2000122070312</v>
+        <v>275.3699951171875</v>
       </c>
       <c r="D94" t="n">
-        <v>271.7000122070312</v>
+        <v>272.9400024414062</v>
       </c>
       <c r="E94" t="n">
-        <v>274.6199951171875</v>
+        <v>273.6799926757812</v>
       </c>
       <c r="F94" t="n">
-        <v>44623400</v>
+        <v>34376900</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B95" t="n">
-        <v>274.8900146484375</v>
+        <v>274.7000122070312</v>
       </c>
       <c r="C95" t="n">
-        <v>275.3699951171875</v>
+        <v>280.1799926757812</v>
       </c>
       <c r="D95" t="n">
-        <v>272.9400024414062</v>
+        <v>274.4500122070312</v>
       </c>
       <c r="E95" t="n">
-        <v>273.6799926757812</v>
+        <v>275.5</v>
       </c>
       <c r="F95" t="n">
-        <v>34376900</v>
+        <v>51931300</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B96" t="n">
-        <v>274.7000122070312</v>
+        <v>275.5899963378906</v>
       </c>
       <c r="C96" t="n">
-        <v>280.1799926757812</v>
+        <v>275.7200012207031</v>
       </c>
       <c r="D96" t="n">
-        <v>274.4500122070312</v>
+        <v>260.1799926757812</v>
       </c>
       <c r="E96" t="n">
-        <v>275.5</v>
+        <v>261.7300109863281</v>
       </c>
       <c r="F96" t="n">
-        <v>51931300</v>
+        <v>81077200</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B97" t="n">
-        <v>275.5899963378906</v>
+        <v>262.010009765625</v>
       </c>
       <c r="C97" t="n">
-        <v>275.7200012207031</v>
+        <v>262.2300109863281</v>
       </c>
       <c r="D97" t="n">
-        <v>260.1799926757812</v>
+        <v>255.4499969482422</v>
       </c>
       <c r="E97" t="n">
-        <v>261.7300109863281</v>
+        <v>255.7799987792969</v>
       </c>
       <c r="F97" t="n">
-        <v>81077200</v>
+        <v>56290700</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B98" t="n">
-        <v>262.010009765625</v>
+        <v>258.0499877929688</v>
       </c>
       <c r="C98" t="n">
-        <v>262.2300109863281</v>
+        <v>266.2900085449219</v>
       </c>
       <c r="D98" t="n">
-        <v>255.4499969482422</v>
+        <v>255.5399932861328</v>
       </c>
       <c r="E98" t="n">
-        <v>255.7799987792969</v>
+        <v>263.8800048828125</v>
       </c>
       <c r="F98" t="n">
-        <v>56290700</v>
+        <v>58469100</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B99" t="n">
-        <v>258.0499877929688</v>
+        <v>263.6000061035156</v>
       </c>
       <c r="C99" t="n">
-        <v>266.2900085449219</v>
+        <v>266.8200073242188</v>
       </c>
       <c r="D99" t="n">
-        <v>255.5399932861328</v>
+        <v>262.4500122070312</v>
       </c>
       <c r="E99" t="n">
-        <v>263.8800048828125</v>
+        <v>264.3500061035156</v>
       </c>
       <c r="F99" t="n">
-        <v>58469100</v>
+        <v>34203300</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B100" t="n">
-        <v>263.6000061035156</v>
+        <v>262.6000061035156</v>
       </c>
       <c r="C100" t="n">
-        <v>266.8200073242188</v>
+        <v>264.4800109863281</v>
       </c>
       <c r="D100" t="n">
-        <v>262.4500122070312</v>
+        <v>260.0499877929688</v>
       </c>
       <c r="E100" t="n">
-        <v>264.3500061035156</v>
+        <v>260.5799865722656</v>
       </c>
       <c r="F100" t="n">
-        <v>34203300</v>
+        <v>30845300</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B101" t="n">
-        <v>262.6000061035156</v>
+        <v>258.9700012207031</v>
       </c>
       <c r="C101" t="n">
-        <v>264.4800109863281</v>
+        <v>264.75</v>
       </c>
       <c r="D101" t="n">
-        <v>260.0499877929688</v>
+        <v>258.1600036621094</v>
       </c>
       <c r="E101" t="n">
-        <v>260.5799865722656</v>
+        <v>264.5799865722656</v>
       </c>
       <c r="F101" t="n">
-        <v>30845300</v>
+        <v>42070500</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B102" t="n">
-        <v>258.9700012207031</v>
+        <v>263.489990234375</v>
       </c>
       <c r="C102" t="n">
-        <v>264.75</v>
+        <v>269.4299926757812</v>
       </c>
       <c r="D102" t="n">
-        <v>258.1600036621094</v>
+        <v>263.3800048828125</v>
       </c>
       <c r="E102" t="n">
-        <v>264.5799865722656</v>
+        <v>266.1799926757812</v>
       </c>
       <c r="F102" t="n">
-        <v>42070500</v>
+        <v>37308200</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B103" t="n">
-        <v>263.489990234375</v>
+        <v>267.8599853515625</v>
       </c>
       <c r="C103" t="n">
-        <v>269.4299926757812</v>
+        <v>274.8900146484375</v>
       </c>
       <c r="D103" t="n">
-        <v>263.3800048828125</v>
+        <v>267.7099914550781</v>
       </c>
       <c r="E103" t="n">
-        <v>266.1799926757812</v>
+        <v>272.1400146484375</v>
       </c>
       <c r="F103" t="n">
-        <v>37308200</v>
+        <v>47014600</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B104" t="n">
-        <v>267.8599853515625</v>
+        <v>271.7799987792969</v>
       </c>
       <c r="C104" t="n">
-        <v>274.8900146484375</v>
+        <v>274.9400024414062</v>
       </c>
       <c r="D104" t="n">
-        <v>267.7099914550781</v>
+        <v>271.0499877929688</v>
       </c>
       <c r="E104" t="n">
-        <v>272.1400146484375</v>
+        <v>274.2300109863281</v>
       </c>
       <c r="F104" t="n">
-        <v>47014600</v>
+        <v>33714300</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B105" t="n">
-        <v>271.7799987792969</v>
+        <v>274.9500122070312</v>
       </c>
       <c r="C105" t="n">
-        <v>274.9400024414062</v>
+        <v>276.1099853515625</v>
       </c>
       <c r="D105" t="n">
-        <v>271.0499877929688</v>
+        <v>270.7999877929688</v>
       </c>
       <c r="E105" t="n">
-        <v>274.2300109863281</v>
+        <v>272.9500122070312</v>
       </c>
       <c r="F105" t="n">
-        <v>33714300</v>
+        <v>32345100</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B106" t="n">
-        <v>274.9500122070312</v>
+        <v>272.8099975585938</v>
       </c>
       <c r="C106" t="n">
-        <v>276.1099853515625</v>
+        <v>272.8099975585938</v>
       </c>
       <c r="D106" t="n">
-        <v>270.7999877929688</v>
+        <v>262.8900146484375</v>
       </c>
       <c r="E106" t="n">
-        <v>272.9500122070312</v>
+        <v>264.1799926757812</v>
       </c>
       <c r="F106" t="n">
-        <v>32345100</v>
+        <v>72366500</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B107" t="n">
-        <v>272.8099975585938</v>
+        <v>262.4100036621094</v>
       </c>
       <c r="C107" t="n">
-        <v>272.8099975585938</v>
+        <v>266.5299987792969</v>
       </c>
       <c r="D107" t="n">
-        <v>262.8900146484375</v>
+        <v>260.2000122070312</v>
       </c>
       <c r="E107" t="n">
-        <v>264.1799926757812</v>
+        <v>264.7200012207031</v>
       </c>
       <c r="F107" t="n">
-        <v>72366500</v>
+        <v>41827900</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B108" t="n">
-        <v>262.4100036621094</v>
+        <v>263.4800109863281</v>
       </c>
       <c r="C108" t="n">
-        <v>266.5299987792969</v>
+        <v>265.5599975585938</v>
       </c>
       <c r="D108" t="n">
-        <v>260.2000122070312</v>
+        <v>260.1300048828125</v>
       </c>
       <c r="E108" t="n">
-        <v>264.7200012207031</v>
+        <v>263.75</v>
       </c>
       <c r="F108" t="n">
-        <v>41827900</v>
+        <v>38568900</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B109" t="n">
-        <v>263.4800109863281</v>
+        <v>264.6499938964844</v>
       </c>
       <c r="C109" t="n">
-        <v>265.5599975585938</v>
+        <v>266.1499938964844</v>
       </c>
       <c r="D109" t="n">
-        <v>260.1300048828125</v>
+        <v>261.4200134277344</v>
       </c>
       <c r="E109" t="n">
-        <v>263.75</v>
+        <v>262.5199890136719</v>
       </c>
       <c r="F109" t="n">
-        <v>38568900</v>
+        <v>39803100</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B110" t="n">
-        <v>264.6499938964844</v>
+        <v>260.7900085449219</v>
       </c>
       <c r="C110" t="n">
-        <v>266.1499938964844</v>
+        <v>261.5599975585938</v>
       </c>
       <c r="D110" t="n">
-        <v>261.4200134277344</v>
+        <v>257.25</v>
       </c>
       <c r="E110" t="n">
-        <v>262.5199890136719</v>
+        <v>260.2900085449219</v>
       </c>
       <c r="F110" t="n">
-        <v>39803100</v>
+        <v>49658600</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B111" t="n">
-        <v>260.7900085449219</v>
+        <v>258.6300048828125</v>
       </c>
       <c r="C111" t="n">
-        <v>261.5599975585938</v>
+        <v>258.7699890136719</v>
       </c>
       <c r="D111" t="n">
-        <v>257.25</v>
+        <v>254.3699951171875</v>
       </c>
       <c r="E111" t="n">
-        <v>260.2900085449219</v>
+        <v>257.4599914550781</v>
       </c>
       <c r="F111" t="n">
-        <v>49658600</v>
+        <v>41120000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B112" t="n">
-        <v>258.6300048828125</v>
+        <v>255.6900024414062</v>
       </c>
       <c r="C112" t="n">
-        <v>258.7699890136719</v>
+        <v>261.1499938964844</v>
       </c>
       <c r="D112" t="n">
-        <v>254.3699951171875</v>
+        <v>253.6799926757812</v>
       </c>
       <c r="E112" t="n">
-        <v>257.4599914550781</v>
+        <v>259.8800048828125</v>
       </c>
       <c r="F112" t="n">
-        <v>41120000</v>
+        <v>38218500</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B113" t="n">
-        <v>255.6900024414062</v>
+        <v>257.6499938964844</v>
       </c>
       <c r="C113" t="n">
-        <v>261.1499938964844</v>
+        <v>262.4800109863281</v>
       </c>
       <c r="D113" t="n">
-        <v>253.6799926757812</v>
+        <v>256.9500122070312</v>
       </c>
       <c r="E113" t="n">
-        <v>259.8800048828125</v>
+        <v>260.8299865722656</v>
       </c>
       <c r="F113" t="n">
-        <v>38218500</v>
+        <v>30590800</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B114" t="n">
-        <v>257.6499938964844</v>
+        <v>261.0899963378906</v>
       </c>
       <c r="C114" t="n">
-        <v>262.4800109863281</v>
+        <v>262.1300048828125</v>
       </c>
       <c r="D114" t="n">
-        <v>256.9500122070312</v>
+        <v>259.5499877929688</v>
       </c>
       <c r="E114" t="n">
-        <v>260.8299865722656</v>
+        <v>260.8099975585938</v>
       </c>
       <c r="F114" t="n">
-        <v>30590800</v>
+        <v>26218900</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B115" t="n">
-        <v>261.0899963378906</v>
+        <v>258.6600036621094</v>
       </c>
       <c r="C115" t="n">
-        <v>262.1300048828125</v>
+        <v>258.9500122070312</v>
       </c>
       <c r="D115" t="n">
-        <v>259.5499877929688</v>
+        <v>254.1799926757812</v>
       </c>
       <c r="E115" t="n">
-        <v>260.8099975585938</v>
+        <v>255.7599945068359</v>
       </c>
       <c r="F115" t="n">
-        <v>26218900</v>
+        <v>40794000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B116" t="n">
-        <v>258.6600036621094</v>
+        <v>255.4799957275391</v>
       </c>
       <c r="C116" t="n">
-        <v>258.9500122070312</v>
+        <v>256.3299865722656</v>
       </c>
       <c r="D116" t="n">
-        <v>254.1799926757812</v>
+        <v>249.5200042724609</v>
       </c>
       <c r="E116" t="n">
-        <v>255.7599945068359</v>
+        <v>250.1199951171875</v>
       </c>
       <c r="F116" t="n">
-        <v>40794000</v>
+        <v>36930000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B117" t="n">
-        <v>255.4799957275391</v>
+        <v>252.1100006103516</v>
       </c>
       <c r="C117" t="n">
-        <v>256.3299865722656</v>
+        <v>253.8899993896484</v>
       </c>
       <c r="D117" t="n">
-        <v>249.5200042724609</v>
+        <v>249.8800048828125</v>
       </c>
       <c r="E117" t="n">
-        <v>250.1199951171875</v>
+        <v>252.8200073242188</v>
       </c>
       <c r="F117" t="n">
-        <v>36930000</v>
+        <v>32074200</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B118" t="n">
-        <v>252.1100006103516</v>
+        <v>252.9600067138672</v>
       </c>
       <c r="C118" t="n">
-        <v>253.8899993896484</v>
+        <v>255.1300048828125</v>
       </c>
       <c r="D118" t="n">
-        <v>249.8800048828125</v>
+        <v>252.1799926757812</v>
       </c>
       <c r="E118" t="n">
-        <v>252.8200073242188</v>
+        <v>254.2299957275391</v>
       </c>
       <c r="F118" t="n">
-        <v>32074200</v>
+        <v>32361600</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B119" t="n">
-        <v>252.9600067138672</v>
+        <v>252.6300048828125</v>
       </c>
       <c r="C119" t="n">
-        <v>255.1300048828125</v>
+        <v>254.9400024414062</v>
       </c>
       <c r="D119" t="n">
-        <v>252.1799926757812</v>
+        <v>249</v>
       </c>
       <c r="E119" t="n">
-        <v>254.2299957275391</v>
+        <v>249.9400024414062</v>
       </c>
       <c r="F119" t="n">
-        <v>32361600</v>
+        <v>35757900</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B120" t="n">
-        <v>252.6300048828125</v>
+        <v>249.3999938964844</v>
       </c>
       <c r="C120" t="n">
-        <v>254.9400024414062</v>
+        <v>251.8300018310547</v>
       </c>
       <c r="D120" t="n">
-        <v>249</v>
+        <v>247.3000030517578</v>
       </c>
       <c r="E120" t="n">
-        <v>249.9400024414062</v>
+        <v>248.9600067138672</v>
       </c>
       <c r="F120" t="n">
-        <v>35757900</v>
+        <v>34864100</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B121" t="n">
-        <v>249.3999938964844</v>
+        <v>247.9799957275391</v>
       </c>
       <c r="C121" t="n">
-        <v>251.8300018310547</v>
+        <v>249.1999969482422</v>
       </c>
       <c r="D121" t="n">
-        <v>247.3000030517578</v>
+        <v>246</v>
       </c>
       <c r="E121" t="n">
-        <v>248.9600067138672</v>
+        <v>247.9900054931641</v>
       </c>
       <c r="F121" t="n">
-        <v>34864100</v>
+        <v>88331100</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B122" t="n">
-        <v>247.9799957275391</v>
+        <v>253.9700012207031</v>
       </c>
       <c r="C122" t="n">
-        <v>249.1999969482422</v>
+        <v>254.6000061035156</v>
       </c>
       <c r="D122" t="n">
-        <v>246</v>
+        <v>250.2799987792969</v>
       </c>
       <c r="E122" t="n">
-        <v>247.9900054931641</v>
+        <v>251.4900054931641</v>
       </c>
       <c r="F122" t="n">
-        <v>88331100</v>
+        <v>40546100</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B123" t="n">
-        <v>253.9700012207031</v>
+        <v>250.3500061035156</v>
       </c>
       <c r="C123" t="n">
-        <v>254.6000061035156</v>
+        <v>254.8300018310547</v>
       </c>
       <c r="D123" t="n">
-        <v>250.2799987792969</v>
+        <v>249.5500030517578</v>
       </c>
       <c r="E123" t="n">
-        <v>251.4900054931641</v>
+        <v>251.6399993896484</v>
       </c>
       <c r="F123" t="n">
-        <v>40546100</v>
+        <v>45152300</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B124" t="n">
-        <v>250.3500061035156</v>
+        <v>254.1000061035156</v>
       </c>
       <c r="C124" t="n">
-        <v>254.8300018310547</v>
+        <v>255</v>
       </c>
       <c r="D124" t="n">
-        <v>249.5500030517578</v>
+        <v>251.6000061035156</v>
       </c>
       <c r="E124" t="n">
-        <v>251.6399993896484</v>
+        <v>252.6199951171875</v>
       </c>
       <c r="F124" t="n">
-        <v>45111500</v>
+        <v>28476700</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B125" t="n">
+        <v>252.1199951171875</v>
+      </c>
+      <c r="C125" t="n">
+        <v>257</v>
+      </c>
+      <c r="D125" t="n">
+        <v>250.7700042724609</v>
+      </c>
+      <c r="E125" t="n">
+        <v>252.8899993896484</v>
+      </c>
+      <c r="F125" t="n">
+        <v>41702500</v>
       </c>
     </row>
   </sheetData>
@@ -5445,7 +5485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5482,2462 +5522,2482 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B2" t="n">
-        <v>507.9477836110377</v>
+        <v>509.3817950243417</v>
       </c>
       <c r="C2" t="n">
-        <v>511.8117209714621</v>
+        <v>514.7096154882738</v>
       </c>
       <c r="D2" t="n">
-        <v>504.5220265940347</v>
+        <v>506.7726497345118</v>
       </c>
       <c r="E2" t="n">
-        <v>509.3419799804688</v>
+        <v>512.4689331054688</v>
       </c>
       <c r="F2" t="n">
-        <v>16213100</v>
+        <v>17617800</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B3" t="n">
-        <v>509.3817950243417</v>
+        <v>511.1145975787894</v>
       </c>
       <c r="C3" t="n">
-        <v>514.7096154882738</v>
+        <v>516.0142062084105</v>
       </c>
       <c r="D3" t="n">
-        <v>506.7726497345118</v>
+        <v>507.549436190283</v>
       </c>
       <c r="E3" t="n">
-        <v>512.4689331054688</v>
+        <v>515.8051147460938</v>
       </c>
       <c r="F3" t="n">
-        <v>17617800</v>
+        <v>19728200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B4" t="n">
-        <v>511.1145975787894</v>
+        <v>512.6680995330014</v>
       </c>
       <c r="C4" t="n">
-        <v>516.0142062084105</v>
+        <v>518.3544751787417</v>
       </c>
       <c r="D4" t="n">
-        <v>507.549436190283</v>
+        <v>509.5709932440202</v>
       </c>
       <c r="E4" t="n">
-        <v>515.8051147460938</v>
+        <v>517.5578002929688</v>
       </c>
       <c r="F4" t="n">
-        <v>19728200</v>
+        <v>22632300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B5" t="n">
-        <v>512.6681599915194</v>
+        <v>515.4963429681408</v>
       </c>
       <c r="C5" t="n">
-        <v>518.3545363078492</v>
+        <v>519.4399047558908</v>
       </c>
       <c r="D5" t="n">
-        <v>509.5710533372991</v>
+        <v>508.5651441188421</v>
       </c>
       <c r="E5" t="n">
-        <v>517.557861328125</v>
+        <v>513.6041870117188</v>
       </c>
       <c r="F5" t="n">
-        <v>22632300</v>
+        <v>21222900</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B6" t="n">
-        <v>515.496404228155</v>
+        <v>514.9585548343116</v>
       </c>
       <c r="C6" t="n">
-        <v>519.4399664845459</v>
+        <v>518.3345307125708</v>
       </c>
       <c r="D6" t="n">
-        <v>508.5652045551738</v>
+        <v>512.8672756929882</v>
       </c>
       <c r="E6" t="n">
-        <v>513.604248046875</v>
+        <v>515.20751953125</v>
       </c>
       <c r="F6" t="n">
-        <v>21222900</v>
+        <v>15112300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B7" t="n">
-        <v>514.9585548343116</v>
+        <v>516.4623876768178</v>
       </c>
       <c r="C7" t="n">
-        <v>518.3345307125708</v>
+        <v>528.8309994124726</v>
       </c>
       <c r="D7" t="n">
-        <v>512.8672756929882</v>
+        <v>516.0541122577388</v>
       </c>
       <c r="E7" t="n">
-        <v>515.20751953125</v>
+        <v>526.3811645507812</v>
       </c>
       <c r="F7" t="n">
-        <v>15112300</v>
+        <v>21388600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B8" t="n">
-        <v>516.4623876768178</v>
+        <v>526.1022689962125</v>
       </c>
       <c r="C8" t="n">
-        <v>528.8309994124726</v>
+        <v>527.6060256392368</v>
       </c>
       <c r="D8" t="n">
-        <v>516.0541122577388</v>
+        <v>519.2806599401652</v>
       </c>
       <c r="E8" t="n">
-        <v>526.3811645507812</v>
+        <v>521.8101196289062</v>
       </c>
       <c r="F8" t="n">
-        <v>21388600</v>
+        <v>14615200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B9" t="n">
-        <v>526.1022689962125</v>
+        <v>521.1130687043808</v>
       </c>
       <c r="C9" t="n">
-        <v>527.6060256392368</v>
+        <v>524.7678538085896</v>
       </c>
       <c r="D9" t="n">
-        <v>519.2806599401652</v>
+        <v>520.923853084141</v>
       </c>
       <c r="E9" t="n">
-        <v>521.8101196289062</v>
+        <v>522.676513671875</v>
       </c>
       <c r="F9" t="n">
-        <v>14615200</v>
+        <v>13363400</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B10" t="n">
-        <v>521.1130687043808</v>
+        <v>520.1769452354545</v>
       </c>
       <c r="C10" t="n">
-        <v>524.7678538085896</v>
+        <v>522.158694647609</v>
       </c>
       <c r="D10" t="n">
-        <v>520.923853084141</v>
+        <v>515.2574000210162</v>
       </c>
       <c r="E10" t="n">
-        <v>522.676513671875</v>
+        <v>520.2366943359375</v>
       </c>
       <c r="F10" t="n">
-        <v>13363400</v>
+        <v>18343600</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B11" t="n">
-        <v>520.1769452354545</v>
+        <v>517.4881335274953</v>
       </c>
       <c r="C11" t="n">
-        <v>522.158694647609</v>
+        <v>521.4118200258811</v>
       </c>
       <c r="D11" t="n">
-        <v>515.2574000210162</v>
+        <v>507.5195762105422</v>
       </c>
       <c r="E11" t="n">
-        <v>520.2366943359375</v>
+        <v>508.8440551757812</v>
       </c>
       <c r="F11" t="n">
-        <v>18343600</v>
+        <v>24133800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B12" t="n">
-        <v>517.4881335274953</v>
+        <v>514.2714771071726</v>
       </c>
       <c r="C12" t="n">
-        <v>521.4118200258811</v>
+        <v>514.2714771071726</v>
       </c>
       <c r="D12" t="n">
-        <v>507.5195762105422</v>
+        <v>509.5610838753375</v>
       </c>
       <c r="E12" t="n">
-        <v>508.8440551757812</v>
+        <v>511.9212646484375</v>
       </c>
       <c r="F12" t="n">
-        <v>24133800</v>
+        <v>14284200</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B13" t="n">
-        <v>514.2714464494894</v>
+        <v>508.1170420708167</v>
       </c>
       <c r="C13" t="n">
-        <v>514.2714464494894</v>
+        <v>513.146147202046</v>
       </c>
       <c r="D13" t="n">
-        <v>509.5610534984588</v>
+        <v>503.9045484424133</v>
       </c>
       <c r="E13" t="n">
-        <v>511.9212341308594</v>
+        <v>511.4432067871094</v>
       </c>
       <c r="F13" t="n">
-        <v>14284200</v>
+        <v>14684300</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B14" t="n">
-        <v>508.1170723899241</v>
+        <v>512.8275263160849</v>
       </c>
       <c r="C14" t="n">
-        <v>513.1461778212379</v>
+        <v>515.0482722356254</v>
       </c>
       <c r="D14" t="n">
-        <v>503.9045785101632</v>
+        <v>507.8880442394631</v>
       </c>
       <c r="E14" t="n">
-        <v>511.4432373046875</v>
+        <v>511.3038330078125</v>
       </c>
       <c r="F14" t="n">
-        <v>14684300</v>
+        <v>14694700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B15" t="n">
-        <v>512.8274957075639</v>
+        <v>510.4573477017149</v>
       </c>
       <c r="C15" t="n">
-        <v>515.0482414945574</v>
+        <v>514.7096236704256</v>
       </c>
       <c r="D15" t="n">
-        <v>507.888013925759</v>
+        <v>506.0257636510178</v>
       </c>
       <c r="E15" t="n">
-        <v>511.3038024902344</v>
+        <v>509.4913330078125</v>
       </c>
       <c r="F15" t="n">
-        <v>14694700</v>
+        <v>15559600</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B16" t="n">
-        <v>510.4573477017149</v>
+        <v>506.9320087638593</v>
       </c>
       <c r="C16" t="n">
-        <v>514.7096236704256</v>
+        <v>513.3453119402852</v>
       </c>
       <c r="D16" t="n">
-        <v>506.0257636510178</v>
+        <v>505.2091619742922</v>
       </c>
       <c r="E16" t="n">
-        <v>509.4913330078125</v>
+        <v>511.4532165527344</v>
       </c>
       <c r="F16" t="n">
-        <v>15559600</v>
+        <v>19867800</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B17" t="n">
-        <v>506.9320390116644</v>
+        <v>512.4788764440519</v>
       </c>
       <c r="C17" t="n">
-        <v>513.3453425707617</v>
+        <v>516.5519656323323</v>
       </c>
       <c r="D17" t="n">
-        <v>505.2091921192977</v>
+        <v>511.3037703677804</v>
       </c>
       <c r="E17" t="n">
-        <v>511.4532470703125</v>
+        <v>514.6498413085938</v>
       </c>
       <c r="F17" t="n">
-        <v>19867800</v>
+        <v>14665600</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B18" t="n">
-        <v>512.4788764440519</v>
+        <v>515.3569857054445</v>
       </c>
       <c r="C18" t="n">
-        <v>516.5519656323323</v>
+        <v>516.5420602391357</v>
       </c>
       <c r="D18" t="n">
-        <v>511.3037703677804</v>
+        <v>510.9154330870712</v>
       </c>
       <c r="E18" t="n">
-        <v>514.6498413085938</v>
+        <v>515.5162963867188</v>
       </c>
       <c r="F18" t="n">
-        <v>14665600</v>
+        <v>15586200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B19" t="n">
-        <v>515.3569857054445</v>
+        <v>518.9918584655633</v>
       </c>
       <c r="C19" t="n">
-        <v>516.5420602391357</v>
+        <v>523.0549187669818</v>
       </c>
       <c r="D19" t="n">
-        <v>510.9154330870712</v>
+        <v>515.566101626736</v>
       </c>
       <c r="E19" t="n">
-        <v>515.5162963867188</v>
+        <v>518.3843383789062</v>
       </c>
       <c r="F19" t="n">
-        <v>15586200</v>
+        <v>18962700</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B20" t="n">
-        <v>518.9919195722497</v>
+        <v>520.2964530626382</v>
       </c>
       <c r="C20" t="n">
-        <v>523.0549803520576</v>
+        <v>521.7802730707533</v>
       </c>
       <c r="D20" t="n">
-        <v>515.5661623300699</v>
+        <v>516.4623598997719</v>
       </c>
       <c r="E20" t="n">
-        <v>518.3843994140625</v>
+        <v>518.404296875</v>
       </c>
       <c r="F20" t="n">
-        <v>18962700</v>
+        <v>14023500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B21" t="n">
-        <v>520.2964530626382</v>
+        <v>520.6250388201142</v>
       </c>
       <c r="C21" t="n">
-        <v>521.7802730707533</v>
+        <v>523.1744351060786</v>
       </c>
       <c r="D21" t="n">
-        <v>516.4623598997719</v>
+        <v>518.5536961256696</v>
       </c>
       <c r="E21" t="n">
-        <v>518.404296875</v>
+        <v>521.441650390625</v>
       </c>
       <c r="F21" t="n">
-        <v>14023500</v>
+        <v>15532400</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B22" t="n">
-        <v>520.6250388201142</v>
+        <v>529.577902779321</v>
       </c>
       <c r="C22" t="n">
-        <v>523.1744351060786</v>
+        <v>532.3662956890146</v>
       </c>
       <c r="D22" t="n">
-        <v>518.5536961256696</v>
+        <v>526.819354031342</v>
       </c>
       <c r="E22" t="n">
-        <v>521.441650390625</v>
+        <v>529.3189697265625</v>
       </c>
       <c r="F22" t="n">
-        <v>15532400</v>
+        <v>18734700</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B23" t="n">
-        <v>529.577902779321</v>
+        <v>547.722348424072</v>
       </c>
       <c r="C23" t="n">
-        <v>532.3662956890146</v>
+        <v>551.4269140414981</v>
       </c>
       <c r="D23" t="n">
-        <v>526.819354031342</v>
+        <v>538.5305910090683</v>
       </c>
       <c r="E23" t="n">
-        <v>529.3189697265625</v>
+        <v>539.8251953125</v>
       </c>
       <c r="F23" t="n">
-        <v>18734700</v>
+        <v>29986700</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B24" t="n">
-        <v>547.7224103521172</v>
+        <v>542.6832878753321</v>
       </c>
       <c r="C24" t="n">
-        <v>551.4269763883988</v>
+        <v>544.0077970763692</v>
       </c>
       <c r="D24" t="n">
-        <v>538.5306518978505</v>
+        <v>534.5072653816836</v>
       </c>
       <c r="E24" t="n">
-        <v>539.8252563476562</v>
+        <v>539.3073120117188</v>
       </c>
       <c r="F24" t="n">
-        <v>29986700</v>
+        <v>36023000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B25" t="n">
-        <v>542.6833492925585</v>
+        <v>528.2831883129468</v>
       </c>
       <c r="C25" t="n">
-        <v>544.0078586434945</v>
+        <v>532.7545848667123</v>
       </c>
       <c r="D25" t="n">
-        <v>534.507325873603</v>
+        <v>519.9578228356851</v>
       </c>
       <c r="E25" t="n">
-        <v>539.307373046875</v>
+        <v>523.582763671875</v>
       </c>
       <c r="F25" t="n">
-        <v>36023000</v>
+        <v>41023100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B26" t="n">
-        <v>528.2831883129468</v>
+        <v>526.6898137654194</v>
       </c>
       <c r="C26" t="n">
-        <v>532.7545848667123</v>
+        <v>527.1279940743384</v>
       </c>
       <c r="D26" t="n">
-        <v>519.9578228356851</v>
+        <v>512.9668501497666</v>
       </c>
       <c r="E26" t="n">
-        <v>523.582763671875</v>
+        <v>515.6656494140625</v>
       </c>
       <c r="F26" t="n">
-        <v>41023100</v>
+        <v>34006400</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B27" t="n">
-        <v>526.6898137654194</v>
+        <v>517.657371934483</v>
       </c>
       <c r="C27" t="n">
-        <v>527.1279940743384</v>
+        <v>522.7860691817526</v>
       </c>
       <c r="D27" t="n">
-        <v>512.9668501497666</v>
+        <v>512.4590180581705</v>
       </c>
       <c r="E27" t="n">
-        <v>515.6656494140625</v>
+        <v>514.888916015625</v>
       </c>
       <c r="F27" t="n">
-        <v>34006400</v>
+        <v>22374700</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B28" t="n">
-        <v>517.657371934483</v>
+        <v>509.6407695643784</v>
       </c>
       <c r="C28" t="n">
-        <v>522.7860691817526</v>
+        <v>513.4150529816625</v>
       </c>
       <c r="D28" t="n">
-        <v>512.4590180581705</v>
+        <v>505.7369892339689</v>
       </c>
       <c r="E28" t="n">
-        <v>514.888916015625</v>
+        <v>512.2001342773438</v>
       </c>
       <c r="F28" t="n">
-        <v>22374700</v>
+        <v>20958700</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B29" t="n">
-        <v>509.6407695643784</v>
+        <v>511.1743415428253</v>
       </c>
       <c r="C29" t="n">
-        <v>513.4150529816625</v>
+        <v>512.6980347767452</v>
       </c>
       <c r="D29" t="n">
-        <v>505.7369892339689</v>
+        <v>504.4821687767013</v>
       </c>
       <c r="E29" t="n">
-        <v>512.2001342773438</v>
+        <v>505.0597839355469</v>
       </c>
       <c r="F29" t="n">
-        <v>20958700</v>
+        <v>23024300</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B30" t="n">
-        <v>511.1743415428253</v>
+        <v>503.5659922381216</v>
       </c>
       <c r="C30" t="n">
-        <v>512.6980347767452</v>
+        <v>503.6058351018555</v>
       </c>
       <c r="D30" t="n">
-        <v>504.4821687767013</v>
+        <v>493.7567764386794</v>
       </c>
       <c r="E30" t="n">
-        <v>505.0597839355469</v>
+        <v>495.0414428710938</v>
       </c>
       <c r="F30" t="n">
-        <v>23024300</v>
+        <v>27406500</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B31" t="n">
-        <v>503.5659922381216</v>
+        <v>494.8920702735404</v>
       </c>
       <c r="C31" t="n">
-        <v>503.6058351018555</v>
+        <v>497.3119999979126</v>
       </c>
       <c r="D31" t="n">
-        <v>493.7567764386794</v>
+        <v>491.2073803526309</v>
       </c>
       <c r="E31" t="n">
-        <v>495.0414428710938</v>
+        <v>494.7626037597656</v>
       </c>
       <c r="F31" t="n">
-        <v>27406500</v>
+        <v>24019800</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B32" t="n">
-        <v>494.8920702735404</v>
+        <v>497.9692915322098</v>
       </c>
       <c r="C32" t="n">
-        <v>497.3119999979126</v>
+        <v>504.7510881917551</v>
       </c>
       <c r="D32" t="n">
-        <v>491.2073803526309</v>
+        <v>496.734405833499</v>
       </c>
       <c r="E32" t="n">
-        <v>494.7626037597656</v>
+        <v>503.9046020507812</v>
       </c>
       <c r="F32" t="n">
-        <v>24019800</v>
+        <v>26101500</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B33" t="n">
-        <v>497.9692613740871</v>
+        <v>502.7095490222416</v>
       </c>
       <c r="C33" t="n">
-        <v>504.7510576229119</v>
+        <v>507.4896898672195</v>
       </c>
       <c r="D33" t="n">
-        <v>496.7343757501637</v>
+        <v>500.2697130079767</v>
       </c>
       <c r="E33" t="n">
-        <v>503.9045715332031</v>
+        <v>506.573486328125</v>
       </c>
       <c r="F33" t="n">
-        <v>26101500</v>
+        <v>17980000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B34" t="n">
-        <v>502.7095490222416</v>
+        <v>507.2506574723947</v>
       </c>
       <c r="C34" t="n">
-        <v>507.4896898672195</v>
+        <v>509.5511194130969</v>
       </c>
       <c r="D34" t="n">
-        <v>500.2697130079767</v>
+        <v>497.0530724082431</v>
       </c>
       <c r="E34" t="n">
-        <v>506.573486328125</v>
+        <v>509.0233154296875</v>
       </c>
       <c r="F34" t="n">
-        <v>17980000</v>
+        <v>26574900</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B35" t="n">
-        <v>507.2506574723947</v>
+        <v>508.1967287528611</v>
       </c>
       <c r="C35" t="n">
-        <v>509.5511194130969</v>
+        <v>511.3735209246628</v>
       </c>
       <c r="D35" t="n">
-        <v>497.0530724082431</v>
+        <v>499.2140928412288</v>
       </c>
       <c r="E35" t="n">
-        <v>509.0233154296875</v>
+        <v>501.205810546875</v>
       </c>
       <c r="F35" t="n">
-        <v>26574900</v>
+        <v>25273100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B36" t="n">
-        <v>508.1967287528611</v>
+        <v>496.1667955235038</v>
       </c>
       <c r="C36" t="n">
-        <v>511.3735209246628</v>
+        <v>509.4814242836766</v>
       </c>
       <c r="D36" t="n">
-        <v>499.2140928412288</v>
+        <v>495.3800584752997</v>
       </c>
       <c r="E36" t="n">
-        <v>501.205810546875</v>
+        <v>508.0672912597656</v>
       </c>
       <c r="F36" t="n">
-        <v>25273100</v>
+        <v>28505700</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B37" t="n">
-        <v>496.166765720741</v>
+        <v>506.3444741681719</v>
       </c>
       <c r="C37" t="n">
-        <v>509.4813936811572</v>
+        <v>509.9992593431845</v>
       </c>
       <c r="D37" t="n">
-        <v>495.3800287197931</v>
+        <v>502.8191251226507</v>
       </c>
       <c r="E37" t="n">
-        <v>508.0672607421875</v>
+        <v>505.388427734375</v>
       </c>
       <c r="F37" t="n">
-        <v>28505700</v>
+        <v>19092800</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B38" t="n">
-        <v>506.3444435928635</v>
+        <v>493.3186219236692</v>
       </c>
       <c r="C38" t="n">
-        <v>509.9992285471841</v>
+        <v>500.8971240097587</v>
       </c>
       <c r="D38" t="n">
-        <v>502.8190947602184</v>
+        <v>484.7641975590383</v>
       </c>
       <c r="E38" t="n">
-        <v>505.3883972167969</v>
+        <v>491.7451782226562</v>
       </c>
       <c r="F38" t="n">
-        <v>19092800</v>
+        <v>33815100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B39" t="n">
-        <v>493.3186219236692</v>
+        <v>488.070453670226</v>
       </c>
       <c r="C39" t="n">
-        <v>500.8971240097587</v>
+        <v>493.1393718315724</v>
       </c>
       <c r="D39" t="n">
-        <v>484.7641975590383</v>
+        <v>480.8305400064438</v>
       </c>
       <c r="E39" t="n">
-        <v>491.7451782226562</v>
+        <v>485.102783203125</v>
       </c>
       <c r="F39" t="n">
-        <v>33815100</v>
+        <v>23245300</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B40" t="n">
-        <v>488.0704229659532</v>
+        <v>491.5879641710541</v>
       </c>
       <c r="C40" t="n">
-        <v>493.1393408084164</v>
+        <v>492.4460215630244</v>
       </c>
       <c r="D40" t="n">
-        <v>480.8305097576304</v>
+        <v>474.4171642897319</v>
       </c>
       <c r="E40" t="n">
-        <v>485.1027526855469</v>
+        <v>477.3404846191406</v>
       </c>
       <c r="F40" t="n">
-        <v>23245300</v>
+        <v>26802500</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B41" t="n">
-        <v>491.5879641710541</v>
+        <v>477.4103368698009</v>
       </c>
       <c r="C41" t="n">
-        <v>492.4460215630244</v>
+        <v>477.8293938228302</v>
       </c>
       <c r="D41" t="n">
-        <v>474.4171642897319</v>
+        <v>467.2036221547232</v>
       </c>
       <c r="E41" t="n">
-        <v>477.3404846191406</v>
+        <v>471.0448608398438</v>
       </c>
       <c r="F41" t="n">
-        <v>26802500</v>
+        <v>31769200</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B42" t="n">
-        <v>477.4103368698009</v>
+        <v>473.9183160323131</v>
       </c>
       <c r="C42" t="n">
-        <v>477.8293938228302</v>
+        <v>475.8139832068258</v>
       </c>
       <c r="D42" t="n">
-        <v>467.2036221547232</v>
+        <v>466.9542001322548</v>
       </c>
       <c r="E42" t="n">
-        <v>471.0448608398438</v>
+        <v>472.9205932617188</v>
       </c>
       <c r="F42" t="n">
-        <v>31769200</v>
+        <v>34421000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B43" t="n">
-        <v>473.9183160323131</v>
+        <v>472.9904142849383</v>
       </c>
       <c r="C43" t="n">
-        <v>475.8139832068258</v>
+        <v>478.0588322743821</v>
       </c>
       <c r="D43" t="n">
-        <v>466.9542001322548</v>
+        <v>463.8313270788984</v>
       </c>
       <c r="E43" t="n">
-        <v>472.9205932617188</v>
+        <v>475.9037475585938</v>
       </c>
       <c r="F43" t="n">
-        <v>34421000</v>
+        <v>28019800</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B44" t="n">
-        <v>472.9904142849383</v>
+        <v>485.2025316262965</v>
       </c>
       <c r="C44" t="n">
-        <v>478.0588322743821</v>
+        <v>487.1979770584782</v>
       </c>
       <c r="D44" t="n">
-        <v>463.8313270788984</v>
+        <v>480.1041831621511</v>
       </c>
       <c r="E44" t="n">
-        <v>475.9037475585938</v>
+        <v>484.3943786621094</v>
       </c>
       <c r="F44" t="n">
-        <v>28019800</v>
+        <v>25709100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B45" t="n">
-        <v>485.2025316262965</v>
+        <v>486.489626354464</v>
       </c>
       <c r="C45" t="n">
-        <v>487.1979770584782</v>
+        <v>491.5081706450152</v>
       </c>
       <c r="D45" t="n">
-        <v>480.1041831621511</v>
+        <v>485.541777548382</v>
       </c>
       <c r="E45" t="n">
-        <v>484.3943786621094</v>
+        <v>490.8895874023438</v>
       </c>
       <c r="F45" t="n">
-        <v>25709100</v>
+        <v>14386700</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B46" t="n">
-        <v>486.489626354464</v>
+        <v>487.3277021324388</v>
       </c>
       <c r="C46" t="n">
-        <v>491.5081706450152</v>
+        <v>488.7444513856018</v>
       </c>
       <c r="D46" t="n">
-        <v>485.541777548382</v>
+        <v>483.5463243869077</v>
       </c>
       <c r="E46" t="n">
-        <v>490.8895874023438</v>
+        <v>485.6315612792969</v>
       </c>
       <c r="F46" t="n">
-        <v>14386700</v>
+        <v>23964000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B47" t="n">
-        <v>487.3277021324388</v>
+        <v>485.6116258193264</v>
       </c>
       <c r="C47" t="n">
-        <v>488.7444513856018</v>
+        <v>492.3761849539621</v>
       </c>
       <c r="D47" t="n">
-        <v>483.5463243869077</v>
+        <v>485.2125428025972</v>
       </c>
       <c r="E47" t="n">
-        <v>485.6315612792969</v>
+        <v>488.8841552734375</v>
       </c>
       <c r="F47" t="n">
-        <v>23964000</v>
+        <v>19562700</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B48" t="n">
-        <v>485.6116258193264</v>
+        <v>475.235297143397</v>
       </c>
       <c r="C48" t="n">
-        <v>492.3761849539621</v>
+        <v>483.1372440988117</v>
       </c>
       <c r="D48" t="n">
-        <v>485.2125428025972</v>
+        <v>474.1178525596479</v>
       </c>
       <c r="E48" t="n">
-        <v>488.8841552734375</v>
+        <v>476.64208984375</v>
       </c>
       <c r="F48" t="n">
-        <v>19562700</v>
+        <v>34615100</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B49" t="n">
-        <v>475.235297143397</v>
+        <v>478.6674679630734</v>
       </c>
       <c r="C49" t="n">
-        <v>483.1372440988117</v>
+        <v>480.2239129901724</v>
       </c>
       <c r="D49" t="n">
-        <v>474.1178525596479</v>
+        <v>475.4048951405118</v>
       </c>
       <c r="E49" t="n">
-        <v>476.64208984375</v>
+        <v>479.7449951171875</v>
       </c>
       <c r="F49" t="n">
-        <v>34615100</v>
+        <v>22318200</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B50" t="n">
-        <v>478.6674679630734</v>
+        <v>481.4211657314621</v>
       </c>
       <c r="C50" t="n">
-        <v>480.2239129901724</v>
+        <v>482.299166614698</v>
       </c>
       <c r="D50" t="n">
-        <v>475.4048951405118</v>
+        <v>477.7894707894466</v>
       </c>
       <c r="E50" t="n">
-        <v>479.7449951171875</v>
+        <v>482.0597229003906</v>
       </c>
       <c r="F50" t="n">
-        <v>22318200</v>
+        <v>22608700</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B51" t="n">
-        <v>481.4211657314621</v>
+        <v>483.7858099301447</v>
       </c>
       <c r="C51" t="n">
-        <v>482.299166614698</v>
+        <v>491.1789088824644</v>
       </c>
       <c r="D51" t="n">
-        <v>477.7894707894466</v>
+        <v>483.2769615726175</v>
       </c>
       <c r="E51" t="n">
-        <v>482.0597229003906</v>
+        <v>489.9018249511719</v>
       </c>
       <c r="F51" t="n">
-        <v>22608700</v>
+        <v>21965900</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B52" t="n">
-        <v>483.7858099301447</v>
+        <v>487.9862027558801</v>
       </c>
       <c r="C52" t="n">
-        <v>491.1789088824644</v>
+        <v>490.9993144973556</v>
       </c>
       <c r="D52" t="n">
-        <v>483.2769615726175</v>
+        <v>487.3875630167038</v>
       </c>
       <c r="E52" t="n">
-        <v>489.9018249511719</v>
+        <v>490.8995361328125</v>
       </c>
       <c r="F52" t="n">
-        <v>21965900</v>
+        <v>14696100</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B53" t="n">
-        <v>487.9862027558801</v>
+        <v>482.9277288439703</v>
       </c>
       <c r="C53" t="n">
-        <v>490.9993144973556</v>
+        <v>483.1472290611572</v>
       </c>
       <c r="D53" t="n">
-        <v>487.3875630167038</v>
+        <v>473.9980982856002</v>
       </c>
       <c r="E53" t="n">
-        <v>490.8995361328125</v>
+        <v>477.4701843261719</v>
       </c>
       <c r="F53" t="n">
-        <v>14696100</v>
+        <v>35756200</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B54" t="n">
-        <v>482.9277288439703</v>
+        <v>475.5445986070271</v>
       </c>
       <c r="C54" t="n">
-        <v>483.1472290611572</v>
+        <v>484.9231863556336</v>
       </c>
       <c r="D54" t="n">
-        <v>473.9980982856002</v>
+        <v>474.7763326037194</v>
       </c>
       <c r="E54" t="n">
-        <v>477.4701843261719</v>
+        <v>482.3690185546875</v>
       </c>
       <c r="F54" t="n">
-        <v>35756200</v>
+        <v>24669200</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B55" t="n">
-        <v>475.5445986070271</v>
+        <v>478.7273480015789</v>
       </c>
       <c r="C55" t="n">
-        <v>484.9231863556336</v>
+        <v>481.3513637649093</v>
       </c>
       <c r="D55" t="n">
-        <v>474.7763326037194</v>
+        <v>475.2552617920193</v>
       </c>
       <c r="E55" t="n">
-        <v>482.3690185546875</v>
+        <v>477.4402770996094</v>
       </c>
       <c r="F55" t="n">
-        <v>24669200</v>
+        <v>21248100</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B56" t="n">
-        <v>478.7273480015789</v>
+        <v>479.0066832317436</v>
       </c>
       <c r="C56" t="n">
-        <v>481.3513637649093</v>
+        <v>479.6252664455081</v>
       </c>
       <c r="D56" t="n">
-        <v>475.2552617920193</v>
+        <v>471.4439279747418</v>
       </c>
       <c r="E56" t="n">
-        <v>477.4402770996094</v>
+        <v>473.7387084960938</v>
       </c>
       <c r="F56" t="n">
-        <v>21248100</v>
+        <v>23727700</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B57" t="n">
-        <v>479.0066832317436</v>
+        <v>470.8353364785088</v>
       </c>
       <c r="C57" t="n">
-        <v>479.6252664455081</v>
+        <v>476.8017293564801</v>
       </c>
       <c r="D57" t="n">
-        <v>471.4439279747418</v>
+        <v>469.8076832860371</v>
       </c>
       <c r="E57" t="n">
-        <v>473.7387084960938</v>
+        <v>475.3051452636719</v>
       </c>
       <c r="F57" t="n">
-        <v>23727700</v>
+        <v>20705600</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B58" t="n">
-        <v>470.8353364785088</v>
+        <v>475.8239455574328</v>
       </c>
       <c r="C58" t="n">
-        <v>476.8017293564801</v>
+        <v>478.9069051052783</v>
       </c>
       <c r="D58" t="n">
-        <v>469.8076832860371</v>
+        <v>473.9182915104317</v>
       </c>
       <c r="E58" t="n">
-        <v>475.3051452636719</v>
+        <v>475.0357360839844</v>
       </c>
       <c r="F58" t="n">
-        <v>20705600</v>
+        <v>24527200</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B59" t="n">
-        <v>475.8239455574328</v>
+        <v>477.1010453906704</v>
       </c>
       <c r="C59" t="n">
-        <v>478.9069051052783</v>
+        <v>488.4850656489584</v>
       </c>
       <c r="D59" t="n">
-        <v>473.9182915104317</v>
+        <v>476.8017407441929</v>
       </c>
       <c r="E59" t="n">
-        <v>475.0357360839844</v>
+        <v>482.8778686523438</v>
       </c>
       <c r="F59" t="n">
-        <v>24527200</v>
+        <v>28573500</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B60" t="n">
-        <v>477.1010453906704</v>
+        <v>486.2501387748106</v>
       </c>
       <c r="C60" t="n">
-        <v>488.4850656489584</v>
+        <v>486.7390436209232</v>
       </c>
       <c r="D60" t="n">
-        <v>476.8017407441929</v>
+        <v>481.39123391446</v>
       </c>
       <c r="E60" t="n">
-        <v>482.8778686523438</v>
+        <v>484.8134460449219</v>
       </c>
       <c r="F60" t="n">
-        <v>28573500</v>
+        <v>70836100</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B61" t="n">
-        <v>486.2501387748106</v>
+        <v>485.0129839081317</v>
       </c>
       <c r="C61" t="n">
-        <v>486.7390436209232</v>
+        <v>487.6170561484318</v>
       </c>
       <c r="D61" t="n">
-        <v>481.39123391446</v>
+        <v>481.5908021440126</v>
       </c>
       <c r="E61" t="n">
-        <v>484.8134460449219</v>
+        <v>483.8157348632812</v>
       </c>
       <c r="F61" t="n">
-        <v>70836100</v>
+        <v>16963000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B62" t="n">
-        <v>485.0129839081317</v>
+        <v>483.8755963136496</v>
       </c>
       <c r="C62" t="n">
-        <v>487.6170561484318</v>
+        <v>486.7190818282799</v>
       </c>
       <c r="D62" t="n">
-        <v>481.5908021440126</v>
+        <v>483.6361221459561</v>
       </c>
       <c r="E62" t="n">
-        <v>483.8157348632812</v>
+        <v>485.7413330078125</v>
       </c>
       <c r="F62" t="n">
-        <v>16963000</v>
+        <v>14683600</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B63" t="n">
-        <v>483.8755963136496</v>
+        <v>484.5739628623746</v>
       </c>
       <c r="C63" t="n">
-        <v>486.7190818282799</v>
+        <v>488.0460488858467</v>
       </c>
       <c r="D63" t="n">
-        <v>483.6361221459561</v>
+        <v>483.7258924615979</v>
       </c>
       <c r="E63" t="n">
-        <v>485.7413330078125</v>
+        <v>486.9086303710938</v>
       </c>
       <c r="F63" t="n">
-        <v>14683600</v>
+        <v>5855900</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B64" t="n">
-        <v>484.5739628623746</v>
+        <v>485.601642461088</v>
       </c>
       <c r="C64" t="n">
-        <v>488.0460488858467</v>
+        <v>487.0084352251927</v>
       </c>
       <c r="D64" t="n">
-        <v>483.7258924615979</v>
+        <v>484.8533503811227</v>
       </c>
       <c r="E64" t="n">
-        <v>486.9086303710938</v>
+        <v>486.599365234375</v>
       </c>
       <c r="F64" t="n">
-        <v>5855900</v>
+        <v>8842200</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B65" t="n">
-        <v>485.601642461088</v>
+        <v>483.7558335295542</v>
       </c>
       <c r="C65" t="n">
-        <v>487.0084352251927</v>
+        <v>487.2379065999322</v>
       </c>
       <c r="D65" t="n">
-        <v>484.8533503811227</v>
+        <v>483.0773893732932</v>
       </c>
       <c r="E65" t="n">
-        <v>486.599365234375</v>
+        <v>485.9907531738281</v>
       </c>
       <c r="F65" t="n">
-        <v>8842200</v>
+        <v>10893400</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B66" t="n">
-        <v>483.7558335295542</v>
+        <v>484.8234150126488</v>
       </c>
       <c r="C66" t="n">
-        <v>487.2379065999322</v>
+        <v>488.5648753746365</v>
       </c>
       <c r="D66" t="n">
-        <v>483.0773893732932</v>
+        <v>484.3944015320139</v>
       </c>
       <c r="E66" t="n">
-        <v>485.9907531738281</v>
+        <v>486.3699035644531</v>
       </c>
       <c r="F66" t="n">
-        <v>10893400</v>
+        <v>13944500</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B67" t="n">
-        <v>484.8234150126488</v>
+        <v>486.7290680267604</v>
       </c>
       <c r="C67" t="n">
-        <v>488.5648753746365</v>
+        <v>487.0284031238816</v>
       </c>
       <c r="D67" t="n">
-        <v>484.3944015320139</v>
+        <v>482.1993981667827</v>
       </c>
       <c r="E67" t="n">
-        <v>486.3699035644531</v>
+        <v>482.5186767578125</v>
       </c>
       <c r="F67" t="n">
-        <v>13944500</v>
+        <v>15601600</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B68" t="n">
-        <v>486.7290680267604</v>
+        <v>483.2869444224563</v>
       </c>
       <c r="C68" t="n">
-        <v>487.0284031238816</v>
+        <v>483.5563186075122</v>
       </c>
       <c r="D68" t="n">
-        <v>482.1993981667827</v>
+        <v>469.0893385249197</v>
       </c>
       <c r="E68" t="n">
-        <v>482.5186767578125</v>
+        <v>471.8630065917969</v>
       </c>
       <c r="F68" t="n">
-        <v>15601600</v>
+        <v>25571600</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B69" t="n">
-        <v>483.2869444224563</v>
+        <v>472.9804293228547</v>
       </c>
       <c r="C69" t="n">
-        <v>483.5563186075122</v>
+        <v>474.9858617296903</v>
       </c>
       <c r="D69" t="n">
-        <v>469.0893385249197</v>
+        <v>468.4308161640092</v>
       </c>
       <c r="E69" t="n">
-        <v>471.8630065917969</v>
+        <v>471.773193359375</v>
       </c>
       <c r="F69" t="n">
-        <v>25571600</v>
+        <v>25250300</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B70" t="n">
-        <v>472.9804293228547</v>
+        <v>472.7210225701547</v>
       </c>
       <c r="C70" t="n">
-        <v>474.9858617296903</v>
+        <v>477.6497753472042</v>
       </c>
       <c r="D70" t="n">
-        <v>468.4308161640092</v>
+        <v>468.6802576477938</v>
       </c>
       <c r="E70" t="n">
-        <v>471.773193359375</v>
+        <v>477.4203186035156</v>
       </c>
       <c r="F70" t="n">
-        <v>25250300</v>
+        <v>23037700</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B71" t="n">
-        <v>472.7210225701547</v>
+        <v>478.6674756822987</v>
       </c>
       <c r="C71" t="n">
-        <v>477.6497753472042</v>
+        <v>488.5848422406915</v>
       </c>
       <c r="D71" t="n">
-        <v>468.6802576477938</v>
+        <v>476.861599942913</v>
       </c>
       <c r="E71" t="n">
-        <v>477.4203186035156</v>
+        <v>482.3690185546875</v>
       </c>
       <c r="F71" t="n">
-        <v>23037700</v>
+        <v>25564200</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B72" t="n">
-        <v>478.6674756822987</v>
+        <v>480.1440867981462</v>
       </c>
       <c r="C72" t="n">
-        <v>488.5848422406915</v>
+        <v>481.5608665012806</v>
       </c>
       <c r="D72" t="n">
-        <v>476.861599942913</v>
+        <v>474.7763335277468</v>
       </c>
       <c r="E72" t="n">
-        <v>482.3690185546875</v>
+        <v>477.0212097167969</v>
       </c>
       <c r="F72" t="n">
-        <v>25564200</v>
+        <v>18162600</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B73" t="n">
-        <v>480.1440867981462</v>
+        <v>472.9804540365218</v>
       </c>
       <c r="C73" t="n">
-        <v>481.5608665012806</v>
+        <v>478.7273469366413</v>
       </c>
       <c r="D73" t="n">
-        <v>474.7763335277468</v>
+        <v>471.1247042989064</v>
       </c>
       <c r="E73" t="n">
-        <v>477.0212097167969</v>
+        <v>478.1885681152344</v>
       </c>
       <c r="F73" t="n">
-        <v>18162600</v>
+        <v>18491000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B74" t="n">
-        <v>472.9804540365218</v>
+        <v>475.5845048686955</v>
       </c>
       <c r="C74" t="n">
-        <v>478.7273469366413</v>
+        <v>479.894643901475</v>
       </c>
       <c r="D74" t="n">
-        <v>471.1247042989064</v>
+        <v>474.5967386659474</v>
       </c>
       <c r="E74" t="n">
-        <v>478.1885681152344</v>
+        <v>476.0933227539062</v>
       </c>
       <c r="F74" t="n">
-        <v>18491000</v>
+        <v>23519900</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B75" t="n">
-        <v>475.5845048686955</v>
+        <v>473.5990225282599</v>
       </c>
       <c r="C75" t="n">
-        <v>479.894643901475</v>
+        <v>474.6965236309785</v>
       </c>
       <c r="D75" t="n">
-        <v>474.5967386659474</v>
+        <v>464.888922501957</v>
       </c>
       <c r="E75" t="n">
-        <v>476.0933227539062</v>
+        <v>469.5981750488281</v>
       </c>
       <c r="F75" t="n">
-        <v>23519900</v>
+        <v>28545800</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B76" t="n">
-        <v>473.5990225282599</v>
+        <v>465.3977566654985</v>
       </c>
       <c r="C76" t="n">
-        <v>474.6965236309785</v>
+        <v>467.1338149970701</v>
       </c>
       <c r="D76" t="n">
-        <v>464.888922501957</v>
+        <v>456.1289340170423</v>
       </c>
       <c r="E76" t="n">
-        <v>469.5981750488281</v>
+        <v>458.3338928222656</v>
       </c>
       <c r="F76" t="n">
-        <v>28545800</v>
+        <v>28184300</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B77" t="n">
-        <v>465.3977566654985</v>
+        <v>463.0630900555096</v>
       </c>
       <c r="C77" t="n">
-        <v>467.1338149970701</v>
+        <v>463.1927988881192</v>
       </c>
       <c r="D77" t="n">
-        <v>456.1289340170423</v>
+        <v>454.8618076165624</v>
       </c>
       <c r="E77" t="n">
-        <v>458.3338928222656</v>
+        <v>455.6200866699219</v>
       </c>
       <c r="F77" t="n">
-        <v>28184300</v>
+        <v>23225800</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B78" t="n">
-        <v>463.0630900555096</v>
+        <v>456.7873986695315</v>
       </c>
       <c r="C78" t="n">
-        <v>463.1927988881192</v>
+        <v>462.1352085061545</v>
       </c>
       <c r="D78" t="n">
-        <v>454.8618076165624</v>
+        <v>455.4404972994736</v>
       </c>
       <c r="E78" t="n">
-        <v>455.6200866699219</v>
+        <v>458.8127746582031</v>
       </c>
       <c r="F78" t="n">
-        <v>23225800</v>
+        <v>34246700</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B79" t="n">
-        <v>456.7873986695315</v>
+        <v>450.1924514863621</v>
       </c>
       <c r="C79" t="n">
-        <v>462.1352085061545</v>
+        <v>455.7597309230742</v>
       </c>
       <c r="D79" t="n">
-        <v>455.4404972994736</v>
+        <v>448.2568669541529</v>
       </c>
       <c r="E79" t="n">
-        <v>458.8127746582031</v>
+        <v>453.4849243164062</v>
       </c>
       <c r="F79" t="n">
-        <v>34246700</v>
+        <v>26130000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B80" t="n">
-        <v>450.1924514863621</v>
+        <v>451.5693196059127</v>
       </c>
       <c r="C80" t="n">
-        <v>455.7597309230742</v>
+        <v>451.6591109990197</v>
       </c>
       <c r="D80" t="n">
-        <v>448.2568669541529</v>
+        <v>437.6810056251358</v>
       </c>
       <c r="E80" t="n">
-        <v>453.4849243164062</v>
+        <v>443.0986328125</v>
       </c>
       <c r="F80" t="n">
-        <v>26130000</v>
+        <v>37980500</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B81" t="n">
-        <v>451.5693196059127</v>
+        <v>446.600636936346</v>
       </c>
       <c r="C81" t="n">
-        <v>451.6591109990197</v>
+        <v>451.8087507279656</v>
       </c>
       <c r="D81" t="n">
-        <v>437.6810056251358</v>
+        <v>443.6873036586902</v>
       </c>
       <c r="E81" t="n">
-        <v>443.0986328125</v>
+        <v>450.1126403808594</v>
       </c>
       <c r="F81" t="n">
-        <v>37980500</v>
+        <v>25349400</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B82" t="n">
-        <v>446.600636936346</v>
+        <v>450.8409629929935</v>
       </c>
       <c r="C82" t="n">
-        <v>451.8087507279656</v>
+        <v>470.0271819611143</v>
       </c>
       <c r="D82" t="n">
-        <v>443.6873036586902</v>
+        <v>449.5040181949105</v>
       </c>
       <c r="E82" t="n">
-        <v>450.1126403808594</v>
+        <v>464.888916015625</v>
       </c>
       <c r="F82" t="n">
-        <v>25349400</v>
+        <v>38000200</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B83" t="n">
-        <v>450.8409629929935</v>
+        <v>464.2503622118351</v>
       </c>
       <c r="C83" t="n">
-        <v>470.0271819611143</v>
+        <v>473.1700058760031</v>
       </c>
       <c r="D83" t="n">
-        <v>449.5040181949105</v>
+        <v>460.9479024031912</v>
       </c>
       <c r="E83" t="n">
-        <v>464.888916015625</v>
+        <v>469.2090454101562</v>
       </c>
       <c r="F83" t="n">
-        <v>38000200</v>
+        <v>29291200</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B84" t="n">
-        <v>464.2503622118351</v>
+        <v>472.62128861771</v>
       </c>
       <c r="C84" t="n">
-        <v>473.1700058760031</v>
+        <v>481.7703893732875</v>
       </c>
       <c r="D84" t="n">
-        <v>460.9479024031912</v>
+        <v>472.0825097961169</v>
       </c>
       <c r="E84" t="n">
-        <v>469.2090454101562</v>
+        <v>479.485595703125</v>
       </c>
       <c r="F84" t="n">
-        <v>29291200</v>
+        <v>29213900</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B85" t="n">
-        <v>472.62128861771</v>
+        <v>482.1095916405993</v>
       </c>
       <c r="C85" t="n">
-        <v>481.7703893732875</v>
+        <v>482.6383834693597</v>
       </c>
       <c r="D85" t="n">
-        <v>472.0825097961169</v>
+        <v>476.9114647448887</v>
       </c>
       <c r="E85" t="n">
-        <v>479.485595703125</v>
+        <v>480.533203125</v>
       </c>
       <c r="F85" t="n">
-        <v>29213900</v>
+        <v>36875400</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B86" t="n">
-        <v>482.1095916405993</v>
+        <v>438.9880283656418</v>
       </c>
       <c r="C86" t="n">
-        <v>482.6383834693597</v>
+        <v>441.4923222419712</v>
       </c>
       <c r="D86" t="n">
-        <v>476.9114647448887</v>
+        <v>420.0612263501361</v>
       </c>
       <c r="E86" t="n">
-        <v>480.533203125</v>
+        <v>432.5128173828125</v>
       </c>
       <c r="F86" t="n">
-        <v>36875400</v>
+        <v>128855300</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B87" t="n">
-        <v>438.9880283656418</v>
+        <v>438.1699022937122</v>
       </c>
       <c r="C87" t="n">
-        <v>441.4923222419712</v>
+        <v>438.5989157576861</v>
       </c>
       <c r="D87" t="n">
-        <v>420.0612263501361</v>
+        <v>425.4788680207893</v>
       </c>
       <c r="E87" t="n">
-        <v>432.5128173828125</v>
+        <v>429.3101196289062</v>
       </c>
       <c r="F87" t="n">
-        <v>128855300</v>
+        <v>58566800</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B88" t="n">
-        <v>438.1699022937122</v>
+        <v>429.2602343395754</v>
       </c>
       <c r="C88" t="n">
-        <v>438.5989157576861</v>
+        <v>429.7590957240154</v>
       </c>
       <c r="D88" t="n">
-        <v>425.4788680207893</v>
+        <v>421.28843915961</v>
       </c>
       <c r="E88" t="n">
-        <v>429.3101196289062</v>
+        <v>422.4058837890625</v>
       </c>
       <c r="F88" t="n">
-        <v>58566800</v>
+        <v>42219900</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B89" t="n">
-        <v>429.2602343395754</v>
+        <v>421.0489834358989</v>
       </c>
       <c r="C89" t="n">
-        <v>429.7590957240154</v>
+        <v>421.0888704228976</v>
       </c>
       <c r="D89" t="n">
-        <v>421.28843915961</v>
+        <v>407.6296003977664</v>
       </c>
       <c r="E89" t="n">
-        <v>422.4058837890625</v>
+        <v>410.2735595703125</v>
       </c>
       <c r="F89" t="n">
-        <v>42219900</v>
+        <v>61424100</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B90" t="n">
-        <v>421.0489834358989</v>
+        <v>410.0640575889883</v>
       </c>
       <c r="C90" t="n">
-        <v>421.0888704228976</v>
+        <v>418.8440057668918</v>
       </c>
       <c r="D90" t="n">
-        <v>407.6296003977664</v>
+        <v>408.3080557741746</v>
       </c>
       <c r="E90" t="n">
-        <v>410.2735595703125</v>
+        <v>413.2467956542969</v>
       </c>
       <c r="F90" t="n">
-        <v>61424100</v>
+        <v>45012400</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B91" t="n">
-        <v>410.0640575889883</v>
+        <v>406.5121603821183</v>
       </c>
       <c r="C91" t="n">
-        <v>418.8440057668918</v>
+        <v>407.3701873334875</v>
       </c>
       <c r="D91" t="n">
-        <v>408.3080557741746</v>
+        <v>391.4265972483441</v>
       </c>
       <c r="E91" t="n">
-        <v>413.2467956542969</v>
+        <v>392.7735290527344</v>
       </c>
       <c r="F91" t="n">
-        <v>45012400</v>
+        <v>66289200</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B92" t="n">
-        <v>406.5121603821183</v>
+        <v>398.2609865133262</v>
       </c>
       <c r="C92" t="n">
-        <v>407.3701873334875</v>
+        <v>400.875015135043</v>
       </c>
       <c r="D92" t="n">
-        <v>391.4265972483441</v>
+        <v>392.0252195920243</v>
       </c>
       <c r="E92" t="n">
-        <v>392.7735290527344</v>
+        <v>400.2265014648438</v>
       </c>
       <c r="F92" t="n">
-        <v>66289200</v>
+        <v>53515300</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B93" t="n">
-        <v>398.2609865133262</v>
+        <v>403.9280678877113</v>
       </c>
       <c r="C93" t="n">
-        <v>400.875015135043</v>
+        <v>413.9452129833927</v>
       </c>
       <c r="D93" t="n">
-        <v>392.0252195920243</v>
+        <v>399.9571203178888</v>
       </c>
       <c r="E93" t="n">
-        <v>400.2265014648438</v>
+        <v>412.6581420898438</v>
       </c>
       <c r="F93" t="n">
-        <v>53515300</v>
+        <v>45480500</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B94" t="n">
-        <v>403.9280678877113</v>
+        <v>418.6644027817824</v>
       </c>
       <c r="C94" t="n">
-        <v>413.9452129833927</v>
+        <v>422.7151545880433</v>
       </c>
       <c r="D94" t="n">
-        <v>399.9571203178888</v>
+        <v>411.76017861217</v>
       </c>
       <c r="E94" t="n">
-        <v>412.6581420898438</v>
+        <v>412.328857421875</v>
       </c>
       <c r="F94" t="n">
-        <v>45480500</v>
+        <v>44857900</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B95" t="n">
-        <v>418.6644027817824</v>
+        <v>415.2322299614449</v>
       </c>
       <c r="C95" t="n">
-        <v>422.7151545880433</v>
+        <v>415.5115911022014</v>
       </c>
       <c r="D95" t="n">
-        <v>411.76017861217</v>
+        <v>400.096793508188</v>
       </c>
       <c r="E95" t="n">
-        <v>412.328857421875</v>
+        <v>403.4491271972656</v>
       </c>
       <c r="F95" t="n">
-        <v>44857900</v>
+        <v>42491000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B96" t="n">
-        <v>415.2322299614449</v>
+        <v>404.0777037056333</v>
       </c>
       <c r="C96" t="n">
-        <v>415.5115911022014</v>
+        <v>405.2749831551046</v>
       </c>
       <c r="D96" t="n">
-        <v>400.096793508188</v>
+        <v>397.1036315998776</v>
       </c>
       <c r="E96" t="n">
-        <v>403.4491271972656</v>
+        <v>400.9248962402344</v>
       </c>
       <c r="F96" t="n">
-        <v>42491000</v>
+        <v>40802400</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B97" t="n">
-        <v>404.0777037056333</v>
+        <v>403.528974460687</v>
       </c>
       <c r="C97" t="n">
-        <v>405.2749831551046</v>
+        <v>404.6164885937555</v>
       </c>
       <c r="D97" t="n">
-        <v>397.1036315998776</v>
+        <v>397.1435245648219</v>
       </c>
       <c r="E97" t="n">
-        <v>400.9248962402344</v>
+        <v>400.4060974121094</v>
       </c>
       <c r="F97" t="n">
-        <v>40802400</v>
+        <v>34091600</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B98" t="n">
-        <v>403.528974460687</v>
+        <v>398.3108793269315</v>
       </c>
       <c r="C98" t="n">
-        <v>404.6164885937555</v>
+        <v>399.6079067287359</v>
       </c>
       <c r="D98" t="n">
-        <v>397.1435245648219</v>
+        <v>393.6315571718042</v>
       </c>
       <c r="E98" t="n">
-        <v>400.4060974121094</v>
+        <v>395.9562377929688</v>
       </c>
       <c r="F98" t="n">
-        <v>34091600</v>
+        <v>32078800</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B99" t="n">
-        <v>398.3108793269315</v>
+        <v>397.2233488345012</v>
       </c>
       <c r="C99" t="n">
-        <v>399.6079067287359</v>
+        <v>401.6432531481791</v>
       </c>
       <c r="D99" t="n">
-        <v>393.6315571718042</v>
+        <v>395.4174731587443</v>
       </c>
       <c r="E99" t="n">
-        <v>395.9562377929688</v>
+        <v>398.6900024414062</v>
       </c>
       <c r="F99" t="n">
-        <v>32078800</v>
+        <v>23223400</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B100" t="n">
-        <v>397.2233488345012</v>
+        <v>400.6900024414062</v>
       </c>
       <c r="C100" t="n">
-        <v>401.6432531481791</v>
+        <v>404.4299926757812</v>
       </c>
       <c r="D100" t="n">
-        <v>395.4174731587443</v>
+        <v>396.6700134277344</v>
       </c>
       <c r="E100" t="n">
-        <v>398.6900024414062</v>
+        <v>398.4599914550781</v>
       </c>
       <c r="F100" t="n">
-        <v>23223400</v>
+        <v>28234000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B101" t="n">
-        <v>400.6900024414062</v>
+        <v>396.1099853515625</v>
       </c>
       <c r="C101" t="n">
-        <v>404.4299926757812</v>
+        <v>400.1199951171875</v>
       </c>
       <c r="D101" t="n">
-        <v>396.6700134277344</v>
+        <v>395.1600036621094</v>
       </c>
       <c r="E101" t="n">
-        <v>398.4599914550781</v>
+        <v>397.2300109863281</v>
       </c>
       <c r="F101" t="n">
-        <v>28234000</v>
+        <v>34015200</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B102" t="n">
-        <v>396.1099853515625</v>
+        <v>395</v>
       </c>
       <c r="C102" t="n">
-        <v>400.1199951171875</v>
+        <v>395.3599853515625</v>
       </c>
       <c r="D102" t="n">
-        <v>395.1600036621094</v>
+        <v>383.1000061035156</v>
       </c>
       <c r="E102" t="n">
-        <v>397.2300109863281</v>
+        <v>384.4700012207031</v>
       </c>
       <c r="F102" t="n">
-        <v>34015200</v>
+        <v>43238300</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B103" t="n">
-        <v>395</v>
+        <v>384.1400146484375</v>
       </c>
       <c r="C103" t="n">
-        <v>395.3599853515625</v>
+        <v>389.3599853515625</v>
       </c>
       <c r="D103" t="n">
-        <v>383.1000061035156</v>
+        <v>381.7099914550781</v>
       </c>
       <c r="E103" t="n">
-        <v>384.4700012207031</v>
+        <v>389</v>
       </c>
       <c r="F103" t="n">
-        <v>43238300</v>
+        <v>33884700</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B104" t="n">
-        <v>384.1400146484375</v>
+        <v>390.5299987792969</v>
       </c>
       <c r="C104" t="n">
-        <v>389.3599853515625</v>
+        <v>401.4700012207031</v>
       </c>
       <c r="D104" t="n">
-        <v>381.7099914550781</v>
+        <v>390.1600036621094</v>
       </c>
       <c r="E104" t="n">
-        <v>389</v>
+        <v>400.6000061035156</v>
       </c>
       <c r="F104" t="n">
-        <v>33884700</v>
+        <v>43625500</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B105" t="n">
-        <v>390.5299987792969</v>
+        <v>404.7099914550781</v>
       </c>
       <c r="C105" t="n">
-        <v>401.4700012207031</v>
+        <v>407.489990234375</v>
       </c>
       <c r="D105" t="n">
-        <v>390.1600036621094</v>
+        <v>398.739990234375</v>
       </c>
       <c r="E105" t="n">
-        <v>400.6000061035156</v>
+        <v>401.7200012207031</v>
       </c>
       <c r="F105" t="n">
-        <v>43625500</v>
+        <v>34405900</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B106" t="n">
-        <v>404.7099914550781</v>
+        <v>390.8800048828125</v>
       </c>
       <c r="C106" t="n">
-        <v>407.489990234375</v>
+        <v>396.8200073242188</v>
       </c>
       <c r="D106" t="n">
-        <v>398.739990234375</v>
+        <v>389.8800048828125</v>
       </c>
       <c r="E106" t="n">
-        <v>401.7200012207031</v>
+        <v>392.739990234375</v>
       </c>
       <c r="F106" t="n">
-        <v>34405900</v>
+        <v>51367200</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B107" t="n">
-        <v>390.8800048828125</v>
+        <v>392.8599853515625</v>
       </c>
       <c r="C107" t="n">
-        <v>396.8200073242188</v>
+        <v>401.1900024414062</v>
       </c>
       <c r="D107" t="n">
-        <v>389.8800048828125</v>
+        <v>390.6300048828125</v>
       </c>
       <c r="E107" t="n">
-        <v>392.739990234375</v>
+        <v>398.5499877929688</v>
       </c>
       <c r="F107" t="n">
-        <v>51367200</v>
+        <v>35474900</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B108" t="n">
-        <v>392.8599853515625</v>
+        <v>393.1400146484375</v>
       </c>
       <c r="C108" t="n">
-        <v>401.1900024414062</v>
+        <v>406.7000122070312</v>
       </c>
       <c r="D108" t="n">
-        <v>390.6300048828125</v>
+        <v>392.6700134277344</v>
       </c>
       <c r="E108" t="n">
-        <v>398.5499877929688</v>
+        <v>403.9299926757812</v>
       </c>
       <c r="F108" t="n">
-        <v>35474900</v>
+        <v>38199200</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B109" t="n">
-        <v>393.1400146484375</v>
+        <v>401.2699890136719</v>
       </c>
       <c r="C109" t="n">
-        <v>406.7000122070312</v>
+        <v>411.0299987792969</v>
       </c>
       <c r="D109" t="n">
-        <v>392.6700134277344</v>
+        <v>400.3099975585938</v>
       </c>
       <c r="E109" t="n">
-        <v>403.9299926757812</v>
+        <v>405.2000122070312</v>
       </c>
       <c r="F109" t="n">
-        <v>38199200</v>
+        <v>35808000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B110" t="n">
-        <v>401.2699890136719</v>
+        <v>404.4200134277344</v>
       </c>
       <c r="C110" t="n">
-        <v>411.0299987792969</v>
+        <v>411.6099853515625</v>
       </c>
       <c r="D110" t="n">
-        <v>400.3099975585938</v>
+        <v>404.3999938964844</v>
       </c>
       <c r="E110" t="n">
-        <v>405.2000122070312</v>
+        <v>410.6799926757812</v>
       </c>
       <c r="F110" t="n">
-        <v>35808000</v>
+        <v>39001300</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B111" t="n">
-        <v>404.4200134277344</v>
+        <v>409.2000122070312</v>
       </c>
       <c r="C111" t="n">
-        <v>411.6099853515625</v>
+        <v>413.0499877929688</v>
       </c>
       <c r="D111" t="n">
-        <v>404.3999938964844</v>
+        <v>408.510009765625</v>
       </c>
       <c r="E111" t="n">
-        <v>410.6799926757812</v>
+        <v>408.9599914550781</v>
       </c>
       <c r="F111" t="n">
-        <v>39001300</v>
+        <v>31123900</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B112" t="n">
-        <v>409.2000122070312</v>
+        <v>404.9200134277344</v>
       </c>
       <c r="C112" t="n">
-        <v>413.0499877929688</v>
+        <v>410.2099914550781</v>
       </c>
       <c r="D112" t="n">
-        <v>408.510009765625</v>
+        <v>403.5</v>
       </c>
       <c r="E112" t="n">
-        <v>408.9599914550781</v>
+        <v>409.4100036621094</v>
       </c>
       <c r="F112" t="n">
-        <v>31123900</v>
+        <v>30131900</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B113" t="n">
-        <v>404.9200134277344</v>
+        <v>410.0299987792969</v>
       </c>
       <c r="C113" t="n">
-        <v>410.2099914550781</v>
+        <v>410.2000122070312</v>
       </c>
       <c r="D113" t="n">
-        <v>403.5</v>
+        <v>402.9299926757812</v>
       </c>
       <c r="E113" t="n">
-        <v>409.4100036621094</v>
+        <v>405.760009765625</v>
       </c>
       <c r="F113" t="n">
-        <v>30131900</v>
+        <v>31706400</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B114" t="n">
-        <v>410.0299987792969</v>
+        <v>405.5700073242188</v>
       </c>
       <c r="C114" t="n">
-        <v>410.2000122070312</v>
+        <v>409.010009765625</v>
       </c>
       <c r="D114" t="n">
-        <v>402.9299926757812</v>
+        <v>401.5899963378906</v>
       </c>
       <c r="E114" t="n">
-        <v>405.760009765625</v>
+        <v>404.8800048828125</v>
       </c>
       <c r="F114" t="n">
-        <v>31706400</v>
+        <v>25512100</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B115" t="n">
-        <v>405.5700073242188</v>
+        <v>404.6300048828125</v>
       </c>
       <c r="C115" t="n">
-        <v>409.010009765625</v>
+        <v>406.1199951171875</v>
       </c>
       <c r="D115" t="n">
-        <v>401.5899963378906</v>
+        <v>401.7099914550781</v>
       </c>
       <c r="E115" t="n">
-        <v>404.8800048828125</v>
+        <v>401.8599853515625</v>
       </c>
       <c r="F115" t="n">
-        <v>25512100</v>
+        <v>27263900</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B116" t="n">
-        <v>404.6300048828125</v>
+        <v>401</v>
       </c>
       <c r="C116" t="n">
-        <v>406.1199951171875</v>
+        <v>404.7999877929688</v>
       </c>
       <c r="D116" t="n">
-        <v>401.7099914550781</v>
+        <v>394.25</v>
       </c>
       <c r="E116" t="n">
-        <v>401.8599853515625</v>
+        <v>395.5499877929688</v>
       </c>
       <c r="F116" t="n">
-        <v>27263900</v>
+        <v>26848000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B117" t="n">
-        <v>401</v>
+        <v>398.0700073242188</v>
       </c>
       <c r="C117" t="n">
-        <v>404.7999877929688</v>
+        <v>400.6300048828125</v>
       </c>
       <c r="D117" t="n">
-        <v>394.25</v>
+        <v>394.7900085449219</v>
       </c>
       <c r="E117" t="n">
-        <v>395.5499877929688</v>
+        <v>399.9500122070312</v>
       </c>
       <c r="F117" t="n">
-        <v>26848000</v>
+        <v>27733700</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B118" t="n">
-        <v>398.0700073242188</v>
+        <v>400.2699890136719</v>
       </c>
       <c r="C118" t="n">
-        <v>400.6300048828125</v>
+        <v>404.3999938964844</v>
       </c>
       <c r="D118" t="n">
-        <v>394.7900085449219</v>
+        <v>397.75</v>
       </c>
       <c r="E118" t="n">
-        <v>399.9500122070312</v>
+        <v>399.4100036621094</v>
       </c>
       <c r="F118" t="n">
-        <v>27733700</v>
+        <v>26228300</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B119" t="n">
-        <v>400.2699890136719</v>
+        <v>397.1300048828125</v>
       </c>
       <c r="C119" t="n">
-        <v>404.3999938964844</v>
+        <v>398</v>
       </c>
       <c r="D119" t="n">
-        <v>397.75</v>
+        <v>391</v>
       </c>
       <c r="E119" t="n">
-        <v>399.4100036621094</v>
+        <v>391.7900085449219</v>
       </c>
       <c r="F119" t="n">
-        <v>26228300</v>
+        <v>25908500</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B120" t="n">
-        <v>397.1300048828125</v>
+        <v>390.1000061035156</v>
       </c>
       <c r="C120" t="n">
-        <v>398</v>
+        <v>392.489990234375</v>
       </c>
       <c r="D120" t="n">
-        <v>391</v>
+        <v>387.0599975585938</v>
       </c>
       <c r="E120" t="n">
-        <v>391.7900085449219</v>
+        <v>389.0199890136719</v>
       </c>
       <c r="F120" t="n">
-        <v>25908500</v>
+        <v>25138800</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B121" t="n">
-        <v>390.1000061035156</v>
+        <v>386.7900085449219</v>
       </c>
       <c r="C121" t="n">
-        <v>392.489990234375</v>
+        <v>387</v>
       </c>
       <c r="D121" t="n">
-        <v>387.0599975585938</v>
+        <v>380.1199951171875</v>
       </c>
       <c r="E121" t="n">
-        <v>389.0199890136719</v>
+        <v>381.8699951171875</v>
       </c>
       <c r="F121" t="n">
-        <v>25138800</v>
+        <v>50853200</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B122" t="n">
-        <v>386.7900085449219</v>
+        <v>383.8999938964844</v>
       </c>
       <c r="C122" t="n">
-        <v>387</v>
+        <v>387.2099914550781</v>
       </c>
       <c r="D122" t="n">
-        <v>380.1199951171875</v>
+        <v>381.6799926757812</v>
       </c>
       <c r="E122" t="n">
-        <v>381.8699951171875</v>
+        <v>383</v>
       </c>
       <c r="F122" t="n">
-        <v>50853200</v>
+        <v>29680100</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B123" t="n">
-        <v>383.8999938964844</v>
+        <v>382.3599853515625</v>
       </c>
       <c r="C123" t="n">
-        <v>387.2099914550781</v>
+        <v>382.4700012207031</v>
       </c>
       <c r="D123" t="n">
-        <v>381.6799926757812</v>
+        <v>371.8500061035156</v>
       </c>
       <c r="E123" t="n">
-        <v>383</v>
+        <v>372.739990234375</v>
       </c>
       <c r="F123" t="n">
-        <v>29680100</v>
+        <v>42733600</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B124" t="n">
-        <v>382.3599853515625</v>
+        <v>376.9200134277344</v>
       </c>
       <c r="C124" t="n">
-        <v>382.4700012207031</v>
+        <v>377.0599975585938</v>
       </c>
       <c r="D124" t="n">
-        <v>371.8500061035156</v>
+        <v>369.6300048828125</v>
       </c>
       <c r="E124" t="n">
-        <v>372.739990234375</v>
+        <v>371.0400085449219</v>
       </c>
       <c r="F124" t="n">
-        <v>42636600</v>
+        <v>31181200</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B125" t="n">
+        <v>370.8200073242188</v>
+      </c>
+      <c r="C125" t="n">
+        <v>374.7200012207031</v>
+      </c>
+      <c r="D125" t="n">
+        <v>365.1900024414062</v>
+      </c>
+      <c r="E125" t="n">
+        <v>365.9700012207031</v>
+      </c>
+      <c r="F125" t="n">
+        <v>36719800</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data.xlsx
+++ b/stock_data.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPY" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSFT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMZN" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,16 +514,16 @@
         <v>45931</v>
       </c>
       <c r="B4" t="n">
-        <v>659.4152702620313</v>
+        <v>659.4153308150761</v>
       </c>
       <c r="C4" t="n">
-        <v>665.5801794564833</v>
+        <v>665.5802405756418</v>
       </c>
       <c r="D4" t="n">
-        <v>659.3059076216911</v>
+        <v>659.3059681646932</v>
       </c>
       <c r="E4" t="n">
-        <v>664.6654052734375</v>
+        <v>664.6654663085938</v>
       </c>
       <c r="F4" t="n">
         <v>72545400</v>
@@ -713,16 +714,16 @@
         <v>45945</v>
       </c>
       <c r="B14" t="n">
-        <v>663.0446129876665</v>
+        <v>663.0446741742268</v>
       </c>
       <c r="C14" t="n">
-        <v>666.4352795829697</v>
+        <v>666.4353410824248</v>
       </c>
       <c r="D14" t="n">
-        <v>655.1992699391986</v>
+        <v>655.1993304017814</v>
       </c>
       <c r="E14" t="n">
-        <v>661.4039306640625</v>
+        <v>661.4039916992188</v>
       </c>
       <c r="F14" t="n">
         <v>81702600</v>
@@ -733,16 +734,16 @@
         <v>45946</v>
       </c>
       <c r="B15" t="n">
-        <v>663.0445999065358</v>
+        <v>663.0446615126489</v>
       </c>
       <c r="C15" t="n">
-        <v>664.9239136533134</v>
+        <v>664.9239754340409</v>
       </c>
       <c r="D15" t="n">
-        <v>653.3895542222015</v>
+        <v>653.3896149312258</v>
       </c>
       <c r="E15" t="n">
-        <v>656.8995971679688</v>
+        <v>656.899658203125</v>
       </c>
       <c r="F15" t="n">
         <v>110563300</v>
@@ -793,16 +794,16 @@
         <v>45951</v>
       </c>
       <c r="B18" t="n">
-        <v>667.638493864759</v>
+        <v>667.6384328159621</v>
       </c>
       <c r="C18" t="n">
-        <v>669.1797060532549</v>
+        <v>669.1796448635298</v>
       </c>
       <c r="D18" t="n">
-        <v>666.1867381348511</v>
+        <v>666.1866772188026</v>
       </c>
       <c r="E18" t="n">
-        <v>667.4893188476562</v>
+        <v>667.4892578125</v>
       </c>
       <c r="F18" t="n">
         <v>56249000</v>
@@ -913,16 +914,16 @@
         <v>45959</v>
       </c>
       <c r="B24" t="n">
-        <v>684.8206562449755</v>
+        <v>684.8205950917289</v>
       </c>
       <c r="C24" t="n">
-        <v>685.795149064121</v>
+        <v>685.795087823854</v>
       </c>
       <c r="D24" t="n">
-        <v>679.0038013689816</v>
+        <v>679.0037407351697</v>
       </c>
       <c r="E24" t="n">
-        <v>683.4982299804688</v>
+        <v>683.4981689453125</v>
       </c>
       <c r="F24" t="n">
         <v>85657100</v>
@@ -933,16 +934,16 @@
         <v>45960</v>
       </c>
       <c r="B25" t="n">
-        <v>680.0279821977349</v>
+        <v>680.0279207971732</v>
       </c>
       <c r="C25" t="n">
-        <v>682.0564104652303</v>
+        <v>682.0563488815194</v>
       </c>
       <c r="D25" t="n">
-        <v>675.9810180664062</v>
+        <v>675.98095703125</v>
       </c>
       <c r="E25" t="n">
-        <v>675.9810180664062</v>
+        <v>675.98095703125</v>
       </c>
       <c r="F25" t="n">
         <v>76335800</v>
@@ -953,16 +954,16 @@
         <v>45961</v>
       </c>
       <c r="B26" t="n">
-        <v>681.1614116072222</v>
+        <v>681.1614729090464</v>
       </c>
       <c r="C26" t="n">
-        <v>681.2012239761448</v>
+        <v>681.2012852815519</v>
       </c>
       <c r="D26" t="n">
-        <v>675.3942622450203</v>
+        <v>675.3943230278239</v>
       </c>
       <c r="E26" t="n">
-        <v>678.1983032226562</v>
+        <v>678.1983642578125</v>
       </c>
       <c r="F26" t="n">
         <v>87164100</v>
@@ -1073,16 +1074,16 @@
         <v>45971</v>
       </c>
       <c r="B32" t="n">
-        <v>673.4056154266486</v>
+        <v>673.4056760856186</v>
       </c>
       <c r="C32" t="n">
-        <v>678.3176487268574</v>
+        <v>678.317709828293</v>
       </c>
       <c r="D32" t="n">
-        <v>671.2081667723378</v>
+        <v>671.2082272333661</v>
       </c>
       <c r="E32" t="n">
-        <v>677.5818481445312</v>
+        <v>677.5819091796875</v>
       </c>
       <c r="F32" t="n">
         <v>75842900</v>
@@ -1113,16 +1114,16 @@
         <v>45973</v>
       </c>
       <c r="B34" t="n">
-        <v>680.9129156193362</v>
+        <v>680.9128544582501</v>
       </c>
       <c r="C34" t="n">
-        <v>681.0819968300743</v>
+        <v>681.081935653801</v>
       </c>
       <c r="D34" t="n">
-        <v>677.0946904605516</v>
+        <v>677.0946296424269</v>
       </c>
       <c r="E34" t="n">
-        <v>679.5109252929688</v>
+        <v>679.5108642578125</v>
       </c>
       <c r="F34" t="n">
         <v>62312500</v>
@@ -1133,16 +1134,16 @@
         <v>45974</v>
       </c>
       <c r="B35" t="n">
-        <v>676.6472315164618</v>
+        <v>676.6471697129602</v>
       </c>
       <c r="C35" t="n">
-        <v>677.0051787486752</v>
+        <v>677.0051169124795</v>
       </c>
       <c r="D35" t="n">
-        <v>666.7237544337754</v>
+        <v>666.7236935366629</v>
       </c>
       <c r="E35" t="n">
-        <v>668.235107421875</v>
+        <v>668.2350463867188</v>
       </c>
       <c r="F35" t="n">
         <v>103457800</v>
@@ -1153,16 +1154,16 @@
         <v>45975</v>
       </c>
       <c r="B36" t="n">
-        <v>661.612768198211</v>
+        <v>661.6128286383953</v>
       </c>
       <c r="C36" t="n">
-        <v>671.8345335183507</v>
+        <v>671.8345948923219</v>
       </c>
       <c r="D36" t="n">
-        <v>659.5147291242073</v>
+        <v>659.5147893727298</v>
       </c>
       <c r="E36" t="n">
-        <v>668.1256713867188</v>
+        <v>668.125732421875</v>
       </c>
       <c r="F36" t="n">
         <v>96846700</v>
@@ -1193,16 +1194,16 @@
         <v>45979</v>
       </c>
       <c r="B38" t="n">
-        <v>658.3512953245886</v>
+        <v>658.351356546523</v>
       </c>
       <c r="C38" t="n">
-        <v>661.354216097308</v>
+        <v>661.3542775984923</v>
       </c>
       <c r="D38" t="n">
-        <v>652.146634691611</v>
+        <v>652.1466953365565</v>
       </c>
       <c r="E38" t="n">
-        <v>656.3427734375</v>
+        <v>656.3428344726562</v>
       </c>
       <c r="F38" t="n">
         <v>114467500</v>
@@ -1213,16 +1214,16 @@
         <v>45980</v>
       </c>
       <c r="B39" t="n">
-        <v>657.0388554539629</v>
+        <v>657.0389163187169</v>
       </c>
       <c r="C39" t="n">
-        <v>663.5617119214406</v>
+        <v>663.561773390439</v>
       </c>
       <c r="D39" t="n">
-        <v>655.0203196831769</v>
+        <v>655.020380360944</v>
       </c>
       <c r="E39" t="n">
-        <v>658.8783569335938</v>
+        <v>658.87841796875</v>
       </c>
       <c r="F39" t="n">
         <v>94703000</v>
@@ -1293,16 +1294,16 @@
         <v>45986</v>
       </c>
       <c r="B43" t="n">
-        <v>664.8444060411854</v>
+        <v>664.8443455838128</v>
       </c>
       <c r="C43" t="n">
-        <v>672.3815071629971</v>
+        <v>672.3814460202411</v>
       </c>
       <c r="D43" t="n">
-        <v>660.717877921785</v>
+        <v>660.7178178396566</v>
       </c>
       <c r="E43" t="n">
-        <v>671.1982421875</v>
+        <v>671.1981811523438</v>
       </c>
       <c r="F43" t="n">
         <v>81077100</v>
@@ -1353,16 +1354,16 @@
         <v>45992</v>
       </c>
       <c r="B46" t="n">
-        <v>674.9667014318244</v>
+        <v>674.9667623359846</v>
       </c>
       <c r="C46" t="n">
-        <v>679.1230277654502</v>
+        <v>679.1230890446475</v>
       </c>
       <c r="D46" t="n">
-        <v>674.8970904760725</v>
+        <v>674.8971513739515</v>
       </c>
       <c r="E46" t="n">
-        <v>676.41845703125</v>
+        <v>676.4185180664062</v>
       </c>
       <c r="F46" t="n">
         <v>61201200</v>
@@ -1473,16 +1474,16 @@
         <v>46000</v>
       </c>
       <c r="B52" t="n">
-        <v>679.2822138612034</v>
+        <v>679.2821528162136</v>
       </c>
       <c r="C52" t="n">
-        <v>681.5095218770947</v>
+        <v>681.5094606319436</v>
       </c>
       <c r="D52" t="n">
-        <v>678.7253868572307</v>
+        <v>678.7253258622812</v>
       </c>
       <c r="E52" t="n">
-        <v>679.1727905273438</v>
+        <v>679.1727294921875</v>
       </c>
       <c r="F52" t="n">
         <v>58310100</v>
@@ -1533,16 +1534,16 @@
         <v>46003</v>
       </c>
       <c r="B55" t="n">
-        <v>684.2737672143002</v>
+        <v>684.2737056052856</v>
       </c>
       <c r="C55" t="n">
-        <v>684.9797692517327</v>
+        <v>684.9797075791527</v>
       </c>
       <c r="D55" t="n">
-        <v>675.3247225627367</v>
+        <v>675.3246617594549</v>
       </c>
       <c r="E55" t="n">
-        <v>677.9000854492188</v>
+        <v>677.9000244140625</v>
       </c>
       <c r="F55" t="n">
         <v>113160300</v>
@@ -2946,6 +2947,26 @@
       </c>
       <c r="F125" t="n">
         <v>96353600</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B126" t="n">
+        <v>642.5</v>
+      </c>
+      <c r="C126" t="n">
+        <v>642.6599731445312</v>
+      </c>
+      <c r="D126" t="n">
+        <v>638.3400268554688</v>
+      </c>
+      <c r="E126" t="n">
+        <v>639.47998046875</v>
+      </c>
+      <c r="F126" t="n">
+        <v>38597554</v>
       </c>
     </row>
   </sheetData>
@@ -2959,7 +2980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5472,6 +5493,26 @@
       </c>
       <c r="F125" t="n">
         <v>41702500</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B126" t="n">
+        <v>253.9100036621094</v>
+      </c>
+      <c r="C126" t="n">
+        <v>255.4929962158203</v>
+      </c>
+      <c r="D126" t="n">
+        <v>251.8000030517578</v>
+      </c>
+      <c r="E126" t="n">
+        <v>252.3600006103516</v>
+      </c>
+      <c r="F126" t="n">
+        <v>17773290</v>
       </c>
     </row>
   </sheetData>
@@ -5485,7 +5526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8000,6 +8041,2572 @@
         <v>36719800</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B126" t="n">
+        <v>362.0400085449219</v>
+      </c>
+      <c r="C126" t="n">
+        <v>362.4249877929688</v>
+      </c>
+      <c r="D126" t="n">
+        <v>356.5799865722656</v>
+      </c>
+      <c r="E126" t="n">
+        <v>360.2449951171875</v>
+      </c>
+      <c r="F126" t="n">
+        <v>16973651</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F126"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B2" t="n">
+        <v>220.0800018310547</v>
+      </c>
+      <c r="C2" t="n">
+        <v>222.6000061035156</v>
+      </c>
+      <c r="D2" t="n">
+        <v>219.3000030517578</v>
+      </c>
+      <c r="E2" t="n">
+        <v>222.1699981689453</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44259200</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B3" t="n">
+        <v>222.0299987792969</v>
+      </c>
+      <c r="C3" t="n">
+        <v>222.2400054931641</v>
+      </c>
+      <c r="D3" t="n">
+        <v>217.8899993896484</v>
+      </c>
+      <c r="E3" t="n">
+        <v>219.5700073242188</v>
+      </c>
+      <c r="F3" t="n">
+        <v>48396400</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B4" t="n">
+        <v>217.3600006103516</v>
+      </c>
+      <c r="C4" t="n">
+        <v>222.1499938964844</v>
+      </c>
+      <c r="D4" t="n">
+        <v>216.6100006103516</v>
+      </c>
+      <c r="E4" t="n">
+        <v>220.6300048828125</v>
+      </c>
+      <c r="F4" t="n">
+        <v>43933800</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B5" t="n">
+        <v>221.0099945068359</v>
+      </c>
+      <c r="C5" t="n">
+        <v>222.8099975585938</v>
+      </c>
+      <c r="D5" t="n">
+        <v>218.9499969482422</v>
+      </c>
+      <c r="E5" t="n">
+        <v>222.4100036621094</v>
+      </c>
+      <c r="F5" t="n">
+        <v>41258600</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B6" t="n">
+        <v>223.4400024414062</v>
+      </c>
+      <c r="C6" t="n">
+        <v>224.1999969482422</v>
+      </c>
+      <c r="D6" t="n">
+        <v>219.3399963378906</v>
+      </c>
+      <c r="E6" t="n">
+        <v>219.5099945068359</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43639000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B7" t="n">
+        <v>221</v>
+      </c>
+      <c r="C7" t="n">
+        <v>221.7299957275391</v>
+      </c>
+      <c r="D7" t="n">
+        <v>216.0299987792969</v>
+      </c>
+      <c r="E7" t="n">
+        <v>220.8999938964844</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43690900</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B8" t="n">
+        <v>220.8800048828125</v>
+      </c>
+      <c r="C8" t="n">
+        <v>222.8899993896484</v>
+      </c>
+      <c r="D8" t="n">
+        <v>220.1699981689453</v>
+      </c>
+      <c r="E8" t="n">
+        <v>221.7799987792969</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31194700</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B9" t="n">
+        <v>222.9199981689453</v>
+      </c>
+      <c r="C9" t="n">
+        <v>226.7299957275391</v>
+      </c>
+      <c r="D9" t="n">
+        <v>221.1900024414062</v>
+      </c>
+      <c r="E9" t="n">
+        <v>225.2200012207031</v>
+      </c>
+      <c r="F9" t="n">
+        <v>46686000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B10" t="n">
+        <v>225</v>
+      </c>
+      <c r="C10" t="n">
+        <v>228.2100067138672</v>
+      </c>
+      <c r="D10" t="n">
+        <v>221.75</v>
+      </c>
+      <c r="E10" t="n">
+        <v>227.7400054931641</v>
+      </c>
+      <c r="F10" t="n">
+        <v>46412100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B11" t="n">
+        <v>226.2100067138672</v>
+      </c>
+      <c r="C11" t="n">
+        <v>228.25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>216</v>
+      </c>
+      <c r="E11" t="n">
+        <v>216.3699951171875</v>
+      </c>
+      <c r="F11" t="n">
+        <v>72367500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B12" t="n">
+        <v>217.6999969482422</v>
+      </c>
+      <c r="C12" t="n">
+        <v>220.6799926757812</v>
+      </c>
+      <c r="D12" t="n">
+        <v>217.0399932861328</v>
+      </c>
+      <c r="E12" t="n">
+        <v>220.0700073242188</v>
+      </c>
+      <c r="F12" t="n">
+        <v>37809700</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B13" t="n">
+        <v>215.5599975585938</v>
+      </c>
+      <c r="C13" t="n">
+        <v>219.3200073242188</v>
+      </c>
+      <c r="D13" t="n">
+        <v>212.6000061035156</v>
+      </c>
+      <c r="E13" t="n">
+        <v>216.3899993896484</v>
+      </c>
+      <c r="F13" t="n">
+        <v>45665600</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B14" t="n">
+        <v>216.6199951171875</v>
+      </c>
+      <c r="C14" t="n">
+        <v>217.7100067138672</v>
+      </c>
+      <c r="D14" t="n">
+        <v>212.6600036621094</v>
+      </c>
+      <c r="E14" t="n">
+        <v>215.5700073242188</v>
+      </c>
+      <c r="F14" t="n">
+        <v>45909500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B15" t="n">
+        <v>215.6699981689453</v>
+      </c>
+      <c r="C15" t="n">
+        <v>218.5899963378906</v>
+      </c>
+      <c r="D15" t="n">
+        <v>212.8099975585938</v>
+      </c>
+      <c r="E15" t="n">
+        <v>214.4700012207031</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42414600</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B16" t="n">
+        <v>214.5599975585938</v>
+      </c>
+      <c r="C16" t="n">
+        <v>214.8000030517578</v>
+      </c>
+      <c r="D16" t="n">
+        <v>211.0299987792969</v>
+      </c>
+      <c r="E16" t="n">
+        <v>213.0399932861328</v>
+      </c>
+      <c r="F16" t="n">
+        <v>45986900</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B17" t="n">
+        <v>213.8800048828125</v>
+      </c>
+      <c r="C17" t="n">
+        <v>216.6900024414062</v>
+      </c>
+      <c r="D17" t="n">
+        <v>213.5899963378906</v>
+      </c>
+      <c r="E17" t="n">
+        <v>216.4799957275391</v>
+      </c>
+      <c r="F17" t="n">
+        <v>38882800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B18" t="n">
+        <v>218.4299926757812</v>
+      </c>
+      <c r="C18" t="n">
+        <v>223.3200073242188</v>
+      </c>
+      <c r="D18" t="n">
+        <v>217.9900054931641</v>
+      </c>
+      <c r="E18" t="n">
+        <v>222.0299987792969</v>
+      </c>
+      <c r="F18" t="n">
+        <v>50494600</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B19" t="n">
+        <v>219.3000030517578</v>
+      </c>
+      <c r="C19" t="n">
+        <v>220.0099945068359</v>
+      </c>
+      <c r="D19" t="n">
+        <v>216.5200042724609</v>
+      </c>
+      <c r="E19" t="n">
+        <v>217.9499969482422</v>
+      </c>
+      <c r="F19" t="n">
+        <v>44308500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B20" t="n">
+        <v>219</v>
+      </c>
+      <c r="C20" t="n">
+        <v>221.3000030517578</v>
+      </c>
+      <c r="D20" t="n">
+        <v>218.1799926757812</v>
+      </c>
+      <c r="E20" t="n">
+        <v>221.0899963378906</v>
+      </c>
+      <c r="F20" t="n">
+        <v>31540000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B21" t="n">
+        <v>221.9700012207031</v>
+      </c>
+      <c r="C21" t="n">
+        <v>225.3999938964844</v>
+      </c>
+      <c r="D21" t="n">
+        <v>221.8999938964844</v>
+      </c>
+      <c r="E21" t="n">
+        <v>224.2100067138672</v>
+      </c>
+      <c r="F21" t="n">
+        <v>38685100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B22" t="n">
+        <v>227.6600036621094</v>
+      </c>
+      <c r="C22" t="n">
+        <v>228.3999938964844</v>
+      </c>
+      <c r="D22" t="n">
+        <v>225.5399932861328</v>
+      </c>
+      <c r="E22" t="n">
+        <v>226.9700012207031</v>
+      </c>
+      <c r="F22" t="n">
+        <v>38267000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B23" t="n">
+        <v>228.2200012207031</v>
+      </c>
+      <c r="C23" t="n">
+        <v>231.4900054931641</v>
+      </c>
+      <c r="D23" t="n">
+        <v>226.2100067138672</v>
+      </c>
+      <c r="E23" t="n">
+        <v>229.25</v>
+      </c>
+      <c r="F23" t="n">
+        <v>47100000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B24" t="n">
+        <v>231.6699981689453</v>
+      </c>
+      <c r="C24" t="n">
+        <v>232.8200073242188</v>
+      </c>
+      <c r="D24" t="n">
+        <v>227.7599945068359</v>
+      </c>
+      <c r="E24" t="n">
+        <v>230.3000030517578</v>
+      </c>
+      <c r="F24" t="n">
+        <v>52036200</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B25" t="n">
+        <v>227.0599975585938</v>
+      </c>
+      <c r="C25" t="n">
+        <v>228.4400024414062</v>
+      </c>
+      <c r="D25" t="n">
+        <v>222.75</v>
+      </c>
+      <c r="E25" t="n">
+        <v>222.8600006103516</v>
+      </c>
+      <c r="F25" t="n">
+        <v>102252900</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B26" t="n">
+        <v>250.1000061035156</v>
+      </c>
+      <c r="C26" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>243.9799957275391</v>
+      </c>
+      <c r="E26" t="n">
+        <v>244.2200012207031</v>
+      </c>
+      <c r="F26" t="n">
+        <v>166340800</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B27" t="n">
+        <v>255.3600006103516</v>
+      </c>
+      <c r="C27" t="n">
+        <v>258.6000061035156</v>
+      </c>
+      <c r="D27" t="n">
+        <v>252.8999938964844</v>
+      </c>
+      <c r="E27" t="n">
+        <v>254</v>
+      </c>
+      <c r="F27" t="n">
+        <v>95997800</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B28" t="n">
+        <v>250.3800048828125</v>
+      </c>
+      <c r="C28" t="n">
+        <v>257.010009765625</v>
+      </c>
+      <c r="D28" t="n">
+        <v>248.6600036621094</v>
+      </c>
+      <c r="E28" t="n">
+        <v>249.3200073242188</v>
+      </c>
+      <c r="F28" t="n">
+        <v>51546300</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B29" t="n">
+        <v>249.0299987792969</v>
+      </c>
+      <c r="C29" t="n">
+        <v>251</v>
+      </c>
+      <c r="D29" t="n">
+        <v>246.1600036621094</v>
+      </c>
+      <c r="E29" t="n">
+        <v>250.1999969482422</v>
+      </c>
+      <c r="F29" t="n">
+        <v>40610700</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B30" t="n">
+        <v>249.1600036621094</v>
+      </c>
+      <c r="C30" t="n">
+        <v>250.3800048828125</v>
+      </c>
+      <c r="D30" t="n">
+        <v>242.1699981689453</v>
+      </c>
+      <c r="E30" t="n">
+        <v>243.0399932861328</v>
+      </c>
+      <c r="F30" t="n">
+        <v>46004200</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B31" t="n">
+        <v>242.8999938964844</v>
+      </c>
+      <c r="C31" t="n">
+        <v>244.8999938964844</v>
+      </c>
+      <c r="D31" t="n">
+        <v>238.4900054931641</v>
+      </c>
+      <c r="E31" t="n">
+        <v>244.4100036621094</v>
+      </c>
+      <c r="F31" t="n">
+        <v>46374300</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B32" t="n">
+        <v>248.3399963378906</v>
+      </c>
+      <c r="C32" t="n">
+        <v>251.75</v>
+      </c>
+      <c r="D32" t="n">
+        <v>245.5899963378906</v>
+      </c>
+      <c r="E32" t="n">
+        <v>248.3999938964844</v>
+      </c>
+      <c r="F32" t="n">
+        <v>36476500</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B33" t="n">
+        <v>248.4100036621094</v>
+      </c>
+      <c r="C33" t="n">
+        <v>249.75</v>
+      </c>
+      <c r="D33" t="n">
+        <v>247.2299957275391</v>
+      </c>
+      <c r="E33" t="n">
+        <v>249.1000061035156</v>
+      </c>
+      <c r="F33" t="n">
+        <v>23564100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B34" t="n">
+        <v>250.2400054931641</v>
+      </c>
+      <c r="C34" t="n">
+        <v>250.3699951171875</v>
+      </c>
+      <c r="D34" t="n">
+        <v>243.75</v>
+      </c>
+      <c r="E34" t="n">
+        <v>244.1999969482422</v>
+      </c>
+      <c r="F34" t="n">
+        <v>31190100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B35" t="n">
+        <v>243.0500030517578</v>
+      </c>
+      <c r="C35" t="n">
+        <v>243.75</v>
+      </c>
+      <c r="D35" t="n">
+        <v>236.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>237.5800018310547</v>
+      </c>
+      <c r="F35" t="n">
+        <v>41401700</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B36" t="n">
+        <v>235.0599975585938</v>
+      </c>
+      <c r="C36" t="n">
+        <v>238.7299957275391</v>
+      </c>
+      <c r="D36" t="n">
+        <v>232.8899993896484</v>
+      </c>
+      <c r="E36" t="n">
+        <v>234.6900024414062</v>
+      </c>
+      <c r="F36" t="n">
+        <v>38956700</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B37" t="n">
+        <v>233.25</v>
+      </c>
+      <c r="C37" t="n">
+        <v>234.6000061035156</v>
+      </c>
+      <c r="D37" t="n">
+        <v>229.1900024414062</v>
+      </c>
+      <c r="E37" t="n">
+        <v>232.8699951171875</v>
+      </c>
+      <c r="F37" t="n">
+        <v>59919000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B38" t="n">
+        <v>228.1000061035156</v>
+      </c>
+      <c r="C38" t="n">
+        <v>230.1999969482422</v>
+      </c>
+      <c r="D38" t="n">
+        <v>222.4199981689453</v>
+      </c>
+      <c r="E38" t="n">
+        <v>222.5500030517578</v>
+      </c>
+      <c r="F38" t="n">
+        <v>60608400</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B39" t="n">
+        <v>223.7400054931641</v>
+      </c>
+      <c r="C39" t="n">
+        <v>223.7400054931641</v>
+      </c>
+      <c r="D39" t="n">
+        <v>218.5200042724609</v>
+      </c>
+      <c r="E39" t="n">
+        <v>222.6900024414062</v>
+      </c>
+      <c r="F39" t="n">
+        <v>58335600</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B40" t="n">
+        <v>227.0500030517578</v>
+      </c>
+      <c r="C40" t="n">
+        <v>227.4100036621094</v>
+      </c>
+      <c r="D40" t="n">
+        <v>216.7400054931641</v>
+      </c>
+      <c r="E40" t="n">
+        <v>217.1399993896484</v>
+      </c>
+      <c r="F40" t="n">
+        <v>50309000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B41" t="n">
+        <v>216.3500061035156</v>
+      </c>
+      <c r="C41" t="n">
+        <v>222.2100067138672</v>
+      </c>
+      <c r="D41" t="n">
+        <v>215.1799926757812</v>
+      </c>
+      <c r="E41" t="n">
+        <v>220.6900024414062</v>
+      </c>
+      <c r="F41" t="n">
+        <v>68490500</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B42" t="n">
+        <v>222.5599975585938</v>
+      </c>
+      <c r="C42" t="n">
+        <v>227.3300018310547</v>
+      </c>
+      <c r="D42" t="n">
+        <v>222.2700042724609</v>
+      </c>
+      <c r="E42" t="n">
+        <v>226.2799987792969</v>
+      </c>
+      <c r="F42" t="n">
+        <v>54318400</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B43" t="n">
+        <v>226.3800048828125</v>
+      </c>
+      <c r="C43" t="n">
+        <v>230.5200042724609</v>
+      </c>
+      <c r="D43" t="n">
+        <v>223.8000030517578</v>
+      </c>
+      <c r="E43" t="n">
+        <v>229.6699981689453</v>
+      </c>
+      <c r="F43" t="n">
+        <v>39379300</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B44" t="n">
+        <v>230.7400054931641</v>
+      </c>
+      <c r="C44" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="D44" t="n">
+        <v>228.7700042724609</v>
+      </c>
+      <c r="E44" t="n">
+        <v>229.1600036621094</v>
+      </c>
+      <c r="F44" t="n">
+        <v>38497900</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B45" t="n">
+        <v>231.2400054931641</v>
+      </c>
+      <c r="C45" t="n">
+        <v>233.2899932861328</v>
+      </c>
+      <c r="D45" t="n">
+        <v>230.2200012207031</v>
+      </c>
+      <c r="E45" t="n">
+        <v>233.2200012207031</v>
+      </c>
+      <c r="F45" t="n">
+        <v>20292300</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B46" t="n">
+        <v>233.2200012207031</v>
+      </c>
+      <c r="C46" t="n">
+        <v>235.8000030517578</v>
+      </c>
+      <c r="D46" t="n">
+        <v>232.25</v>
+      </c>
+      <c r="E46" t="n">
+        <v>233.8800048828125</v>
+      </c>
+      <c r="F46" t="n">
+        <v>42904000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B47" t="n">
+        <v>235.0099945068359</v>
+      </c>
+      <c r="C47" t="n">
+        <v>238.9700012207031</v>
+      </c>
+      <c r="D47" t="n">
+        <v>233.5500030517578</v>
+      </c>
+      <c r="E47" t="n">
+        <v>234.4199981689453</v>
+      </c>
+      <c r="F47" t="n">
+        <v>45785400</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B48" t="n">
+        <v>233.3500061035156</v>
+      </c>
+      <c r="C48" t="n">
+        <v>233.3800048828125</v>
+      </c>
+      <c r="D48" t="n">
+        <v>230.6100006103516</v>
+      </c>
+      <c r="E48" t="n">
+        <v>232.3800048828125</v>
+      </c>
+      <c r="F48" t="n">
+        <v>35495100</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B49" t="n">
+        <v>232.7700042724609</v>
+      </c>
+      <c r="C49" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="D49" t="n">
+        <v>226.8000030517578</v>
+      </c>
+      <c r="E49" t="n">
+        <v>229.1100006103516</v>
+      </c>
+      <c r="F49" t="n">
+        <v>45683200</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B50" t="n">
+        <v>230.3200073242188</v>
+      </c>
+      <c r="C50" t="n">
+        <v>231.2400054931641</v>
+      </c>
+      <c r="D50" t="n">
+        <v>228.5500030517578</v>
+      </c>
+      <c r="E50" t="n">
+        <v>229.5299987792969</v>
+      </c>
+      <c r="F50" t="n">
+        <v>33117400</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B51" t="n">
+        <v>229.5899963378906</v>
+      </c>
+      <c r="C51" t="n">
+        <v>230.8300018310547</v>
+      </c>
+      <c r="D51" t="n">
+        <v>226.2700042724609</v>
+      </c>
+      <c r="E51" t="n">
+        <v>226.8899993896484</v>
+      </c>
+      <c r="F51" t="n">
+        <v>35019200</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B52" t="n">
+        <v>226.8399963378906</v>
+      </c>
+      <c r="C52" t="n">
+        <v>228.5700073242188</v>
+      </c>
+      <c r="D52" t="n">
+        <v>225.1100006103516</v>
+      </c>
+      <c r="E52" t="n">
+        <v>227.9199981689453</v>
+      </c>
+      <c r="F52" t="n">
+        <v>25841700</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B53" t="n">
+        <v>228.8099975585938</v>
+      </c>
+      <c r="C53" t="n">
+        <v>232.4199981689453</v>
+      </c>
+      <c r="D53" t="n">
+        <v>228.4600067138672</v>
+      </c>
+      <c r="E53" t="n">
+        <v>231.7799987792969</v>
+      </c>
+      <c r="F53" t="n">
+        <v>38790700</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B54" t="n">
+        <v>230.7100067138672</v>
+      </c>
+      <c r="C54" t="n">
+        <v>232.1100006103516</v>
+      </c>
+      <c r="D54" t="n">
+        <v>228.6900024414062</v>
+      </c>
+      <c r="E54" t="n">
+        <v>230.2799987792969</v>
+      </c>
+      <c r="F54" t="n">
+        <v>28249600</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B55" t="n">
+        <v>229.8699951171875</v>
+      </c>
+      <c r="C55" t="n">
+        <v>230.0800018310547</v>
+      </c>
+      <c r="D55" t="n">
+        <v>225.1199951171875</v>
+      </c>
+      <c r="E55" t="n">
+        <v>226.1900024414062</v>
+      </c>
+      <c r="F55" t="n">
+        <v>35639100</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B56" t="n">
+        <v>227.9299926757812</v>
+      </c>
+      <c r="C56" t="n">
+        <v>227.9299926757812</v>
+      </c>
+      <c r="D56" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>222.5399932861328</v>
+      </c>
+      <c r="F56" t="n">
+        <v>47286100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B57" t="n">
+        <v>223.0399932861328</v>
+      </c>
+      <c r="C57" t="n">
+        <v>223.6600036621094</v>
+      </c>
+      <c r="D57" t="n">
+        <v>221.1300048828125</v>
+      </c>
+      <c r="E57" t="n">
+        <v>222.5599975585938</v>
+      </c>
+      <c r="F57" t="n">
+        <v>39298900</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B58" t="n">
+        <v>224.6600036621094</v>
+      </c>
+      <c r="C58" t="n">
+        <v>225.1900024414062</v>
+      </c>
+      <c r="D58" t="n">
+        <v>220.9900054931641</v>
+      </c>
+      <c r="E58" t="n">
+        <v>221.2700042724609</v>
+      </c>
+      <c r="F58" t="n">
+        <v>44034400</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B59" t="n">
+        <v>225.7100067138672</v>
+      </c>
+      <c r="C59" t="n">
+        <v>229.2299957275391</v>
+      </c>
+      <c r="D59" t="n">
+        <v>224.4100036621094</v>
+      </c>
+      <c r="E59" t="n">
+        <v>226.7599945068359</v>
+      </c>
+      <c r="F59" t="n">
+        <v>50272400</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B60" t="n">
+        <v>226.7599945068359</v>
+      </c>
+      <c r="C60" t="n">
+        <v>229.1300048828125</v>
+      </c>
+      <c r="D60" t="n">
+        <v>225.5800018310547</v>
+      </c>
+      <c r="E60" t="n">
+        <v>227.3500061035156</v>
+      </c>
+      <c r="F60" t="n">
+        <v>85544400</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B61" t="n">
+        <v>228.6100006103516</v>
+      </c>
+      <c r="C61" t="n">
+        <v>229.4799957275391</v>
+      </c>
+      <c r="D61" t="n">
+        <v>226.7100067138672</v>
+      </c>
+      <c r="E61" t="n">
+        <v>228.4299926757812</v>
+      </c>
+      <c r="F61" t="n">
+        <v>32261300</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B62" t="n">
+        <v>229.0599975585938</v>
+      </c>
+      <c r="C62" t="n">
+        <v>232.4499969482422</v>
+      </c>
+      <c r="D62" t="n">
+        <v>228.7299957275391</v>
+      </c>
+      <c r="E62" t="n">
+        <v>232.1399993896484</v>
+      </c>
+      <c r="F62" t="n">
+        <v>29230200</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B63" t="n">
+        <v>232.1300048828125</v>
+      </c>
+      <c r="C63" t="n">
+        <v>232.9499969482422</v>
+      </c>
+      <c r="D63" t="n">
+        <v>231.3300018310547</v>
+      </c>
+      <c r="E63" t="n">
+        <v>232.3800048828125</v>
+      </c>
+      <c r="F63" t="n">
+        <v>11420500</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B64" t="n">
+        <v>232.0399932861328</v>
+      </c>
+      <c r="C64" t="n">
+        <v>232.9900054931641</v>
+      </c>
+      <c r="D64" t="n">
+        <v>231.1799926757812</v>
+      </c>
+      <c r="E64" t="n">
+        <v>232.5200042724609</v>
+      </c>
+      <c r="F64" t="n">
+        <v>15994700</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B65" t="n">
+        <v>231.9400024414062</v>
+      </c>
+      <c r="C65" t="n">
+        <v>232.6000061035156</v>
+      </c>
+      <c r="D65" t="n">
+        <v>230.7700042724609</v>
+      </c>
+      <c r="E65" t="n">
+        <v>232.0700073242188</v>
+      </c>
+      <c r="F65" t="n">
+        <v>19797900</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B66" t="n">
+        <v>231.2100067138672</v>
+      </c>
+      <c r="C66" t="n">
+        <v>232.7700042724609</v>
+      </c>
+      <c r="D66" t="n">
+        <v>230.1999969482422</v>
+      </c>
+      <c r="E66" t="n">
+        <v>232.5299987792969</v>
+      </c>
+      <c r="F66" t="n">
+        <v>21910500</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B67" t="n">
+        <v>232.9100036621094</v>
+      </c>
+      <c r="C67" t="n">
+        <v>232.9900054931641</v>
+      </c>
+      <c r="D67" t="n">
+        <v>230.1199951171875</v>
+      </c>
+      <c r="E67" t="n">
+        <v>230.8200073242188</v>
+      </c>
+      <c r="F67" t="n">
+        <v>24383700</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B68" t="n">
+        <v>231.3399963378906</v>
+      </c>
+      <c r="C68" t="n">
+        <v>235.4600067138672</v>
+      </c>
+      <c r="D68" t="n">
+        <v>224.6999969482422</v>
+      </c>
+      <c r="E68" t="n">
+        <v>226.5</v>
+      </c>
+      <c r="F68" t="n">
+        <v>51456200</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B69" t="n">
+        <v>228.8399963378906</v>
+      </c>
+      <c r="C69" t="n">
+        <v>234</v>
+      </c>
+      <c r="D69" t="n">
+        <v>227.1799926757812</v>
+      </c>
+      <c r="E69" t="n">
+        <v>233.0599975585938</v>
+      </c>
+      <c r="F69" t="n">
+        <v>49733300</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B70" t="n">
+        <v>232.1000061035156</v>
+      </c>
+      <c r="C70" t="n">
+        <v>243.1799926757812</v>
+      </c>
+      <c r="D70" t="n">
+        <v>232.0700073242188</v>
+      </c>
+      <c r="E70" t="n">
+        <v>240.9299926757812</v>
+      </c>
+      <c r="F70" t="n">
+        <v>53764700</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B71" t="n">
+        <v>239.6100006103516</v>
+      </c>
+      <c r="C71" t="n">
+        <v>245.2899932861328</v>
+      </c>
+      <c r="D71" t="n">
+        <v>239.5200042724609</v>
+      </c>
+      <c r="E71" t="n">
+        <v>241.5599975585938</v>
+      </c>
+      <c r="F71" t="n">
+        <v>42236500</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B72" t="n">
+        <v>243.0599975585938</v>
+      </c>
+      <c r="C72" t="n">
+        <v>246.4100036621094</v>
+      </c>
+      <c r="D72" t="n">
+        <v>241.8800048828125</v>
+      </c>
+      <c r="E72" t="n">
+        <v>246.2899932861328</v>
+      </c>
+      <c r="F72" t="n">
+        <v>39509800</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B73" t="n">
+        <v>244.5700073242188</v>
+      </c>
+      <c r="C73" t="n">
+        <v>247.8600006103516</v>
+      </c>
+      <c r="D73" t="n">
+        <v>242.2400054931641</v>
+      </c>
+      <c r="E73" t="n">
+        <v>247.3800048828125</v>
+      </c>
+      <c r="F73" t="n">
+        <v>34560000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B74" t="n">
+        <v>246.7299957275391</v>
+      </c>
+      <c r="C74" t="n">
+        <v>248.9400024414062</v>
+      </c>
+      <c r="D74" t="n">
+        <v>245.9600067138672</v>
+      </c>
+      <c r="E74" t="n">
+        <v>246.4700012207031</v>
+      </c>
+      <c r="F74" t="n">
+        <v>35867800</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B75" t="n">
+        <v>246.5299987792969</v>
+      </c>
+      <c r="C75" t="n">
+        <v>247.6600036621094</v>
+      </c>
+      <c r="D75" t="n">
+        <v>240.25</v>
+      </c>
+      <c r="E75" t="n">
+        <v>242.6000061035156</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38371800</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B76" t="n">
+        <v>241.1499938964844</v>
+      </c>
+      <c r="C76" t="n">
+        <v>241.2799987792969</v>
+      </c>
+      <c r="D76" t="n">
+        <v>236.2200012207031</v>
+      </c>
+      <c r="E76" t="n">
+        <v>236.6499938964844</v>
+      </c>
+      <c r="F76" t="n">
+        <v>41410600</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B77" t="n">
+        <v>239.3099975585938</v>
+      </c>
+      <c r="C77" t="n">
+        <v>240.6499938964844</v>
+      </c>
+      <c r="D77" t="n">
+        <v>236.6300048828125</v>
+      </c>
+      <c r="E77" t="n">
+        <v>238.1799926757812</v>
+      </c>
+      <c r="F77" t="n">
+        <v>43003600</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B78" t="n">
+        <v>239.0899963378906</v>
+      </c>
+      <c r="C78" t="n">
+        <v>239.5700073242188</v>
+      </c>
+      <c r="D78" t="n">
+        <v>236.4100036621094</v>
+      </c>
+      <c r="E78" t="n">
+        <v>239.1199951171875</v>
+      </c>
+      <c r="F78" t="n">
+        <v>45888300</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B79" t="n">
+        <v>233.7599945068359</v>
+      </c>
+      <c r="C79" t="n">
+        <v>235.0899963378906</v>
+      </c>
+      <c r="D79" t="n">
+        <v>229.3399963378906</v>
+      </c>
+      <c r="E79" t="n">
+        <v>231</v>
+      </c>
+      <c r="F79" t="n">
+        <v>47737900</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B80" t="n">
+        <v>231.0899963378906</v>
+      </c>
+      <c r="C80" t="n">
+        <v>232.3000030517578</v>
+      </c>
+      <c r="D80" t="n">
+        <v>226.8800048828125</v>
+      </c>
+      <c r="E80" t="n">
+        <v>231.3099975585938</v>
+      </c>
+      <c r="F80" t="n">
+        <v>47276100</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B81" t="n">
+        <v>234.0500030517578</v>
+      </c>
+      <c r="C81" t="n">
+        <v>235.7200012207031</v>
+      </c>
+      <c r="D81" t="n">
+        <v>230.8999938964844</v>
+      </c>
+      <c r="E81" t="n">
+        <v>234.3399963378906</v>
+      </c>
+      <c r="F81" t="n">
+        <v>31913300</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B82" t="n">
+        <v>234.9600067138672</v>
+      </c>
+      <c r="C82" t="n">
+        <v>240.4499969482422</v>
+      </c>
+      <c r="D82" t="n">
+        <v>234.5700073242188</v>
+      </c>
+      <c r="E82" t="n">
+        <v>239.1600036621094</v>
+      </c>
+      <c r="F82" t="n">
+        <v>33778500</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B83" t="n">
+        <v>239.9799957275391</v>
+      </c>
+      <c r="C83" t="n">
+        <v>240.9499969482422</v>
+      </c>
+      <c r="D83" t="n">
+        <v>237.5399932861328</v>
+      </c>
+      <c r="E83" t="n">
+        <v>238.4199981689453</v>
+      </c>
+      <c r="F83" t="n">
+        <v>32825500</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B84" t="n">
+        <v>239.6900024414062</v>
+      </c>
+      <c r="C84" t="n">
+        <v>244.8800048828125</v>
+      </c>
+      <c r="D84" t="n">
+        <v>238.0800018310547</v>
+      </c>
+      <c r="E84" t="n">
+        <v>244.6799926757812</v>
+      </c>
+      <c r="F84" t="n">
+        <v>38029200</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B85" t="n">
+        <v>246.3699951171875</v>
+      </c>
+      <c r="C85" t="n">
+        <v>247.7799987792969</v>
+      </c>
+      <c r="D85" t="n">
+        <v>241.5299987792969</v>
+      </c>
+      <c r="E85" t="n">
+        <v>243.0099945068359</v>
+      </c>
+      <c r="F85" t="n">
+        <v>40882700</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B86" t="n">
+        <v>242.8200073242188</v>
+      </c>
+      <c r="C86" t="n">
+        <v>243</v>
+      </c>
+      <c r="D86" t="n">
+        <v>236.7400054931641</v>
+      </c>
+      <c r="E86" t="n">
+        <v>241.7299957275391</v>
+      </c>
+      <c r="F86" t="n">
+        <v>47229600</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B87" t="n">
+        <v>239.8899993896484</v>
+      </c>
+      <c r="C87" t="n">
+        <v>243.3200073242188</v>
+      </c>
+      <c r="D87" t="n">
+        <v>237.6399993896484</v>
+      </c>
+      <c r="E87" t="n">
+        <v>239.3000030517578</v>
+      </c>
+      <c r="F87" t="n">
+        <v>46585000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B88" t="n">
+        <v>238.3099975585938</v>
+      </c>
+      <c r="C88" t="n">
+        <v>245.6300048828125</v>
+      </c>
+      <c r="D88" t="n">
+        <v>238.1699981689453</v>
+      </c>
+      <c r="E88" t="n">
+        <v>242.9600067138672</v>
+      </c>
+      <c r="F88" t="n">
+        <v>37546100</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B89" t="n">
+        <v>244.9799957275391</v>
+      </c>
+      <c r="C89" t="n">
+        <v>246.3500061035156</v>
+      </c>
+      <c r="D89" t="n">
+        <v>235.4499969482422</v>
+      </c>
+      <c r="E89" t="n">
+        <v>238.6199951171875</v>
+      </c>
+      <c r="F89" t="n">
+        <v>53831300</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B90" t="n">
+        <v>238.8600006103516</v>
+      </c>
+      <c r="C90" t="n">
+        <v>238.8600006103516</v>
+      </c>
+      <c r="D90" t="n">
+        <v>231.8200073242188</v>
+      </c>
+      <c r="E90" t="n">
+        <v>232.9900054931641</v>
+      </c>
+      <c r="F90" t="n">
+        <v>51299900</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B91" t="n">
+        <v>224.9100036621094</v>
+      </c>
+      <c r="C91" t="n">
+        <v>226.3099975585938</v>
+      </c>
+      <c r="D91" t="n">
+        <v>220.3800048828125</v>
+      </c>
+      <c r="E91" t="n">
+        <v>222.6900024414062</v>
+      </c>
+      <c r="F91" t="n">
+        <v>103509200</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B92" t="n">
+        <v>202.6999969482422</v>
+      </c>
+      <c r="C92" t="n">
+        <v>211.4400024414062</v>
+      </c>
+      <c r="D92" t="n">
+        <v>200.3099975585938</v>
+      </c>
+      <c r="E92" t="n">
+        <v>210.3200073242188</v>
+      </c>
+      <c r="F92" t="n">
+        <v>179210900</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B93" t="n">
+        <v>208.9700012207031</v>
+      </c>
+      <c r="C93" t="n">
+        <v>212.8099975585938</v>
+      </c>
+      <c r="D93" t="n">
+        <v>203.3500061035156</v>
+      </c>
+      <c r="E93" t="n">
+        <v>208.7200012207031</v>
+      </c>
+      <c r="F93" t="n">
+        <v>91178400</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B94" t="n">
+        <v>208.8000030517578</v>
+      </c>
+      <c r="C94" t="n">
+        <v>212.6499938964844</v>
+      </c>
+      <c r="D94" t="n">
+        <v>206.4100036621094</v>
+      </c>
+      <c r="E94" t="n">
+        <v>206.9600067138672</v>
+      </c>
+      <c r="F94" t="n">
+        <v>67175000</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B95" t="n">
+        <v>208.0599975585938</v>
+      </c>
+      <c r="C95" t="n">
+        <v>208.5700073242188</v>
+      </c>
+      <c r="D95" t="n">
+        <v>202.4900054931641</v>
+      </c>
+      <c r="E95" t="n">
+        <v>204.0800018310547</v>
+      </c>
+      <c r="F95" t="n">
+        <v>65545500</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B96" t="n">
+        <v>203.9600067138672</v>
+      </c>
+      <c r="C96" t="n">
+        <v>203.9600067138672</v>
+      </c>
+      <c r="D96" t="n">
+        <v>197.5599975585938</v>
+      </c>
+      <c r="E96" t="n">
+        <v>199.6000061035156</v>
+      </c>
+      <c r="F96" t="n">
+        <v>83975400</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B97" t="n">
+        <v>198.8800048828125</v>
+      </c>
+      <c r="C97" t="n">
+        <v>201.1600036621094</v>
+      </c>
+      <c r="D97" t="n">
+        <v>197.2799987792969</v>
+      </c>
+      <c r="E97" t="n">
+        <v>198.7899932861328</v>
+      </c>
+      <c r="F97" t="n">
+        <v>66321600</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B98" t="n">
+        <v>198.1300048828125</v>
+      </c>
+      <c r="C98" t="n">
+        <v>201.7400054931641</v>
+      </c>
+      <c r="D98" t="n">
+        <v>196</v>
+      </c>
+      <c r="E98" t="n">
+        <v>201.1499938964844</v>
+      </c>
+      <c r="F98" t="n">
+        <v>69879200</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B99" t="n">
+        <v>202.0700073242188</v>
+      </c>
+      <c r="C99" t="n">
+        <v>206.8600006103516</v>
+      </c>
+      <c r="D99" t="n">
+        <v>201.5099945068359</v>
+      </c>
+      <c r="E99" t="n">
+        <v>204.7899932861328</v>
+      </c>
+      <c r="F99" t="n">
+        <v>51003300</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B100" t="n">
+        <v>203.8000030517578</v>
+      </c>
+      <c r="C100" t="n">
+        <v>205.6399993896484</v>
+      </c>
+      <c r="D100" t="n">
+        <v>202.8099975585938</v>
+      </c>
+      <c r="E100" t="n">
+        <v>204.8600006103516</v>
+      </c>
+      <c r="F100" t="n">
+        <v>35669600</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B101" t="n">
+        <v>204.7599945068359</v>
+      </c>
+      <c r="C101" t="n">
+        <v>211.1699981689453</v>
+      </c>
+      <c r="D101" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="E101" t="n">
+        <v>210.1100006103516</v>
+      </c>
+      <c r="F101" t="n">
+        <v>65881600</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B102" t="n">
+        <v>208.1000061035156</v>
+      </c>
+      <c r="C102" t="n">
+        <v>208.4299926757812</v>
+      </c>
+      <c r="D102" t="n">
+        <v>203.1100006103516</v>
+      </c>
+      <c r="E102" t="n">
+        <v>205.2700042724609</v>
+      </c>
+      <c r="F102" t="n">
+        <v>53581500</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B103" t="n">
+        <v>205.4700012207031</v>
+      </c>
+      <c r="C103" t="n">
+        <v>210.3600006103516</v>
+      </c>
+      <c r="D103" t="n">
+        <v>203.25</v>
+      </c>
+      <c r="E103" t="n">
+        <v>208.5599975585938</v>
+      </c>
+      <c r="F103" t="n">
+        <v>41137200</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B104" t="n">
+        <v>210.4600067138672</v>
+      </c>
+      <c r="C104" t="n">
+        <v>211.5899963378906</v>
+      </c>
+      <c r="D104" t="n">
+        <v>208.9299926757812</v>
+      </c>
+      <c r="E104" t="n">
+        <v>210.6399993896484</v>
+      </c>
+      <c r="F104" t="n">
+        <v>41346400</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B105" t="n">
+        <v>210.7299957275391</v>
+      </c>
+      <c r="C105" t="n">
+        <v>211.0500030517578</v>
+      </c>
+      <c r="D105" t="n">
+        <v>205.3500061035156</v>
+      </c>
+      <c r="E105" t="n">
+        <v>207.9199981689453</v>
+      </c>
+      <c r="F105" t="n">
+        <v>47756800</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B106" t="n">
+        <v>206.8300018310547</v>
+      </c>
+      <c r="C106" t="n">
+        <v>210.3300018310547</v>
+      </c>
+      <c r="D106" t="n">
+        <v>205.1999969482422</v>
+      </c>
+      <c r="E106" t="n">
+        <v>210</v>
+      </c>
+      <c r="F106" t="n">
+        <v>57422800</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B107" t="n">
+        <v>204.5500030517578</v>
+      </c>
+      <c r="C107" t="n">
+        <v>209.7299957275391</v>
+      </c>
+      <c r="D107" t="n">
+        <v>203.4600067138672</v>
+      </c>
+      <c r="E107" t="n">
+        <v>208.3899993896484</v>
+      </c>
+      <c r="F107" t="n">
+        <v>46001000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B108" t="n">
+        <v>203.1000061035156</v>
+      </c>
+      <c r="C108" t="n">
+        <v>209.1799926757812</v>
+      </c>
+      <c r="D108" t="n">
+        <v>202.4799957275391</v>
+      </c>
+      <c r="E108" t="n">
+        <v>208.7299957275391</v>
+      </c>
+      <c r="F108" t="n">
+        <v>43184900</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B109" t="n">
+        <v>210.4700012207031</v>
+      </c>
+      <c r="C109" t="n">
+        <v>217.5399932861328</v>
+      </c>
+      <c r="D109" t="n">
+        <v>210.1499938964844</v>
+      </c>
+      <c r="E109" t="n">
+        <v>216.8200073242188</v>
+      </c>
+      <c r="F109" t="n">
+        <v>54731100</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B110" t="n">
+        <v>215.9799957275391</v>
+      </c>
+      <c r="C110" t="n">
+        <v>220.4700012207031</v>
+      </c>
+      <c r="D110" t="n">
+        <v>215.5899963378906</v>
+      </c>
+      <c r="E110" t="n">
+        <v>218.9400024414062</v>
+      </c>
+      <c r="F110" t="n">
+        <v>60943400</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B111" t="n">
+        <v>214.9900054931641</v>
+      </c>
+      <c r="C111" t="n">
+        <v>217.3200073242188</v>
+      </c>
+      <c r="D111" t="n">
+        <v>212.5299987792969</v>
+      </c>
+      <c r="E111" t="n">
+        <v>213.2100067138672</v>
+      </c>
+      <c r="F111" t="n">
+        <v>51152700</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B112" t="n">
+        <v>210.4499969482422</v>
+      </c>
+      <c r="C112" t="n">
+        <v>213.8200073242188</v>
+      </c>
+      <c r="D112" t="n">
+        <v>207.1100006103516</v>
+      </c>
+      <c r="E112" t="n">
+        <v>213.4900054931641</v>
+      </c>
+      <c r="F112" t="n">
+        <v>54642900</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B113" t="n">
+        <v>214.1900024414062</v>
+      </c>
+      <c r="C113" t="n">
+        <v>215.6499938964844</v>
+      </c>
+      <c r="D113" t="n">
+        <v>212.4299926757812</v>
+      </c>
+      <c r="E113" t="n">
+        <v>214.3300018310547</v>
+      </c>
+      <c r="F113" t="n">
+        <v>35678800</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B114" t="n">
+        <v>215.7100067138672</v>
+      </c>
+      <c r="C114" t="n">
+        <v>217</v>
+      </c>
+      <c r="D114" t="n">
+        <v>211.3500061035156</v>
+      </c>
+      <c r="E114" t="n">
+        <v>212.6499938964844</v>
+      </c>
+      <c r="F114" t="n">
+        <v>34199300</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B115" t="n">
+        <v>210.3899993896484</v>
+      </c>
+      <c r="C115" t="n">
+        <v>211.7100067138672</v>
+      </c>
+      <c r="D115" t="n">
+        <v>208.1499938964844</v>
+      </c>
+      <c r="E115" t="n">
+        <v>209.5299987792969</v>
+      </c>
+      <c r="F115" t="n">
+        <v>44349500</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B116" t="n">
+        <v>209.6100006103516</v>
+      </c>
+      <c r="C116" t="n">
+        <v>210.5599975585938</v>
+      </c>
+      <c r="D116" t="n">
+        <v>206.2200012207031</v>
+      </c>
+      <c r="E116" t="n">
+        <v>207.6699981689453</v>
+      </c>
+      <c r="F116" t="n">
+        <v>35662100</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B117" t="n">
+        <v>208.3500061035156</v>
+      </c>
+      <c r="C117" t="n">
+        <v>212.7200012207031</v>
+      </c>
+      <c r="D117" t="n">
+        <v>207.4499969482422</v>
+      </c>
+      <c r="E117" t="n">
+        <v>211.7400054931641</v>
+      </c>
+      <c r="F117" t="n">
+        <v>42209300</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B118" t="n">
+        <v>212.8200073242188</v>
+      </c>
+      <c r="C118" t="n">
+        <v>215.6999969482422</v>
+      </c>
+      <c r="D118" t="n">
+        <v>212.4299926757812</v>
+      </c>
+      <c r="E118" t="n">
+        <v>215.1999969482422</v>
+      </c>
+      <c r="F118" t="n">
+        <v>44969900</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B119" t="n">
+        <v>213.9299926757812</v>
+      </c>
+      <c r="C119" t="n">
+        <v>215.1399993896484</v>
+      </c>
+      <c r="D119" t="n">
+        <v>208.8300018310547</v>
+      </c>
+      <c r="E119" t="n">
+        <v>209.8699951171875</v>
+      </c>
+      <c r="F119" t="n">
+        <v>37846600</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B120" t="n">
+        <v>207.0599975585938</v>
+      </c>
+      <c r="C120" t="n">
+        <v>209.1199951171875</v>
+      </c>
+      <c r="D120" t="n">
+        <v>206.0500030517578</v>
+      </c>
+      <c r="E120" t="n">
+        <v>208.7599945068359</v>
+      </c>
+      <c r="F120" t="n">
+        <v>36440600</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B121" t="n">
+        <v>207.3999938964844</v>
+      </c>
+      <c r="C121" t="n">
+        <v>207.5399932861328</v>
+      </c>
+      <c r="D121" t="n">
+        <v>204.3200073242188</v>
+      </c>
+      <c r="E121" t="n">
+        <v>205.3699951171875</v>
+      </c>
+      <c r="F121" t="n">
+        <v>63694600</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B122" t="n">
+        <v>209.7899932861328</v>
+      </c>
+      <c r="C122" t="n">
+        <v>212.8000030517578</v>
+      </c>
+      <c r="D122" t="n">
+        <v>209.5099945068359</v>
+      </c>
+      <c r="E122" t="n">
+        <v>210.1399993896484</v>
+      </c>
+      <c r="F122" t="n">
+        <v>44277400</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B123" t="n">
+        <v>207.9499969482422</v>
+      </c>
+      <c r="C123" t="n">
+        <v>209.3500061035156</v>
+      </c>
+      <c r="D123" t="n">
+        <v>206.6399993896484</v>
+      </c>
+      <c r="E123" t="n">
+        <v>207.2400054931641</v>
+      </c>
+      <c r="F123" t="n">
+        <v>35351400</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B124" t="n">
+        <v>211.5599975585938</v>
+      </c>
+      <c r="C124" t="n">
+        <v>213.0700073242188</v>
+      </c>
+      <c r="D124" t="n">
+        <v>209.8999938964844</v>
+      </c>
+      <c r="E124" t="n">
+        <v>211.7100067138672</v>
+      </c>
+      <c r="F124" t="n">
+        <v>36388800</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B125" t="n">
+        <v>210.6100006103516</v>
+      </c>
+      <c r="C125" t="n">
+        <v>212.8899993896484</v>
+      </c>
+      <c r="D125" t="n">
+        <v>207.1199951171875</v>
+      </c>
+      <c r="E125" t="n">
+        <v>207.5399932861328</v>
+      </c>
+      <c r="F125" t="n">
+        <v>46654700</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B126" t="n">
+        <v>206.3249969482422</v>
+      </c>
+      <c r="C126" t="n">
+        <v>206.4199981689453</v>
+      </c>
+      <c r="D126" t="n">
+        <v>200.2700042724609</v>
+      </c>
+      <c r="E126" t="n">
+        <v>200.8399963378906</v>
+      </c>
+      <c r="F126" t="n">
+        <v>24190678</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_data.xlsx
+++ b/stock_data.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPY" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMZN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSFT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,8 +20,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +61,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -467,7 +473,7465 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B2" t="n">
+        <v>668.324542434099</v>
+      </c>
+      <c r="C2" t="n">
+        <v>670.1342452495495</v>
+      </c>
+      <c r="D2" t="n">
+        <v>649.1437803121401</v>
+      </c>
+      <c r="E2" t="n">
+        <v>649.32275390625</v>
+      </c>
+      <c r="F2" t="n">
+        <v>159422600</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B3" t="n">
+        <v>656.9095884512618</v>
+      </c>
+      <c r="C3" t="n">
+        <v>661.3642043859337</v>
+      </c>
+      <c r="D3" t="n">
+        <v>656.0345659370097</v>
+      </c>
+      <c r="E3" t="n">
+        <v>659.2860107421875</v>
+      </c>
+      <c r="F3" t="n">
+        <v>79560500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B4" t="n">
+        <v>653.4492417720955</v>
+      </c>
+      <c r="C4" t="n">
+        <v>662.0602448848334</v>
+      </c>
+      <c r="D4" t="n">
+        <v>649.4718888267987</v>
+      </c>
+      <c r="E4" t="n">
+        <v>658.4805908203125</v>
+      </c>
+      <c r="F4" t="n">
+        <v>88779600</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B5" t="n">
+        <v>663.0446741742268</v>
+      </c>
+      <c r="C5" t="n">
+        <v>666.4353410824248</v>
+      </c>
+      <c r="D5" t="n">
+        <v>655.1993304017814</v>
+      </c>
+      <c r="E5" t="n">
+        <v>661.4039916992188</v>
+      </c>
+      <c r="F5" t="n">
+        <v>81702600</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B6" t="n">
+        <v>663.0446615126489</v>
+      </c>
+      <c r="C6" t="n">
+        <v>664.9239754340409</v>
+      </c>
+      <c r="D6" t="n">
+        <v>653.3896149312258</v>
+      </c>
+      <c r="E6" t="n">
+        <v>656.899658203125</v>
+      </c>
+      <c r="F6" t="n">
+        <v>110563300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B7" t="n">
+        <v>655.7660892614911</v>
+      </c>
+      <c r="C7" t="n">
+        <v>661.9906565438909</v>
+      </c>
+      <c r="D7" t="n">
+        <v>654.4138037793879</v>
+      </c>
+      <c r="E7" t="n">
+        <v>660.62841796875</v>
+      </c>
+      <c r="F7" t="n">
+        <v>96500900</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B8" t="n">
+        <v>663.5418206897375</v>
+      </c>
+      <c r="C8" t="n">
+        <v>668.4041493887289</v>
+      </c>
+      <c r="D8" t="n">
+        <v>663.4921159142255</v>
+      </c>
+      <c r="E8" t="n">
+        <v>667.499267578125</v>
+      </c>
+      <c r="F8" t="n">
+        <v>60493400</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B9" t="n">
+        <v>667.6384328159621</v>
+      </c>
+      <c r="C9" t="n">
+        <v>669.1796448635298</v>
+      </c>
+      <c r="D9" t="n">
+        <v>666.1866772188026</v>
+      </c>
+      <c r="E9" t="n">
+        <v>667.4892578125</v>
+      </c>
+      <c r="F9" t="n">
+        <v>56249000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B10" t="n">
+        <v>668.1953369980629</v>
+      </c>
+      <c r="C10" t="n">
+        <v>668.1953369980629</v>
+      </c>
+      <c r="D10" t="n">
+        <v>659.5445816579371</v>
+      </c>
+      <c r="E10" t="n">
+        <v>664.0191040039062</v>
+      </c>
+      <c r="F10" t="n">
+        <v>80564000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B11" t="n">
+        <v>664.3372592841532</v>
+      </c>
+      <c r="C11" t="n">
+        <v>668.9012985038863</v>
+      </c>
+      <c r="D11" t="n">
+        <v>664.019063764971</v>
+      </c>
+      <c r="E11" t="n">
+        <v>667.9566650390625</v>
+      </c>
+      <c r="F11" t="n">
+        <v>65604500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B12" t="n">
+        <v>672.6300829996666</v>
+      </c>
+      <c r="C12" t="n">
+        <v>674.628651928334</v>
+      </c>
+      <c r="D12" t="n">
+        <v>671.8246714345047</v>
+      </c>
+      <c r="E12" t="n">
+        <v>673.4155883789062</v>
+      </c>
+      <c r="F12" t="n">
+        <v>74356500</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B13" t="n">
+        <v>678.8645527756448</v>
+      </c>
+      <c r="C13" t="n">
+        <v>681.658640907831</v>
+      </c>
+      <c r="D13" t="n">
+        <v>678.2580209918731</v>
+      </c>
+      <c r="E13" t="n">
+        <v>681.3603515625</v>
+      </c>
+      <c r="F13" t="n">
+        <v>63339800</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B14" t="n">
+        <v>683.1600908523567</v>
+      </c>
+      <c r="C14" t="n">
+        <v>685.0095454543999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>680.9526890414517</v>
+      </c>
+      <c r="E14" t="n">
+        <v>683.1700439453125</v>
+      </c>
+      <c r="F14" t="n">
+        <v>61738100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B15" t="n">
+        <v>684.8205950917289</v>
+      </c>
+      <c r="C15" t="n">
+        <v>685.795087823854</v>
+      </c>
+      <c r="D15" t="n">
+        <v>679.0037407351697</v>
+      </c>
+      <c r="E15" t="n">
+        <v>683.4981689453125</v>
+      </c>
+      <c r="F15" t="n">
+        <v>85657100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B16" t="n">
+        <v>680.0279207971732</v>
+      </c>
+      <c r="C16" t="n">
+        <v>682.0563488815194</v>
+      </c>
+      <c r="D16" t="n">
+        <v>675.98095703125</v>
+      </c>
+      <c r="E16" t="n">
+        <v>675.98095703125</v>
+      </c>
+      <c r="F16" t="n">
+        <v>76335800</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B17" t="n">
+        <v>681.1614729090464</v>
+      </c>
+      <c r="C17" t="n">
+        <v>681.2012852815519</v>
+      </c>
+      <c r="D17" t="n">
+        <v>675.3943230278239</v>
+      </c>
+      <c r="E17" t="n">
+        <v>678.1983642578125</v>
+      </c>
+      <c r="F17" t="n">
+        <v>87164100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B18" t="n">
+        <v>681.7878948104295</v>
+      </c>
+      <c r="C18" t="n">
+        <v>681.9171636388411</v>
+      </c>
+      <c r="D18" t="n">
+        <v>676.0903560257897</v>
+      </c>
+      <c r="E18" t="n">
+        <v>679.4711303710938</v>
+      </c>
+      <c r="F18" t="n">
+        <v>57315000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B19" t="n">
+        <v>672.2820616639051</v>
+      </c>
+      <c r="C19" t="n">
+        <v>676.1103005794487</v>
+      </c>
+      <c r="D19" t="n">
+        <v>670.7607556049009</v>
+      </c>
+      <c r="E19" t="n">
+        <v>671.4169921875</v>
+      </c>
+      <c r="F19" t="n">
+        <v>78427000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B20" t="n">
+        <v>671.1583975728993</v>
+      </c>
+      <c r="C20" t="n">
+        <v>677.0051112074705</v>
+      </c>
+      <c r="D20" t="n">
+        <v>670.3529860359731</v>
+      </c>
+      <c r="E20" t="n">
+        <v>673.7437133789062</v>
+      </c>
+      <c r="F20" t="n">
+        <v>74402400</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B21" t="n">
+        <v>672.6399897028363</v>
+      </c>
+      <c r="C21" t="n">
+        <v>673.5448715272548</v>
+      </c>
+      <c r="D21" t="n">
+        <v>664.9338680034818</v>
+      </c>
+      <c r="E21" t="n">
+        <v>666.514892578125</v>
+      </c>
+      <c r="F21" t="n">
+        <v>85035300</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B22" t="n">
+        <v>664.1284090392404</v>
+      </c>
+      <c r="C22" t="n">
+        <v>667.2805048704689</v>
+      </c>
+      <c r="D22" t="n">
+        <v>657.4663915648358</v>
+      </c>
+      <c r="E22" t="n">
+        <v>667.1710815429688</v>
+      </c>
+      <c r="F22" t="n">
+        <v>100592400</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B23" t="n">
+        <v>673.4056760856186</v>
+      </c>
+      <c r="C23" t="n">
+        <v>678.317709828293</v>
+      </c>
+      <c r="D23" t="n">
+        <v>671.2082272333661</v>
+      </c>
+      <c r="E23" t="n">
+        <v>677.5819091796875</v>
+      </c>
+      <c r="F23" t="n">
+        <v>75842900</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B24" t="n">
+        <v>676.1002762110339</v>
+      </c>
+      <c r="C24" t="n">
+        <v>679.6997756663966</v>
+      </c>
+      <c r="D24" t="n">
+        <v>674.8871520395073</v>
+      </c>
+      <c r="E24" t="n">
+        <v>679.1329956054688</v>
+      </c>
+      <c r="F24" t="n">
+        <v>58953400</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B25" t="n">
+        <v>680.9128544582501</v>
+      </c>
+      <c r="C25" t="n">
+        <v>681.081935653801</v>
+      </c>
+      <c r="D25" t="n">
+        <v>677.0946296424269</v>
+      </c>
+      <c r="E25" t="n">
+        <v>679.5108642578125</v>
+      </c>
+      <c r="F25" t="n">
+        <v>62312500</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B26" t="n">
+        <v>676.6471697129602</v>
+      </c>
+      <c r="C26" t="n">
+        <v>677.0051169124795</v>
+      </c>
+      <c r="D26" t="n">
+        <v>666.7236935366629</v>
+      </c>
+      <c r="E26" t="n">
+        <v>668.2350463867188</v>
+      </c>
+      <c r="F26" t="n">
+        <v>103457800</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B27" t="n">
+        <v>661.6128286383953</v>
+      </c>
+      <c r="C27" t="n">
+        <v>671.8345948923219</v>
+      </c>
+      <c r="D27" t="n">
+        <v>659.5147893727298</v>
+      </c>
+      <c r="E27" t="n">
+        <v>668.125732421875</v>
+      </c>
+      <c r="F27" t="n">
+        <v>96846700</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B28" t="n">
+        <v>665.9083353081996</v>
+      </c>
+      <c r="C28" t="n">
+        <v>669.8956413839408</v>
+      </c>
+      <c r="D28" t="n">
+        <v>658.4209391867944</v>
+      </c>
+      <c r="E28" t="n">
+        <v>661.901123046875</v>
+      </c>
+      <c r="F28" t="n">
+        <v>90456100</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B29" t="n">
+        <v>658.351356546523</v>
+      </c>
+      <c r="C29" t="n">
+        <v>661.3542775984923</v>
+      </c>
+      <c r="D29" t="n">
+        <v>652.1466953365565</v>
+      </c>
+      <c r="E29" t="n">
+        <v>656.3428344726562</v>
+      </c>
+      <c r="F29" t="n">
+        <v>114467500</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B30" t="n">
+        <v>657.0389163187169</v>
+      </c>
+      <c r="C30" t="n">
+        <v>663.561773390439</v>
+      </c>
+      <c r="D30" t="n">
+        <v>655.020380360944</v>
+      </c>
+      <c r="E30" t="n">
+        <v>658.87841796875</v>
+      </c>
+      <c r="F30" t="n">
+        <v>94703000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B31" t="n">
+        <v>669.1001291109939</v>
+      </c>
+      <c r="C31" t="n">
+        <v>671.7351497651099</v>
+      </c>
+      <c r="D31" t="n">
+        <v>648.1991802397498</v>
+      </c>
+      <c r="E31" t="n">
+        <v>648.8355712890625</v>
+      </c>
+      <c r="F31" t="n">
+        <v>165293500</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B32" t="n">
+        <v>651.3412595795126</v>
+      </c>
+      <c r="C32" t="n">
+        <v>660.7874729698119</v>
+      </c>
+      <c r="D32" t="n">
+        <v>647.1650267848305</v>
+      </c>
+      <c r="E32" t="n">
+        <v>655.2987670898438</v>
+      </c>
+      <c r="F32" t="n">
+        <v>123956200</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B33" t="n">
+        <v>658.9380055466532</v>
+      </c>
+      <c r="C33" t="n">
+        <v>666.2662734630499</v>
+      </c>
+      <c r="D33" t="n">
+        <v>657.8442577670318</v>
+      </c>
+      <c r="E33" t="n">
+        <v>664.9437866210938</v>
+      </c>
+      <c r="F33" t="n">
+        <v>80437900</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B34" t="n">
+        <v>664.8443455838128</v>
+      </c>
+      <c r="C34" t="n">
+        <v>672.3814460202411</v>
+      </c>
+      <c r="D34" t="n">
+        <v>660.7178178396566</v>
+      </c>
+      <c r="E34" t="n">
+        <v>671.1981811523438</v>
+      </c>
+      <c r="F34" t="n">
+        <v>81077100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B35" t="n">
+        <v>673.7934667684052</v>
+      </c>
+      <c r="C35" t="n">
+        <v>677.8404309302599</v>
+      </c>
+      <c r="D35" t="n">
+        <v>672.8885849296569</v>
+      </c>
+      <c r="E35" t="n">
+        <v>675.8318481445312</v>
+      </c>
+      <c r="F35" t="n">
+        <v>71879600</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B36" t="n">
+        <v>677.0051081523229</v>
+      </c>
+      <c r="C36" t="n">
+        <v>679.7991961322198</v>
+      </c>
+      <c r="D36" t="n">
+        <v>676.6471609574353</v>
+      </c>
+      <c r="E36" t="n">
+        <v>679.5208129882812</v>
+      </c>
+      <c r="F36" t="n">
+        <v>49212000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B37" t="n">
+        <v>674.9667623359846</v>
+      </c>
+      <c r="C37" t="n">
+        <v>679.1230890446475</v>
+      </c>
+      <c r="D37" t="n">
+        <v>674.8971513739515</v>
+      </c>
+      <c r="E37" t="n">
+        <v>676.4185180664062</v>
+      </c>
+      <c r="F37" t="n">
+        <v>61201200</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B38" t="n">
+        <v>678.0591325179204</v>
+      </c>
+      <c r="C38" t="n">
+        <v>679.9483994968172</v>
+      </c>
+      <c r="D38" t="n">
+        <v>675.4838303983408</v>
+      </c>
+      <c r="E38" t="n">
+        <v>677.67138671875</v>
+      </c>
+      <c r="F38" t="n">
+        <v>62953800</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B39" t="n">
+        <v>676.7167950740063</v>
+      </c>
+      <c r="C39" t="n">
+        <v>681.0321891246488</v>
+      </c>
+      <c r="D39" t="n">
+        <v>675.8417725523884</v>
+      </c>
+      <c r="E39" t="n">
+        <v>680.0180053710938</v>
+      </c>
+      <c r="F39" t="n">
+        <v>57238500</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B40" t="n">
+        <v>681.4199577792665</v>
+      </c>
+      <c r="C40" t="n">
+        <v>681.4895687361658</v>
+      </c>
+      <c r="D40" t="n">
+        <v>677.4824173401821</v>
+      </c>
+      <c r="E40" t="n">
+        <v>680.51513671875</v>
+      </c>
+      <c r="F40" t="n">
+        <v>61970300</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B41" t="n">
+        <v>681.5890143183475</v>
+      </c>
+      <c r="C41" t="n">
+        <v>684.4925257185774</v>
+      </c>
+      <c r="D41" t="n">
+        <v>680.7040993957534</v>
+      </c>
+      <c r="E41" t="n">
+        <v>681.8078002929688</v>
+      </c>
+      <c r="F41" t="n">
+        <v>79241000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B42" t="n">
+        <v>682.7027235077143</v>
+      </c>
+      <c r="C42" t="n">
+        <v>682.7524282821314</v>
+      </c>
+      <c r="D42" t="n">
+        <v>677.7111260885928</v>
+      </c>
+      <c r="E42" t="n">
+        <v>679.7594604492188</v>
+      </c>
+      <c r="F42" t="n">
+        <v>55231500</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B43" t="n">
+        <v>679.2821528162136</v>
+      </c>
+      <c r="C43" t="n">
+        <v>681.5094606319436</v>
+      </c>
+      <c r="D43" t="n">
+        <v>678.7253258622812</v>
+      </c>
+      <c r="E43" t="n">
+        <v>679.1727294921875</v>
+      </c>
+      <c r="F43" t="n">
+        <v>58310100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B44" t="n">
+        <v>678.6955405173951</v>
+      </c>
+      <c r="C44" t="n">
+        <v>685.0692222502689</v>
+      </c>
+      <c r="D44" t="n">
+        <v>677.4526176554032</v>
+      </c>
+      <c r="E44" t="n">
+        <v>683.6771850585938</v>
+      </c>
+      <c r="F44" t="n">
+        <v>85671300</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B45" t="n">
+        <v>681.2609148661827</v>
+      </c>
+      <c r="C45" t="n">
+        <v>685.3476304583654</v>
+      </c>
+      <c r="D45" t="n">
+        <v>678.3076987410943</v>
+      </c>
+      <c r="E45" t="n">
+        <v>685.26806640625</v>
+      </c>
+      <c r="F45" t="n">
+        <v>86173700</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B46" t="n">
+        <v>684.2737056052856</v>
+      </c>
+      <c r="C46" t="n">
+        <v>684.9797075791527</v>
+      </c>
+      <c r="D46" t="n">
+        <v>675.3246617594549</v>
+      </c>
+      <c r="E46" t="n">
+        <v>677.9000244140625</v>
+      </c>
+      <c r="F46" t="n">
+        <v>113160300</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B47" t="n">
+        <v>681.8574988128718</v>
+      </c>
+      <c r="C47" t="n">
+        <v>681.8774049984522</v>
+      </c>
+      <c r="D47" t="n">
+        <v>675.4042533093998</v>
+      </c>
+      <c r="E47" t="n">
+        <v>676.8758544921875</v>
+      </c>
+      <c r="F47" t="n">
+        <v>90811000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B48" t="n">
+        <v>675.3843754405706</v>
+      </c>
+      <c r="C48" t="n">
+        <v>677.2239376857725</v>
+      </c>
+      <c r="D48" t="n">
+        <v>671.1584377196804</v>
+      </c>
+      <c r="E48" t="n">
+        <v>675.0264282226562</v>
+      </c>
+      <c r="F48" t="n">
+        <v>122030600</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B49" t="n">
+        <v>676.0406154817738</v>
+      </c>
+      <c r="C49" t="n">
+        <v>676.5874893555698</v>
+      </c>
+      <c r="D49" t="n">
+        <v>667.3998140691156</v>
+      </c>
+      <c r="E49" t="n">
+        <v>667.5986938476562</v>
+      </c>
+      <c r="F49" t="n">
+        <v>110625200</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B50" t="n">
+        <v>673.7635606688432</v>
+      </c>
+      <c r="C50" t="n">
+        <v>676.8857972779194</v>
+      </c>
+      <c r="D50" t="n">
+        <v>671.0788959983324</v>
+      </c>
+      <c r="E50" t="n">
+        <v>672.6399536132812</v>
+      </c>
+      <c r="F50" t="n">
+        <v>108650100</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B51" t="n">
+        <v>674.747283458469</v>
+      </c>
+      <c r="C51" t="n">
+        <v>679.2350273728672</v>
+      </c>
+      <c r="D51" t="n">
+        <v>674.6275542880097</v>
+      </c>
+      <c r="E51" t="n">
+        <v>678.7363891601562</v>
+      </c>
+      <c r="F51" t="n">
+        <v>103599500</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B52" t="n">
+        <v>682.0772531068674</v>
+      </c>
+      <c r="C52" t="n">
+        <v>683.4933686131409</v>
+      </c>
+      <c r="D52" t="n">
+        <v>678.7364013691785</v>
+      </c>
+      <c r="E52" t="n">
+        <v>682.96484375</v>
+      </c>
+      <c r="F52" t="n">
+        <v>69556700</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B53" t="n">
+        <v>682.0572680421344</v>
+      </c>
+      <c r="C53" t="n">
+        <v>686.325640311278</v>
+      </c>
+      <c r="D53" t="n">
+        <v>682.0074163952171</v>
+      </c>
+      <c r="E53" t="n">
+        <v>686.0863037109375</v>
+      </c>
+      <c r="F53" t="n">
+        <v>64840000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B54" t="n">
+        <v>686.0763204450832</v>
+      </c>
+      <c r="C54" t="n">
+        <v>688.9484813838191</v>
+      </c>
+      <c r="D54" t="n">
+        <v>685.9267046355759</v>
+      </c>
+      <c r="E54" t="n">
+        <v>688.4996948242188</v>
+      </c>
+      <c r="F54" t="n">
+        <v>39445600</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B55" t="n">
+        <v>688.758988861415</v>
+      </c>
+      <c r="C55" t="n">
+        <v>689.7761694005526</v>
+      </c>
+      <c r="D55" t="n">
+        <v>687.392725060237</v>
+      </c>
+      <c r="E55" t="n">
+        <v>688.4298706054688</v>
+      </c>
+      <c r="F55" t="n">
+        <v>41613300</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B56" t="n">
+        <v>685.6674092439482</v>
+      </c>
+      <c r="C56" t="n">
+        <v>687.322922191004</v>
+      </c>
+      <c r="D56" t="n">
+        <v>684.2014421207446</v>
+      </c>
+      <c r="E56" t="n">
+        <v>685.9765625</v>
+      </c>
+      <c r="F56" t="n">
+        <v>62559500</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B57" t="n">
+        <v>685.5777200962995</v>
+      </c>
+      <c r="C57" t="n">
+        <v>686.6846823672308</v>
+      </c>
+      <c r="D57" t="n">
+        <v>684.7100944386586</v>
+      </c>
+      <c r="E57" t="n">
+        <v>685.138916015625</v>
+      </c>
+      <c r="F57" t="n">
+        <v>47160700</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B58" t="n">
+        <v>685.2685588951464</v>
+      </c>
+      <c r="C58" t="n">
+        <v>685.4879304984822</v>
+      </c>
+      <c r="D58" t="n">
+        <v>679.8533550408816</v>
+      </c>
+      <c r="E58" t="n">
+        <v>680.062744140625</v>
+      </c>
+      <c r="F58" t="n">
+        <v>74144800</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B59" t="n">
+        <v>683.8424472770359</v>
+      </c>
+      <c r="C59" t="n">
+        <v>684.999261161205</v>
+      </c>
+      <c r="D59" t="n">
+        <v>677.9684744567207</v>
+      </c>
+      <c r="E59" t="n">
+        <v>681.309326171875</v>
+      </c>
+      <c r="F59" t="n">
+        <v>89377200</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B60" t="n">
+        <v>684.6701449336617</v>
+      </c>
+      <c r="C60" t="n">
+        <v>687.5522884526621</v>
+      </c>
+      <c r="D60" t="n">
+        <v>684.5106074856512</v>
+      </c>
+      <c r="E60" t="n">
+        <v>685.846923828125</v>
+      </c>
+      <c r="F60" t="n">
+        <v>71927200</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B61" t="n">
+        <v>686.0563439630641</v>
+      </c>
+      <c r="C61" t="n">
+        <v>690.4344019511112</v>
+      </c>
+      <c r="D61" t="n">
+        <v>685.9067890249802</v>
+      </c>
+      <c r="E61" t="n">
+        <v>689.92578125</v>
+      </c>
+      <c r="F61" t="n">
+        <v>69273800</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B62" t="n">
+        <v>690.3047811958188</v>
+      </c>
+      <c r="C62" t="n">
+        <v>692.0699799720542</v>
+      </c>
+      <c r="D62" t="n">
+        <v>687.4426026835383</v>
+      </c>
+      <c r="E62" t="n">
+        <v>687.701904296875</v>
+      </c>
+      <c r="F62" t="n">
+        <v>75588300</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B63" t="n">
+        <v>686.9439569075789</v>
+      </c>
+      <c r="C63" t="n">
+        <v>688.7390423054183</v>
+      </c>
+      <c r="D63" t="n">
+        <v>685.6175622141362</v>
+      </c>
+      <c r="E63" t="n">
+        <v>687.632080078125</v>
+      </c>
+      <c r="F63" t="n">
+        <v>64019200</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B64" t="n">
+        <v>688.7489932725086</v>
+      </c>
+      <c r="C64" t="n">
+        <v>693.4162394407576</v>
+      </c>
+      <c r="D64" t="n">
+        <v>687.3029303433501</v>
+      </c>
+      <c r="E64" t="n">
+        <v>692.1796264648438</v>
+      </c>
+      <c r="F64" t="n">
+        <v>80125500</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B65" t="n">
+        <v>688.7988836287034</v>
+      </c>
+      <c r="C65" t="n">
+        <v>694.1941832506386</v>
+      </c>
+      <c r="D65" t="n">
+        <v>688.7490319805348</v>
+      </c>
+      <c r="E65" t="n">
+        <v>693.2666625976562</v>
+      </c>
+      <c r="F65" t="n">
+        <v>63976000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B66" t="n">
+        <v>693.595779418591</v>
+      </c>
+      <c r="C66" t="n">
+        <v>694.1941818021349</v>
+      </c>
+      <c r="D66" t="n">
+        <v>689.467040360938</v>
+      </c>
+      <c r="E66" t="n">
+        <v>691.8804931640625</v>
+      </c>
+      <c r="F66" t="n">
+        <v>78309700</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B67" t="n">
+        <v>689.1180078469732</v>
+      </c>
+      <c r="C67" t="n">
+        <v>689.8360176539858</v>
+      </c>
+      <c r="D67" t="n">
+        <v>684.1714948792828</v>
+      </c>
+      <c r="E67" t="n">
+        <v>688.479736328125</v>
+      </c>
+      <c r="F67" t="n">
+        <v>94676700</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B68" t="n">
+        <v>692.6782853429351</v>
+      </c>
+      <c r="C68" t="n">
+        <v>693.5558934557131</v>
+      </c>
+      <c r="D68" t="n">
+        <v>689.3673203481677</v>
+      </c>
+      <c r="E68" t="n">
+        <v>690.3546142578125</v>
+      </c>
+      <c r="F68" t="n">
+        <v>77862000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B69" t="n">
+        <v>691.7707369284135</v>
+      </c>
+      <c r="C69" t="n">
+        <v>692.3591568004221</v>
+      </c>
+      <c r="D69" t="n">
+        <v>688.22043529661</v>
+      </c>
+      <c r="E69" t="n">
+        <v>689.7761840820312</v>
+      </c>
+      <c r="F69" t="n">
+        <v>79289200</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B70" t="n">
+        <v>679.6338820353151</v>
+      </c>
+      <c r="C70" t="n">
+        <v>682.9049778344743</v>
+      </c>
+      <c r="D70" t="n">
+        <v>674.7272992054969</v>
+      </c>
+      <c r="E70" t="n">
+        <v>675.7345581054688</v>
+      </c>
+      <c r="F70" t="n">
+        <v>111623300</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B71" t="n">
+        <v>677.7989248999835</v>
+      </c>
+      <c r="C71" t="n">
+        <v>686.8641332264262</v>
+      </c>
+      <c r="D71" t="n">
+        <v>676.2830453044572</v>
+      </c>
+      <c r="E71" t="n">
+        <v>683.5332641601562</v>
+      </c>
+      <c r="F71" t="n">
+        <v>127844500</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B72" t="n">
+        <v>687.9711412752974</v>
+      </c>
+      <c r="C72" t="n">
+        <v>689.2476843606095</v>
+      </c>
+      <c r="D72" t="n">
+        <v>685.0491285530771</v>
+      </c>
+      <c r="E72" t="n">
+        <v>687.103515625</v>
+      </c>
+      <c r="F72" t="n">
+        <v>77112200</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B73" t="n">
+        <v>686.2757685331861</v>
+      </c>
+      <c r="C73" t="n">
+        <v>689.0781127396581</v>
+      </c>
+      <c r="D73" t="n">
+        <v>685.2884137823622</v>
+      </c>
+      <c r="E73" t="n">
+        <v>687.352783203125</v>
+      </c>
+      <c r="F73" t="n">
+        <v>63059600</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B74" t="n">
+        <v>688.609372319757</v>
+      </c>
+      <c r="C74" t="n">
+        <v>692.2394730275811</v>
+      </c>
+      <c r="D74" t="n">
+        <v>688.0409174669724</v>
+      </c>
+      <c r="E74" t="n">
+        <v>690.84326171875</v>
+      </c>
+      <c r="F74" t="n">
+        <v>60473800</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B75" t="n">
+        <v>692.2893344912051</v>
+      </c>
+      <c r="C75" t="n">
+        <v>694.6329705879123</v>
+      </c>
+      <c r="D75" t="n">
+        <v>691.6810104865692</v>
+      </c>
+      <c r="E75" t="n">
+        <v>693.5957641601562</v>
+      </c>
+      <c r="F75" t="n">
+        <v>55506100</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B76" t="n">
+        <v>695.1515053497095</v>
+      </c>
+      <c r="C76" t="n">
+        <v>695.9393926651097</v>
+      </c>
+      <c r="D76" t="n">
+        <v>692.0499903412962</v>
+      </c>
+      <c r="E76" t="n">
+        <v>693.5259399414062</v>
+      </c>
+      <c r="F76" t="n">
+        <v>61172200</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B77" t="n">
+        <v>694.4933553961189</v>
+      </c>
+      <c r="C77" t="n">
+        <v>695.1615135683285</v>
+      </c>
+      <c r="D77" t="n">
+        <v>682.9648421722587</v>
+      </c>
+      <c r="E77" t="n">
+        <v>692.1497192382812</v>
+      </c>
+      <c r="F77" t="n">
+        <v>97486200</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B78" t="n">
+        <v>689.9058246991844</v>
+      </c>
+      <c r="C78" t="n">
+        <v>692.3192774332931</v>
+      </c>
+      <c r="D78" t="n">
+        <v>685.2485609149509</v>
+      </c>
+      <c r="E78" t="n">
+        <v>690.0853271484375</v>
+      </c>
+      <c r="F78" t="n">
+        <v>101835100</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B79" t="n">
+        <v>687.7019133171445</v>
+      </c>
+      <c r="C79" t="n">
+        <v>695.0318708971434</v>
+      </c>
+      <c r="D79" t="n">
+        <v>687.5423149981101</v>
+      </c>
+      <c r="E79" t="n">
+        <v>693.5159912109375</v>
+      </c>
+      <c r="F79" t="n">
+        <v>79286500</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B80" t="n">
+        <v>694.3138377504575</v>
+      </c>
+      <c r="C80" t="n">
+        <v>695.0617950648859</v>
+      </c>
+      <c r="D80" t="n">
+        <v>682.1670182684101</v>
+      </c>
+      <c r="E80" t="n">
+        <v>687.6520385742188</v>
+      </c>
+      <c r="F80" t="n">
+        <v>107904600</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B81" t="n">
+        <v>688.4697490630058</v>
+      </c>
+      <c r="C81" t="n">
+        <v>689.5667896413613</v>
+      </c>
+      <c r="D81" t="n">
+        <v>679.9031787408285</v>
+      </c>
+      <c r="E81" t="n">
+        <v>684.3211059570312</v>
+      </c>
+      <c r="F81" t="n">
+        <v>105204600</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B82" t="n">
+        <v>679.0854402743204</v>
+      </c>
+      <c r="C82" t="n">
+        <v>681.8279505601881</v>
+      </c>
+      <c r="D82" t="n">
+        <v>673.9494421186707</v>
+      </c>
+      <c r="E82" t="n">
+        <v>675.7744750976562</v>
+      </c>
+      <c r="F82" t="n">
+        <v>113610800</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B83" t="n">
+        <v>679.6039887472712</v>
+      </c>
+      <c r="C83" t="n">
+        <v>690.4244132010324</v>
+      </c>
+      <c r="D83" t="n">
+        <v>678.995603890688</v>
+      </c>
+      <c r="E83" t="n">
+        <v>688.739013671875</v>
+      </c>
+      <c r="F83" t="n">
+        <v>89127600</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B84" t="n">
+        <v>687.5423060693106</v>
+      </c>
+      <c r="C84" t="n">
+        <v>693.9747512796714</v>
+      </c>
+      <c r="D84" t="n">
+        <v>686.4652913399738</v>
+      </c>
+      <c r="E84" t="n">
+        <v>692.0599975585938</v>
+      </c>
+      <c r="F84" t="n">
+        <v>73885200</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B85" t="n">
+        <v>693.0572335194393</v>
+      </c>
+      <c r="C85" t="n">
+        <v>694.64286887948</v>
+      </c>
+      <c r="D85" t="n">
+        <v>689.7761552680904</v>
+      </c>
+      <c r="E85" t="n">
+        <v>690.2349243164062</v>
+      </c>
+      <c r="F85" t="n">
+        <v>65185700</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B86" t="n">
+        <v>694.4933668556342</v>
+      </c>
+      <c r="C86" t="n">
+        <v>695.2413241987686</v>
+      </c>
+      <c r="D86" t="n">
+        <v>687.3029816841566</v>
+      </c>
+      <c r="E86" t="n">
+        <v>690.075439453125</v>
+      </c>
+      <c r="F86" t="n">
+        <v>76353900</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B87" t="n">
+        <v>692.3491972008484</v>
+      </c>
+      <c r="C87" t="n">
+        <v>693.4561594586687</v>
+      </c>
+      <c r="D87" t="n">
+        <v>678.5169776231163</v>
+      </c>
+      <c r="E87" t="n">
+        <v>679.41455078125</v>
+      </c>
+      <c r="F87" t="n">
+        <v>118829000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B88" t="n">
+        <v>679.833354327075</v>
+      </c>
+      <c r="C88" t="n">
+        <v>684.410879804094</v>
+      </c>
+      <c r="D88" t="n">
+        <v>675.6747287653898</v>
+      </c>
+      <c r="E88" t="n">
+        <v>679.8931884765625</v>
+      </c>
+      <c r="F88" t="n">
+        <v>96267500</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B89" t="n">
+        <v>678.287593220413</v>
+      </c>
+      <c r="C89" t="n">
+        <v>683.074507822494</v>
+      </c>
+      <c r="D89" t="n">
+        <v>673.9394826742099</v>
+      </c>
+      <c r="E89" t="n">
+        <v>680.9901733398438</v>
+      </c>
+      <c r="F89" t="n">
+        <v>81354700</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B90" t="n">
+        <v>682.157061237011</v>
+      </c>
+      <c r="C90" t="n">
+        <v>687.2730943282486</v>
+      </c>
+      <c r="D90" t="n">
+        <v>680.9702998190471</v>
+      </c>
+      <c r="E90" t="n">
+        <v>684.4208374023438</v>
+      </c>
+      <c r="F90" t="n">
+        <v>73570300</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B91" t="n">
+        <v>681.9775120282383</v>
+      </c>
+      <c r="C91" t="n">
+        <v>684.311104689823</v>
+      </c>
+      <c r="D91" t="n">
+        <v>679.6937101433548</v>
+      </c>
+      <c r="E91" t="n">
+        <v>682.61572265625</v>
+      </c>
+      <c r="F91" t="n">
+        <v>58649400</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B92" t="n">
+        <v>680.4616860592505</v>
+      </c>
+      <c r="C92" t="n">
+        <v>688.1805961724377</v>
+      </c>
+      <c r="D92" t="n">
+        <v>679.8732661615737</v>
+      </c>
+      <c r="E92" t="n">
+        <v>687.5523071289062</v>
+      </c>
+      <c r="F92" t="n">
+        <v>100034000</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B93" t="n">
+        <v>685.9566804858357</v>
+      </c>
+      <c r="C93" t="n">
+        <v>688.1207533479937</v>
+      </c>
+      <c r="D93" t="n">
+        <v>678.5169762252317</v>
+      </c>
+      <c r="E93" t="n">
+        <v>680.531494140625</v>
+      </c>
+      <c r="F93" t="n">
+        <v>90558100</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B94" t="n">
+        <v>680.0427976196477</v>
+      </c>
+      <c r="C94" t="n">
+        <v>686.4751816677359</v>
+      </c>
+      <c r="D94" t="n">
+        <v>678.1479481229125</v>
+      </c>
+      <c r="E94" t="n">
+        <v>685.4779052734375</v>
+      </c>
+      <c r="F94" t="n">
+        <v>73798700</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B95" t="n">
+        <v>688.3002642742074</v>
+      </c>
+      <c r="C95" t="n">
+        <v>691.7907319065998</v>
+      </c>
+      <c r="D95" t="n">
+        <v>688.2204651135966</v>
+      </c>
+      <c r="E95" t="n">
+        <v>691.26220703125</v>
+      </c>
+      <c r="F95" t="n">
+        <v>56369500</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B96" t="n">
+        <v>691.391808867856</v>
+      </c>
+      <c r="C96" t="n">
+        <v>691.4117130049051</v>
+      </c>
+      <c r="D96" t="n">
+        <v>682.4860770890911</v>
+      </c>
+      <c r="E96" t="n">
+        <v>687.422607421875</v>
+      </c>
+      <c r="F96" t="n">
+        <v>71671000</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B97" t="n">
+        <v>681.2295779636313</v>
+      </c>
+      <c r="C97" t="n">
+        <v>684.9892686841309</v>
+      </c>
+      <c r="D97" t="n">
+        <v>679.7835149777827</v>
+      </c>
+      <c r="E97" t="n">
+        <v>684.1216430664062</v>
+      </c>
+      <c r="F97" t="n">
+        <v>83308900</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B98" t="n">
+        <v>676.8515442239554</v>
+      </c>
+      <c r="C98" t="n">
+        <v>686.744509644098</v>
+      </c>
+      <c r="D98" t="n">
+        <v>676.1734035367807</v>
+      </c>
+      <c r="E98" t="n">
+        <v>684.5106201171875</v>
+      </c>
+      <c r="F98" t="n">
+        <v>87477200</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B99" t="n">
+        <v>673.221445388408</v>
+      </c>
+      <c r="C99" t="n">
+        <v>680.7508704958498</v>
+      </c>
+      <c r="D99" t="n">
+        <v>667.8361281509542</v>
+      </c>
+      <c r="E99" t="n">
+        <v>678.4771118164062</v>
+      </c>
+      <c r="F99" t="n">
+        <v>105003100</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B100" t="n">
+        <v>679.7735096903759</v>
+      </c>
+      <c r="C100" t="n">
+        <v>685.2186606854194</v>
+      </c>
+      <c r="D100" t="n">
+        <v>677.7689744100875</v>
+      </c>
+      <c r="E100" t="n">
+        <v>683.2639770507812</v>
+      </c>
+      <c r="F100" t="n">
+        <v>79182200</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B101" t="n">
+        <v>680.2223290726917</v>
+      </c>
+      <c r="C101" t="n">
+        <v>683.6629449535216</v>
+      </c>
+      <c r="D101" t="n">
+        <v>673.7699188745959</v>
+      </c>
+      <c r="E101" t="n">
+        <v>679.4544067382812</v>
+      </c>
+      <c r="F101" t="n">
+        <v>106606500</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B102" t="n">
+        <v>671.5758690877306</v>
+      </c>
+      <c r="C102" t="n">
+        <v>674.2685275228549</v>
+      </c>
+      <c r="D102" t="n">
+        <v>667.9358467743081</v>
+      </c>
+      <c r="E102" t="n">
+        <v>670.5487060546875</v>
+      </c>
+      <c r="F102" t="n">
+        <v>100687000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B103" t="n">
+        <v>664.5750801817165</v>
+      </c>
+      <c r="C103" t="n">
+        <v>678.0681991431876</v>
+      </c>
+      <c r="D103" t="n">
+        <v>660.5859743093405</v>
+      </c>
+      <c r="E103" t="n">
+        <v>676.4227294921875</v>
+      </c>
+      <c r="F103" t="n">
+        <v>102667700</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B104" t="n">
+        <v>675.87413967305</v>
+      </c>
+      <c r="C104" t="n">
+        <v>681.4987932365287</v>
+      </c>
+      <c r="D104" t="n">
+        <v>672.9222404542279</v>
+      </c>
+      <c r="E104" t="n">
+        <v>675.3356323242188</v>
+      </c>
+      <c r="F104" t="n">
+        <v>81505300</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B105" t="n">
+        <v>675.7345715953234</v>
+      </c>
+      <c r="C105" t="n">
+        <v>678.2277626375325</v>
+      </c>
+      <c r="D105" t="n">
+        <v>671.5061293267642</v>
+      </c>
+      <c r="E105" t="n">
+        <v>674.4879760742188</v>
+      </c>
+      <c r="F105" t="n">
+        <v>68441700</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B106" t="n">
+        <v>669.3319958917509</v>
+      </c>
+      <c r="C106" t="n">
+        <v>669.8207124533001</v>
+      </c>
+      <c r="D106" t="n">
+        <v>664.0564256954588</v>
+      </c>
+      <c r="E106" t="n">
+        <v>664.2459106445312</v>
+      </c>
+      <c r="F106" t="n">
+        <v>108882200</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B107" t="n">
+        <v>667.4472371497842</v>
+      </c>
+      <c r="C107" t="n">
+        <v>670.5088831921612</v>
+      </c>
+      <c r="D107" t="n">
+        <v>659.5587462493693</v>
+      </c>
+      <c r="E107" t="n">
+        <v>660.4862060546875</v>
+      </c>
+      <c r="F107" t="n">
+        <v>97200200</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B108" t="n">
+        <v>666.5596317087426</v>
+      </c>
+      <c r="C108" t="n">
+        <v>670.239584206393</v>
+      </c>
+      <c r="D108" t="n">
+        <v>665.3030536555561</v>
+      </c>
+      <c r="E108" t="n">
+        <v>667.2078857421875</v>
+      </c>
+      <c r="F108" t="n">
+        <v>82023100</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B109" t="n">
+        <v>670.5586914524959</v>
+      </c>
+      <c r="C109" t="n">
+        <v>672.60309589337</v>
+      </c>
+      <c r="D109" t="n">
+        <v>667.8760155087483</v>
+      </c>
+      <c r="E109" t="n">
+        <v>668.9630126953125</v>
+      </c>
+      <c r="F109" t="n">
+        <v>87128000</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B110" t="n">
+        <v>666.5396583763402</v>
+      </c>
+      <c r="C110" t="n">
+        <v>667.8959397089973</v>
+      </c>
+      <c r="D110" t="n">
+        <v>659.3892034355257</v>
+      </c>
+      <c r="E110" t="n">
+        <v>659.6285400390625</v>
+      </c>
+      <c r="F110" t="n">
+        <v>82062600</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B111" t="n">
+        <v>655.1806813207687</v>
+      </c>
+      <c r="C111" t="n">
+        <v>661.1743225351036</v>
+      </c>
+      <c r="D111" t="n">
+        <v>653.3855958813168</v>
+      </c>
+      <c r="E111" t="n">
+        <v>658.0029907226562</v>
+      </c>
+      <c r="F111" t="n">
+        <v>111272500</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B112" t="n">
+        <v>656.510009765625</v>
+      </c>
+      <c r="C112" t="n">
+        <v>656.6900024414062</v>
+      </c>
+      <c r="D112" t="n">
+        <v>644.719970703125</v>
+      </c>
+      <c r="E112" t="n">
+        <v>648.5700073242188</v>
+      </c>
+      <c r="F112" t="n">
+        <v>163617500</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B113" t="n">
+        <v>658.0700073242188</v>
+      </c>
+      <c r="C113" t="n">
+        <v>662.6199951171875</v>
+      </c>
+      <c r="D113" t="n">
+        <v>653.9400024414062</v>
+      </c>
+      <c r="E113" t="n">
+        <v>655.3800048828125</v>
+      </c>
+      <c r="F113" t="n">
+        <v>134802700</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B114" t="n">
+        <v>651.3200073242188</v>
+      </c>
+      <c r="C114" t="n">
+        <v>657.030029296875</v>
+      </c>
+      <c r="D114" t="n">
+        <v>649.8800048828125</v>
+      </c>
+      <c r="E114" t="n">
+        <v>653.1799926757812</v>
+      </c>
+      <c r="F114" t="n">
+        <v>96457500</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B115" t="n">
+        <v>658.6699829101562</v>
+      </c>
+      <c r="C115" t="n">
+        <v>660.8900146484375</v>
+      </c>
+      <c r="D115" t="n">
+        <v>654.239990234375</v>
+      </c>
+      <c r="E115" t="n">
+        <v>656.8200073242188</v>
+      </c>
+      <c r="F115" t="n">
+        <v>90653800</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B116" t="n">
+        <v>652.0599975585938</v>
+      </c>
+      <c r="C116" t="n">
+        <v>654.8499755859375</v>
+      </c>
+      <c r="D116" t="n">
+        <v>644.8200073242188</v>
+      </c>
+      <c r="E116" t="n">
+        <v>645.0900268554688</v>
+      </c>
+      <c r="F116" t="n">
+        <v>96494400</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B117" t="n">
+        <v>642.5</v>
+      </c>
+      <c r="C117" t="n">
+        <v>642.6599731445312</v>
+      </c>
+      <c r="D117" t="n">
+        <v>633.1099853515625</v>
+      </c>
+      <c r="E117" t="n">
+        <v>634.0900268554688</v>
+      </c>
+      <c r="F117" t="n">
+        <v>103649400</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B118" t="n">
+        <v>640.1099853515625</v>
+      </c>
+      <c r="C118" t="n">
+        <v>640.3699951171875</v>
+      </c>
+      <c r="D118" t="n">
+        <v>629.280029296875</v>
+      </c>
+      <c r="E118" t="n">
+        <v>631.969970703125</v>
+      </c>
+      <c r="F118" t="n">
+        <v>99275900</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B119" t="n">
+        <v>638.9400024414062</v>
+      </c>
+      <c r="C119" t="n">
+        <v>651.5399780273438</v>
+      </c>
+      <c r="D119" t="n">
+        <v>637.97998046875</v>
+      </c>
+      <c r="E119" t="n">
+        <v>650.3400268554688</v>
+      </c>
+      <c r="F119" t="n">
+        <v>152534100</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B120" t="n">
+        <v>653.9000244140625</v>
+      </c>
+      <c r="C120" t="n">
+        <v>658.52001953125</v>
+      </c>
+      <c r="D120" t="n">
+        <v>653</v>
+      </c>
+      <c r="E120" t="n">
+        <v>655.239990234375</v>
+      </c>
+      <c r="F120" t="n">
+        <v>97841500</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B121" t="n">
+        <v>646.4199829101562</v>
+      </c>
+      <c r="C121" t="n">
+        <v>658.2000122070312</v>
+      </c>
+      <c r="D121" t="n">
+        <v>645.1099853515625</v>
+      </c>
+      <c r="E121" t="n">
+        <v>655.8300170898438</v>
+      </c>
+      <c r="F121" t="n">
+        <v>68358700</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B122" t="n">
+        <v>655.8599853515625</v>
+      </c>
+      <c r="C122" t="n">
+        <v>659.719970703125</v>
+      </c>
+      <c r="D122" t="n">
+        <v>655.52001953125</v>
+      </c>
+      <c r="E122" t="n">
+        <v>658.9299926757812</v>
+      </c>
+      <c r="F122" t="n">
+        <v>38994200</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B123" t="n">
+        <v>656.6500244140625</v>
+      </c>
+      <c r="C123" t="n">
+        <v>658.3599853515625</v>
+      </c>
+      <c r="D123" t="n">
+        <v>651.0599975585938</v>
+      </c>
+      <c r="E123" t="n">
+        <v>656.7449951171875</v>
+      </c>
+      <c r="F123" t="n">
+        <v>35090154</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F123"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B2" t="n">
+        <v>226.2100067138672</v>
+      </c>
+      <c r="C2" t="n">
+        <v>228.25</v>
+      </c>
+      <c r="D2" t="n">
+        <v>216</v>
+      </c>
+      <c r="E2" t="n">
+        <v>216.3699951171875</v>
+      </c>
+      <c r="F2" t="n">
+        <v>72367500</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B3" t="n">
+        <v>217.6999969482422</v>
+      </c>
+      <c r="C3" t="n">
+        <v>220.6799926757812</v>
+      </c>
+      <c r="D3" t="n">
+        <v>217.0399932861328</v>
+      </c>
+      <c r="E3" t="n">
+        <v>220.0700073242188</v>
+      </c>
+      <c r="F3" t="n">
+        <v>37809700</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B4" t="n">
+        <v>215.5599975585938</v>
+      </c>
+      <c r="C4" t="n">
+        <v>219.3200073242188</v>
+      </c>
+      <c r="D4" t="n">
+        <v>212.6000061035156</v>
+      </c>
+      <c r="E4" t="n">
+        <v>216.3899993896484</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45665600</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B5" t="n">
+        <v>216.6199951171875</v>
+      </c>
+      <c r="C5" t="n">
+        <v>217.7100067138672</v>
+      </c>
+      <c r="D5" t="n">
+        <v>212.6600036621094</v>
+      </c>
+      <c r="E5" t="n">
+        <v>215.5700073242188</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45909500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B6" t="n">
+        <v>215.6699981689453</v>
+      </c>
+      <c r="C6" t="n">
+        <v>218.5899963378906</v>
+      </c>
+      <c r="D6" t="n">
+        <v>212.8099975585938</v>
+      </c>
+      <c r="E6" t="n">
+        <v>214.4700012207031</v>
+      </c>
+      <c r="F6" t="n">
+        <v>42414600</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B7" t="n">
+        <v>214.5599975585938</v>
+      </c>
+      <c r="C7" t="n">
+        <v>214.8000030517578</v>
+      </c>
+      <c r="D7" t="n">
+        <v>211.0299987792969</v>
+      </c>
+      <c r="E7" t="n">
+        <v>213.0399932861328</v>
+      </c>
+      <c r="F7" t="n">
+        <v>45986900</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B8" t="n">
+        <v>213.8800048828125</v>
+      </c>
+      <c r="C8" t="n">
+        <v>216.6900024414062</v>
+      </c>
+      <c r="D8" t="n">
+        <v>213.5899963378906</v>
+      </c>
+      <c r="E8" t="n">
+        <v>216.4799957275391</v>
+      </c>
+      <c r="F8" t="n">
+        <v>38882800</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B9" t="n">
+        <v>218.4299926757812</v>
+      </c>
+      <c r="C9" t="n">
+        <v>223.3200073242188</v>
+      </c>
+      <c r="D9" t="n">
+        <v>217.9900054931641</v>
+      </c>
+      <c r="E9" t="n">
+        <v>222.0299987792969</v>
+      </c>
+      <c r="F9" t="n">
+        <v>50494600</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B10" t="n">
+        <v>219.3000030517578</v>
+      </c>
+      <c r="C10" t="n">
+        <v>220.0099945068359</v>
+      </c>
+      <c r="D10" t="n">
+        <v>216.5200042724609</v>
+      </c>
+      <c r="E10" t="n">
+        <v>217.9499969482422</v>
+      </c>
+      <c r="F10" t="n">
+        <v>44308500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B11" t="n">
+        <v>219</v>
+      </c>
+      <c r="C11" t="n">
+        <v>221.3000030517578</v>
+      </c>
+      <c r="D11" t="n">
+        <v>218.1799926757812</v>
+      </c>
+      <c r="E11" t="n">
+        <v>221.0899963378906</v>
+      </c>
+      <c r="F11" t="n">
+        <v>31540000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B12" t="n">
+        <v>221.9700012207031</v>
+      </c>
+      <c r="C12" t="n">
+        <v>225.3999938964844</v>
+      </c>
+      <c r="D12" t="n">
+        <v>221.8999938964844</v>
+      </c>
+      <c r="E12" t="n">
+        <v>224.2100067138672</v>
+      </c>
+      <c r="F12" t="n">
+        <v>38685100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B13" t="n">
+        <v>227.6600036621094</v>
+      </c>
+      <c r="C13" t="n">
+        <v>228.3999938964844</v>
+      </c>
+      <c r="D13" t="n">
+        <v>225.5399932861328</v>
+      </c>
+      <c r="E13" t="n">
+        <v>226.9700012207031</v>
+      </c>
+      <c r="F13" t="n">
+        <v>38267000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B14" t="n">
+        <v>228.2200012207031</v>
+      </c>
+      <c r="C14" t="n">
+        <v>231.4900054931641</v>
+      </c>
+      <c r="D14" t="n">
+        <v>226.2100067138672</v>
+      </c>
+      <c r="E14" t="n">
+        <v>229.25</v>
+      </c>
+      <c r="F14" t="n">
+        <v>47100000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B15" t="n">
+        <v>231.6699981689453</v>
+      </c>
+      <c r="C15" t="n">
+        <v>232.8200073242188</v>
+      </c>
+      <c r="D15" t="n">
+        <v>227.7599945068359</v>
+      </c>
+      <c r="E15" t="n">
+        <v>230.3000030517578</v>
+      </c>
+      <c r="F15" t="n">
+        <v>52036200</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B16" t="n">
+        <v>227.0599975585938</v>
+      </c>
+      <c r="C16" t="n">
+        <v>228.4400024414062</v>
+      </c>
+      <c r="D16" t="n">
+        <v>222.75</v>
+      </c>
+      <c r="E16" t="n">
+        <v>222.8600006103516</v>
+      </c>
+      <c r="F16" t="n">
+        <v>102252900</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B17" t="n">
+        <v>250.1000061035156</v>
+      </c>
+      <c r="C17" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>243.9799957275391</v>
+      </c>
+      <c r="E17" t="n">
+        <v>244.2200012207031</v>
+      </c>
+      <c r="F17" t="n">
+        <v>166340800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B18" t="n">
+        <v>255.3600006103516</v>
+      </c>
+      <c r="C18" t="n">
+        <v>258.6000061035156</v>
+      </c>
+      <c r="D18" t="n">
+        <v>252.8999938964844</v>
+      </c>
+      <c r="E18" t="n">
+        <v>254</v>
+      </c>
+      <c r="F18" t="n">
+        <v>95997800</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B19" t="n">
+        <v>250.3800048828125</v>
+      </c>
+      <c r="C19" t="n">
+        <v>257.010009765625</v>
+      </c>
+      <c r="D19" t="n">
+        <v>248.6600036621094</v>
+      </c>
+      <c r="E19" t="n">
+        <v>249.3200073242188</v>
+      </c>
+      <c r="F19" t="n">
+        <v>51546300</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B20" t="n">
+        <v>249.0299987792969</v>
+      </c>
+      <c r="C20" t="n">
+        <v>251</v>
+      </c>
+      <c r="D20" t="n">
+        <v>246.1600036621094</v>
+      </c>
+      <c r="E20" t="n">
+        <v>250.1999969482422</v>
+      </c>
+      <c r="F20" t="n">
+        <v>40610700</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B21" t="n">
+        <v>249.1600036621094</v>
+      </c>
+      <c r="C21" t="n">
+        <v>250.3800048828125</v>
+      </c>
+      <c r="D21" t="n">
+        <v>242.1699981689453</v>
+      </c>
+      <c r="E21" t="n">
+        <v>243.0399932861328</v>
+      </c>
+      <c r="F21" t="n">
+        <v>46004200</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B22" t="n">
+        <v>242.8999938964844</v>
+      </c>
+      <c r="C22" t="n">
+        <v>244.8999938964844</v>
+      </c>
+      <c r="D22" t="n">
+        <v>238.4900054931641</v>
+      </c>
+      <c r="E22" t="n">
+        <v>244.4100036621094</v>
+      </c>
+      <c r="F22" t="n">
+        <v>46374300</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B23" t="n">
+        <v>248.3399963378906</v>
+      </c>
+      <c r="C23" t="n">
+        <v>251.75</v>
+      </c>
+      <c r="D23" t="n">
+        <v>245.5899963378906</v>
+      </c>
+      <c r="E23" t="n">
+        <v>248.3999938964844</v>
+      </c>
+      <c r="F23" t="n">
+        <v>36476500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B24" t="n">
+        <v>248.4100036621094</v>
+      </c>
+      <c r="C24" t="n">
+        <v>249.75</v>
+      </c>
+      <c r="D24" t="n">
+        <v>247.2299957275391</v>
+      </c>
+      <c r="E24" t="n">
+        <v>249.1000061035156</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23564100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B25" t="n">
+        <v>250.2400054931641</v>
+      </c>
+      <c r="C25" t="n">
+        <v>250.3699951171875</v>
+      </c>
+      <c r="D25" t="n">
+        <v>243.75</v>
+      </c>
+      <c r="E25" t="n">
+        <v>244.1999969482422</v>
+      </c>
+      <c r="F25" t="n">
+        <v>31190100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B26" t="n">
+        <v>243.0500030517578</v>
+      </c>
+      <c r="C26" t="n">
+        <v>243.75</v>
+      </c>
+      <c r="D26" t="n">
+        <v>236.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>237.5800018310547</v>
+      </c>
+      <c r="F26" t="n">
+        <v>41401700</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B27" t="n">
+        <v>235.0599975585938</v>
+      </c>
+      <c r="C27" t="n">
+        <v>238.7299957275391</v>
+      </c>
+      <c r="D27" t="n">
+        <v>232.8899993896484</v>
+      </c>
+      <c r="E27" t="n">
+        <v>234.6900024414062</v>
+      </c>
+      <c r="F27" t="n">
+        <v>38956700</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B28" t="n">
+        <v>233.25</v>
+      </c>
+      <c r="C28" t="n">
+        <v>234.6000061035156</v>
+      </c>
+      <c r="D28" t="n">
+        <v>229.1900024414062</v>
+      </c>
+      <c r="E28" t="n">
+        <v>232.8699951171875</v>
+      </c>
+      <c r="F28" t="n">
+        <v>59919000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B29" t="n">
+        <v>228.1000061035156</v>
+      </c>
+      <c r="C29" t="n">
+        <v>230.1999969482422</v>
+      </c>
+      <c r="D29" t="n">
+        <v>222.4199981689453</v>
+      </c>
+      <c r="E29" t="n">
+        <v>222.5500030517578</v>
+      </c>
+      <c r="F29" t="n">
+        <v>60608400</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B30" t="n">
+        <v>223.7400054931641</v>
+      </c>
+      <c r="C30" t="n">
+        <v>223.7400054931641</v>
+      </c>
+      <c r="D30" t="n">
+        <v>218.5200042724609</v>
+      </c>
+      <c r="E30" t="n">
+        <v>222.6900024414062</v>
+      </c>
+      <c r="F30" t="n">
+        <v>58335600</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B31" t="n">
+        <v>227.0500030517578</v>
+      </c>
+      <c r="C31" t="n">
+        <v>227.4100036621094</v>
+      </c>
+      <c r="D31" t="n">
+        <v>216.7400054931641</v>
+      </c>
+      <c r="E31" t="n">
+        <v>217.1399993896484</v>
+      </c>
+      <c r="F31" t="n">
+        <v>50309000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B32" t="n">
+        <v>216.3500061035156</v>
+      </c>
+      <c r="C32" t="n">
+        <v>222.2100067138672</v>
+      </c>
+      <c r="D32" t="n">
+        <v>215.1799926757812</v>
+      </c>
+      <c r="E32" t="n">
+        <v>220.6900024414062</v>
+      </c>
+      <c r="F32" t="n">
+        <v>68490500</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B33" t="n">
+        <v>222.5599975585938</v>
+      </c>
+      <c r="C33" t="n">
+        <v>227.3300018310547</v>
+      </c>
+      <c r="D33" t="n">
+        <v>222.2700042724609</v>
+      </c>
+      <c r="E33" t="n">
+        <v>226.2799987792969</v>
+      </c>
+      <c r="F33" t="n">
+        <v>54318400</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B34" t="n">
+        <v>226.3800048828125</v>
+      </c>
+      <c r="C34" t="n">
+        <v>230.5200042724609</v>
+      </c>
+      <c r="D34" t="n">
+        <v>223.8000030517578</v>
+      </c>
+      <c r="E34" t="n">
+        <v>229.6699981689453</v>
+      </c>
+      <c r="F34" t="n">
+        <v>39379300</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B35" t="n">
+        <v>230.7400054931641</v>
+      </c>
+      <c r="C35" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="D35" t="n">
+        <v>228.7700042724609</v>
+      </c>
+      <c r="E35" t="n">
+        <v>229.1600036621094</v>
+      </c>
+      <c r="F35" t="n">
+        <v>38497900</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B36" t="n">
+        <v>231.2400054931641</v>
+      </c>
+      <c r="C36" t="n">
+        <v>233.2899932861328</v>
+      </c>
+      <c r="D36" t="n">
+        <v>230.2200012207031</v>
+      </c>
+      <c r="E36" t="n">
+        <v>233.2200012207031</v>
+      </c>
+      <c r="F36" t="n">
+        <v>20292300</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B37" t="n">
+        <v>233.2200012207031</v>
+      </c>
+      <c r="C37" t="n">
+        <v>235.8000030517578</v>
+      </c>
+      <c r="D37" t="n">
+        <v>232.25</v>
+      </c>
+      <c r="E37" t="n">
+        <v>233.8800048828125</v>
+      </c>
+      <c r="F37" t="n">
+        <v>42904000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B38" t="n">
+        <v>235.0099945068359</v>
+      </c>
+      <c r="C38" t="n">
+        <v>238.9700012207031</v>
+      </c>
+      <c r="D38" t="n">
+        <v>233.5500030517578</v>
+      </c>
+      <c r="E38" t="n">
+        <v>234.4199981689453</v>
+      </c>
+      <c r="F38" t="n">
+        <v>45785400</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B39" t="n">
+        <v>233.3500061035156</v>
+      </c>
+      <c r="C39" t="n">
+        <v>233.3800048828125</v>
+      </c>
+      <c r="D39" t="n">
+        <v>230.6100006103516</v>
+      </c>
+      <c r="E39" t="n">
+        <v>232.3800048828125</v>
+      </c>
+      <c r="F39" t="n">
+        <v>35495100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B40" t="n">
+        <v>232.7700042724609</v>
+      </c>
+      <c r="C40" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>226.8000030517578</v>
+      </c>
+      <c r="E40" t="n">
+        <v>229.1100006103516</v>
+      </c>
+      <c r="F40" t="n">
+        <v>45683200</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B41" t="n">
+        <v>230.3200073242188</v>
+      </c>
+      <c r="C41" t="n">
+        <v>231.2400054931641</v>
+      </c>
+      <c r="D41" t="n">
+        <v>228.5500030517578</v>
+      </c>
+      <c r="E41" t="n">
+        <v>229.5299987792969</v>
+      </c>
+      <c r="F41" t="n">
+        <v>33117400</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B42" t="n">
+        <v>229.5899963378906</v>
+      </c>
+      <c r="C42" t="n">
+        <v>230.8300018310547</v>
+      </c>
+      <c r="D42" t="n">
+        <v>226.2700042724609</v>
+      </c>
+      <c r="E42" t="n">
+        <v>226.8899993896484</v>
+      </c>
+      <c r="F42" t="n">
+        <v>35019200</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B43" t="n">
+        <v>226.8399963378906</v>
+      </c>
+      <c r="C43" t="n">
+        <v>228.5700073242188</v>
+      </c>
+      <c r="D43" t="n">
+        <v>225.1100006103516</v>
+      </c>
+      <c r="E43" t="n">
+        <v>227.9199981689453</v>
+      </c>
+      <c r="F43" t="n">
+        <v>25841700</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B44" t="n">
+        <v>228.8099975585938</v>
+      </c>
+      <c r="C44" t="n">
+        <v>232.4199981689453</v>
+      </c>
+      <c r="D44" t="n">
+        <v>228.4600067138672</v>
+      </c>
+      <c r="E44" t="n">
+        <v>231.7799987792969</v>
+      </c>
+      <c r="F44" t="n">
+        <v>38790700</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B45" t="n">
+        <v>230.7100067138672</v>
+      </c>
+      <c r="C45" t="n">
+        <v>232.1100006103516</v>
+      </c>
+      <c r="D45" t="n">
+        <v>228.6900024414062</v>
+      </c>
+      <c r="E45" t="n">
+        <v>230.2799987792969</v>
+      </c>
+      <c r="F45" t="n">
+        <v>28249600</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B46" t="n">
+        <v>229.8699951171875</v>
+      </c>
+      <c r="C46" t="n">
+        <v>230.0800018310547</v>
+      </c>
+      <c r="D46" t="n">
+        <v>225.1199951171875</v>
+      </c>
+      <c r="E46" t="n">
+        <v>226.1900024414062</v>
+      </c>
+      <c r="F46" t="n">
+        <v>35639100</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B47" t="n">
+        <v>227.9299926757812</v>
+      </c>
+      <c r="C47" t="n">
+        <v>227.9299926757812</v>
+      </c>
+      <c r="D47" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>222.5399932861328</v>
+      </c>
+      <c r="F47" t="n">
+        <v>47286100</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B48" t="n">
+        <v>223.0399932861328</v>
+      </c>
+      <c r="C48" t="n">
+        <v>223.6600036621094</v>
+      </c>
+      <c r="D48" t="n">
+        <v>221.1300048828125</v>
+      </c>
+      <c r="E48" t="n">
+        <v>222.5599975585938</v>
+      </c>
+      <c r="F48" t="n">
+        <v>39298900</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B49" t="n">
+        <v>224.6600036621094</v>
+      </c>
+      <c r="C49" t="n">
+        <v>225.1900024414062</v>
+      </c>
+      <c r="D49" t="n">
+        <v>220.9900054931641</v>
+      </c>
+      <c r="E49" t="n">
+        <v>221.2700042724609</v>
+      </c>
+      <c r="F49" t="n">
+        <v>44034400</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B50" t="n">
+        <v>225.7100067138672</v>
+      </c>
+      <c r="C50" t="n">
+        <v>229.2299957275391</v>
+      </c>
+      <c r="D50" t="n">
+        <v>224.4100036621094</v>
+      </c>
+      <c r="E50" t="n">
+        <v>226.7599945068359</v>
+      </c>
+      <c r="F50" t="n">
+        <v>50272400</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B51" t="n">
+        <v>226.7599945068359</v>
+      </c>
+      <c r="C51" t="n">
+        <v>229.1300048828125</v>
+      </c>
+      <c r="D51" t="n">
+        <v>225.5800018310547</v>
+      </c>
+      <c r="E51" t="n">
+        <v>227.3500061035156</v>
+      </c>
+      <c r="F51" t="n">
+        <v>85544400</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B52" t="n">
+        <v>228.6100006103516</v>
+      </c>
+      <c r="C52" t="n">
+        <v>229.4799957275391</v>
+      </c>
+      <c r="D52" t="n">
+        <v>226.7100067138672</v>
+      </c>
+      <c r="E52" t="n">
+        <v>228.4299926757812</v>
+      </c>
+      <c r="F52" t="n">
+        <v>32261300</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B53" t="n">
+        <v>229.0599975585938</v>
+      </c>
+      <c r="C53" t="n">
+        <v>232.4499969482422</v>
+      </c>
+      <c r="D53" t="n">
+        <v>228.7299957275391</v>
+      </c>
+      <c r="E53" t="n">
+        <v>232.1399993896484</v>
+      </c>
+      <c r="F53" t="n">
+        <v>29230200</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B54" t="n">
+        <v>232.1300048828125</v>
+      </c>
+      <c r="C54" t="n">
+        <v>232.9499969482422</v>
+      </c>
+      <c r="D54" t="n">
+        <v>231.3300018310547</v>
+      </c>
+      <c r="E54" t="n">
+        <v>232.3800048828125</v>
+      </c>
+      <c r="F54" t="n">
+        <v>11420500</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B55" t="n">
+        <v>232.0399932861328</v>
+      </c>
+      <c r="C55" t="n">
+        <v>232.9900054931641</v>
+      </c>
+      <c r="D55" t="n">
+        <v>231.1799926757812</v>
+      </c>
+      <c r="E55" t="n">
+        <v>232.5200042724609</v>
+      </c>
+      <c r="F55" t="n">
+        <v>15994700</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B56" t="n">
+        <v>231.9400024414062</v>
+      </c>
+      <c r="C56" t="n">
+        <v>232.6000061035156</v>
+      </c>
+      <c r="D56" t="n">
+        <v>230.7700042724609</v>
+      </c>
+      <c r="E56" t="n">
+        <v>232.0700073242188</v>
+      </c>
+      <c r="F56" t="n">
+        <v>19797900</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B57" t="n">
+        <v>231.2100067138672</v>
+      </c>
+      <c r="C57" t="n">
+        <v>232.7700042724609</v>
+      </c>
+      <c r="D57" t="n">
+        <v>230.1999969482422</v>
+      </c>
+      <c r="E57" t="n">
+        <v>232.5299987792969</v>
+      </c>
+      <c r="F57" t="n">
+        <v>21910500</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B58" t="n">
+        <v>232.9100036621094</v>
+      </c>
+      <c r="C58" t="n">
+        <v>232.9900054931641</v>
+      </c>
+      <c r="D58" t="n">
+        <v>230.1199951171875</v>
+      </c>
+      <c r="E58" t="n">
+        <v>230.8200073242188</v>
+      </c>
+      <c r="F58" t="n">
+        <v>24383700</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B59" t="n">
+        <v>231.3399963378906</v>
+      </c>
+      <c r="C59" t="n">
+        <v>235.4600067138672</v>
+      </c>
+      <c r="D59" t="n">
+        <v>224.6999969482422</v>
+      </c>
+      <c r="E59" t="n">
+        <v>226.5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>51456200</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B60" t="n">
+        <v>228.8399963378906</v>
+      </c>
+      <c r="C60" t="n">
+        <v>234</v>
+      </c>
+      <c r="D60" t="n">
+        <v>227.1799926757812</v>
+      </c>
+      <c r="E60" t="n">
+        <v>233.0599975585938</v>
+      </c>
+      <c r="F60" t="n">
+        <v>49733300</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B61" t="n">
+        <v>232.1000061035156</v>
+      </c>
+      <c r="C61" t="n">
+        <v>243.1799926757812</v>
+      </c>
+      <c r="D61" t="n">
+        <v>232.0700073242188</v>
+      </c>
+      <c r="E61" t="n">
+        <v>240.9299926757812</v>
+      </c>
+      <c r="F61" t="n">
+        <v>53764700</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B62" t="n">
+        <v>239.6100006103516</v>
+      </c>
+      <c r="C62" t="n">
+        <v>245.2899932861328</v>
+      </c>
+      <c r="D62" t="n">
+        <v>239.5200042724609</v>
+      </c>
+      <c r="E62" t="n">
+        <v>241.5599975585938</v>
+      </c>
+      <c r="F62" t="n">
+        <v>42236500</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B63" t="n">
+        <v>243.0599975585938</v>
+      </c>
+      <c r="C63" t="n">
+        <v>246.4100036621094</v>
+      </c>
+      <c r="D63" t="n">
+        <v>241.8800048828125</v>
+      </c>
+      <c r="E63" t="n">
+        <v>246.2899932861328</v>
+      </c>
+      <c r="F63" t="n">
+        <v>39509800</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B64" t="n">
+        <v>244.5700073242188</v>
+      </c>
+      <c r="C64" t="n">
+        <v>247.8600006103516</v>
+      </c>
+      <c r="D64" t="n">
+        <v>242.2400054931641</v>
+      </c>
+      <c r="E64" t="n">
+        <v>247.3800048828125</v>
+      </c>
+      <c r="F64" t="n">
+        <v>34560000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B65" t="n">
+        <v>246.7299957275391</v>
+      </c>
+      <c r="C65" t="n">
+        <v>248.9400024414062</v>
+      </c>
+      <c r="D65" t="n">
+        <v>245.9600067138672</v>
+      </c>
+      <c r="E65" t="n">
+        <v>246.4700012207031</v>
+      </c>
+      <c r="F65" t="n">
+        <v>35867800</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B66" t="n">
+        <v>246.5299987792969</v>
+      </c>
+      <c r="C66" t="n">
+        <v>247.6600036621094</v>
+      </c>
+      <c r="D66" t="n">
+        <v>240.25</v>
+      </c>
+      <c r="E66" t="n">
+        <v>242.6000061035156</v>
+      </c>
+      <c r="F66" t="n">
+        <v>38371800</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B67" t="n">
+        <v>241.1499938964844</v>
+      </c>
+      <c r="C67" t="n">
+        <v>241.2799987792969</v>
+      </c>
+      <c r="D67" t="n">
+        <v>236.2200012207031</v>
+      </c>
+      <c r="E67" t="n">
+        <v>236.6499938964844</v>
+      </c>
+      <c r="F67" t="n">
+        <v>41410600</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B68" t="n">
+        <v>239.3099975585938</v>
+      </c>
+      <c r="C68" t="n">
+        <v>240.6499938964844</v>
+      </c>
+      <c r="D68" t="n">
+        <v>236.6300048828125</v>
+      </c>
+      <c r="E68" t="n">
+        <v>238.1799926757812</v>
+      </c>
+      <c r="F68" t="n">
+        <v>43003600</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B69" t="n">
+        <v>239.0899963378906</v>
+      </c>
+      <c r="C69" t="n">
+        <v>239.5700073242188</v>
+      </c>
+      <c r="D69" t="n">
+        <v>236.4100036621094</v>
+      </c>
+      <c r="E69" t="n">
+        <v>239.1199951171875</v>
+      </c>
+      <c r="F69" t="n">
+        <v>45888300</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B70" t="n">
+        <v>233.7599945068359</v>
+      </c>
+      <c r="C70" t="n">
+        <v>235.0899963378906</v>
+      </c>
+      <c r="D70" t="n">
+        <v>229.3399963378906</v>
+      </c>
+      <c r="E70" t="n">
+        <v>231</v>
+      </c>
+      <c r="F70" t="n">
+        <v>47737900</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B71" t="n">
+        <v>231.0899963378906</v>
+      </c>
+      <c r="C71" t="n">
+        <v>232.3000030517578</v>
+      </c>
+      <c r="D71" t="n">
+        <v>226.8800048828125</v>
+      </c>
+      <c r="E71" t="n">
+        <v>231.3099975585938</v>
+      </c>
+      <c r="F71" t="n">
+        <v>47276100</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B72" t="n">
+        <v>234.0500030517578</v>
+      </c>
+      <c r="C72" t="n">
+        <v>235.7200012207031</v>
+      </c>
+      <c r="D72" t="n">
+        <v>230.8999938964844</v>
+      </c>
+      <c r="E72" t="n">
+        <v>234.3399963378906</v>
+      </c>
+      <c r="F72" t="n">
+        <v>31913300</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B73" t="n">
+        <v>234.9600067138672</v>
+      </c>
+      <c r="C73" t="n">
+        <v>240.4499969482422</v>
+      </c>
+      <c r="D73" t="n">
+        <v>234.5700073242188</v>
+      </c>
+      <c r="E73" t="n">
+        <v>239.1600036621094</v>
+      </c>
+      <c r="F73" t="n">
+        <v>33778500</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B74" t="n">
+        <v>239.9799957275391</v>
+      </c>
+      <c r="C74" t="n">
+        <v>240.9499969482422</v>
+      </c>
+      <c r="D74" t="n">
+        <v>237.5399932861328</v>
+      </c>
+      <c r="E74" t="n">
+        <v>238.4199981689453</v>
+      </c>
+      <c r="F74" t="n">
+        <v>32825500</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B75" t="n">
+        <v>239.6900024414062</v>
+      </c>
+      <c r="C75" t="n">
+        <v>244.8800048828125</v>
+      </c>
+      <c r="D75" t="n">
+        <v>238.0800018310547</v>
+      </c>
+      <c r="E75" t="n">
+        <v>244.6799926757812</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38029200</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B76" t="n">
+        <v>246.3699951171875</v>
+      </c>
+      <c r="C76" t="n">
+        <v>247.7799987792969</v>
+      </c>
+      <c r="D76" t="n">
+        <v>241.5299987792969</v>
+      </c>
+      <c r="E76" t="n">
+        <v>243.0099945068359</v>
+      </c>
+      <c r="F76" t="n">
+        <v>40882700</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B77" t="n">
+        <v>242.8200073242188</v>
+      </c>
+      <c r="C77" t="n">
+        <v>243</v>
+      </c>
+      <c r="D77" t="n">
+        <v>236.7400054931641</v>
+      </c>
+      <c r="E77" t="n">
+        <v>241.7299957275391</v>
+      </c>
+      <c r="F77" t="n">
+        <v>47229600</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B78" t="n">
+        <v>239.8899993896484</v>
+      </c>
+      <c r="C78" t="n">
+        <v>243.3200073242188</v>
+      </c>
+      <c r="D78" t="n">
+        <v>237.6399993896484</v>
+      </c>
+      <c r="E78" t="n">
+        <v>239.3000030517578</v>
+      </c>
+      <c r="F78" t="n">
+        <v>46585000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B79" t="n">
+        <v>238.3099975585938</v>
+      </c>
+      <c r="C79" t="n">
+        <v>245.6300048828125</v>
+      </c>
+      <c r="D79" t="n">
+        <v>238.1699981689453</v>
+      </c>
+      <c r="E79" t="n">
+        <v>242.9600067138672</v>
+      </c>
+      <c r="F79" t="n">
+        <v>37546100</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B80" t="n">
+        <v>244.9799957275391</v>
+      </c>
+      <c r="C80" t="n">
+        <v>246.3500061035156</v>
+      </c>
+      <c r="D80" t="n">
+        <v>235.4499969482422</v>
+      </c>
+      <c r="E80" t="n">
+        <v>238.6199951171875</v>
+      </c>
+      <c r="F80" t="n">
+        <v>53831300</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B81" t="n">
+        <v>238.8600006103516</v>
+      </c>
+      <c r="C81" t="n">
+        <v>238.8600006103516</v>
+      </c>
+      <c r="D81" t="n">
+        <v>231.8200073242188</v>
+      </c>
+      <c r="E81" t="n">
+        <v>232.9900054931641</v>
+      </c>
+      <c r="F81" t="n">
+        <v>51299900</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B82" t="n">
+        <v>224.9100036621094</v>
+      </c>
+      <c r="C82" t="n">
+        <v>226.3099975585938</v>
+      </c>
+      <c r="D82" t="n">
+        <v>220.3800048828125</v>
+      </c>
+      <c r="E82" t="n">
+        <v>222.6900024414062</v>
+      </c>
+      <c r="F82" t="n">
+        <v>103509200</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B83" t="n">
+        <v>202.6999969482422</v>
+      </c>
+      <c r="C83" t="n">
+        <v>211.4400024414062</v>
+      </c>
+      <c r="D83" t="n">
+        <v>200.3099975585938</v>
+      </c>
+      <c r="E83" t="n">
+        <v>210.3200073242188</v>
+      </c>
+      <c r="F83" t="n">
+        <v>179210900</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B84" t="n">
+        <v>208.9700012207031</v>
+      </c>
+      <c r="C84" t="n">
+        <v>212.8099975585938</v>
+      </c>
+      <c r="D84" t="n">
+        <v>203.3500061035156</v>
+      </c>
+      <c r="E84" t="n">
+        <v>208.7200012207031</v>
+      </c>
+      <c r="F84" t="n">
+        <v>91178400</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B85" t="n">
+        <v>208.8000030517578</v>
+      </c>
+      <c r="C85" t="n">
+        <v>212.6499938964844</v>
+      </c>
+      <c r="D85" t="n">
+        <v>206.4100036621094</v>
+      </c>
+      <c r="E85" t="n">
+        <v>206.9600067138672</v>
+      </c>
+      <c r="F85" t="n">
+        <v>67175000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B86" t="n">
+        <v>208.0599975585938</v>
+      </c>
+      <c r="C86" t="n">
+        <v>208.5700073242188</v>
+      </c>
+      <c r="D86" t="n">
+        <v>202.4900054931641</v>
+      </c>
+      <c r="E86" t="n">
+        <v>204.0800018310547</v>
+      </c>
+      <c r="F86" t="n">
+        <v>65545500</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B87" t="n">
+        <v>203.9600067138672</v>
+      </c>
+      <c r="C87" t="n">
+        <v>203.9600067138672</v>
+      </c>
+      <c r="D87" t="n">
+        <v>197.5599975585938</v>
+      </c>
+      <c r="E87" t="n">
+        <v>199.6000061035156</v>
+      </c>
+      <c r="F87" t="n">
+        <v>83975400</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B88" t="n">
+        <v>198.8800048828125</v>
+      </c>
+      <c r="C88" t="n">
+        <v>201.1600036621094</v>
+      </c>
+      <c r="D88" t="n">
+        <v>197.2799987792969</v>
+      </c>
+      <c r="E88" t="n">
+        <v>198.7899932861328</v>
+      </c>
+      <c r="F88" t="n">
+        <v>66321600</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B89" t="n">
+        <v>198.1300048828125</v>
+      </c>
+      <c r="C89" t="n">
+        <v>201.7400054931641</v>
+      </c>
+      <c r="D89" t="n">
+        <v>196</v>
+      </c>
+      <c r="E89" t="n">
+        <v>201.1499938964844</v>
+      </c>
+      <c r="F89" t="n">
+        <v>69879200</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B90" t="n">
+        <v>202.0700073242188</v>
+      </c>
+      <c r="C90" t="n">
+        <v>206.8600006103516</v>
+      </c>
+      <c r="D90" t="n">
+        <v>201.5099945068359</v>
+      </c>
+      <c r="E90" t="n">
+        <v>204.7899932861328</v>
+      </c>
+      <c r="F90" t="n">
+        <v>51003300</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B91" t="n">
+        <v>203.8000030517578</v>
+      </c>
+      <c r="C91" t="n">
+        <v>205.6399993896484</v>
+      </c>
+      <c r="D91" t="n">
+        <v>202.8099975585938</v>
+      </c>
+      <c r="E91" t="n">
+        <v>204.8600006103516</v>
+      </c>
+      <c r="F91" t="n">
+        <v>35669600</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B92" t="n">
+        <v>204.7599945068359</v>
+      </c>
+      <c r="C92" t="n">
+        <v>211.1699981689453</v>
+      </c>
+      <c r="D92" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="E92" t="n">
+        <v>210.1100006103516</v>
+      </c>
+      <c r="F92" t="n">
+        <v>65881600</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B93" t="n">
+        <v>208.1000061035156</v>
+      </c>
+      <c r="C93" t="n">
+        <v>208.4299926757812</v>
+      </c>
+      <c r="D93" t="n">
+        <v>203.1100006103516</v>
+      </c>
+      <c r="E93" t="n">
+        <v>205.2700042724609</v>
+      </c>
+      <c r="F93" t="n">
+        <v>53581500</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B94" t="n">
+        <v>205.4700012207031</v>
+      </c>
+      <c r="C94" t="n">
+        <v>210.3600006103516</v>
+      </c>
+      <c r="D94" t="n">
+        <v>203.25</v>
+      </c>
+      <c r="E94" t="n">
+        <v>208.5599975585938</v>
+      </c>
+      <c r="F94" t="n">
+        <v>41137200</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B95" t="n">
+        <v>210.4600067138672</v>
+      </c>
+      <c r="C95" t="n">
+        <v>211.5899963378906</v>
+      </c>
+      <c r="D95" t="n">
+        <v>208.9299926757812</v>
+      </c>
+      <c r="E95" t="n">
+        <v>210.6399993896484</v>
+      </c>
+      <c r="F95" t="n">
+        <v>41346400</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B96" t="n">
+        <v>210.7299957275391</v>
+      </c>
+      <c r="C96" t="n">
+        <v>211.0500030517578</v>
+      </c>
+      <c r="D96" t="n">
+        <v>205.3500061035156</v>
+      </c>
+      <c r="E96" t="n">
+        <v>207.9199981689453</v>
+      </c>
+      <c r="F96" t="n">
+        <v>47756800</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B97" t="n">
+        <v>206.8300018310547</v>
+      </c>
+      <c r="C97" t="n">
+        <v>210.3300018310547</v>
+      </c>
+      <c r="D97" t="n">
+        <v>205.1999969482422</v>
+      </c>
+      <c r="E97" t="n">
+        <v>210</v>
+      </c>
+      <c r="F97" t="n">
+        <v>57422800</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B98" t="n">
+        <v>204.5500030517578</v>
+      </c>
+      <c r="C98" t="n">
+        <v>209.7299957275391</v>
+      </c>
+      <c r="D98" t="n">
+        <v>203.4600067138672</v>
+      </c>
+      <c r="E98" t="n">
+        <v>208.3899993896484</v>
+      </c>
+      <c r="F98" t="n">
+        <v>46001000</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B99" t="n">
+        <v>203.1000061035156</v>
+      </c>
+      <c r="C99" t="n">
+        <v>209.1799926757812</v>
+      </c>
+      <c r="D99" t="n">
+        <v>202.4799957275391</v>
+      </c>
+      <c r="E99" t="n">
+        <v>208.7299957275391</v>
+      </c>
+      <c r="F99" t="n">
+        <v>43184900</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B100" t="n">
+        <v>210.4700012207031</v>
+      </c>
+      <c r="C100" t="n">
+        <v>217.5399932861328</v>
+      </c>
+      <c r="D100" t="n">
+        <v>210.1499938964844</v>
+      </c>
+      <c r="E100" t="n">
+        <v>216.8200073242188</v>
+      </c>
+      <c r="F100" t="n">
+        <v>54731100</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B101" t="n">
+        <v>215.9799957275391</v>
+      </c>
+      <c r="C101" t="n">
+        <v>220.4700012207031</v>
+      </c>
+      <c r="D101" t="n">
+        <v>215.5899963378906</v>
+      </c>
+      <c r="E101" t="n">
+        <v>218.9400024414062</v>
+      </c>
+      <c r="F101" t="n">
+        <v>60943400</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B102" t="n">
+        <v>214.9900054931641</v>
+      </c>
+      <c r="C102" t="n">
+        <v>217.3200073242188</v>
+      </c>
+      <c r="D102" t="n">
+        <v>212.5299987792969</v>
+      </c>
+      <c r="E102" t="n">
+        <v>213.2100067138672</v>
+      </c>
+      <c r="F102" t="n">
+        <v>51152700</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B103" t="n">
+        <v>210.4499969482422</v>
+      </c>
+      <c r="C103" t="n">
+        <v>213.8200073242188</v>
+      </c>
+      <c r="D103" t="n">
+        <v>207.1100006103516</v>
+      </c>
+      <c r="E103" t="n">
+        <v>213.4900054931641</v>
+      </c>
+      <c r="F103" t="n">
+        <v>54642900</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B104" t="n">
+        <v>214.1900024414062</v>
+      </c>
+      <c r="C104" t="n">
+        <v>215.6499938964844</v>
+      </c>
+      <c r="D104" t="n">
+        <v>212.4299926757812</v>
+      </c>
+      <c r="E104" t="n">
+        <v>214.3300018310547</v>
+      </c>
+      <c r="F104" t="n">
+        <v>35678800</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B105" t="n">
+        <v>215.7100067138672</v>
+      </c>
+      <c r="C105" t="n">
+        <v>217</v>
+      </c>
+      <c r="D105" t="n">
+        <v>211.3500061035156</v>
+      </c>
+      <c r="E105" t="n">
+        <v>212.6499938964844</v>
+      </c>
+      <c r="F105" t="n">
+        <v>34199300</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B106" t="n">
+        <v>210.3899993896484</v>
+      </c>
+      <c r="C106" t="n">
+        <v>211.7100067138672</v>
+      </c>
+      <c r="D106" t="n">
+        <v>208.1499938964844</v>
+      </c>
+      <c r="E106" t="n">
+        <v>209.5299987792969</v>
+      </c>
+      <c r="F106" t="n">
+        <v>44349500</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B107" t="n">
+        <v>209.6100006103516</v>
+      </c>
+      <c r="C107" t="n">
+        <v>210.5599975585938</v>
+      </c>
+      <c r="D107" t="n">
+        <v>206.2200012207031</v>
+      </c>
+      <c r="E107" t="n">
+        <v>207.6699981689453</v>
+      </c>
+      <c r="F107" t="n">
+        <v>35662100</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B108" t="n">
+        <v>208.3500061035156</v>
+      </c>
+      <c r="C108" t="n">
+        <v>212.7200012207031</v>
+      </c>
+      <c r="D108" t="n">
+        <v>207.4499969482422</v>
+      </c>
+      <c r="E108" t="n">
+        <v>211.7400054931641</v>
+      </c>
+      <c r="F108" t="n">
+        <v>42209300</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B109" t="n">
+        <v>212.8200073242188</v>
+      </c>
+      <c r="C109" t="n">
+        <v>215.6999969482422</v>
+      </c>
+      <c r="D109" t="n">
+        <v>212.4299926757812</v>
+      </c>
+      <c r="E109" t="n">
+        <v>215.1999969482422</v>
+      </c>
+      <c r="F109" t="n">
+        <v>44969900</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B110" t="n">
+        <v>213.9299926757812</v>
+      </c>
+      <c r="C110" t="n">
+        <v>215.1399993896484</v>
+      </c>
+      <c r="D110" t="n">
+        <v>208.8300018310547</v>
+      </c>
+      <c r="E110" t="n">
+        <v>209.8699951171875</v>
+      </c>
+      <c r="F110" t="n">
+        <v>37846600</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B111" t="n">
+        <v>207.0599975585938</v>
+      </c>
+      <c r="C111" t="n">
+        <v>209.1199951171875</v>
+      </c>
+      <c r="D111" t="n">
+        <v>206.0500030517578</v>
+      </c>
+      <c r="E111" t="n">
+        <v>208.7599945068359</v>
+      </c>
+      <c r="F111" t="n">
+        <v>36440600</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B112" t="n">
+        <v>207.3999938964844</v>
+      </c>
+      <c r="C112" t="n">
+        <v>207.5399932861328</v>
+      </c>
+      <c r="D112" t="n">
+        <v>204.3200073242188</v>
+      </c>
+      <c r="E112" t="n">
+        <v>205.3699951171875</v>
+      </c>
+      <c r="F112" t="n">
+        <v>63694600</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B113" t="n">
+        <v>209.7899932861328</v>
+      </c>
+      <c r="C113" t="n">
+        <v>212.8000030517578</v>
+      </c>
+      <c r="D113" t="n">
+        <v>209.5099945068359</v>
+      </c>
+      <c r="E113" t="n">
+        <v>210.1399993896484</v>
+      </c>
+      <c r="F113" t="n">
+        <v>44277400</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B114" t="n">
+        <v>207.9499969482422</v>
+      </c>
+      <c r="C114" t="n">
+        <v>209.3500061035156</v>
+      </c>
+      <c r="D114" t="n">
+        <v>206.6399993896484</v>
+      </c>
+      <c r="E114" t="n">
+        <v>207.2400054931641</v>
+      </c>
+      <c r="F114" t="n">
+        <v>35351400</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B115" t="n">
+        <v>211.5599975585938</v>
+      </c>
+      <c r="C115" t="n">
+        <v>213.0700073242188</v>
+      </c>
+      <c r="D115" t="n">
+        <v>209.8999938964844</v>
+      </c>
+      <c r="E115" t="n">
+        <v>211.7100067138672</v>
+      </c>
+      <c r="F115" t="n">
+        <v>36388800</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B116" t="n">
+        <v>210.6100006103516</v>
+      </c>
+      <c r="C116" t="n">
+        <v>212.8899993896484</v>
+      </c>
+      <c r="D116" t="n">
+        <v>207.1199951171875</v>
+      </c>
+      <c r="E116" t="n">
+        <v>207.5399932861328</v>
+      </c>
+      <c r="F116" t="n">
+        <v>46746000</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B117" t="n">
+        <v>206.4600067138672</v>
+      </c>
+      <c r="C117" t="n">
+        <v>206.6000061035156</v>
+      </c>
+      <c r="D117" t="n">
+        <v>199.1399993896484</v>
+      </c>
+      <c r="E117" t="n">
+        <v>199.3399963378906</v>
+      </c>
+      <c r="F117" t="n">
+        <v>56009800</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B118" t="n">
+        <v>201.4799957275391</v>
+      </c>
+      <c r="C118" t="n">
+        <v>203.8000030517578</v>
+      </c>
+      <c r="D118" t="n">
+        <v>199.9799957275391</v>
+      </c>
+      <c r="E118" t="n">
+        <v>200.9499969482422</v>
+      </c>
+      <c r="F118" t="n">
+        <v>46373800</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B119" t="n">
+        <v>204.8500061035156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>210.2799987792969</v>
+      </c>
+      <c r="D119" t="n">
+        <v>204.1399993896484</v>
+      </c>
+      <c r="E119" t="n">
+        <v>208.2700042724609</v>
+      </c>
+      <c r="F119" t="n">
+        <v>58470100</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B120" t="n">
+        <v>210.4400024414062</v>
+      </c>
+      <c r="C120" t="n">
+        <v>213.5800018310547</v>
+      </c>
+      <c r="D120" t="n">
+        <v>208.1900024414062</v>
+      </c>
+      <c r="E120" t="n">
+        <v>210.5700073242188</v>
+      </c>
+      <c r="F120" t="n">
+        <v>45955400</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B121" t="n">
+        <v>206.5399932861328</v>
+      </c>
+      <c r="C121" t="n">
+        <v>212.2100067138672</v>
+      </c>
+      <c r="D121" t="n">
+        <v>204.8999938964844</v>
+      </c>
+      <c r="E121" t="n">
+        <v>209.7700042724609</v>
+      </c>
+      <c r="F121" t="n">
+        <v>31453000</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B122" t="n">
+        <v>209.8000030517578</v>
+      </c>
+      <c r="C122" t="n">
+        <v>212.9499969482422</v>
+      </c>
+      <c r="D122" t="n">
+        <v>209.5899963378906</v>
+      </c>
+      <c r="E122" t="n">
+        <v>212.7899932861328</v>
+      </c>
+      <c r="F122" t="n">
+        <v>25300800</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B123" t="n">
+        <v>211.2400054931641</v>
+      </c>
+      <c r="C123" t="n">
+        <v>213.1499938964844</v>
+      </c>
+      <c r="D123" t="n">
+        <v>209.0800018310547</v>
+      </c>
+      <c r="E123" t="n">
+        <v>212.9006958007812</v>
+      </c>
+      <c r="F123" t="n">
+        <v>14808447</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F123"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B2" t="n">
+        <v>517.4881335274953</v>
+      </c>
+      <c r="C2" t="n">
+        <v>521.4118200258811</v>
+      </c>
+      <c r="D2" t="n">
+        <v>507.5195762105422</v>
+      </c>
+      <c r="E2" t="n">
+        <v>508.8440551757812</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24133800</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B3" t="n">
+        <v>514.2714771071726</v>
+      </c>
+      <c r="C3" t="n">
+        <v>514.2714771071726</v>
+      </c>
+      <c r="D3" t="n">
+        <v>509.5610838753375</v>
+      </c>
+      <c r="E3" t="n">
+        <v>511.9212646484375</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14284200</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B4" t="n">
+        <v>508.1170420708167</v>
+      </c>
+      <c r="C4" t="n">
+        <v>513.146147202046</v>
+      </c>
+      <c r="D4" t="n">
+        <v>503.9045484424133</v>
+      </c>
+      <c r="E4" t="n">
+        <v>511.4432067871094</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14684300</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B5" t="n">
+        <v>512.8275263160849</v>
+      </c>
+      <c r="C5" t="n">
+        <v>515.0482722356254</v>
+      </c>
+      <c r="D5" t="n">
+        <v>507.8880442394631</v>
+      </c>
+      <c r="E5" t="n">
+        <v>511.3038330078125</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14694700</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B6" t="n">
+        <v>510.4573477017149</v>
+      </c>
+      <c r="C6" t="n">
+        <v>514.7096236704256</v>
+      </c>
+      <c r="D6" t="n">
+        <v>506.0257636510178</v>
+      </c>
+      <c r="E6" t="n">
+        <v>509.4913330078125</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15559600</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B7" t="n">
+        <v>506.9320087638593</v>
+      </c>
+      <c r="C7" t="n">
+        <v>513.3453119402852</v>
+      </c>
+      <c r="D7" t="n">
+        <v>505.2091619742922</v>
+      </c>
+      <c r="E7" t="n">
+        <v>511.4532165527344</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19867800</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B8" t="n">
+        <v>512.4788764440519</v>
+      </c>
+      <c r="C8" t="n">
+        <v>516.5519656323323</v>
+      </c>
+      <c r="D8" t="n">
+        <v>511.3037703677804</v>
+      </c>
+      <c r="E8" t="n">
+        <v>514.6498413085938</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14665600</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B9" t="n">
+        <v>515.3569857054445</v>
+      </c>
+      <c r="C9" t="n">
+        <v>516.5420602391357</v>
+      </c>
+      <c r="D9" t="n">
+        <v>510.9154330870712</v>
+      </c>
+      <c r="E9" t="n">
+        <v>515.5162963867188</v>
+      </c>
+      <c r="F9" t="n">
+        <v>15586200</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B10" t="n">
+        <v>518.9918584655633</v>
+      </c>
+      <c r="C10" t="n">
+        <v>523.0549187669818</v>
+      </c>
+      <c r="D10" t="n">
+        <v>515.566101626736</v>
+      </c>
+      <c r="E10" t="n">
+        <v>518.3843383789062</v>
+      </c>
+      <c r="F10" t="n">
+        <v>18962700</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B11" t="n">
+        <v>520.2964530626382</v>
+      </c>
+      <c r="C11" t="n">
+        <v>521.7802730707533</v>
+      </c>
+      <c r="D11" t="n">
+        <v>516.4623598997719</v>
+      </c>
+      <c r="E11" t="n">
+        <v>518.404296875</v>
+      </c>
+      <c r="F11" t="n">
+        <v>14023500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B12" t="n">
+        <v>520.6250388201142</v>
+      </c>
+      <c r="C12" t="n">
+        <v>523.1744351060786</v>
+      </c>
+      <c r="D12" t="n">
+        <v>518.5536961256696</v>
+      </c>
+      <c r="E12" t="n">
+        <v>521.441650390625</v>
+      </c>
+      <c r="F12" t="n">
+        <v>15532400</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B13" t="n">
+        <v>529.577902779321</v>
+      </c>
+      <c r="C13" t="n">
+        <v>532.3662956890146</v>
+      </c>
+      <c r="D13" t="n">
+        <v>526.819354031342</v>
+      </c>
+      <c r="E13" t="n">
+        <v>529.3189697265625</v>
+      </c>
+      <c r="F13" t="n">
+        <v>18734700</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B14" t="n">
+        <v>547.722348424072</v>
+      </c>
+      <c r="C14" t="n">
+        <v>551.4269140414981</v>
+      </c>
+      <c r="D14" t="n">
+        <v>538.5305910090683</v>
+      </c>
+      <c r="E14" t="n">
+        <v>539.8251953125</v>
+      </c>
+      <c r="F14" t="n">
+        <v>29986700</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B15" t="n">
+        <v>542.6832878753321</v>
+      </c>
+      <c r="C15" t="n">
+        <v>544.0077970763692</v>
+      </c>
+      <c r="D15" t="n">
+        <v>534.5072653816836</v>
+      </c>
+      <c r="E15" t="n">
+        <v>539.3073120117188</v>
+      </c>
+      <c r="F15" t="n">
+        <v>36023000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B16" t="n">
+        <v>528.2831883129468</v>
+      </c>
+      <c r="C16" t="n">
+        <v>532.7545848667123</v>
+      </c>
+      <c r="D16" t="n">
+        <v>519.9578228356851</v>
+      </c>
+      <c r="E16" t="n">
+        <v>523.582763671875</v>
+      </c>
+      <c r="F16" t="n">
+        <v>41023100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B17" t="n">
+        <v>526.6898137654194</v>
+      </c>
+      <c r="C17" t="n">
+        <v>527.1279940743384</v>
+      </c>
+      <c r="D17" t="n">
+        <v>512.9668501497666</v>
+      </c>
+      <c r="E17" t="n">
+        <v>515.6656494140625</v>
+      </c>
+      <c r="F17" t="n">
+        <v>34006400</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B18" t="n">
+        <v>517.657371934483</v>
+      </c>
+      <c r="C18" t="n">
+        <v>522.7860691817526</v>
+      </c>
+      <c r="D18" t="n">
+        <v>512.4590180581705</v>
+      </c>
+      <c r="E18" t="n">
+        <v>514.888916015625</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22374700</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B19" t="n">
+        <v>509.6407695643784</v>
+      </c>
+      <c r="C19" t="n">
+        <v>513.4150529816625</v>
+      </c>
+      <c r="D19" t="n">
+        <v>505.7369892339689</v>
+      </c>
+      <c r="E19" t="n">
+        <v>512.2001342773438</v>
+      </c>
+      <c r="F19" t="n">
+        <v>20958700</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B20" t="n">
+        <v>511.1743415428253</v>
+      </c>
+      <c r="C20" t="n">
+        <v>512.6980347767452</v>
+      </c>
+      <c r="D20" t="n">
+        <v>504.4821687767013</v>
+      </c>
+      <c r="E20" t="n">
+        <v>505.0597839355469</v>
+      </c>
+      <c r="F20" t="n">
+        <v>23024300</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B21" t="n">
+        <v>503.5659922381216</v>
+      </c>
+      <c r="C21" t="n">
+        <v>503.6058351018555</v>
+      </c>
+      <c r="D21" t="n">
+        <v>493.7567764386794</v>
+      </c>
+      <c r="E21" t="n">
+        <v>495.0414428710938</v>
+      </c>
+      <c r="F21" t="n">
+        <v>27406500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B22" t="n">
+        <v>494.8920702735404</v>
+      </c>
+      <c r="C22" t="n">
+        <v>497.3119999979126</v>
+      </c>
+      <c r="D22" t="n">
+        <v>491.2073803526309</v>
+      </c>
+      <c r="E22" t="n">
+        <v>494.7626037597656</v>
+      </c>
+      <c r="F22" t="n">
+        <v>24019800</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B23" t="n">
+        <v>497.9692915322098</v>
+      </c>
+      <c r="C23" t="n">
+        <v>504.7510881917551</v>
+      </c>
+      <c r="D23" t="n">
+        <v>496.734405833499</v>
+      </c>
+      <c r="E23" t="n">
+        <v>503.9046020507812</v>
+      </c>
+      <c r="F23" t="n">
+        <v>26101500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B24" t="n">
+        <v>502.7095490222416</v>
+      </c>
+      <c r="C24" t="n">
+        <v>507.4896898672195</v>
+      </c>
+      <c r="D24" t="n">
+        <v>500.2697130079767</v>
+      </c>
+      <c r="E24" t="n">
+        <v>506.573486328125</v>
+      </c>
+      <c r="F24" t="n">
+        <v>17980000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B25" t="n">
+        <v>507.2506574723947</v>
+      </c>
+      <c r="C25" t="n">
+        <v>509.5511194130969</v>
+      </c>
+      <c r="D25" t="n">
+        <v>497.0530724082431</v>
+      </c>
+      <c r="E25" t="n">
+        <v>509.0233154296875</v>
+      </c>
+      <c r="F25" t="n">
+        <v>26574900</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B26" t="n">
+        <v>508.1967287528611</v>
+      </c>
+      <c r="C26" t="n">
+        <v>511.3735209246628</v>
+      </c>
+      <c r="D26" t="n">
+        <v>499.2140928412288</v>
+      </c>
+      <c r="E26" t="n">
+        <v>501.205810546875</v>
+      </c>
+      <c r="F26" t="n">
+        <v>25273100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B27" t="n">
+        <v>496.1667955235038</v>
+      </c>
+      <c r="C27" t="n">
+        <v>509.4814242836766</v>
+      </c>
+      <c r="D27" t="n">
+        <v>495.3800584752997</v>
+      </c>
+      <c r="E27" t="n">
+        <v>508.0672912597656</v>
+      </c>
+      <c r="F27" t="n">
+        <v>28505700</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B28" t="n">
+        <v>506.3444741681719</v>
+      </c>
+      <c r="C28" t="n">
+        <v>509.9992593431845</v>
+      </c>
+      <c r="D28" t="n">
+        <v>502.8191251226507</v>
+      </c>
+      <c r="E28" t="n">
+        <v>505.388427734375</v>
+      </c>
+      <c r="F28" t="n">
+        <v>19092800</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B29" t="n">
+        <v>493.3186219236692</v>
+      </c>
+      <c r="C29" t="n">
+        <v>500.8971240097587</v>
+      </c>
+      <c r="D29" t="n">
+        <v>484.7641975590383</v>
+      </c>
+      <c r="E29" t="n">
+        <v>491.7451782226562</v>
+      </c>
+      <c r="F29" t="n">
+        <v>33815100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B30" t="n">
+        <v>488.070453670226</v>
+      </c>
+      <c r="C30" t="n">
+        <v>493.1393718315724</v>
+      </c>
+      <c r="D30" t="n">
+        <v>480.8305400064438</v>
+      </c>
+      <c r="E30" t="n">
+        <v>485.102783203125</v>
+      </c>
+      <c r="F30" t="n">
+        <v>23245300</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B31" t="n">
+        <v>491.5879641710541</v>
+      </c>
+      <c r="C31" t="n">
+        <v>492.4460215630244</v>
+      </c>
+      <c r="D31" t="n">
+        <v>474.4171642897319</v>
+      </c>
+      <c r="E31" t="n">
+        <v>477.3404846191406</v>
+      </c>
+      <c r="F31" t="n">
+        <v>26802500</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B32" t="n">
+        <v>477.4103368698009</v>
+      </c>
+      <c r="C32" t="n">
+        <v>477.8293938228302</v>
+      </c>
+      <c r="D32" t="n">
+        <v>467.2036221547232</v>
+      </c>
+      <c r="E32" t="n">
+        <v>471.0448608398438</v>
+      </c>
+      <c r="F32" t="n">
+        <v>31769200</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B33" t="n">
+        <v>473.9183160323131</v>
+      </c>
+      <c r="C33" t="n">
+        <v>475.8139832068258</v>
+      </c>
+      <c r="D33" t="n">
+        <v>466.9542001322548</v>
+      </c>
+      <c r="E33" t="n">
+        <v>472.9205932617188</v>
+      </c>
+      <c r="F33" t="n">
+        <v>34421000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B34" t="n">
+        <v>472.9904142849383</v>
+      </c>
+      <c r="C34" t="n">
+        <v>478.0588322743821</v>
+      </c>
+      <c r="D34" t="n">
+        <v>463.8313270788984</v>
+      </c>
+      <c r="E34" t="n">
+        <v>475.9037475585938</v>
+      </c>
+      <c r="F34" t="n">
+        <v>28019800</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B35" t="n">
+        <v>485.2025316262965</v>
+      </c>
+      <c r="C35" t="n">
+        <v>487.1979770584782</v>
+      </c>
+      <c r="D35" t="n">
+        <v>480.1041831621511</v>
+      </c>
+      <c r="E35" t="n">
+        <v>484.3943786621094</v>
+      </c>
+      <c r="F35" t="n">
+        <v>25709100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B36" t="n">
+        <v>486.489626354464</v>
+      </c>
+      <c r="C36" t="n">
+        <v>491.5081706450152</v>
+      </c>
+      <c r="D36" t="n">
+        <v>485.541777548382</v>
+      </c>
+      <c r="E36" t="n">
+        <v>490.8895874023438</v>
+      </c>
+      <c r="F36" t="n">
+        <v>14386700</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B37" t="n">
+        <v>487.3277021324388</v>
+      </c>
+      <c r="C37" t="n">
+        <v>488.7444513856018</v>
+      </c>
+      <c r="D37" t="n">
+        <v>483.5463243869077</v>
+      </c>
+      <c r="E37" t="n">
+        <v>485.6315612792969</v>
+      </c>
+      <c r="F37" t="n">
+        <v>23964000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B38" t="n">
+        <v>485.6116258193264</v>
+      </c>
+      <c r="C38" t="n">
+        <v>492.3761849539621</v>
+      </c>
+      <c r="D38" t="n">
+        <v>485.2125428025972</v>
+      </c>
+      <c r="E38" t="n">
+        <v>488.8841552734375</v>
+      </c>
+      <c r="F38" t="n">
+        <v>19562700</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B39" t="n">
+        <v>475.235297143397</v>
+      </c>
+      <c r="C39" t="n">
+        <v>483.1372440988117</v>
+      </c>
+      <c r="D39" t="n">
+        <v>474.1178525596479</v>
+      </c>
+      <c r="E39" t="n">
+        <v>476.64208984375</v>
+      </c>
+      <c r="F39" t="n">
+        <v>34615100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B40" t="n">
+        <v>478.6674679630734</v>
+      </c>
+      <c r="C40" t="n">
+        <v>480.2239129901724</v>
+      </c>
+      <c r="D40" t="n">
+        <v>475.4048951405118</v>
+      </c>
+      <c r="E40" t="n">
+        <v>479.7449951171875</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22318200</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B41" t="n">
+        <v>481.4211657314621</v>
+      </c>
+      <c r="C41" t="n">
+        <v>482.299166614698</v>
+      </c>
+      <c r="D41" t="n">
+        <v>477.7894707894466</v>
+      </c>
+      <c r="E41" t="n">
+        <v>482.0597229003906</v>
+      </c>
+      <c r="F41" t="n">
+        <v>22608700</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B42" t="n">
+        <v>483.7858099301447</v>
+      </c>
+      <c r="C42" t="n">
+        <v>491.1789088824644</v>
+      </c>
+      <c r="D42" t="n">
+        <v>483.2769615726175</v>
+      </c>
+      <c r="E42" t="n">
+        <v>489.9018249511719</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21965900</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B43" t="n">
+        <v>487.9862027558801</v>
+      </c>
+      <c r="C43" t="n">
+        <v>490.9993144973556</v>
+      </c>
+      <c r="D43" t="n">
+        <v>487.3875630167038</v>
+      </c>
+      <c r="E43" t="n">
+        <v>490.8995361328125</v>
+      </c>
+      <c r="F43" t="n">
+        <v>14696100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B44" t="n">
+        <v>482.9277288439703</v>
+      </c>
+      <c r="C44" t="n">
+        <v>483.1472290611572</v>
+      </c>
+      <c r="D44" t="n">
+        <v>473.9980982856002</v>
+      </c>
+      <c r="E44" t="n">
+        <v>477.4701843261719</v>
+      </c>
+      <c r="F44" t="n">
+        <v>35756200</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B45" t="n">
+        <v>475.5445986070271</v>
+      </c>
+      <c r="C45" t="n">
+        <v>484.9231863556336</v>
+      </c>
+      <c r="D45" t="n">
+        <v>474.7763326037194</v>
+      </c>
+      <c r="E45" t="n">
+        <v>482.3690185546875</v>
+      </c>
+      <c r="F45" t="n">
+        <v>24669200</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B46" t="n">
+        <v>478.7273480015789</v>
+      </c>
+      <c r="C46" t="n">
+        <v>481.3513637649093</v>
+      </c>
+      <c r="D46" t="n">
+        <v>475.2552617920193</v>
+      </c>
+      <c r="E46" t="n">
+        <v>477.4402770996094</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21248100</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B47" t="n">
+        <v>479.0066832317436</v>
+      </c>
+      <c r="C47" t="n">
+        <v>479.6252664455081</v>
+      </c>
+      <c r="D47" t="n">
+        <v>471.4439279747418</v>
+      </c>
+      <c r="E47" t="n">
+        <v>473.7387084960938</v>
+      </c>
+      <c r="F47" t="n">
+        <v>23727700</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B48" t="n">
+        <v>470.8353364785088</v>
+      </c>
+      <c r="C48" t="n">
+        <v>476.8017293564801</v>
+      </c>
+      <c r="D48" t="n">
+        <v>469.8076832860371</v>
+      </c>
+      <c r="E48" t="n">
+        <v>475.3051452636719</v>
+      </c>
+      <c r="F48" t="n">
+        <v>20705600</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B49" t="n">
+        <v>475.8239455574328</v>
+      </c>
+      <c r="C49" t="n">
+        <v>478.9069051052783</v>
+      </c>
+      <c r="D49" t="n">
+        <v>473.9182915104317</v>
+      </c>
+      <c r="E49" t="n">
+        <v>475.0357360839844</v>
+      </c>
+      <c r="F49" t="n">
+        <v>24527200</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B50" t="n">
+        <v>477.1010453906704</v>
+      </c>
+      <c r="C50" t="n">
+        <v>488.4850656489584</v>
+      </c>
+      <c r="D50" t="n">
+        <v>476.8017407441929</v>
+      </c>
+      <c r="E50" t="n">
+        <v>482.8778686523438</v>
+      </c>
+      <c r="F50" t="n">
+        <v>28573500</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B51" t="n">
+        <v>486.2501387748106</v>
+      </c>
+      <c r="C51" t="n">
+        <v>486.7390436209232</v>
+      </c>
+      <c r="D51" t="n">
+        <v>481.39123391446</v>
+      </c>
+      <c r="E51" t="n">
+        <v>484.8134460449219</v>
+      </c>
+      <c r="F51" t="n">
+        <v>70836100</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B52" t="n">
+        <v>485.0129839081317</v>
+      </c>
+      <c r="C52" t="n">
+        <v>487.6170561484318</v>
+      </c>
+      <c r="D52" t="n">
+        <v>481.5908021440126</v>
+      </c>
+      <c r="E52" t="n">
+        <v>483.8157348632812</v>
+      </c>
+      <c r="F52" t="n">
+        <v>16963000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B53" t="n">
+        <v>483.8755963136496</v>
+      </c>
+      <c r="C53" t="n">
+        <v>486.7190818282799</v>
+      </c>
+      <c r="D53" t="n">
+        <v>483.6361221459561</v>
+      </c>
+      <c r="E53" t="n">
+        <v>485.7413330078125</v>
+      </c>
+      <c r="F53" t="n">
+        <v>14683600</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B54" t="n">
+        <v>484.5739628623746</v>
+      </c>
+      <c r="C54" t="n">
+        <v>488.0460488858467</v>
+      </c>
+      <c r="D54" t="n">
+        <v>483.7258924615979</v>
+      </c>
+      <c r="E54" t="n">
+        <v>486.9086303710938</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5855900</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B55" t="n">
+        <v>485.601642461088</v>
+      </c>
+      <c r="C55" t="n">
+        <v>487.0084352251927</v>
+      </c>
+      <c r="D55" t="n">
+        <v>484.8533503811227</v>
+      </c>
+      <c r="E55" t="n">
+        <v>486.599365234375</v>
+      </c>
+      <c r="F55" t="n">
+        <v>8842200</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B56" t="n">
+        <v>483.7558335295542</v>
+      </c>
+      <c r="C56" t="n">
+        <v>487.2379065999322</v>
+      </c>
+      <c r="D56" t="n">
+        <v>483.0773893732932</v>
+      </c>
+      <c r="E56" t="n">
+        <v>485.9907531738281</v>
+      </c>
+      <c r="F56" t="n">
+        <v>10893400</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B57" t="n">
+        <v>484.8234150126488</v>
+      </c>
+      <c r="C57" t="n">
+        <v>488.5648753746365</v>
+      </c>
+      <c r="D57" t="n">
+        <v>484.3944015320139</v>
+      </c>
+      <c r="E57" t="n">
+        <v>486.3699035644531</v>
+      </c>
+      <c r="F57" t="n">
+        <v>13944500</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B58" t="n">
+        <v>486.7290680267604</v>
+      </c>
+      <c r="C58" t="n">
+        <v>487.0284031238816</v>
+      </c>
+      <c r="D58" t="n">
+        <v>482.1993981667827</v>
+      </c>
+      <c r="E58" t="n">
+        <v>482.5186767578125</v>
+      </c>
+      <c r="F58" t="n">
+        <v>15601600</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B59" t="n">
+        <v>483.2869444224563</v>
+      </c>
+      <c r="C59" t="n">
+        <v>483.5563186075122</v>
+      </c>
+      <c r="D59" t="n">
+        <v>469.0893385249197</v>
+      </c>
+      <c r="E59" t="n">
+        <v>471.8630065917969</v>
+      </c>
+      <c r="F59" t="n">
+        <v>25571600</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B60" t="n">
+        <v>472.9804293228547</v>
+      </c>
+      <c r="C60" t="n">
+        <v>474.9858617296903</v>
+      </c>
+      <c r="D60" t="n">
+        <v>468.4308161640092</v>
+      </c>
+      <c r="E60" t="n">
+        <v>471.773193359375</v>
+      </c>
+      <c r="F60" t="n">
+        <v>25250300</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B61" t="n">
+        <v>472.7210225701547</v>
+      </c>
+      <c r="C61" t="n">
+        <v>477.6497753472042</v>
+      </c>
+      <c r="D61" t="n">
+        <v>468.6802576477938</v>
+      </c>
+      <c r="E61" t="n">
+        <v>477.4203186035156</v>
+      </c>
+      <c r="F61" t="n">
+        <v>23037700</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B62" t="n">
+        <v>478.6674756822987</v>
+      </c>
+      <c r="C62" t="n">
+        <v>488.5848422406915</v>
+      </c>
+      <c r="D62" t="n">
+        <v>476.861599942913</v>
+      </c>
+      <c r="E62" t="n">
+        <v>482.3690185546875</v>
+      </c>
+      <c r="F62" t="n">
+        <v>25564200</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B63" t="n">
+        <v>480.1440867981462</v>
+      </c>
+      <c r="C63" t="n">
+        <v>481.5608665012806</v>
+      </c>
+      <c r="D63" t="n">
+        <v>474.7763335277468</v>
+      </c>
+      <c r="E63" t="n">
+        <v>477.0212097167969</v>
+      </c>
+      <c r="F63" t="n">
+        <v>18162600</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B64" t="n">
+        <v>472.9804540365218</v>
+      </c>
+      <c r="C64" t="n">
+        <v>478.7273469366413</v>
+      </c>
+      <c r="D64" t="n">
+        <v>471.1247042989064</v>
+      </c>
+      <c r="E64" t="n">
+        <v>478.1885681152344</v>
+      </c>
+      <c r="F64" t="n">
+        <v>18491000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B65" t="n">
+        <v>475.5845048686955</v>
+      </c>
+      <c r="C65" t="n">
+        <v>479.894643901475</v>
+      </c>
+      <c r="D65" t="n">
+        <v>474.5967386659474</v>
+      </c>
+      <c r="E65" t="n">
+        <v>476.0933227539062</v>
+      </c>
+      <c r="F65" t="n">
+        <v>23519900</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B66" t="n">
+        <v>473.5990225282599</v>
+      </c>
+      <c r="C66" t="n">
+        <v>474.6965236309785</v>
+      </c>
+      <c r="D66" t="n">
+        <v>464.888922501957</v>
+      </c>
+      <c r="E66" t="n">
+        <v>469.5981750488281</v>
+      </c>
+      <c r="F66" t="n">
+        <v>28545800</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B67" t="n">
+        <v>465.3977566654985</v>
+      </c>
+      <c r="C67" t="n">
+        <v>467.1338149970701</v>
+      </c>
+      <c r="D67" t="n">
+        <v>456.1289340170423</v>
+      </c>
+      <c r="E67" t="n">
+        <v>458.3338928222656</v>
+      </c>
+      <c r="F67" t="n">
+        <v>28184300</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B68" t="n">
+        <v>463.0630900555096</v>
+      </c>
+      <c r="C68" t="n">
+        <v>463.1927988881192</v>
+      </c>
+      <c r="D68" t="n">
+        <v>454.8618076165624</v>
+      </c>
+      <c r="E68" t="n">
+        <v>455.6200866699219</v>
+      </c>
+      <c r="F68" t="n">
+        <v>23225800</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B69" t="n">
+        <v>456.7873986695315</v>
+      </c>
+      <c r="C69" t="n">
+        <v>462.1352085061545</v>
+      </c>
+      <c r="D69" t="n">
+        <v>455.4404972994736</v>
+      </c>
+      <c r="E69" t="n">
+        <v>458.8127746582031</v>
+      </c>
+      <c r="F69" t="n">
+        <v>34246700</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B70" t="n">
+        <v>450.1924514863621</v>
+      </c>
+      <c r="C70" t="n">
+        <v>455.7597309230742</v>
+      </c>
+      <c r="D70" t="n">
+        <v>448.2568669541529</v>
+      </c>
+      <c r="E70" t="n">
+        <v>453.4849243164062</v>
+      </c>
+      <c r="F70" t="n">
+        <v>26130000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B71" t="n">
+        <v>451.5693196059127</v>
+      </c>
+      <c r="C71" t="n">
+        <v>451.6591109990197</v>
+      </c>
+      <c r="D71" t="n">
+        <v>437.6810056251358</v>
+      </c>
+      <c r="E71" t="n">
+        <v>443.0986328125</v>
+      </c>
+      <c r="F71" t="n">
+        <v>37980500</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B72" t="n">
+        <v>446.600636936346</v>
+      </c>
+      <c r="C72" t="n">
+        <v>451.8087507279656</v>
+      </c>
+      <c r="D72" t="n">
+        <v>443.6873036586902</v>
+      </c>
+      <c r="E72" t="n">
+        <v>450.1126403808594</v>
+      </c>
+      <c r="F72" t="n">
+        <v>25349400</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B73" t="n">
+        <v>450.8409629929935</v>
+      </c>
+      <c r="C73" t="n">
+        <v>470.0271819611143</v>
+      </c>
+      <c r="D73" t="n">
+        <v>449.5040181949105</v>
+      </c>
+      <c r="E73" t="n">
+        <v>464.888916015625</v>
+      </c>
+      <c r="F73" t="n">
+        <v>38000200</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B74" t="n">
+        <v>464.2503622118351</v>
+      </c>
+      <c r="C74" t="n">
+        <v>473.1700058760031</v>
+      </c>
+      <c r="D74" t="n">
+        <v>460.9479024031912</v>
+      </c>
+      <c r="E74" t="n">
+        <v>469.2090454101562</v>
+      </c>
+      <c r="F74" t="n">
+        <v>29291200</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B75" t="n">
+        <v>472.62128861771</v>
+      </c>
+      <c r="C75" t="n">
+        <v>481.7703893732875</v>
+      </c>
+      <c r="D75" t="n">
+        <v>472.0825097961169</v>
+      </c>
+      <c r="E75" t="n">
+        <v>479.485595703125</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29213900</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B76" t="n">
+        <v>482.1095916405993</v>
+      </c>
+      <c r="C76" t="n">
+        <v>482.6383834693597</v>
+      </c>
+      <c r="D76" t="n">
+        <v>476.9114647448887</v>
+      </c>
+      <c r="E76" t="n">
+        <v>480.533203125</v>
+      </c>
+      <c r="F76" t="n">
+        <v>36875400</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B77" t="n">
+        <v>438.9880283656418</v>
+      </c>
+      <c r="C77" t="n">
+        <v>441.4923222419712</v>
+      </c>
+      <c r="D77" t="n">
+        <v>420.0612263501361</v>
+      </c>
+      <c r="E77" t="n">
+        <v>432.5128173828125</v>
+      </c>
+      <c r="F77" t="n">
+        <v>128855300</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B78" t="n">
+        <v>438.1699022937122</v>
+      </c>
+      <c r="C78" t="n">
+        <v>438.5989157576861</v>
+      </c>
+      <c r="D78" t="n">
+        <v>425.4788680207893</v>
+      </c>
+      <c r="E78" t="n">
+        <v>429.3101196289062</v>
+      </c>
+      <c r="F78" t="n">
+        <v>58566800</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B79" t="n">
+        <v>429.2602343395754</v>
+      </c>
+      <c r="C79" t="n">
+        <v>429.7590957240154</v>
+      </c>
+      <c r="D79" t="n">
+        <v>421.28843915961</v>
+      </c>
+      <c r="E79" t="n">
+        <v>422.4058837890625</v>
+      </c>
+      <c r="F79" t="n">
+        <v>42219900</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B80" t="n">
+        <v>421.0489834358989</v>
+      </c>
+      <c r="C80" t="n">
+        <v>421.0888704228976</v>
+      </c>
+      <c r="D80" t="n">
+        <v>407.6296003977664</v>
+      </c>
+      <c r="E80" t="n">
+        <v>410.2735595703125</v>
+      </c>
+      <c r="F80" t="n">
+        <v>61424100</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B81" t="n">
+        <v>410.0640575889883</v>
+      </c>
+      <c r="C81" t="n">
+        <v>418.8440057668918</v>
+      </c>
+      <c r="D81" t="n">
+        <v>408.3080557741746</v>
+      </c>
+      <c r="E81" t="n">
+        <v>413.2467956542969</v>
+      </c>
+      <c r="F81" t="n">
+        <v>45012400</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B82" t="n">
+        <v>406.5121603821183</v>
+      </c>
+      <c r="C82" t="n">
+        <v>407.3701873334875</v>
+      </c>
+      <c r="D82" t="n">
+        <v>391.4265972483441</v>
+      </c>
+      <c r="E82" t="n">
+        <v>392.7735290527344</v>
+      </c>
+      <c r="F82" t="n">
+        <v>66289200</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B83" t="n">
+        <v>398.2609865133262</v>
+      </c>
+      <c r="C83" t="n">
+        <v>400.875015135043</v>
+      </c>
+      <c r="D83" t="n">
+        <v>392.0252195920243</v>
+      </c>
+      <c r="E83" t="n">
+        <v>400.2265014648438</v>
+      </c>
+      <c r="F83" t="n">
+        <v>53515300</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B84" t="n">
+        <v>403.9280678877113</v>
+      </c>
+      <c r="C84" t="n">
+        <v>413.9452129833927</v>
+      </c>
+      <c r="D84" t="n">
+        <v>399.9571203178888</v>
+      </c>
+      <c r="E84" t="n">
+        <v>412.6581420898438</v>
+      </c>
+      <c r="F84" t="n">
+        <v>45480500</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B85" t="n">
+        <v>418.6644027817824</v>
+      </c>
+      <c r="C85" t="n">
+        <v>422.7151545880433</v>
+      </c>
+      <c r="D85" t="n">
+        <v>411.76017861217</v>
+      </c>
+      <c r="E85" t="n">
+        <v>412.328857421875</v>
+      </c>
+      <c r="F85" t="n">
+        <v>44857900</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B86" t="n">
+        <v>415.2322299614449</v>
+      </c>
+      <c r="C86" t="n">
+        <v>415.5115911022014</v>
+      </c>
+      <c r="D86" t="n">
+        <v>400.096793508188</v>
+      </c>
+      <c r="E86" t="n">
+        <v>403.4491271972656</v>
+      </c>
+      <c r="F86" t="n">
+        <v>42491000</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B87" t="n">
+        <v>404.0777037056333</v>
+      </c>
+      <c r="C87" t="n">
+        <v>405.2749831551046</v>
+      </c>
+      <c r="D87" t="n">
+        <v>397.1036315998776</v>
+      </c>
+      <c r="E87" t="n">
+        <v>400.9248962402344</v>
+      </c>
+      <c r="F87" t="n">
+        <v>40802400</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B88" t="n">
+        <v>403.528974460687</v>
+      </c>
+      <c r="C88" t="n">
+        <v>404.6164885937555</v>
+      </c>
+      <c r="D88" t="n">
+        <v>397.1435245648219</v>
+      </c>
+      <c r="E88" t="n">
+        <v>400.4060974121094</v>
+      </c>
+      <c r="F88" t="n">
+        <v>34091600</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B89" t="n">
+        <v>398.3108793269315</v>
+      </c>
+      <c r="C89" t="n">
+        <v>399.6079067287359</v>
+      </c>
+      <c r="D89" t="n">
+        <v>393.6315571718042</v>
+      </c>
+      <c r="E89" t="n">
+        <v>395.9562377929688</v>
+      </c>
+      <c r="F89" t="n">
+        <v>32078800</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B90" t="n">
+        <v>397.2233488345012</v>
+      </c>
+      <c r="C90" t="n">
+        <v>401.6432531481791</v>
+      </c>
+      <c r="D90" t="n">
+        <v>395.4174731587443</v>
+      </c>
+      <c r="E90" t="n">
+        <v>398.6900024414062</v>
+      </c>
+      <c r="F90" t="n">
+        <v>23223400</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B91" t="n">
+        <v>400.6900024414062</v>
+      </c>
+      <c r="C91" t="n">
+        <v>404.4299926757812</v>
+      </c>
+      <c r="D91" t="n">
+        <v>396.6700134277344</v>
+      </c>
+      <c r="E91" t="n">
+        <v>398.4599914550781</v>
+      </c>
+      <c r="F91" t="n">
+        <v>28234000</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B92" t="n">
+        <v>396.1099853515625</v>
+      </c>
+      <c r="C92" t="n">
+        <v>400.1199951171875</v>
+      </c>
+      <c r="D92" t="n">
+        <v>395.1600036621094</v>
+      </c>
+      <c r="E92" t="n">
+        <v>397.2300109863281</v>
+      </c>
+      <c r="F92" t="n">
+        <v>34015200</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B93" t="n">
+        <v>395</v>
+      </c>
+      <c r="C93" t="n">
+        <v>395.3599853515625</v>
+      </c>
+      <c r="D93" t="n">
+        <v>383.1000061035156</v>
+      </c>
+      <c r="E93" t="n">
+        <v>384.4700012207031</v>
+      </c>
+      <c r="F93" t="n">
+        <v>43238300</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B94" t="n">
+        <v>384.1400146484375</v>
+      </c>
+      <c r="C94" t="n">
+        <v>389.3599853515625</v>
+      </c>
+      <c r="D94" t="n">
+        <v>381.7099914550781</v>
+      </c>
+      <c r="E94" t="n">
+        <v>389</v>
+      </c>
+      <c r="F94" t="n">
+        <v>33884700</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B95" t="n">
+        <v>390.5299987792969</v>
+      </c>
+      <c r="C95" t="n">
+        <v>401.4700012207031</v>
+      </c>
+      <c r="D95" t="n">
+        <v>390.1600036621094</v>
+      </c>
+      <c r="E95" t="n">
+        <v>400.6000061035156</v>
+      </c>
+      <c r="F95" t="n">
+        <v>43625500</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B96" t="n">
+        <v>404.7099914550781</v>
+      </c>
+      <c r="C96" t="n">
+        <v>407.489990234375</v>
+      </c>
+      <c r="D96" t="n">
+        <v>398.739990234375</v>
+      </c>
+      <c r="E96" t="n">
+        <v>401.7200012207031</v>
+      </c>
+      <c r="F96" t="n">
+        <v>34405900</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B97" t="n">
+        <v>390.8800048828125</v>
+      </c>
+      <c r="C97" t="n">
+        <v>396.8200073242188</v>
+      </c>
+      <c r="D97" t="n">
+        <v>389.8800048828125</v>
+      </c>
+      <c r="E97" t="n">
+        <v>392.739990234375</v>
+      </c>
+      <c r="F97" t="n">
+        <v>51367200</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B98" t="n">
+        <v>392.8599853515625</v>
+      </c>
+      <c r="C98" t="n">
+        <v>401.1900024414062</v>
+      </c>
+      <c r="D98" t="n">
+        <v>390.6300048828125</v>
+      </c>
+      <c r="E98" t="n">
+        <v>398.5499877929688</v>
+      </c>
+      <c r="F98" t="n">
+        <v>35474900</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B99" t="n">
+        <v>393.1400146484375</v>
+      </c>
+      <c r="C99" t="n">
+        <v>406.7000122070312</v>
+      </c>
+      <c r="D99" t="n">
+        <v>392.6700134277344</v>
+      </c>
+      <c r="E99" t="n">
+        <v>403.9299926757812</v>
+      </c>
+      <c r="F99" t="n">
+        <v>38199200</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B100" t="n">
+        <v>401.2699890136719</v>
+      </c>
+      <c r="C100" t="n">
+        <v>411.0299987792969</v>
+      </c>
+      <c r="D100" t="n">
+        <v>400.3099975585938</v>
+      </c>
+      <c r="E100" t="n">
+        <v>405.2000122070312</v>
+      </c>
+      <c r="F100" t="n">
+        <v>35808000</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B101" t="n">
+        <v>404.4200134277344</v>
+      </c>
+      <c r="C101" t="n">
+        <v>411.6099853515625</v>
+      </c>
+      <c r="D101" t="n">
+        <v>404.3999938964844</v>
+      </c>
+      <c r="E101" t="n">
+        <v>410.6799926757812</v>
+      </c>
+      <c r="F101" t="n">
+        <v>39001300</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B102" t="n">
+        <v>409.2000122070312</v>
+      </c>
+      <c r="C102" t="n">
+        <v>413.0499877929688</v>
+      </c>
+      <c r="D102" t="n">
+        <v>408.510009765625</v>
+      </c>
+      <c r="E102" t="n">
+        <v>408.9599914550781</v>
+      </c>
+      <c r="F102" t="n">
+        <v>31123900</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B103" t="n">
+        <v>404.9200134277344</v>
+      </c>
+      <c r="C103" t="n">
+        <v>410.2099914550781</v>
+      </c>
+      <c r="D103" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="E103" t="n">
+        <v>409.4100036621094</v>
+      </c>
+      <c r="F103" t="n">
+        <v>30131900</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B104" t="n">
+        <v>410.0299987792969</v>
+      </c>
+      <c r="C104" t="n">
+        <v>410.2000122070312</v>
+      </c>
+      <c r="D104" t="n">
+        <v>402.9299926757812</v>
+      </c>
+      <c r="E104" t="n">
+        <v>405.760009765625</v>
+      </c>
+      <c r="F104" t="n">
+        <v>31706400</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B105" t="n">
+        <v>405.5700073242188</v>
+      </c>
+      <c r="C105" t="n">
+        <v>409.010009765625</v>
+      </c>
+      <c r="D105" t="n">
+        <v>401.5899963378906</v>
+      </c>
+      <c r="E105" t="n">
+        <v>404.8800048828125</v>
+      </c>
+      <c r="F105" t="n">
+        <v>25512100</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B106" t="n">
+        <v>404.6300048828125</v>
+      </c>
+      <c r="C106" t="n">
+        <v>406.1199951171875</v>
+      </c>
+      <c r="D106" t="n">
+        <v>401.7099914550781</v>
+      </c>
+      <c r="E106" t="n">
+        <v>401.8599853515625</v>
+      </c>
+      <c r="F106" t="n">
+        <v>27263900</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B107" t="n">
+        <v>401</v>
+      </c>
+      <c r="C107" t="n">
+        <v>404.7999877929688</v>
+      </c>
+      <c r="D107" t="n">
+        <v>394.25</v>
+      </c>
+      <c r="E107" t="n">
+        <v>395.5499877929688</v>
+      </c>
+      <c r="F107" t="n">
+        <v>26848000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B108" t="n">
+        <v>398.0700073242188</v>
+      </c>
+      <c r="C108" t="n">
+        <v>400.6300048828125</v>
+      </c>
+      <c r="D108" t="n">
+        <v>394.7900085449219</v>
+      </c>
+      <c r="E108" t="n">
+        <v>399.9500122070312</v>
+      </c>
+      <c r="F108" t="n">
+        <v>27733700</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B109" t="n">
+        <v>400.2699890136719</v>
+      </c>
+      <c r="C109" t="n">
+        <v>404.3999938964844</v>
+      </c>
+      <c r="D109" t="n">
+        <v>397.75</v>
+      </c>
+      <c r="E109" t="n">
+        <v>399.4100036621094</v>
+      </c>
+      <c r="F109" t="n">
+        <v>26228300</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B110" t="n">
+        <v>397.1300048828125</v>
+      </c>
+      <c r="C110" t="n">
+        <v>398</v>
+      </c>
+      <c r="D110" t="n">
+        <v>391</v>
+      </c>
+      <c r="E110" t="n">
+        <v>391.7900085449219</v>
+      </c>
+      <c r="F110" t="n">
+        <v>25908500</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B111" t="n">
+        <v>390.1000061035156</v>
+      </c>
+      <c r="C111" t="n">
+        <v>392.489990234375</v>
+      </c>
+      <c r="D111" t="n">
+        <v>387.0599975585938</v>
+      </c>
+      <c r="E111" t="n">
+        <v>389.0199890136719</v>
+      </c>
+      <c r="F111" t="n">
+        <v>25138800</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B112" t="n">
+        <v>386.7900085449219</v>
+      </c>
+      <c r="C112" t="n">
+        <v>387</v>
+      </c>
+      <c r="D112" t="n">
+        <v>380.1199951171875</v>
+      </c>
+      <c r="E112" t="n">
+        <v>381.8699951171875</v>
+      </c>
+      <c r="F112" t="n">
+        <v>50853200</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B113" t="n">
+        <v>383.8999938964844</v>
+      </c>
+      <c r="C113" t="n">
+        <v>387.2099914550781</v>
+      </c>
+      <c r="D113" t="n">
+        <v>381.6799926757812</v>
+      </c>
+      <c r="E113" t="n">
+        <v>383</v>
+      </c>
+      <c r="F113" t="n">
+        <v>29680100</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B114" t="n">
+        <v>382.3599853515625</v>
+      </c>
+      <c r="C114" t="n">
+        <v>382.4700012207031</v>
+      </c>
+      <c r="D114" t="n">
+        <v>371.8500061035156</v>
+      </c>
+      <c r="E114" t="n">
+        <v>372.739990234375</v>
+      </c>
+      <c r="F114" t="n">
+        <v>42733600</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B115" t="n">
+        <v>376.9200134277344</v>
+      </c>
+      <c r="C115" t="n">
+        <v>377.0599975585938</v>
+      </c>
+      <c r="D115" t="n">
+        <v>369.6300048828125</v>
+      </c>
+      <c r="E115" t="n">
+        <v>371.0400085449219</v>
+      </c>
+      <c r="F115" t="n">
+        <v>31181200</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B116" t="n">
+        <v>370.8200073242188</v>
+      </c>
+      <c r="C116" t="n">
+        <v>374.7200012207031</v>
+      </c>
+      <c r="D116" t="n">
+        <v>365.1900024414062</v>
+      </c>
+      <c r="E116" t="n">
+        <v>365.9700012207031</v>
+      </c>
+      <c r="F116" t="n">
+        <v>36836600</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B117" t="n">
+        <v>361.8999938964844</v>
+      </c>
+      <c r="C117" t="n">
+        <v>362.4500122070312</v>
+      </c>
+      <c r="D117" t="n">
+        <v>356.510009765625</v>
+      </c>
+      <c r="E117" t="n">
+        <v>356.7699890136719</v>
+      </c>
+      <c r="F117" t="n">
+        <v>37883400</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B118" t="n">
+        <v>361.8999938964844</v>
+      </c>
+      <c r="C118" t="n">
+        <v>365.3599853515625</v>
+      </c>
+      <c r="D118" t="n">
+        <v>356.2799987792969</v>
+      </c>
+      <c r="E118" t="n">
+        <v>358.9599914550781</v>
+      </c>
+      <c r="F118" t="n">
+        <v>44797000</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B119" t="n">
+        <v>364.5499877929688</v>
+      </c>
+      <c r="C119" t="n">
+        <v>372.8999938964844</v>
+      </c>
+      <c r="D119" t="n">
+        <v>363.0700073242188</v>
+      </c>
+      <c r="E119" t="n">
+        <v>370.1700134277344</v>
+      </c>
+      <c r="F119" t="n">
+        <v>45244400</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B120" t="n">
+        <v>373.489990234375</v>
+      </c>
+      <c r="C120" t="n">
+        <v>373.989990234375</v>
+      </c>
+      <c r="D120" t="n">
+        <v>368.2000122070312</v>
+      </c>
+      <c r="E120" t="n">
+        <v>369.3699951171875</v>
+      </c>
+      <c r="F120" t="n">
+        <v>29417200</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B121" t="n">
+        <v>367.2099914550781</v>
+      </c>
+      <c r="C121" t="n">
+        <v>373.6400146484375</v>
+      </c>
+      <c r="D121" t="n">
+        <v>364.1499938964844</v>
+      </c>
+      <c r="E121" t="n">
+        <v>373.4599914550781</v>
+      </c>
+      <c r="F121" t="n">
+        <v>24099100</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B122" t="n">
+        <v>373.489990234375</v>
+      </c>
+      <c r="C122" t="n">
+        <v>373.7300109863281</v>
+      </c>
+      <c r="D122" t="n">
+        <v>369.5</v>
+      </c>
+      <c r="E122" t="n">
+        <v>372.8800048828125</v>
+      </c>
+      <c r="F122" t="n">
+        <v>16095200</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B123" t="n">
+        <v>370.3450012207031</v>
+      </c>
+      <c r="C123" t="n">
+        <v>371.7799987792969</v>
+      </c>
+      <c r="D123" t="n">
+        <v>366.5700073242188</v>
+      </c>
+      <c r="E123" t="n">
+        <v>370.760009765625</v>
+      </c>
+      <c r="F123" t="n">
+        <v>11489334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F123"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
         <v>45940</v>
       </c>
       <c r="B2" t="n">
@@ -487,7 +7951,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>45943</v>
       </c>
       <c r="B3" t="n">
@@ -507,7 +7971,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>45944</v>
       </c>
       <c r="B4" t="n">
@@ -527,7 +7991,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>45945</v>
       </c>
       <c r="B5" t="n">
@@ -547,7 +8011,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>45946</v>
       </c>
       <c r="B6" t="n">
@@ -567,7 +8031,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>45947</v>
       </c>
       <c r="B7" t="n">
@@ -587,7 +8051,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>45950</v>
       </c>
       <c r="B8" t="n">
@@ -607,7 +8071,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>45951</v>
       </c>
       <c r="B9" t="n">
@@ -627,7 +8091,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>45952</v>
       </c>
       <c r="B10" t="n">
@@ -647,7 +8111,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>45953</v>
       </c>
       <c r="B11" t="n">
@@ -667,7 +8131,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>45954</v>
       </c>
       <c r="B12" t="n">
@@ -687,7 +8151,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>45957</v>
       </c>
       <c r="B13" t="n">
@@ -707,7 +8171,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>45958</v>
       </c>
       <c r="B14" t="n">
@@ -727,7 +8191,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>45959</v>
       </c>
       <c r="B15" t="n">
@@ -747,7 +8211,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>45960</v>
       </c>
       <c r="B16" t="n">
@@ -767,7 +8231,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>45961</v>
       </c>
       <c r="B17" t="n">
@@ -787,7 +8251,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>45964</v>
       </c>
       <c r="B18" t="n">
@@ -807,7 +8271,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>45965</v>
       </c>
       <c r="B19" t="n">
@@ -827,7 +8291,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>45966</v>
       </c>
       <c r="B20" t="n">
@@ -847,7 +8311,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>45967</v>
       </c>
       <c r="B21" t="n">
@@ -867,7 +8331,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>45968</v>
       </c>
       <c r="B22" t="n">
@@ -887,7 +8351,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>45971</v>
       </c>
       <c r="B23" t="n">
@@ -907,7 +8371,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>45972</v>
       </c>
       <c r="B24" t="n">
@@ -927,7 +8391,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>45973</v>
       </c>
       <c r="B25" t="n">
@@ -947,7 +8411,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>45974</v>
       </c>
       <c r="B26" t="n">
@@ -967,7 +8431,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>45975</v>
       </c>
       <c r="B27" t="n">
@@ -987,7 +8451,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>45978</v>
       </c>
       <c r="B28" t="n">
@@ -1007,7 +8471,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45979</v>
       </c>
       <c r="B29" t="n">
@@ -1027,7 +8491,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45980</v>
       </c>
       <c r="B30" t="n">
@@ -1047,7 +8511,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45981</v>
       </c>
       <c r="B31" t="n">
@@ -1067,7 +8531,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45982</v>
       </c>
       <c r="B32" t="n">
@@ -1087,7 +8551,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45985</v>
       </c>
       <c r="B33" t="n">
@@ -1107,7 +8571,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45986</v>
       </c>
       <c r="B34" t="n">
@@ -1127,7 +8591,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45987</v>
       </c>
       <c r="B35" t="n">
@@ -1147,7 +8611,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45989</v>
       </c>
       <c r="B36" t="n">
@@ -1167,7 +8631,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B37" t="n">
@@ -1187,7 +8651,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>45993</v>
       </c>
       <c r="B38" t="n">
@@ -1207,7 +8671,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>45994</v>
       </c>
       <c r="B39" t="n">
@@ -1227,7 +8691,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="B40" t="n">
@@ -1247,7 +8711,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>45996</v>
       </c>
       <c r="B41" t="n">
@@ -1267,7 +8731,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>45999</v>
       </c>
       <c r="B42" t="n">
@@ -1287,7 +8751,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>46000</v>
       </c>
       <c r="B43" t="n">
@@ -1307,7 +8771,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>46001</v>
       </c>
       <c r="B44" t="n">
@@ -1327,7 +8791,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>46002</v>
       </c>
       <c r="B45" t="n">
@@ -1347,7 +8811,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>46003</v>
       </c>
       <c r="B46" t="n">
@@ -1367,7 +8831,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>46006</v>
       </c>
       <c r="B47" t="n">
@@ -1387,7 +8851,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>46007</v>
       </c>
       <c r="B48" t="n">
@@ -1407,7 +8871,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>46008</v>
       </c>
       <c r="B49" t="n">
@@ -1427,7 +8891,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="B50" t="n">
@@ -1447,7 +8911,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>46010</v>
       </c>
       <c r="B51" t="n">
@@ -1467,7 +8931,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>46013</v>
       </c>
       <c r="B52" t="n">
@@ -1487,7 +8951,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>46014</v>
       </c>
       <c r="B53" t="n">
@@ -1507,7 +8971,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>46015</v>
       </c>
       <c r="B54" t="n">
@@ -1527,7 +8991,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>46017</v>
       </c>
       <c r="B55" t="n">
@@ -1547,7 +9011,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>46020</v>
       </c>
       <c r="B56" t="n">
@@ -1567,7 +9031,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>46021</v>
       </c>
       <c r="B57" t="n">
@@ -1587,7 +9051,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>46022</v>
       </c>
       <c r="B58" t="n">
@@ -1607,7 +9071,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>46024</v>
       </c>
       <c r="B59" t="n">
@@ -1627,7 +9091,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>46027</v>
       </c>
       <c r="B60" t="n">
@@ -1647,7 +9111,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="B61" t="n">
@@ -1667,7 +9131,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46029</v>
       </c>
       <c r="B62" t="n">
@@ -1687,7 +9151,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>46030</v>
       </c>
       <c r="B63" t="n">
@@ -1707,7 +9171,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>46031</v>
       </c>
       <c r="B64" t="n">
@@ -1727,7 +9191,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>46034</v>
       </c>
       <c r="B65" t="n">
@@ -1747,7 +9211,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>46035</v>
       </c>
       <c r="B66" t="n">
@@ -1767,7 +9231,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="B67" t="n">
@@ -1787,7 +9251,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="B68" t="n">
@@ -1807,7 +9271,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>46038</v>
       </c>
       <c r="B69" t="n">
@@ -1827,7 +9291,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>46042</v>
       </c>
       <c r="B70" t="n">
@@ -1847,7 +9311,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>46043</v>
       </c>
       <c r="B71" t="n">
@@ -1867,7 +9331,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>46044</v>
       </c>
       <c r="B72" t="n">
@@ -1887,7 +9351,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>46045</v>
       </c>
       <c r="B73" t="n">
@@ -1907,7 +9371,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>46048</v>
       </c>
       <c r="B74" t="n">
@@ -1927,7 +9391,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>46049</v>
       </c>
       <c r="B75" t="n">
@@ -1947,7 +9411,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>46050</v>
       </c>
       <c r="B76" t="n">
@@ -1967,7 +9431,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="3" t="n">
         <v>46051</v>
       </c>
       <c r="B77" t="n">
@@ -1987,7 +9451,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>46052</v>
       </c>
       <c r="B78" t="n">
@@ -2007,7 +9471,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="3" t="n">
         <v>46055</v>
       </c>
       <c r="B79" t="n">
@@ -2027,7 +9491,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="3" t="n">
         <v>46056</v>
       </c>
       <c r="B80" t="n">
@@ -2047,7 +9511,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="3" t="n">
         <v>46057</v>
       </c>
       <c r="B81" t="n">
@@ -2067,7 +9531,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="3" t="n">
         <v>46058</v>
       </c>
       <c r="B82" t="n">
@@ -2087,7 +9551,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="3" t="n">
         <v>46059</v>
       </c>
       <c r="B83" t="n">
@@ -2107,7 +9571,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="3" t="n">
         <v>46062</v>
       </c>
       <c r="B84" t="n">
@@ -2127,7 +9591,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="B85" t="n">
@@ -2147,7 +9611,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="3" t="n">
         <v>46064</v>
       </c>
       <c r="B86" t="n">
@@ -2167,7 +9631,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="3" t="n">
         <v>46065</v>
       </c>
       <c r="B87" t="n">
@@ -2187,7 +9651,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="3" t="n">
         <v>46066</v>
       </c>
       <c r="B88" t="n">
@@ -2207,7 +9671,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="3" t="n">
         <v>46070</v>
       </c>
       <c r="B89" t="n">
@@ -2227,7 +9691,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="3" t="n">
         <v>46071</v>
       </c>
       <c r="B90" t="n">
@@ -2247,7 +9711,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="3" t="n">
         <v>46072</v>
       </c>
       <c r="B91" t="n">
@@ -2267,7 +9731,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="3" t="n">
         <v>46073</v>
       </c>
       <c r="B92" t="n">
@@ -2287,7 +9751,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="3" t="n">
         <v>46076</v>
       </c>
       <c r="B93" t="n">
@@ -2307,7 +9771,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="3" t="n">
         <v>46077</v>
       </c>
       <c r="B94" t="n">
@@ -2327,7 +9791,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="3" t="n">
         <v>46078</v>
       </c>
       <c r="B95" t="n">
@@ -2347,7 +9811,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="3" t="n">
         <v>46079</v>
       </c>
       <c r="B96" t="n">
@@ -2367,7 +9831,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="3" t="n">
         <v>46080</v>
       </c>
       <c r="B97" t="n">
@@ -2387,7 +9851,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="3" t="n">
         <v>46083</v>
       </c>
       <c r="B98" t="n">
@@ -2407,7 +9871,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="3" t="n">
         <v>46084</v>
       </c>
       <c r="B99" t="n">
@@ -2427,7 +9891,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="3" t="n">
         <v>46085</v>
       </c>
       <c r="B100" t="n">
@@ -2447,7 +9911,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="3" t="n">
         <v>46086</v>
       </c>
       <c r="B101" t="n">
@@ -2467,7 +9931,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="3" t="n">
         <v>46087</v>
       </c>
       <c r="B102" t="n">
@@ -2487,7 +9951,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="3" t="n">
         <v>46090</v>
       </c>
       <c r="B103" t="n">
@@ -2507,7 +9971,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="B104" t="n">
@@ -2527,7 +9991,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="3" t="n">
         <v>46092</v>
       </c>
       <c r="B105" t="n">
@@ -2547,7 +10011,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="3" t="n">
         <v>46093</v>
       </c>
       <c r="B106" t="n">
@@ -2567,7 +10031,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="3" t="n">
         <v>46094</v>
       </c>
       <c r="B107" t="n">
@@ -2587,7 +10051,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="3" t="n">
         <v>46097</v>
       </c>
       <c r="B108" t="n">
@@ -2607,7 +10071,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="B109" t="n">
@@ -2627,7 +10091,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="3" t="n">
         <v>46099</v>
       </c>
       <c r="B110" t="n">
@@ -2647,7 +10111,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="3" t="n">
         <v>46100</v>
       </c>
       <c r="B111" t="n">
@@ -2667,7 +10131,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="3" t="n">
         <v>46101</v>
       </c>
       <c r="B112" t="n">
@@ -2687,7 +10151,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="3" t="n">
         <v>46104</v>
       </c>
       <c r="B113" t="n">
@@ -2707,7 +10171,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="3" t="n">
         <v>46105</v>
       </c>
       <c r="B114" t="n">
@@ -2727,7 +10191,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="3" t="n">
         <v>46106</v>
       </c>
       <c r="B115" t="n">
@@ -2747,7 +10211,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="3" t="n">
         <v>46107</v>
       </c>
       <c r="B116" t="n">
@@ -2767,7 +10231,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="3" t="n">
         <v>46108</v>
       </c>
       <c r="B117" t="n">
@@ -2787,7 +10251,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="3" t="n">
         <v>46111</v>
       </c>
       <c r="B118" t="n">
@@ -2807,7 +10271,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="3" t="n">
         <v>46112</v>
       </c>
       <c r="B119" t="n">
@@ -2827,7 +10291,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B120" t="n">
@@ -2847,7 +10311,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="3" t="n">
         <v>46114</v>
       </c>
       <c r="B121" t="n">
@@ -2867,7 +10331,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="3" t="n">
         <v>46118</v>
       </c>
       <c r="B122" t="n">
@@ -2887,7 +10351,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="3" t="n">
         <v>46119</v>
       </c>
       <c r="B123" t="n">
@@ -2900,10 +10364,10 @@
         <v>245.6999969482422</v>
       </c>
       <c r="E123" t="n">
-        <v>251.9600067138672</v>
+        <v>251.8099975585938</v>
       </c>
       <c r="F123" t="n">
-        <v>38630849</v>
+        <v>39764175</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data.xlsx
+++ b/stock_data.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMZN" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSFT" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10373,4 +10374,2490 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F123"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B2" t="n">
+        <v>729.6995938834806</v>
+      </c>
+      <c r="C2" t="n">
+        <v>734.0423674154782</v>
+      </c>
+      <c r="D2" t="n">
+        <v>703.333716456913</v>
+      </c>
+      <c r="E2" t="n">
+        <v>704.1223754882812</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16980100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B3" t="n">
+        <v>711.8194939498104</v>
+      </c>
+      <c r="C3" t="n">
+        <v>718.7379155876384</v>
+      </c>
+      <c r="D3" t="n">
+        <v>706.4584651360833</v>
+      </c>
+      <c r="E3" t="n">
+        <v>714.5050048828125</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9251800</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B4" t="n">
+        <v>706.598254382022</v>
+      </c>
+      <c r="C4" t="n">
+        <v>714.3552394376962</v>
+      </c>
+      <c r="D4" t="n">
+        <v>698.1623510959027</v>
+      </c>
+      <c r="E4" t="n">
+        <v>707.466796875</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8829800</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B5" t="n">
+        <v>715.8627565899488</v>
+      </c>
+      <c r="C5" t="n">
+        <v>722.6913629779451</v>
+      </c>
+      <c r="D5" t="n">
+        <v>708.3253746524584</v>
+      </c>
+      <c r="E5" t="n">
+        <v>716.3519287109375</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10246800</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B6" t="n">
+        <v>716.3519343648386</v>
+      </c>
+      <c r="C6" t="n">
+        <v>724.2786798244232</v>
+      </c>
+      <c r="D6" t="n">
+        <v>702.7047754671785</v>
+      </c>
+      <c r="E6" t="n">
+        <v>710.881103515625</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9017000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B7" t="n">
+        <v>705.8994251244851</v>
+      </c>
+      <c r="C7" t="n">
+        <v>717.3402516818879</v>
+      </c>
+      <c r="D7" t="n">
+        <v>704.9410060739878</v>
+      </c>
+      <c r="E7" t="n">
+        <v>715.7229614257812</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12232400</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B8" t="n">
+        <v>719.9858621042338</v>
+      </c>
+      <c r="C8" t="n">
+        <v>732.5448748734839</v>
+      </c>
+      <c r="D8" t="n">
+        <v>718.9775387090459</v>
+      </c>
+      <c r="E8" t="n">
+        <v>730.947509765625</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8900200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B9" t="n">
+        <v>734.7911237948646</v>
+      </c>
+      <c r="C9" t="n">
+        <v>737.2669635645257</v>
+      </c>
+      <c r="D9" t="n">
+        <v>727.5332426508437</v>
+      </c>
+      <c r="E9" t="n">
+        <v>732.0457153320312</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7647300</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B10" t="n">
+        <v>732.6047674176828</v>
+      </c>
+      <c r="C10" t="n">
+        <v>739.3634223567747</v>
+      </c>
+      <c r="D10" t="n">
+        <v>722.8211423130082</v>
+      </c>
+      <c r="E10" t="n">
+        <v>732.1854248046875</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8734500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B11" t="n">
+        <v>733.4733185275871</v>
+      </c>
+      <c r="C11" t="n">
+        <v>741.170406509876</v>
+      </c>
+      <c r="D11" t="n">
+        <v>731.8759534115667</v>
+      </c>
+      <c r="E11" t="n">
+        <v>732.7744750976562</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9856000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B12" t="n">
+        <v>735.5598112729552</v>
+      </c>
+      <c r="C12" t="n">
+        <v>739.9724753796752</v>
+      </c>
+      <c r="D12" t="n">
+        <v>729.9292742962166</v>
+      </c>
+      <c r="E12" t="n">
+        <v>737.127197265625</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9151300</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B13" t="n">
+        <v>748.4781384032651</v>
+      </c>
+      <c r="C13" t="n">
+        <v>754.4881061640369</v>
+      </c>
+      <c r="D13" t="n">
+        <v>746.7610395763271</v>
+      </c>
+      <c r="E13" t="n">
+        <v>749.5663452148438</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11321100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B14" t="n">
+        <v>751.3733793283152</v>
+      </c>
+      <c r="C14" t="n">
+        <v>757.1337649704751</v>
+      </c>
+      <c r="D14" t="n">
+        <v>744.2752651341964</v>
+      </c>
+      <c r="E14" t="n">
+        <v>750.1853637695312</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12193800</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B15" t="n">
+        <v>753.4897913670577</v>
+      </c>
+      <c r="C15" t="n">
+        <v>757.8924011644837</v>
+      </c>
+      <c r="D15" t="n">
+        <v>741.2702382858599</v>
+      </c>
+      <c r="E15" t="n">
+        <v>750.4149169921875</v>
+      </c>
+      <c r="F15" t="n">
+        <v>26818600</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B16" t="n">
+        <v>668.0328178882455</v>
+      </c>
+      <c r="C16" t="n">
+        <v>679.8230975870755</v>
+      </c>
+      <c r="D16" t="n">
+        <v>649.0844652813799</v>
+      </c>
+      <c r="E16" t="n">
+        <v>665.3572387695312</v>
+      </c>
+      <c r="F16" t="n">
+        <v>88440100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B17" t="n">
+        <v>673.383812052831</v>
+      </c>
+      <c r="C17" t="n">
+        <v>673.7631824593219</v>
+      </c>
+      <c r="D17" t="n">
+        <v>644.4921293755289</v>
+      </c>
+      <c r="E17" t="n">
+        <v>647.2674560546875</v>
+      </c>
+      <c r="F17" t="n">
+        <v>56953200</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B18" t="n">
+        <v>654.90470367213</v>
+      </c>
+      <c r="C18" t="n">
+        <v>658.2291607688485</v>
+      </c>
+      <c r="D18" t="n">
+        <v>635.1177890022415</v>
+      </c>
+      <c r="E18" t="n">
+        <v>636.645263671875</v>
+      </c>
+      <c r="F18" t="n">
+        <v>33003600</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B19" t="n">
+        <v>626.9913515895119</v>
+      </c>
+      <c r="C19" t="n">
+        <v>640.6684891460408</v>
+      </c>
+      <c r="D19" t="n">
+        <v>624.9647727272926</v>
+      </c>
+      <c r="E19" t="n">
+        <v>626.2725830078125</v>
+      </c>
+      <c r="F19" t="n">
+        <v>27356600</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B20" t="n">
+        <v>631.2542465797685</v>
+      </c>
+      <c r="C20" t="n">
+        <v>641.1576663615418</v>
+      </c>
+      <c r="D20" t="n">
+        <v>625.4938610947797</v>
+      </c>
+      <c r="E20" t="n">
+        <v>634.88818359375</v>
+      </c>
+      <c r="F20" t="n">
+        <v>20219900</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B21" t="n">
+        <v>634.7882936522686</v>
+      </c>
+      <c r="C21" t="n">
+        <v>634.938067569805</v>
+      </c>
+      <c r="D21" t="n">
+        <v>616.9681222612256</v>
+      </c>
+      <c r="E21" t="n">
+        <v>617.9065551757812</v>
+      </c>
+      <c r="F21" t="n">
+        <v>23628800</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B22" t="n">
+        <v>615.4606203242017</v>
+      </c>
+      <c r="C22" t="n">
+        <v>621.0912176885568</v>
+      </c>
+      <c r="D22" t="n">
+        <v>600.1961723842201</v>
+      </c>
+      <c r="E22" t="n">
+        <v>620.6719360351562</v>
+      </c>
+      <c r="F22" t="n">
+        <v>29946800</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B23" t="n">
+        <v>630.0363359130761</v>
+      </c>
+      <c r="C23" t="n">
+        <v>633.9397808237388</v>
+      </c>
+      <c r="D23" t="n">
+        <v>617.077966360211</v>
+      </c>
+      <c r="E23" t="n">
+        <v>630.7052001953125</v>
+      </c>
+      <c r="F23" t="n">
+        <v>19245000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B24" t="n">
+        <v>626.9514668906089</v>
+      </c>
+      <c r="C24" t="n">
+        <v>628.5088598168925</v>
+      </c>
+      <c r="D24" t="n">
+        <v>618.3558571038752</v>
+      </c>
+      <c r="E24" t="n">
+        <v>626.0330200195312</v>
+      </c>
+      <c r="F24" t="n">
+        <v>13302200</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B25" t="n">
+        <v>627.0812350986922</v>
+      </c>
+      <c r="C25" t="n">
+        <v>627.939784558569</v>
+      </c>
+      <c r="D25" t="n">
+        <v>606.7552442025384</v>
+      </c>
+      <c r="E25" t="n">
+        <v>607.9931640625</v>
+      </c>
+      <c r="F25" t="n">
+        <v>24493300</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B26" t="n">
+        <v>612.0463872625083</v>
+      </c>
+      <c r="C26" t="n">
+        <v>616.6187572691151</v>
+      </c>
+      <c r="D26" t="n">
+        <v>601.993193452889</v>
+      </c>
+      <c r="E26" t="n">
+        <v>608.8717041015625</v>
+      </c>
+      <c r="F26" t="n">
+        <v>20973800</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B27" t="n">
+        <v>600.7852061056304</v>
+      </c>
+      <c r="C27" t="n">
+        <v>612.6553687237855</v>
+      </c>
+      <c r="D27" t="n">
+        <v>594.2062431482154</v>
+      </c>
+      <c r="E27" t="n">
+        <v>608.4424438476562</v>
+      </c>
+      <c r="F27" t="n">
+        <v>20724100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B28" t="n">
+        <v>608.0230519623859</v>
+      </c>
+      <c r="C28" t="n">
+        <v>610.6686515784111</v>
+      </c>
+      <c r="D28" t="n">
+        <v>594.4058732487083</v>
+      </c>
+      <c r="E28" t="n">
+        <v>601.0048217773438</v>
+      </c>
+      <c r="F28" t="n">
+        <v>16501300</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B29" t="n">
+        <v>590.612218909938</v>
+      </c>
+      <c r="C29" t="n">
+        <v>602.6520806612418</v>
+      </c>
+      <c r="D29" t="n">
+        <v>582.8053290854997</v>
+      </c>
+      <c r="E29" t="n">
+        <v>596.6920776367188</v>
+      </c>
+      <c r="F29" t="n">
+        <v>25500600</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B30" t="n">
+        <v>592.7286370493186</v>
+      </c>
+      <c r="C30" t="n">
+        <v>594.3359951431619</v>
+      </c>
+      <c r="D30" t="n">
+        <v>580.2794874440681</v>
+      </c>
+      <c r="E30" t="n">
+        <v>589.3343505859375</v>
+      </c>
+      <c r="F30" t="n">
+        <v>24744700</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B31" t="n">
+        <v>602.4923362369276</v>
+      </c>
+      <c r="C31" t="n">
+        <v>605.706930555967</v>
+      </c>
+      <c r="D31" t="n">
+        <v>582.375956312388</v>
+      </c>
+      <c r="E31" t="n">
+        <v>588.1663208007812</v>
+      </c>
+      <c r="F31" t="n">
+        <v>20603000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B32" t="n">
+        <v>587.517412968027</v>
+      </c>
+      <c r="C32" t="n">
+        <v>597.1213460929463</v>
+      </c>
+      <c r="D32" t="n">
+        <v>580.88848479756</v>
+      </c>
+      <c r="E32" t="n">
+        <v>593.2578125</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21052600</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B33" t="n">
+        <v>597.7203367937327</v>
+      </c>
+      <c r="C33" t="n">
+        <v>615.6703584886146</v>
+      </c>
+      <c r="D33" t="n">
+        <v>596.6321908004635</v>
+      </c>
+      <c r="E33" t="n">
+        <v>612.0264282226562</v>
+      </c>
+      <c r="F33" t="n">
+        <v>23554900</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B34" t="n">
+        <v>622.9580871825591</v>
+      </c>
+      <c r="C34" t="n">
+        <v>635.9862849922763</v>
+      </c>
+      <c r="D34" t="n">
+        <v>617.2675924687619</v>
+      </c>
+      <c r="E34" t="n">
+        <v>635.1576538085938</v>
+      </c>
+      <c r="F34" t="n">
+        <v>25213000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B35" t="n">
+        <v>636.6252677780955</v>
+      </c>
+      <c r="C35" t="n">
+        <v>637.2941320349476</v>
+      </c>
+      <c r="D35" t="n">
+        <v>630.5753884422047</v>
+      </c>
+      <c r="E35" t="n">
+        <v>632.5520629882812</v>
+      </c>
+      <c r="F35" t="n">
+        <v>15209500</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B36" t="n">
+        <v>635.0179876534709</v>
+      </c>
+      <c r="C36" t="n">
+        <v>646.9679727244463</v>
+      </c>
+      <c r="D36" t="n">
+        <v>634.4389389877349</v>
+      </c>
+      <c r="E36" t="n">
+        <v>646.8681640625</v>
+      </c>
+      <c r="F36" t="n">
+        <v>11033200</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B37" t="n">
+        <v>638.4821234657416</v>
+      </c>
+      <c r="C37" t="n">
+        <v>644.2425087257971</v>
+      </c>
+      <c r="D37" t="n">
+        <v>636.6951341862962</v>
+      </c>
+      <c r="E37" t="n">
+        <v>639.7999267578125</v>
+      </c>
+      <c r="F37" t="n">
+        <v>13029900</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B38" t="n">
+        <v>641.2675300698932</v>
+      </c>
+      <c r="C38" t="n">
+        <v>646.7882651016448</v>
+      </c>
+      <c r="D38" t="n">
+        <v>637.0046400682228</v>
+      </c>
+      <c r="E38" t="n">
+        <v>646.01953125</v>
+      </c>
+      <c r="F38" t="n">
+        <v>11640900</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B39" t="n">
+        <v>643.3340098224904</v>
+      </c>
+      <c r="C39" t="n">
+        <v>647.7665988470103</v>
+      </c>
+      <c r="D39" t="n">
+        <v>636.4854785031988</v>
+      </c>
+      <c r="E39" t="n">
+        <v>638.5320434570312</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11134300</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B40" t="n">
+        <v>674.87134871331</v>
+      </c>
+      <c r="C40" t="n">
+        <v>674.9711573797597</v>
+      </c>
+      <c r="D40" t="n">
+        <v>658.9479666864565</v>
+      </c>
+      <c r="E40" t="n">
+        <v>660.425537109375</v>
+      </c>
+      <c r="F40" t="n">
+        <v>29874600</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B41" t="n">
+        <v>662.8913386215002</v>
+      </c>
+      <c r="C41" t="n">
+        <v>673.5634922785046</v>
+      </c>
+      <c r="D41" t="n">
+        <v>661.2840414153883</v>
+      </c>
+      <c r="E41" t="n">
+        <v>672.2955932617188</v>
+      </c>
+      <c r="F41" t="n">
+        <v>21207900</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B42" t="n">
+        <v>668.2224435191038</v>
+      </c>
+      <c r="C42" t="n">
+        <v>675.5801331063639</v>
+      </c>
+      <c r="D42" t="n">
+        <v>663.9595535520253</v>
+      </c>
+      <c r="E42" t="n">
+        <v>665.6866455078125</v>
+      </c>
+      <c r="F42" t="n">
+        <v>13161000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B43" t="n">
+        <v>662.6617867420982</v>
+      </c>
+      <c r="C43" t="n">
+        <v>663.3705623262879</v>
+      </c>
+      <c r="D43" t="n">
+        <v>652.2492080192432</v>
+      </c>
+      <c r="E43" t="n">
+        <v>655.8631591796875</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12997100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B44" t="n">
+        <v>648.8648024836247</v>
+      </c>
+      <c r="C44" t="n">
+        <v>653.4171862971667</v>
+      </c>
+      <c r="D44" t="n">
+        <v>642.3257510862366</v>
+      </c>
+      <c r="E44" t="n">
+        <v>649.0444946289062</v>
+      </c>
+      <c r="F44" t="n">
+        <v>16910900</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B45" t="n">
+        <v>642.2158631242634</v>
+      </c>
+      <c r="C45" t="n">
+        <v>654.1858943512054</v>
+      </c>
+      <c r="D45" t="n">
+        <v>639.730030479328</v>
+      </c>
+      <c r="E45" t="n">
+        <v>651.6201782226562</v>
+      </c>
+      <c r="F45" t="n">
+        <v>13056700</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B46" t="n">
+        <v>648.7150654102267</v>
+      </c>
+      <c r="C46" t="n">
+        <v>709.8128965395189</v>
+      </c>
+      <c r="D46" t="n">
+        <v>637.543746077992</v>
+      </c>
+      <c r="E46" t="n">
+        <v>643.1543579101562</v>
+      </c>
+      <c r="F46" t="n">
+        <v>14016900</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B47" t="n">
+        <v>645.1476664750544</v>
+      </c>
+      <c r="C47" t="n">
+        <v>652.4414097008485</v>
+      </c>
+      <c r="D47" t="n">
+        <v>638.1536544261938</v>
+      </c>
+      <c r="E47" t="n">
+        <v>646.9561157226562</v>
+      </c>
+      <c r="F47" t="n">
+        <v>15549100</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B48" t="n">
+        <v>642.9495426008936</v>
+      </c>
+      <c r="C48" t="n">
+        <v>661.973233609148</v>
+      </c>
+      <c r="D48" t="n">
+        <v>642.6498114209788</v>
+      </c>
+      <c r="E48" t="n">
+        <v>656.587890625</v>
+      </c>
+      <c r="F48" t="n">
+        <v>14309100</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B49" t="n">
+        <v>655.0491556477624</v>
+      </c>
+      <c r="C49" t="n">
+        <v>660.664343241777</v>
+      </c>
+      <c r="D49" t="n">
+        <v>648.644665798819</v>
+      </c>
+      <c r="E49" t="n">
+        <v>648.9443969726562</v>
+      </c>
+      <c r="F49" t="n">
+        <v>15598500</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B50" t="n">
+        <v>656.4679564970005</v>
+      </c>
+      <c r="C50" t="n">
+        <v>669.9863502083882</v>
+      </c>
+      <c r="D50" t="n">
+        <v>655.8984367998282</v>
+      </c>
+      <c r="E50" t="n">
+        <v>663.881591796875</v>
+      </c>
+      <c r="F50" t="n">
+        <v>20260300</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B51" t="n">
+        <v>665.8499012351181</v>
+      </c>
+      <c r="C51" t="n">
+        <v>670.4260003995075</v>
+      </c>
+      <c r="D51" t="n">
+        <v>657.6169598101359</v>
+      </c>
+      <c r="E51" t="n">
+        <v>658.2064819335938</v>
+      </c>
+      <c r="F51" t="n">
+        <v>49977100</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B52" t="n">
+        <v>661.0840391473547</v>
+      </c>
+      <c r="C52" t="n">
+        <v>673.0038267300547</v>
+      </c>
+      <c r="D52" t="n">
+        <v>656.0883162216827</v>
+      </c>
+      <c r="E52" t="n">
+        <v>660.9341430664062</v>
+      </c>
+      <c r="F52" t="n">
+        <v>15659400</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B53" t="n">
+        <v>659.4853234816244</v>
+      </c>
+      <c r="C53" t="n">
+        <v>665.4302455294139</v>
+      </c>
+      <c r="D53" t="n">
+        <v>657.6868755551602</v>
+      </c>
+      <c r="E53" t="n">
+        <v>664.3711547851562</v>
+      </c>
+      <c r="F53" t="n">
+        <v>8486800</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B54" t="n">
+        <v>661.9632786179176</v>
+      </c>
+      <c r="C54" t="n">
+        <v>667.6084088263418</v>
+      </c>
+      <c r="D54" t="n">
+        <v>661.633543835896</v>
+      </c>
+      <c r="E54" t="n">
+        <v>666.9789428710938</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5627500</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B55" t="n">
+        <v>667.4885344385556</v>
+      </c>
+      <c r="C55" t="n">
+        <v>668.3777877623371</v>
+      </c>
+      <c r="D55" t="n">
+        <v>660.7543096382171</v>
+      </c>
+      <c r="E55" t="n">
+        <v>662.7225952148438</v>
+      </c>
+      <c r="F55" t="n">
+        <v>7133800</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B56" t="n">
+        <v>657.4471149030659</v>
+      </c>
+      <c r="C56" t="n">
+        <v>659.6851889371151</v>
+      </c>
+      <c r="D56" t="n">
+        <v>653.8302165118</v>
+      </c>
+      <c r="E56" t="n">
+        <v>658.1265258789062</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8506500</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B57" t="n">
+        <v>658.1265110341435</v>
+      </c>
+      <c r="C57" t="n">
+        <v>671.6449047754843</v>
+      </c>
+      <c r="D57" t="n">
+        <v>657.2772625792347</v>
+      </c>
+      <c r="E57" t="n">
+        <v>665.3803100585938</v>
+      </c>
+      <c r="F57" t="n">
+        <v>9187500</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B58" t="n">
+        <v>664.1813161961976</v>
+      </c>
+      <c r="C58" t="n">
+        <v>664.4311023248911</v>
+      </c>
+      <c r="D58" t="n">
+        <v>658.8758612620638</v>
+      </c>
+      <c r="E58" t="n">
+        <v>659.5253295898438</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7940400</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B59" t="n">
+        <v>662.1630447721155</v>
+      </c>
+      <c r="C59" t="n">
+        <v>663.8216588672108</v>
+      </c>
+      <c r="D59" t="n">
+        <v>642.9495146869224</v>
+      </c>
+      <c r="E59" t="n">
+        <v>649.8535766601562</v>
+      </c>
+      <c r="F59" t="n">
+        <v>13726500</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B60" t="n">
+        <v>650.4531272549772</v>
+      </c>
+      <c r="C60" t="n">
+        <v>663.9715218041853</v>
+      </c>
+      <c r="D60" t="n">
+        <v>647.1959061445123</v>
+      </c>
+      <c r="E60" t="n">
+        <v>658.2264404296875</v>
+      </c>
+      <c r="F60" t="n">
+        <v>12213700</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B61" t="n">
+        <v>659.0057810200069</v>
+      </c>
+      <c r="C61" t="n">
+        <v>664.9507033148827</v>
+      </c>
+      <c r="D61" t="n">
+        <v>651.3423593634897</v>
+      </c>
+      <c r="E61" t="n">
+        <v>660.0548706054688</v>
+      </c>
+      <c r="F61" t="n">
+        <v>11074400</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B62" t="n">
+        <v>655.0791375151089</v>
+      </c>
+      <c r="C62" t="n">
+        <v>658.5861445899717</v>
+      </c>
+      <c r="D62" t="n">
+        <v>644.2583851266311</v>
+      </c>
+      <c r="E62" t="n">
+        <v>648.1350708007812</v>
+      </c>
+      <c r="F62" t="n">
+        <v>12846300</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B63" t="n">
+        <v>645.3274855180696</v>
+      </c>
+      <c r="C63" t="n">
+        <v>646.5464125947736</v>
+      </c>
+      <c r="D63" t="n">
+        <v>635.1761427603</v>
+      </c>
+      <c r="E63" t="n">
+        <v>645.50732421875</v>
+      </c>
+      <c r="F63" t="n">
+        <v>11921700</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B64" t="n">
+        <v>644.8878661181845</v>
+      </c>
+      <c r="C64" t="n">
+        <v>654.3897406244424</v>
+      </c>
+      <c r="D64" t="n">
+        <v>642.3000548798136</v>
+      </c>
+      <c r="E64" t="n">
+        <v>652.5013427734375</v>
+      </c>
+      <c r="F64" t="n">
+        <v>11634900</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B65" t="n">
+        <v>651.9718010113269</v>
+      </c>
+      <c r="C65" t="n">
+        <v>653.4105105723186</v>
+      </c>
+      <c r="D65" t="n">
+        <v>640.6814191818085</v>
+      </c>
+      <c r="E65" t="n">
+        <v>641.4207763671875</v>
+      </c>
+      <c r="F65" t="n">
+        <v>14797200</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B66" t="n">
+        <v>641.720599826752</v>
+      </c>
+      <c r="C66" t="n">
+        <v>641.720599826752</v>
+      </c>
+      <c r="D66" t="n">
+        <v>623.5660991574318</v>
+      </c>
+      <c r="E66" t="n">
+        <v>630.5501708984375</v>
+      </c>
+      <c r="F66" t="n">
+        <v>18030400</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B67" t="n">
+        <v>625.9640568168747</v>
+      </c>
+      <c r="C67" t="n">
+        <v>627.9124008742662</v>
+      </c>
+      <c r="D67" t="n">
+        <v>614.2940558608916</v>
+      </c>
+      <c r="E67" t="n">
+        <v>614.9934692382812</v>
+      </c>
+      <c r="F67" t="n">
+        <v>15527900</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B68" t="n">
+        <v>617.9508982377323</v>
+      </c>
+      <c r="C68" t="n">
+        <v>623.6360331340583</v>
+      </c>
+      <c r="D68" t="n">
+        <v>613.7045339245012</v>
+      </c>
+      <c r="E68" t="n">
+        <v>620.2689208984375</v>
+      </c>
+      <c r="F68" t="n">
+        <v>13076100</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B69" t="n">
+        <v>623.6460522405506</v>
+      </c>
+      <c r="C69" t="n">
+        <v>628.5418850412981</v>
+      </c>
+      <c r="D69" t="n">
+        <v>619.5495838845379</v>
+      </c>
+      <c r="E69" t="n">
+        <v>619.7194213867188</v>
+      </c>
+      <c r="F69" t="n">
+        <v>17012500</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B70" t="n">
+        <v>607.3600037753715</v>
+      </c>
+      <c r="C70" t="n">
+        <v>610.8770121629093</v>
+      </c>
+      <c r="D70" t="n">
+        <v>599.4867397151437</v>
+      </c>
+      <c r="E70" t="n">
+        <v>603.6032104492188</v>
+      </c>
+      <c r="F70" t="n">
+        <v>15169600</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B71" t="n">
+        <v>606.2209580964126</v>
+      </c>
+      <c r="C71" t="n">
+        <v>617.7411240978843</v>
+      </c>
+      <c r="D71" t="n">
+        <v>599.5666821865381</v>
+      </c>
+      <c r="E71" t="n">
+        <v>612.4356689453125</v>
+      </c>
+      <c r="F71" t="n">
+        <v>14494700</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B72" t="n">
+        <v>628.811597152667</v>
+      </c>
+      <c r="C72" t="n">
+        <v>660.0049216653568</v>
+      </c>
+      <c r="D72" t="n">
+        <v>626.0140046136898</v>
+      </c>
+      <c r="E72" t="n">
+        <v>647.0759887695312</v>
+      </c>
+      <c r="F72" t="n">
+        <v>21394700</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B73" t="n">
+        <v>644.2184496993522</v>
+      </c>
+      <c r="C73" t="n">
+        <v>665.9198400091174</v>
+      </c>
+      <c r="D73" t="n">
+        <v>643.8987161260534</v>
+      </c>
+      <c r="E73" t="n">
+        <v>658.1964721679688</v>
+      </c>
+      <c r="F73" t="n">
+        <v>22797700</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B74" t="n">
+        <v>664.5609947255355</v>
+      </c>
+      <c r="C74" t="n">
+        <v>674.7023359243682</v>
+      </c>
+      <c r="D74" t="n">
+        <v>660.7242529636108</v>
+      </c>
+      <c r="E74" t="n">
+        <v>671.7847900390625</v>
+      </c>
+      <c r="F74" t="n">
+        <v>16327400</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B75" t="n">
+        <v>674.0129574053085</v>
+      </c>
+      <c r="C75" t="n">
+        <v>676.2410302656567</v>
+      </c>
+      <c r="D75" t="n">
+        <v>664.0913982323968</v>
+      </c>
+      <c r="E75" t="n">
+        <v>672.394287109375</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13297400</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B76" t="n">
+        <v>673.9229813666298</v>
+      </c>
+      <c r="C76" t="n">
+        <v>677.1002536346601</v>
+      </c>
+      <c r="D76" t="n">
+        <v>665.5301429727417</v>
+      </c>
+      <c r="E76" t="n">
+        <v>668.1578979492188</v>
+      </c>
+      <c r="F76" t="n">
+        <v>25709600</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B77" t="n">
+        <v>736.7991536844581</v>
+      </c>
+      <c r="C77" t="n">
+        <v>743.363540655783</v>
+      </c>
+      <c r="D77" t="n">
+        <v>711.9404325537852</v>
+      </c>
+      <c r="E77" t="n">
+        <v>737.6784057617188</v>
+      </c>
+      <c r="F77" t="n">
+        <v>59852900</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B78" t="n">
+        <v>726.8776752394725</v>
+      </c>
+      <c r="C78" t="n">
+        <v>731.5436633097714</v>
+      </c>
+      <c r="D78" t="n">
+        <v>712.9796010924755</v>
+      </c>
+      <c r="E78" t="n">
+        <v>715.8870849609375</v>
+      </c>
+      <c r="F78" t="n">
+        <v>23744600</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B79" t="n">
+        <v>713.9886602426056</v>
+      </c>
+      <c r="C79" t="n">
+        <v>720.6829408229889</v>
+      </c>
+      <c r="D79" t="n">
+        <v>702.9181827036907</v>
+      </c>
+      <c r="E79" t="n">
+        <v>705.8056640625</v>
+      </c>
+      <c r="F79" t="n">
+        <v>14365200</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B80" t="n">
+        <v>706.7648539132639</v>
+      </c>
+      <c r="C80" t="n">
+        <v>716.3866205151361</v>
+      </c>
+      <c r="D80" t="n">
+        <v>685.8227628297016</v>
+      </c>
+      <c r="E80" t="n">
+        <v>691.1082763671875</v>
+      </c>
+      <c r="F80" t="n">
+        <v>13760700</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B81" t="n">
+        <v>687.1416843315144</v>
+      </c>
+      <c r="C81" t="n">
+        <v>688.2407799622291</v>
+      </c>
+      <c r="D81" t="n">
+        <v>666.8890651090074</v>
+      </c>
+      <c r="E81" t="n">
+        <v>668.417724609375</v>
+      </c>
+      <c r="F81" t="n">
+        <v>16882800</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B82" t="n">
+        <v>663.0123852284637</v>
+      </c>
+      <c r="C82" t="n">
+        <v>680.9170392363125</v>
+      </c>
+      <c r="D82" t="n">
+        <v>652.9409906690098</v>
+      </c>
+      <c r="E82" t="n">
+        <v>669.63671875</v>
+      </c>
+      <c r="F82" t="n">
+        <v>17131800</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B83" t="n">
+        <v>664.920685797671</v>
+      </c>
+      <c r="C83" t="n">
+        <v>671.4151252649915</v>
+      </c>
+      <c r="D83" t="n">
+        <v>645.9469408650316</v>
+      </c>
+      <c r="E83" t="n">
+        <v>660.8941650390625</v>
+      </c>
+      <c r="F83" t="n">
+        <v>18159300</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B84" t="n">
+        <v>662.6126578425271</v>
+      </c>
+      <c r="C84" t="n">
+        <v>682.7254419812133</v>
+      </c>
+      <c r="D84" t="n">
+        <v>658.2164585284562</v>
+      </c>
+      <c r="E84" t="n">
+        <v>676.640625</v>
+      </c>
+      <c r="F84" t="n">
+        <v>14837500</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B85" t="n">
+        <v>677.0202983345941</v>
+      </c>
+      <c r="C85" t="n">
+        <v>680.0677378888336</v>
+      </c>
+      <c r="D85" t="n">
+        <v>669.216982119095</v>
+      </c>
+      <c r="E85" t="n">
+        <v>670.1461791992188</v>
+      </c>
+      <c r="F85" t="n">
+        <v>10455800</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B86" t="n">
+        <v>673.4234361526849</v>
+      </c>
+      <c r="C86" t="n">
+        <v>678.6889475196376</v>
+      </c>
+      <c r="D86" t="n">
+        <v>656.5378686274887</v>
+      </c>
+      <c r="E86" t="n">
+        <v>668.1179809570312</v>
+      </c>
+      <c r="F86" t="n">
+        <v>14323800</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B87" t="n">
+        <v>669.3968787035581</v>
+      </c>
+      <c r="C87" t="n">
+        <v>675.421749916193</v>
+      </c>
+      <c r="D87" t="n">
+        <v>644.7280570616384</v>
+      </c>
+      <c r="E87" t="n">
+        <v>649.254150390625</v>
+      </c>
+      <c r="F87" t="n">
+        <v>14960100</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B88" t="n">
+        <v>644.5481137374378</v>
+      </c>
+      <c r="C88" t="n">
+        <v>650.872715705495</v>
+      </c>
+      <c r="D88" t="n">
+        <v>634.0271535178357</v>
+      </c>
+      <c r="E88" t="n">
+        <v>639.2227172851562</v>
+      </c>
+      <c r="F88" t="n">
+        <v>12336400</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B89" t="n">
+        <v>638.952945338547</v>
+      </c>
+      <c r="C89" t="n">
+        <v>642.0502690775812</v>
+      </c>
+      <c r="D89" t="n">
+        <v>628.2620863630333</v>
+      </c>
+      <c r="E89" t="n">
+        <v>638.7431030273438</v>
+      </c>
+      <c r="F89" t="n">
+        <v>12674700</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B90" t="n">
+        <v>633.2578140286595</v>
+      </c>
+      <c r="C90" t="n">
+        <v>644.4482453696517</v>
+      </c>
+      <c r="D90" t="n">
+        <v>627.6126838179015</v>
+      </c>
+      <c r="E90" t="n">
+        <v>642.6697387695312</v>
+      </c>
+      <c r="F90" t="n">
+        <v>14649200</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B91" t="n">
+        <v>638.0237449576674</v>
+      </c>
+      <c r="C91" t="n">
+        <v>646.6363661317032</v>
+      </c>
+      <c r="D91" t="n">
+        <v>636.1752909436037</v>
+      </c>
+      <c r="E91" t="n">
+        <v>644.2284545898438</v>
+      </c>
+      <c r="F91" t="n">
+        <v>10035700</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B92" t="n">
+        <v>639.1428111159805</v>
+      </c>
+      <c r="C92" t="n">
+        <v>662.7825455010891</v>
+      </c>
+      <c r="D92" t="n">
+        <v>638.2336163631846</v>
+      </c>
+      <c r="E92" t="n">
+        <v>655.09912109375</v>
+      </c>
+      <c r="F92" t="n">
+        <v>14183500</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B93" t="n">
+        <v>651.9817939677475</v>
+      </c>
+      <c r="C93" t="n">
+        <v>657.1374142434245</v>
+      </c>
+      <c r="D93" t="n">
+        <v>635.455964272141</v>
+      </c>
+      <c r="E93" t="n">
+        <v>636.7048950195312</v>
+      </c>
+      <c r="F93" t="n">
+        <v>8605900</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B94" t="n">
+        <v>632.5384628258726</v>
+      </c>
+      <c r="C94" t="n">
+        <v>640.5615620292823</v>
+      </c>
+      <c r="D94" t="n">
+        <v>628.4419334902003</v>
+      </c>
+      <c r="E94" t="n">
+        <v>638.7531127929688</v>
+      </c>
+      <c r="F94" t="n">
+        <v>10135600</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B95" t="n">
+        <v>641.9803720795121</v>
+      </c>
+      <c r="C95" t="n">
+        <v>653.3206382422114</v>
+      </c>
+      <c r="D95" t="n">
+        <v>641.5906910720822</v>
+      </c>
+      <c r="E95" t="n">
+        <v>653.1307983398438</v>
+      </c>
+      <c r="F95" t="n">
+        <v>11330700</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B96" t="n">
+        <v>649.9935020296807</v>
+      </c>
+      <c r="C96" t="n">
+        <v>660.4345752110744</v>
+      </c>
+      <c r="D96" t="n">
+        <v>646.9461232211356</v>
+      </c>
+      <c r="E96" t="n">
+        <v>656.447998046875</v>
+      </c>
+      <c r="F96" t="n">
+        <v>10637700</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B97" t="n">
+        <v>642.8995542116262</v>
+      </c>
+      <c r="C97" t="n">
+        <v>648.8844201349368</v>
+      </c>
+      <c r="D97" t="n">
+        <v>637.5740968396581</v>
+      </c>
+      <c r="E97" t="n">
+        <v>647.62548828125</v>
+      </c>
+      <c r="F97" t="n">
+        <v>15703000</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B98" t="n">
+        <v>636.6149203669017</v>
+      </c>
+      <c r="C98" t="n">
+        <v>659.3754626922687</v>
+      </c>
+      <c r="D98" t="n">
+        <v>633.9572226725116</v>
+      </c>
+      <c r="E98" t="n">
+        <v>653.0009155273438</v>
+      </c>
+      <c r="F98" t="n">
+        <v>9816100</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B99" t="n">
+        <v>647.7354225434952</v>
+      </c>
+      <c r="C99" t="n">
+        <v>658.4762268569145</v>
+      </c>
+      <c r="D99" t="n">
+        <v>638.2935549799161</v>
+      </c>
+      <c r="E99" t="n">
+        <v>654.5196533203125</v>
+      </c>
+      <c r="F99" t="n">
+        <v>12263800</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B100" t="n">
+        <v>657.397151925757</v>
+      </c>
+      <c r="C100" t="n">
+        <v>672.1944798634893</v>
+      </c>
+      <c r="D100" t="n">
+        <v>657.1073609851721</v>
+      </c>
+      <c r="E100" t="n">
+        <v>667.1587524414062</v>
+      </c>
+      <c r="F100" t="n">
+        <v>10810100</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B101" t="n">
+        <v>661.363765843265</v>
+      </c>
+      <c r="C101" t="n">
+        <v>670.1262833419206</v>
+      </c>
+      <c r="D101" t="n">
+        <v>649.7537106790966</v>
+      </c>
+      <c r="E101" t="n">
+        <v>660.0049438476562</v>
+      </c>
+      <c r="F101" t="n">
+        <v>13341400</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B102" t="n">
+        <v>647.3457881163396</v>
+      </c>
+      <c r="C102" t="n">
+        <v>648.9143914185428</v>
+      </c>
+      <c r="D102" t="n">
+        <v>635.5658346648192</v>
+      </c>
+      <c r="E102" t="n">
+        <v>644.308349609375</v>
+      </c>
+      <c r="F102" t="n">
+        <v>13159400</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B103" t="n">
+        <v>634.2369839533108</v>
+      </c>
+      <c r="C103" t="n">
+        <v>647.195859029807</v>
+      </c>
+      <c r="D103" t="n">
+        <v>626.2438278402449</v>
+      </c>
+      <c r="E103" t="n">
+        <v>646.836181640625</v>
+      </c>
+      <c r="F103" t="n">
+        <v>13489700</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B104" t="n">
+        <v>653.0009245574777</v>
+      </c>
+      <c r="C104" t="n">
+        <v>659.7351492208539</v>
+      </c>
+      <c r="D104" t="n">
+        <v>648.444827744844</v>
+      </c>
+      <c r="E104" t="n">
+        <v>653.510498046875</v>
+      </c>
+      <c r="F104" t="n">
+        <v>9859300</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B105" t="n">
+        <v>654.1999146227295</v>
+      </c>
+      <c r="C105" t="n">
+        <v>658.5561703533895</v>
+      </c>
+      <c r="D105" t="n">
+        <v>647.8053649208291</v>
+      </c>
+      <c r="E105" t="n">
+        <v>654.2998046875</v>
+      </c>
+      <c r="F105" t="n">
+        <v>8977200</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B106" t="n">
+        <v>648.1950599902964</v>
+      </c>
+      <c r="C106" t="n">
+        <v>652.9409968457168</v>
+      </c>
+      <c r="D106" t="n">
+        <v>636.355220859953</v>
+      </c>
+      <c r="E106" t="n">
+        <v>637.6340942382812</v>
+      </c>
+      <c r="F106" t="n">
+        <v>11617500</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B107" t="n">
+        <v>623.3562813254467</v>
+      </c>
+      <c r="C107" t="n">
+        <v>628.6317326131165</v>
+      </c>
+      <c r="D107" t="n">
+        <v>609.0285222575777</v>
+      </c>
+      <c r="E107" t="n">
+        <v>613.1849975585938</v>
+      </c>
+      <c r="F107" t="n">
+        <v>18957600</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B108" t="n">
+        <v>632</v>
+      </c>
+      <c r="C108" t="n">
+        <v>634.75</v>
+      </c>
+      <c r="D108" t="n">
+        <v>623.0999755859375</v>
+      </c>
+      <c r="E108" t="n">
+        <v>627.4500122070312</v>
+      </c>
+      <c r="F108" t="n">
+        <v>15134900</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B109" t="n">
+        <v>627.989990234375</v>
+      </c>
+      <c r="C109" t="n">
+        <v>636.5499877929688</v>
+      </c>
+      <c r="D109" t="n">
+        <v>621.7000122070312</v>
+      </c>
+      <c r="E109" t="n">
+        <v>622.6599731445312</v>
+      </c>
+      <c r="F109" t="n">
+        <v>10348800</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B110" t="n">
+        <v>616.3400268554688</v>
+      </c>
+      <c r="C110" t="n">
+        <v>622.6500244140625</v>
+      </c>
+      <c r="D110" t="n">
+        <v>614.6099853515625</v>
+      </c>
+      <c r="E110" t="n">
+        <v>615.6799926757812</v>
+      </c>
+      <c r="F110" t="n">
+        <v>11726300</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B111" t="n">
+        <v>612.1500244140625</v>
+      </c>
+      <c r="C111" t="n">
+        <v>613</v>
+      </c>
+      <c r="D111" t="n">
+        <v>602.260009765625</v>
+      </c>
+      <c r="E111" t="n">
+        <v>606.7000122070312</v>
+      </c>
+      <c r="F111" t="n">
+        <v>13247700</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B112" t="n">
+        <v>603.530029296875</v>
+      </c>
+      <c r="C112" t="n">
+        <v>603.9600219726562</v>
+      </c>
+      <c r="D112" t="n">
+        <v>587.25</v>
+      </c>
+      <c r="E112" t="n">
+        <v>593.6599731445312</v>
+      </c>
+      <c r="F112" t="n">
+        <v>21214900</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B113" t="n">
+        <v>605.7899780273438</v>
+      </c>
+      <c r="C113" t="n">
+        <v>608.6400146484375</v>
+      </c>
+      <c r="D113" t="n">
+        <v>599.010009765625</v>
+      </c>
+      <c r="E113" t="n">
+        <v>604.0599975585938</v>
+      </c>
+      <c r="F113" t="n">
+        <v>13638000</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B114" t="n">
+        <v>599.0999755859375</v>
+      </c>
+      <c r="C114" t="n">
+        <v>601</v>
+      </c>
+      <c r="D114" t="n">
+        <v>591</v>
+      </c>
+      <c r="E114" t="n">
+        <v>592.9199829101562</v>
+      </c>
+      <c r="F114" t="n">
+        <v>10739700</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B115" t="n">
+        <v>598.739990234375</v>
+      </c>
+      <c r="C115" t="n">
+        <v>603.6699829101562</v>
+      </c>
+      <c r="D115" t="n">
+        <v>593.4000244140625</v>
+      </c>
+      <c r="E115" t="n">
+        <v>594.8900146484375</v>
+      </c>
+      <c r="F115" t="n">
+        <v>12585000</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B116" t="n">
+        <v>582.489990234375</v>
+      </c>
+      <c r="C116" t="n">
+        <v>583</v>
+      </c>
+      <c r="D116" t="n">
+        <v>543.3499755859375</v>
+      </c>
+      <c r="E116" t="n">
+        <v>547.5399780273438</v>
+      </c>
+      <c r="F116" t="n">
+        <v>35780100</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B117" t="n">
+        <v>540.0999755859375</v>
+      </c>
+      <c r="C117" t="n">
+        <v>543.5999755859375</v>
+      </c>
+      <c r="D117" t="n">
+        <v>520.260009765625</v>
+      </c>
+      <c r="E117" t="n">
+        <v>525.719970703125</v>
+      </c>
+      <c r="F117" t="n">
+        <v>30133000</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B118" t="n">
+        <v>536.3800048828125</v>
+      </c>
+      <c r="C118" t="n">
+        <v>539.5499877929688</v>
+      </c>
+      <c r="D118" t="n">
+        <v>528.5399780273438</v>
+      </c>
+      <c r="E118" t="n">
+        <v>536.3800048828125</v>
+      </c>
+      <c r="F118" t="n">
+        <v>22795200</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B119" t="n">
+        <v>549.97998046875</v>
+      </c>
+      <c r="C119" t="n">
+        <v>573.6900024414062</v>
+      </c>
+      <c r="D119" t="n">
+        <v>546.77001953125</v>
+      </c>
+      <c r="E119" t="n">
+        <v>572.1300048828125</v>
+      </c>
+      <c r="F119" t="n">
+        <v>32898300</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B120" t="n">
+        <v>580.1300048828125</v>
+      </c>
+      <c r="C120" t="n">
+        <v>592.5499877929688</v>
+      </c>
+      <c r="D120" t="n">
+        <v>573.8200073242188</v>
+      </c>
+      <c r="E120" t="n">
+        <v>579.22998046875</v>
+      </c>
+      <c r="F120" t="n">
+        <v>23608100</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B121" t="n">
+        <v>566.0399780273438</v>
+      </c>
+      <c r="C121" t="n">
+        <v>578.5</v>
+      </c>
+      <c r="D121" t="n">
+        <v>559.7000122070312</v>
+      </c>
+      <c r="E121" t="n">
+        <v>574.4600219726562</v>
+      </c>
+      <c r="F121" t="n">
+        <v>13518500</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B122" t="n">
+        <v>577.6900024414062</v>
+      </c>
+      <c r="C122" t="n">
+        <v>582.7899780273438</v>
+      </c>
+      <c r="D122" t="n">
+        <v>572</v>
+      </c>
+      <c r="E122" t="n">
+        <v>573.02001953125</v>
+      </c>
+      <c r="F122" t="n">
+        <v>9489600</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B123" t="n">
+        <v>571.9000244140625</v>
+      </c>
+      <c r="C123" t="n">
+        <v>572.9600219726562</v>
+      </c>
+      <c r="D123" t="n">
+        <v>564.760009765625</v>
+      </c>
+      <c r="E123" t="n">
+        <v>569.530029296875</v>
+      </c>
+      <c r="F123" t="n">
+        <v>5218536</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/stock_data.xlsx
+++ b/stock_data.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSFT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPY" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSFT" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMZN" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,19 +478,19 @@
         <v>45950</v>
       </c>
       <c r="B2" t="n">
-        <v>512.4788764440519</v>
+        <v>255.4032084113237</v>
       </c>
       <c r="C2" t="n">
-        <v>516.5519656323323</v>
+        <v>263.8770629877272</v>
       </c>
       <c r="D2" t="n">
-        <v>511.3037703677804</v>
+        <v>255.143708503654</v>
       </c>
       <c r="E2" t="n">
-        <v>514.6498413085938</v>
+        <v>261.7411193847656</v>
       </c>
       <c r="F2" t="n">
-        <v>14665600</v>
+        <v>90483000</v>
       </c>
     </row>
     <row r="3">
@@ -498,19 +498,19 @@
         <v>45951</v>
       </c>
       <c r="B3" t="n">
-        <v>515.3569857054445</v>
+        <v>261.3818200057694</v>
       </c>
       <c r="C3" t="n">
-        <v>516.5420602391357</v>
+        <v>264.7853366806196</v>
       </c>
       <c r="D3" t="n">
-        <v>510.9154330870712</v>
+        <v>261.3318968470685</v>
       </c>
       <c r="E3" t="n">
-        <v>515.5162963867188</v>
+        <v>262.2701110839844</v>
       </c>
       <c r="F3" t="n">
-        <v>15586200</v>
+        <v>46695900</v>
       </c>
     </row>
     <row r="4">
@@ -518,19 +518,19 @@
         <v>45952</v>
       </c>
       <c r="B4" t="n">
-        <v>518.9919195722497</v>
+        <v>262.1503352574342</v>
       </c>
       <c r="C4" t="n">
-        <v>523.0549803520576</v>
+        <v>262.349966966352</v>
       </c>
       <c r="D4" t="n">
-        <v>515.5661623300699</v>
+        <v>254.9440691826199</v>
       </c>
       <c r="E4" t="n">
-        <v>518.3843994140625</v>
+        <v>257.9583435058594</v>
       </c>
       <c r="F4" t="n">
-        <v>18962700</v>
+        <v>45015300</v>
       </c>
     </row>
     <row r="5">
@@ -538,19 +538,19 @@
         <v>45953</v>
       </c>
       <c r="B5" t="n">
-        <v>520.2964530626382</v>
+        <v>259.4454820834593</v>
       </c>
       <c r="C5" t="n">
-        <v>521.7802730707533</v>
+        <v>260.1241811137136</v>
       </c>
       <c r="D5" t="n">
-        <v>516.4623598997719</v>
+        <v>257.5191611036844</v>
       </c>
       <c r="E5" t="n">
-        <v>518.404296875</v>
+        <v>259.0861511230469</v>
       </c>
       <c r="F5" t="n">
-        <v>14023500</v>
+        <v>32754900</v>
       </c>
     </row>
     <row r="6">
@@ -558,19 +558,19 @@
         <v>45954</v>
       </c>
       <c r="B6" t="n">
-        <v>520.6250388201142</v>
+        <v>260.6931034322695</v>
       </c>
       <c r="C6" t="n">
-        <v>523.1744351060786</v>
+        <v>263.6275126875418</v>
       </c>
       <c r="D6" t="n">
-        <v>518.5536961256696</v>
+        <v>258.6869175950168</v>
       </c>
       <c r="E6" t="n">
-        <v>521.441650390625</v>
+        <v>262.3200073242188</v>
       </c>
       <c r="F6" t="n">
-        <v>15532400</v>
+        <v>38253700</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
         <v>45957</v>
       </c>
       <c r="B7" t="n">
-        <v>529.577902779321</v>
+        <v>264.376098228409</v>
       </c>
       <c r="C7" t="n">
-        <v>532.3662956890146</v>
+        <v>268.60802232244</v>
       </c>
       <c r="D7" t="n">
-        <v>526.819354031342</v>
+        <v>264.1465248140549</v>
       </c>
       <c r="E7" t="n">
-        <v>529.3189697265625</v>
+        <v>268.2986145019531</v>
       </c>
       <c r="F7" t="n">
-        <v>18734700</v>
+        <v>44888200</v>
       </c>
     </row>
     <row r="8">
@@ -598,19 +598,19 @@
         <v>45958</v>
       </c>
       <c r="B8" t="n">
-        <v>547.7224103521172</v>
+        <v>268.4782600095115</v>
       </c>
       <c r="C8" t="n">
-        <v>551.4269763883988</v>
+        <v>269.3765722048576</v>
       </c>
       <c r="D8" t="n">
-        <v>538.5306518978505</v>
+        <v>267.6398616921066</v>
       </c>
       <c r="E8" t="n">
-        <v>539.8252563476562</v>
+        <v>268.4882507324219</v>
       </c>
       <c r="F8" t="n">
-        <v>29986700</v>
+        <v>41534800</v>
       </c>
     </row>
     <row r="9">
@@ -618,19 +618,19 @@
         <v>45959</v>
       </c>
       <c r="B9" t="n">
-        <v>542.6833492925585</v>
+        <v>268.7677057947778</v>
       </c>
       <c r="C9" t="n">
-        <v>544.0078586434945</v>
+        <v>270.8936584399069</v>
       </c>
       <c r="D9" t="n">
-        <v>534.507325873603</v>
+        <v>266.6018207191691</v>
       </c>
       <c r="E9" t="n">
-        <v>539.307373046875</v>
+        <v>269.1869201660156</v>
       </c>
       <c r="F9" t="n">
-        <v>36023000</v>
+        <v>51086700</v>
       </c>
     </row>
     <row r="10">
@@ -638,19 +638,19 @@
         <v>45960</v>
       </c>
       <c r="B10" t="n">
-        <v>528.2831883129468</v>
+        <v>271.4725408872279</v>
       </c>
       <c r="C10" t="n">
-        <v>532.7545848667123</v>
+        <v>273.6184749716116</v>
       </c>
       <c r="D10" t="n">
-        <v>519.9578228356851</v>
+        <v>267.969239224885</v>
       </c>
       <c r="E10" t="n">
-        <v>523.582763671875</v>
+        <v>270.8836669921875</v>
       </c>
       <c r="F10" t="n">
-        <v>41023100</v>
+        <v>69886500</v>
       </c>
     </row>
     <row r="11">
@@ -658,19 +658,19 @@
         <v>45961</v>
       </c>
       <c r="B11" t="n">
-        <v>526.6898137654194</v>
+        <v>276.4630533049319</v>
       </c>
       <c r="C11" t="n">
-        <v>527.1279940743384</v>
+        <v>276.7924425807819</v>
       </c>
       <c r="D11" t="n">
-        <v>512.9668501497666</v>
+        <v>268.647962249571</v>
       </c>
       <c r="E11" t="n">
-        <v>515.6656494140625</v>
+        <v>269.8556518554688</v>
       </c>
       <c r="F11" t="n">
-        <v>34006400</v>
+        <v>86167100</v>
       </c>
     </row>
     <row r="12">
@@ -678,19 +678,19 @@
         <v>45964</v>
       </c>
       <c r="B12" t="n">
-        <v>517.657371934483</v>
+        <v>269.9055662700252</v>
       </c>
       <c r="C12" t="n">
-        <v>522.7860691817526</v>
+        <v>270.3347409275427</v>
       </c>
       <c r="D12" t="n">
-        <v>512.4590180581705</v>
+        <v>265.7434858777505</v>
       </c>
       <c r="E12" t="n">
-        <v>514.888916015625</v>
+        <v>268.5381469726562</v>
       </c>
       <c r="F12" t="n">
-        <v>22374700</v>
+        <v>50194600</v>
       </c>
     </row>
     <row r="13">
@@ -698,19 +698,19 @@
         <v>45965</v>
       </c>
       <c r="B13" t="n">
-        <v>509.6407695643784</v>
+        <v>267.8195068636227</v>
       </c>
       <c r="C13" t="n">
-        <v>513.4150529816625</v>
+        <v>270.9734988318123</v>
       </c>
       <c r="D13" t="n">
-        <v>505.7369892339689</v>
+        <v>267.1108661194202</v>
       </c>
       <c r="E13" t="n">
-        <v>512.2001342773438</v>
+        <v>269.5262756347656</v>
       </c>
       <c r="F13" t="n">
-        <v>20958700</v>
+        <v>49274800</v>
       </c>
     </row>
     <row r="14">
@@ -718,19 +718,19 @@
         <v>45966</v>
       </c>
       <c r="B14" t="n">
-        <v>511.1743415428253</v>
+        <v>268.0989800730272</v>
       </c>
       <c r="C14" t="n">
-        <v>512.6980347767452</v>
+        <v>271.1831284425123</v>
       </c>
       <c r="D14" t="n">
-        <v>504.4821687767013</v>
+        <v>266.4221834255846</v>
       </c>
       <c r="E14" t="n">
-        <v>505.0597839355469</v>
+        <v>269.6260986328125</v>
       </c>
       <c r="F14" t="n">
-        <v>23024300</v>
+        <v>43683100</v>
       </c>
     </row>
     <row r="15">
@@ -738,19 +738,19 @@
         <v>45967</v>
       </c>
       <c r="B15" t="n">
-        <v>503.5659922381216</v>
+        <v>267.3803770260164</v>
       </c>
       <c r="C15" t="n">
-        <v>503.6058351018555</v>
+        <v>272.8798740142925</v>
       </c>
       <c r="D15" t="n">
-        <v>493.7567764386794</v>
+        <v>267.3803770260164</v>
       </c>
       <c r="E15" t="n">
-        <v>495.0414428710938</v>
+        <v>269.2567749023438</v>
       </c>
       <c r="F15" t="n">
-        <v>27406500</v>
+        <v>51204000</v>
       </c>
     </row>
     <row r="16">
@@ -758,19 +758,19 @@
         <v>45968</v>
       </c>
       <c r="B16" t="n">
-        <v>494.8920702735404</v>
+        <v>269.2867154149515</v>
       </c>
       <c r="C16" t="n">
-        <v>497.3119999979126</v>
+        <v>271.7719991063764</v>
       </c>
       <c r="D16" t="n">
-        <v>491.2073803526309</v>
+        <v>266.2624809601513</v>
       </c>
       <c r="E16" t="n">
-        <v>494.7626037597656</v>
+        <v>267.9592590332031</v>
       </c>
       <c r="F16" t="n">
-        <v>24019800</v>
+        <v>48227400</v>
       </c>
     </row>
     <row r="17">
@@ -778,19 +778,19 @@
         <v>45971</v>
       </c>
       <c r="B17" t="n">
-        <v>497.9692613740871</v>
+        <v>268.7085692371889</v>
       </c>
       <c r="C17" t="n">
-        <v>504.7510576229119</v>
+        <v>273.4741297822401</v>
       </c>
       <c r="D17" t="n">
-        <v>496.7343757501637</v>
+        <v>267.2099714283653</v>
       </c>
       <c r="E17" t="n">
-        <v>503.9045715332031</v>
+        <v>269.1781311035156</v>
       </c>
       <c r="F17" t="n">
-        <v>26101500</v>
+        <v>41312400</v>
       </c>
     </row>
     <row r="18">
@@ -798,19 +798,19 @@
         <v>45972</v>
       </c>
       <c r="B18" t="n">
-        <v>502.7095490222416</v>
+        <v>269.5577590596557</v>
       </c>
       <c r="C18" t="n">
-        <v>507.4896898672195</v>
+        <v>275.6520624227355</v>
       </c>
       <c r="D18" t="n">
-        <v>500.2697130079767</v>
+        <v>269.5477586519058</v>
       </c>
       <c r="E18" t="n">
-        <v>506.573486328125</v>
+        <v>274.99267578125</v>
       </c>
       <c r="F18" t="n">
-        <v>17980000</v>
+        <v>46208300</v>
       </c>
     </row>
     <row r="19">
@@ -818,19 +818,19 @@
         <v>45973</v>
       </c>
       <c r="B19" t="n">
-        <v>507.2506574723947</v>
+        <v>274.7429239716485</v>
       </c>
       <c r="C19" t="n">
-        <v>509.5511194130969</v>
+        <v>275.4722525277038</v>
       </c>
       <c r="D19" t="n">
-        <v>497.0530724082431</v>
+        <v>271.4460210796085</v>
       </c>
       <c r="E19" t="n">
-        <v>509.0233154296875</v>
+        <v>273.21435546875</v>
       </c>
       <c r="F19" t="n">
-        <v>26574900</v>
+        <v>48398000</v>
       </c>
     </row>
     <row r="20">
@@ -838,19 +838,19 @@
         <v>45974</v>
       </c>
       <c r="B20" t="n">
-        <v>508.1967287528611</v>
+        <v>273.8537435218178</v>
       </c>
       <c r="C20" t="n">
-        <v>511.3735209246628</v>
+        <v>276.4413491841305</v>
       </c>
       <c r="D20" t="n">
-        <v>499.2140928412288</v>
+        <v>271.8356428219928</v>
       </c>
       <c r="E20" t="n">
-        <v>501.205810546875</v>
+        <v>272.6948547363281</v>
       </c>
       <c r="F20" t="n">
-        <v>25273100</v>
+        <v>49602800</v>
       </c>
     </row>
     <row r="21">
@@ -858,19 +858,19 @@
         <v>45975</v>
       </c>
       <c r="B21" t="n">
-        <v>496.166765720741</v>
+        <v>270.7965900477885</v>
       </c>
       <c r="C21" t="n">
-        <v>509.4813936811572</v>
+        <v>275.702003472256</v>
       </c>
       <c r="D21" t="n">
-        <v>495.3800287197931</v>
+        <v>269.3479639093673</v>
       </c>
       <c r="E21" t="n">
-        <v>508.0672607421875</v>
+        <v>272.1553344726562</v>
       </c>
       <c r="F21" t="n">
-        <v>28505700</v>
+        <v>47431300</v>
       </c>
     </row>
     <row r="22">
@@ -878,19 +878,19 @@
         <v>45978</v>
       </c>
       <c r="B22" t="n">
-        <v>506.3444435928635</v>
+        <v>268.5687054184609</v>
       </c>
       <c r="C22" t="n">
-        <v>509.9992285471841</v>
+        <v>270.2371271729127</v>
       </c>
       <c r="D22" t="n">
-        <v>502.8190947602184</v>
+        <v>265.4815977121726</v>
       </c>
       <c r="E22" t="n">
-        <v>505.3883972167969</v>
+        <v>267.2099609375</v>
       </c>
       <c r="F22" t="n">
-        <v>19092800</v>
+        <v>45018300</v>
       </c>
     </row>
     <row r="23">
@@ -898,19 +898,19 @@
         <v>45979</v>
       </c>
       <c r="B23" t="n">
-        <v>493.3186219236692</v>
+        <v>269.7376065335732</v>
       </c>
       <c r="C23" t="n">
-        <v>500.8971240097587</v>
+        <v>270.4569347049811</v>
       </c>
       <c r="D23" t="n">
-        <v>484.7641975590383</v>
+        <v>265.0719890725528</v>
       </c>
       <c r="E23" t="n">
-        <v>491.7451782226562</v>
+        <v>267.1900024414062</v>
       </c>
       <c r="F23" t="n">
-        <v>33815100</v>
+        <v>45677300</v>
       </c>
     </row>
     <row r="24">
@@ -918,19 +918,19 @@
         <v>45980</v>
       </c>
       <c r="B24" t="n">
-        <v>488.0704229659532</v>
+        <v>265.2817633125939</v>
       </c>
       <c r="C24" t="n">
-        <v>493.1393408084164</v>
+        <v>271.9555110777923</v>
       </c>
       <c r="D24" t="n">
-        <v>480.8305097576304</v>
+        <v>265.2517925781922</v>
       </c>
       <c r="E24" t="n">
-        <v>485.1027526855469</v>
+        <v>268.3089294433594</v>
       </c>
       <c r="F24" t="n">
-        <v>23245300</v>
+        <v>40424500</v>
       </c>
     </row>
     <row r="25">
@@ -938,19 +938,19 @@
         <v>45981</v>
       </c>
       <c r="B25" t="n">
-        <v>491.5879641710541</v>
+        <v>270.5768036466949</v>
       </c>
       <c r="C25" t="n">
-        <v>492.4460215630244</v>
+        <v>275.1725094767523</v>
       </c>
       <c r="D25" t="n">
-        <v>474.4171642897319</v>
+        <v>265.6714205454633</v>
       </c>
       <c r="E25" t="n">
-        <v>477.3404846191406</v>
+        <v>266.0010986328125</v>
       </c>
       <c r="F25" t="n">
-        <v>26802500</v>
+        <v>45823600</v>
       </c>
     </row>
     <row r="26">
@@ -958,19 +958,19 @@
         <v>45982</v>
       </c>
       <c r="B26" t="n">
-        <v>477.4103368698009</v>
+        <v>265.7013768088059</v>
       </c>
       <c r="C26" t="n">
-        <v>477.8293938228302</v>
+        <v>273.0744516711978</v>
       </c>
       <c r="D26" t="n">
-        <v>467.2036221547232</v>
+        <v>265.4216397990326</v>
       </c>
       <c r="E26" t="n">
-        <v>471.0448608398438</v>
+        <v>271.2361755371094</v>
       </c>
       <c r="F26" t="n">
-        <v>31769200</v>
+        <v>59030800</v>
       </c>
     </row>
     <row r="27">
@@ -978,19 +978,19 @@
         <v>45985</v>
       </c>
       <c r="B27" t="n">
-        <v>473.9183160323131</v>
+        <v>270.6467521230613</v>
       </c>
       <c r="C27" t="n">
-        <v>475.8139832068258</v>
+        <v>276.7410558404627</v>
       </c>
       <c r="D27" t="n">
-        <v>466.9542001322548</v>
+        <v>270.6467521230613</v>
       </c>
       <c r="E27" t="n">
-        <v>472.9205932617188</v>
+        <v>275.6620788574219</v>
       </c>
       <c r="F27" t="n">
-        <v>34421000</v>
+        <v>65585800</v>
       </c>
     </row>
     <row r="28">
@@ -998,19 +998,19 @@
         <v>45986</v>
       </c>
       <c r="B28" t="n">
-        <v>472.9904142849383</v>
+        <v>275.012667049666</v>
       </c>
       <c r="C28" t="n">
-        <v>478.0588322743821</v>
+        <v>280.1179060838009</v>
       </c>
       <c r="D28" t="n">
-        <v>463.8313270788984</v>
+        <v>274.9926967216935</v>
       </c>
       <c r="E28" t="n">
-        <v>475.9037475585938</v>
+        <v>276.7110900878906</v>
       </c>
       <c r="F28" t="n">
-        <v>28019800</v>
+        <v>46914200</v>
       </c>
     </row>
     <row r="29">
@@ -1018,19 +1018,19 @@
         <v>45987</v>
       </c>
       <c r="B29" t="n">
-        <v>485.2025316262965</v>
+        <v>276.7010825487222</v>
       </c>
       <c r="C29" t="n">
-        <v>487.1979770584782</v>
+        <v>279.2686873678638</v>
       </c>
       <c r="D29" t="n">
-        <v>480.1041831621511</v>
+        <v>276.3714044558947</v>
       </c>
       <c r="E29" t="n">
-        <v>484.3943786621094</v>
+        <v>277.29052734375</v>
       </c>
       <c r="F29" t="n">
-        <v>25709100</v>
+        <v>33431400</v>
       </c>
     </row>
     <row r="30">
@@ -1038,19 +1038,19 @@
         <v>45989</v>
       </c>
       <c r="B30" t="n">
-        <v>486.489626354464</v>
+        <v>277.0008150112318</v>
       </c>
       <c r="C30" t="n">
-        <v>491.5081706450152</v>
+        <v>278.7391786268174</v>
       </c>
       <c r="D30" t="n">
-        <v>485.541777548382</v>
+        <v>275.7319827496524</v>
       </c>
       <c r="E30" t="n">
-        <v>490.8895874023438</v>
+        <v>278.5893249511719</v>
       </c>
       <c r="F30" t="n">
-        <v>14386700</v>
+        <v>20135600</v>
       </c>
     </row>
     <row r="31">
@@ -1058,19 +1058,19 @@
         <v>45992</v>
       </c>
       <c r="B31" t="n">
-        <v>487.3277021324388</v>
+        <v>277.7501195744996</v>
       </c>
       <c r="C31" t="n">
-        <v>488.7444513856018</v>
+        <v>283.1550658399818</v>
       </c>
       <c r="D31" t="n">
-        <v>483.5463243869077</v>
+        <v>275.881872572025</v>
       </c>
       <c r="E31" t="n">
-        <v>485.6315612792969</v>
+        <v>282.8353576660156</v>
       </c>
       <c r="F31" t="n">
-        <v>23964000</v>
+        <v>46587700</v>
       </c>
     </row>
     <row r="32">
@@ -1078,19 +1078,19 @@
         <v>45993</v>
       </c>
       <c r="B32" t="n">
-        <v>485.6116258193264</v>
+        <v>282.7354345985028</v>
       </c>
       <c r="C32" t="n">
-        <v>492.3761849539621</v>
+        <v>287.1313151163589</v>
       </c>
       <c r="D32" t="n">
-        <v>485.2125428025972</v>
+        <v>282.3657853749787</v>
       </c>
       <c r="E32" t="n">
-        <v>488.8841552734375</v>
+        <v>285.9224548339844</v>
       </c>
       <c r="F32" t="n">
-        <v>19562700</v>
+        <v>53669500</v>
       </c>
     </row>
     <row r="33">
@@ -1098,19 +1098,19 @@
         <v>45994</v>
       </c>
       <c r="B33" t="n">
-        <v>475.235297143397</v>
+        <v>285.9324708384744</v>
       </c>
       <c r="C33" t="n">
-        <v>483.1372440988117</v>
+        <v>288.3501915351014</v>
       </c>
       <c r="D33" t="n">
-        <v>474.1178525596479</v>
+        <v>283.0351573834178</v>
       </c>
       <c r="E33" t="n">
-        <v>476.64208984375</v>
+        <v>283.8843688964844</v>
       </c>
       <c r="F33" t="n">
-        <v>34615100</v>
+        <v>43538700</v>
       </c>
     </row>
     <row r="34">
@@ -1118,19 +1118,19 @@
         <v>45995</v>
       </c>
       <c r="B34" t="n">
-        <v>478.6674679630734</v>
+        <v>283.8344068650217</v>
       </c>
       <c r="C34" t="n">
-        <v>480.2239129901724</v>
+        <v>284.4638227692578</v>
       </c>
       <c r="D34" t="n">
-        <v>475.4048951405118</v>
+        <v>278.3295482939282</v>
       </c>
       <c r="E34" t="n">
-        <v>479.7449951171875</v>
+        <v>280.4375915527344</v>
       </c>
       <c r="F34" t="n">
-        <v>22318200</v>
+        <v>43989100</v>
       </c>
     </row>
     <row r="35">
@@ -1138,19 +1138,19 @@
         <v>45996</v>
       </c>
       <c r="B35" t="n">
-        <v>481.4211657314621</v>
+        <v>280.2777430659675</v>
       </c>
       <c r="C35" t="n">
-        <v>482.299166614698</v>
+        <v>280.8771882481053</v>
       </c>
       <c r="D35" t="n">
-        <v>477.7894707894466</v>
+        <v>277.7900501334527</v>
       </c>
       <c r="E35" t="n">
-        <v>482.0597229003906</v>
+        <v>278.5193786621094</v>
       </c>
       <c r="F35" t="n">
-        <v>22608700</v>
+        <v>47265800</v>
       </c>
     </row>
     <row r="36">
@@ -1158,19 +1158,19 @@
         <v>45999</v>
       </c>
       <c r="B36" t="n">
-        <v>483.7858099301447</v>
+        <v>277.8699843761556</v>
       </c>
       <c r="C36" t="n">
-        <v>491.1789088824644</v>
+        <v>279.4085531850005</v>
       </c>
       <c r="D36" t="n">
-        <v>483.2769615726175</v>
+        <v>275.8918244790692</v>
       </c>
       <c r="E36" t="n">
-        <v>489.9018249511719</v>
+        <v>277.6302185058594</v>
       </c>
       <c r="F36" t="n">
-        <v>21965900</v>
+        <v>38211800</v>
       </c>
     </row>
     <row r="37">
@@ -1178,19 +1178,19 @@
         <v>46000</v>
       </c>
       <c r="B37" t="n">
-        <v>487.9862027558801</v>
+        <v>277.8999627322321</v>
       </c>
       <c r="C37" t="n">
-        <v>490.9993144973556</v>
+        <v>279.7682096639769</v>
       </c>
       <c r="D37" t="n">
-        <v>487.3875630167038</v>
+        <v>276.6611317163261</v>
       </c>
       <c r="E37" t="n">
-        <v>490.8995361328125</v>
+        <v>276.9208679199219</v>
       </c>
       <c r="F37" t="n">
-        <v>14696100</v>
+        <v>32193300</v>
       </c>
     </row>
     <row r="38">
@@ -1198,19 +1198,19 @@
         <v>46001</v>
       </c>
       <c r="B38" t="n">
-        <v>482.9277288439703</v>
+        <v>277.490342786908</v>
       </c>
       <c r="C38" t="n">
-        <v>483.1472290611572</v>
+        <v>279.4884730680018</v>
       </c>
       <c r="D38" t="n">
-        <v>473.9980982856002</v>
+        <v>276.1815698919154</v>
       </c>
       <c r="E38" t="n">
-        <v>477.4701843261719</v>
+        <v>278.5193786621094</v>
       </c>
       <c r="F38" t="n">
-        <v>35756200</v>
+        <v>33038300</v>
       </c>
     </row>
     <row r="39">
@@ -1218,19 +1218,19 @@
         <v>46002</v>
       </c>
       <c r="B39" t="n">
-        <v>475.5445986070271</v>
+        <v>278.8390875870869</v>
       </c>
       <c r="C39" t="n">
-        <v>484.9231863556336</v>
+        <v>279.3286197507982</v>
       </c>
       <c r="D39" t="n">
-        <v>474.7763326037194</v>
+        <v>273.5540244422053</v>
       </c>
       <c r="E39" t="n">
-        <v>482.3690185546875</v>
+        <v>277.7700805664062</v>
       </c>
       <c r="F39" t="n">
-        <v>24669200</v>
+        <v>33248000</v>
       </c>
     </row>
     <row r="40">
@@ -1238,19 +1238,19 @@
         <v>46003</v>
       </c>
       <c r="B40" t="n">
-        <v>478.7273480015789</v>
+        <v>277.64021728323</v>
       </c>
       <c r="C40" t="n">
-        <v>481.3513637649093</v>
+        <v>278.9589906850317</v>
       </c>
       <c r="D40" t="n">
-        <v>475.2552617920193</v>
+        <v>276.5612402656973</v>
       </c>
       <c r="E40" t="n">
-        <v>477.4402770996094</v>
+        <v>278.0198669433594</v>
       </c>
       <c r="F40" t="n">
-        <v>21248100</v>
+        <v>39532900</v>
       </c>
     </row>
     <row r="41">
@@ -1258,19 +1258,19 @@
         <v>46006</v>
       </c>
       <c r="B41" t="n">
-        <v>479.0066832317436</v>
+        <v>279.8880911943856</v>
       </c>
       <c r="C41" t="n">
-        <v>479.6252664455081</v>
+        <v>279.8880911943856</v>
       </c>
       <c r="D41" t="n">
-        <v>471.4439279747418</v>
+        <v>272.5849275039148</v>
       </c>
       <c r="E41" t="n">
-        <v>473.7387084960938</v>
+        <v>273.8537292480469</v>
       </c>
       <c r="F41" t="n">
-        <v>23727700</v>
+        <v>50409100</v>
       </c>
     </row>
     <row r="42">
@@ -1278,19 +1278,19 @@
         <v>46007</v>
       </c>
       <c r="B42" t="n">
-        <v>470.8353364785088</v>
+        <v>272.5649667835892</v>
       </c>
       <c r="C42" t="n">
-        <v>476.8017293564801</v>
+        <v>275.2424541197232</v>
       </c>
       <c r="D42" t="n">
-        <v>469.8076832860371</v>
+        <v>271.535930878856</v>
       </c>
       <c r="E42" t="n">
-        <v>475.3051452636719</v>
+        <v>274.353271484375</v>
       </c>
       <c r="F42" t="n">
-        <v>20705600</v>
+        <v>37648600</v>
       </c>
     </row>
     <row r="43">
@@ -1298,19 +1298,19 @@
         <v>46008</v>
       </c>
       <c r="B43" t="n">
-        <v>475.8239455574328</v>
+        <v>274.7529265191943</v>
       </c>
       <c r="C43" t="n">
-        <v>478.9069051052783</v>
+        <v>275.9018453851206</v>
       </c>
       <c r="D43" t="n">
-        <v>473.9182915104317</v>
+        <v>271.3860817211021</v>
       </c>
       <c r="E43" t="n">
-        <v>475.0357360839844</v>
+        <v>271.5858764648438</v>
       </c>
       <c r="F43" t="n">
-        <v>24527200</v>
+        <v>50138700</v>
       </c>
     </row>
     <row r="44">
@@ -1318,19 +1318,19 @@
         <v>46009</v>
       </c>
       <c r="B44" t="n">
-        <v>477.1010453906704</v>
+        <v>273.3542023206923</v>
       </c>
       <c r="C44" t="n">
-        <v>488.4850656489584</v>
+        <v>273.374203136776</v>
       </c>
       <c r="D44" t="n">
-        <v>476.8017407441929</v>
+        <v>266.7004552212896</v>
       </c>
       <c r="E44" t="n">
-        <v>482.8778686523438</v>
+        <v>271.935546875</v>
       </c>
       <c r="F44" t="n">
-        <v>28573500</v>
+        <v>51630700</v>
       </c>
     </row>
     <row r="45">
@@ -1338,19 +1338,19 @@
         <v>46010</v>
       </c>
       <c r="B45" t="n">
-        <v>486.2501387748106</v>
+        <v>271.8955859651445</v>
       </c>
       <c r="C45" t="n">
-        <v>486.7390436209232</v>
+        <v>274.343307881706</v>
       </c>
       <c r="D45" t="n">
-        <v>481.39123391446</v>
+        <v>269.6476892826471</v>
       </c>
       <c r="E45" t="n">
-        <v>484.8134460449219</v>
+        <v>273.4141845703125</v>
       </c>
       <c r="F45" t="n">
-        <v>70836100</v>
+        <v>144632000</v>
       </c>
     </row>
     <row r="46">
@@ -1358,19 +1358,19 @@
         <v>46013</v>
       </c>
       <c r="B46" t="n">
-        <v>485.0129839081317</v>
+        <v>272.6048920133635</v>
       </c>
       <c r="C46" t="n">
-        <v>487.6170561484318</v>
+        <v>273.6239579412959</v>
       </c>
       <c r="D46" t="n">
-        <v>481.5908021440126</v>
+        <v>270.2571133897843</v>
       </c>
       <c r="E46" t="n">
-        <v>483.8157348632812</v>
+        <v>270.7166748046875</v>
       </c>
       <c r="F46" t="n">
-        <v>16963000</v>
+        <v>36571800</v>
       </c>
     </row>
     <row r="47">
@@ -1378,19 +1378,19 @@
         <v>46014</v>
       </c>
       <c r="B47" t="n">
-        <v>483.8755963136496</v>
+        <v>270.5868091030317</v>
       </c>
       <c r="C47" t="n">
-        <v>486.7190818282799</v>
+        <v>272.2452609569047</v>
       </c>
       <c r="D47" t="n">
-        <v>483.6361221459561</v>
+        <v>269.3080068949797</v>
       </c>
       <c r="E47" t="n">
-        <v>485.7413330078125</v>
+        <v>272.1053771972656</v>
       </c>
       <c r="F47" t="n">
-        <v>14683600</v>
+        <v>29642000</v>
       </c>
     </row>
     <row r="48">
@@ -1398,19 +1398,19 @@
         <v>46015</v>
       </c>
       <c r="B48" t="n">
-        <v>484.5739628623746</v>
+        <v>272.085389177814</v>
       </c>
       <c r="C48" t="n">
-        <v>488.0460488858467</v>
+        <v>275.1724967178681</v>
       </c>
       <c r="D48" t="n">
-        <v>483.7258924615979</v>
+        <v>271.9455359163183</v>
       </c>
       <c r="E48" t="n">
-        <v>486.9086303710938</v>
+        <v>273.5540161132812</v>
       </c>
       <c r="F48" t="n">
-        <v>5855900</v>
+        <v>17910600</v>
       </c>
     </row>
     <row r="49">
@@ -1418,19 +1418,19 @@
         <v>46017</v>
       </c>
       <c r="B49" t="n">
-        <v>485.601642461088</v>
+        <v>273.9037084592662</v>
       </c>
       <c r="C49" t="n">
-        <v>487.0084352251927</v>
+        <v>275.1125687682936</v>
       </c>
       <c r="D49" t="n">
-        <v>484.8533503811227</v>
+        <v>272.6049054553</v>
       </c>
       <c r="E49" t="n">
-        <v>486.599365234375</v>
+        <v>273.1444091796875</v>
       </c>
       <c r="F49" t="n">
-        <v>8842200</v>
+        <v>21521800</v>
       </c>
     </row>
     <row r="50">
@@ -1438,19 +1438,19 @@
         <v>46020</v>
       </c>
       <c r="B50" t="n">
-        <v>483.7558335295542</v>
+        <v>272.4350823114352</v>
       </c>
       <c r="C50" t="n">
-        <v>487.2379065999322</v>
+        <v>274.103504063292</v>
       </c>
       <c r="D50" t="n">
-        <v>483.0773893732932</v>
+        <v>272.0954038139857</v>
       </c>
       <c r="E50" t="n">
-        <v>485.9907531738281</v>
+        <v>273.5040893554688</v>
       </c>
       <c r="F50" t="n">
-        <v>10893400</v>
+        <v>23715200</v>
       </c>
     </row>
     <row r="51">
@@ -1458,19 +1458,19 @@
         <v>46021</v>
       </c>
       <c r="B51" t="n">
-        <v>484.8234150126488</v>
+        <v>272.5549704076282</v>
       </c>
       <c r="C51" t="n">
-        <v>488.5648753746365</v>
+        <v>273.8237722152489</v>
       </c>
       <c r="D51" t="n">
-        <v>484.3944015320139</v>
+        <v>272.0254670796708</v>
       </c>
       <c r="E51" t="n">
-        <v>486.3699035644531</v>
+        <v>272.82470703125</v>
       </c>
       <c r="F51" t="n">
-        <v>13944500</v>
+        <v>22139600</v>
       </c>
     </row>
     <row r="52">
@@ -1478,19 +1478,19 @@
         <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>486.7290680267604</v>
+        <v>272.804725327361</v>
       </c>
       <c r="C52" t="n">
-        <v>487.0284031238816</v>
+        <v>273.4241408373621</v>
       </c>
       <c r="D52" t="n">
-        <v>482.1993981667827</v>
+        <v>271.4959524300237</v>
       </c>
       <c r="E52" t="n">
-        <v>482.5186767578125</v>
+        <v>271.6058349609375</v>
       </c>
       <c r="F52" t="n">
-        <v>15601600</v>
+        <v>27293600</v>
       </c>
     </row>
     <row r="53">
@@ -1498,19 +1498,19 @@
         <v>46024</v>
       </c>
       <c r="B53" t="n">
-        <v>483.2869444224563</v>
+        <v>272.0054842546519</v>
       </c>
       <c r="C53" t="n">
-        <v>483.5563186075122</v>
+        <v>277.5802543100492</v>
       </c>
       <c r="D53" t="n">
-        <v>469.0893385249197</v>
+        <v>268.7485221479618</v>
       </c>
       <c r="E53" t="n">
-        <v>471.8630065917969</v>
+        <v>270.7566528320312</v>
       </c>
       <c r="F53" t="n">
-        <v>25571600</v>
+        <v>37838100</v>
       </c>
     </row>
     <row r="54">
@@ -1518,19 +1518,19 @@
         <v>46027</v>
       </c>
       <c r="B54" t="n">
-        <v>472.9804293228547</v>
+        <v>270.387007446453</v>
       </c>
       <c r="C54" t="n">
-        <v>474.9858617296903</v>
+        <v>271.2561892506844</v>
       </c>
       <c r="D54" t="n">
-        <v>468.4308161640092</v>
+        <v>265.8912142612155</v>
       </c>
       <c r="E54" t="n">
-        <v>471.773193359375</v>
+        <v>267.0101623535156</v>
       </c>
       <c r="F54" t="n">
-        <v>25250300</v>
+        <v>45647200</v>
       </c>
     </row>
     <row r="55">
@@ -1538,19 +1538,19 @@
         <v>46028</v>
       </c>
       <c r="B55" t="n">
-        <v>472.7210225701547</v>
+        <v>266.7503924619391</v>
       </c>
       <c r="C55" t="n">
-        <v>477.6497753472042</v>
+        <v>267.2998660934885</v>
       </c>
       <c r="D55" t="n">
-        <v>468.6802576477938</v>
+        <v>261.8749496989937</v>
       </c>
       <c r="E55" t="n">
-        <v>477.4203186035156</v>
+        <v>262.1147155761719</v>
       </c>
       <c r="F55" t="n">
-        <v>23037700</v>
+        <v>52352100</v>
       </c>
     </row>
     <row r="56">
@@ -1558,19 +1558,19 @@
         <v>46029</v>
       </c>
       <c r="B56" t="n">
-        <v>478.6674756822987</v>
+        <v>262.9539513876447</v>
       </c>
       <c r="C56" t="n">
-        <v>488.5848422406915</v>
+        <v>263.4334831315393</v>
       </c>
       <c r="D56" t="n">
-        <v>476.861599942913</v>
+        <v>259.5671060011504</v>
       </c>
       <c r="E56" t="n">
-        <v>482.3690185546875</v>
+        <v>260.0866088867188</v>
       </c>
       <c r="F56" t="n">
-        <v>25564200</v>
+        <v>48309800</v>
       </c>
     </row>
     <row r="57">
@@ -1578,19 +1578,19 @@
         <v>46030</v>
       </c>
       <c r="B57" t="n">
-        <v>480.1440867981462</v>
+        <v>256.7797203952787</v>
       </c>
       <c r="C57" t="n">
-        <v>481.5608665012806</v>
+        <v>259.0476178563403</v>
       </c>
       <c r="D57" t="n">
-        <v>474.7763335277468</v>
+        <v>255.4609622909548</v>
       </c>
       <c r="E57" t="n">
-        <v>477.0212097167969</v>
+        <v>258.7978515625</v>
       </c>
       <c r="F57" t="n">
-        <v>18162600</v>
+        <v>50419300</v>
       </c>
     </row>
     <row r="58">
@@ -1598,19 +1598,19 @@
         <v>46031</v>
       </c>
       <c r="B58" t="n">
-        <v>472.9804540365218</v>
+        <v>258.8377955175017</v>
       </c>
       <c r="C58" t="n">
-        <v>478.7273469366413</v>
+        <v>259.9667440583015</v>
       </c>
       <c r="D58" t="n">
-        <v>471.1247042989064</v>
+        <v>255.9804837142826</v>
       </c>
       <c r="E58" t="n">
-        <v>478.1885681152344</v>
+        <v>259.1275329589844</v>
       </c>
       <c r="F58" t="n">
-        <v>18491000</v>
+        <v>39997000</v>
       </c>
     </row>
     <row r="59">
@@ -1618,19 +1618,19 @@
         <v>46034</v>
       </c>
       <c r="B59" t="n">
-        <v>475.5845048686955</v>
+        <v>258.9177364764393</v>
       </c>
       <c r="C59" t="n">
-        <v>479.894643901475</v>
+        <v>261.055720113683</v>
       </c>
       <c r="D59" t="n">
-        <v>474.5967386659474</v>
+        <v>256.5599267903311</v>
       </c>
       <c r="E59" t="n">
-        <v>476.0933227539062</v>
+        <v>260.0067138671875</v>
       </c>
       <c r="F59" t="n">
-        <v>23519900</v>
+        <v>45263800</v>
       </c>
     </row>
     <row r="60">
@@ -1638,19 +1638,19 @@
         <v>46035</v>
       </c>
       <c r="B60" t="n">
-        <v>473.5990225282599</v>
+        <v>258.4781303943212</v>
       </c>
       <c r="C60" t="n">
-        <v>474.6965236309785</v>
+        <v>261.5652379723006</v>
       </c>
       <c r="D60" t="n">
-        <v>464.888922501957</v>
+        <v>258.148452318208</v>
       </c>
       <c r="E60" t="n">
-        <v>469.5981750488281</v>
+        <v>260.8059387207031</v>
       </c>
       <c r="F60" t="n">
-        <v>28545800</v>
+        <v>45730800</v>
       </c>
     </row>
     <row r="61">
@@ -1658,19 +1658,19 @@
         <v>46036</v>
       </c>
       <c r="B61" t="n">
-        <v>465.3977566654985</v>
+        <v>259.247418118488</v>
       </c>
       <c r="C61" t="n">
-        <v>467.1338149970701</v>
+        <v>261.5752571005171</v>
       </c>
       <c r="D61" t="n">
-        <v>456.1289340170423</v>
+        <v>256.4700180914029</v>
       </c>
       <c r="E61" t="n">
-        <v>458.3338928222656</v>
+        <v>259.7169799804688</v>
       </c>
       <c r="F61" t="n">
-        <v>28184300</v>
+        <v>40019400</v>
       </c>
     </row>
     <row r="62">
@@ -1678,19 +1678,19 @@
         <v>46037</v>
       </c>
       <c r="B62" t="n">
-        <v>463.0630900555096</v>
+        <v>260.4063187564486</v>
       </c>
       <c r="C62" t="n">
-        <v>463.1927988881192</v>
+        <v>260.7959687899761</v>
       </c>
       <c r="D62" t="n">
-        <v>454.8618076165624</v>
+        <v>256.8096782083212</v>
       </c>
       <c r="E62" t="n">
-        <v>455.6200866699219</v>
+        <v>257.9685974121094</v>
       </c>
       <c r="F62" t="n">
-        <v>23225800</v>
+        <v>39388600</v>
       </c>
     </row>
     <row r="63">
@@ -1698,19 +1698,19 @@
         <v>46038</v>
       </c>
       <c r="B63" t="n">
-        <v>456.7873986695315</v>
+        <v>257.6589020182799</v>
       </c>
       <c r="C63" t="n">
-        <v>462.1352085061545</v>
+        <v>258.6579671912775</v>
       </c>
       <c r="D63" t="n">
-        <v>455.4404972994736</v>
+        <v>254.6916772349149</v>
       </c>
       <c r="E63" t="n">
-        <v>458.8127746582031</v>
+        <v>255.2911224365234</v>
       </c>
       <c r="F63" t="n">
-        <v>34246700</v>
+        <v>72142800</v>
       </c>
     </row>
     <row r="64">
@@ -1718,19 +1718,19 @@
         <v>46042</v>
       </c>
       <c r="B64" t="n">
-        <v>450.1924514863621</v>
+        <v>252.4937373957159</v>
       </c>
       <c r="C64" t="n">
-        <v>455.7597309230742</v>
+        <v>254.5518092169813</v>
       </c>
       <c r="D64" t="n">
-        <v>448.2568669541529</v>
+        <v>243.1924430560896</v>
       </c>
       <c r="E64" t="n">
-        <v>453.4849243164062</v>
+        <v>246.4693756103516</v>
       </c>
       <c r="F64" t="n">
-        <v>26130000</v>
+        <v>80267500</v>
       </c>
     </row>
     <row r="65">
@@ -1738,19 +1738,19 @@
         <v>46043</v>
       </c>
       <c r="B65" t="n">
-        <v>451.5693196059127</v>
+        <v>248.4675090444481</v>
       </c>
       <c r="C65" t="n">
-        <v>451.6591109990197</v>
+        <v>251.3248360900433</v>
       </c>
       <c r="D65" t="n">
-        <v>437.6810056251358</v>
+        <v>244.9507953165175</v>
       </c>
       <c r="E65" t="n">
-        <v>443.0986328125</v>
+        <v>247.4184875488281</v>
       </c>
       <c r="F65" t="n">
-        <v>37980500</v>
+        <v>54641700</v>
       </c>
     </row>
     <row r="66">
@@ -1758,19 +1758,19 @@
         <v>46044</v>
       </c>
       <c r="B66" t="n">
-        <v>446.600636936346</v>
+        <v>248.9670398844787</v>
       </c>
       <c r="C66" t="n">
-        <v>451.8087507279656</v>
+        <v>250.7653602579427</v>
       </c>
       <c r="D66" t="n">
-        <v>443.6873036586902</v>
+        <v>247.9180183962477</v>
       </c>
       <c r="E66" t="n">
-        <v>450.1126403808594</v>
+        <v>248.1178436279297</v>
       </c>
       <c r="F66" t="n">
-        <v>25349400</v>
+        <v>39708300</v>
       </c>
     </row>
     <row r="67">
@@ -1778,19 +1778,19 @@
         <v>46045</v>
       </c>
       <c r="B67" t="n">
-        <v>450.8409629929935</v>
+        <v>247.0888078223564</v>
       </c>
       <c r="C67" t="n">
-        <v>470.0271819611143</v>
+        <v>249.176850391454</v>
       </c>
       <c r="D67" t="n">
-        <v>449.5040181949105</v>
+        <v>244.4512611104123</v>
       </c>
       <c r="E67" t="n">
-        <v>464.888916015625</v>
+        <v>247.8081207275391</v>
       </c>
       <c r="F67" t="n">
-        <v>38000200</v>
+        <v>41689000</v>
       </c>
     </row>
     <row r="68">
@@ -1798,19 +1798,19 @@
         <v>46048</v>
       </c>
       <c r="B68" t="n">
-        <v>464.2503622118351</v>
+        <v>251.2449001563489</v>
       </c>
       <c r="C68" t="n">
-        <v>473.1700058760031</v>
+        <v>256.320152957849</v>
       </c>
       <c r="D68" t="n">
-        <v>460.9479024031912</v>
+        <v>249.5664780183616</v>
       </c>
       <c r="E68" t="n">
-        <v>469.2090454101562</v>
+        <v>255.1712341308594</v>
       </c>
       <c r="F68" t="n">
-        <v>29291200</v>
+        <v>55969200</v>
       </c>
     </row>
     <row r="69">
@@ -1818,19 +1818,19 @@
         <v>46049</v>
       </c>
       <c r="B69" t="n">
-        <v>472.62128861771</v>
+        <v>258.9277169221324</v>
       </c>
       <c r="C69" t="n">
-        <v>481.7703893732875</v>
+        <v>261.705116697089</v>
       </c>
       <c r="D69" t="n">
-        <v>472.0825097961169</v>
+        <v>257.9685924683142</v>
       </c>
       <c r="E69" t="n">
-        <v>479.485595703125</v>
+        <v>258.0285339355469</v>
       </c>
       <c r="F69" t="n">
-        <v>29213900</v>
+        <v>49648300</v>
       </c>
     </row>
     <row r="70">
@@ -1838,19 +1838,19 @@
         <v>46050</v>
       </c>
       <c r="B70" t="n">
-        <v>482.1095916405993</v>
+        <v>257.409147241713</v>
       </c>
       <c r="C70" t="n">
-        <v>482.6383834693597</v>
+        <v>258.6180076181917</v>
       </c>
       <c r="D70" t="n">
-        <v>476.9114647448887</v>
+        <v>254.2720830679268</v>
       </c>
       <c r="E70" t="n">
-        <v>480.533203125</v>
+        <v>256.2002868652344</v>
       </c>
       <c r="F70" t="n">
-        <v>36875400</v>
+        <v>41288000</v>
       </c>
     </row>
     <row r="71">
@@ -1858,19 +1858,19 @@
         <v>46051</v>
       </c>
       <c r="B71" t="n">
-        <v>438.9880283656418</v>
+        <v>257.758806680925</v>
       </c>
       <c r="C71" t="n">
-        <v>441.4923222419712</v>
+        <v>259.4072580677027</v>
       </c>
       <c r="D71" t="n">
-        <v>420.0612263501361</v>
+        <v>254.1721664792058</v>
       </c>
       <c r="E71" t="n">
-        <v>432.5128173828125</v>
+        <v>258.0385437011719</v>
       </c>
       <c r="F71" t="n">
-        <v>128855300</v>
+        <v>67253000</v>
       </c>
     </row>
     <row r="72">
@@ -1878,19 +1878,19 @@
         <v>46052</v>
       </c>
       <c r="B72" t="n">
-        <v>438.1699022937122</v>
+        <v>254.9314433110553</v>
       </c>
       <c r="C72" t="n">
-        <v>438.5989157576861</v>
+        <v>261.6551472598355</v>
       </c>
       <c r="D72" t="n">
-        <v>425.4788680207893</v>
+        <v>251.9442331321547</v>
       </c>
       <c r="E72" t="n">
-        <v>429.3101196289062</v>
+        <v>259.2374267578125</v>
       </c>
       <c r="F72" t="n">
-        <v>58566800</v>
+        <v>92443400</v>
       </c>
     </row>
     <row r="73">
@@ -1898,19 +1898,19 @@
         <v>46055</v>
       </c>
       <c r="B73" t="n">
-        <v>429.2602343395754</v>
+        <v>259.7869174093499</v>
       </c>
       <c r="C73" t="n">
-        <v>429.7590957240154</v>
+        <v>270.2371306501278</v>
       </c>
       <c r="D73" t="n">
-        <v>421.28843915961</v>
+        <v>258.9676766447768</v>
       </c>
       <c r="E73" t="n">
-        <v>422.4058837890625</v>
+        <v>269.7575988769531</v>
       </c>
       <c r="F73" t="n">
-        <v>42219900</v>
+        <v>73913400</v>
       </c>
     </row>
     <row r="74">
@@ -1918,19 +1918,19 @@
         <v>46056</v>
       </c>
       <c r="B74" t="n">
-        <v>421.0489834358989</v>
+        <v>268.9483513556569</v>
       </c>
       <c r="C74" t="n">
-        <v>421.0888704228976</v>
+        <v>271.6258386480508</v>
       </c>
       <c r="D74" t="n">
-        <v>407.6296003977664</v>
+        <v>267.3598109321867</v>
       </c>
       <c r="E74" t="n">
-        <v>410.2735595703125</v>
+        <v>269.2280883789062</v>
       </c>
       <c r="F74" t="n">
-        <v>61424100</v>
+        <v>64394700</v>
       </c>
     </row>
     <row r="75">
@@ -1938,19 +1938,19 @@
         <v>46057</v>
       </c>
       <c r="B75" t="n">
-        <v>410.0640575889883</v>
+        <v>272.03545112075</v>
       </c>
       <c r="C75" t="n">
-        <v>418.8440057668918</v>
+        <v>278.6892285045384</v>
       </c>
       <c r="D75" t="n">
-        <v>408.3080557741746</v>
+        <v>272.03545112075</v>
       </c>
       <c r="E75" t="n">
-        <v>413.2467956542969</v>
+        <v>276.2315063476562</v>
       </c>
       <c r="F75" t="n">
-        <v>45012400</v>
+        <v>90545700</v>
       </c>
     </row>
     <row r="76">
@@ -1958,19 +1958,19 @@
         <v>46058</v>
       </c>
       <c r="B76" t="n">
-        <v>406.5121603821183</v>
+        <v>277.8699949435269</v>
       </c>
       <c r="C76" t="n">
-        <v>407.3701873334875</v>
+        <v>279.2387093202658</v>
       </c>
       <c r="D76" t="n">
-        <v>391.4265972483441</v>
+        <v>272.9745818081728</v>
       </c>
       <c r="E76" t="n">
-        <v>392.7735290527344</v>
+        <v>275.6520690917969</v>
       </c>
       <c r="F76" t="n">
-        <v>66289200</v>
+        <v>52977400</v>
       </c>
     </row>
     <row r="77">
@@ -1978,19 +1978,19 @@
         <v>46059</v>
       </c>
       <c r="B77" t="n">
-        <v>398.2609865133262</v>
+        <v>276.8609202349588</v>
       </c>
       <c r="C77" t="n">
-        <v>400.875015135043</v>
+        <v>280.6473855638201</v>
       </c>
       <c r="D77" t="n">
-        <v>392.0252195920243</v>
+        <v>276.6710954236804</v>
       </c>
       <c r="E77" t="n">
-        <v>400.2265014648438</v>
+        <v>277.8599853515625</v>
       </c>
       <c r="F77" t="n">
-        <v>53515300</v>
+        <v>50453400</v>
       </c>
     </row>
     <row r="78">
@@ -1998,19 +1998,19 @@
         <v>46062</v>
       </c>
       <c r="B78" t="n">
-        <v>403.9280678877113</v>
+        <v>277.9100036621094</v>
       </c>
       <c r="C78" t="n">
-        <v>413.9452129833927</v>
+        <v>278.2000122070312</v>
       </c>
       <c r="D78" t="n">
-        <v>399.9571203178888</v>
+        <v>271.7000122070312</v>
       </c>
       <c r="E78" t="n">
-        <v>412.6581420898438</v>
+        <v>274.6199951171875</v>
       </c>
       <c r="F78" t="n">
-        <v>45480500</v>
+        <v>44623400</v>
       </c>
     </row>
     <row r="79">
@@ -2018,19 +2018,19 @@
         <v>46063</v>
       </c>
       <c r="B79" t="n">
-        <v>418.6644027817824</v>
+        <v>274.8900146484375</v>
       </c>
       <c r="C79" t="n">
-        <v>422.7151545880433</v>
+        <v>275.3699951171875</v>
       </c>
       <c r="D79" t="n">
-        <v>411.76017861217</v>
+        <v>272.9400024414062</v>
       </c>
       <c r="E79" t="n">
-        <v>412.328857421875</v>
+        <v>273.6799926757812</v>
       </c>
       <c r="F79" t="n">
-        <v>44857900</v>
+        <v>34376900</v>
       </c>
     </row>
     <row r="80">
@@ -2038,19 +2038,19 @@
         <v>46064</v>
       </c>
       <c r="B80" t="n">
-        <v>415.2322299614449</v>
+        <v>274.7000122070312</v>
       </c>
       <c r="C80" t="n">
-        <v>415.5115911022014</v>
+        <v>280.1799926757812</v>
       </c>
       <c r="D80" t="n">
-        <v>400.096793508188</v>
+        <v>274.4500122070312</v>
       </c>
       <c r="E80" t="n">
-        <v>403.4491271972656</v>
+        <v>275.5</v>
       </c>
       <c r="F80" t="n">
-        <v>42491000</v>
+        <v>51931300</v>
       </c>
     </row>
     <row r="81">
@@ -2058,19 +2058,19 @@
         <v>46065</v>
       </c>
       <c r="B81" t="n">
-        <v>404.0777037056333</v>
+        <v>275.5899963378906</v>
       </c>
       <c r="C81" t="n">
-        <v>405.2749831551046</v>
+        <v>275.7200012207031</v>
       </c>
       <c r="D81" t="n">
-        <v>397.1036315998776</v>
+        <v>260.1799926757812</v>
       </c>
       <c r="E81" t="n">
-        <v>400.9248962402344</v>
+        <v>261.7300109863281</v>
       </c>
       <c r="F81" t="n">
-        <v>40802400</v>
+        <v>81077200</v>
       </c>
     </row>
     <row r="82">
@@ -2078,19 +2078,19 @@
         <v>46066</v>
       </c>
       <c r="B82" t="n">
-        <v>403.528974460687</v>
+        <v>262.010009765625</v>
       </c>
       <c r="C82" t="n">
-        <v>404.6164885937555</v>
+        <v>262.2300109863281</v>
       </c>
       <c r="D82" t="n">
-        <v>397.1435245648219</v>
+        <v>255.4499969482422</v>
       </c>
       <c r="E82" t="n">
-        <v>400.4060974121094</v>
+        <v>255.7799987792969</v>
       </c>
       <c r="F82" t="n">
-        <v>34091600</v>
+        <v>56290700</v>
       </c>
     </row>
     <row r="83">
@@ -2098,19 +2098,19 @@
         <v>46070</v>
       </c>
       <c r="B83" t="n">
-        <v>398.3108793269315</v>
+        <v>258.0499877929688</v>
       </c>
       <c r="C83" t="n">
-        <v>399.6079067287359</v>
+        <v>266.2900085449219</v>
       </c>
       <c r="D83" t="n">
-        <v>393.6315571718042</v>
+        <v>255.5399932861328</v>
       </c>
       <c r="E83" t="n">
-        <v>395.9562377929688</v>
+        <v>263.8800048828125</v>
       </c>
       <c r="F83" t="n">
-        <v>32078800</v>
+        <v>58469100</v>
       </c>
     </row>
     <row r="84">
@@ -2118,19 +2118,19 @@
         <v>46071</v>
       </c>
       <c r="B84" t="n">
-        <v>397.2233488345012</v>
+        <v>263.6000061035156</v>
       </c>
       <c r="C84" t="n">
-        <v>401.6432531481791</v>
+        <v>266.8200073242188</v>
       </c>
       <c r="D84" t="n">
-        <v>395.4174731587443</v>
+        <v>262.4500122070312</v>
       </c>
       <c r="E84" t="n">
-        <v>398.6900024414062</v>
+        <v>264.3500061035156</v>
       </c>
       <c r="F84" t="n">
-        <v>23223400</v>
+        <v>34203300</v>
       </c>
     </row>
     <row r="85">
@@ -2138,19 +2138,19 @@
         <v>46072</v>
       </c>
       <c r="B85" t="n">
-        <v>400.6900024414062</v>
+        <v>262.6000061035156</v>
       </c>
       <c r="C85" t="n">
-        <v>404.4299926757812</v>
+        <v>264.4800109863281</v>
       </c>
       <c r="D85" t="n">
-        <v>396.6700134277344</v>
+        <v>260.0499877929688</v>
       </c>
       <c r="E85" t="n">
-        <v>398.4599914550781</v>
+        <v>260.5799865722656</v>
       </c>
       <c r="F85" t="n">
-        <v>28234000</v>
+        <v>30845300</v>
       </c>
     </row>
     <row r="86">
@@ -2158,19 +2158,19 @@
         <v>46073</v>
       </c>
       <c r="B86" t="n">
-        <v>396.1099853515625</v>
+        <v>258.9700012207031</v>
       </c>
       <c r="C86" t="n">
-        <v>400.1199951171875</v>
+        <v>264.75</v>
       </c>
       <c r="D86" t="n">
-        <v>395.1600036621094</v>
+        <v>258.1600036621094</v>
       </c>
       <c r="E86" t="n">
-        <v>397.2300109863281</v>
+        <v>264.5799865722656</v>
       </c>
       <c r="F86" t="n">
-        <v>34015200</v>
+        <v>42070500</v>
       </c>
     </row>
     <row r="87">
@@ -2178,19 +2178,19 @@
         <v>46076</v>
       </c>
       <c r="B87" t="n">
-        <v>395</v>
+        <v>263.489990234375</v>
       </c>
       <c r="C87" t="n">
-        <v>395.3599853515625</v>
+        <v>269.4299926757812</v>
       </c>
       <c r="D87" t="n">
-        <v>383.1000061035156</v>
+        <v>263.3800048828125</v>
       </c>
       <c r="E87" t="n">
-        <v>384.4700012207031</v>
+        <v>266.1799926757812</v>
       </c>
       <c r="F87" t="n">
-        <v>43238300</v>
+        <v>37308200</v>
       </c>
     </row>
     <row r="88">
@@ -2198,19 +2198,19 @@
         <v>46077</v>
       </c>
       <c r="B88" t="n">
-        <v>384.1400146484375</v>
+        <v>267.8599853515625</v>
       </c>
       <c r="C88" t="n">
-        <v>389.3599853515625</v>
+        <v>274.8900146484375</v>
       </c>
       <c r="D88" t="n">
-        <v>381.7099914550781</v>
+        <v>267.7099914550781</v>
       </c>
       <c r="E88" t="n">
-        <v>389</v>
+        <v>272.1400146484375</v>
       </c>
       <c r="F88" t="n">
-        <v>33884700</v>
+        <v>47014600</v>
       </c>
     </row>
     <row r="89">
@@ -2218,19 +2218,19 @@
         <v>46078</v>
       </c>
       <c r="B89" t="n">
-        <v>390.5299987792969</v>
+        <v>271.7799987792969</v>
       </c>
       <c r="C89" t="n">
-        <v>401.4700012207031</v>
+        <v>274.9400024414062</v>
       </c>
       <c r="D89" t="n">
-        <v>390.1600036621094</v>
+        <v>271.0499877929688</v>
       </c>
       <c r="E89" t="n">
-        <v>400.6000061035156</v>
+        <v>274.2300109863281</v>
       </c>
       <c r="F89" t="n">
-        <v>43625500</v>
+        <v>33714300</v>
       </c>
     </row>
     <row r="90">
@@ -2238,19 +2238,19 @@
         <v>46079</v>
       </c>
       <c r="B90" t="n">
-        <v>404.7099914550781</v>
+        <v>274.9500122070312</v>
       </c>
       <c r="C90" t="n">
-        <v>407.489990234375</v>
+        <v>276.1099853515625</v>
       </c>
       <c r="D90" t="n">
-        <v>398.739990234375</v>
+        <v>270.7999877929688</v>
       </c>
       <c r="E90" t="n">
-        <v>401.7200012207031</v>
+        <v>272.9500122070312</v>
       </c>
       <c r="F90" t="n">
-        <v>34405900</v>
+        <v>32345100</v>
       </c>
     </row>
     <row r="91">
@@ -2258,19 +2258,19 @@
         <v>46080</v>
       </c>
       <c r="B91" t="n">
-        <v>390.8800048828125</v>
+        <v>272.8099975585938</v>
       </c>
       <c r="C91" t="n">
-        <v>396.8200073242188</v>
+        <v>272.8099975585938</v>
       </c>
       <c r="D91" t="n">
-        <v>389.8800048828125</v>
+        <v>262.8900146484375</v>
       </c>
       <c r="E91" t="n">
-        <v>392.739990234375</v>
+        <v>264.1799926757812</v>
       </c>
       <c r="F91" t="n">
-        <v>51367200</v>
+        <v>72366500</v>
       </c>
     </row>
     <row r="92">
@@ -2278,19 +2278,19 @@
         <v>46083</v>
       </c>
       <c r="B92" t="n">
-        <v>392.8599853515625</v>
+        <v>262.4100036621094</v>
       </c>
       <c r="C92" t="n">
-        <v>401.1900024414062</v>
+        <v>266.5299987792969</v>
       </c>
       <c r="D92" t="n">
-        <v>390.6300048828125</v>
+        <v>260.2000122070312</v>
       </c>
       <c r="E92" t="n">
-        <v>398.5499877929688</v>
+        <v>264.7200012207031</v>
       </c>
       <c r="F92" t="n">
-        <v>35474900</v>
+        <v>41827900</v>
       </c>
     </row>
     <row r="93">
@@ -2298,19 +2298,19 @@
         <v>46084</v>
       </c>
       <c r="B93" t="n">
-        <v>393.1400146484375</v>
+        <v>263.4800109863281</v>
       </c>
       <c r="C93" t="n">
-        <v>406.7000122070312</v>
+        <v>265.5599975585938</v>
       </c>
       <c r="D93" t="n">
-        <v>392.6700134277344</v>
+        <v>260.1300048828125</v>
       </c>
       <c r="E93" t="n">
-        <v>403.9299926757812</v>
+        <v>263.75</v>
       </c>
       <c r="F93" t="n">
-        <v>38199200</v>
+        <v>38568900</v>
       </c>
     </row>
     <row r="94">
@@ -2318,19 +2318,19 @@
         <v>46085</v>
       </c>
       <c r="B94" t="n">
-        <v>401.2699890136719</v>
+        <v>264.6499938964844</v>
       </c>
       <c r="C94" t="n">
-        <v>411.0299987792969</v>
+        <v>266.1499938964844</v>
       </c>
       <c r="D94" t="n">
-        <v>400.3099975585938</v>
+        <v>261.4200134277344</v>
       </c>
       <c r="E94" t="n">
-        <v>405.2000122070312</v>
+        <v>262.5199890136719</v>
       </c>
       <c r="F94" t="n">
-        <v>35808000</v>
+        <v>39803100</v>
       </c>
     </row>
     <row r="95">
@@ -2338,19 +2338,19 @@
         <v>46086</v>
       </c>
       <c r="B95" t="n">
-        <v>404.4200134277344</v>
+        <v>260.7900085449219</v>
       </c>
       <c r="C95" t="n">
-        <v>411.6099853515625</v>
+        <v>261.5599975585938</v>
       </c>
       <c r="D95" t="n">
-        <v>404.3999938964844</v>
+        <v>257.25</v>
       </c>
       <c r="E95" t="n">
-        <v>410.6799926757812</v>
+        <v>260.2900085449219</v>
       </c>
       <c r="F95" t="n">
-        <v>39001300</v>
+        <v>49658600</v>
       </c>
     </row>
     <row r="96">
@@ -2358,19 +2358,19 @@
         <v>46087</v>
       </c>
       <c r="B96" t="n">
-        <v>409.2000122070312</v>
+        <v>258.6300048828125</v>
       </c>
       <c r="C96" t="n">
-        <v>413.0499877929688</v>
+        <v>258.7699890136719</v>
       </c>
       <c r="D96" t="n">
-        <v>408.510009765625</v>
+        <v>254.3699951171875</v>
       </c>
       <c r="E96" t="n">
-        <v>408.9599914550781</v>
+        <v>257.4599914550781</v>
       </c>
       <c r="F96" t="n">
-        <v>31123900</v>
+        <v>41120000</v>
       </c>
     </row>
     <row r="97">
@@ -2378,19 +2378,19 @@
         <v>46090</v>
       </c>
       <c r="B97" t="n">
-        <v>404.9200134277344</v>
+        <v>255.6900024414062</v>
       </c>
       <c r="C97" t="n">
-        <v>410.2099914550781</v>
+        <v>261.1499938964844</v>
       </c>
       <c r="D97" t="n">
-        <v>403.5</v>
+        <v>253.6799926757812</v>
       </c>
       <c r="E97" t="n">
-        <v>409.4100036621094</v>
+        <v>259.8800048828125</v>
       </c>
       <c r="F97" t="n">
-        <v>30131900</v>
+        <v>38218500</v>
       </c>
     </row>
     <row r="98">
@@ -2398,19 +2398,19 @@
         <v>46091</v>
       </c>
       <c r="B98" t="n">
-        <v>410.0299987792969</v>
+        <v>257.6499938964844</v>
       </c>
       <c r="C98" t="n">
-        <v>410.2000122070312</v>
+        <v>262.4800109863281</v>
       </c>
       <c r="D98" t="n">
-        <v>402.9299926757812</v>
+        <v>256.9500122070312</v>
       </c>
       <c r="E98" t="n">
-        <v>405.760009765625</v>
+        <v>260.8299865722656</v>
       </c>
       <c r="F98" t="n">
-        <v>31706400</v>
+        <v>30590800</v>
       </c>
     </row>
     <row r="99">
@@ -2418,19 +2418,19 @@
         <v>46092</v>
       </c>
       <c r="B99" t="n">
-        <v>405.5700073242188</v>
+        <v>261.0899963378906</v>
       </c>
       <c r="C99" t="n">
-        <v>409.010009765625</v>
+        <v>262.1300048828125</v>
       </c>
       <c r="D99" t="n">
-        <v>401.5899963378906</v>
+        <v>259.5499877929688</v>
       </c>
       <c r="E99" t="n">
-        <v>404.8800048828125</v>
+        <v>260.8099975585938</v>
       </c>
       <c r="F99" t="n">
-        <v>25512100</v>
+        <v>26218900</v>
       </c>
     </row>
     <row r="100">
@@ -2438,19 +2438,19 @@
         <v>46093</v>
       </c>
       <c r="B100" t="n">
-        <v>404.6300048828125</v>
+        <v>258.6600036621094</v>
       </c>
       <c r="C100" t="n">
-        <v>406.1199951171875</v>
+        <v>258.9500122070312</v>
       </c>
       <c r="D100" t="n">
-        <v>401.7099914550781</v>
+        <v>254.1799926757812</v>
       </c>
       <c r="E100" t="n">
-        <v>401.8599853515625</v>
+        <v>255.7599945068359</v>
       </c>
       <c r="F100" t="n">
-        <v>27263900</v>
+        <v>40794000</v>
       </c>
     </row>
     <row r="101">
@@ -2458,19 +2458,19 @@
         <v>46094</v>
       </c>
       <c r="B101" t="n">
-        <v>401</v>
+        <v>255.4799957275391</v>
       </c>
       <c r="C101" t="n">
-        <v>404.7999877929688</v>
+        <v>256.3299865722656</v>
       </c>
       <c r="D101" t="n">
-        <v>394.25</v>
+        <v>249.5200042724609</v>
       </c>
       <c r="E101" t="n">
-        <v>395.5499877929688</v>
+        <v>250.1199951171875</v>
       </c>
       <c r="F101" t="n">
-        <v>26848000</v>
+        <v>36930000</v>
       </c>
     </row>
     <row r="102">
@@ -2478,19 +2478,19 @@
         <v>46097</v>
       </c>
       <c r="B102" t="n">
-        <v>398.0700073242188</v>
+        <v>252.1100006103516</v>
       </c>
       <c r="C102" t="n">
-        <v>400.6300048828125</v>
+        <v>253.8899993896484</v>
       </c>
       <c r="D102" t="n">
-        <v>394.7900085449219</v>
+        <v>249.8800048828125</v>
       </c>
       <c r="E102" t="n">
-        <v>399.9500122070312</v>
+        <v>252.8200073242188</v>
       </c>
       <c r="F102" t="n">
-        <v>27733700</v>
+        <v>32074200</v>
       </c>
     </row>
     <row r="103">
@@ -2498,19 +2498,19 @@
         <v>46098</v>
       </c>
       <c r="B103" t="n">
-        <v>400.2699890136719</v>
+        <v>252.9600067138672</v>
       </c>
       <c r="C103" t="n">
-        <v>404.3999938964844</v>
+        <v>255.1300048828125</v>
       </c>
       <c r="D103" t="n">
-        <v>397.75</v>
+        <v>252.1799926757812</v>
       </c>
       <c r="E103" t="n">
-        <v>399.4100036621094</v>
+        <v>254.2299957275391</v>
       </c>
       <c r="F103" t="n">
-        <v>26228300</v>
+        <v>32361600</v>
       </c>
     </row>
     <row r="104">
@@ -2518,19 +2518,19 @@
         <v>46099</v>
       </c>
       <c r="B104" t="n">
-        <v>397.1300048828125</v>
+        <v>252.6300048828125</v>
       </c>
       <c r="C104" t="n">
-        <v>398</v>
+        <v>254.9400024414062</v>
       </c>
       <c r="D104" t="n">
-        <v>391</v>
+        <v>249</v>
       </c>
       <c r="E104" t="n">
-        <v>391.7900085449219</v>
+        <v>249.9400024414062</v>
       </c>
       <c r="F104" t="n">
-        <v>25908500</v>
+        <v>35757900</v>
       </c>
     </row>
     <row r="105">
@@ -2538,19 +2538,19 @@
         <v>46100</v>
       </c>
       <c r="B105" t="n">
-        <v>390.1000061035156</v>
+        <v>249.3999938964844</v>
       </c>
       <c r="C105" t="n">
-        <v>392.489990234375</v>
+        <v>251.8300018310547</v>
       </c>
       <c r="D105" t="n">
-        <v>387.0599975585938</v>
+        <v>247.3000030517578</v>
       </c>
       <c r="E105" t="n">
-        <v>389.0199890136719</v>
+        <v>248.9600067138672</v>
       </c>
       <c r="F105" t="n">
-        <v>25138800</v>
+        <v>34864100</v>
       </c>
     </row>
     <row r="106">
@@ -2558,19 +2558,19 @@
         <v>46101</v>
       </c>
       <c r="B106" t="n">
-        <v>386.7900085449219</v>
+        <v>247.9799957275391</v>
       </c>
       <c r="C106" t="n">
-        <v>387</v>
+        <v>249.1999969482422</v>
       </c>
       <c r="D106" t="n">
-        <v>380.1199951171875</v>
+        <v>246</v>
       </c>
       <c r="E106" t="n">
-        <v>381.8699951171875</v>
+        <v>247.9900054931641</v>
       </c>
       <c r="F106" t="n">
-        <v>50853200</v>
+        <v>88331100</v>
       </c>
     </row>
     <row r="107">
@@ -2578,19 +2578,19 @@
         <v>46104</v>
       </c>
       <c r="B107" t="n">
-        <v>383.8999938964844</v>
+        <v>253.9700012207031</v>
       </c>
       <c r="C107" t="n">
-        <v>387.2099914550781</v>
+        <v>254.6000061035156</v>
       </c>
       <c r="D107" t="n">
-        <v>381.6799926757812</v>
+        <v>250.2799987792969</v>
       </c>
       <c r="E107" t="n">
-        <v>383</v>
+        <v>251.4900054931641</v>
       </c>
       <c r="F107" t="n">
-        <v>29680100</v>
+        <v>40546100</v>
       </c>
     </row>
     <row r="108">
@@ -2598,19 +2598,19 @@
         <v>46105</v>
       </c>
       <c r="B108" t="n">
-        <v>382.3599853515625</v>
+        <v>250.3500061035156</v>
       </c>
       <c r="C108" t="n">
-        <v>382.4700012207031</v>
+        <v>254.8300018310547</v>
       </c>
       <c r="D108" t="n">
-        <v>371.8500061035156</v>
+        <v>249.5500030517578</v>
       </c>
       <c r="E108" t="n">
-        <v>372.739990234375</v>
+        <v>251.6399993896484</v>
       </c>
       <c r="F108" t="n">
-        <v>42733600</v>
+        <v>45152300</v>
       </c>
     </row>
     <row r="109">
@@ -2618,19 +2618,19 @@
         <v>46106</v>
       </c>
       <c r="B109" t="n">
-        <v>376.9200134277344</v>
+        <v>254.1000061035156</v>
       </c>
       <c r="C109" t="n">
-        <v>377.0599975585938</v>
+        <v>255</v>
       </c>
       <c r="D109" t="n">
-        <v>369.6300048828125</v>
+        <v>251.6000061035156</v>
       </c>
       <c r="E109" t="n">
-        <v>371.0400085449219</v>
+        <v>252.6199951171875</v>
       </c>
       <c r="F109" t="n">
-        <v>31181200</v>
+        <v>28476700</v>
       </c>
     </row>
     <row r="110">
@@ -2638,19 +2638,19 @@
         <v>46107</v>
       </c>
       <c r="B110" t="n">
-        <v>370.8200073242188</v>
+        <v>252.1199951171875</v>
       </c>
       <c r="C110" t="n">
-        <v>374.7200012207031</v>
+        <v>257</v>
       </c>
       <c r="D110" t="n">
-        <v>365.1900024414062</v>
+        <v>250.7700042724609</v>
       </c>
       <c r="E110" t="n">
-        <v>365.9700012207031</v>
+        <v>252.8899993896484</v>
       </c>
       <c r="F110" t="n">
-        <v>36836600</v>
+        <v>41796700</v>
       </c>
     </row>
     <row r="111">
@@ -2658,19 +2658,19 @@
         <v>46108</v>
       </c>
       <c r="B111" t="n">
-        <v>361.8999938964844</v>
+        <v>253.8999938964844</v>
       </c>
       <c r="C111" t="n">
-        <v>362.4500122070312</v>
+        <v>255.4900054931641</v>
       </c>
       <c r="D111" t="n">
-        <v>356.510009765625</v>
+        <v>248.0700073242188</v>
       </c>
       <c r="E111" t="n">
-        <v>356.7699890136719</v>
+        <v>248.8000030517578</v>
       </c>
       <c r="F111" t="n">
-        <v>37883400</v>
+        <v>47900000</v>
       </c>
     </row>
     <row r="112">
@@ -2678,19 +2678,19 @@
         <v>46111</v>
       </c>
       <c r="B112" t="n">
-        <v>361.8999938964844</v>
+        <v>250.0700073242188</v>
       </c>
       <c r="C112" t="n">
-        <v>365.3599853515625</v>
+        <v>250.8699951171875</v>
       </c>
       <c r="D112" t="n">
-        <v>356.2799987792969</v>
+        <v>245.5099945068359</v>
       </c>
       <c r="E112" t="n">
-        <v>358.9599914550781</v>
+        <v>246.6300048828125</v>
       </c>
       <c r="F112" t="n">
-        <v>44797000</v>
+        <v>39446200</v>
       </c>
     </row>
     <row r="113">
@@ -2698,19 +2698,19 @@
         <v>46112</v>
       </c>
       <c r="B113" t="n">
-        <v>364.5499877929688</v>
+        <v>247.9100036621094</v>
       </c>
       <c r="C113" t="n">
-        <v>372.8999938964844</v>
+        <v>255.4799957275391</v>
       </c>
       <c r="D113" t="n">
-        <v>363.0700073242188</v>
+        <v>247.1000061035156</v>
       </c>
       <c r="E113" t="n">
-        <v>370.1700134277344</v>
+        <v>253.7899932861328</v>
       </c>
       <c r="F113" t="n">
-        <v>45244400</v>
+        <v>49598100</v>
       </c>
     </row>
     <row r="114">
@@ -2718,19 +2718,19 @@
         <v>46113</v>
       </c>
       <c r="B114" t="n">
-        <v>373.489990234375</v>
+        <v>254.0800018310547</v>
       </c>
       <c r="C114" t="n">
-        <v>373.989990234375</v>
+        <v>256.1799926757812</v>
       </c>
       <c r="D114" t="n">
-        <v>368.2000122070312</v>
+        <v>253.3300018310547</v>
       </c>
       <c r="E114" t="n">
-        <v>369.3699951171875</v>
+        <v>255.6300048828125</v>
       </c>
       <c r="F114" t="n">
-        <v>29417200</v>
+        <v>40059400</v>
       </c>
     </row>
     <row r="115">
@@ -2738,19 +2738,19 @@
         <v>46114</v>
       </c>
       <c r="B115" t="n">
-        <v>367.2099914550781</v>
+        <v>254.1999969482422</v>
       </c>
       <c r="C115" t="n">
-        <v>373.6400146484375</v>
+        <v>256.1300048828125</v>
       </c>
       <c r="D115" t="n">
-        <v>364.1499938964844</v>
+        <v>250.6499938964844</v>
       </c>
       <c r="E115" t="n">
-        <v>373.4599914550781</v>
+        <v>255.9199981689453</v>
       </c>
       <c r="F115" t="n">
-        <v>24099100</v>
+        <v>31289400</v>
       </c>
     </row>
     <row r="116">
@@ -2758,19 +2758,19 @@
         <v>46118</v>
       </c>
       <c r="B116" t="n">
-        <v>373.489990234375</v>
+        <v>256.510009765625</v>
       </c>
       <c r="C116" t="n">
-        <v>373.7300109863281</v>
+        <v>262.1600036621094</v>
       </c>
       <c r="D116" t="n">
-        <v>369.5</v>
+        <v>256.4599914550781</v>
       </c>
       <c r="E116" t="n">
-        <v>372.8800048828125</v>
+        <v>258.8599853515625</v>
       </c>
       <c r="F116" t="n">
-        <v>16146600</v>
+        <v>29329900</v>
       </c>
     </row>
     <row r="117">
@@ -2778,19 +2778,19 @@
         <v>46119</v>
       </c>
       <c r="B117" t="n">
-        <v>370.3399963378906</v>
+        <v>256.1600036621094</v>
       </c>
       <c r="C117" t="n">
-        <v>372.4500122070312</v>
+        <v>256.2000122070312</v>
       </c>
       <c r="D117" t="n">
-        <v>366.5599975585938</v>
+        <v>245.6999969482422</v>
       </c>
       <c r="E117" t="n">
-        <v>372.2900085449219</v>
+        <v>253.5</v>
       </c>
       <c r="F117" t="n">
-        <v>21443300</v>
+        <v>62148000</v>
       </c>
     </row>
     <row r="118">
@@ -2798,19 +2798,19 @@
         <v>46120</v>
       </c>
       <c r="B118" t="n">
-        <v>384.9800109863281</v>
+        <v>258.4500122070312</v>
       </c>
       <c r="C118" t="n">
-        <v>385</v>
+        <v>259.75</v>
       </c>
       <c r="D118" t="n">
-        <v>371.4100036621094</v>
+        <v>256.5299987792969</v>
       </c>
       <c r="E118" t="n">
-        <v>374.3299865722656</v>
+        <v>258.8999938964844</v>
       </c>
       <c r="F118" t="n">
-        <v>33064800</v>
+        <v>41032800</v>
       </c>
     </row>
     <row r="119">
@@ -2818,19 +2818,19 @@
         <v>46121</v>
       </c>
       <c r="B119" t="n">
-        <v>372.5</v>
+        <v>259</v>
       </c>
       <c r="C119" t="n">
-        <v>373.5</v>
+        <v>261.1199951171875</v>
       </c>
       <c r="D119" t="n">
-        <v>367.0499877929688</v>
+        <v>256.0700073242188</v>
       </c>
       <c r="E119" t="n">
-        <v>373.0700073242188</v>
+        <v>260.489990234375</v>
       </c>
       <c r="F119" t="n">
-        <v>30435300</v>
+        <v>28121600</v>
       </c>
     </row>
     <row r="120">
@@ -2838,19 +2838,19 @@
         <v>46122</v>
       </c>
       <c r="B120" t="n">
-        <v>372.9800109863281</v>
+        <v>259.9800109863281</v>
       </c>
       <c r="C120" t="n">
-        <v>375.6400146484375</v>
+        <v>262.1900024414062</v>
       </c>
       <c r="D120" t="n">
-        <v>370.0299987792969</v>
+        <v>259.0199890136719</v>
       </c>
       <c r="E120" t="n">
-        <v>370.8699951171875</v>
+        <v>260.4800109863281</v>
       </c>
       <c r="F120" t="n">
-        <v>28111100</v>
+        <v>31291500</v>
       </c>
     </row>
     <row r="121">
@@ -2858,19 +2858,19 @@
         <v>46125</v>
       </c>
       <c r="B121" t="n">
-        <v>373.6099853515625</v>
+        <v>259.7300109863281</v>
       </c>
       <c r="C121" t="n">
-        <v>384.5400085449219</v>
+        <v>260.1799926757812</v>
       </c>
       <c r="D121" t="n">
-        <v>371.0199890136719</v>
+        <v>256.6600036621094</v>
       </c>
       <c r="E121" t="n">
-        <v>384.3699951171875</v>
+        <v>259.2000122070312</v>
       </c>
       <c r="F121" t="n">
-        <v>35745800</v>
+        <v>36234700</v>
       </c>
     </row>
     <row r="122">
@@ -2878,19 +2878,19 @@
         <v>46126</v>
       </c>
       <c r="B122" t="n">
-        <v>387.9200134277344</v>
+        <v>259.25</v>
       </c>
       <c r="C122" t="n">
-        <v>394.6900024414062</v>
+        <v>261.9299926757812</v>
       </c>
       <c r="D122" t="n">
-        <v>386.5199890136719</v>
+        <v>257.1900024414062</v>
       </c>
       <c r="E122" t="n">
-        <v>393.1099853515625</v>
+        <v>258.8299865722656</v>
       </c>
       <c r="F122" t="n">
-        <v>37504500</v>
+        <v>48370700</v>
       </c>
     </row>
     <row r="123">
@@ -2898,19 +2898,39 @@
         <v>46127</v>
       </c>
       <c r="B123" t="n">
-        <v>398</v>
+        <v>258.1600036621094</v>
       </c>
       <c r="C123" t="n">
-        <v>414.3699951171875</v>
+        <v>266.5599975585938</v>
       </c>
       <c r="D123" t="n">
-        <v>396.7300109863281</v>
+        <v>257.8099975585938</v>
       </c>
       <c r="E123" t="n">
-        <v>411.2200012207031</v>
+        <v>266.4299926757812</v>
       </c>
       <c r="F123" t="n">
-        <v>44793300</v>
+        <v>49735000</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B124" t="n">
+        <v>266.7999877929688</v>
+      </c>
+      <c r="C124" t="n">
+        <v>267.1600036621094</v>
+      </c>
+      <c r="D124" t="n">
+        <v>261.2699890136719</v>
+      </c>
+      <c r="E124" t="n">
+        <v>263.9599914550781</v>
+      </c>
+      <c r="F124" t="n">
+        <v>24583355</v>
       </c>
     </row>
   </sheetData>
@@ -2924,7 +2944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5397,6 +5417,26 @@
       </c>
       <c r="F123" t="n">
         <v>58138100</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B124" t="n">
+        <v>701.0599975585938</v>
+      </c>
+      <c r="C124" t="n">
+        <v>702.780029296875</v>
+      </c>
+      <c r="D124" t="n">
+        <v>698.530029296875</v>
+      </c>
+      <c r="E124" t="n">
+        <v>700.47998046875</v>
+      </c>
+      <c r="F124" t="n">
+        <v>31426463</v>
       </c>
     </row>
   </sheetData>
@@ -5410,7 +5450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5450,19 +5490,19 @@
         <v>45950</v>
       </c>
       <c r="B2" t="n">
-        <v>255.4032084113237</v>
+        <v>512.4788764440519</v>
       </c>
       <c r="C2" t="n">
-        <v>263.8770629877272</v>
+        <v>516.5519656323323</v>
       </c>
       <c r="D2" t="n">
-        <v>255.143708503654</v>
+        <v>511.3037703677804</v>
       </c>
       <c r="E2" t="n">
-        <v>261.7411193847656</v>
+        <v>514.6498413085938</v>
       </c>
       <c r="F2" t="n">
-        <v>90483000</v>
+        <v>14665600</v>
       </c>
     </row>
     <row r="3">
@@ -5470,19 +5510,19 @@
         <v>45951</v>
       </c>
       <c r="B3" t="n">
-        <v>261.3818200057694</v>
+        <v>515.3569857054445</v>
       </c>
       <c r="C3" t="n">
-        <v>264.7853366806196</v>
+        <v>516.5420602391357</v>
       </c>
       <c r="D3" t="n">
-        <v>261.3318968470685</v>
+        <v>510.9154330870712</v>
       </c>
       <c r="E3" t="n">
-        <v>262.2701110839844</v>
+        <v>515.5162963867188</v>
       </c>
       <c r="F3" t="n">
-        <v>46695900</v>
+        <v>15586200</v>
       </c>
     </row>
     <row r="4">
@@ -5490,19 +5530,19 @@
         <v>45952</v>
       </c>
       <c r="B4" t="n">
-        <v>262.1503352574342</v>
+        <v>518.9918584655633</v>
       </c>
       <c r="C4" t="n">
-        <v>262.349966966352</v>
+        <v>523.0549187669818</v>
       </c>
       <c r="D4" t="n">
-        <v>254.9440691826199</v>
+        <v>515.566101626736</v>
       </c>
       <c r="E4" t="n">
-        <v>257.9583435058594</v>
+        <v>518.3843383789062</v>
       </c>
       <c r="F4" t="n">
-        <v>45015300</v>
+        <v>18962700</v>
       </c>
     </row>
     <row r="5">
@@ -5510,19 +5550,19 @@
         <v>45953</v>
       </c>
       <c r="B5" t="n">
-        <v>259.4454820834593</v>
+        <v>520.2964530626382</v>
       </c>
       <c r="C5" t="n">
-        <v>260.1241811137136</v>
+        <v>521.7802730707533</v>
       </c>
       <c r="D5" t="n">
-        <v>257.5191611036844</v>
+        <v>516.4623598997719</v>
       </c>
       <c r="E5" t="n">
-        <v>259.0861511230469</v>
+        <v>518.404296875</v>
       </c>
       <c r="F5" t="n">
-        <v>32754900</v>
+        <v>14023500</v>
       </c>
     </row>
     <row r="6">
@@ -5530,19 +5570,19 @@
         <v>45954</v>
       </c>
       <c r="B6" t="n">
-        <v>260.6931034322695</v>
+        <v>520.6250388201142</v>
       </c>
       <c r="C6" t="n">
-        <v>263.6275126875418</v>
+        <v>523.1744351060786</v>
       </c>
       <c r="D6" t="n">
-        <v>258.6869175950168</v>
+        <v>518.5536961256696</v>
       </c>
       <c r="E6" t="n">
-        <v>262.3200073242188</v>
+        <v>521.441650390625</v>
       </c>
       <c r="F6" t="n">
-        <v>38253700</v>
+        <v>15532400</v>
       </c>
     </row>
     <row r="7">
@@ -5550,19 +5590,19 @@
         <v>45957</v>
       </c>
       <c r="B7" t="n">
-        <v>264.376098228409</v>
+        <v>529.577902779321</v>
       </c>
       <c r="C7" t="n">
-        <v>268.60802232244</v>
+        <v>532.3662956890146</v>
       </c>
       <c r="D7" t="n">
-        <v>264.1465248140549</v>
+        <v>526.819354031342</v>
       </c>
       <c r="E7" t="n">
-        <v>268.2986145019531</v>
+        <v>529.3189697265625</v>
       </c>
       <c r="F7" t="n">
-        <v>44888200</v>
+        <v>18734700</v>
       </c>
     </row>
     <row r="8">
@@ -5570,19 +5610,19 @@
         <v>45958</v>
       </c>
       <c r="B8" t="n">
-        <v>268.4782600095115</v>
+        <v>547.722348424072</v>
       </c>
       <c r="C8" t="n">
-        <v>269.3765722048576</v>
+        <v>551.4269140414981</v>
       </c>
       <c r="D8" t="n">
-        <v>267.6398616921066</v>
+        <v>538.5305910090683</v>
       </c>
       <c r="E8" t="n">
-        <v>268.4882507324219</v>
+        <v>539.8251953125</v>
       </c>
       <c r="F8" t="n">
-        <v>41534800</v>
+        <v>29986700</v>
       </c>
     </row>
     <row r="9">
@@ -5590,19 +5630,19 @@
         <v>45959</v>
       </c>
       <c r="B9" t="n">
-        <v>268.7677057947778</v>
+        <v>542.6832878753321</v>
       </c>
       <c r="C9" t="n">
-        <v>270.8936584399069</v>
+        <v>544.0077970763692</v>
       </c>
       <c r="D9" t="n">
-        <v>266.6018207191691</v>
+        <v>534.5072653816836</v>
       </c>
       <c r="E9" t="n">
-        <v>269.1869201660156</v>
+        <v>539.3073120117188</v>
       </c>
       <c r="F9" t="n">
-        <v>51086700</v>
+        <v>36023000</v>
       </c>
     </row>
     <row r="10">
@@ -5610,19 +5650,19 @@
         <v>45960</v>
       </c>
       <c r="B10" t="n">
-        <v>271.4725408872279</v>
+        <v>528.2831883129468</v>
       </c>
       <c r="C10" t="n">
-        <v>273.6184749716116</v>
+        <v>532.7545848667123</v>
       </c>
       <c r="D10" t="n">
-        <v>267.969239224885</v>
+        <v>519.9578228356851</v>
       </c>
       <c r="E10" t="n">
-        <v>270.8836669921875</v>
+        <v>523.582763671875</v>
       </c>
       <c r="F10" t="n">
-        <v>69886500</v>
+        <v>41023100</v>
       </c>
     </row>
     <row r="11">
@@ -5630,19 +5670,19 @@
         <v>45961</v>
       </c>
       <c r="B11" t="n">
-        <v>276.4630533049319</v>
+        <v>526.6898137654194</v>
       </c>
       <c r="C11" t="n">
-        <v>276.7924425807819</v>
+        <v>527.1279940743384</v>
       </c>
       <c r="D11" t="n">
-        <v>268.647962249571</v>
+        <v>512.9668501497666</v>
       </c>
       <c r="E11" t="n">
-        <v>269.8556518554688</v>
+        <v>515.6656494140625</v>
       </c>
       <c r="F11" t="n">
-        <v>86167100</v>
+        <v>34006400</v>
       </c>
     </row>
     <row r="12">
@@ -5650,19 +5690,19 @@
         <v>45964</v>
       </c>
       <c r="B12" t="n">
-        <v>269.9055662700252</v>
+        <v>517.657371934483</v>
       </c>
       <c r="C12" t="n">
-        <v>270.3347409275427</v>
+        <v>522.7860691817526</v>
       </c>
       <c r="D12" t="n">
-        <v>265.7434858777505</v>
+        <v>512.4590180581705</v>
       </c>
       <c r="E12" t="n">
-        <v>268.5381469726562</v>
+        <v>514.888916015625</v>
       </c>
       <c r="F12" t="n">
-        <v>50194600</v>
+        <v>22374700</v>
       </c>
     </row>
     <row r="13">
@@ -5670,19 +5710,19 @@
         <v>45965</v>
       </c>
       <c r="B13" t="n">
-        <v>267.8195068636227</v>
+        <v>509.6407695643784</v>
       </c>
       <c r="C13" t="n">
-        <v>270.9734988318123</v>
+        <v>513.4150529816625</v>
       </c>
       <c r="D13" t="n">
-        <v>267.1108661194202</v>
+        <v>505.7369892339689</v>
       </c>
       <c r="E13" t="n">
-        <v>269.5262756347656</v>
+        <v>512.2001342773438</v>
       </c>
       <c r="F13" t="n">
-        <v>49274800</v>
+        <v>20958700</v>
       </c>
     </row>
     <row r="14">
@@ -5690,19 +5730,19 @@
         <v>45966</v>
       </c>
       <c r="B14" t="n">
-        <v>268.0989800730272</v>
+        <v>511.1743415428253</v>
       </c>
       <c r="C14" t="n">
-        <v>271.1831284425123</v>
+        <v>512.6980347767452</v>
       </c>
       <c r="D14" t="n">
-        <v>266.4221834255846</v>
+        <v>504.4821687767013</v>
       </c>
       <c r="E14" t="n">
-        <v>269.6260986328125</v>
+        <v>505.0597839355469</v>
       </c>
       <c r="F14" t="n">
-        <v>43683100</v>
+        <v>23024300</v>
       </c>
     </row>
     <row r="15">
@@ -5710,19 +5750,19 @@
         <v>45967</v>
       </c>
       <c r="B15" t="n">
-        <v>267.3803770260164</v>
+        <v>503.5659922381216</v>
       </c>
       <c r="C15" t="n">
-        <v>272.8798740142925</v>
+        <v>503.6058351018555</v>
       </c>
       <c r="D15" t="n">
-        <v>267.3803770260164</v>
+        <v>493.7567764386794</v>
       </c>
       <c r="E15" t="n">
-        <v>269.2567749023438</v>
+        <v>495.0414428710938</v>
       </c>
       <c r="F15" t="n">
-        <v>51204000</v>
+        <v>27406500</v>
       </c>
     </row>
     <row r="16">
@@ -5730,19 +5770,19 @@
         <v>45968</v>
       </c>
       <c r="B16" t="n">
-        <v>269.2867154149515</v>
+        <v>494.8920702735404</v>
       </c>
       <c r="C16" t="n">
-        <v>271.7719991063764</v>
+        <v>497.3119999979126</v>
       </c>
       <c r="D16" t="n">
-        <v>266.2624809601513</v>
+        <v>491.2073803526309</v>
       </c>
       <c r="E16" t="n">
-        <v>267.9592590332031</v>
+        <v>494.7626037597656</v>
       </c>
       <c r="F16" t="n">
-        <v>48227400</v>
+        <v>24019800</v>
       </c>
     </row>
     <row r="17">
@@ -5750,19 +5790,19 @@
         <v>45971</v>
       </c>
       <c r="B17" t="n">
-        <v>268.7085692371889</v>
+        <v>497.9692915322098</v>
       </c>
       <c r="C17" t="n">
-        <v>273.4741297822401</v>
+        <v>504.7510881917551</v>
       </c>
       <c r="D17" t="n">
-        <v>267.2099714283653</v>
+        <v>496.734405833499</v>
       </c>
       <c r="E17" t="n">
-        <v>269.1781311035156</v>
+        <v>503.9046020507812</v>
       </c>
       <c r="F17" t="n">
-        <v>41312400</v>
+        <v>26101500</v>
       </c>
     </row>
     <row r="18">
@@ -5770,19 +5810,19 @@
         <v>45972</v>
       </c>
       <c r="B18" t="n">
-        <v>269.5577590596557</v>
+        <v>502.7095490222416</v>
       </c>
       <c r="C18" t="n">
-        <v>275.6520624227355</v>
+        <v>507.4896898672195</v>
       </c>
       <c r="D18" t="n">
-        <v>269.5477586519058</v>
+        <v>500.2697130079767</v>
       </c>
       <c r="E18" t="n">
-        <v>274.99267578125</v>
+        <v>506.573486328125</v>
       </c>
       <c r="F18" t="n">
-        <v>46208300</v>
+        <v>17980000</v>
       </c>
     </row>
     <row r="19">
@@ -5790,19 +5830,19 @@
         <v>45973</v>
       </c>
       <c r="B19" t="n">
-        <v>274.7429239716485</v>
+        <v>507.2506574723947</v>
       </c>
       <c r="C19" t="n">
-        <v>275.4722525277038</v>
+        <v>509.5511194130969</v>
       </c>
       <c r="D19" t="n">
-        <v>271.4460210796085</v>
+        <v>497.0530724082431</v>
       </c>
       <c r="E19" t="n">
-        <v>273.21435546875</v>
+        <v>509.0233154296875</v>
       </c>
       <c r="F19" t="n">
-        <v>48398000</v>
+        <v>26574900</v>
       </c>
     </row>
     <row r="20">
@@ -5810,19 +5850,19 @@
         <v>45974</v>
       </c>
       <c r="B20" t="n">
-        <v>273.8537435218178</v>
+        <v>508.1967287528611</v>
       </c>
       <c r="C20" t="n">
-        <v>276.4413491841305</v>
+        <v>511.3735209246628</v>
       </c>
       <c r="D20" t="n">
-        <v>271.8356428219928</v>
+        <v>499.2140928412288</v>
       </c>
       <c r="E20" t="n">
-        <v>272.6948547363281</v>
+        <v>501.205810546875</v>
       </c>
       <c r="F20" t="n">
-        <v>49602800</v>
+        <v>25273100</v>
       </c>
     </row>
     <row r="21">
@@ -5830,19 +5870,19 @@
         <v>45975</v>
       </c>
       <c r="B21" t="n">
-        <v>270.7965900477885</v>
+        <v>496.1667955235038</v>
       </c>
       <c r="C21" t="n">
-        <v>275.702003472256</v>
+        <v>509.4814242836766</v>
       </c>
       <c r="D21" t="n">
-        <v>269.3479639093673</v>
+        <v>495.3800584752997</v>
       </c>
       <c r="E21" t="n">
-        <v>272.1553344726562</v>
+        <v>508.0672912597656</v>
       </c>
       <c r="F21" t="n">
-        <v>47431300</v>
+        <v>28505700</v>
       </c>
     </row>
     <row r="22">
@@ -5850,19 +5890,19 @@
         <v>45978</v>
       </c>
       <c r="B22" t="n">
-        <v>268.5687054184609</v>
+        <v>506.3444741681719</v>
       </c>
       <c r="C22" t="n">
-        <v>270.2371271729127</v>
+        <v>509.9992593431845</v>
       </c>
       <c r="D22" t="n">
-        <v>265.4815977121726</v>
+        <v>502.8191251226507</v>
       </c>
       <c r="E22" t="n">
-        <v>267.2099609375</v>
+        <v>505.388427734375</v>
       </c>
       <c r="F22" t="n">
-        <v>45018300</v>
+        <v>19092800</v>
       </c>
     </row>
     <row r="23">
@@ -5870,19 +5910,19 @@
         <v>45979</v>
       </c>
       <c r="B23" t="n">
-        <v>269.7376065335732</v>
+        <v>493.3186219236692</v>
       </c>
       <c r="C23" t="n">
-        <v>270.4569347049811</v>
+        <v>500.8971240097587</v>
       </c>
       <c r="D23" t="n">
-        <v>265.0719890725528</v>
+        <v>484.7641975590383</v>
       </c>
       <c r="E23" t="n">
-        <v>267.1900024414062</v>
+        <v>491.7451782226562</v>
       </c>
       <c r="F23" t="n">
-        <v>45677300</v>
+        <v>33815100</v>
       </c>
     </row>
     <row r="24">
@@ -5890,19 +5930,19 @@
         <v>45980</v>
       </c>
       <c r="B24" t="n">
-        <v>265.2817633125939</v>
+        <v>488.070453670226</v>
       </c>
       <c r="C24" t="n">
-        <v>271.9555110777923</v>
+        <v>493.1393718315724</v>
       </c>
       <c r="D24" t="n">
-        <v>265.2517925781922</v>
+        <v>480.8305400064438</v>
       </c>
       <c r="E24" t="n">
-        <v>268.3089294433594</v>
+        <v>485.102783203125</v>
       </c>
       <c r="F24" t="n">
-        <v>40424500</v>
+        <v>23245300</v>
       </c>
     </row>
     <row r="25">
@@ -5910,19 +5950,19 @@
         <v>45981</v>
       </c>
       <c r="B25" t="n">
-        <v>270.5768036466949</v>
+        <v>491.5879641710541</v>
       </c>
       <c r="C25" t="n">
-        <v>275.1725094767523</v>
+        <v>492.4460215630244</v>
       </c>
       <c r="D25" t="n">
-        <v>265.6714205454633</v>
+        <v>474.4171642897319</v>
       </c>
       <c r="E25" t="n">
-        <v>266.0010986328125</v>
+        <v>477.3404846191406</v>
       </c>
       <c r="F25" t="n">
-        <v>45823600</v>
+        <v>26802500</v>
       </c>
     </row>
     <row r="26">
@@ -5930,19 +5970,19 @@
         <v>45982</v>
       </c>
       <c r="B26" t="n">
-        <v>265.7013768088059</v>
+        <v>477.4103368698009</v>
       </c>
       <c r="C26" t="n">
-        <v>273.0744516711978</v>
+        <v>477.8293938228302</v>
       </c>
       <c r="D26" t="n">
-        <v>265.4216397990326</v>
+        <v>467.2036221547232</v>
       </c>
       <c r="E26" t="n">
-        <v>271.2361755371094</v>
+        <v>471.0448608398438</v>
       </c>
       <c r="F26" t="n">
-        <v>59030800</v>
+        <v>31769200</v>
       </c>
     </row>
     <row r="27">
@@ -5950,19 +5990,19 @@
         <v>45985</v>
       </c>
       <c r="B27" t="n">
-        <v>270.6467521230613</v>
+        <v>473.9183160323131</v>
       </c>
       <c r="C27" t="n">
-        <v>276.7410558404627</v>
+        <v>475.8139832068258</v>
       </c>
       <c r="D27" t="n">
-        <v>270.6467521230613</v>
+        <v>466.9542001322548</v>
       </c>
       <c r="E27" t="n">
-        <v>275.6620788574219</v>
+        <v>472.9205932617188</v>
       </c>
       <c r="F27" t="n">
-        <v>65585800</v>
+        <v>34421000</v>
       </c>
     </row>
     <row r="28">
@@ -5970,19 +6010,19 @@
         <v>45986</v>
       </c>
       <c r="B28" t="n">
-        <v>275.012667049666</v>
+        <v>472.9904142849383</v>
       </c>
       <c r="C28" t="n">
-        <v>280.1179060838009</v>
+        <v>478.0588322743821</v>
       </c>
       <c r="D28" t="n">
-        <v>274.9926967216935</v>
+        <v>463.8313270788984</v>
       </c>
       <c r="E28" t="n">
-        <v>276.7110900878906</v>
+        <v>475.9037475585938</v>
       </c>
       <c r="F28" t="n">
-        <v>46914200</v>
+        <v>28019800</v>
       </c>
     </row>
     <row r="29">
@@ -5990,19 +6030,19 @@
         <v>45987</v>
       </c>
       <c r="B29" t="n">
-        <v>276.7010825487222</v>
+        <v>485.2025316262965</v>
       </c>
       <c r="C29" t="n">
-        <v>279.2686873678638</v>
+        <v>487.1979770584782</v>
       </c>
       <c r="D29" t="n">
-        <v>276.3714044558947</v>
+        <v>480.1041831621511</v>
       </c>
       <c r="E29" t="n">
-        <v>277.29052734375</v>
+        <v>484.3943786621094</v>
       </c>
       <c r="F29" t="n">
-        <v>33431400</v>
+        <v>25709100</v>
       </c>
     </row>
     <row r="30">
@@ -6010,19 +6050,19 @@
         <v>45989</v>
       </c>
       <c r="B30" t="n">
-        <v>277.0008150112318</v>
+        <v>486.489626354464</v>
       </c>
       <c r="C30" t="n">
-        <v>278.7391786268174</v>
+        <v>491.5081706450152</v>
       </c>
       <c r="D30" t="n">
-        <v>275.7319827496524</v>
+        <v>485.541777548382</v>
       </c>
       <c r="E30" t="n">
-        <v>278.5893249511719</v>
+        <v>490.8895874023438</v>
       </c>
       <c r="F30" t="n">
-        <v>20135600</v>
+        <v>14386700</v>
       </c>
     </row>
     <row r="31">
@@ -6030,19 +6070,19 @@
         <v>45992</v>
       </c>
       <c r="B31" t="n">
-        <v>277.7501195744996</v>
+        <v>487.3277021324388</v>
       </c>
       <c r="C31" t="n">
-        <v>283.1550658399818</v>
+        <v>488.7444513856018</v>
       </c>
       <c r="D31" t="n">
-        <v>275.881872572025</v>
+        <v>483.5463243869077</v>
       </c>
       <c r="E31" t="n">
-        <v>282.8353576660156</v>
+        <v>485.6315612792969</v>
       </c>
       <c r="F31" t="n">
-        <v>46587700</v>
+        <v>23964000</v>
       </c>
     </row>
     <row r="32">
@@ -6050,19 +6090,19 @@
         <v>45993</v>
       </c>
       <c r="B32" t="n">
-        <v>282.7354345985028</v>
+        <v>485.6116258193264</v>
       </c>
       <c r="C32" t="n">
-        <v>287.1313151163589</v>
+        <v>492.3761849539621</v>
       </c>
       <c r="D32" t="n">
-        <v>282.3657853749787</v>
+        <v>485.2125428025972</v>
       </c>
       <c r="E32" t="n">
-        <v>285.9224548339844</v>
+        <v>488.8841552734375</v>
       </c>
       <c r="F32" t="n">
-        <v>53669500</v>
+        <v>19562700</v>
       </c>
     </row>
     <row r="33">
@@ -6070,19 +6110,19 @@
         <v>45994</v>
       </c>
       <c r="B33" t="n">
-        <v>285.9324708384744</v>
+        <v>475.235297143397</v>
       </c>
       <c r="C33" t="n">
-        <v>288.3501915351014</v>
+        <v>483.1372440988117</v>
       </c>
       <c r="D33" t="n">
-        <v>283.0351573834178</v>
+        <v>474.1178525596479</v>
       </c>
       <c r="E33" t="n">
-        <v>283.8843688964844</v>
+        <v>476.64208984375</v>
       </c>
       <c r="F33" t="n">
-        <v>43538700</v>
+        <v>34615100</v>
       </c>
     </row>
     <row r="34">
@@ -6090,19 +6130,19 @@
         <v>45995</v>
       </c>
       <c r="B34" t="n">
-        <v>283.8344068650217</v>
+        <v>478.6674679630734</v>
       </c>
       <c r="C34" t="n">
-        <v>284.4638227692578</v>
+        <v>480.2239129901724</v>
       </c>
       <c r="D34" t="n">
-        <v>278.3295482939282</v>
+        <v>475.4048951405118</v>
       </c>
       <c r="E34" t="n">
-        <v>280.4375915527344</v>
+        <v>479.7449951171875</v>
       </c>
       <c r="F34" t="n">
-        <v>43989100</v>
+        <v>22318200</v>
       </c>
     </row>
     <row r="35">
@@ -6110,19 +6150,19 @@
         <v>45996</v>
       </c>
       <c r="B35" t="n">
-        <v>280.2777430659675</v>
+        <v>481.4211657314621</v>
       </c>
       <c r="C35" t="n">
-        <v>280.8771882481053</v>
+        <v>482.299166614698</v>
       </c>
       <c r="D35" t="n">
-        <v>277.7900501334527</v>
+        <v>477.7894707894466</v>
       </c>
       <c r="E35" t="n">
-        <v>278.5193786621094</v>
+        <v>482.0597229003906</v>
       </c>
       <c r="F35" t="n">
-        <v>47265800</v>
+        <v>22608700</v>
       </c>
     </row>
     <row r="36">
@@ -6130,19 +6170,19 @@
         <v>45999</v>
       </c>
       <c r="B36" t="n">
-        <v>277.8699843761556</v>
+        <v>483.7858099301447</v>
       </c>
       <c r="C36" t="n">
-        <v>279.4085531850005</v>
+        <v>491.1789088824644</v>
       </c>
       <c r="D36" t="n">
-        <v>275.8918244790692</v>
+        <v>483.2769615726175</v>
       </c>
       <c r="E36" t="n">
-        <v>277.6302185058594</v>
+        <v>489.9018249511719</v>
       </c>
       <c r="F36" t="n">
-        <v>38211800</v>
+        <v>21965900</v>
       </c>
     </row>
     <row r="37">
@@ -6150,19 +6190,19 @@
         <v>46000</v>
       </c>
       <c r="B37" t="n">
-        <v>277.8999627322321</v>
+        <v>487.9862027558801</v>
       </c>
       <c r="C37" t="n">
-        <v>279.7682096639769</v>
+        <v>490.9993144973556</v>
       </c>
       <c r="D37" t="n">
-        <v>276.6611317163261</v>
+        <v>487.3875630167038</v>
       </c>
       <c r="E37" t="n">
-        <v>276.9208679199219</v>
+        <v>490.8995361328125</v>
       </c>
       <c r="F37" t="n">
-        <v>32193300</v>
+        <v>14696100</v>
       </c>
     </row>
     <row r="38">
@@ -6170,19 +6210,19 @@
         <v>46001</v>
       </c>
       <c r="B38" t="n">
-        <v>277.490342786908</v>
+        <v>482.9277288439703</v>
       </c>
       <c r="C38" t="n">
-        <v>279.4884730680018</v>
+        <v>483.1472290611572</v>
       </c>
       <c r="D38" t="n">
-        <v>276.1815698919154</v>
+        <v>473.9980982856002</v>
       </c>
       <c r="E38" t="n">
-        <v>278.5193786621094</v>
+        <v>477.4701843261719</v>
       </c>
       <c r="F38" t="n">
-        <v>33038300</v>
+        <v>35756200</v>
       </c>
     </row>
     <row r="39">
@@ -6190,19 +6230,19 @@
         <v>46002</v>
       </c>
       <c r="B39" t="n">
-        <v>278.8390875870869</v>
+        <v>475.5445986070271</v>
       </c>
       <c r="C39" t="n">
-        <v>279.3286197507982</v>
+        <v>484.9231863556336</v>
       </c>
       <c r="D39" t="n">
-        <v>273.5540244422053</v>
+        <v>474.7763326037194</v>
       </c>
       <c r="E39" t="n">
-        <v>277.7700805664062</v>
+        <v>482.3690185546875</v>
       </c>
       <c r="F39" t="n">
-        <v>33248000</v>
+        <v>24669200</v>
       </c>
     </row>
     <row r="40">
@@ -6210,19 +6250,19 @@
         <v>46003</v>
       </c>
       <c r="B40" t="n">
-        <v>277.64021728323</v>
+        <v>478.7273480015789</v>
       </c>
       <c r="C40" t="n">
-        <v>278.9589906850317</v>
+        <v>481.3513637649093</v>
       </c>
       <c r="D40" t="n">
-        <v>276.5612402656973</v>
+        <v>475.2552617920193</v>
       </c>
       <c r="E40" t="n">
-        <v>278.0198669433594</v>
+        <v>477.4402770996094</v>
       </c>
       <c r="F40" t="n">
-        <v>39532900</v>
+        <v>21248100</v>
       </c>
     </row>
     <row r="41">
@@ -6230,19 +6270,19 @@
         <v>46006</v>
       </c>
       <c r="B41" t="n">
-        <v>279.8880911943856</v>
+        <v>479.0066832317436</v>
       </c>
       <c r="C41" t="n">
-        <v>279.8880911943856</v>
+        <v>479.6252664455081</v>
       </c>
       <c r="D41" t="n">
-        <v>272.5849275039148</v>
+        <v>471.4439279747418</v>
       </c>
       <c r="E41" t="n">
-        <v>273.8537292480469</v>
+        <v>473.7387084960938</v>
       </c>
       <c r="F41" t="n">
-        <v>50409100</v>
+        <v>23727700</v>
       </c>
     </row>
     <row r="42">
@@ -6250,19 +6290,19 @@
         <v>46007</v>
       </c>
       <c r="B42" t="n">
-        <v>272.5649667835892</v>
+        <v>470.8353364785088</v>
       </c>
       <c r="C42" t="n">
-        <v>275.2424541197232</v>
+        <v>476.8017293564801</v>
       </c>
       <c r="D42" t="n">
-        <v>271.535930878856</v>
+        <v>469.8076832860371</v>
       </c>
       <c r="E42" t="n">
-        <v>274.353271484375</v>
+        <v>475.3051452636719</v>
       </c>
       <c r="F42" t="n">
-        <v>37648600</v>
+        <v>20705600</v>
       </c>
     </row>
     <row r="43">
@@ -6270,19 +6310,19 @@
         <v>46008</v>
       </c>
       <c r="B43" t="n">
-        <v>274.7529265191943</v>
+        <v>475.8239455574328</v>
       </c>
       <c r="C43" t="n">
-        <v>275.9018453851206</v>
+        <v>478.9069051052783</v>
       </c>
       <c r="D43" t="n">
-        <v>271.3860817211021</v>
+        <v>473.9182915104317</v>
       </c>
       <c r="E43" t="n">
-        <v>271.5858764648438</v>
+        <v>475.0357360839844</v>
       </c>
       <c r="F43" t="n">
-        <v>50138700</v>
+        <v>24527200</v>
       </c>
     </row>
     <row r="44">
@@ -6290,19 +6330,19 @@
         <v>46009</v>
       </c>
       <c r="B44" t="n">
-        <v>273.3542023206923</v>
+        <v>477.1010453906704</v>
       </c>
       <c r="C44" t="n">
-        <v>273.374203136776</v>
+        <v>488.4850656489584</v>
       </c>
       <c r="D44" t="n">
-        <v>266.7004552212896</v>
+        <v>476.8017407441929</v>
       </c>
       <c r="E44" t="n">
-        <v>271.935546875</v>
+        <v>482.8778686523438</v>
       </c>
       <c r="F44" t="n">
-        <v>51630700</v>
+        <v>28573500</v>
       </c>
     </row>
     <row r="45">
@@ -6310,19 +6350,19 @@
         <v>46010</v>
       </c>
       <c r="B45" t="n">
-        <v>271.8955859651445</v>
+        <v>486.2501387748106</v>
       </c>
       <c r="C45" t="n">
-        <v>274.343307881706</v>
+        <v>486.7390436209232</v>
       </c>
       <c r="D45" t="n">
-        <v>269.6476892826471</v>
+        <v>481.39123391446</v>
       </c>
       <c r="E45" t="n">
-        <v>273.4141845703125</v>
+        <v>484.8134460449219</v>
       </c>
       <c r="F45" t="n">
-        <v>144632000</v>
+        <v>70836100</v>
       </c>
     </row>
     <row r="46">
@@ -6330,19 +6370,19 @@
         <v>46013</v>
       </c>
       <c r="B46" t="n">
-        <v>272.6048920133635</v>
+        <v>485.0129839081317</v>
       </c>
       <c r="C46" t="n">
-        <v>273.6239579412959</v>
+        <v>487.6170561484318</v>
       </c>
       <c r="D46" t="n">
-        <v>270.2571133897843</v>
+        <v>481.5908021440126</v>
       </c>
       <c r="E46" t="n">
-        <v>270.7166748046875</v>
+        <v>483.8157348632812</v>
       </c>
       <c r="F46" t="n">
-        <v>36571800</v>
+        <v>16963000</v>
       </c>
     </row>
     <row r="47">
@@ -6350,19 +6390,19 @@
         <v>46014</v>
       </c>
       <c r="B47" t="n">
-        <v>270.5868091030317</v>
+        <v>483.8755963136496</v>
       </c>
       <c r="C47" t="n">
-        <v>272.2452609569047</v>
+        <v>486.7190818282799</v>
       </c>
       <c r="D47" t="n">
-        <v>269.3080068949797</v>
+        <v>483.6361221459561</v>
       </c>
       <c r="E47" t="n">
-        <v>272.1053771972656</v>
+        <v>485.7413330078125</v>
       </c>
       <c r="F47" t="n">
-        <v>29642000</v>
+        <v>14683600</v>
       </c>
     </row>
     <row r="48">
@@ -6370,19 +6410,19 @@
         <v>46015</v>
       </c>
       <c r="B48" t="n">
-        <v>272.085389177814</v>
+        <v>484.5739628623746</v>
       </c>
       <c r="C48" t="n">
-        <v>275.1724967178681</v>
+        <v>488.0460488858467</v>
       </c>
       <c r="D48" t="n">
-        <v>271.9455359163183</v>
+        <v>483.7258924615979</v>
       </c>
       <c r="E48" t="n">
-        <v>273.5540161132812</v>
+        <v>486.9086303710938</v>
       </c>
       <c r="F48" t="n">
-        <v>17910600</v>
+        <v>5855900</v>
       </c>
     </row>
     <row r="49">
@@ -6390,19 +6430,19 @@
         <v>46017</v>
       </c>
       <c r="B49" t="n">
-        <v>273.9037084592662</v>
+        <v>485.601642461088</v>
       </c>
       <c r="C49" t="n">
-        <v>275.1125687682936</v>
+        <v>487.0084352251927</v>
       </c>
       <c r="D49" t="n">
-        <v>272.6049054553</v>
+        <v>484.8533503811227</v>
       </c>
       <c r="E49" t="n">
-        <v>273.1444091796875</v>
+        <v>486.599365234375</v>
       </c>
       <c r="F49" t="n">
-        <v>21521800</v>
+        <v>8842200</v>
       </c>
     </row>
     <row r="50">
@@ -6410,19 +6450,19 @@
         <v>46020</v>
       </c>
       <c r="B50" t="n">
-        <v>272.4350823114352</v>
+        <v>483.7558335295542</v>
       </c>
       <c r="C50" t="n">
-        <v>274.103504063292</v>
+        <v>487.2379065999322</v>
       </c>
       <c r="D50" t="n">
-        <v>272.0954038139857</v>
+        <v>483.0773893732932</v>
       </c>
       <c r="E50" t="n">
-        <v>273.5040893554688</v>
+        <v>485.9907531738281</v>
       </c>
       <c r="F50" t="n">
-        <v>23715200</v>
+        <v>10893400</v>
       </c>
     </row>
     <row r="51">
@@ -6430,19 +6470,19 @@
         <v>46021</v>
       </c>
       <c r="B51" t="n">
-        <v>272.5549704076282</v>
+        <v>484.8234150126488</v>
       </c>
       <c r="C51" t="n">
-        <v>273.8237722152489</v>
+        <v>488.5648753746365</v>
       </c>
       <c r="D51" t="n">
-        <v>272.0254670796708</v>
+        <v>484.3944015320139</v>
       </c>
       <c r="E51" t="n">
-        <v>272.82470703125</v>
+        <v>486.3699035644531</v>
       </c>
       <c r="F51" t="n">
-        <v>22139600</v>
+        <v>13944500</v>
       </c>
     </row>
     <row r="52">
@@ -6450,19 +6490,19 @@
         <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>272.804725327361</v>
+        <v>486.7290680267604</v>
       </c>
       <c r="C52" t="n">
-        <v>273.4241408373621</v>
+        <v>487.0284031238816</v>
       </c>
       <c r="D52" t="n">
-        <v>271.4959524300237</v>
+        <v>482.1993981667827</v>
       </c>
       <c r="E52" t="n">
-        <v>271.6058349609375</v>
+        <v>482.5186767578125</v>
       </c>
       <c r="F52" t="n">
-        <v>27293600</v>
+        <v>15601600</v>
       </c>
     </row>
     <row r="53">
@@ -6470,19 +6510,19 @@
         <v>46024</v>
       </c>
       <c r="B53" t="n">
-        <v>272.0054842546519</v>
+        <v>483.2869444224563</v>
       </c>
       <c r="C53" t="n">
-        <v>277.5802543100492</v>
+        <v>483.5563186075122</v>
       </c>
       <c r="D53" t="n">
-        <v>268.7485221479618</v>
+        <v>469.0893385249197</v>
       </c>
       <c r="E53" t="n">
-        <v>270.7566528320312</v>
+        <v>471.8630065917969</v>
       </c>
       <c r="F53" t="n">
-        <v>37838100</v>
+        <v>25571600</v>
       </c>
     </row>
     <row r="54">
@@ -6490,19 +6530,19 @@
         <v>46027</v>
       </c>
       <c r="B54" t="n">
-        <v>270.387007446453</v>
+        <v>472.9804293228547</v>
       </c>
       <c r="C54" t="n">
-        <v>271.2561892506844</v>
+        <v>474.9858617296903</v>
       </c>
       <c r="D54" t="n">
-        <v>265.8912142612155</v>
+        <v>468.4308161640092</v>
       </c>
       <c r="E54" t="n">
-        <v>267.0101623535156</v>
+        <v>471.773193359375</v>
       </c>
       <c r="F54" t="n">
-        <v>45647200</v>
+        <v>25250300</v>
       </c>
     </row>
     <row r="55">
@@ -6510,19 +6550,19 @@
         <v>46028</v>
       </c>
       <c r="B55" t="n">
-        <v>266.7503924619391</v>
+        <v>472.7210225701547</v>
       </c>
       <c r="C55" t="n">
-        <v>267.2998660934885</v>
+        <v>477.6497753472042</v>
       </c>
       <c r="D55" t="n">
-        <v>261.8749496989937</v>
+        <v>468.6802576477938</v>
       </c>
       <c r="E55" t="n">
-        <v>262.1147155761719</v>
+        <v>477.4203186035156</v>
       </c>
       <c r="F55" t="n">
-        <v>52352100</v>
+        <v>23037700</v>
       </c>
     </row>
     <row r="56">
@@ -6530,19 +6570,19 @@
         <v>46029</v>
       </c>
       <c r="B56" t="n">
-        <v>262.9539513876447</v>
+        <v>478.6674756822987</v>
       </c>
       <c r="C56" t="n">
-        <v>263.4334831315393</v>
+        <v>488.5848422406915</v>
       </c>
       <c r="D56" t="n">
-        <v>259.5671060011504</v>
+        <v>476.861599942913</v>
       </c>
       <c r="E56" t="n">
-        <v>260.0866088867188</v>
+        <v>482.3690185546875</v>
       </c>
       <c r="F56" t="n">
-        <v>48309800</v>
+        <v>25564200</v>
       </c>
     </row>
     <row r="57">
@@ -6550,19 +6590,19 @@
         <v>46030</v>
       </c>
       <c r="B57" t="n">
-        <v>256.7797203952787</v>
+        <v>480.1440867981462</v>
       </c>
       <c r="C57" t="n">
-        <v>259.0476178563403</v>
+        <v>481.5608665012806</v>
       </c>
       <c r="D57" t="n">
-        <v>255.4609622909548</v>
+        <v>474.7763335277468</v>
       </c>
       <c r="E57" t="n">
-        <v>258.7978515625</v>
+        <v>477.0212097167969</v>
       </c>
       <c r="F57" t="n">
-        <v>50419300</v>
+        <v>18162600</v>
       </c>
     </row>
     <row r="58">
@@ -6570,19 +6610,19 @@
         <v>46031</v>
       </c>
       <c r="B58" t="n">
-        <v>258.8377955175017</v>
+        <v>472.9804540365218</v>
       </c>
       <c r="C58" t="n">
-        <v>259.9667440583015</v>
+        <v>478.7273469366413</v>
       </c>
       <c r="D58" t="n">
-        <v>255.9804837142826</v>
+        <v>471.1247042989064</v>
       </c>
       <c r="E58" t="n">
-        <v>259.1275329589844</v>
+        <v>478.1885681152344</v>
       </c>
       <c r="F58" t="n">
-        <v>39997000</v>
+        <v>18491000</v>
       </c>
     </row>
     <row r="59">
@@ -6590,19 +6630,19 @@
         <v>46034</v>
       </c>
       <c r="B59" t="n">
-        <v>258.9177364764393</v>
+        <v>475.5845048686955</v>
       </c>
       <c r="C59" t="n">
-        <v>261.055720113683</v>
+        <v>479.894643901475</v>
       </c>
       <c r="D59" t="n">
-        <v>256.5599267903311</v>
+        <v>474.5967386659474</v>
       </c>
       <c r="E59" t="n">
-        <v>260.0067138671875</v>
+        <v>476.0933227539062</v>
       </c>
       <c r="F59" t="n">
-        <v>45263800</v>
+        <v>23519900</v>
       </c>
     </row>
     <row r="60">
@@ -6610,19 +6650,19 @@
         <v>46035</v>
       </c>
       <c r="B60" t="n">
-        <v>258.4781303943212</v>
+        <v>473.5990225282599</v>
       </c>
       <c r="C60" t="n">
-        <v>261.5652379723006</v>
+        <v>474.6965236309785</v>
       </c>
       <c r="D60" t="n">
-        <v>258.148452318208</v>
+        <v>464.888922501957</v>
       </c>
       <c r="E60" t="n">
-        <v>260.8059387207031</v>
+        <v>469.5981750488281</v>
       </c>
       <c r="F60" t="n">
-        <v>45730800</v>
+        <v>28545800</v>
       </c>
     </row>
     <row r="61">
@@ -6630,19 +6670,19 @@
         <v>46036</v>
       </c>
       <c r="B61" t="n">
-        <v>259.247418118488</v>
+        <v>465.3977566654985</v>
       </c>
       <c r="C61" t="n">
-        <v>261.5752571005171</v>
+        <v>467.1338149970701</v>
       </c>
       <c r="D61" t="n">
-        <v>256.4700180914029</v>
+        <v>456.1289340170423</v>
       </c>
       <c r="E61" t="n">
-        <v>259.7169799804688</v>
+        <v>458.3338928222656</v>
       </c>
       <c r="F61" t="n">
-        <v>40019400</v>
+        <v>28184300</v>
       </c>
     </row>
     <row r="62">
@@ -6650,19 +6690,19 @@
         <v>46037</v>
       </c>
       <c r="B62" t="n">
-        <v>260.4063187564486</v>
+        <v>463.0630900555096</v>
       </c>
       <c r="C62" t="n">
-        <v>260.7959687899761</v>
+        <v>463.1927988881192</v>
       </c>
       <c r="D62" t="n">
-        <v>256.8096782083212</v>
+        <v>454.8618076165624</v>
       </c>
       <c r="E62" t="n">
-        <v>257.9685974121094</v>
+        <v>455.6200866699219</v>
       </c>
       <c r="F62" t="n">
-        <v>39388600</v>
+        <v>23225800</v>
       </c>
     </row>
     <row r="63">
@@ -6670,19 +6710,19 @@
         <v>46038</v>
       </c>
       <c r="B63" t="n">
-        <v>257.6589020182799</v>
+        <v>456.7873986695315</v>
       </c>
       <c r="C63" t="n">
-        <v>258.6579671912775</v>
+        <v>462.1352085061545</v>
       </c>
       <c r="D63" t="n">
-        <v>254.6916772349149</v>
+        <v>455.4404972994736</v>
       </c>
       <c r="E63" t="n">
-        <v>255.2911224365234</v>
+        <v>458.8127746582031</v>
       </c>
       <c r="F63" t="n">
-        <v>72142800</v>
+        <v>34246700</v>
       </c>
     </row>
     <row r="64">
@@ -6690,19 +6730,19 @@
         <v>46042</v>
       </c>
       <c r="B64" t="n">
-        <v>252.4937373957159</v>
+        <v>450.1924514863621</v>
       </c>
       <c r="C64" t="n">
-        <v>254.5518092169813</v>
+        <v>455.7597309230742</v>
       </c>
       <c r="D64" t="n">
-        <v>243.1924430560896</v>
+        <v>448.2568669541529</v>
       </c>
       <c r="E64" t="n">
-        <v>246.4693756103516</v>
+        <v>453.4849243164062</v>
       </c>
       <c r="F64" t="n">
-        <v>80267500</v>
+        <v>26130000</v>
       </c>
     </row>
     <row r="65">
@@ -6710,19 +6750,19 @@
         <v>46043</v>
       </c>
       <c r="B65" t="n">
-        <v>248.4675090444481</v>
+        <v>451.5693196059127</v>
       </c>
       <c r="C65" t="n">
-        <v>251.3248360900433</v>
+        <v>451.6591109990197</v>
       </c>
       <c r="D65" t="n">
-        <v>244.9507953165175</v>
+        <v>437.6810056251358</v>
       </c>
       <c r="E65" t="n">
-        <v>247.4184875488281</v>
+        <v>443.0986328125</v>
       </c>
       <c r="F65" t="n">
-        <v>54641700</v>
+        <v>37980500</v>
       </c>
     </row>
     <row r="66">
@@ -6730,19 +6770,19 @@
         <v>46044</v>
       </c>
       <c r="B66" t="n">
-        <v>248.9670398844787</v>
+        <v>446.600636936346</v>
       </c>
       <c r="C66" t="n">
-        <v>250.7653602579427</v>
+        <v>451.8087507279656</v>
       </c>
       <c r="D66" t="n">
-        <v>247.9180183962477</v>
+        <v>443.6873036586902</v>
       </c>
       <c r="E66" t="n">
-        <v>248.1178436279297</v>
+        <v>450.1126403808594</v>
       </c>
       <c r="F66" t="n">
-        <v>39708300</v>
+        <v>25349400</v>
       </c>
     </row>
     <row r="67">
@@ -6750,19 +6790,19 @@
         <v>46045</v>
       </c>
       <c r="B67" t="n">
-        <v>247.0888078223564</v>
+        <v>450.8409629929935</v>
       </c>
       <c r="C67" t="n">
-        <v>249.176850391454</v>
+        <v>470.0271819611143</v>
       </c>
       <c r="D67" t="n">
-        <v>244.4512611104123</v>
+        <v>449.5040181949105</v>
       </c>
       <c r="E67" t="n">
-        <v>247.8081207275391</v>
+        <v>464.888916015625</v>
       </c>
       <c r="F67" t="n">
-        <v>41689000</v>
+        <v>38000200</v>
       </c>
     </row>
     <row r="68">
@@ -6770,19 +6810,19 @@
         <v>46048</v>
       </c>
       <c r="B68" t="n">
-        <v>251.2449001563489</v>
+        <v>464.2503622118351</v>
       </c>
       <c r="C68" t="n">
-        <v>256.320152957849</v>
+        <v>473.1700058760031</v>
       </c>
       <c r="D68" t="n">
-        <v>249.5664780183616</v>
+        <v>460.9479024031912</v>
       </c>
       <c r="E68" t="n">
-        <v>255.1712341308594</v>
+        <v>469.2090454101562</v>
       </c>
       <c r="F68" t="n">
-        <v>55969200</v>
+        <v>29291200</v>
       </c>
     </row>
     <row r="69">
@@ -6790,19 +6830,19 @@
         <v>46049</v>
       </c>
       <c r="B69" t="n">
-        <v>258.9277169221324</v>
+        <v>472.62128861771</v>
       </c>
       <c r="C69" t="n">
-        <v>261.705116697089</v>
+        <v>481.7703893732875</v>
       </c>
       <c r="D69" t="n">
-        <v>257.9685924683142</v>
+        <v>472.0825097961169</v>
       </c>
       <c r="E69" t="n">
-        <v>258.0285339355469</v>
+        <v>479.485595703125</v>
       </c>
       <c r="F69" t="n">
-        <v>49648300</v>
+        <v>29213900</v>
       </c>
     </row>
     <row r="70">
@@ -6810,19 +6850,19 @@
         <v>46050</v>
       </c>
       <c r="B70" t="n">
-        <v>257.409147241713</v>
+        <v>482.1095916405993</v>
       </c>
       <c r="C70" t="n">
-        <v>258.6180076181917</v>
+        <v>482.6383834693597</v>
       </c>
       <c r="D70" t="n">
-        <v>254.2720830679268</v>
+        <v>476.9114647448887</v>
       </c>
       <c r="E70" t="n">
-        <v>256.2002868652344</v>
+        <v>480.533203125</v>
       </c>
       <c r="F70" t="n">
-        <v>41288000</v>
+        <v>36875400</v>
       </c>
     </row>
     <row r="71">
@@ -6830,19 +6870,19 @@
         <v>46051</v>
       </c>
       <c r="B71" t="n">
-        <v>257.758806680925</v>
+        <v>438.9880283656418</v>
       </c>
       <c r="C71" t="n">
-        <v>259.4072580677027</v>
+        <v>441.4923222419712</v>
       </c>
       <c r="D71" t="n">
-        <v>254.1721664792058</v>
+        <v>420.0612263501361</v>
       </c>
       <c r="E71" t="n">
-        <v>258.0385437011719</v>
+        <v>432.5128173828125</v>
       </c>
       <c r="F71" t="n">
-        <v>67253000</v>
+        <v>128855300</v>
       </c>
     </row>
     <row r="72">
@@ -6850,19 +6890,19 @@
         <v>46052</v>
       </c>
       <c r="B72" t="n">
-        <v>254.9314433110553</v>
+        <v>438.1699022937122</v>
       </c>
       <c r="C72" t="n">
-        <v>261.6551472598355</v>
+        <v>438.5989157576861</v>
       </c>
       <c r="D72" t="n">
-        <v>251.9442331321547</v>
+        <v>425.4788680207893</v>
       </c>
       <c r="E72" t="n">
-        <v>259.2374267578125</v>
+        <v>429.3101196289062</v>
       </c>
       <c r="F72" t="n">
-        <v>92443400</v>
+        <v>58566800</v>
       </c>
     </row>
     <row r="73">
@@ -6870,19 +6910,19 @@
         <v>46055</v>
       </c>
       <c r="B73" t="n">
-        <v>259.7869174093499</v>
+        <v>429.2602343395754</v>
       </c>
       <c r="C73" t="n">
-        <v>270.2371306501278</v>
+        <v>429.7590957240154</v>
       </c>
       <c r="D73" t="n">
-        <v>258.9676766447768</v>
+        <v>421.28843915961</v>
       </c>
       <c r="E73" t="n">
-        <v>269.7575988769531</v>
+        <v>422.4058837890625</v>
       </c>
       <c r="F73" t="n">
-        <v>73913400</v>
+        <v>42219900</v>
       </c>
     </row>
     <row r="74">
@@ -6890,19 +6930,19 @@
         <v>46056</v>
       </c>
       <c r="B74" t="n">
-        <v>268.9483513556569</v>
+        <v>421.0489834358989</v>
       </c>
       <c r="C74" t="n">
-        <v>271.6258386480508</v>
+        <v>421.0888704228976</v>
       </c>
       <c r="D74" t="n">
-        <v>267.3598109321867</v>
+        <v>407.6296003977664</v>
       </c>
       <c r="E74" t="n">
-        <v>269.2280883789062</v>
+        <v>410.2735595703125</v>
       </c>
       <c r="F74" t="n">
-        <v>64394700</v>
+        <v>61424100</v>
       </c>
     </row>
     <row r="75">
@@ -6910,19 +6950,19 @@
         <v>46057</v>
       </c>
       <c r="B75" t="n">
-        <v>272.03545112075</v>
+        <v>410.0640575889883</v>
       </c>
       <c r="C75" t="n">
-        <v>278.6892285045384</v>
+        <v>418.8440057668918</v>
       </c>
       <c r="D75" t="n">
-        <v>272.03545112075</v>
+        <v>408.3080557741746</v>
       </c>
       <c r="E75" t="n">
-        <v>276.2315063476562</v>
+        <v>413.2467956542969</v>
       </c>
       <c r="F75" t="n">
-        <v>90545700</v>
+        <v>45012400</v>
       </c>
     </row>
     <row r="76">
@@ -6930,19 +6970,19 @@
         <v>46058</v>
       </c>
       <c r="B76" t="n">
-        <v>277.8699949435269</v>
+        <v>406.5121603821183</v>
       </c>
       <c r="C76" t="n">
-        <v>279.2387093202658</v>
+        <v>407.3701873334875</v>
       </c>
       <c r="D76" t="n">
-        <v>272.9745818081728</v>
+        <v>391.4265972483441</v>
       </c>
       <c r="E76" t="n">
-        <v>275.6520690917969</v>
+        <v>392.7735290527344</v>
       </c>
       <c r="F76" t="n">
-        <v>52977400</v>
+        <v>66289200</v>
       </c>
     </row>
     <row r="77">
@@ -6950,19 +6990,19 @@
         <v>46059</v>
       </c>
       <c r="B77" t="n">
-        <v>276.8609202349588</v>
+        <v>398.2609865133262</v>
       </c>
       <c r="C77" t="n">
-        <v>280.6473855638201</v>
+        <v>400.875015135043</v>
       </c>
       <c r="D77" t="n">
-        <v>276.6710954236804</v>
+        <v>392.0252195920243</v>
       </c>
       <c r="E77" t="n">
-        <v>277.8599853515625</v>
+        <v>400.2265014648438</v>
       </c>
       <c r="F77" t="n">
-        <v>50453400</v>
+        <v>53515300</v>
       </c>
     </row>
     <row r="78">
@@ -6970,19 +7010,19 @@
         <v>46062</v>
       </c>
       <c r="B78" t="n">
-        <v>277.9100036621094</v>
+        <v>403.9280678877113</v>
       </c>
       <c r="C78" t="n">
-        <v>278.2000122070312</v>
+        <v>413.9452129833927</v>
       </c>
       <c r="D78" t="n">
-        <v>271.7000122070312</v>
+        <v>399.9571203178888</v>
       </c>
       <c r="E78" t="n">
-        <v>274.6199951171875</v>
+        <v>412.6581420898438</v>
       </c>
       <c r="F78" t="n">
-        <v>44623400</v>
+        <v>45480500</v>
       </c>
     </row>
     <row r="79">
@@ -6990,19 +7030,19 @@
         <v>46063</v>
       </c>
       <c r="B79" t="n">
-        <v>274.8900146484375</v>
+        <v>418.6644027817824</v>
       </c>
       <c r="C79" t="n">
-        <v>275.3699951171875</v>
+        <v>422.7151545880433</v>
       </c>
       <c r="D79" t="n">
-        <v>272.9400024414062</v>
+        <v>411.76017861217</v>
       </c>
       <c r="E79" t="n">
-        <v>273.6799926757812</v>
+        <v>412.328857421875</v>
       </c>
       <c r="F79" t="n">
-        <v>34376900</v>
+        <v>44857900</v>
       </c>
     </row>
     <row r="80">
@@ -7010,19 +7050,19 @@
         <v>46064</v>
       </c>
       <c r="B80" t="n">
-        <v>274.7000122070312</v>
+        <v>415.2322299614449</v>
       </c>
       <c r="C80" t="n">
-        <v>280.1799926757812</v>
+        <v>415.5115911022014</v>
       </c>
       <c r="D80" t="n">
-        <v>274.4500122070312</v>
+        <v>400.096793508188</v>
       </c>
       <c r="E80" t="n">
-        <v>275.5</v>
+        <v>403.4491271972656</v>
       </c>
       <c r="F80" t="n">
-        <v>51931300</v>
+        <v>42491000</v>
       </c>
     </row>
     <row r="81">
@@ -7030,19 +7070,19 @@
         <v>46065</v>
       </c>
       <c r="B81" t="n">
-        <v>275.5899963378906</v>
+        <v>404.0777037056333</v>
       </c>
       <c r="C81" t="n">
-        <v>275.7200012207031</v>
+        <v>405.2749831551046</v>
       </c>
       <c r="D81" t="n">
-        <v>260.1799926757812</v>
+        <v>397.1036315998776</v>
       </c>
       <c r="E81" t="n">
-        <v>261.7300109863281</v>
+        <v>400.9248962402344</v>
       </c>
       <c r="F81" t="n">
-        <v>81077200</v>
+        <v>40802400</v>
       </c>
     </row>
     <row r="82">
@@ -7050,19 +7090,19 @@
         <v>46066</v>
       </c>
       <c r="B82" t="n">
-        <v>262.010009765625</v>
+        <v>403.528974460687</v>
       </c>
       <c r="C82" t="n">
-        <v>262.2300109863281</v>
+        <v>404.6164885937555</v>
       </c>
       <c r="D82" t="n">
-        <v>255.4499969482422</v>
+        <v>397.1435245648219</v>
       </c>
       <c r="E82" t="n">
-        <v>255.7799987792969</v>
+        <v>400.4060974121094</v>
       </c>
       <c r="F82" t="n">
-        <v>56290700</v>
+        <v>34091600</v>
       </c>
     </row>
     <row r="83">
@@ -7070,19 +7110,19 @@
         <v>46070</v>
       </c>
       <c r="B83" t="n">
-        <v>258.0499877929688</v>
+        <v>398.3108793269315</v>
       </c>
       <c r="C83" t="n">
-        <v>266.2900085449219</v>
+        <v>399.6079067287359</v>
       </c>
       <c r="D83" t="n">
-        <v>255.5399932861328</v>
+        <v>393.6315571718042</v>
       </c>
       <c r="E83" t="n">
-        <v>263.8800048828125</v>
+        <v>395.9562377929688</v>
       </c>
       <c r="F83" t="n">
-        <v>58469100</v>
+        <v>32078800</v>
       </c>
     </row>
     <row r="84">
@@ -7090,19 +7130,19 @@
         <v>46071</v>
       </c>
       <c r="B84" t="n">
-        <v>263.6000061035156</v>
+        <v>397.2233488345012</v>
       </c>
       <c r="C84" t="n">
-        <v>266.8200073242188</v>
+        <v>401.6432531481791</v>
       </c>
       <c r="D84" t="n">
-        <v>262.4500122070312</v>
+        <v>395.4174731587443</v>
       </c>
       <c r="E84" t="n">
-        <v>264.3500061035156</v>
+        <v>398.6900024414062</v>
       </c>
       <c r="F84" t="n">
-        <v>34203300</v>
+        <v>23223400</v>
       </c>
     </row>
     <row r="85">
@@ -7110,19 +7150,19 @@
         <v>46072</v>
       </c>
       <c r="B85" t="n">
-        <v>262.6000061035156</v>
+        <v>400.6900024414062</v>
       </c>
       <c r="C85" t="n">
-        <v>264.4800109863281</v>
+        <v>404.4299926757812</v>
       </c>
       <c r="D85" t="n">
-        <v>260.0499877929688</v>
+        <v>396.6700134277344</v>
       </c>
       <c r="E85" t="n">
-        <v>260.5799865722656</v>
+        <v>398.4599914550781</v>
       </c>
       <c r="F85" t="n">
-        <v>30845300</v>
+        <v>28234000</v>
       </c>
     </row>
     <row r="86">
@@ -7130,19 +7170,19 @@
         <v>46073</v>
       </c>
       <c r="B86" t="n">
-        <v>258.9700012207031</v>
+        <v>396.1099853515625</v>
       </c>
       <c r="C86" t="n">
-        <v>264.75</v>
+        <v>400.1199951171875</v>
       </c>
       <c r="D86" t="n">
-        <v>258.1600036621094</v>
+        <v>395.1600036621094</v>
       </c>
       <c r="E86" t="n">
-        <v>264.5799865722656</v>
+        <v>397.2300109863281</v>
       </c>
       <c r="F86" t="n">
-        <v>42070500</v>
+        <v>34015200</v>
       </c>
     </row>
     <row r="87">
@@ -7150,19 +7190,19 @@
         <v>46076</v>
       </c>
       <c r="B87" t="n">
-        <v>263.489990234375</v>
+        <v>395</v>
       </c>
       <c r="C87" t="n">
-        <v>269.4299926757812</v>
+        <v>395.3599853515625</v>
       </c>
       <c r="D87" t="n">
-        <v>263.3800048828125</v>
+        <v>383.1000061035156</v>
       </c>
       <c r="E87" t="n">
-        <v>266.1799926757812</v>
+        <v>384.4700012207031</v>
       </c>
       <c r="F87" t="n">
-        <v>37308200</v>
+        <v>43238300</v>
       </c>
     </row>
     <row r="88">
@@ -7170,19 +7210,19 @@
         <v>46077</v>
       </c>
       <c r="B88" t="n">
-        <v>267.8599853515625</v>
+        <v>384.1400146484375</v>
       </c>
       <c r="C88" t="n">
-        <v>274.8900146484375</v>
+        <v>389.3599853515625</v>
       </c>
       <c r="D88" t="n">
-        <v>267.7099914550781</v>
+        <v>381.7099914550781</v>
       </c>
       <c r="E88" t="n">
-        <v>272.1400146484375</v>
+        <v>389</v>
       </c>
       <c r="F88" t="n">
-        <v>47014600</v>
+        <v>33884700</v>
       </c>
     </row>
     <row r="89">
@@ -7190,19 +7230,19 @@
         <v>46078</v>
       </c>
       <c r="B89" t="n">
-        <v>271.7799987792969</v>
+        <v>390.5299987792969</v>
       </c>
       <c r="C89" t="n">
-        <v>274.9400024414062</v>
+        <v>401.4700012207031</v>
       </c>
       <c r="D89" t="n">
-        <v>271.0499877929688</v>
+        <v>390.1600036621094</v>
       </c>
       <c r="E89" t="n">
-        <v>274.2300109863281</v>
+        <v>400.6000061035156</v>
       </c>
       <c r="F89" t="n">
-        <v>33714300</v>
+        <v>43625500</v>
       </c>
     </row>
     <row r="90">
@@ -7210,19 +7250,19 @@
         <v>46079</v>
       </c>
       <c r="B90" t="n">
-        <v>274.9500122070312</v>
+        <v>404.7099914550781</v>
       </c>
       <c r="C90" t="n">
-        <v>276.1099853515625</v>
+        <v>407.489990234375</v>
       </c>
       <c r="D90" t="n">
-        <v>270.7999877929688</v>
+        <v>398.739990234375</v>
       </c>
       <c r="E90" t="n">
-        <v>272.9500122070312</v>
+        <v>401.7200012207031</v>
       </c>
       <c r="F90" t="n">
-        <v>32345100</v>
+        <v>34405900</v>
       </c>
     </row>
     <row r="91">
@@ -7230,19 +7270,19 @@
         <v>46080</v>
       </c>
       <c r="B91" t="n">
-        <v>272.8099975585938</v>
+        <v>390.8800048828125</v>
       </c>
       <c r="C91" t="n">
-        <v>272.8099975585938</v>
+        <v>396.8200073242188</v>
       </c>
       <c r="D91" t="n">
-        <v>262.8900146484375</v>
+        <v>389.8800048828125</v>
       </c>
       <c r="E91" t="n">
-        <v>264.1799926757812</v>
+        <v>392.739990234375</v>
       </c>
       <c r="F91" t="n">
-        <v>72366500</v>
+        <v>51367200</v>
       </c>
     </row>
     <row r="92">
@@ -7250,19 +7290,19 @@
         <v>46083</v>
       </c>
       <c r="B92" t="n">
-        <v>262.4100036621094</v>
+        <v>392.8599853515625</v>
       </c>
       <c r="C92" t="n">
-        <v>266.5299987792969</v>
+        <v>401.1900024414062</v>
       </c>
       <c r="D92" t="n">
-        <v>260.2000122070312</v>
+        <v>390.6300048828125</v>
       </c>
       <c r="E92" t="n">
-        <v>264.7200012207031</v>
+        <v>398.5499877929688</v>
       </c>
       <c r="F92" t="n">
-        <v>41827900</v>
+        <v>35474900</v>
       </c>
     </row>
     <row r="93">
@@ -7270,19 +7310,19 @@
         <v>46084</v>
       </c>
       <c r="B93" t="n">
-        <v>263.4800109863281</v>
+        <v>393.1400146484375</v>
       </c>
       <c r="C93" t="n">
-        <v>265.5599975585938</v>
+        <v>406.7000122070312</v>
       </c>
       <c r="D93" t="n">
-        <v>260.1300048828125</v>
+        <v>392.6700134277344</v>
       </c>
       <c r="E93" t="n">
-        <v>263.75</v>
+        <v>403.9299926757812</v>
       </c>
       <c r="F93" t="n">
-        <v>38568900</v>
+        <v>38199200</v>
       </c>
     </row>
     <row r="94">
@@ -7290,19 +7330,19 @@
         <v>46085</v>
       </c>
       <c r="B94" t="n">
-        <v>264.6499938964844</v>
+        <v>401.2699890136719</v>
       </c>
       <c r="C94" t="n">
-        <v>266.1499938964844</v>
+        <v>411.0299987792969</v>
       </c>
       <c r="D94" t="n">
-        <v>261.4200134277344</v>
+        <v>400.3099975585938</v>
       </c>
       <c r="E94" t="n">
-        <v>262.5199890136719</v>
+        <v>405.2000122070312</v>
       </c>
       <c r="F94" t="n">
-        <v>39803100</v>
+        <v>35808000</v>
       </c>
     </row>
     <row r="95">
@@ -7310,19 +7350,19 @@
         <v>46086</v>
       </c>
       <c r="B95" t="n">
-        <v>260.7900085449219</v>
+        <v>404.4200134277344</v>
       </c>
       <c r="C95" t="n">
-        <v>261.5599975585938</v>
+        <v>411.6099853515625</v>
       </c>
       <c r="D95" t="n">
-        <v>257.25</v>
+        <v>404.3999938964844</v>
       </c>
       <c r="E95" t="n">
-        <v>260.2900085449219</v>
+        <v>410.6799926757812</v>
       </c>
       <c r="F95" t="n">
-        <v>49658600</v>
+        <v>39001300</v>
       </c>
     </row>
     <row r="96">
@@ -7330,19 +7370,19 @@
         <v>46087</v>
       </c>
       <c r="B96" t="n">
-        <v>258.6300048828125</v>
+        <v>409.2000122070312</v>
       </c>
       <c r="C96" t="n">
-        <v>258.7699890136719</v>
+        <v>413.0499877929688</v>
       </c>
       <c r="D96" t="n">
-        <v>254.3699951171875</v>
+        <v>408.510009765625</v>
       </c>
       <c r="E96" t="n">
-        <v>257.4599914550781</v>
+        <v>408.9599914550781</v>
       </c>
       <c r="F96" t="n">
-        <v>41120000</v>
+        <v>31123900</v>
       </c>
     </row>
     <row r="97">
@@ -7350,19 +7390,19 @@
         <v>46090</v>
       </c>
       <c r="B97" t="n">
-        <v>255.6900024414062</v>
+        <v>404.9200134277344</v>
       </c>
       <c r="C97" t="n">
-        <v>261.1499938964844</v>
+        <v>410.2099914550781</v>
       </c>
       <c r="D97" t="n">
-        <v>253.6799926757812</v>
+        <v>403.5</v>
       </c>
       <c r="E97" t="n">
-        <v>259.8800048828125</v>
+        <v>409.4100036621094</v>
       </c>
       <c r="F97" t="n">
-        <v>38218500</v>
+        <v>30131900</v>
       </c>
     </row>
     <row r="98">
@@ -7370,19 +7410,19 @@
         <v>46091</v>
       </c>
       <c r="B98" t="n">
-        <v>257.6499938964844</v>
+        <v>410.0299987792969</v>
       </c>
       <c r="C98" t="n">
-        <v>262.4800109863281</v>
+        <v>410.2000122070312</v>
       </c>
       <c r="D98" t="n">
-        <v>256.9500122070312</v>
+        <v>402.9299926757812</v>
       </c>
       <c r="E98" t="n">
-        <v>260.8299865722656</v>
+        <v>405.760009765625</v>
       </c>
       <c r="F98" t="n">
-        <v>30590800</v>
+        <v>31706400</v>
       </c>
     </row>
     <row r="99">
@@ -7390,19 +7430,19 @@
         <v>46092</v>
       </c>
       <c r="B99" t="n">
-        <v>261.0899963378906</v>
+        <v>405.5700073242188</v>
       </c>
       <c r="C99" t="n">
-        <v>262.1300048828125</v>
+        <v>409.010009765625</v>
       </c>
       <c r="D99" t="n">
-        <v>259.5499877929688</v>
+        <v>401.5899963378906</v>
       </c>
       <c r="E99" t="n">
-        <v>260.8099975585938</v>
+        <v>404.8800048828125</v>
       </c>
       <c r="F99" t="n">
-        <v>26218900</v>
+        <v>25512100</v>
       </c>
     </row>
     <row r="100">
@@ -7410,19 +7450,19 @@
         <v>46093</v>
       </c>
       <c r="B100" t="n">
-        <v>258.6600036621094</v>
+        <v>404.6300048828125</v>
       </c>
       <c r="C100" t="n">
-        <v>258.9500122070312</v>
+        <v>406.1199951171875</v>
       </c>
       <c r="D100" t="n">
-        <v>254.1799926757812</v>
+        <v>401.7099914550781</v>
       </c>
       <c r="E100" t="n">
-        <v>255.7599945068359</v>
+        <v>401.8599853515625</v>
       </c>
       <c r="F100" t="n">
-        <v>40794000</v>
+        <v>27263900</v>
       </c>
     </row>
     <row r="101">
@@ -7430,19 +7470,19 @@
         <v>46094</v>
       </c>
       <c r="B101" t="n">
-        <v>255.4799957275391</v>
+        <v>401</v>
       </c>
       <c r="C101" t="n">
-        <v>256.3299865722656</v>
+        <v>404.7999877929688</v>
       </c>
       <c r="D101" t="n">
-        <v>249.5200042724609</v>
+        <v>394.25</v>
       </c>
       <c r="E101" t="n">
-        <v>250.1199951171875</v>
+        <v>395.5499877929688</v>
       </c>
       <c r="F101" t="n">
-        <v>36930000</v>
+        <v>26848000</v>
       </c>
     </row>
     <row r="102">
@@ -7450,19 +7490,19 @@
         <v>46097</v>
       </c>
       <c r="B102" t="n">
-        <v>252.1100006103516</v>
+        <v>398.0700073242188</v>
       </c>
       <c r="C102" t="n">
-        <v>253.8899993896484</v>
+        <v>400.6300048828125</v>
       </c>
       <c r="D102" t="n">
-        <v>249.8800048828125</v>
+        <v>394.7900085449219</v>
       </c>
       <c r="E102" t="n">
-        <v>252.8200073242188</v>
+        <v>399.9500122070312</v>
       </c>
       <c r="F102" t="n">
-        <v>32074200</v>
+        <v>27733700</v>
       </c>
     </row>
     <row r="103">
@@ -7470,19 +7510,19 @@
         <v>46098</v>
       </c>
       <c r="B103" t="n">
-        <v>252.9600067138672</v>
+        <v>400.2699890136719</v>
       </c>
       <c r="C103" t="n">
-        <v>255.1300048828125</v>
+        <v>404.3999938964844</v>
       </c>
       <c r="D103" t="n">
-        <v>252.1799926757812</v>
+        <v>397.75</v>
       </c>
       <c r="E103" t="n">
-        <v>254.2299957275391</v>
+        <v>399.4100036621094</v>
       </c>
       <c r="F103" t="n">
-        <v>32361600</v>
+        <v>26228300</v>
       </c>
     </row>
     <row r="104">
@@ -7490,19 +7530,19 @@
         <v>46099</v>
       </c>
       <c r="B104" t="n">
-        <v>252.6300048828125</v>
+        <v>397.1300048828125</v>
       </c>
       <c r="C104" t="n">
-        <v>254.9400024414062</v>
+        <v>398</v>
       </c>
       <c r="D104" t="n">
-        <v>249</v>
+        <v>391</v>
       </c>
       <c r="E104" t="n">
-        <v>249.9400024414062</v>
+        <v>391.7900085449219</v>
       </c>
       <c r="F104" t="n">
-        <v>35757900</v>
+        <v>25908500</v>
       </c>
     </row>
     <row r="105">
@@ -7510,19 +7550,19 @@
         <v>46100</v>
       </c>
       <c r="B105" t="n">
-        <v>249.3999938964844</v>
+        <v>390.1000061035156</v>
       </c>
       <c r="C105" t="n">
-        <v>251.8300018310547</v>
+        <v>392.489990234375</v>
       </c>
       <c r="D105" t="n">
-        <v>247.3000030517578</v>
+        <v>387.0599975585938</v>
       </c>
       <c r="E105" t="n">
-        <v>248.9600067138672</v>
+        <v>389.0199890136719</v>
       </c>
       <c r="F105" t="n">
-        <v>34864100</v>
+        <v>25138800</v>
       </c>
     </row>
     <row r="106">
@@ -7530,19 +7570,19 @@
         <v>46101</v>
       </c>
       <c r="B106" t="n">
-        <v>247.9799957275391</v>
+        <v>386.7900085449219</v>
       </c>
       <c r="C106" t="n">
-        <v>249.1999969482422</v>
+        <v>387</v>
       </c>
       <c r="D106" t="n">
-        <v>246</v>
+        <v>380.1199951171875</v>
       </c>
       <c r="E106" t="n">
-        <v>247.9900054931641</v>
+        <v>381.8699951171875</v>
       </c>
       <c r="F106" t="n">
-        <v>88331100</v>
+        <v>50853200</v>
       </c>
     </row>
     <row r="107">
@@ -7550,19 +7590,19 @@
         <v>46104</v>
       </c>
       <c r="B107" t="n">
-        <v>253.9700012207031</v>
+        <v>383.8999938964844</v>
       </c>
       <c r="C107" t="n">
-        <v>254.6000061035156</v>
+        <v>387.2099914550781</v>
       </c>
       <c r="D107" t="n">
-        <v>250.2799987792969</v>
+        <v>381.6799926757812</v>
       </c>
       <c r="E107" t="n">
-        <v>251.4900054931641</v>
+        <v>383</v>
       </c>
       <c r="F107" t="n">
-        <v>40546100</v>
+        <v>29680100</v>
       </c>
     </row>
     <row r="108">
@@ -7570,19 +7610,19 @@
         <v>46105</v>
       </c>
       <c r="B108" t="n">
-        <v>250.3500061035156</v>
+        <v>382.3599853515625</v>
       </c>
       <c r="C108" t="n">
-        <v>254.8300018310547</v>
+        <v>382.4700012207031</v>
       </c>
       <c r="D108" t="n">
-        <v>249.5500030517578</v>
+        <v>371.8500061035156</v>
       </c>
       <c r="E108" t="n">
-        <v>251.6399993896484</v>
+        <v>372.739990234375</v>
       </c>
       <c r="F108" t="n">
-        <v>45152300</v>
+        <v>42733600</v>
       </c>
     </row>
     <row r="109">
@@ -7590,19 +7630,19 @@
         <v>46106</v>
       </c>
       <c r="B109" t="n">
-        <v>254.1000061035156</v>
+        <v>376.9200134277344</v>
       </c>
       <c r="C109" t="n">
-        <v>255</v>
+        <v>377.0599975585938</v>
       </c>
       <c r="D109" t="n">
-        <v>251.6000061035156</v>
+        <v>369.6300048828125</v>
       </c>
       <c r="E109" t="n">
-        <v>252.6199951171875</v>
+        <v>371.0400085449219</v>
       </c>
       <c r="F109" t="n">
-        <v>28476700</v>
+        <v>31181200</v>
       </c>
     </row>
     <row r="110">
@@ -7610,19 +7650,19 @@
         <v>46107</v>
       </c>
       <c r="B110" t="n">
-        <v>252.1199951171875</v>
+        <v>370.8200073242188</v>
       </c>
       <c r="C110" t="n">
-        <v>257</v>
+        <v>374.7200012207031</v>
       </c>
       <c r="D110" t="n">
-        <v>250.7700042724609</v>
+        <v>365.1900024414062</v>
       </c>
       <c r="E110" t="n">
-        <v>252.8899993896484</v>
+        <v>365.9700012207031</v>
       </c>
       <c r="F110" t="n">
-        <v>41796700</v>
+        <v>36836600</v>
       </c>
     </row>
     <row r="111">
@@ -7630,19 +7670,19 @@
         <v>46108</v>
       </c>
       <c r="B111" t="n">
-        <v>253.8999938964844</v>
+        <v>361.8999938964844</v>
       </c>
       <c r="C111" t="n">
-        <v>255.4900054931641</v>
+        <v>362.4500122070312</v>
       </c>
       <c r="D111" t="n">
-        <v>248.0700073242188</v>
+        <v>356.510009765625</v>
       </c>
       <c r="E111" t="n">
-        <v>248.8000030517578</v>
+        <v>356.7699890136719</v>
       </c>
       <c r="F111" t="n">
-        <v>47900000</v>
+        <v>37883400</v>
       </c>
     </row>
     <row r="112">
@@ -7650,19 +7690,19 @@
         <v>46111</v>
       </c>
       <c r="B112" t="n">
-        <v>250.0700073242188</v>
+        <v>361.8999938964844</v>
       </c>
       <c r="C112" t="n">
-        <v>250.8699951171875</v>
+        <v>365.3599853515625</v>
       </c>
       <c r="D112" t="n">
-        <v>245.5099945068359</v>
+        <v>356.2799987792969</v>
       </c>
       <c r="E112" t="n">
-        <v>246.6300048828125</v>
+        <v>358.9599914550781</v>
       </c>
       <c r="F112" t="n">
-        <v>39446200</v>
+        <v>44797000</v>
       </c>
     </row>
     <row r="113">
@@ -7670,19 +7710,19 @@
         <v>46112</v>
       </c>
       <c r="B113" t="n">
-        <v>247.9100036621094</v>
+        <v>364.5499877929688</v>
       </c>
       <c r="C113" t="n">
-        <v>255.4799957275391</v>
+        <v>372.8999938964844</v>
       </c>
       <c r="D113" t="n">
-        <v>247.1000061035156</v>
+        <v>363.0700073242188</v>
       </c>
       <c r="E113" t="n">
-        <v>253.7899932861328</v>
+        <v>370.1700134277344</v>
       </c>
       <c r="F113" t="n">
-        <v>49598100</v>
+        <v>45244400</v>
       </c>
     </row>
     <row r="114">
@@ -7690,19 +7730,19 @@
         <v>46113</v>
       </c>
       <c r="B114" t="n">
-        <v>254.0800018310547</v>
+        <v>373.489990234375</v>
       </c>
       <c r="C114" t="n">
-        <v>256.1799926757812</v>
+        <v>373.989990234375</v>
       </c>
       <c r="D114" t="n">
-        <v>253.3300018310547</v>
+        <v>368.2000122070312</v>
       </c>
       <c r="E114" t="n">
-        <v>255.6300048828125</v>
+        <v>369.3699951171875</v>
       </c>
       <c r="F114" t="n">
-        <v>40059400</v>
+        <v>29417200</v>
       </c>
     </row>
     <row r="115">
@@ -7710,19 +7750,19 @@
         <v>46114</v>
       </c>
       <c r="B115" t="n">
-        <v>254.1999969482422</v>
+        <v>367.2099914550781</v>
       </c>
       <c r="C115" t="n">
-        <v>256.1300048828125</v>
+        <v>373.6400146484375</v>
       </c>
       <c r="D115" t="n">
-        <v>250.6499938964844</v>
+        <v>364.1499938964844</v>
       </c>
       <c r="E115" t="n">
-        <v>255.9199981689453</v>
+        <v>373.4599914550781</v>
       </c>
       <c r="F115" t="n">
-        <v>31289400</v>
+        <v>24099100</v>
       </c>
     </row>
     <row r="116">
@@ -7730,19 +7770,19 @@
         <v>46118</v>
       </c>
       <c r="B116" t="n">
-        <v>256.510009765625</v>
+        <v>373.489990234375</v>
       </c>
       <c r="C116" t="n">
-        <v>262.1600036621094</v>
+        <v>373.7300109863281</v>
       </c>
       <c r="D116" t="n">
-        <v>256.4599914550781</v>
+        <v>369.5</v>
       </c>
       <c r="E116" t="n">
-        <v>258.8599853515625</v>
+        <v>372.8800048828125</v>
       </c>
       <c r="F116" t="n">
-        <v>29329900</v>
+        <v>16146600</v>
       </c>
     </row>
     <row r="117">
@@ -7750,19 +7790,19 @@
         <v>46119</v>
       </c>
       <c r="B117" t="n">
-        <v>256.1600036621094</v>
+        <v>370.3399963378906</v>
       </c>
       <c r="C117" t="n">
-        <v>256.2000122070312</v>
+        <v>372.4500122070312</v>
       </c>
       <c r="D117" t="n">
-        <v>245.6999969482422</v>
+        <v>366.5599975585938</v>
       </c>
       <c r="E117" t="n">
-        <v>253.5</v>
+        <v>372.2900085449219</v>
       </c>
       <c r="F117" t="n">
-        <v>62148000</v>
+        <v>21443300</v>
       </c>
     </row>
     <row r="118">
@@ -7770,19 +7810,19 @@
         <v>46120</v>
       </c>
       <c r="B118" t="n">
-        <v>258.4500122070312</v>
+        <v>384.9800109863281</v>
       </c>
       <c r="C118" t="n">
-        <v>259.75</v>
+        <v>385</v>
       </c>
       <c r="D118" t="n">
-        <v>256.5299987792969</v>
+        <v>371.4100036621094</v>
       </c>
       <c r="E118" t="n">
-        <v>258.8999938964844</v>
+        <v>374.3299865722656</v>
       </c>
       <c r="F118" t="n">
-        <v>41032800</v>
+        <v>33064800</v>
       </c>
     </row>
     <row r="119">
@@ -7790,19 +7830,19 @@
         <v>46121</v>
       </c>
       <c r="B119" t="n">
-        <v>259</v>
+        <v>372.5</v>
       </c>
       <c r="C119" t="n">
-        <v>261.1199951171875</v>
+        <v>373.5</v>
       </c>
       <c r="D119" t="n">
-        <v>256.0700073242188</v>
+        <v>367.0499877929688</v>
       </c>
       <c r="E119" t="n">
-        <v>260.489990234375</v>
+        <v>373.0700073242188</v>
       </c>
       <c r="F119" t="n">
-        <v>28121600</v>
+        <v>30435300</v>
       </c>
     </row>
     <row r="120">
@@ -7810,19 +7850,19 @@
         <v>46122</v>
       </c>
       <c r="B120" t="n">
-        <v>259.9800109863281</v>
+        <v>372.9800109863281</v>
       </c>
       <c r="C120" t="n">
-        <v>262.1900024414062</v>
+        <v>375.6400146484375</v>
       </c>
       <c r="D120" t="n">
-        <v>259.0199890136719</v>
+        <v>370.0299987792969</v>
       </c>
       <c r="E120" t="n">
-        <v>260.4800109863281</v>
+        <v>370.8699951171875</v>
       </c>
       <c r="F120" t="n">
-        <v>31291500</v>
+        <v>28111100</v>
       </c>
     </row>
     <row r="121">
@@ -7830,19 +7870,19 @@
         <v>46125</v>
       </c>
       <c r="B121" t="n">
-        <v>259.7300109863281</v>
+        <v>373.6099853515625</v>
       </c>
       <c r="C121" t="n">
-        <v>260.1799926757812</v>
+        <v>384.5400085449219</v>
       </c>
       <c r="D121" t="n">
-        <v>256.6600036621094</v>
+        <v>371.0199890136719</v>
       </c>
       <c r="E121" t="n">
-        <v>259.2000122070312</v>
+        <v>384.3699951171875</v>
       </c>
       <c r="F121" t="n">
-        <v>36234700</v>
+        <v>35745800</v>
       </c>
     </row>
     <row r="122">
@@ -7850,19 +7890,19 @@
         <v>46126</v>
       </c>
       <c r="B122" t="n">
-        <v>259.25</v>
+        <v>387.9200134277344</v>
       </c>
       <c r="C122" t="n">
-        <v>261.9299926757812</v>
+        <v>394.6900024414062</v>
       </c>
       <c r="D122" t="n">
-        <v>257.1900024414062</v>
+        <v>386.5199890136719</v>
       </c>
       <c r="E122" t="n">
-        <v>258.8299865722656</v>
+        <v>393.1099853515625</v>
       </c>
       <c r="F122" t="n">
-        <v>48370700</v>
+        <v>37504500</v>
       </c>
     </row>
     <row r="123">
@@ -7870,19 +7910,39 @@
         <v>46127</v>
       </c>
       <c r="B123" t="n">
-        <v>258.1600036621094</v>
+        <v>398</v>
       </c>
       <c r="C123" t="n">
-        <v>266.5599975585938</v>
+        <v>414.3699951171875</v>
       </c>
       <c r="D123" t="n">
-        <v>257.8099975585938</v>
+        <v>396.7300109863281</v>
       </c>
       <c r="E123" t="n">
-        <v>266.4299926757812</v>
+        <v>411.2200012207031</v>
       </c>
       <c r="F123" t="n">
-        <v>49735000</v>
+        <v>44793300</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B124" t="n">
+        <v>419.989990234375</v>
+      </c>
+      <c r="C124" t="n">
+        <v>420.5599975585938</v>
+      </c>
+      <c r="D124" t="n">
+        <v>412.1400146484375</v>
+      </c>
+      <c r="E124" t="n">
+        <v>418.6799926757812</v>
+      </c>
+      <c r="F124" t="n">
+        <v>25774334</v>
       </c>
     </row>
   </sheetData>
@@ -7896,7 +7956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10369,6 +10429,26 @@
       </c>
       <c r="F123" t="n">
         <v>42961200</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B124" t="n">
+        <v>248.9799957275391</v>
+      </c>
+      <c r="C124" t="n">
+        <v>250</v>
+      </c>
+      <c r="D124" t="n">
+        <v>244.1999969482422</v>
+      </c>
+      <c r="E124" t="n">
+        <v>249.1600952148438</v>
+      </c>
+      <c r="F124" t="n">
+        <v>25859542</v>
       </c>
     </row>
   </sheetData>
@@ -10382,7 +10462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12857,6 +12937,26 @@
         <v>14927200</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="3" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B124" t="n">
+        <v>675.989990234375</v>
+      </c>
+      <c r="C124" t="n">
+        <v>677.4099731445312</v>
+      </c>
+      <c r="D124" t="n">
+        <v>667.75</v>
+      </c>
+      <c r="E124" t="n">
+        <v>674.3599853515625</v>
+      </c>
+      <c r="F124" t="n">
+        <v>5337240</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_data.xlsx
+++ b/stock_data.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSFT" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPY" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSFT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMZN" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,19 +478,19 @@
         <v>45950</v>
       </c>
       <c r="B2" t="n">
-        <v>255.4032084113237</v>
+        <v>512.4788764440519</v>
       </c>
       <c r="C2" t="n">
-        <v>263.8770629877272</v>
+        <v>516.5519656323323</v>
       </c>
       <c r="D2" t="n">
-        <v>255.143708503654</v>
+        <v>511.3037703677804</v>
       </c>
       <c r="E2" t="n">
-        <v>261.7411193847656</v>
+        <v>514.6498413085938</v>
       </c>
       <c r="F2" t="n">
-        <v>90483000</v>
+        <v>14665600</v>
       </c>
     </row>
     <row r="3">
@@ -498,19 +498,19 @@
         <v>45951</v>
       </c>
       <c r="B3" t="n">
-        <v>261.3818200057694</v>
+        <v>515.3569857054445</v>
       </c>
       <c r="C3" t="n">
-        <v>264.7853366806196</v>
+        <v>516.5420602391357</v>
       </c>
       <c r="D3" t="n">
-        <v>261.3318968470685</v>
+        <v>510.9154330870712</v>
       </c>
       <c r="E3" t="n">
-        <v>262.2701110839844</v>
+        <v>515.5162963867188</v>
       </c>
       <c r="F3" t="n">
-        <v>46695900</v>
+        <v>15586200</v>
       </c>
     </row>
     <row r="4">
@@ -518,19 +518,19 @@
         <v>45952</v>
       </c>
       <c r="B4" t="n">
-        <v>262.1503352574342</v>
+        <v>518.9919195722497</v>
       </c>
       <c r="C4" t="n">
-        <v>262.349966966352</v>
+        <v>523.0549803520576</v>
       </c>
       <c r="D4" t="n">
-        <v>254.9440691826199</v>
+        <v>515.5661623300699</v>
       </c>
       <c r="E4" t="n">
-        <v>257.9583435058594</v>
+        <v>518.3843994140625</v>
       </c>
       <c r="F4" t="n">
-        <v>45015300</v>
+        <v>18962700</v>
       </c>
     </row>
     <row r="5">
@@ -538,19 +538,19 @@
         <v>45953</v>
       </c>
       <c r="B5" t="n">
-        <v>259.4454820834593</v>
+        <v>520.2964530626382</v>
       </c>
       <c r="C5" t="n">
-        <v>260.1241811137136</v>
+        <v>521.7802730707533</v>
       </c>
       <c r="D5" t="n">
-        <v>257.5191611036844</v>
+        <v>516.4623598997719</v>
       </c>
       <c r="E5" t="n">
-        <v>259.0861511230469</v>
+        <v>518.404296875</v>
       </c>
       <c r="F5" t="n">
-        <v>32754900</v>
+        <v>14023500</v>
       </c>
     </row>
     <row r="6">
@@ -558,19 +558,19 @@
         <v>45954</v>
       </c>
       <c r="B6" t="n">
-        <v>260.6931034322695</v>
+        <v>520.6250388201142</v>
       </c>
       <c r="C6" t="n">
-        <v>263.6275126875418</v>
+        <v>523.1744351060786</v>
       </c>
       <c r="D6" t="n">
-        <v>258.6869175950168</v>
+        <v>518.5536961256696</v>
       </c>
       <c r="E6" t="n">
-        <v>262.3200073242188</v>
+        <v>521.441650390625</v>
       </c>
       <c r="F6" t="n">
-        <v>38253700</v>
+        <v>15532400</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
         <v>45957</v>
       </c>
       <c r="B7" t="n">
-        <v>264.376098228409</v>
+        <v>529.577902779321</v>
       </c>
       <c r="C7" t="n">
-        <v>268.60802232244</v>
+        <v>532.3662956890146</v>
       </c>
       <c r="D7" t="n">
-        <v>264.1465248140549</v>
+        <v>526.819354031342</v>
       </c>
       <c r="E7" t="n">
-        <v>268.2986145019531</v>
+        <v>529.3189697265625</v>
       </c>
       <c r="F7" t="n">
-        <v>44888200</v>
+        <v>18734700</v>
       </c>
     </row>
     <row r="8">
@@ -598,19 +598,19 @@
         <v>45958</v>
       </c>
       <c r="B8" t="n">
-        <v>268.4782600095115</v>
+        <v>547.7224103521172</v>
       </c>
       <c r="C8" t="n">
-        <v>269.3765722048576</v>
+        <v>551.4269763883988</v>
       </c>
       <c r="D8" t="n">
-        <v>267.6398616921066</v>
+        <v>538.5306518978505</v>
       </c>
       <c r="E8" t="n">
-        <v>268.4882507324219</v>
+        <v>539.8252563476562</v>
       </c>
       <c r="F8" t="n">
-        <v>41534800</v>
+        <v>29986700</v>
       </c>
     </row>
     <row r="9">
@@ -618,19 +618,19 @@
         <v>45959</v>
       </c>
       <c r="B9" t="n">
-        <v>268.7677057947778</v>
+        <v>542.6833492925585</v>
       </c>
       <c r="C9" t="n">
-        <v>270.8936584399069</v>
+        <v>544.0078586434945</v>
       </c>
       <c r="D9" t="n">
-        <v>266.6018207191691</v>
+        <v>534.507325873603</v>
       </c>
       <c r="E9" t="n">
-        <v>269.1869201660156</v>
+        <v>539.307373046875</v>
       </c>
       <c r="F9" t="n">
-        <v>51086700</v>
+        <v>36023000</v>
       </c>
     </row>
     <row r="10">
@@ -638,19 +638,19 @@
         <v>45960</v>
       </c>
       <c r="B10" t="n">
-        <v>271.4725408872279</v>
+        <v>528.2831883129468</v>
       </c>
       <c r="C10" t="n">
-        <v>273.6184749716116</v>
+        <v>532.7545848667123</v>
       </c>
       <c r="D10" t="n">
-        <v>267.969239224885</v>
+        <v>519.9578228356851</v>
       </c>
       <c r="E10" t="n">
-        <v>270.8836669921875</v>
+        <v>523.582763671875</v>
       </c>
       <c r="F10" t="n">
-        <v>69886500</v>
+        <v>41023100</v>
       </c>
     </row>
     <row r="11">
@@ -658,19 +658,19 @@
         <v>45961</v>
       </c>
       <c r="B11" t="n">
-        <v>276.4630533049319</v>
+        <v>526.6898137654194</v>
       </c>
       <c r="C11" t="n">
-        <v>276.7924425807819</v>
+        <v>527.1279940743384</v>
       </c>
       <c r="D11" t="n">
-        <v>268.647962249571</v>
+        <v>512.9668501497666</v>
       </c>
       <c r="E11" t="n">
-        <v>269.8556518554688</v>
+        <v>515.6656494140625</v>
       </c>
       <c r="F11" t="n">
-        <v>86167100</v>
+        <v>34006400</v>
       </c>
     </row>
     <row r="12">
@@ -678,19 +678,19 @@
         <v>45964</v>
       </c>
       <c r="B12" t="n">
-        <v>269.9055662700252</v>
+        <v>517.657371934483</v>
       </c>
       <c r="C12" t="n">
-        <v>270.3347409275427</v>
+        <v>522.7860691817526</v>
       </c>
       <c r="D12" t="n">
-        <v>265.7434858777505</v>
+        <v>512.4590180581705</v>
       </c>
       <c r="E12" t="n">
-        <v>268.5381469726562</v>
+        <v>514.888916015625</v>
       </c>
       <c r="F12" t="n">
-        <v>50194600</v>
+        <v>22374700</v>
       </c>
     </row>
     <row r="13">
@@ -698,19 +698,19 @@
         <v>45965</v>
       </c>
       <c r="B13" t="n">
-        <v>267.8195068636227</v>
+        <v>509.6407695643784</v>
       </c>
       <c r="C13" t="n">
-        <v>270.9734988318123</v>
+        <v>513.4150529816625</v>
       </c>
       <c r="D13" t="n">
-        <v>267.1108661194202</v>
+        <v>505.7369892339689</v>
       </c>
       <c r="E13" t="n">
-        <v>269.5262756347656</v>
+        <v>512.2001342773438</v>
       </c>
       <c r="F13" t="n">
-        <v>49274800</v>
+        <v>20958700</v>
       </c>
     </row>
     <row r="14">
@@ -718,19 +718,19 @@
         <v>45966</v>
       </c>
       <c r="B14" t="n">
-        <v>268.0989800730272</v>
+        <v>511.1743415428253</v>
       </c>
       <c r="C14" t="n">
-        <v>271.1831284425123</v>
+        <v>512.6980347767452</v>
       </c>
       <c r="D14" t="n">
-        <v>266.4221834255846</v>
+        <v>504.4821687767013</v>
       </c>
       <c r="E14" t="n">
-        <v>269.6260986328125</v>
+        <v>505.0597839355469</v>
       </c>
       <c r="F14" t="n">
-        <v>43683100</v>
+        <v>23024300</v>
       </c>
     </row>
     <row r="15">
@@ -738,19 +738,19 @@
         <v>45967</v>
       </c>
       <c r="B15" t="n">
-        <v>267.3803770260164</v>
+        <v>503.5659922381216</v>
       </c>
       <c r="C15" t="n">
-        <v>272.8798740142925</v>
+        <v>503.6058351018555</v>
       </c>
       <c r="D15" t="n">
-        <v>267.3803770260164</v>
+        <v>493.7567764386794</v>
       </c>
       <c r="E15" t="n">
-        <v>269.2567749023438</v>
+        <v>495.0414428710938</v>
       </c>
       <c r="F15" t="n">
-        <v>51204000</v>
+        <v>27406500</v>
       </c>
     </row>
     <row r="16">
@@ -758,19 +758,19 @@
         <v>45968</v>
       </c>
       <c r="B16" t="n">
-        <v>269.2867154149515</v>
+        <v>494.8920702735404</v>
       </c>
       <c r="C16" t="n">
-        <v>271.7719991063764</v>
+        <v>497.3119999979126</v>
       </c>
       <c r="D16" t="n">
-        <v>266.2624809601513</v>
+        <v>491.2073803526309</v>
       </c>
       <c r="E16" t="n">
-        <v>267.9592590332031</v>
+        <v>494.7626037597656</v>
       </c>
       <c r="F16" t="n">
-        <v>48227400</v>
+        <v>24019800</v>
       </c>
     </row>
     <row r="17">
@@ -778,19 +778,19 @@
         <v>45971</v>
       </c>
       <c r="B17" t="n">
-        <v>268.7085692371889</v>
+        <v>497.9692613740871</v>
       </c>
       <c r="C17" t="n">
-        <v>273.4741297822401</v>
+        <v>504.7510576229119</v>
       </c>
       <c r="D17" t="n">
-        <v>267.2099714283653</v>
+        <v>496.7343757501637</v>
       </c>
       <c r="E17" t="n">
-        <v>269.1781311035156</v>
+        <v>503.9045715332031</v>
       </c>
       <c r="F17" t="n">
-        <v>41312400</v>
+        <v>26101500</v>
       </c>
     </row>
     <row r="18">
@@ -798,19 +798,19 @@
         <v>45972</v>
       </c>
       <c r="B18" t="n">
-        <v>269.5577590596557</v>
+        <v>502.7095490222416</v>
       </c>
       <c r="C18" t="n">
-        <v>275.6520624227355</v>
+        <v>507.4896898672195</v>
       </c>
       <c r="D18" t="n">
-        <v>269.5477586519058</v>
+        <v>500.2697130079767</v>
       </c>
       <c r="E18" t="n">
-        <v>274.99267578125</v>
+        <v>506.573486328125</v>
       </c>
       <c r="F18" t="n">
-        <v>46208300</v>
+        <v>17980000</v>
       </c>
     </row>
     <row r="19">
@@ -818,19 +818,19 @@
         <v>45973</v>
       </c>
       <c r="B19" t="n">
-        <v>274.7429239716485</v>
+        <v>507.2506574723947</v>
       </c>
       <c r="C19" t="n">
-        <v>275.4722525277038</v>
+        <v>509.5511194130969</v>
       </c>
       <c r="D19" t="n">
-        <v>271.4460210796085</v>
+        <v>497.0530724082431</v>
       </c>
       <c r="E19" t="n">
-        <v>273.21435546875</v>
+        <v>509.0233154296875</v>
       </c>
       <c r="F19" t="n">
-        <v>48398000</v>
+        <v>26574900</v>
       </c>
     </row>
     <row r="20">
@@ -838,19 +838,19 @@
         <v>45974</v>
       </c>
       <c r="B20" t="n">
-        <v>273.8537435218178</v>
+        <v>508.1967287528611</v>
       </c>
       <c r="C20" t="n">
-        <v>276.4413491841305</v>
+        <v>511.3735209246628</v>
       </c>
       <c r="D20" t="n">
-        <v>271.8356428219928</v>
+        <v>499.2140928412288</v>
       </c>
       <c r="E20" t="n">
-        <v>272.6948547363281</v>
+        <v>501.205810546875</v>
       </c>
       <c r="F20" t="n">
-        <v>49602800</v>
+        <v>25273100</v>
       </c>
     </row>
     <row r="21">
@@ -858,19 +858,19 @@
         <v>45975</v>
       </c>
       <c r="B21" t="n">
-        <v>270.7965900477885</v>
+        <v>496.166765720741</v>
       </c>
       <c r="C21" t="n">
-        <v>275.702003472256</v>
+        <v>509.4813936811572</v>
       </c>
       <c r="D21" t="n">
-        <v>269.3479639093673</v>
+        <v>495.3800287197931</v>
       </c>
       <c r="E21" t="n">
-        <v>272.1553344726562</v>
+        <v>508.0672607421875</v>
       </c>
       <c r="F21" t="n">
-        <v>47431300</v>
+        <v>28505700</v>
       </c>
     </row>
     <row r="22">
@@ -878,19 +878,19 @@
         <v>45978</v>
       </c>
       <c r="B22" t="n">
-        <v>268.5687054184609</v>
+        <v>506.3444435928635</v>
       </c>
       <c r="C22" t="n">
-        <v>270.2371271729127</v>
+        <v>509.9992285471841</v>
       </c>
       <c r="D22" t="n">
-        <v>265.4815977121726</v>
+        <v>502.8190947602184</v>
       </c>
       <c r="E22" t="n">
-        <v>267.2099609375</v>
+        <v>505.3883972167969</v>
       </c>
       <c r="F22" t="n">
-        <v>45018300</v>
+        <v>19092800</v>
       </c>
     </row>
     <row r="23">
@@ -898,19 +898,19 @@
         <v>45979</v>
       </c>
       <c r="B23" t="n">
-        <v>269.7376065335732</v>
+        <v>493.3186219236692</v>
       </c>
       <c r="C23" t="n">
-        <v>270.4569347049811</v>
+        <v>500.8971240097587</v>
       </c>
       <c r="D23" t="n">
-        <v>265.0719890725528</v>
+        <v>484.7641975590383</v>
       </c>
       <c r="E23" t="n">
-        <v>267.1900024414062</v>
+        <v>491.7451782226562</v>
       </c>
       <c r="F23" t="n">
-        <v>45677300</v>
+        <v>33815100</v>
       </c>
     </row>
     <row r="24">
@@ -918,19 +918,19 @@
         <v>45980</v>
       </c>
       <c r="B24" t="n">
-        <v>265.2817633125939</v>
+        <v>488.0704229659532</v>
       </c>
       <c r="C24" t="n">
-        <v>271.9555110777923</v>
+        <v>493.1393408084164</v>
       </c>
       <c r="D24" t="n">
-        <v>265.2517925781922</v>
+        <v>480.8305097576304</v>
       </c>
       <c r="E24" t="n">
-        <v>268.3089294433594</v>
+        <v>485.1027526855469</v>
       </c>
       <c r="F24" t="n">
-        <v>40424500</v>
+        <v>23245300</v>
       </c>
     </row>
     <row r="25">
@@ -938,19 +938,19 @@
         <v>45981</v>
       </c>
       <c r="B25" t="n">
-        <v>270.5768036466949</v>
+        <v>491.5879641710541</v>
       </c>
       <c r="C25" t="n">
-        <v>275.1725094767523</v>
+        <v>492.4460215630244</v>
       </c>
       <c r="D25" t="n">
-        <v>265.6714205454633</v>
+        <v>474.4171642897319</v>
       </c>
       <c r="E25" t="n">
-        <v>266.0010986328125</v>
+        <v>477.3404846191406</v>
       </c>
       <c r="F25" t="n">
-        <v>45823600</v>
+        <v>26802500</v>
       </c>
     </row>
     <row r="26">
@@ -958,19 +958,19 @@
         <v>45982</v>
       </c>
       <c r="B26" t="n">
-        <v>265.7013768088059</v>
+        <v>477.4103368698009</v>
       </c>
       <c r="C26" t="n">
-        <v>273.0744516711978</v>
+        <v>477.8293938228302</v>
       </c>
       <c r="D26" t="n">
-        <v>265.4216397990326</v>
+        <v>467.2036221547232</v>
       </c>
       <c r="E26" t="n">
-        <v>271.2361755371094</v>
+        <v>471.0448608398438</v>
       </c>
       <c r="F26" t="n">
-        <v>59030800</v>
+        <v>31769200</v>
       </c>
     </row>
     <row r="27">
@@ -978,19 +978,19 @@
         <v>45985</v>
       </c>
       <c r="B27" t="n">
-        <v>270.6467521230613</v>
+        <v>473.9183160323131</v>
       </c>
       <c r="C27" t="n">
-        <v>276.7410558404627</v>
+        <v>475.8139832068258</v>
       </c>
       <c r="D27" t="n">
-        <v>270.6467521230613</v>
+        <v>466.9542001322548</v>
       </c>
       <c r="E27" t="n">
-        <v>275.6620788574219</v>
+        <v>472.9205932617188</v>
       </c>
       <c r="F27" t="n">
-        <v>65585800</v>
+        <v>34421000</v>
       </c>
     </row>
     <row r="28">
@@ -998,19 +998,19 @@
         <v>45986</v>
       </c>
       <c r="B28" t="n">
-        <v>275.012667049666</v>
+        <v>472.9904142849383</v>
       </c>
       <c r="C28" t="n">
-        <v>280.1179060838009</v>
+        <v>478.0588322743821</v>
       </c>
       <c r="D28" t="n">
-        <v>274.9926967216935</v>
+        <v>463.8313270788984</v>
       </c>
       <c r="E28" t="n">
-        <v>276.7110900878906</v>
+        <v>475.9037475585938</v>
       </c>
       <c r="F28" t="n">
-        <v>46914200</v>
+        <v>28019800</v>
       </c>
     </row>
     <row r="29">
@@ -1018,19 +1018,19 @@
         <v>45987</v>
       </c>
       <c r="B29" t="n">
-        <v>276.7010825487222</v>
+        <v>485.2025316262965</v>
       </c>
       <c r="C29" t="n">
-        <v>279.2686873678638</v>
+        <v>487.1979770584782</v>
       </c>
       <c r="D29" t="n">
-        <v>276.3714044558947</v>
+        <v>480.1041831621511</v>
       </c>
       <c r="E29" t="n">
-        <v>277.29052734375</v>
+        <v>484.3943786621094</v>
       </c>
       <c r="F29" t="n">
-        <v>33431400</v>
+        <v>25709100</v>
       </c>
     </row>
     <row r="30">
@@ -1038,19 +1038,19 @@
         <v>45989</v>
       </c>
       <c r="B30" t="n">
-        <v>277.0008150112318</v>
+        <v>486.489626354464</v>
       </c>
       <c r="C30" t="n">
-        <v>278.7391786268174</v>
+        <v>491.5081706450152</v>
       </c>
       <c r="D30" t="n">
-        <v>275.7319827496524</v>
+        <v>485.541777548382</v>
       </c>
       <c r="E30" t="n">
-        <v>278.5893249511719</v>
+        <v>490.8895874023438</v>
       </c>
       <c r="F30" t="n">
-        <v>20135600</v>
+        <v>14386700</v>
       </c>
     </row>
     <row r="31">
@@ -1058,19 +1058,19 @@
         <v>45992</v>
       </c>
       <c r="B31" t="n">
-        <v>277.7501195744996</v>
+        <v>487.3277021324388</v>
       </c>
       <c r="C31" t="n">
-        <v>283.1550658399818</v>
+        <v>488.7444513856018</v>
       </c>
       <c r="D31" t="n">
-        <v>275.881872572025</v>
+        <v>483.5463243869077</v>
       </c>
       <c r="E31" t="n">
-        <v>282.8353576660156</v>
+        <v>485.6315612792969</v>
       </c>
       <c r="F31" t="n">
-        <v>46587700</v>
+        <v>23964000</v>
       </c>
     </row>
     <row r="32">
@@ -1078,19 +1078,19 @@
         <v>45993</v>
       </c>
       <c r="B32" t="n">
-        <v>282.7354345985028</v>
+        <v>485.6116258193264</v>
       </c>
       <c r="C32" t="n">
-        <v>287.1313151163589</v>
+        <v>492.3761849539621</v>
       </c>
       <c r="D32" t="n">
-        <v>282.3657853749787</v>
+        <v>485.2125428025972</v>
       </c>
       <c r="E32" t="n">
-        <v>285.9224548339844</v>
+        <v>488.8841552734375</v>
       </c>
       <c r="F32" t="n">
-        <v>53669500</v>
+        <v>19562700</v>
       </c>
     </row>
     <row r="33">
@@ -1098,19 +1098,19 @@
         <v>45994</v>
       </c>
       <c r="B33" t="n">
-        <v>285.9324708384744</v>
+        <v>475.235297143397</v>
       </c>
       <c r="C33" t="n">
-        <v>288.3501915351014</v>
+        <v>483.1372440988117</v>
       </c>
       <c r="D33" t="n">
-        <v>283.0351573834178</v>
+        <v>474.1178525596479</v>
       </c>
       <c r="E33" t="n">
-        <v>283.8843688964844</v>
+        <v>476.64208984375</v>
       </c>
       <c r="F33" t="n">
-        <v>43538700</v>
+        <v>34615100</v>
       </c>
     </row>
     <row r="34">
@@ -1118,19 +1118,19 @@
         <v>45995</v>
       </c>
       <c r="B34" t="n">
-        <v>283.8344068650217</v>
+        <v>478.6674679630734</v>
       </c>
       <c r="C34" t="n">
-        <v>284.4638227692578</v>
+        <v>480.2239129901724</v>
       </c>
       <c r="D34" t="n">
-        <v>278.3295482939282</v>
+        <v>475.4048951405118</v>
       </c>
       <c r="E34" t="n">
-        <v>280.4375915527344</v>
+        <v>479.7449951171875</v>
       </c>
       <c r="F34" t="n">
-        <v>43989100</v>
+        <v>22318200</v>
       </c>
     </row>
     <row r="35">
@@ -1138,19 +1138,19 @@
         <v>45996</v>
       </c>
       <c r="B35" t="n">
-        <v>280.2777430659675</v>
+        <v>481.4211657314621</v>
       </c>
       <c r="C35" t="n">
-        <v>280.8771882481053</v>
+        <v>482.299166614698</v>
       </c>
       <c r="D35" t="n">
-        <v>277.7900501334527</v>
+        <v>477.7894707894466</v>
       </c>
       <c r="E35" t="n">
-        <v>278.5193786621094</v>
+        <v>482.0597229003906</v>
       </c>
       <c r="F35" t="n">
-        <v>47265800</v>
+        <v>22608700</v>
       </c>
     </row>
     <row r="36">
@@ -1158,19 +1158,19 @@
         <v>45999</v>
       </c>
       <c r="B36" t="n">
-        <v>277.8699843761556</v>
+        <v>483.7858099301447</v>
       </c>
       <c r="C36" t="n">
-        <v>279.4085531850005</v>
+        <v>491.1789088824644</v>
       </c>
       <c r="D36" t="n">
-        <v>275.8918244790692</v>
+        <v>483.2769615726175</v>
       </c>
       <c r="E36" t="n">
-        <v>277.6302185058594</v>
+        <v>489.9018249511719</v>
       </c>
       <c r="F36" t="n">
-        <v>38211800</v>
+        <v>21965900</v>
       </c>
     </row>
     <row r="37">
@@ -1178,19 +1178,19 @@
         <v>46000</v>
       </c>
       <c r="B37" t="n">
-        <v>277.8999627322321</v>
+        <v>487.9862027558801</v>
       </c>
       <c r="C37" t="n">
-        <v>279.7682096639769</v>
+        <v>490.9993144973556</v>
       </c>
       <c r="D37" t="n">
-        <v>276.6611317163261</v>
+        <v>487.3875630167038</v>
       </c>
       <c r="E37" t="n">
-        <v>276.9208679199219</v>
+        <v>490.8995361328125</v>
       </c>
       <c r="F37" t="n">
-        <v>32193300</v>
+        <v>14696100</v>
       </c>
     </row>
     <row r="38">
@@ -1198,19 +1198,19 @@
         <v>46001</v>
       </c>
       <c r="B38" t="n">
-        <v>277.490342786908</v>
+        <v>482.9277288439703</v>
       </c>
       <c r="C38" t="n">
-        <v>279.4884730680018</v>
+        <v>483.1472290611572</v>
       </c>
       <c r="D38" t="n">
-        <v>276.1815698919154</v>
+        <v>473.9980982856002</v>
       </c>
       <c r="E38" t="n">
-        <v>278.5193786621094</v>
+        <v>477.4701843261719</v>
       </c>
       <c r="F38" t="n">
-        <v>33038300</v>
+        <v>35756200</v>
       </c>
     </row>
     <row r="39">
@@ -1218,19 +1218,19 @@
         <v>46002</v>
       </c>
       <c r="B39" t="n">
-        <v>278.8390875870869</v>
+        <v>475.5445986070271</v>
       </c>
       <c r="C39" t="n">
-        <v>279.3286197507982</v>
+        <v>484.9231863556336</v>
       </c>
       <c r="D39" t="n">
-        <v>273.5540244422053</v>
+        <v>474.7763326037194</v>
       </c>
       <c r="E39" t="n">
-        <v>277.7700805664062</v>
+        <v>482.3690185546875</v>
       </c>
       <c r="F39" t="n">
-        <v>33248000</v>
+        <v>24669200</v>
       </c>
     </row>
     <row r="40">
@@ -1238,19 +1238,19 @@
         <v>46003</v>
       </c>
       <c r="B40" t="n">
-        <v>277.64021728323</v>
+        <v>478.7273480015789</v>
       </c>
       <c r="C40" t="n">
-        <v>278.9589906850317</v>
+        <v>481.3513637649093</v>
       </c>
       <c r="D40" t="n">
-        <v>276.5612402656973</v>
+        <v>475.2552617920193</v>
       </c>
       <c r="E40" t="n">
-        <v>278.0198669433594</v>
+        <v>477.4402770996094</v>
       </c>
       <c r="F40" t="n">
-        <v>39532900</v>
+        <v>21248100</v>
       </c>
     </row>
     <row r="41">
@@ -1258,19 +1258,19 @@
         <v>46006</v>
       </c>
       <c r="B41" t="n">
-        <v>279.8880911943856</v>
+        <v>479.0066832317436</v>
       </c>
       <c r="C41" t="n">
-        <v>279.8880911943856</v>
+        <v>479.6252664455081</v>
       </c>
       <c r="D41" t="n">
-        <v>272.5849275039148</v>
+        <v>471.4439279747418</v>
       </c>
       <c r="E41" t="n">
-        <v>273.8537292480469</v>
+        <v>473.7387084960938</v>
       </c>
       <c r="F41" t="n">
-        <v>50409100</v>
+        <v>23727700</v>
       </c>
     </row>
     <row r="42">
@@ -1278,19 +1278,19 @@
         <v>46007</v>
       </c>
       <c r="B42" t="n">
-        <v>272.5649667835892</v>
+        <v>470.8353364785088</v>
       </c>
       <c r="C42" t="n">
-        <v>275.2424541197232</v>
+        <v>476.8017293564801</v>
       </c>
       <c r="D42" t="n">
-        <v>271.535930878856</v>
+        <v>469.8076832860371</v>
       </c>
       <c r="E42" t="n">
-        <v>274.353271484375</v>
+        <v>475.3051452636719</v>
       </c>
       <c r="F42" t="n">
-        <v>37648600</v>
+        <v>20705600</v>
       </c>
     </row>
     <row r="43">
@@ -1298,19 +1298,19 @@
         <v>46008</v>
       </c>
       <c r="B43" t="n">
-        <v>274.7529265191943</v>
+        <v>475.8239455574328</v>
       </c>
       <c r="C43" t="n">
-        <v>275.9018453851206</v>
+        <v>478.9069051052783</v>
       </c>
       <c r="D43" t="n">
-        <v>271.3860817211021</v>
+        <v>473.9182915104317</v>
       </c>
       <c r="E43" t="n">
-        <v>271.5858764648438</v>
+        <v>475.0357360839844</v>
       </c>
       <c r="F43" t="n">
-        <v>50138700</v>
+        <v>24527200</v>
       </c>
     </row>
     <row r="44">
@@ -1318,19 +1318,19 @@
         <v>46009</v>
       </c>
       <c r="B44" t="n">
-        <v>273.3542023206923</v>
+        <v>477.1010453906704</v>
       </c>
       <c r="C44" t="n">
-        <v>273.374203136776</v>
+        <v>488.4850656489584</v>
       </c>
       <c r="D44" t="n">
-        <v>266.7004552212896</v>
+        <v>476.8017407441929</v>
       </c>
       <c r="E44" t="n">
-        <v>271.935546875</v>
+        <v>482.8778686523438</v>
       </c>
       <c r="F44" t="n">
-        <v>51630700</v>
+        <v>28573500</v>
       </c>
     </row>
     <row r="45">
@@ -1338,19 +1338,19 @@
         <v>46010</v>
       </c>
       <c r="B45" t="n">
-        <v>271.8955859651445</v>
+        <v>486.2501387748106</v>
       </c>
       <c r="C45" t="n">
-        <v>274.343307881706</v>
+        <v>486.7390436209232</v>
       </c>
       <c r="D45" t="n">
-        <v>269.6476892826471</v>
+        <v>481.39123391446</v>
       </c>
       <c r="E45" t="n">
-        <v>273.4141845703125</v>
+        <v>484.8134460449219</v>
       </c>
       <c r="F45" t="n">
-        <v>144632000</v>
+        <v>70836100</v>
       </c>
     </row>
     <row r="46">
@@ -1358,19 +1358,19 @@
         <v>46013</v>
       </c>
       <c r="B46" t="n">
-        <v>272.6048920133635</v>
+        <v>485.0129839081317</v>
       </c>
       <c r="C46" t="n">
-        <v>273.6239579412959</v>
+        <v>487.6170561484318</v>
       </c>
       <c r="D46" t="n">
-        <v>270.2571133897843</v>
+        <v>481.5908021440126</v>
       </c>
       <c r="E46" t="n">
-        <v>270.7166748046875</v>
+        <v>483.8157348632812</v>
       </c>
       <c r="F46" t="n">
-        <v>36571800</v>
+        <v>16963000</v>
       </c>
     </row>
     <row r="47">
@@ -1378,19 +1378,19 @@
         <v>46014</v>
       </c>
       <c r="B47" t="n">
-        <v>270.5868091030317</v>
+        <v>483.8755963136496</v>
       </c>
       <c r="C47" t="n">
-        <v>272.2452609569047</v>
+        <v>486.7190818282799</v>
       </c>
       <c r="D47" t="n">
-        <v>269.3080068949797</v>
+        <v>483.6361221459561</v>
       </c>
       <c r="E47" t="n">
-        <v>272.1053771972656</v>
+        <v>485.7413330078125</v>
       </c>
       <c r="F47" t="n">
-        <v>29642000</v>
+        <v>14683600</v>
       </c>
     </row>
     <row r="48">
@@ -1398,19 +1398,19 @@
         <v>46015</v>
       </c>
       <c r="B48" t="n">
-        <v>272.085389177814</v>
+        <v>484.5739628623746</v>
       </c>
       <c r="C48" t="n">
-        <v>275.1724967178681</v>
+        <v>488.0460488858467</v>
       </c>
       <c r="D48" t="n">
-        <v>271.9455359163183</v>
+        <v>483.7258924615979</v>
       </c>
       <c r="E48" t="n">
-        <v>273.5540161132812</v>
+        <v>486.9086303710938</v>
       </c>
       <c r="F48" t="n">
-        <v>17910600</v>
+        <v>5855900</v>
       </c>
     </row>
     <row r="49">
@@ -1418,19 +1418,19 @@
         <v>46017</v>
       </c>
       <c r="B49" t="n">
-        <v>273.9037084592662</v>
+        <v>485.601642461088</v>
       </c>
       <c r="C49" t="n">
-        <v>275.1125687682936</v>
+        <v>487.0084352251927</v>
       </c>
       <c r="D49" t="n">
-        <v>272.6049054553</v>
+        <v>484.8533503811227</v>
       </c>
       <c r="E49" t="n">
-        <v>273.1444091796875</v>
+        <v>486.599365234375</v>
       </c>
       <c r="F49" t="n">
-        <v>21521800</v>
+        <v>8842200</v>
       </c>
     </row>
     <row r="50">
@@ -1438,19 +1438,19 @@
         <v>46020</v>
       </c>
       <c r="B50" t="n">
-        <v>272.4350823114352</v>
+        <v>483.7558335295542</v>
       </c>
       <c r="C50" t="n">
-        <v>274.103504063292</v>
+        <v>487.2379065999322</v>
       </c>
       <c r="D50" t="n">
-        <v>272.0954038139857</v>
+        <v>483.0773893732932</v>
       </c>
       <c r="E50" t="n">
-        <v>273.5040893554688</v>
+        <v>485.9907531738281</v>
       </c>
       <c r="F50" t="n">
-        <v>23715200</v>
+        <v>10893400</v>
       </c>
     </row>
     <row r="51">
@@ -1458,19 +1458,19 @@
         <v>46021</v>
       </c>
       <c r="B51" t="n">
-        <v>272.5549704076282</v>
+        <v>484.8234150126488</v>
       </c>
       <c r="C51" t="n">
-        <v>273.8237722152489</v>
+        <v>488.5648753746365</v>
       </c>
       <c r="D51" t="n">
-        <v>272.0254670796708</v>
+        <v>484.3944015320139</v>
       </c>
       <c r="E51" t="n">
-        <v>272.82470703125</v>
+        <v>486.3699035644531</v>
       </c>
       <c r="F51" t="n">
-        <v>22139600</v>
+        <v>13944500</v>
       </c>
     </row>
     <row r="52">
@@ -1478,19 +1478,19 @@
         <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>272.804725327361</v>
+        <v>486.7290680267604</v>
       </c>
       <c r="C52" t="n">
-        <v>273.4241408373621</v>
+        <v>487.0284031238816</v>
       </c>
       <c r="D52" t="n">
-        <v>271.4959524300237</v>
+        <v>482.1993981667827</v>
       </c>
       <c r="E52" t="n">
-        <v>271.6058349609375</v>
+        <v>482.5186767578125</v>
       </c>
       <c r="F52" t="n">
-        <v>27293600</v>
+        <v>15601600</v>
       </c>
     </row>
     <row r="53">
@@ -1498,19 +1498,19 @@
         <v>46024</v>
       </c>
       <c r="B53" t="n">
-        <v>272.0054842546519</v>
+        <v>483.2869444224563</v>
       </c>
       <c r="C53" t="n">
-        <v>277.5802543100492</v>
+        <v>483.5563186075122</v>
       </c>
       <c r="D53" t="n">
-        <v>268.7485221479618</v>
+        <v>469.0893385249197</v>
       </c>
       <c r="E53" t="n">
-        <v>270.7566528320312</v>
+        <v>471.8630065917969</v>
       </c>
       <c r="F53" t="n">
-        <v>37838100</v>
+        <v>25571600</v>
       </c>
     </row>
     <row r="54">
@@ -1518,19 +1518,19 @@
         <v>46027</v>
       </c>
       <c r="B54" t="n">
-        <v>270.387007446453</v>
+        <v>472.9804293228547</v>
       </c>
       <c r="C54" t="n">
-        <v>271.2561892506844</v>
+        <v>474.9858617296903</v>
       </c>
       <c r="D54" t="n">
-        <v>265.8912142612155</v>
+        <v>468.4308161640092</v>
       </c>
       <c r="E54" t="n">
-        <v>267.0101623535156</v>
+        <v>471.773193359375</v>
       </c>
       <c r="F54" t="n">
-        <v>45647200</v>
+        <v>25250300</v>
       </c>
     </row>
     <row r="55">
@@ -1538,19 +1538,19 @@
         <v>46028</v>
       </c>
       <c r="B55" t="n">
-        <v>266.7503924619391</v>
+        <v>472.7210225701547</v>
       </c>
       <c r="C55" t="n">
-        <v>267.2998660934885</v>
+        <v>477.6497753472042</v>
       </c>
       <c r="D55" t="n">
-        <v>261.8749496989937</v>
+        <v>468.6802576477938</v>
       </c>
       <c r="E55" t="n">
-        <v>262.1147155761719</v>
+        <v>477.4203186035156</v>
       </c>
       <c r="F55" t="n">
-        <v>52352100</v>
+        <v>23037700</v>
       </c>
     </row>
     <row r="56">
@@ -1558,19 +1558,19 @@
         <v>46029</v>
       </c>
       <c r="B56" t="n">
-        <v>262.9539513876447</v>
+        <v>478.6674756822987</v>
       </c>
       <c r="C56" t="n">
-        <v>263.4334831315393</v>
+        <v>488.5848422406915</v>
       </c>
       <c r="D56" t="n">
-        <v>259.5671060011504</v>
+        <v>476.861599942913</v>
       </c>
       <c r="E56" t="n">
-        <v>260.0866088867188</v>
+        <v>482.3690185546875</v>
       </c>
       <c r="F56" t="n">
-        <v>48309800</v>
+        <v>25564200</v>
       </c>
     </row>
     <row r="57">
@@ -1578,19 +1578,19 @@
         <v>46030</v>
       </c>
       <c r="B57" t="n">
-        <v>256.7797203952787</v>
+        <v>480.1440867981462</v>
       </c>
       <c r="C57" t="n">
-        <v>259.0476178563403</v>
+        <v>481.5608665012806</v>
       </c>
       <c r="D57" t="n">
-        <v>255.4609622909548</v>
+        <v>474.7763335277468</v>
       </c>
       <c r="E57" t="n">
-        <v>258.7978515625</v>
+        <v>477.0212097167969</v>
       </c>
       <c r="F57" t="n">
-        <v>50419300</v>
+        <v>18162600</v>
       </c>
     </row>
     <row r="58">
@@ -1598,19 +1598,19 @@
         <v>46031</v>
       </c>
       <c r="B58" t="n">
-        <v>258.8377955175017</v>
+        <v>472.9804540365218</v>
       </c>
       <c r="C58" t="n">
-        <v>259.9667440583015</v>
+        <v>478.7273469366413</v>
       </c>
       <c r="D58" t="n">
-        <v>255.9804837142826</v>
+        <v>471.1247042989064</v>
       </c>
       <c r="E58" t="n">
-        <v>259.1275329589844</v>
+        <v>478.1885681152344</v>
       </c>
       <c r="F58" t="n">
-        <v>39997000</v>
+        <v>18491000</v>
       </c>
     </row>
     <row r="59">
@@ -1618,19 +1618,19 @@
         <v>46034</v>
       </c>
       <c r="B59" t="n">
-        <v>258.9177364764393</v>
+        <v>475.5845048686955</v>
       </c>
       <c r="C59" t="n">
-        <v>261.055720113683</v>
+        <v>479.894643901475</v>
       </c>
       <c r="D59" t="n">
-        <v>256.5599267903311</v>
+        <v>474.5967386659474</v>
       </c>
       <c r="E59" t="n">
-        <v>260.0067138671875</v>
+        <v>476.0933227539062</v>
       </c>
       <c r="F59" t="n">
-        <v>45263800</v>
+        <v>23519900</v>
       </c>
     </row>
     <row r="60">
@@ -1638,19 +1638,19 @@
         <v>46035</v>
       </c>
       <c r="B60" t="n">
-        <v>258.4781303943212</v>
+        <v>473.5990225282599</v>
       </c>
       <c r="C60" t="n">
-        <v>261.5652379723006</v>
+        <v>474.6965236309785</v>
       </c>
       <c r="D60" t="n">
-        <v>258.148452318208</v>
+        <v>464.888922501957</v>
       </c>
       <c r="E60" t="n">
-        <v>260.8059387207031</v>
+        <v>469.5981750488281</v>
       </c>
       <c r="F60" t="n">
-        <v>45730800</v>
+        <v>28545800</v>
       </c>
     </row>
     <row r="61">
@@ -1658,19 +1658,19 @@
         <v>46036</v>
       </c>
       <c r="B61" t="n">
-        <v>259.247418118488</v>
+        <v>465.3977566654985</v>
       </c>
       <c r="C61" t="n">
-        <v>261.5752571005171</v>
+        <v>467.1338149970701</v>
       </c>
       <c r="D61" t="n">
-        <v>256.4700180914029</v>
+        <v>456.1289340170423</v>
       </c>
       <c r="E61" t="n">
-        <v>259.7169799804688</v>
+        <v>458.3338928222656</v>
       </c>
       <c r="F61" t="n">
-        <v>40019400</v>
+        <v>28184300</v>
       </c>
     </row>
     <row r="62">
@@ -1678,19 +1678,19 @@
         <v>46037</v>
       </c>
       <c r="B62" t="n">
-        <v>260.4063187564486</v>
+        <v>463.0630900555096</v>
       </c>
       <c r="C62" t="n">
-        <v>260.7959687899761</v>
+        <v>463.1927988881192</v>
       </c>
       <c r="D62" t="n">
-        <v>256.8096782083212</v>
+        <v>454.8618076165624</v>
       </c>
       <c r="E62" t="n">
-        <v>257.9685974121094</v>
+        <v>455.6200866699219</v>
       </c>
       <c r="F62" t="n">
-        <v>39388600</v>
+        <v>23225800</v>
       </c>
     </row>
     <row r="63">
@@ -1698,19 +1698,19 @@
         <v>46038</v>
       </c>
       <c r="B63" t="n">
-        <v>257.6589020182799</v>
+        <v>456.7873986695315</v>
       </c>
       <c r="C63" t="n">
-        <v>258.6579671912775</v>
+        <v>462.1352085061545</v>
       </c>
       <c r="D63" t="n">
-        <v>254.6916772349149</v>
+        <v>455.4404972994736</v>
       </c>
       <c r="E63" t="n">
-        <v>255.2911224365234</v>
+        <v>458.8127746582031</v>
       </c>
       <c r="F63" t="n">
-        <v>72142800</v>
+        <v>34246700</v>
       </c>
     </row>
     <row r="64">
@@ -1718,19 +1718,19 @@
         <v>46042</v>
       </c>
       <c r="B64" t="n">
-        <v>252.4937373957159</v>
+        <v>450.1924514863621</v>
       </c>
       <c r="C64" t="n">
-        <v>254.5518092169813</v>
+        <v>455.7597309230742</v>
       </c>
       <c r="D64" t="n">
-        <v>243.1924430560896</v>
+        <v>448.2568669541529</v>
       </c>
       <c r="E64" t="n">
-        <v>246.4693756103516</v>
+        <v>453.4849243164062</v>
       </c>
       <c r="F64" t="n">
-        <v>80267500</v>
+        <v>26130000</v>
       </c>
     </row>
     <row r="65">
@@ -1738,19 +1738,19 @@
         <v>46043</v>
       </c>
       <c r="B65" t="n">
-        <v>248.4675090444481</v>
+        <v>451.5693196059127</v>
       </c>
       <c r="C65" t="n">
-        <v>251.3248360900433</v>
+        <v>451.6591109990197</v>
       </c>
       <c r="D65" t="n">
-        <v>244.9507953165175</v>
+        <v>437.6810056251358</v>
       </c>
       <c r="E65" t="n">
-        <v>247.4184875488281</v>
+        <v>443.0986328125</v>
       </c>
       <c r="F65" t="n">
-        <v>54641700</v>
+        <v>37980500</v>
       </c>
     </row>
     <row r="66">
@@ -1758,19 +1758,19 @@
         <v>46044</v>
       </c>
       <c r="B66" t="n">
-        <v>248.9670398844787</v>
+        <v>446.600636936346</v>
       </c>
       <c r="C66" t="n">
-        <v>250.7653602579427</v>
+        <v>451.8087507279656</v>
       </c>
       <c r="D66" t="n">
-        <v>247.9180183962477</v>
+        <v>443.6873036586902</v>
       </c>
       <c r="E66" t="n">
-        <v>248.1178436279297</v>
+        <v>450.1126403808594</v>
       </c>
       <c r="F66" t="n">
-        <v>39708300</v>
+        <v>25349400</v>
       </c>
     </row>
     <row r="67">
@@ -1778,19 +1778,19 @@
         <v>46045</v>
       </c>
       <c r="B67" t="n">
-        <v>247.0888078223564</v>
+        <v>450.8409629929935</v>
       </c>
       <c r="C67" t="n">
-        <v>249.176850391454</v>
+        <v>470.0271819611143</v>
       </c>
       <c r="D67" t="n">
-        <v>244.4512611104123</v>
+        <v>449.5040181949105</v>
       </c>
       <c r="E67" t="n">
-        <v>247.8081207275391</v>
+        <v>464.888916015625</v>
       </c>
       <c r="F67" t="n">
-        <v>41689000</v>
+        <v>38000200</v>
       </c>
     </row>
     <row r="68">
@@ -1798,19 +1798,19 @@
         <v>46048</v>
       </c>
       <c r="B68" t="n">
-        <v>251.2449001563489</v>
+        <v>464.2503622118351</v>
       </c>
       <c r="C68" t="n">
-        <v>256.320152957849</v>
+        <v>473.1700058760031</v>
       </c>
       <c r="D68" t="n">
-        <v>249.5664780183616</v>
+        <v>460.9479024031912</v>
       </c>
       <c r="E68" t="n">
-        <v>255.1712341308594</v>
+        <v>469.2090454101562</v>
       </c>
       <c r="F68" t="n">
-        <v>55969200</v>
+        <v>29291200</v>
       </c>
     </row>
     <row r="69">
@@ -1818,19 +1818,19 @@
         <v>46049</v>
       </c>
       <c r="B69" t="n">
-        <v>258.9277169221324</v>
+        <v>472.62128861771</v>
       </c>
       <c r="C69" t="n">
-        <v>261.705116697089</v>
+        <v>481.7703893732875</v>
       </c>
       <c r="D69" t="n">
-        <v>257.9685924683142</v>
+        <v>472.0825097961169</v>
       </c>
       <c r="E69" t="n">
-        <v>258.0285339355469</v>
+        <v>479.485595703125</v>
       </c>
       <c r="F69" t="n">
-        <v>49648300</v>
+        <v>29213900</v>
       </c>
     </row>
     <row r="70">
@@ -1838,19 +1838,19 @@
         <v>46050</v>
       </c>
       <c r="B70" t="n">
-        <v>257.409147241713</v>
+        <v>482.1095916405993</v>
       </c>
       <c r="C70" t="n">
-        <v>258.6180076181917</v>
+        <v>482.6383834693597</v>
       </c>
       <c r="D70" t="n">
-        <v>254.2720830679268</v>
+        <v>476.9114647448887</v>
       </c>
       <c r="E70" t="n">
-        <v>256.2002868652344</v>
+        <v>480.533203125</v>
       </c>
       <c r="F70" t="n">
-        <v>41288000</v>
+        <v>36875400</v>
       </c>
     </row>
     <row r="71">
@@ -1858,19 +1858,19 @@
         <v>46051</v>
       </c>
       <c r="B71" t="n">
-        <v>257.758806680925</v>
+        <v>438.9880283656418</v>
       </c>
       <c r="C71" t="n">
-        <v>259.4072580677027</v>
+        <v>441.4923222419712</v>
       </c>
       <c r="D71" t="n">
-        <v>254.1721664792058</v>
+        <v>420.0612263501361</v>
       </c>
       <c r="E71" t="n">
-        <v>258.0385437011719</v>
+        <v>432.5128173828125</v>
       </c>
       <c r="F71" t="n">
-        <v>67253000</v>
+        <v>128855300</v>
       </c>
     </row>
     <row r="72">
@@ -1878,19 +1878,19 @@
         <v>46052</v>
       </c>
       <c r="B72" t="n">
-        <v>254.9314433110553</v>
+        <v>438.1699022937122</v>
       </c>
       <c r="C72" t="n">
-        <v>261.6551472598355</v>
+        <v>438.5989157576861</v>
       </c>
       <c r="D72" t="n">
-        <v>251.9442331321547</v>
+        <v>425.4788680207893</v>
       </c>
       <c r="E72" t="n">
-        <v>259.2374267578125</v>
+        <v>429.3101196289062</v>
       </c>
       <c r="F72" t="n">
-        <v>92443400</v>
+        <v>58566800</v>
       </c>
     </row>
     <row r="73">
@@ -1898,19 +1898,19 @@
         <v>46055</v>
       </c>
       <c r="B73" t="n">
-        <v>259.7869174093499</v>
+        <v>429.2602343395754</v>
       </c>
       <c r="C73" t="n">
-        <v>270.2371306501278</v>
+        <v>429.7590957240154</v>
       </c>
       <c r="D73" t="n">
-        <v>258.9676766447768</v>
+        <v>421.28843915961</v>
       </c>
       <c r="E73" t="n">
-        <v>269.7575988769531</v>
+        <v>422.4058837890625</v>
       </c>
       <c r="F73" t="n">
-        <v>73913400</v>
+        <v>42219900</v>
       </c>
     </row>
     <row r="74">
@@ -1918,19 +1918,19 @@
         <v>46056</v>
       </c>
       <c r="B74" t="n">
-        <v>268.9483513556569</v>
+        <v>421.0489834358989</v>
       </c>
       <c r="C74" t="n">
-        <v>271.6258386480508</v>
+        <v>421.0888704228976</v>
       </c>
       <c r="D74" t="n">
-        <v>267.3598109321867</v>
+        <v>407.6296003977664</v>
       </c>
       <c r="E74" t="n">
-        <v>269.2280883789062</v>
+        <v>410.2735595703125</v>
       </c>
       <c r="F74" t="n">
-        <v>64394700</v>
+        <v>61424100</v>
       </c>
     </row>
     <row r="75">
@@ -1938,19 +1938,19 @@
         <v>46057</v>
       </c>
       <c r="B75" t="n">
-        <v>272.03545112075</v>
+        <v>410.0640575889883</v>
       </c>
       <c r="C75" t="n">
-        <v>278.6892285045384</v>
+        <v>418.8440057668918</v>
       </c>
       <c r="D75" t="n">
-        <v>272.03545112075</v>
+        <v>408.3080557741746</v>
       </c>
       <c r="E75" t="n">
-        <v>276.2315063476562</v>
+        <v>413.2467956542969</v>
       </c>
       <c r="F75" t="n">
-        <v>90545700</v>
+        <v>45012400</v>
       </c>
     </row>
     <row r="76">
@@ -1958,19 +1958,19 @@
         <v>46058</v>
       </c>
       <c r="B76" t="n">
-        <v>277.8699949435269</v>
+        <v>406.5121603821183</v>
       </c>
       <c r="C76" t="n">
-        <v>279.2387093202658</v>
+        <v>407.3701873334875</v>
       </c>
       <c r="D76" t="n">
-        <v>272.9745818081728</v>
+        <v>391.4265972483441</v>
       </c>
       <c r="E76" t="n">
-        <v>275.6520690917969</v>
+        <v>392.7735290527344</v>
       </c>
       <c r="F76" t="n">
-        <v>52977400</v>
+        <v>66289200</v>
       </c>
     </row>
     <row r="77">
@@ -1978,19 +1978,19 @@
         <v>46059</v>
       </c>
       <c r="B77" t="n">
-        <v>276.8609202349588</v>
+        <v>398.2609865133262</v>
       </c>
       <c r="C77" t="n">
-        <v>280.6473855638201</v>
+        <v>400.875015135043</v>
       </c>
       <c r="D77" t="n">
-        <v>276.6710954236804</v>
+        <v>392.0252195920243</v>
       </c>
       <c r="E77" t="n">
-        <v>277.8599853515625</v>
+        <v>400.2265014648438</v>
       </c>
       <c r="F77" t="n">
-        <v>50453400</v>
+        <v>53515300</v>
       </c>
     </row>
     <row r="78">
@@ -1998,19 +1998,19 @@
         <v>46062</v>
       </c>
       <c r="B78" t="n">
-        <v>277.9100036621094</v>
+        <v>403.9280678877113</v>
       </c>
       <c r="C78" t="n">
-        <v>278.2000122070312</v>
+        <v>413.9452129833927</v>
       </c>
       <c r="D78" t="n">
-        <v>271.7000122070312</v>
+        <v>399.9571203178888</v>
       </c>
       <c r="E78" t="n">
-        <v>274.6199951171875</v>
+        <v>412.6581420898438</v>
       </c>
       <c r="F78" t="n">
-        <v>44623400</v>
+        <v>45480500</v>
       </c>
     </row>
     <row r="79">
@@ -2018,19 +2018,19 @@
         <v>46063</v>
       </c>
       <c r="B79" t="n">
-        <v>274.8900146484375</v>
+        <v>418.6644027817824</v>
       </c>
       <c r="C79" t="n">
-        <v>275.3699951171875</v>
+        <v>422.7151545880433</v>
       </c>
       <c r="D79" t="n">
-        <v>272.9400024414062</v>
+        <v>411.76017861217</v>
       </c>
       <c r="E79" t="n">
-        <v>273.6799926757812</v>
+        <v>412.328857421875</v>
       </c>
       <c r="F79" t="n">
-        <v>34376900</v>
+        <v>44857900</v>
       </c>
     </row>
     <row r="80">
@@ -2038,19 +2038,19 @@
         <v>46064</v>
       </c>
       <c r="B80" t="n">
-        <v>274.7000122070312</v>
+        <v>415.2322299614449</v>
       </c>
       <c r="C80" t="n">
-        <v>280.1799926757812</v>
+        <v>415.5115911022014</v>
       </c>
       <c r="D80" t="n">
-        <v>274.4500122070312</v>
+        <v>400.096793508188</v>
       </c>
       <c r="E80" t="n">
-        <v>275.5</v>
+        <v>403.4491271972656</v>
       </c>
       <c r="F80" t="n">
-        <v>51931300</v>
+        <v>42491000</v>
       </c>
     </row>
     <row r="81">
@@ -2058,19 +2058,19 @@
         <v>46065</v>
       </c>
       <c r="B81" t="n">
-        <v>275.5899963378906</v>
+        <v>404.0777037056333</v>
       </c>
       <c r="C81" t="n">
-        <v>275.7200012207031</v>
+        <v>405.2749831551046</v>
       </c>
       <c r="D81" t="n">
-        <v>260.1799926757812</v>
+        <v>397.1036315998776</v>
       </c>
       <c r="E81" t="n">
-        <v>261.7300109863281</v>
+        <v>400.9248962402344</v>
       </c>
       <c r="F81" t="n">
-        <v>81077200</v>
+        <v>40802400</v>
       </c>
     </row>
     <row r="82">
@@ -2078,19 +2078,19 @@
         <v>46066</v>
       </c>
       <c r="B82" t="n">
-        <v>262.010009765625</v>
+        <v>403.528974460687</v>
       </c>
       <c r="C82" t="n">
-        <v>262.2300109863281</v>
+        <v>404.6164885937555</v>
       </c>
       <c r="D82" t="n">
-        <v>255.4499969482422</v>
+        <v>397.1435245648219</v>
       </c>
       <c r="E82" t="n">
-        <v>255.7799987792969</v>
+        <v>400.4060974121094</v>
       </c>
       <c r="F82" t="n">
-        <v>56290700</v>
+        <v>34091600</v>
       </c>
     </row>
     <row r="83">
@@ -2098,19 +2098,19 @@
         <v>46070</v>
       </c>
       <c r="B83" t="n">
-        <v>258.0499877929688</v>
+        <v>398.3108793269315</v>
       </c>
       <c r="C83" t="n">
-        <v>266.2900085449219</v>
+        <v>399.6079067287359</v>
       </c>
       <c r="D83" t="n">
-        <v>255.5399932861328</v>
+        <v>393.6315571718042</v>
       </c>
       <c r="E83" t="n">
-        <v>263.8800048828125</v>
+        <v>395.9562377929688</v>
       </c>
       <c r="F83" t="n">
-        <v>58469100</v>
+        <v>32078800</v>
       </c>
     </row>
     <row r="84">
@@ -2118,19 +2118,19 @@
         <v>46071</v>
       </c>
       <c r="B84" t="n">
-        <v>263.6000061035156</v>
+        <v>397.2233488345012</v>
       </c>
       <c r="C84" t="n">
-        <v>266.8200073242188</v>
+        <v>401.6432531481791</v>
       </c>
       <c r="D84" t="n">
-        <v>262.4500122070312</v>
+        <v>395.4174731587443</v>
       </c>
       <c r="E84" t="n">
-        <v>264.3500061035156</v>
+        <v>398.6900024414062</v>
       </c>
       <c r="F84" t="n">
-        <v>34203300</v>
+        <v>23223400</v>
       </c>
     </row>
     <row r="85">
@@ -2138,19 +2138,19 @@
         <v>46072</v>
       </c>
       <c r="B85" t="n">
-        <v>262.6000061035156</v>
+        <v>400.6900024414062</v>
       </c>
       <c r="C85" t="n">
-        <v>264.4800109863281</v>
+        <v>404.4299926757812</v>
       </c>
       <c r="D85" t="n">
-        <v>260.0499877929688</v>
+        <v>396.6700134277344</v>
       </c>
       <c r="E85" t="n">
-        <v>260.5799865722656</v>
+        <v>398.4599914550781</v>
       </c>
       <c r="F85" t="n">
-        <v>30845300</v>
+        <v>28234000</v>
       </c>
     </row>
     <row r="86">
@@ -2158,19 +2158,19 @@
         <v>46073</v>
       </c>
       <c r="B86" t="n">
-        <v>258.9700012207031</v>
+        <v>396.1099853515625</v>
       </c>
       <c r="C86" t="n">
-        <v>264.75</v>
+        <v>400.1199951171875</v>
       </c>
       <c r="D86" t="n">
-        <v>258.1600036621094</v>
+        <v>395.1600036621094</v>
       </c>
       <c r="E86" t="n">
-        <v>264.5799865722656</v>
+        <v>397.2300109863281</v>
       </c>
       <c r="F86" t="n">
-        <v>42070500</v>
+        <v>34015200</v>
       </c>
     </row>
     <row r="87">
@@ -2178,19 +2178,19 @@
         <v>46076</v>
       </c>
       <c r="B87" t="n">
-        <v>263.489990234375</v>
+        <v>395</v>
       </c>
       <c r="C87" t="n">
-        <v>269.4299926757812</v>
+        <v>395.3599853515625</v>
       </c>
       <c r="D87" t="n">
-        <v>263.3800048828125</v>
+        <v>383.1000061035156</v>
       </c>
       <c r="E87" t="n">
-        <v>266.1799926757812</v>
+        <v>384.4700012207031</v>
       </c>
       <c r="F87" t="n">
-        <v>37308200</v>
+        <v>43238300</v>
       </c>
     </row>
     <row r="88">
@@ -2198,19 +2198,19 @@
         <v>46077</v>
       </c>
       <c r="B88" t="n">
-        <v>267.8599853515625</v>
+        <v>384.1400146484375</v>
       </c>
       <c r="C88" t="n">
-        <v>274.8900146484375</v>
+        <v>389.3599853515625</v>
       </c>
       <c r="D88" t="n">
-        <v>267.7099914550781</v>
+        <v>381.7099914550781</v>
       </c>
       <c r="E88" t="n">
-        <v>272.1400146484375</v>
+        <v>389</v>
       </c>
       <c r="F88" t="n">
-        <v>47014600</v>
+        <v>33884700</v>
       </c>
     </row>
     <row r="89">
@@ -2218,19 +2218,19 @@
         <v>46078</v>
       </c>
       <c r="B89" t="n">
-        <v>271.7799987792969</v>
+        <v>390.5299987792969</v>
       </c>
       <c r="C89" t="n">
-        <v>274.9400024414062</v>
+        <v>401.4700012207031</v>
       </c>
       <c r="D89" t="n">
-        <v>271.0499877929688</v>
+        <v>390.1600036621094</v>
       </c>
       <c r="E89" t="n">
-        <v>274.2300109863281</v>
+        <v>400.6000061035156</v>
       </c>
       <c r="F89" t="n">
-        <v>33714300</v>
+        <v>43625500</v>
       </c>
     </row>
     <row r="90">
@@ -2238,19 +2238,19 @@
         <v>46079</v>
       </c>
       <c r="B90" t="n">
-        <v>274.9500122070312</v>
+        <v>404.7099914550781</v>
       </c>
       <c r="C90" t="n">
-        <v>276.1099853515625</v>
+        <v>407.489990234375</v>
       </c>
       <c r="D90" t="n">
-        <v>270.7999877929688</v>
+        <v>398.739990234375</v>
       </c>
       <c r="E90" t="n">
-        <v>272.9500122070312</v>
+        <v>401.7200012207031</v>
       </c>
       <c r="F90" t="n">
-        <v>32345100</v>
+        <v>34405900</v>
       </c>
     </row>
     <row r="91">
@@ -2258,19 +2258,19 @@
         <v>46080</v>
       </c>
       <c r="B91" t="n">
-        <v>272.8099975585938</v>
+        <v>390.8800048828125</v>
       </c>
       <c r="C91" t="n">
-        <v>272.8099975585938</v>
+        <v>396.8200073242188</v>
       </c>
       <c r="D91" t="n">
-        <v>262.8900146484375</v>
+        <v>389.8800048828125</v>
       </c>
       <c r="E91" t="n">
-        <v>264.1799926757812</v>
+        <v>392.739990234375</v>
       </c>
       <c r="F91" t="n">
-        <v>72366500</v>
+        <v>51367200</v>
       </c>
     </row>
     <row r="92">
@@ -2278,19 +2278,19 @@
         <v>46083</v>
       </c>
       <c r="B92" t="n">
-        <v>262.4100036621094</v>
+        <v>392.8599853515625</v>
       </c>
       <c r="C92" t="n">
-        <v>266.5299987792969</v>
+        <v>401.1900024414062</v>
       </c>
       <c r="D92" t="n">
-        <v>260.2000122070312</v>
+        <v>390.6300048828125</v>
       </c>
       <c r="E92" t="n">
-        <v>264.7200012207031</v>
+        <v>398.5499877929688</v>
       </c>
       <c r="F92" t="n">
-        <v>41827900</v>
+        <v>35474900</v>
       </c>
     </row>
     <row r="93">
@@ -2298,19 +2298,19 @@
         <v>46084</v>
       </c>
       <c r="B93" t="n">
-        <v>263.4800109863281</v>
+        <v>393.1400146484375</v>
       </c>
       <c r="C93" t="n">
-        <v>265.5599975585938</v>
+        <v>406.7000122070312</v>
       </c>
       <c r="D93" t="n">
-        <v>260.1300048828125</v>
+        <v>392.6700134277344</v>
       </c>
       <c r="E93" t="n">
-        <v>263.75</v>
+        <v>403.9299926757812</v>
       </c>
       <c r="F93" t="n">
-        <v>38568900</v>
+        <v>38199200</v>
       </c>
     </row>
     <row r="94">
@@ -2318,19 +2318,19 @@
         <v>46085</v>
       </c>
       <c r="B94" t="n">
-        <v>264.6499938964844</v>
+        <v>401.2699890136719</v>
       </c>
       <c r="C94" t="n">
-        <v>266.1499938964844</v>
+        <v>411.0299987792969</v>
       </c>
       <c r="D94" t="n">
-        <v>261.4200134277344</v>
+        <v>400.3099975585938</v>
       </c>
       <c r="E94" t="n">
-        <v>262.5199890136719</v>
+        <v>405.2000122070312</v>
       </c>
       <c r="F94" t="n">
-        <v>39803100</v>
+        <v>35808000</v>
       </c>
     </row>
     <row r="95">
@@ -2338,19 +2338,19 @@
         <v>46086</v>
       </c>
       <c r="B95" t="n">
-        <v>260.7900085449219</v>
+        <v>404.4200134277344</v>
       </c>
       <c r="C95" t="n">
-        <v>261.5599975585938</v>
+        <v>411.6099853515625</v>
       </c>
       <c r="D95" t="n">
-        <v>257.25</v>
+        <v>404.3999938964844</v>
       </c>
       <c r="E95" t="n">
-        <v>260.2900085449219</v>
+        <v>410.6799926757812</v>
       </c>
       <c r="F95" t="n">
-        <v>49658600</v>
+        <v>39001300</v>
       </c>
     </row>
     <row r="96">
@@ -2358,19 +2358,19 @@
         <v>46087</v>
       </c>
       <c r="B96" t="n">
-        <v>258.6300048828125</v>
+        <v>409.2000122070312</v>
       </c>
       <c r="C96" t="n">
-        <v>258.7699890136719</v>
+        <v>413.0499877929688</v>
       </c>
       <c r="D96" t="n">
-        <v>254.3699951171875</v>
+        <v>408.510009765625</v>
       </c>
       <c r="E96" t="n">
-        <v>257.4599914550781</v>
+        <v>408.9599914550781</v>
       </c>
       <c r="F96" t="n">
-        <v>41120000</v>
+        <v>31123900</v>
       </c>
     </row>
     <row r="97">
@@ -2378,19 +2378,19 @@
         <v>46090</v>
       </c>
       <c r="B97" t="n">
-        <v>255.6900024414062</v>
+        <v>404.9200134277344</v>
       </c>
       <c r="C97" t="n">
-        <v>261.1499938964844</v>
+        <v>410.2099914550781</v>
       </c>
       <c r="D97" t="n">
-        <v>253.6799926757812</v>
+        <v>403.5</v>
       </c>
       <c r="E97" t="n">
-        <v>259.8800048828125</v>
+        <v>409.4100036621094</v>
       </c>
       <c r="F97" t="n">
-        <v>38218500</v>
+        <v>30131900</v>
       </c>
     </row>
     <row r="98">
@@ -2398,19 +2398,19 @@
         <v>46091</v>
       </c>
       <c r="B98" t="n">
-        <v>257.6499938964844</v>
+        <v>410.0299987792969</v>
       </c>
       <c r="C98" t="n">
-        <v>262.4800109863281</v>
+        <v>410.2000122070312</v>
       </c>
       <c r="D98" t="n">
-        <v>256.9500122070312</v>
+        <v>402.9299926757812</v>
       </c>
       <c r="E98" t="n">
-        <v>260.8299865722656</v>
+        <v>405.760009765625</v>
       </c>
       <c r="F98" t="n">
-        <v>30590800</v>
+        <v>31706400</v>
       </c>
     </row>
     <row r="99">
@@ -2418,19 +2418,19 @@
         <v>46092</v>
       </c>
       <c r="B99" t="n">
-        <v>261.0899963378906</v>
+        <v>405.5700073242188</v>
       </c>
       <c r="C99" t="n">
-        <v>262.1300048828125</v>
+        <v>409.010009765625</v>
       </c>
       <c r="D99" t="n">
-        <v>259.5499877929688</v>
+        <v>401.5899963378906</v>
       </c>
       <c r="E99" t="n">
-        <v>260.8099975585938</v>
+        <v>404.8800048828125</v>
       </c>
       <c r="F99" t="n">
-        <v>26218900</v>
+        <v>25512100</v>
       </c>
     </row>
     <row r="100">
@@ -2438,19 +2438,19 @@
         <v>46093</v>
       </c>
       <c r="B100" t="n">
-        <v>258.6600036621094</v>
+        <v>404.6300048828125</v>
       </c>
       <c r="C100" t="n">
-        <v>258.9500122070312</v>
+        <v>406.1199951171875</v>
       </c>
       <c r="D100" t="n">
-        <v>254.1799926757812</v>
+        <v>401.7099914550781</v>
       </c>
       <c r="E100" t="n">
-        <v>255.7599945068359</v>
+        <v>401.8599853515625</v>
       </c>
       <c r="F100" t="n">
-        <v>40794000</v>
+        <v>27263900</v>
       </c>
     </row>
     <row r="101">
@@ -2458,19 +2458,19 @@
         <v>46094</v>
       </c>
       <c r="B101" t="n">
-        <v>255.4799957275391</v>
+        <v>401</v>
       </c>
       <c r="C101" t="n">
-        <v>256.3299865722656</v>
+        <v>404.7999877929688</v>
       </c>
       <c r="D101" t="n">
-        <v>249.5200042724609</v>
+        <v>394.25</v>
       </c>
       <c r="E101" t="n">
-        <v>250.1199951171875</v>
+        <v>395.5499877929688</v>
       </c>
       <c r="F101" t="n">
-        <v>36930000</v>
+        <v>26848000</v>
       </c>
     </row>
     <row r="102">
@@ -2478,19 +2478,19 @@
         <v>46097</v>
       </c>
       <c r="B102" t="n">
-        <v>252.1100006103516</v>
+        <v>398.0700073242188</v>
       </c>
       <c r="C102" t="n">
-        <v>253.8899993896484</v>
+        <v>400.6300048828125</v>
       </c>
       <c r="D102" t="n">
-        <v>249.8800048828125</v>
+        <v>394.7900085449219</v>
       </c>
       <c r="E102" t="n">
-        <v>252.8200073242188</v>
+        <v>399.9500122070312</v>
       </c>
       <c r="F102" t="n">
-        <v>32074200</v>
+        <v>27733700</v>
       </c>
     </row>
     <row r="103">
@@ -2498,19 +2498,19 @@
         <v>46098</v>
       </c>
       <c r="B103" t="n">
-        <v>252.9600067138672</v>
+        <v>400.2699890136719</v>
       </c>
       <c r="C103" t="n">
-        <v>255.1300048828125</v>
+        <v>404.3999938964844</v>
       </c>
       <c r="D103" t="n">
-        <v>252.1799926757812</v>
+        <v>397.75</v>
       </c>
       <c r="E103" t="n">
-        <v>254.2299957275391</v>
+        <v>399.4100036621094</v>
       </c>
       <c r="F103" t="n">
-        <v>32361600</v>
+        <v>26228300</v>
       </c>
     </row>
     <row r="104">
@@ -2518,19 +2518,19 @@
         <v>46099</v>
       </c>
       <c r="B104" t="n">
-        <v>252.6300048828125</v>
+        <v>397.1300048828125</v>
       </c>
       <c r="C104" t="n">
-        <v>254.9400024414062</v>
+        <v>398</v>
       </c>
       <c r="D104" t="n">
-        <v>249</v>
+        <v>391</v>
       </c>
       <c r="E104" t="n">
-        <v>249.9400024414062</v>
+        <v>391.7900085449219</v>
       </c>
       <c r="F104" t="n">
-        <v>35757900</v>
+        <v>25908500</v>
       </c>
     </row>
     <row r="105">
@@ -2538,19 +2538,19 @@
         <v>46100</v>
       </c>
       <c r="B105" t="n">
-        <v>249.3999938964844</v>
+        <v>390.1000061035156</v>
       </c>
       <c r="C105" t="n">
-        <v>251.8300018310547</v>
+        <v>392.489990234375</v>
       </c>
       <c r="D105" t="n">
-        <v>247.3000030517578</v>
+        <v>387.0599975585938</v>
       </c>
       <c r="E105" t="n">
-        <v>248.9600067138672</v>
+        <v>389.0199890136719</v>
       </c>
       <c r="F105" t="n">
-        <v>34864100</v>
+        <v>25138800</v>
       </c>
     </row>
     <row r="106">
@@ -2558,19 +2558,19 @@
         <v>46101</v>
       </c>
       <c r="B106" t="n">
-        <v>247.9799957275391</v>
+        <v>386.7900085449219</v>
       </c>
       <c r="C106" t="n">
-        <v>249.1999969482422</v>
+        <v>387</v>
       </c>
       <c r="D106" t="n">
-        <v>246</v>
+        <v>380.1199951171875</v>
       </c>
       <c r="E106" t="n">
-        <v>247.9900054931641</v>
+        <v>381.8699951171875</v>
       </c>
       <c r="F106" t="n">
-        <v>88331100</v>
+        <v>50853200</v>
       </c>
     </row>
     <row r="107">
@@ -2578,19 +2578,19 @@
         <v>46104</v>
       </c>
       <c r="B107" t="n">
-        <v>253.9700012207031</v>
+        <v>383.8999938964844</v>
       </c>
       <c r="C107" t="n">
-        <v>254.6000061035156</v>
+        <v>387.2099914550781</v>
       </c>
       <c r="D107" t="n">
-        <v>250.2799987792969</v>
+        <v>381.6799926757812</v>
       </c>
       <c r="E107" t="n">
-        <v>251.4900054931641</v>
+        <v>383</v>
       </c>
       <c r="F107" t="n">
-        <v>40546100</v>
+        <v>29680100</v>
       </c>
     </row>
     <row r="108">
@@ -2598,19 +2598,19 @@
         <v>46105</v>
       </c>
       <c r="B108" t="n">
-        <v>250.3500061035156</v>
+        <v>382.3599853515625</v>
       </c>
       <c r="C108" t="n">
-        <v>254.8300018310547</v>
+        <v>382.4700012207031</v>
       </c>
       <c r="D108" t="n">
-        <v>249.5500030517578</v>
+        <v>371.8500061035156</v>
       </c>
       <c r="E108" t="n">
-        <v>251.6399993896484</v>
+        <v>372.739990234375</v>
       </c>
       <c r="F108" t="n">
-        <v>45152300</v>
+        <v>42733600</v>
       </c>
     </row>
     <row r="109">
@@ -2618,19 +2618,19 @@
         <v>46106</v>
       </c>
       <c r="B109" t="n">
-        <v>254.1000061035156</v>
+        <v>376.9200134277344</v>
       </c>
       <c r="C109" t="n">
-        <v>255</v>
+        <v>377.0599975585938</v>
       </c>
       <c r="D109" t="n">
-        <v>251.6000061035156</v>
+        <v>369.6300048828125</v>
       </c>
       <c r="E109" t="n">
-        <v>252.6199951171875</v>
+        <v>371.0400085449219</v>
       </c>
       <c r="F109" t="n">
-        <v>28476700</v>
+        <v>31181200</v>
       </c>
     </row>
     <row r="110">
@@ -2638,19 +2638,19 @@
         <v>46107</v>
       </c>
       <c r="B110" t="n">
-        <v>252.1199951171875</v>
+        <v>370.8200073242188</v>
       </c>
       <c r="C110" t="n">
-        <v>257</v>
+        <v>374.7200012207031</v>
       </c>
       <c r="D110" t="n">
-        <v>250.7700042724609</v>
+        <v>365.1900024414062</v>
       </c>
       <c r="E110" t="n">
-        <v>252.8899993896484</v>
+        <v>365.9700012207031</v>
       </c>
       <c r="F110" t="n">
-        <v>41796700</v>
+        <v>36836600</v>
       </c>
     </row>
     <row r="111">
@@ -2658,19 +2658,19 @@
         <v>46108</v>
       </c>
       <c r="B111" t="n">
-        <v>253.8999938964844</v>
+        <v>361.8999938964844</v>
       </c>
       <c r="C111" t="n">
-        <v>255.4900054931641</v>
+        <v>362.4500122070312</v>
       </c>
       <c r="D111" t="n">
-        <v>248.0700073242188</v>
+        <v>356.510009765625</v>
       </c>
       <c r="E111" t="n">
-        <v>248.8000030517578</v>
+        <v>356.7699890136719</v>
       </c>
       <c r="F111" t="n">
-        <v>47900000</v>
+        <v>37883400</v>
       </c>
     </row>
     <row r="112">
@@ -2678,19 +2678,19 @@
         <v>46111</v>
       </c>
       <c r="B112" t="n">
-        <v>250.0700073242188</v>
+        <v>361.8999938964844</v>
       </c>
       <c r="C112" t="n">
-        <v>250.8699951171875</v>
+        <v>365.3599853515625</v>
       </c>
       <c r="D112" t="n">
-        <v>245.5099945068359</v>
+        <v>356.2799987792969</v>
       </c>
       <c r="E112" t="n">
-        <v>246.6300048828125</v>
+        <v>358.9599914550781</v>
       </c>
       <c r="F112" t="n">
-        <v>39446200</v>
+        <v>44797000</v>
       </c>
     </row>
     <row r="113">
@@ -2698,19 +2698,19 @@
         <v>46112</v>
       </c>
       <c r="B113" t="n">
-        <v>247.9100036621094</v>
+        <v>364.5499877929688</v>
       </c>
       <c r="C113" t="n">
-        <v>255.4799957275391</v>
+        <v>372.8999938964844</v>
       </c>
       <c r="D113" t="n">
-        <v>247.1000061035156</v>
+        <v>363.0700073242188</v>
       </c>
       <c r="E113" t="n">
-        <v>253.7899932861328</v>
+        <v>370.1700134277344</v>
       </c>
       <c r="F113" t="n">
-        <v>49598100</v>
+        <v>45244400</v>
       </c>
     </row>
     <row r="114">
@@ -2718,19 +2718,19 @@
         <v>46113</v>
       </c>
       <c r="B114" t="n">
-        <v>254.0800018310547</v>
+        <v>373.489990234375</v>
       </c>
       <c r="C114" t="n">
-        <v>256.1799926757812</v>
+        <v>373.989990234375</v>
       </c>
       <c r="D114" t="n">
-        <v>253.3300018310547</v>
+        <v>368.2000122070312</v>
       </c>
       <c r="E114" t="n">
-        <v>255.6300048828125</v>
+        <v>369.3699951171875</v>
       </c>
       <c r="F114" t="n">
-        <v>40059400</v>
+        <v>29417200</v>
       </c>
     </row>
     <row r="115">
@@ -2738,19 +2738,19 @@
         <v>46114</v>
       </c>
       <c r="B115" t="n">
-        <v>254.1999969482422</v>
+        <v>367.2099914550781</v>
       </c>
       <c r="C115" t="n">
-        <v>256.1300048828125</v>
+        <v>373.6400146484375</v>
       </c>
       <c r="D115" t="n">
-        <v>250.6499938964844</v>
+        <v>364.1499938964844</v>
       </c>
       <c r="E115" t="n">
-        <v>255.9199981689453</v>
+        <v>373.4599914550781</v>
       </c>
       <c r="F115" t="n">
-        <v>31289400</v>
+        <v>24099100</v>
       </c>
     </row>
     <row r="116">
@@ -2758,19 +2758,19 @@
         <v>46118</v>
       </c>
       <c r="B116" t="n">
-        <v>256.510009765625</v>
+        <v>373.489990234375</v>
       </c>
       <c r="C116" t="n">
-        <v>262.1600036621094</v>
+        <v>373.7300109863281</v>
       </c>
       <c r="D116" t="n">
-        <v>256.4599914550781</v>
+        <v>369.5</v>
       </c>
       <c r="E116" t="n">
-        <v>258.8599853515625</v>
+        <v>372.8800048828125</v>
       </c>
       <c r="F116" t="n">
-        <v>29329900</v>
+        <v>16146600</v>
       </c>
     </row>
     <row r="117">
@@ -2778,19 +2778,19 @@
         <v>46119</v>
       </c>
       <c r="B117" t="n">
-        <v>256.1600036621094</v>
+        <v>370.3399963378906</v>
       </c>
       <c r="C117" t="n">
-        <v>256.2000122070312</v>
+        <v>372.4500122070312</v>
       </c>
       <c r="D117" t="n">
-        <v>245.6999969482422</v>
+        <v>366.5599975585938</v>
       </c>
       <c r="E117" t="n">
-        <v>253.5</v>
+        <v>372.2900085449219</v>
       </c>
       <c r="F117" t="n">
-        <v>62148000</v>
+        <v>21443300</v>
       </c>
     </row>
     <row r="118">
@@ -2798,19 +2798,19 @@
         <v>46120</v>
       </c>
       <c r="B118" t="n">
-        <v>258.4500122070312</v>
+        <v>384.9800109863281</v>
       </c>
       <c r="C118" t="n">
-        <v>259.75</v>
+        <v>385</v>
       </c>
       <c r="D118" t="n">
-        <v>256.5299987792969</v>
+        <v>371.4100036621094</v>
       </c>
       <c r="E118" t="n">
-        <v>258.8999938964844</v>
+        <v>374.3299865722656</v>
       </c>
       <c r="F118" t="n">
-        <v>41032800</v>
+        <v>33064800</v>
       </c>
     </row>
     <row r="119">
@@ -2818,19 +2818,19 @@
         <v>46121</v>
       </c>
       <c r="B119" t="n">
-        <v>259</v>
+        <v>372.5</v>
       </c>
       <c r="C119" t="n">
-        <v>261.1199951171875</v>
+        <v>373.5</v>
       </c>
       <c r="D119" t="n">
-        <v>256.0700073242188</v>
+        <v>367.0499877929688</v>
       </c>
       <c r="E119" t="n">
-        <v>260.489990234375</v>
+        <v>373.0700073242188</v>
       </c>
       <c r="F119" t="n">
-        <v>28121600</v>
+        <v>30435300</v>
       </c>
     </row>
     <row r="120">
@@ -2838,19 +2838,19 @@
         <v>46122</v>
       </c>
       <c r="B120" t="n">
-        <v>259.9800109863281</v>
+        <v>372.9800109863281</v>
       </c>
       <c r="C120" t="n">
-        <v>262.1900024414062</v>
+        <v>375.6400146484375</v>
       </c>
       <c r="D120" t="n">
-        <v>259.0199890136719</v>
+        <v>370.0299987792969</v>
       </c>
       <c r="E120" t="n">
-        <v>260.4800109863281</v>
+        <v>370.8699951171875</v>
       </c>
       <c r="F120" t="n">
-        <v>31291500</v>
+        <v>28111100</v>
       </c>
     </row>
     <row r="121">
@@ -2858,19 +2858,19 @@
         <v>46125</v>
       </c>
       <c r="B121" t="n">
-        <v>259.7300109863281</v>
+        <v>373.6099853515625</v>
       </c>
       <c r="C121" t="n">
-        <v>260.1799926757812</v>
+        <v>384.5400085449219</v>
       </c>
       <c r="D121" t="n">
-        <v>256.6600036621094</v>
+        <v>371.0199890136719</v>
       </c>
       <c r="E121" t="n">
-        <v>259.2000122070312</v>
+        <v>384.3699951171875</v>
       </c>
       <c r="F121" t="n">
-        <v>36234700</v>
+        <v>35745800</v>
       </c>
     </row>
     <row r="122">
@@ -2878,19 +2878,19 @@
         <v>46126</v>
       </c>
       <c r="B122" t="n">
-        <v>259.25</v>
+        <v>387.9200134277344</v>
       </c>
       <c r="C122" t="n">
-        <v>261.9299926757812</v>
+        <v>394.6900024414062</v>
       </c>
       <c r="D122" t="n">
-        <v>257.1900024414062</v>
+        <v>386.5199890136719</v>
       </c>
       <c r="E122" t="n">
-        <v>258.8299865722656</v>
+        <v>393.1099853515625</v>
       </c>
       <c r="F122" t="n">
-        <v>48370700</v>
+        <v>37504500</v>
       </c>
     </row>
     <row r="123">
@@ -2898,19 +2898,19 @@
         <v>46127</v>
       </c>
       <c r="B123" t="n">
-        <v>258.1600036621094</v>
+        <v>398</v>
       </c>
       <c r="C123" t="n">
-        <v>266.5599975585938</v>
+        <v>414.3699951171875</v>
       </c>
       <c r="D123" t="n">
-        <v>257.8099975585938</v>
+        <v>396.7300109863281</v>
       </c>
       <c r="E123" t="n">
-        <v>266.4299926757812</v>
+        <v>411.2200012207031</v>
       </c>
       <c r="F123" t="n">
-        <v>49735000</v>
+        <v>45063400</v>
       </c>
     </row>
     <row r="124">
@@ -2918,19 +2918,39 @@
         <v>46128</v>
       </c>
       <c r="B124" t="n">
-        <v>266.7999877929688</v>
+        <v>419.8599853515625</v>
       </c>
       <c r="C124" t="n">
-        <v>267.1600036621094</v>
+        <v>420.8200073242188</v>
       </c>
       <c r="D124" t="n">
-        <v>261.2699890136719</v>
+        <v>412.1400146484375</v>
       </c>
       <c r="E124" t="n">
-        <v>263.9599914550781</v>
+        <v>420.260009765625</v>
       </c>
       <c r="F124" t="n">
-        <v>24583355</v>
+        <v>41642400</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B125" t="n">
+        <v>424.8200073242188</v>
+      </c>
+      <c r="C125" t="n">
+        <v>431.5799865722656</v>
+      </c>
+      <c r="D125" t="n">
+        <v>420.6900024414062</v>
+      </c>
+      <c r="E125" t="n">
+        <v>422.7900085449219</v>
+      </c>
+      <c r="F125" t="n">
+        <v>47812100</v>
       </c>
     </row>
   </sheetData>
@@ -2944,7 +2964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5416,7 +5436,7 @@
         <v>699.9400024414062</v>
       </c>
       <c r="F123" t="n">
-        <v>58138100</v>
+        <v>58240400</v>
       </c>
     </row>
     <row r="124">
@@ -5433,10 +5453,30 @@
         <v>698.530029296875</v>
       </c>
       <c r="E124" t="n">
-        <v>700.47998046875</v>
+        <v>701.6599731445312</v>
       </c>
       <c r="F124" t="n">
-        <v>31426463</v>
+        <v>49972400</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B125" t="n">
+        <v>706.1400146484375</v>
+      </c>
+      <c r="C125" t="n">
+        <v>712.3900146484375</v>
+      </c>
+      <c r="D125" t="n">
+        <v>705.760009765625</v>
+      </c>
+      <c r="E125" t="n">
+        <v>710.1400146484375</v>
+      </c>
+      <c r="F125" t="n">
+        <v>70538900</v>
       </c>
     </row>
   </sheetData>
@@ -5450,7 +5490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5490,19 +5530,19 @@
         <v>45950</v>
       </c>
       <c r="B2" t="n">
-        <v>512.4788764440519</v>
+        <v>255.4032084113237</v>
       </c>
       <c r="C2" t="n">
-        <v>516.5519656323323</v>
+        <v>263.8770629877272</v>
       </c>
       <c r="D2" t="n">
-        <v>511.3037703677804</v>
+        <v>255.143708503654</v>
       </c>
       <c r="E2" t="n">
-        <v>514.6498413085938</v>
+        <v>261.7411193847656</v>
       </c>
       <c r="F2" t="n">
-        <v>14665600</v>
+        <v>90483000</v>
       </c>
     </row>
     <row r="3">
@@ -5510,19 +5550,19 @@
         <v>45951</v>
       </c>
       <c r="B3" t="n">
-        <v>515.3569857054445</v>
+        <v>261.3817895915523</v>
       </c>
       <c r="C3" t="n">
-        <v>516.5420602391357</v>
+        <v>264.7853058703715</v>
       </c>
       <c r="D3" t="n">
-        <v>510.9154330870712</v>
+        <v>261.3318664386604</v>
       </c>
       <c r="E3" t="n">
-        <v>515.5162963867188</v>
+        <v>262.2700805664062</v>
       </c>
       <c r="F3" t="n">
-        <v>15586200</v>
+        <v>46695900</v>
       </c>
     </row>
     <row r="4">
@@ -5530,19 +5570,19 @@
         <v>45952</v>
       </c>
       <c r="B4" t="n">
-        <v>518.9918584655633</v>
+        <v>262.1503352574342</v>
       </c>
       <c r="C4" t="n">
-        <v>523.0549187669818</v>
+        <v>262.349966966352</v>
       </c>
       <c r="D4" t="n">
-        <v>515.566101626736</v>
+        <v>254.9440691826199</v>
       </c>
       <c r="E4" t="n">
-        <v>518.3843383789062</v>
+        <v>257.9583435058594</v>
       </c>
       <c r="F4" t="n">
-        <v>18962700</v>
+        <v>45015300</v>
       </c>
     </row>
     <row r="5">
@@ -5550,19 +5590,19 @@
         <v>45953</v>
       </c>
       <c r="B5" t="n">
-        <v>520.2964530626382</v>
+        <v>259.4454820834593</v>
       </c>
       <c r="C5" t="n">
-        <v>521.7802730707533</v>
+        <v>260.1241811137136</v>
       </c>
       <c r="D5" t="n">
-        <v>516.4623598997719</v>
+        <v>257.5191611036844</v>
       </c>
       <c r="E5" t="n">
-        <v>518.404296875</v>
+        <v>259.0861511230469</v>
       </c>
       <c r="F5" t="n">
-        <v>14023500</v>
+        <v>32754900</v>
       </c>
     </row>
     <row r="6">
@@ -5570,19 +5610,19 @@
         <v>45954</v>
       </c>
       <c r="B6" t="n">
-        <v>520.6250388201142</v>
+        <v>260.6931337605782</v>
       </c>
       <c r="C6" t="n">
-        <v>523.1744351060786</v>
+        <v>263.6275433572314</v>
       </c>
       <c r="D6" t="n">
-        <v>518.5536961256696</v>
+        <v>258.6869476899315</v>
       </c>
       <c r="E6" t="n">
-        <v>521.441650390625</v>
+        <v>262.3200378417969</v>
       </c>
       <c r="F6" t="n">
-        <v>15532400</v>
+        <v>38253700</v>
       </c>
     </row>
     <row r="7">
@@ -5590,19 +5630,19 @@
         <v>45957</v>
       </c>
       <c r="B7" t="n">
-        <v>529.577902779321</v>
+        <v>264.376098228409</v>
       </c>
       <c r="C7" t="n">
-        <v>532.3662956890146</v>
+        <v>268.60802232244</v>
       </c>
       <c r="D7" t="n">
-        <v>526.819354031342</v>
+        <v>264.1465248140549</v>
       </c>
       <c r="E7" t="n">
-        <v>529.3189697265625</v>
+        <v>268.2986145019531</v>
       </c>
       <c r="F7" t="n">
-        <v>18734700</v>
+        <v>44888200</v>
       </c>
     </row>
     <row r="8">
@@ -5610,19 +5650,19 @@
         <v>45958</v>
       </c>
       <c r="B8" t="n">
-        <v>547.722348424072</v>
+        <v>268.4782600095115</v>
       </c>
       <c r="C8" t="n">
-        <v>551.4269140414981</v>
+        <v>269.3765722048576</v>
       </c>
       <c r="D8" t="n">
-        <v>538.5305910090683</v>
+        <v>267.6398616921066</v>
       </c>
       <c r="E8" t="n">
-        <v>539.8251953125</v>
+        <v>268.4882507324219</v>
       </c>
       <c r="F8" t="n">
-        <v>29986700</v>
+        <v>41534800</v>
       </c>
     </row>
     <row r="9">
@@ -5630,19 +5670,19 @@
         <v>45959</v>
       </c>
       <c r="B9" t="n">
-        <v>542.6832878753321</v>
+        <v>268.7677057947778</v>
       </c>
       <c r="C9" t="n">
-        <v>544.0077970763692</v>
+        <v>270.8936584399069</v>
       </c>
       <c r="D9" t="n">
-        <v>534.5072653816836</v>
+        <v>266.6018207191691</v>
       </c>
       <c r="E9" t="n">
-        <v>539.3073120117188</v>
+        <v>269.1869201660156</v>
       </c>
       <c r="F9" t="n">
-        <v>36023000</v>
+        <v>51086700</v>
       </c>
     </row>
     <row r="10">
@@ -5650,19 +5690,19 @@
         <v>45960</v>
       </c>
       <c r="B10" t="n">
-        <v>528.2831883129468</v>
+        <v>271.4725408872279</v>
       </c>
       <c r="C10" t="n">
-        <v>532.7545848667123</v>
+        <v>273.6184749716116</v>
       </c>
       <c r="D10" t="n">
-        <v>519.9578228356851</v>
+        <v>267.969239224885</v>
       </c>
       <c r="E10" t="n">
-        <v>523.582763671875</v>
+        <v>270.8836669921875</v>
       </c>
       <c r="F10" t="n">
-        <v>41023100</v>
+        <v>69886500</v>
       </c>
     </row>
     <row r="11">
@@ -5670,19 +5710,19 @@
         <v>45961</v>
       </c>
       <c r="B11" t="n">
-        <v>526.6898137654194</v>
+        <v>276.4630533049319</v>
       </c>
       <c r="C11" t="n">
-        <v>527.1279940743384</v>
+        <v>276.7924425807819</v>
       </c>
       <c r="D11" t="n">
-        <v>512.9668501497666</v>
+        <v>268.647962249571</v>
       </c>
       <c r="E11" t="n">
-        <v>515.6656494140625</v>
+        <v>269.8556518554688</v>
       </c>
       <c r="F11" t="n">
-        <v>34006400</v>
+        <v>86167100</v>
       </c>
     </row>
     <row r="12">
@@ -5690,19 +5730,19 @@
         <v>45964</v>
       </c>
       <c r="B12" t="n">
-        <v>517.657371934483</v>
+        <v>269.9055662700252</v>
       </c>
       <c r="C12" t="n">
-        <v>522.7860691817526</v>
+        <v>270.3347409275427</v>
       </c>
       <c r="D12" t="n">
-        <v>512.4590180581705</v>
+        <v>265.7434858777505</v>
       </c>
       <c r="E12" t="n">
-        <v>514.888916015625</v>
+        <v>268.5381469726562</v>
       </c>
       <c r="F12" t="n">
-        <v>22374700</v>
+        <v>50194600</v>
       </c>
     </row>
     <row r="13">
@@ -5710,19 +5750,19 @@
         <v>45965</v>
       </c>
       <c r="B13" t="n">
-        <v>509.6407695643784</v>
+        <v>267.8195068636227</v>
       </c>
       <c r="C13" t="n">
-        <v>513.4150529816625</v>
+        <v>270.9734988318123</v>
       </c>
       <c r="D13" t="n">
-        <v>505.7369892339689</v>
+        <v>267.1108661194202</v>
       </c>
       <c r="E13" t="n">
-        <v>512.2001342773438</v>
+        <v>269.5262756347656</v>
       </c>
       <c r="F13" t="n">
-        <v>20958700</v>
+        <v>49274800</v>
       </c>
     </row>
     <row r="14">
@@ -5730,19 +5770,19 @@
         <v>45966</v>
       </c>
       <c r="B14" t="n">
-        <v>511.1743415428253</v>
+        <v>268.0989800730272</v>
       </c>
       <c r="C14" t="n">
-        <v>512.6980347767452</v>
+        <v>271.1831284425123</v>
       </c>
       <c r="D14" t="n">
-        <v>504.4821687767013</v>
+        <v>266.4221834255846</v>
       </c>
       <c r="E14" t="n">
-        <v>505.0597839355469</v>
+        <v>269.6260986328125</v>
       </c>
       <c r="F14" t="n">
-        <v>23024300</v>
+        <v>43683100</v>
       </c>
     </row>
     <row r="15">
@@ -5750,19 +5790,19 @@
         <v>45967</v>
       </c>
       <c r="B15" t="n">
-        <v>503.5659922381216</v>
+        <v>267.3803770260164</v>
       </c>
       <c r="C15" t="n">
-        <v>503.6058351018555</v>
+        <v>272.8798740142925</v>
       </c>
       <c r="D15" t="n">
-        <v>493.7567764386794</v>
+        <v>267.3803770260164</v>
       </c>
       <c r="E15" t="n">
-        <v>495.0414428710938</v>
+        <v>269.2567749023438</v>
       </c>
       <c r="F15" t="n">
-        <v>27406500</v>
+        <v>51204000</v>
       </c>
     </row>
     <row r="16">
@@ -5770,19 +5810,19 @@
         <v>45968</v>
       </c>
       <c r="B16" t="n">
-        <v>494.8920702735404</v>
+        <v>269.2867154149515</v>
       </c>
       <c r="C16" t="n">
-        <v>497.3119999979126</v>
+        <v>271.7719991063764</v>
       </c>
       <c r="D16" t="n">
-        <v>491.2073803526309</v>
+        <v>266.2624809601513</v>
       </c>
       <c r="E16" t="n">
-        <v>494.7626037597656</v>
+        <v>267.9592590332031</v>
       </c>
       <c r="F16" t="n">
-        <v>24019800</v>
+        <v>48227400</v>
       </c>
     </row>
     <row r="17">
@@ -5790,19 +5830,19 @@
         <v>45971</v>
       </c>
       <c r="B17" t="n">
-        <v>497.9692915322098</v>
+        <v>268.7085692371889</v>
       </c>
       <c r="C17" t="n">
-        <v>504.7510881917551</v>
+        <v>273.4741297822401</v>
       </c>
       <c r="D17" t="n">
-        <v>496.734405833499</v>
+        <v>267.2099714283653</v>
       </c>
       <c r="E17" t="n">
-        <v>503.9046020507812</v>
+        <v>269.1781311035156</v>
       </c>
       <c r="F17" t="n">
-        <v>26101500</v>
+        <v>41312400</v>
       </c>
     </row>
     <row r="18">
@@ -5810,19 +5850,19 @@
         <v>45972</v>
       </c>
       <c r="B18" t="n">
-        <v>502.7095490222416</v>
+        <v>269.5577590596557</v>
       </c>
       <c r="C18" t="n">
-        <v>507.4896898672195</v>
+        <v>275.6520624227355</v>
       </c>
       <c r="D18" t="n">
-        <v>500.2697130079767</v>
+        <v>269.5477586519058</v>
       </c>
       <c r="E18" t="n">
-        <v>506.573486328125</v>
+        <v>274.99267578125</v>
       </c>
       <c r="F18" t="n">
-        <v>17980000</v>
+        <v>46208300</v>
       </c>
     </row>
     <row r="19">
@@ -5830,19 +5870,19 @@
         <v>45973</v>
       </c>
       <c r="B19" t="n">
-        <v>507.2506574723947</v>
+        <v>274.7429239716485</v>
       </c>
       <c r="C19" t="n">
-        <v>509.5511194130969</v>
+        <v>275.4722525277038</v>
       </c>
       <c r="D19" t="n">
-        <v>497.0530724082431</v>
+        <v>271.4460210796085</v>
       </c>
       <c r="E19" t="n">
-        <v>509.0233154296875</v>
+        <v>273.21435546875</v>
       </c>
       <c r="F19" t="n">
-        <v>26574900</v>
+        <v>48398000</v>
       </c>
     </row>
     <row r="20">
@@ -5850,19 +5890,19 @@
         <v>45974</v>
       </c>
       <c r="B20" t="n">
-        <v>508.1967287528611</v>
+        <v>273.8537435218178</v>
       </c>
       <c r="C20" t="n">
-        <v>511.3735209246628</v>
+        <v>276.4413491841305</v>
       </c>
       <c r="D20" t="n">
-        <v>499.2140928412288</v>
+        <v>271.8356428219928</v>
       </c>
       <c r="E20" t="n">
-        <v>501.205810546875</v>
+        <v>272.6948547363281</v>
       </c>
       <c r="F20" t="n">
-        <v>25273100</v>
+        <v>49602800</v>
       </c>
     </row>
     <row r="21">
@@ -5870,19 +5910,19 @@
         <v>45975</v>
       </c>
       <c r="B21" t="n">
-        <v>496.1667955235038</v>
+        <v>270.7965900477885</v>
       </c>
       <c r="C21" t="n">
-        <v>509.4814242836766</v>
+        <v>275.702003472256</v>
       </c>
       <c r="D21" t="n">
-        <v>495.3800584752997</v>
+        <v>269.3479639093673</v>
       </c>
       <c r="E21" t="n">
-        <v>508.0672912597656</v>
+        <v>272.1553344726562</v>
       </c>
       <c r="F21" t="n">
-        <v>28505700</v>
+        <v>47431300</v>
       </c>
     </row>
     <row r="22">
@@ -5890,19 +5930,19 @@
         <v>45978</v>
       </c>
       <c r="B22" t="n">
-        <v>506.3444741681719</v>
+        <v>268.5687054184609</v>
       </c>
       <c r="C22" t="n">
-        <v>509.9992593431845</v>
+        <v>270.2371271729127</v>
       </c>
       <c r="D22" t="n">
-        <v>502.8191251226507</v>
+        <v>265.4815977121726</v>
       </c>
       <c r="E22" t="n">
-        <v>505.388427734375</v>
+        <v>267.2099609375</v>
       </c>
       <c r="F22" t="n">
-        <v>19092800</v>
+        <v>45018300</v>
       </c>
     </row>
     <row r="23">
@@ -5910,19 +5950,19 @@
         <v>45979</v>
       </c>
       <c r="B23" t="n">
-        <v>493.3186219236692</v>
+        <v>269.7376065335732</v>
       </c>
       <c r="C23" t="n">
-        <v>500.8971240097587</v>
+        <v>270.4569347049811</v>
       </c>
       <c r="D23" t="n">
-        <v>484.7641975590383</v>
+        <v>265.0719890725528</v>
       </c>
       <c r="E23" t="n">
-        <v>491.7451782226562</v>
+        <v>267.1900024414062</v>
       </c>
       <c r="F23" t="n">
-        <v>33815100</v>
+        <v>45677300</v>
       </c>
     </row>
     <row r="24">
@@ -5930,19 +5970,19 @@
         <v>45980</v>
       </c>
       <c r="B24" t="n">
-        <v>488.070453670226</v>
+        <v>265.2817633125939</v>
       </c>
       <c r="C24" t="n">
-        <v>493.1393718315724</v>
+        <v>271.9555110777923</v>
       </c>
       <c r="D24" t="n">
-        <v>480.8305400064438</v>
+        <v>265.2517925781922</v>
       </c>
       <c r="E24" t="n">
-        <v>485.102783203125</v>
+        <v>268.3089294433594</v>
       </c>
       <c r="F24" t="n">
-        <v>23245300</v>
+        <v>40424500</v>
       </c>
     </row>
     <row r="25">
@@ -5950,19 +5990,19 @@
         <v>45981</v>
       </c>
       <c r="B25" t="n">
-        <v>491.5879641710541</v>
+        <v>270.5768036466949</v>
       </c>
       <c r="C25" t="n">
-        <v>492.4460215630244</v>
+        <v>275.1725094767523</v>
       </c>
       <c r="D25" t="n">
-        <v>474.4171642897319</v>
+        <v>265.6714205454633</v>
       </c>
       <c r="E25" t="n">
-        <v>477.3404846191406</v>
+        <v>266.0010986328125</v>
       </c>
       <c r="F25" t="n">
-        <v>26802500</v>
+        <v>45823600</v>
       </c>
     </row>
     <row r="26">
@@ -5970,19 +6010,19 @@
         <v>45982</v>
       </c>
       <c r="B26" t="n">
-        <v>477.4103368698009</v>
+        <v>265.7013768088059</v>
       </c>
       <c r="C26" t="n">
-        <v>477.8293938228302</v>
+        <v>273.0744516711978</v>
       </c>
       <c r="D26" t="n">
-        <v>467.2036221547232</v>
+        <v>265.4216397990326</v>
       </c>
       <c r="E26" t="n">
-        <v>471.0448608398438</v>
+        <v>271.2361755371094</v>
       </c>
       <c r="F26" t="n">
-        <v>31769200</v>
+        <v>59030800</v>
       </c>
     </row>
     <row r="27">
@@ -5990,19 +6030,19 @@
         <v>45985</v>
       </c>
       <c r="B27" t="n">
-        <v>473.9183160323131</v>
+        <v>270.6467521230613</v>
       </c>
       <c r="C27" t="n">
-        <v>475.8139832068258</v>
+        <v>276.7410558404627</v>
       </c>
       <c r="D27" t="n">
-        <v>466.9542001322548</v>
+        <v>270.6467521230613</v>
       </c>
       <c r="E27" t="n">
-        <v>472.9205932617188</v>
+        <v>275.6620788574219</v>
       </c>
       <c r="F27" t="n">
-        <v>34421000</v>
+        <v>65585800</v>
       </c>
     </row>
     <row r="28">
@@ -6010,19 +6050,19 @@
         <v>45986</v>
       </c>
       <c r="B28" t="n">
-        <v>472.9904142849383</v>
+        <v>275.012667049666</v>
       </c>
       <c r="C28" t="n">
-        <v>478.0588322743821</v>
+        <v>280.1179060838009</v>
       </c>
       <c r="D28" t="n">
-        <v>463.8313270788984</v>
+        <v>274.9926967216935</v>
       </c>
       <c r="E28" t="n">
-        <v>475.9037475585938</v>
+        <v>276.7110900878906</v>
       </c>
       <c r="F28" t="n">
-        <v>28019800</v>
+        <v>46914200</v>
       </c>
     </row>
     <row r="29">
@@ -6030,19 +6070,19 @@
         <v>45987</v>
       </c>
       <c r="B29" t="n">
-        <v>485.2025316262965</v>
+        <v>276.7010825487222</v>
       </c>
       <c r="C29" t="n">
-        <v>487.1979770584782</v>
+        <v>279.2686873678638</v>
       </c>
       <c r="D29" t="n">
-        <v>480.1041831621511</v>
+        <v>276.3714044558947</v>
       </c>
       <c r="E29" t="n">
-        <v>484.3943786621094</v>
+        <v>277.29052734375</v>
       </c>
       <c r="F29" t="n">
-        <v>25709100</v>
+        <v>33431400</v>
       </c>
     </row>
     <row r="30">
@@ -6050,19 +6090,19 @@
         <v>45989</v>
       </c>
       <c r="B30" t="n">
-        <v>486.489626354464</v>
+        <v>277.0008150112318</v>
       </c>
       <c r="C30" t="n">
-        <v>491.5081706450152</v>
+        <v>278.7391786268174</v>
       </c>
       <c r="D30" t="n">
-        <v>485.541777548382</v>
+        <v>275.7319827496524</v>
       </c>
       <c r="E30" t="n">
-        <v>490.8895874023438</v>
+        <v>278.5893249511719</v>
       </c>
       <c r="F30" t="n">
-        <v>14386700</v>
+        <v>20135600</v>
       </c>
     </row>
     <row r="31">
@@ -6070,19 +6110,19 @@
         <v>45992</v>
       </c>
       <c r="B31" t="n">
-        <v>487.3277021324388</v>
+        <v>277.7501195744996</v>
       </c>
       <c r="C31" t="n">
-        <v>488.7444513856018</v>
+        <v>283.1550658399818</v>
       </c>
       <c r="D31" t="n">
-        <v>483.5463243869077</v>
+        <v>275.881872572025</v>
       </c>
       <c r="E31" t="n">
-        <v>485.6315612792969</v>
+        <v>282.8353576660156</v>
       </c>
       <c r="F31" t="n">
-        <v>23964000</v>
+        <v>46587700</v>
       </c>
     </row>
     <row r="32">
@@ -6090,19 +6130,19 @@
         <v>45993</v>
       </c>
       <c r="B32" t="n">
-        <v>485.6116258193264</v>
+        <v>282.7354345985028</v>
       </c>
       <c r="C32" t="n">
-        <v>492.3761849539621</v>
+        <v>287.1313151163589</v>
       </c>
       <c r="D32" t="n">
-        <v>485.2125428025972</v>
+        <v>282.3657853749787</v>
       </c>
       <c r="E32" t="n">
-        <v>488.8841552734375</v>
+        <v>285.9224548339844</v>
       </c>
       <c r="F32" t="n">
-        <v>19562700</v>
+        <v>53669500</v>
       </c>
     </row>
     <row r="33">
@@ -6110,19 +6150,19 @@
         <v>45994</v>
       </c>
       <c r="B33" t="n">
-        <v>475.235297143397</v>
+        <v>285.9324708384744</v>
       </c>
       <c r="C33" t="n">
-        <v>483.1372440988117</v>
+        <v>288.3501915351014</v>
       </c>
       <c r="D33" t="n">
-        <v>474.1178525596479</v>
+        <v>283.0351573834178</v>
       </c>
       <c r="E33" t="n">
-        <v>476.64208984375</v>
+        <v>283.8843688964844</v>
       </c>
       <c r="F33" t="n">
-        <v>34615100</v>
+        <v>43538700</v>
       </c>
     </row>
     <row r="34">
@@ -6130,19 +6170,19 @@
         <v>45995</v>
       </c>
       <c r="B34" t="n">
-        <v>478.6674679630734</v>
+        <v>283.8344068650217</v>
       </c>
       <c r="C34" t="n">
-        <v>480.2239129901724</v>
+        <v>284.4638227692578</v>
       </c>
       <c r="D34" t="n">
-        <v>475.4048951405118</v>
+        <v>278.3295482939282</v>
       </c>
       <c r="E34" t="n">
-        <v>479.7449951171875</v>
+        <v>280.4375915527344</v>
       </c>
       <c r="F34" t="n">
-        <v>22318200</v>
+        <v>43989100</v>
       </c>
     </row>
     <row r="35">
@@ -6150,19 +6190,19 @@
         <v>45996</v>
       </c>
       <c r="B35" t="n">
-        <v>481.4211657314621</v>
+        <v>280.2777430659675</v>
       </c>
       <c r="C35" t="n">
-        <v>482.299166614698</v>
+        <v>280.8771882481053</v>
       </c>
       <c r="D35" t="n">
-        <v>477.7894707894466</v>
+        <v>277.7900501334527</v>
       </c>
       <c r="E35" t="n">
-        <v>482.0597229003906</v>
+        <v>278.5193786621094</v>
       </c>
       <c r="F35" t="n">
-        <v>22608700</v>
+        <v>47265800</v>
       </c>
     </row>
     <row r="36">
@@ -6170,19 +6210,19 @@
         <v>45999</v>
       </c>
       <c r="B36" t="n">
-        <v>483.7858099301447</v>
+        <v>277.8699843761556</v>
       </c>
       <c r="C36" t="n">
-        <v>491.1789088824644</v>
+        <v>279.4085531850005</v>
       </c>
       <c r="D36" t="n">
-        <v>483.2769615726175</v>
+        <v>275.8918244790692</v>
       </c>
       <c r="E36" t="n">
-        <v>489.9018249511719</v>
+        <v>277.6302185058594</v>
       </c>
       <c r="F36" t="n">
-        <v>21965900</v>
+        <v>38211800</v>
       </c>
     </row>
     <row r="37">
@@ -6190,19 +6230,19 @@
         <v>46000</v>
       </c>
       <c r="B37" t="n">
-        <v>487.9862027558801</v>
+        <v>277.8999627322321</v>
       </c>
       <c r="C37" t="n">
-        <v>490.9993144973556</v>
+        <v>279.7682096639769</v>
       </c>
       <c r="D37" t="n">
-        <v>487.3875630167038</v>
+        <v>276.6611317163261</v>
       </c>
       <c r="E37" t="n">
-        <v>490.8995361328125</v>
+        <v>276.9208679199219</v>
       </c>
       <c r="F37" t="n">
-        <v>14696100</v>
+        <v>32193300</v>
       </c>
     </row>
     <row r="38">
@@ -6210,19 +6250,19 @@
         <v>46001</v>
       </c>
       <c r="B38" t="n">
-        <v>482.9277288439703</v>
+        <v>277.490342786908</v>
       </c>
       <c r="C38" t="n">
-        <v>483.1472290611572</v>
+        <v>279.4884730680018</v>
       </c>
       <c r="D38" t="n">
-        <v>473.9980982856002</v>
+        <v>276.1815698919154</v>
       </c>
       <c r="E38" t="n">
-        <v>477.4701843261719</v>
+        <v>278.5193786621094</v>
       </c>
       <c r="F38" t="n">
-        <v>35756200</v>
+        <v>33038300</v>
       </c>
     </row>
     <row r="39">
@@ -6230,19 +6270,19 @@
         <v>46002</v>
       </c>
       <c r="B39" t="n">
-        <v>475.5445986070271</v>
+        <v>278.8390875870869</v>
       </c>
       <c r="C39" t="n">
-        <v>484.9231863556336</v>
+        <v>279.3286197507982</v>
       </c>
       <c r="D39" t="n">
-        <v>474.7763326037194</v>
+        <v>273.5540244422053</v>
       </c>
       <c r="E39" t="n">
-        <v>482.3690185546875</v>
+        <v>277.7700805664062</v>
       </c>
       <c r="F39" t="n">
-        <v>24669200</v>
+        <v>33248000</v>
       </c>
     </row>
     <row r="40">
@@ -6250,19 +6290,19 @@
         <v>46003</v>
       </c>
       <c r="B40" t="n">
-        <v>478.7273480015789</v>
+        <v>277.64021728323</v>
       </c>
       <c r="C40" t="n">
-        <v>481.3513637649093</v>
+        <v>278.9589906850317</v>
       </c>
       <c r="D40" t="n">
-        <v>475.2552617920193</v>
+        <v>276.5612402656973</v>
       </c>
       <c r="E40" t="n">
-        <v>477.4402770996094</v>
+        <v>278.0198669433594</v>
       </c>
       <c r="F40" t="n">
-        <v>21248100</v>
+        <v>39532900</v>
       </c>
     </row>
     <row r="41">
@@ -6270,19 +6310,19 @@
         <v>46006</v>
       </c>
       <c r="B41" t="n">
-        <v>479.0066832317436</v>
+        <v>279.8880911943856</v>
       </c>
       <c r="C41" t="n">
-        <v>479.6252664455081</v>
+        <v>279.8880911943856</v>
       </c>
       <c r="D41" t="n">
-        <v>471.4439279747418</v>
+        <v>272.5849275039148</v>
       </c>
       <c r="E41" t="n">
-        <v>473.7387084960938</v>
+        <v>273.8537292480469</v>
       </c>
       <c r="F41" t="n">
-        <v>23727700</v>
+        <v>50409100</v>
       </c>
     </row>
     <row r="42">
@@ -6290,19 +6330,19 @@
         <v>46007</v>
       </c>
       <c r="B42" t="n">
-        <v>470.8353364785088</v>
+        <v>272.5649667835892</v>
       </c>
       <c r="C42" t="n">
-        <v>476.8017293564801</v>
+        <v>275.2424541197232</v>
       </c>
       <c r="D42" t="n">
-        <v>469.8076832860371</v>
+        <v>271.535930878856</v>
       </c>
       <c r="E42" t="n">
-        <v>475.3051452636719</v>
+        <v>274.353271484375</v>
       </c>
       <c r="F42" t="n">
-        <v>20705600</v>
+        <v>37648600</v>
       </c>
     </row>
     <row r="43">
@@ -6310,19 +6350,19 @@
         <v>46008</v>
       </c>
       <c r="B43" t="n">
-        <v>475.8239455574328</v>
+        <v>274.7529265191943</v>
       </c>
       <c r="C43" t="n">
-        <v>478.9069051052783</v>
+        <v>275.9018453851206</v>
       </c>
       <c r="D43" t="n">
-        <v>473.9182915104317</v>
+        <v>271.3860817211021</v>
       </c>
       <c r="E43" t="n">
-        <v>475.0357360839844</v>
+        <v>271.5858764648438</v>
       </c>
       <c r="F43" t="n">
-        <v>24527200</v>
+        <v>50138700</v>
       </c>
     </row>
     <row r="44">
@@ -6330,19 +6370,19 @@
         <v>46009</v>
       </c>
       <c r="B44" t="n">
-        <v>477.1010453906704</v>
+        <v>273.3542023206923</v>
       </c>
       <c r="C44" t="n">
-        <v>488.4850656489584</v>
+        <v>273.374203136776</v>
       </c>
       <c r="D44" t="n">
-        <v>476.8017407441929</v>
+        <v>266.7004552212896</v>
       </c>
       <c r="E44" t="n">
-        <v>482.8778686523438</v>
+        <v>271.935546875</v>
       </c>
       <c r="F44" t="n">
-        <v>28573500</v>
+        <v>51630700</v>
       </c>
     </row>
     <row r="45">
@@ -6350,19 +6390,19 @@
         <v>46010</v>
       </c>
       <c r="B45" t="n">
-        <v>486.2501387748106</v>
+        <v>271.8955859651445</v>
       </c>
       <c r="C45" t="n">
-        <v>486.7390436209232</v>
+        <v>274.343307881706</v>
       </c>
       <c r="D45" t="n">
-        <v>481.39123391446</v>
+        <v>269.6476892826471</v>
       </c>
       <c r="E45" t="n">
-        <v>484.8134460449219</v>
+        <v>273.4141845703125</v>
       </c>
       <c r="F45" t="n">
-        <v>70836100</v>
+        <v>144632000</v>
       </c>
     </row>
     <row r="46">
@@ -6370,19 +6410,19 @@
         <v>46013</v>
       </c>
       <c r="B46" t="n">
-        <v>485.0129839081317</v>
+        <v>272.6048920133635</v>
       </c>
       <c r="C46" t="n">
-        <v>487.6170561484318</v>
+        <v>273.6239579412959</v>
       </c>
       <c r="D46" t="n">
-        <v>481.5908021440126</v>
+        <v>270.2571133897843</v>
       </c>
       <c r="E46" t="n">
-        <v>483.8157348632812</v>
+        <v>270.7166748046875</v>
       </c>
       <c r="F46" t="n">
-        <v>16963000</v>
+        <v>36571800</v>
       </c>
     </row>
     <row r="47">
@@ -6390,19 +6430,19 @@
         <v>46014</v>
       </c>
       <c r="B47" t="n">
-        <v>483.8755963136496</v>
+        <v>270.5868091030317</v>
       </c>
       <c r="C47" t="n">
-        <v>486.7190818282799</v>
+        <v>272.2452609569047</v>
       </c>
       <c r="D47" t="n">
-        <v>483.6361221459561</v>
+        <v>269.3080068949797</v>
       </c>
       <c r="E47" t="n">
-        <v>485.7413330078125</v>
+        <v>272.1053771972656</v>
       </c>
       <c r="F47" t="n">
-        <v>14683600</v>
+        <v>29642000</v>
       </c>
     </row>
     <row r="48">
@@ -6410,19 +6450,19 @@
         <v>46015</v>
       </c>
       <c r="B48" t="n">
-        <v>484.5739628623746</v>
+        <v>272.085389177814</v>
       </c>
       <c r="C48" t="n">
-        <v>488.0460488858467</v>
+        <v>275.1724967178681</v>
       </c>
       <c r="D48" t="n">
-        <v>483.7258924615979</v>
+        <v>271.9455359163183</v>
       </c>
       <c r="E48" t="n">
-        <v>486.9086303710938</v>
+        <v>273.5540161132812</v>
       </c>
       <c r="F48" t="n">
-        <v>5855900</v>
+        <v>17910600</v>
       </c>
     </row>
     <row r="49">
@@ -6430,19 +6470,19 @@
         <v>46017</v>
       </c>
       <c r="B49" t="n">
-        <v>485.601642461088</v>
+        <v>273.9037084592662</v>
       </c>
       <c r="C49" t="n">
-        <v>487.0084352251927</v>
+        <v>275.1125687682936</v>
       </c>
       <c r="D49" t="n">
-        <v>484.8533503811227</v>
+        <v>272.6049054553</v>
       </c>
       <c r="E49" t="n">
-        <v>486.599365234375</v>
+        <v>273.1444091796875</v>
       </c>
       <c r="F49" t="n">
-        <v>8842200</v>
+        <v>21521800</v>
       </c>
     </row>
     <row r="50">
@@ -6450,19 +6490,19 @@
         <v>46020</v>
       </c>
       <c r="B50" t="n">
-        <v>483.7558335295542</v>
+        <v>272.4350823114352</v>
       </c>
       <c r="C50" t="n">
-        <v>487.2379065999322</v>
+        <v>274.103504063292</v>
       </c>
       <c r="D50" t="n">
-        <v>483.0773893732932</v>
+        <v>272.0954038139857</v>
       </c>
       <c r="E50" t="n">
-        <v>485.9907531738281</v>
+        <v>273.5040893554688</v>
       </c>
       <c r="F50" t="n">
-        <v>10893400</v>
+        <v>23715200</v>
       </c>
     </row>
     <row r="51">
@@ -6470,19 +6510,19 @@
         <v>46021</v>
       </c>
       <c r="B51" t="n">
-        <v>484.8234150126488</v>
+        <v>272.5549704076282</v>
       </c>
       <c r="C51" t="n">
-        <v>488.5648753746365</v>
+        <v>273.8237722152489</v>
       </c>
       <c r="D51" t="n">
-        <v>484.3944015320139</v>
+        <v>272.0254670796708</v>
       </c>
       <c r="E51" t="n">
-        <v>486.3699035644531</v>
+        <v>272.82470703125</v>
       </c>
       <c r="F51" t="n">
-        <v>13944500</v>
+        <v>22139600</v>
       </c>
     </row>
     <row r="52">
@@ -6490,19 +6530,19 @@
         <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>486.7290680267604</v>
+        <v>272.804725327361</v>
       </c>
       <c r="C52" t="n">
-        <v>487.0284031238816</v>
+        <v>273.4241408373621</v>
       </c>
       <c r="D52" t="n">
-        <v>482.1993981667827</v>
+        <v>271.4959524300237</v>
       </c>
       <c r="E52" t="n">
-        <v>482.5186767578125</v>
+        <v>271.6058349609375</v>
       </c>
       <c r="F52" t="n">
-        <v>15601600</v>
+        <v>27293600</v>
       </c>
     </row>
     <row r="53">
@@ -6510,19 +6550,19 @@
         <v>46024</v>
       </c>
       <c r="B53" t="n">
-        <v>483.2869444224563</v>
+        <v>272.0054842546519</v>
       </c>
       <c r="C53" t="n">
-        <v>483.5563186075122</v>
+        <v>277.5802543100492</v>
       </c>
       <c r="D53" t="n">
-        <v>469.0893385249197</v>
+        <v>268.7485221479618</v>
       </c>
       <c r="E53" t="n">
-        <v>471.8630065917969</v>
+        <v>270.7566528320312</v>
       </c>
       <c r="F53" t="n">
-        <v>25571600</v>
+        <v>37838100</v>
       </c>
     </row>
     <row r="54">
@@ -6530,19 +6570,19 @@
         <v>46027</v>
       </c>
       <c r="B54" t="n">
-        <v>472.9804293228547</v>
+        <v>270.387007446453</v>
       </c>
       <c r="C54" t="n">
-        <v>474.9858617296903</v>
+        <v>271.2561892506844</v>
       </c>
       <c r="D54" t="n">
-        <v>468.4308161640092</v>
+        <v>265.8912142612155</v>
       </c>
       <c r="E54" t="n">
-        <v>471.773193359375</v>
+        <v>267.0101623535156</v>
       </c>
       <c r="F54" t="n">
-        <v>25250300</v>
+        <v>45647200</v>
       </c>
     </row>
     <row r="55">
@@ -6550,19 +6590,19 @@
         <v>46028</v>
       </c>
       <c r="B55" t="n">
-        <v>472.7210225701547</v>
+        <v>266.7503924619391</v>
       </c>
       <c r="C55" t="n">
-        <v>477.6497753472042</v>
+        <v>267.2998660934885</v>
       </c>
       <c r="D55" t="n">
-        <v>468.6802576477938</v>
+        <v>261.8749496989937</v>
       </c>
       <c r="E55" t="n">
-        <v>477.4203186035156</v>
+        <v>262.1147155761719</v>
       </c>
       <c r="F55" t="n">
-        <v>23037700</v>
+        <v>52352100</v>
       </c>
     </row>
     <row r="56">
@@ -6570,19 +6610,19 @@
         <v>46029</v>
       </c>
       <c r="B56" t="n">
-        <v>478.6674756822987</v>
+        <v>262.9539513876447</v>
       </c>
       <c r="C56" t="n">
-        <v>488.5848422406915</v>
+        <v>263.4334831315393</v>
       </c>
       <c r="D56" t="n">
-        <v>476.861599942913</v>
+        <v>259.5671060011504</v>
       </c>
       <c r="E56" t="n">
-        <v>482.3690185546875</v>
+        <v>260.0866088867188</v>
       </c>
       <c r="F56" t="n">
-        <v>25564200</v>
+        <v>48309800</v>
       </c>
     </row>
     <row r="57">
@@ -6590,19 +6630,19 @@
         <v>46030</v>
       </c>
       <c r="B57" t="n">
-        <v>480.1440867981462</v>
+        <v>256.7797203952787</v>
       </c>
       <c r="C57" t="n">
-        <v>481.5608665012806</v>
+        <v>259.0476178563403</v>
       </c>
       <c r="D57" t="n">
-        <v>474.7763335277468</v>
+        <v>255.4609622909548</v>
       </c>
       <c r="E57" t="n">
-        <v>477.0212097167969</v>
+        <v>258.7978515625</v>
       </c>
       <c r="F57" t="n">
-        <v>18162600</v>
+        <v>50419300</v>
       </c>
     </row>
     <row r="58">
@@ -6610,19 +6650,19 @@
         <v>46031</v>
       </c>
       <c r="B58" t="n">
-        <v>472.9804540365218</v>
+        <v>258.8377955175017</v>
       </c>
       <c r="C58" t="n">
-        <v>478.7273469366413</v>
+        <v>259.9667440583015</v>
       </c>
       <c r="D58" t="n">
-        <v>471.1247042989064</v>
+        <v>255.9804837142826</v>
       </c>
       <c r="E58" t="n">
-        <v>478.1885681152344</v>
+        <v>259.1275329589844</v>
       </c>
       <c r="F58" t="n">
-        <v>18491000</v>
+        <v>39997000</v>
       </c>
     </row>
     <row r="59">
@@ -6630,19 +6670,19 @@
         <v>46034</v>
       </c>
       <c r="B59" t="n">
-        <v>475.5845048686955</v>
+        <v>258.9177364764393</v>
       </c>
       <c r="C59" t="n">
-        <v>479.894643901475</v>
+        <v>261.055720113683</v>
       </c>
       <c r="D59" t="n">
-        <v>474.5967386659474</v>
+        <v>256.5599267903311</v>
       </c>
       <c r="E59" t="n">
-        <v>476.0933227539062</v>
+        <v>260.0067138671875</v>
       </c>
       <c r="F59" t="n">
-        <v>23519900</v>
+        <v>45263800</v>
       </c>
     </row>
     <row r="60">
@@ -6650,19 +6690,19 @@
         <v>46035</v>
       </c>
       <c r="B60" t="n">
-        <v>473.5990225282599</v>
+        <v>258.4781303943212</v>
       </c>
       <c r="C60" t="n">
-        <v>474.6965236309785</v>
+        <v>261.5652379723006</v>
       </c>
       <c r="D60" t="n">
-        <v>464.888922501957</v>
+        <v>258.148452318208</v>
       </c>
       <c r="E60" t="n">
-        <v>469.5981750488281</v>
+        <v>260.8059387207031</v>
       </c>
       <c r="F60" t="n">
-        <v>28545800</v>
+        <v>45730800</v>
       </c>
     </row>
     <row r="61">
@@ -6670,19 +6710,19 @@
         <v>46036</v>
       </c>
       <c r="B61" t="n">
-        <v>465.3977566654985</v>
+        <v>259.247418118488</v>
       </c>
       <c r="C61" t="n">
-        <v>467.1338149970701</v>
+        <v>261.5752571005171</v>
       </c>
       <c r="D61" t="n">
-        <v>456.1289340170423</v>
+        <v>256.4700180914029</v>
       </c>
       <c r="E61" t="n">
-        <v>458.3338928222656</v>
+        <v>259.7169799804688</v>
       </c>
       <c r="F61" t="n">
-        <v>28184300</v>
+        <v>40019400</v>
       </c>
     </row>
     <row r="62">
@@ -6690,19 +6730,19 @@
         <v>46037</v>
       </c>
       <c r="B62" t="n">
-        <v>463.0630900555096</v>
+        <v>260.4063187564486</v>
       </c>
       <c r="C62" t="n">
-        <v>463.1927988881192</v>
+        <v>260.7959687899761</v>
       </c>
       <c r="D62" t="n">
-        <v>454.8618076165624</v>
+        <v>256.8096782083212</v>
       </c>
       <c r="E62" t="n">
-        <v>455.6200866699219</v>
+        <v>257.9685974121094</v>
       </c>
       <c r="F62" t="n">
-        <v>23225800</v>
+        <v>39388600</v>
       </c>
     </row>
     <row r="63">
@@ -6710,19 +6750,19 @@
         <v>46038</v>
       </c>
       <c r="B63" t="n">
-        <v>456.7873986695315</v>
+        <v>257.6589020182799</v>
       </c>
       <c r="C63" t="n">
-        <v>462.1352085061545</v>
+        <v>258.6579671912775</v>
       </c>
       <c r="D63" t="n">
-        <v>455.4404972994736</v>
+        <v>254.6916772349149</v>
       </c>
       <c r="E63" t="n">
-        <v>458.8127746582031</v>
+        <v>255.2911224365234</v>
       </c>
       <c r="F63" t="n">
-        <v>34246700</v>
+        <v>72142800</v>
       </c>
     </row>
     <row r="64">
@@ -6730,19 +6770,19 @@
         <v>46042</v>
       </c>
       <c r="B64" t="n">
-        <v>450.1924514863621</v>
+        <v>252.4937373957159</v>
       </c>
       <c r="C64" t="n">
-        <v>455.7597309230742</v>
+        <v>254.5518092169813</v>
       </c>
       <c r="D64" t="n">
-        <v>448.2568669541529</v>
+        <v>243.1924430560896</v>
       </c>
       <c r="E64" t="n">
-        <v>453.4849243164062</v>
+        <v>246.4693756103516</v>
       </c>
       <c r="F64" t="n">
-        <v>26130000</v>
+        <v>80267500</v>
       </c>
     </row>
     <row r="65">
@@ -6750,19 +6790,19 @@
         <v>46043</v>
       </c>
       <c r="B65" t="n">
-        <v>451.5693196059127</v>
+        <v>248.4675090444481</v>
       </c>
       <c r="C65" t="n">
-        <v>451.6591109990197</v>
+        <v>251.3248360900433</v>
       </c>
       <c r="D65" t="n">
-        <v>437.6810056251358</v>
+        <v>244.9507953165175</v>
       </c>
       <c r="E65" t="n">
-        <v>443.0986328125</v>
+        <v>247.4184875488281</v>
       </c>
       <c r="F65" t="n">
-        <v>37980500</v>
+        <v>54641700</v>
       </c>
     </row>
     <row r="66">
@@ -6770,19 +6810,19 @@
         <v>46044</v>
       </c>
       <c r="B66" t="n">
-        <v>446.600636936346</v>
+        <v>248.9670398844787</v>
       </c>
       <c r="C66" t="n">
-        <v>451.8087507279656</v>
+        <v>250.7653602579427</v>
       </c>
       <c r="D66" t="n">
-        <v>443.6873036586902</v>
+        <v>247.9180183962477</v>
       </c>
       <c r="E66" t="n">
-        <v>450.1126403808594</v>
+        <v>248.1178436279297</v>
       </c>
       <c r="F66" t="n">
-        <v>25349400</v>
+        <v>39708300</v>
       </c>
     </row>
     <row r="67">
@@ -6790,19 +6830,19 @@
         <v>46045</v>
       </c>
       <c r="B67" t="n">
-        <v>450.8409629929935</v>
+        <v>247.0888078223564</v>
       </c>
       <c r="C67" t="n">
-        <v>470.0271819611143</v>
+        <v>249.176850391454</v>
       </c>
       <c r="D67" t="n">
-        <v>449.5040181949105</v>
+        <v>244.4512611104123</v>
       </c>
       <c r="E67" t="n">
-        <v>464.888916015625</v>
+        <v>247.8081207275391</v>
       </c>
       <c r="F67" t="n">
-        <v>38000200</v>
+        <v>41689000</v>
       </c>
     </row>
     <row r="68">
@@ -6810,19 +6850,19 @@
         <v>46048</v>
       </c>
       <c r="B68" t="n">
-        <v>464.2503622118351</v>
+        <v>251.2449001563489</v>
       </c>
       <c r="C68" t="n">
-        <v>473.1700058760031</v>
+        <v>256.320152957849</v>
       </c>
       <c r="D68" t="n">
-        <v>460.9479024031912</v>
+        <v>249.5664780183616</v>
       </c>
       <c r="E68" t="n">
-        <v>469.2090454101562</v>
+        <v>255.1712341308594</v>
       </c>
       <c r="F68" t="n">
-        <v>29291200</v>
+        <v>55969200</v>
       </c>
     </row>
     <row r="69">
@@ -6830,19 +6870,19 @@
         <v>46049</v>
       </c>
       <c r="B69" t="n">
-        <v>472.62128861771</v>
+        <v>258.9277169221324</v>
       </c>
       <c r="C69" t="n">
-        <v>481.7703893732875</v>
+        <v>261.705116697089</v>
       </c>
       <c r="D69" t="n">
-        <v>472.0825097961169</v>
+        <v>257.9685924683142</v>
       </c>
       <c r="E69" t="n">
-        <v>479.485595703125</v>
+        <v>258.0285339355469</v>
       </c>
       <c r="F69" t="n">
-        <v>29213900</v>
+        <v>49648300</v>
       </c>
     </row>
     <row r="70">
@@ -6850,19 +6890,19 @@
         <v>46050</v>
       </c>
       <c r="B70" t="n">
-        <v>482.1095916405993</v>
+        <v>257.409147241713</v>
       </c>
       <c r="C70" t="n">
-        <v>482.6383834693597</v>
+        <v>258.6180076181917</v>
       </c>
       <c r="D70" t="n">
-        <v>476.9114647448887</v>
+        <v>254.2720830679268</v>
       </c>
       <c r="E70" t="n">
-        <v>480.533203125</v>
+        <v>256.2002868652344</v>
       </c>
       <c r="F70" t="n">
-        <v>36875400</v>
+        <v>41288000</v>
       </c>
     </row>
     <row r="71">
@@ -6870,19 +6910,19 @@
         <v>46051</v>
       </c>
       <c r="B71" t="n">
-        <v>438.9880283656418</v>
+        <v>257.758806680925</v>
       </c>
       <c r="C71" t="n">
-        <v>441.4923222419712</v>
+        <v>259.4072580677027</v>
       </c>
       <c r="D71" t="n">
-        <v>420.0612263501361</v>
+        <v>254.1721664792058</v>
       </c>
       <c r="E71" t="n">
-        <v>432.5128173828125</v>
+        <v>258.0385437011719</v>
       </c>
       <c r="F71" t="n">
-        <v>128855300</v>
+        <v>67253000</v>
       </c>
     </row>
     <row r="72">
@@ -6890,19 +6930,19 @@
         <v>46052</v>
       </c>
       <c r="B72" t="n">
-        <v>438.1699022937122</v>
+        <v>254.9314433110553</v>
       </c>
       <c r="C72" t="n">
-        <v>438.5989157576861</v>
+        <v>261.6551472598355</v>
       </c>
       <c r="D72" t="n">
-        <v>425.4788680207893</v>
+        <v>251.9442331321547</v>
       </c>
       <c r="E72" t="n">
-        <v>429.3101196289062</v>
+        <v>259.2374267578125</v>
       </c>
       <c r="F72" t="n">
-        <v>58566800</v>
+        <v>92443400</v>
       </c>
     </row>
     <row r="73">
@@ -6910,19 +6950,19 @@
         <v>46055</v>
       </c>
       <c r="B73" t="n">
-        <v>429.2602343395754</v>
+        <v>259.7869174093499</v>
       </c>
       <c r="C73" t="n">
-        <v>429.7590957240154</v>
+        <v>270.2371306501278</v>
       </c>
       <c r="D73" t="n">
-        <v>421.28843915961</v>
+        <v>258.9676766447768</v>
       </c>
       <c r="E73" t="n">
-        <v>422.4058837890625</v>
+        <v>269.7575988769531</v>
       </c>
       <c r="F73" t="n">
-        <v>42219900</v>
+        <v>73913400</v>
       </c>
     </row>
     <row r="74">
@@ -6930,19 +6970,19 @@
         <v>46056</v>
       </c>
       <c r="B74" t="n">
-        <v>421.0489834358989</v>
+        <v>268.9483513556569</v>
       </c>
       <c r="C74" t="n">
-        <v>421.0888704228976</v>
+        <v>271.6258386480508</v>
       </c>
       <c r="D74" t="n">
-        <v>407.6296003977664</v>
+        <v>267.3598109321867</v>
       </c>
       <c r="E74" t="n">
-        <v>410.2735595703125</v>
+        <v>269.2280883789062</v>
       </c>
       <c r="F74" t="n">
-        <v>61424100</v>
+        <v>64394700</v>
       </c>
     </row>
     <row r="75">
@@ -6950,19 +6990,19 @@
         <v>46057</v>
       </c>
       <c r="B75" t="n">
-        <v>410.0640575889883</v>
+        <v>272.03545112075</v>
       </c>
       <c r="C75" t="n">
-        <v>418.8440057668918</v>
+        <v>278.6892285045384</v>
       </c>
       <c r="D75" t="n">
-        <v>408.3080557741746</v>
+        <v>272.03545112075</v>
       </c>
       <c r="E75" t="n">
-        <v>413.2467956542969</v>
+        <v>276.2315063476562</v>
       </c>
       <c r="F75" t="n">
-        <v>45012400</v>
+        <v>90545700</v>
       </c>
     </row>
     <row r="76">
@@ -6970,19 +7010,19 @@
         <v>46058</v>
       </c>
       <c r="B76" t="n">
-        <v>406.5121603821183</v>
+        <v>277.8699949435269</v>
       </c>
       <c r="C76" t="n">
-        <v>407.3701873334875</v>
+        <v>279.2387093202658</v>
       </c>
       <c r="D76" t="n">
-        <v>391.4265972483441</v>
+        <v>272.9745818081728</v>
       </c>
       <c r="E76" t="n">
-        <v>392.7735290527344</v>
+        <v>275.6520690917969</v>
       </c>
       <c r="F76" t="n">
-        <v>66289200</v>
+        <v>52977400</v>
       </c>
     </row>
     <row r="77">
@@ -6990,19 +7030,19 @@
         <v>46059</v>
       </c>
       <c r="B77" t="n">
-        <v>398.2609865133262</v>
+        <v>276.8609202349588</v>
       </c>
       <c r="C77" t="n">
-        <v>400.875015135043</v>
+        <v>280.6473855638201</v>
       </c>
       <c r="D77" t="n">
-        <v>392.0252195920243</v>
+        <v>276.6710954236804</v>
       </c>
       <c r="E77" t="n">
-        <v>400.2265014648438</v>
+        <v>277.8599853515625</v>
       </c>
       <c r="F77" t="n">
-        <v>53515300</v>
+        <v>50453400</v>
       </c>
     </row>
     <row r="78">
@@ -7010,19 +7050,19 @@
         <v>46062</v>
       </c>
       <c r="B78" t="n">
-        <v>403.9280678877113</v>
+        <v>277.9100036621094</v>
       </c>
       <c r="C78" t="n">
-        <v>413.9452129833927</v>
+        <v>278.2000122070312</v>
       </c>
       <c r="D78" t="n">
-        <v>399.9571203178888</v>
+        <v>271.7000122070312</v>
       </c>
       <c r="E78" t="n">
-        <v>412.6581420898438</v>
+        <v>274.6199951171875</v>
       </c>
       <c r="F78" t="n">
-        <v>45480500</v>
+        <v>44623400</v>
       </c>
     </row>
     <row r="79">
@@ -7030,19 +7070,19 @@
         <v>46063</v>
       </c>
       <c r="B79" t="n">
-        <v>418.6644027817824</v>
+        <v>274.8900146484375</v>
       </c>
       <c r="C79" t="n">
-        <v>422.7151545880433</v>
+        <v>275.3699951171875</v>
       </c>
       <c r="D79" t="n">
-        <v>411.76017861217</v>
+        <v>272.9400024414062</v>
       </c>
       <c r="E79" t="n">
-        <v>412.328857421875</v>
+        <v>273.6799926757812</v>
       </c>
       <c r="F79" t="n">
-        <v>44857900</v>
+        <v>34376900</v>
       </c>
     </row>
     <row r="80">
@@ -7050,19 +7090,19 @@
         <v>46064</v>
       </c>
       <c r="B80" t="n">
-        <v>415.2322299614449</v>
+        <v>274.7000122070312</v>
       </c>
       <c r="C80" t="n">
-        <v>415.5115911022014</v>
+        <v>280.1799926757812</v>
       </c>
       <c r="D80" t="n">
-        <v>400.096793508188</v>
+        <v>274.4500122070312</v>
       </c>
       <c r="E80" t="n">
-        <v>403.4491271972656</v>
+        <v>275.5</v>
       </c>
       <c r="F80" t="n">
-        <v>42491000</v>
+        <v>51931300</v>
       </c>
     </row>
     <row r="81">
@@ -7070,19 +7110,19 @@
         <v>46065</v>
       </c>
       <c r="B81" t="n">
-        <v>404.0777037056333</v>
+        <v>275.5899963378906</v>
       </c>
       <c r="C81" t="n">
-        <v>405.2749831551046</v>
+        <v>275.7200012207031</v>
       </c>
       <c r="D81" t="n">
-        <v>397.1036315998776</v>
+        <v>260.1799926757812</v>
       </c>
       <c r="E81" t="n">
-        <v>400.9248962402344</v>
+        <v>261.7300109863281</v>
       </c>
       <c r="F81" t="n">
-        <v>40802400</v>
+        <v>81077200</v>
       </c>
     </row>
     <row r="82">
@@ -7090,19 +7130,19 @@
         <v>46066</v>
       </c>
       <c r="B82" t="n">
-        <v>403.528974460687</v>
+        <v>262.010009765625</v>
       </c>
       <c r="C82" t="n">
-        <v>404.6164885937555</v>
+        <v>262.2300109863281</v>
       </c>
       <c r="D82" t="n">
-        <v>397.1435245648219</v>
+        <v>255.4499969482422</v>
       </c>
       <c r="E82" t="n">
-        <v>400.4060974121094</v>
+        <v>255.7799987792969</v>
       </c>
       <c r="F82" t="n">
-        <v>34091600</v>
+        <v>56290700</v>
       </c>
     </row>
     <row r="83">
@@ -7110,19 +7150,19 @@
         <v>46070</v>
       </c>
       <c r="B83" t="n">
-        <v>398.3108793269315</v>
+        <v>258.0499877929688</v>
       </c>
       <c r="C83" t="n">
-        <v>399.6079067287359</v>
+        <v>266.2900085449219</v>
       </c>
       <c r="D83" t="n">
-        <v>393.6315571718042</v>
+        <v>255.5399932861328</v>
       </c>
       <c r="E83" t="n">
-        <v>395.9562377929688</v>
+        <v>263.8800048828125</v>
       </c>
       <c r="F83" t="n">
-        <v>32078800</v>
+        <v>58469100</v>
       </c>
     </row>
     <row r="84">
@@ -7130,19 +7170,19 @@
         <v>46071</v>
       </c>
       <c r="B84" t="n">
-        <v>397.2233488345012</v>
+        <v>263.6000061035156</v>
       </c>
       <c r="C84" t="n">
-        <v>401.6432531481791</v>
+        <v>266.8200073242188</v>
       </c>
       <c r="D84" t="n">
-        <v>395.4174731587443</v>
+        <v>262.4500122070312</v>
       </c>
       <c r="E84" t="n">
-        <v>398.6900024414062</v>
+        <v>264.3500061035156</v>
       </c>
       <c r="F84" t="n">
-        <v>23223400</v>
+        <v>34203300</v>
       </c>
     </row>
     <row r="85">
@@ -7150,19 +7190,19 @@
         <v>46072</v>
       </c>
       <c r="B85" t="n">
-        <v>400.6900024414062</v>
+        <v>262.6000061035156</v>
       </c>
       <c r="C85" t="n">
-        <v>404.4299926757812</v>
+        <v>264.4800109863281</v>
       </c>
       <c r="D85" t="n">
-        <v>396.6700134277344</v>
+        <v>260.0499877929688</v>
       </c>
       <c r="E85" t="n">
-        <v>398.4599914550781</v>
+        <v>260.5799865722656</v>
       </c>
       <c r="F85" t="n">
-        <v>28234000</v>
+        <v>30845300</v>
       </c>
     </row>
     <row r="86">
@@ -7170,19 +7210,19 @@
         <v>46073</v>
       </c>
       <c r="B86" t="n">
-        <v>396.1099853515625</v>
+        <v>258.9700012207031</v>
       </c>
       <c r="C86" t="n">
-        <v>400.1199951171875</v>
+        <v>264.75</v>
       </c>
       <c r="D86" t="n">
-        <v>395.1600036621094</v>
+        <v>258.1600036621094</v>
       </c>
       <c r="E86" t="n">
-        <v>397.2300109863281</v>
+        <v>264.5799865722656</v>
       </c>
       <c r="F86" t="n">
-        <v>34015200</v>
+        <v>42070500</v>
       </c>
     </row>
     <row r="87">
@@ -7190,19 +7230,19 @@
         <v>46076</v>
       </c>
       <c r="B87" t="n">
-        <v>395</v>
+        <v>263.489990234375</v>
       </c>
       <c r="C87" t="n">
-        <v>395.3599853515625</v>
+        <v>269.4299926757812</v>
       </c>
       <c r="D87" t="n">
-        <v>383.1000061035156</v>
+        <v>263.3800048828125</v>
       </c>
       <c r="E87" t="n">
-        <v>384.4700012207031</v>
+        <v>266.1799926757812</v>
       </c>
       <c r="F87" t="n">
-        <v>43238300</v>
+        <v>37308200</v>
       </c>
     </row>
     <row r="88">
@@ -7210,19 +7250,19 @@
         <v>46077</v>
       </c>
       <c r="B88" t="n">
-        <v>384.1400146484375</v>
+        <v>267.8599853515625</v>
       </c>
       <c r="C88" t="n">
-        <v>389.3599853515625</v>
+        <v>274.8900146484375</v>
       </c>
       <c r="D88" t="n">
-        <v>381.7099914550781</v>
+        <v>267.7099914550781</v>
       </c>
       <c r="E88" t="n">
-        <v>389</v>
+        <v>272.1400146484375</v>
       </c>
       <c r="F88" t="n">
-        <v>33884700</v>
+        <v>47014600</v>
       </c>
     </row>
     <row r="89">
@@ -7230,19 +7270,19 @@
         <v>46078</v>
       </c>
       <c r="B89" t="n">
-        <v>390.5299987792969</v>
+        <v>271.7799987792969</v>
       </c>
       <c r="C89" t="n">
-        <v>401.4700012207031</v>
+        <v>274.9400024414062</v>
       </c>
       <c r="D89" t="n">
-        <v>390.1600036621094</v>
+        <v>271.0499877929688</v>
       </c>
       <c r="E89" t="n">
-        <v>400.6000061035156</v>
+        <v>274.2300109863281</v>
       </c>
       <c r="F89" t="n">
-        <v>43625500</v>
+        <v>33714300</v>
       </c>
     </row>
     <row r="90">
@@ -7250,19 +7290,19 @@
         <v>46079</v>
       </c>
       <c r="B90" t="n">
-        <v>404.7099914550781</v>
+        <v>274.9500122070312</v>
       </c>
       <c r="C90" t="n">
-        <v>407.489990234375</v>
+        <v>276.1099853515625</v>
       </c>
       <c r="D90" t="n">
-        <v>398.739990234375</v>
+        <v>270.7999877929688</v>
       </c>
       <c r="E90" t="n">
-        <v>401.7200012207031</v>
+        <v>272.9500122070312</v>
       </c>
       <c r="F90" t="n">
-        <v>34405900</v>
+        <v>32345100</v>
       </c>
     </row>
     <row r="91">
@@ -7270,19 +7310,19 @@
         <v>46080</v>
       </c>
       <c r="B91" t="n">
-        <v>390.8800048828125</v>
+        <v>272.8099975585938</v>
       </c>
       <c r="C91" t="n">
-        <v>396.8200073242188</v>
+        <v>272.8099975585938</v>
       </c>
       <c r="D91" t="n">
-        <v>389.8800048828125</v>
+        <v>262.8900146484375</v>
       </c>
       <c r="E91" t="n">
-        <v>392.739990234375</v>
+        <v>264.1799926757812</v>
       </c>
       <c r="F91" t="n">
-        <v>51367200</v>
+        <v>72366500</v>
       </c>
     </row>
     <row r="92">
@@ -7290,19 +7330,19 @@
         <v>46083</v>
       </c>
       <c r="B92" t="n">
-        <v>392.8599853515625</v>
+        <v>262.4100036621094</v>
       </c>
       <c r="C92" t="n">
-        <v>401.1900024414062</v>
+        <v>266.5299987792969</v>
       </c>
       <c r="D92" t="n">
-        <v>390.6300048828125</v>
+        <v>260.2000122070312</v>
       </c>
       <c r="E92" t="n">
-        <v>398.5499877929688</v>
+        <v>264.7200012207031</v>
       </c>
       <c r="F92" t="n">
-        <v>35474900</v>
+        <v>41827900</v>
       </c>
     </row>
     <row r="93">
@@ -7310,19 +7350,19 @@
         <v>46084</v>
       </c>
       <c r="B93" t="n">
-        <v>393.1400146484375</v>
+        <v>263.4800109863281</v>
       </c>
       <c r="C93" t="n">
-        <v>406.7000122070312</v>
+        <v>265.5599975585938</v>
       </c>
       <c r="D93" t="n">
-        <v>392.6700134277344</v>
+        <v>260.1300048828125</v>
       </c>
       <c r="E93" t="n">
-        <v>403.9299926757812</v>
+        <v>263.75</v>
       </c>
       <c r="F93" t="n">
-        <v>38199200</v>
+        <v>38568900</v>
       </c>
     </row>
     <row r="94">
@@ -7330,19 +7370,19 @@
         <v>46085</v>
       </c>
       <c r="B94" t="n">
-        <v>401.2699890136719</v>
+        <v>264.6499938964844</v>
       </c>
       <c r="C94" t="n">
-        <v>411.0299987792969</v>
+        <v>266.1499938964844</v>
       </c>
       <c r="D94" t="n">
-        <v>400.3099975585938</v>
+        <v>261.4200134277344</v>
       </c>
       <c r="E94" t="n">
-        <v>405.2000122070312</v>
+        <v>262.5199890136719</v>
       </c>
       <c r="F94" t="n">
-        <v>35808000</v>
+        <v>39803100</v>
       </c>
     </row>
     <row r="95">
@@ -7350,19 +7390,19 @@
         <v>46086</v>
       </c>
       <c r="B95" t="n">
-        <v>404.4200134277344</v>
+        <v>260.7900085449219</v>
       </c>
       <c r="C95" t="n">
-        <v>411.6099853515625</v>
+        <v>261.5599975585938</v>
       </c>
       <c r="D95" t="n">
-        <v>404.3999938964844</v>
+        <v>257.25</v>
       </c>
       <c r="E95" t="n">
-        <v>410.6799926757812</v>
+        <v>260.2900085449219</v>
       </c>
       <c r="F95" t="n">
-        <v>39001300</v>
+        <v>49658600</v>
       </c>
     </row>
     <row r="96">
@@ -7370,19 +7410,19 @@
         <v>46087</v>
       </c>
       <c r="B96" t="n">
-        <v>409.2000122070312</v>
+        <v>258.6300048828125</v>
       </c>
       <c r="C96" t="n">
-        <v>413.0499877929688</v>
+        <v>258.7699890136719</v>
       </c>
       <c r="D96" t="n">
-        <v>408.510009765625</v>
+        <v>254.3699951171875</v>
       </c>
       <c r="E96" t="n">
-        <v>408.9599914550781</v>
+        <v>257.4599914550781</v>
       </c>
       <c r="F96" t="n">
-        <v>31123900</v>
+        <v>41120000</v>
       </c>
     </row>
     <row r="97">
@@ -7390,19 +7430,19 @@
         <v>46090</v>
       </c>
       <c r="B97" t="n">
-        <v>404.9200134277344</v>
+        <v>255.6900024414062</v>
       </c>
       <c r="C97" t="n">
-        <v>410.2099914550781</v>
+        <v>261.1499938964844</v>
       </c>
       <c r="D97" t="n">
-        <v>403.5</v>
+        <v>253.6799926757812</v>
       </c>
       <c r="E97" t="n">
-        <v>409.4100036621094</v>
+        <v>259.8800048828125</v>
       </c>
       <c r="F97" t="n">
-        <v>30131900</v>
+        <v>38218500</v>
       </c>
     </row>
     <row r="98">
@@ -7410,19 +7450,19 @@
         <v>46091</v>
       </c>
       <c r="B98" t="n">
-        <v>410.0299987792969</v>
+        <v>257.6499938964844</v>
       </c>
       <c r="C98" t="n">
-        <v>410.2000122070312</v>
+        <v>262.4800109863281</v>
       </c>
       <c r="D98" t="n">
-        <v>402.9299926757812</v>
+        <v>256.9500122070312</v>
       </c>
       <c r="E98" t="n">
-        <v>405.760009765625</v>
+        <v>260.8299865722656</v>
       </c>
       <c r="F98" t="n">
-        <v>31706400</v>
+        <v>30590800</v>
       </c>
     </row>
     <row r="99">
@@ -7430,19 +7470,19 @@
         <v>46092</v>
       </c>
       <c r="B99" t="n">
-        <v>405.5700073242188</v>
+        <v>261.0899963378906</v>
       </c>
       <c r="C99" t="n">
-        <v>409.010009765625</v>
+        <v>262.1300048828125</v>
       </c>
       <c r="D99" t="n">
-        <v>401.5899963378906</v>
+        <v>259.5499877929688</v>
       </c>
       <c r="E99" t="n">
-        <v>404.8800048828125</v>
+        <v>260.8099975585938</v>
       </c>
       <c r="F99" t="n">
-        <v>25512100</v>
+        <v>26218900</v>
       </c>
     </row>
     <row r="100">
@@ -7450,19 +7490,19 @@
         <v>46093</v>
       </c>
       <c r="B100" t="n">
-        <v>404.6300048828125</v>
+        <v>258.6600036621094</v>
       </c>
       <c r="C100" t="n">
-        <v>406.1199951171875</v>
+        <v>258.9500122070312</v>
       </c>
       <c r="D100" t="n">
-        <v>401.7099914550781</v>
+        <v>254.1799926757812</v>
       </c>
       <c r="E100" t="n">
-        <v>401.8599853515625</v>
+        <v>255.7599945068359</v>
       </c>
       <c r="F100" t="n">
-        <v>27263900</v>
+        <v>40794000</v>
       </c>
     </row>
     <row r="101">
@@ -7470,19 +7510,19 @@
         <v>46094</v>
       </c>
       <c r="B101" t="n">
-        <v>401</v>
+        <v>255.4799957275391</v>
       </c>
       <c r="C101" t="n">
-        <v>404.7999877929688</v>
+        <v>256.3299865722656</v>
       </c>
       <c r="D101" t="n">
-        <v>394.25</v>
+        <v>249.5200042724609</v>
       </c>
       <c r="E101" t="n">
-        <v>395.5499877929688</v>
+        <v>250.1199951171875</v>
       </c>
       <c r="F101" t="n">
-        <v>26848000</v>
+        <v>36930000</v>
       </c>
     </row>
     <row r="102">
@@ -7490,19 +7530,19 @@
         <v>46097</v>
       </c>
       <c r="B102" t="n">
-        <v>398.0700073242188</v>
+        <v>252.1100006103516</v>
       </c>
       <c r="C102" t="n">
-        <v>400.6300048828125</v>
+        <v>253.8899993896484</v>
       </c>
       <c r="D102" t="n">
-        <v>394.7900085449219</v>
+        <v>249.8800048828125</v>
       </c>
       <c r="E102" t="n">
-        <v>399.9500122070312</v>
+        <v>252.8200073242188</v>
       </c>
       <c r="F102" t="n">
-        <v>27733700</v>
+        <v>32074200</v>
       </c>
     </row>
     <row r="103">
@@ -7510,19 +7550,19 @@
         <v>46098</v>
       </c>
       <c r="B103" t="n">
-        <v>400.2699890136719</v>
+        <v>252.9600067138672</v>
       </c>
       <c r="C103" t="n">
-        <v>404.3999938964844</v>
+        <v>255.1300048828125</v>
       </c>
       <c r="D103" t="n">
-        <v>397.75</v>
+        <v>252.1799926757812</v>
       </c>
       <c r="E103" t="n">
-        <v>399.4100036621094</v>
+        <v>254.2299957275391</v>
       </c>
       <c r="F103" t="n">
-        <v>26228300</v>
+        <v>32361600</v>
       </c>
     </row>
     <row r="104">
@@ -7530,19 +7570,19 @@
         <v>46099</v>
       </c>
       <c r="B104" t="n">
-        <v>397.1300048828125</v>
+        <v>252.6300048828125</v>
       </c>
       <c r="C104" t="n">
-        <v>398</v>
+        <v>254.9400024414062</v>
       </c>
       <c r="D104" t="n">
-        <v>391</v>
+        <v>249</v>
       </c>
       <c r="E104" t="n">
-        <v>391.7900085449219</v>
+        <v>249.9400024414062</v>
       </c>
       <c r="F104" t="n">
-        <v>25908500</v>
+        <v>35757900</v>
       </c>
     </row>
     <row r="105">
@@ -7550,19 +7590,19 @@
         <v>46100</v>
       </c>
       <c r="B105" t="n">
-        <v>390.1000061035156</v>
+        <v>249.3999938964844</v>
       </c>
       <c r="C105" t="n">
-        <v>392.489990234375</v>
+        <v>251.8300018310547</v>
       </c>
       <c r="D105" t="n">
-        <v>387.0599975585938</v>
+        <v>247.3000030517578</v>
       </c>
       <c r="E105" t="n">
-        <v>389.0199890136719</v>
+        <v>248.9600067138672</v>
       </c>
       <c r="F105" t="n">
-        <v>25138800</v>
+        <v>34864100</v>
       </c>
     </row>
     <row r="106">
@@ -7570,19 +7610,19 @@
         <v>46101</v>
       </c>
       <c r="B106" t="n">
-        <v>386.7900085449219</v>
+        <v>247.9799957275391</v>
       </c>
       <c r="C106" t="n">
-        <v>387</v>
+        <v>249.1999969482422</v>
       </c>
       <c r="D106" t="n">
-        <v>380.1199951171875</v>
+        <v>246</v>
       </c>
       <c r="E106" t="n">
-        <v>381.8699951171875</v>
+        <v>247.9900054931641</v>
       </c>
       <c r="F106" t="n">
-        <v>50853200</v>
+        <v>88331100</v>
       </c>
     </row>
     <row r="107">
@@ -7590,19 +7630,19 @@
         <v>46104</v>
       </c>
       <c r="B107" t="n">
-        <v>383.8999938964844</v>
+        <v>253.9700012207031</v>
       </c>
       <c r="C107" t="n">
-        <v>387.2099914550781</v>
+        <v>254.6000061035156</v>
       </c>
       <c r="D107" t="n">
-        <v>381.6799926757812</v>
+        <v>250.2799987792969</v>
       </c>
       <c r="E107" t="n">
-        <v>383</v>
+        <v>251.4900054931641</v>
       </c>
       <c r="F107" t="n">
-        <v>29680100</v>
+        <v>40546100</v>
       </c>
     </row>
     <row r="108">
@@ -7610,19 +7650,19 @@
         <v>46105</v>
       </c>
       <c r="B108" t="n">
-        <v>382.3599853515625</v>
+        <v>250.3500061035156</v>
       </c>
       <c r="C108" t="n">
-        <v>382.4700012207031</v>
+        <v>254.8300018310547</v>
       </c>
       <c r="D108" t="n">
-        <v>371.8500061035156</v>
+        <v>249.5500030517578</v>
       </c>
       <c r="E108" t="n">
-        <v>372.739990234375</v>
+        <v>251.6399993896484</v>
       </c>
       <c r="F108" t="n">
-        <v>42733600</v>
+        <v>45152300</v>
       </c>
     </row>
     <row r="109">
@@ -7630,19 +7670,19 @@
         <v>46106</v>
       </c>
       <c r="B109" t="n">
-        <v>376.9200134277344</v>
+        <v>254.1000061035156</v>
       </c>
       <c r="C109" t="n">
-        <v>377.0599975585938</v>
+        <v>255</v>
       </c>
       <c r="D109" t="n">
-        <v>369.6300048828125</v>
+        <v>251.6000061035156</v>
       </c>
       <c r="E109" t="n">
-        <v>371.0400085449219</v>
+        <v>252.6199951171875</v>
       </c>
       <c r="F109" t="n">
-        <v>31181200</v>
+        <v>28476700</v>
       </c>
     </row>
     <row r="110">
@@ -7650,19 +7690,19 @@
         <v>46107</v>
       </c>
       <c r="B110" t="n">
-        <v>370.8200073242188</v>
+        <v>252.1199951171875</v>
       </c>
       <c r="C110" t="n">
-        <v>374.7200012207031</v>
+        <v>257</v>
       </c>
       <c r="D110" t="n">
-        <v>365.1900024414062</v>
+        <v>250.7700042724609</v>
       </c>
       <c r="E110" t="n">
-        <v>365.9700012207031</v>
+        <v>252.8899993896484</v>
       </c>
       <c r="F110" t="n">
-        <v>36836600</v>
+        <v>41796700</v>
       </c>
     </row>
     <row r="111">
@@ -7670,19 +7710,19 @@
         <v>46108</v>
       </c>
       <c r="B111" t="n">
-        <v>361.8999938964844</v>
+        <v>253.8999938964844</v>
       </c>
       <c r="C111" t="n">
-        <v>362.4500122070312</v>
+        <v>255.4900054931641</v>
       </c>
       <c r="D111" t="n">
-        <v>356.510009765625</v>
+        <v>248.0700073242188</v>
       </c>
       <c r="E111" t="n">
-        <v>356.7699890136719</v>
+        <v>248.8000030517578</v>
       </c>
       <c r="F111" t="n">
-        <v>37883400</v>
+        <v>47900000</v>
       </c>
     </row>
     <row r="112">
@@ -7690,19 +7730,19 @@
         <v>46111</v>
       </c>
       <c r="B112" t="n">
-        <v>361.8999938964844</v>
+        <v>250.0700073242188</v>
       </c>
       <c r="C112" t="n">
-        <v>365.3599853515625</v>
+        <v>250.8699951171875</v>
       </c>
       <c r="D112" t="n">
-        <v>356.2799987792969</v>
+        <v>245.5099945068359</v>
       </c>
       <c r="E112" t="n">
-        <v>358.9599914550781</v>
+        <v>246.6300048828125</v>
       </c>
       <c r="F112" t="n">
-        <v>44797000</v>
+        <v>39446200</v>
       </c>
     </row>
     <row r="113">
@@ -7710,19 +7750,19 @@
         <v>46112</v>
       </c>
       <c r="B113" t="n">
-        <v>364.5499877929688</v>
+        <v>247.9100036621094</v>
       </c>
       <c r="C113" t="n">
-        <v>372.8999938964844</v>
+        <v>255.4799957275391</v>
       </c>
       <c r="D113" t="n">
-        <v>363.0700073242188</v>
+        <v>247.1000061035156</v>
       </c>
       <c r="E113" t="n">
-        <v>370.1700134277344</v>
+        <v>253.7899932861328</v>
       </c>
       <c r="F113" t="n">
-        <v>45244400</v>
+        <v>49598100</v>
       </c>
     </row>
     <row r="114">
@@ -7730,19 +7770,19 @@
         <v>46113</v>
       </c>
       <c r="B114" t="n">
-        <v>373.489990234375</v>
+        <v>254.0800018310547</v>
       </c>
       <c r="C114" t="n">
-        <v>373.989990234375</v>
+        <v>256.1799926757812</v>
       </c>
       <c r="D114" t="n">
-        <v>368.2000122070312</v>
+        <v>253.3300018310547</v>
       </c>
       <c r="E114" t="n">
-        <v>369.3699951171875</v>
+        <v>255.6300048828125</v>
       </c>
       <c r="F114" t="n">
-        <v>29417200</v>
+        <v>40059400</v>
       </c>
     </row>
     <row r="115">
@@ -7750,19 +7790,19 @@
         <v>46114</v>
       </c>
       <c r="B115" t="n">
-        <v>367.2099914550781</v>
+        <v>254.1999969482422</v>
       </c>
       <c r="C115" t="n">
-        <v>373.6400146484375</v>
+        <v>256.1300048828125</v>
       </c>
       <c r="D115" t="n">
-        <v>364.1499938964844</v>
+        <v>250.6499938964844</v>
       </c>
       <c r="E115" t="n">
-        <v>373.4599914550781</v>
+        <v>255.9199981689453</v>
       </c>
       <c r="F115" t="n">
-        <v>24099100</v>
+        <v>31289400</v>
       </c>
     </row>
     <row r="116">
@@ -7770,19 +7810,19 @@
         <v>46118</v>
       </c>
       <c r="B116" t="n">
-        <v>373.489990234375</v>
+        <v>256.510009765625</v>
       </c>
       <c r="C116" t="n">
-        <v>373.7300109863281</v>
+        <v>262.1600036621094</v>
       </c>
       <c r="D116" t="n">
-        <v>369.5</v>
+        <v>256.4599914550781</v>
       </c>
       <c r="E116" t="n">
-        <v>372.8800048828125</v>
+        <v>258.8599853515625</v>
       </c>
       <c r="F116" t="n">
-        <v>16146600</v>
+        <v>29329900</v>
       </c>
     </row>
     <row r="117">
@@ -7790,19 +7830,19 @@
         <v>46119</v>
       </c>
       <c r="B117" t="n">
-        <v>370.3399963378906</v>
+        <v>256.1600036621094</v>
       </c>
       <c r="C117" t="n">
-        <v>372.4500122070312</v>
+        <v>256.2000122070312</v>
       </c>
       <c r="D117" t="n">
-        <v>366.5599975585938</v>
+        <v>245.6999969482422</v>
       </c>
       <c r="E117" t="n">
-        <v>372.2900085449219</v>
+        <v>253.5</v>
       </c>
       <c r="F117" t="n">
-        <v>21443300</v>
+        <v>62148000</v>
       </c>
     </row>
     <row r="118">
@@ -7810,19 +7850,19 @@
         <v>46120</v>
       </c>
       <c r="B118" t="n">
-        <v>384.9800109863281</v>
+        <v>258.4500122070312</v>
       </c>
       <c r="C118" t="n">
-        <v>385</v>
+        <v>259.75</v>
       </c>
       <c r="D118" t="n">
-        <v>371.4100036621094</v>
+        <v>256.5299987792969</v>
       </c>
       <c r="E118" t="n">
-        <v>374.3299865722656</v>
+        <v>258.8999938964844</v>
       </c>
       <c r="F118" t="n">
-        <v>33064800</v>
+        <v>41032800</v>
       </c>
     </row>
     <row r="119">
@@ -7830,19 +7870,19 @@
         <v>46121</v>
       </c>
       <c r="B119" t="n">
-        <v>372.5</v>
+        <v>259</v>
       </c>
       <c r="C119" t="n">
-        <v>373.5</v>
+        <v>261.1199951171875</v>
       </c>
       <c r="D119" t="n">
-        <v>367.0499877929688</v>
+        <v>256.0700073242188</v>
       </c>
       <c r="E119" t="n">
-        <v>373.0700073242188</v>
+        <v>260.489990234375</v>
       </c>
       <c r="F119" t="n">
-        <v>30435300</v>
+        <v>28121600</v>
       </c>
     </row>
     <row r="120">
@@ -7850,19 +7890,19 @@
         <v>46122</v>
       </c>
       <c r="B120" t="n">
-        <v>372.9800109863281</v>
+        <v>259.9800109863281</v>
       </c>
       <c r="C120" t="n">
-        <v>375.6400146484375</v>
+        <v>262.1900024414062</v>
       </c>
       <c r="D120" t="n">
-        <v>370.0299987792969</v>
+        <v>259.0199890136719</v>
       </c>
       <c r="E120" t="n">
-        <v>370.8699951171875</v>
+        <v>260.4800109863281</v>
       </c>
       <c r="F120" t="n">
-        <v>28111100</v>
+        <v>31291500</v>
       </c>
     </row>
     <row r="121">
@@ -7870,19 +7910,19 @@
         <v>46125</v>
       </c>
       <c r="B121" t="n">
-        <v>373.6099853515625</v>
+        <v>259.7300109863281</v>
       </c>
       <c r="C121" t="n">
-        <v>384.5400085449219</v>
+        <v>260.1799926757812</v>
       </c>
       <c r="D121" t="n">
-        <v>371.0199890136719</v>
+        <v>256.6600036621094</v>
       </c>
       <c r="E121" t="n">
-        <v>384.3699951171875</v>
+        <v>259.2000122070312</v>
       </c>
       <c r="F121" t="n">
-        <v>35745800</v>
+        <v>36234700</v>
       </c>
     </row>
     <row r="122">
@@ -7890,19 +7930,19 @@
         <v>46126</v>
       </c>
       <c r="B122" t="n">
-        <v>387.9200134277344</v>
+        <v>259.25</v>
       </c>
       <c r="C122" t="n">
-        <v>394.6900024414062</v>
+        <v>261.9299926757812</v>
       </c>
       <c r="D122" t="n">
-        <v>386.5199890136719</v>
+        <v>257.1900024414062</v>
       </c>
       <c r="E122" t="n">
-        <v>393.1099853515625</v>
+        <v>258.8299865722656</v>
       </c>
       <c r="F122" t="n">
-        <v>37504500</v>
+        <v>48370700</v>
       </c>
     </row>
     <row r="123">
@@ -7910,19 +7950,19 @@
         <v>46127</v>
       </c>
       <c r="B123" t="n">
-        <v>398</v>
+        <v>258.1600036621094</v>
       </c>
       <c r="C123" t="n">
-        <v>414.3699951171875</v>
+        <v>266.5599975585938</v>
       </c>
       <c r="D123" t="n">
-        <v>396.7300109863281</v>
+        <v>257.8099975585938</v>
       </c>
       <c r="E123" t="n">
-        <v>411.2200012207031</v>
+        <v>266.4299926757812</v>
       </c>
       <c r="F123" t="n">
-        <v>44793300</v>
+        <v>49913500</v>
       </c>
     </row>
     <row r="124">
@@ -7930,19 +7970,39 @@
         <v>46128</v>
       </c>
       <c r="B124" t="n">
-        <v>419.989990234375</v>
+        <v>266.7999877929688</v>
       </c>
       <c r="C124" t="n">
-        <v>420.5599975585938</v>
+        <v>267.1600036621094</v>
       </c>
       <c r="D124" t="n">
-        <v>412.1400146484375</v>
+        <v>261.2699890136719</v>
       </c>
       <c r="E124" t="n">
-        <v>418.6799926757812</v>
+        <v>263.3999938964844</v>
       </c>
       <c r="F124" t="n">
-        <v>25774334</v>
+        <v>43323100</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B125" t="n">
+        <v>266.9599914550781</v>
+      </c>
+      <c r="C125" t="n">
+        <v>272.2999877929688</v>
+      </c>
+      <c r="D125" t="n">
+        <v>266.7200012207031</v>
+      </c>
+      <c r="E125" t="n">
+        <v>270.2300109863281</v>
+      </c>
+      <c r="F125" t="n">
+        <v>61314800</v>
       </c>
     </row>
   </sheetData>
@@ -7956,7 +8016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10428,7 +10488,7 @@
         <v>248.5</v>
       </c>
       <c r="F123" t="n">
-        <v>42961200</v>
+        <v>43045200</v>
       </c>
     </row>
     <row r="124">
@@ -10436,7 +10496,7 @@
         <v>46128</v>
       </c>
       <c r="B124" t="n">
-        <v>248.9799957275391</v>
+        <v>248.5099945068359</v>
       </c>
       <c r="C124" t="n">
         <v>250</v>
@@ -10445,10 +10505,30 @@
         <v>244.1999969482422</v>
       </c>
       <c r="E124" t="n">
-        <v>249.1600952148438</v>
+        <v>249.6999969482422</v>
       </c>
       <c r="F124" t="n">
-        <v>25859542</v>
+        <v>41895700</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B125" t="n">
+        <v>254.9900054931641</v>
+      </c>
+      <c r="C125" t="n">
+        <v>256.1799926757812</v>
+      </c>
+      <c r="D125" t="n">
+        <v>250.1100006103516</v>
+      </c>
+      <c r="E125" t="n">
+        <v>250.5599975585938</v>
+      </c>
+      <c r="F125" t="n">
+        <v>51897500</v>
       </c>
     </row>
   </sheetData>
@@ -10462,7 +10542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12934,7 +13014,7 @@
         <v>671.5800170898438</v>
       </c>
       <c r="F123" t="n">
-        <v>14927200</v>
+        <v>14952600</v>
       </c>
     </row>
     <row r="124">
@@ -12945,16 +13025,36 @@
         <v>675.989990234375</v>
       </c>
       <c r="C124" t="n">
-        <v>677.4099731445312</v>
+        <v>677.5800170898438</v>
       </c>
       <c r="D124" t="n">
         <v>667.75</v>
       </c>
       <c r="E124" t="n">
-        <v>674.3599853515625</v>
+        <v>676.8699951171875</v>
       </c>
       <c r="F124" t="n">
-        <v>5337240</v>
+        <v>9544800</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B125" t="n">
+        <v>678.5999755859375</v>
+      </c>
+      <c r="C125" t="n">
+        <v>691.52001953125</v>
+      </c>
+      <c r="D125" t="n">
+        <v>675.1300048828125</v>
+      </c>
+      <c r="E125" t="n">
+        <v>688.5499877929688</v>
+      </c>
+      <c r="F125" t="n">
+        <v>16246200</v>
       </c>
     </row>
   </sheetData>
